--- a/dist/Module_Declarative_Fluxuri.xlsx
+++ b/dist/Module_Declarative_Fluxuri.xlsx
@@ -54,6 +54,15 @@
     <sheet name="Reguli_LEASING_FIN" sheetId="45" state="visible" r:id="rId45"/>
     <sheet name="Jurnale_LEASING_FIN" sheetId="46" state="visible" r:id="rId46"/>
     <sheet name="NotaExport_LEASING_FIN" sheetId="47" state="visible" r:id="rId47"/>
+    <sheet name="Declarații_SALARII" sheetId="48" state="visible" r:id="rId48"/>
+    <sheet name="Reguli_SALARII" sheetId="49" state="visible" r:id="rId49"/>
+    <sheet name="Jurnale_SALARII" sheetId="50" state="visible" r:id="rId50"/>
+    <sheet name="NotaExport_SALARII" sheetId="51" state="visible" r:id="rId51"/>
+    <sheet name="Declarații_DECONT" sheetId="52" state="visible" r:id="rId52"/>
+    <sheet name="Reguli_DECONT" sheetId="53" state="visible" r:id="rId53"/>
+    <sheet name="Registru_DECONT" sheetId="54" state="visible" r:id="rId54"/>
+    <sheet name="Jurnale_DECONT" sheetId="55" state="visible" r:id="rId55"/>
+    <sheet name="NotaExport_DECONT" sheetId="56" state="visible" r:id="rId56"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1" refMode="A1" iterate="0" iterateCount="100" iterateDelta="0.0001"/>
@@ -479,8 +488,8 @@
     <xf numFmtId="0" fontId="9" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -4214,7 +4223,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:C20"/>
+  <dimension ref="A1:C24"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="36" customWidth="1" style="39" min="1" max="1"/>
@@ -4392,6 +4401,66 @@
       <c r="C20" s="51" t="inlineStr">
         <is>
           <t>art. 28 alin. (14) CF — NU se cumulează cu limitarea de 50%</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="49" t="inlineStr">
+        <is>
+          <t>CAS — pensie (pe brut)</t>
+        </is>
+      </c>
+      <c r="B21" s="50" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="C21" s="51" t="inlineStr">
+        <is>
+          <t>art. 138 CF</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="49" t="inlineStr">
+        <is>
+          <t>CASS — sănătate (pe brut + tichete)</t>
+        </is>
+      </c>
+      <c r="B22" s="50" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="C22" s="51" t="inlineStr">
+        <is>
+          <t>art. 156 CF — tichetele intră în bază, dar NU în baza CAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="49" t="inlineStr">
+        <is>
+          <t>Impozit pe venit (pe venit net + tichete)</t>
+        </is>
+      </c>
+      <c r="B23" s="50" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="C23" s="51" t="inlineStr">
+        <is>
+          <t>art. 78 CF</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="49" t="inlineStr">
+        <is>
+          <t>CAM — asigurare de muncă (pe brut)</t>
+        </is>
+      </c>
+      <c r="B24" s="50" t="n">
+        <v>0.0225</v>
+      </c>
+      <c r="C24" s="51" t="inlineStr">
+        <is>
+          <t>art. 220^3 CF — cheltuiala angajatorului, nu reținere</t>
         </is>
       </c>
     </row>
@@ -5509,9 +5578,9 @@
         <v>0</v>
       </c>
       <c r="D28" s="65" t="n"/>
-      <c r="E28" s="65">
+      <c r="E28" s="65" t="str">
         <f>IF(OR(Declarații_NEUTRALIZARE!B13="BUNURI",Declarații_NEUTRALIZARE!B13="SERVICII"),Declarații_NEUTRALIZARE!B34,0)</f>
-        <v/>
+        <v>4427</v>
       </c>
       <c r="F28" s="66">
         <f>IF(OR(Declarații_NEUTRALIZARE!B13="BUNURI",Declarații_NEUTRALIZARE!B13="SERVICII"),Declarații_NEUTRALIZARE!B28,0)</f>
@@ -6951,9 +7020,9 @@
         <v>0</v>
       </c>
       <c r="D7" s="65" t="n"/>
-      <c r="E7" s="65">
+      <c r="E7" s="65" t="str">
         <f>Declarații_AMANUNT!B23</f>
-        <v/>
+        <v>378.AM.21</v>
       </c>
       <c r="F7" s="66">
         <f>Declarații_AMANUNT!B15</f>
@@ -6975,9 +7044,9 @@
         <v>0</v>
       </c>
       <c r="D8" s="65" t="n"/>
-      <c r="E8" s="65">
+      <c r="E8" s="65" t="str">
         <f>Declarații_AMANUNT!B24</f>
-        <v/>
+        <v>4428.AM</v>
       </c>
       <c r="F8" s="66">
         <f>Declarații_AMANUNT!B17</f>
@@ -7322,9 +7391,9 @@
         <v>0</v>
       </c>
       <c r="D27" s="65" t="n"/>
-      <c r="E27" s="65">
+      <c r="E27" s="65" t="str">
         <f>Declarații_AMANUNT!B29</f>
-        <v/>
+        <v>4427</v>
       </c>
       <c r="F27" s="66">
         <f>Declarații_AMANUNT!B17</f>
@@ -7434,9 +7503,9 @@
         <v>0</v>
       </c>
       <c r="D33" s="65" t="n"/>
-      <c r="E33" s="65">
+      <c r="E33" s="65" t="str">
         <f>Declarații_AMANUNT!B31</f>
-        <v/>
+        <v>4423</v>
       </c>
       <c r="F33" s="66">
         <f>Declarații_AMANUNT!B17-Declarații_AMANUNT!B19</f>
@@ -8673,7 +8742,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:H27"/>
+  <dimension ref="A1:H26"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="8" customWidth="1" style="39" min="1" max="1"/>
@@ -8851,27 +8920,27 @@
       </c>
       <c r="D8" s="56" t="inlineStr">
         <is>
-          <t>Lunar + plăți</t>
+          <t>Lunar, pe registru de angajați</t>
         </is>
       </c>
       <c r="E8" s="56" t="inlineStr">
         <is>
-          <t>Brut, Tichete, Avans, Angajat, Luna — vezi fișierul Salarii AS Kids</t>
+          <t>Brut, tichete, avans, pe angajat; cotele CAS/CASS/impozit/CAM</t>
         </is>
       </c>
       <c r="F8" s="56" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Fără deducere personală și fără facilități sectoriale — vezi Reguli, tabelul C</t>
         </is>
       </c>
       <c r="G8" s="56" t="inlineStr">
         <is>
-          <t>B1 Costuri; B2 Plăți net+taxe; B3 Tichete — EXEMPLU EXTERN complet</t>
+          <t>B1 Plata avansului; B2 Costurile lunii; B3 Plăți (net, taxe, CAM)</t>
         </is>
       </c>
       <c r="H8" s="56" t="inlineStr">
         <is>
-          <t>EXEMPLU EXTERN</t>
+          <t>IMPLEMENTAT</t>
         </is>
       </c>
     </row>
@@ -8888,7 +8957,7 @@
       </c>
       <c r="C9" s="56" t="inlineStr">
         <is>
-          <t>F-35 + deplasări</t>
+          <t>F-35</t>
         </is>
       </c>
       <c r="D9" s="56" t="inlineStr">
@@ -8898,22 +8967,22 @@
       </c>
       <c r="E9" s="56" t="inlineStr">
         <is>
-          <t>Linii decont, Titular, Avans, Cotă TVA — vezi Deconturi AS Kids</t>
+          <t>Linii de decont (furnizor, sumă, natură, tip document, CUI), avans, cote</t>
         </is>
       </c>
       <c r="F9" s="56" t="inlineStr">
         <is>
-          <t>Platitor TVA, % ded. vehicule</t>
+          <t>Plătitor de TVA; % deducere vehicule; matricea document × CUI</t>
         </is>
       </c>
       <c r="G9" s="56" t="inlineStr">
         <is>
-          <t>B1 Avans; B2 Cheltuieli; B3 Regularizare; B4 Plată — EXEMPLU EXTERN complet</t>
+          <t>B1 Avans; B2 Cheltuieli + TVA; B3 Regularizare avans; B4 Plată / restituire</t>
         </is>
       </c>
       <c r="H9" s="56" t="inlineStr">
         <is>
-          <t>EXEMPLU EXTERN</t>
+          <t>IMPLEMENTAT</t>
         </is>
       </c>
     </row>
@@ -8930,32 +8999,32 @@
       </c>
       <c r="C10" s="56" t="inlineStr">
         <is>
-          <t>F-26 + F-28 + reeval</t>
+          <t>F-50</t>
         </is>
       </c>
       <c r="D10" s="56" t="inlineStr">
         <is>
-          <t>Pe contract + lună</t>
+          <t>Pe contract + lunar</t>
         </is>
       </c>
       <c r="E10" s="56" t="inlineStr">
         <is>
-          <t>Contract, Scadențar, Regim vehicul, Curs BNR — vezi Template_leasing_financiar_auto</t>
+          <t>Valoare contract, avans, rată, dobândă, comision, CASCO, regim vehicul, durată</t>
         </is>
       </c>
       <c r="F10" s="56" t="inlineStr">
         <is>
-          <t>MIXT/EXCLUSIV/EXCEPTAT; Capitalizare vs Cheltuială TVA neded.</t>
+          <t>MIXT 50% / EXCLUSIV 100% / EXCEPTAT; capitalizare vs. cheltuială pentru TVA nededusă</t>
         </is>
       </c>
       <c r="G10" s="56" t="inlineStr">
         <is>
-          <t>B1–B7 pe momente — EXEMPLU EXTERN complet</t>
+          <t>B1 Avans; B2 TVA avans; B3 Intrare + 167; B4 Stingere avans; B5 Factura lunară; B6 Corecție TVA 50%; B7 Limitare 50% cheltuieli; B8 Amortizare</t>
         </is>
       </c>
       <c r="H10" s="56" t="inlineStr">
         <is>
-          <t>ÎNLOCUIT — vezi rândul MOD_LEASING_FIN implementat mai jos</t>
+          <t>IMPLEMENTAT</t>
         </is>
       </c>
     </row>
@@ -9295,86 +9364,44 @@
         </is>
       </c>
     </row>
-    <row r="20" ht="15" customHeight="1" s="40">
-      <c r="A20" s="57" t="inlineStr">
-        <is>
-          <t>NU</t>
-        </is>
-      </c>
-      <c r="B20" s="58" t="inlineStr">
-        <is>
-          <t>MOD_LEASING_FIN</t>
-        </is>
-      </c>
-      <c r="C20" s="58" t="inlineStr">
-        <is>
-          <t>F-50</t>
-        </is>
-      </c>
-      <c r="D20" s="58" t="inlineStr">
-        <is>
-          <t>Pe contract + lunar</t>
-        </is>
-      </c>
-      <c r="E20" s="58" t="inlineStr">
-        <is>
-          <t>Valoare contract, avans, rată, dobândă, comision, CASCO, regim vehicul, durată</t>
-        </is>
-      </c>
-      <c r="F20" s="58" t="inlineStr">
-        <is>
-          <t>MIXT 50% / EXCLUSIV 100% / EXCEPTAT; capitalizare vs. cheltuială pentru TVA nededusă</t>
-        </is>
-      </c>
-      <c r="G20" s="58" t="inlineStr">
-        <is>
-          <t>B1 Avans; B2 TVA avans; B3 Intrare + 167; B4 Stingere avans; B5 Factura lunară; B6 Corecție TVA 50%; B7 Limitare 50% cheltuieli; B8 Amortizare</t>
-        </is>
-      </c>
-      <c r="H20" s="58" t="inlineStr">
-        <is>
-          <t>IMPLEMENTAT</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="15" customHeight="1" s="40"/>
+    <row r="20" ht="15" customHeight="1" s="40"/>
+    <row r="21" ht="15" customHeight="1" s="40">
+      <c r="A21" s="42" t="inlineStr">
+        <is>
+          <t>REGULĂ DE SUMONARE</t>
+        </is>
+      </c>
+    </row>
     <row r="22" ht="15" customHeight="1" s="40">
-      <c r="A22" s="42" t="inlineStr">
-        <is>
-          <t>REGULĂ DE SUMONARE</t>
+      <c r="A22" s="43" t="inlineStr">
+        <is>
+          <t>1. În CatalogModule setezi Activ=DA doar pe modulele necesare lunii.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="43" t="inlineStr">
         <is>
-          <t>1. În CatalogModule setezi Activ=DA doar pe modulele necesare lunii.</t>
+          <t>2. Completezi variabilele din foaia Declarații_Modul (galben).</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="43" t="inlineStr">
         <is>
-          <t>2. Completezi variabilele din foaia Declarații_Modul (galben).</t>
+          <t>3. Jurnalele și NotaExport se populează automat doar pentru modulele active.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="43" t="inlineStr">
         <is>
-          <t>3. Jurnalele și NotaExport se populează automat doar pentru modulele active.</t>
+          <t>4. Verifici Check=0 pe fiecare bloc; filtrezi NotaExport pe Include=DA și imporți.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="43" t="inlineStr">
-        <is>
-          <t>4. Verifici Check=0 pe fiecare bloc; filtrezi NotaExport pe Include=DA și imporți.</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="43" t="inlineStr">
         <is>
           <t>Nu se creează conturi noi din modul — se folosesc doar conturile din politica declarată + planul de conturi pe rol.</t>
         </is>
@@ -9384,12 +9411,12 @@
   <mergeCells count="9">
     <mergeCell ref="A3:H3"/>
     <mergeCell ref="A26:H26"/>
+    <mergeCell ref="A21:H21"/>
     <mergeCell ref="A25:H25"/>
     <mergeCell ref="A24:H24"/>
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="A23:H23"/>
-    <mergeCell ref="A27:H27"/>
     <mergeCell ref="A22:H22"/>
   </mergeCells>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
@@ -9769,9 +9796,9 @@
         <v>0</v>
       </c>
       <c r="D21" s="65" t="n"/>
-      <c r="E21" s="65">
+      <c r="E21" s="65" t="str">
         <f>Declarații_TVA_INC!B28</f>
-        <v/>
+        <v>4428.INC</v>
       </c>
       <c r="F21" s="66">
         <f>Declarații_TVA_INC!B20</f>
@@ -18902,6 +18929,1370 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet48.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:L51"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" style="40" min="1" max="1"/>
+    <col width="22" customWidth="1" style="40" min="2" max="2"/>
+    <col width="12" customWidth="1" style="40" min="3" max="3"/>
+    <col width="12" customWidth="1" style="40" min="4" max="4"/>
+    <col width="12" customWidth="1" style="40" min="5" max="5"/>
+    <col width="12" customWidth="1" style="40" min="6" max="6"/>
+    <col width="12" customWidth="1" style="40" min="7" max="7"/>
+    <col width="13" customWidth="1" style="40" min="8" max="8"/>
+    <col width="12" customWidth="1" style="40" min="9" max="9"/>
+    <col width="13" customWidth="1" style="40" min="10" max="10"/>
+    <col width="14" customWidth="1" style="40" min="11" max="11"/>
+    <col width="12" customWidth="1" style="40" min="12" max="12"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="77" t="inlineStr">
+        <is>
+          <t>MOD_SALARII — Declarații (input)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="78" t="inlineStr">
+        <is>
+          <t>Completează galben: antetul, apoi brut / tichete / avans pe fiecare angajat. Restul coloanelor din registru sunt formule. Valorile implicite sunt cele din statul real din 31.07.2026, ca modulul să poată fi verificat contra lui.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="79" t="inlineStr">
+        <is>
+          <t>1. Antet</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="80" t="inlineStr">
+        <is>
+          <t>Societate</t>
+        </is>
+      </c>
+      <c r="B5" s="80" t="str">
+        <f>Parametri!B5</f>
+        <v>SC EXEMPLU SRL</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="80" t="inlineStr">
+        <is>
+          <t>CUI</t>
+        </is>
+      </c>
+      <c r="B6" s="80" t="str">
+        <f>Parametri!B6</f>
+        <v>RO00000000</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="80" t="inlineStr">
+        <is>
+          <t>Luna (AAAA-LL)</t>
+        </is>
+      </c>
+      <c r="B7" s="81" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="80" t="inlineStr">
+        <is>
+          <t>Data notei de costuri (ultima zi a lunii)</t>
+        </is>
+      </c>
+      <c r="B8" s="81" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="C8" s="78" t="inlineStr">
+        <is>
+          <t>Costurile se înregistrează la închiderea lunii</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="80" t="inlineStr">
+        <is>
+          <t>Data plăților (din extras)</t>
+        </is>
+      </c>
+      <c r="B9" s="81" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="C9" s="78" t="inlineStr">
+        <is>
+          <t>Netul și taxele se plătesc în luna următoare</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="80" t="inlineStr">
+        <is>
+          <t>Data plății avansului</t>
+        </is>
+      </c>
+      <c r="B10" s="81" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="79" t="inlineStr">
+        <is>
+          <t>2. Cote (din Parametri — se schimbă doar când se schimbă legea)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="80" t="inlineStr">
+        <is>
+          <t>CAS (pensie), pe brut</t>
+        </is>
+      </c>
+      <c r="B13" s="80">
+        <f>Parametri!B21</f>
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="80" t="inlineStr">
+        <is>
+          <t>CASS (sănătate), pe brut + tichete</t>
+        </is>
+      </c>
+      <c r="B14" s="80">
+        <f>Parametri!B22</f>
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="80" t="inlineStr">
+        <is>
+          <t>Impozit pe venit, pe venit net + tichete</t>
+        </is>
+      </c>
+      <c r="B15" s="80">
+        <f>Parametri!B23</f>
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="80" t="inlineStr">
+        <is>
+          <t>CAM (asigurare de muncă), pe brut</t>
+        </is>
+      </c>
+      <c r="B16" s="80">
+        <f>Parametri!B24</f>
+        <v>0.0225</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="79" t="inlineStr">
+        <is>
+          <t>3. Registrul angajaților</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="78" t="inlineStr">
+        <is>
+          <t>Coloanele F–L sunt formule. Rotunjirea e la leu, la fiecare pas — la fel ca în statul de plată; altfel totalurile diferă de cele din soft cu câțiva lei.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="82" t="inlineStr">
+        <is>
+          <t>Nr.</t>
+        </is>
+      </c>
+      <c r="B20" s="82" t="inlineStr">
+        <is>
+          <t>Angajat</t>
+        </is>
+      </c>
+      <c r="C20" s="82" t="inlineStr">
+        <is>
+          <t>Brut</t>
+        </is>
+      </c>
+      <c r="D20" s="82" t="inlineStr">
+        <is>
+          <t>Tichete</t>
+        </is>
+      </c>
+      <c r="E20" s="82" t="inlineStr">
+        <is>
+          <t>Avans</t>
+        </is>
+      </c>
+      <c r="F20" s="82" t="inlineStr">
+        <is>
+          <t>CAS</t>
+        </is>
+      </c>
+      <c r="G20" s="82" t="inlineStr">
+        <is>
+          <t>CASS</t>
+        </is>
+      </c>
+      <c r="H20" s="82" t="inlineStr">
+        <is>
+          <t>Venit net</t>
+        </is>
+      </c>
+      <c r="I20" s="82" t="inlineStr">
+        <is>
+          <t>Impozit</t>
+        </is>
+      </c>
+      <c r="J20" s="82" t="inlineStr">
+        <is>
+          <t>Salariu net</t>
+        </is>
+      </c>
+      <c r="K20" s="82" t="inlineStr">
+        <is>
+          <t>Total de plată</t>
+        </is>
+      </c>
+      <c r="L20" s="82" t="inlineStr">
+        <is>
+          <t>CAM</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="80" t="n">
+        <v>1</v>
+      </c>
+      <c r="B21" s="81" t="inlineStr">
+        <is>
+          <t>CHIRIACESCU DIANA-ELENA</t>
+        </is>
+      </c>
+      <c r="C21" s="81" t="n">
+        <v>24610</v>
+      </c>
+      <c r="D21" s="81" t="n">
+        <v>690</v>
+      </c>
+      <c r="E21" s="81" t="n">
+        <v>0</v>
+      </c>
+      <c r="F21" s="80">
+        <f>IF($C21="","",ROUND($C21*B13,0))</f>
+        <v>6153</v>
+      </c>
+      <c r="G21" s="80">
+        <f>IF($C21="","",ROUND(($C21+$D21)*B14,0))</f>
+        <v>2530</v>
+      </c>
+      <c r="H21" s="80">
+        <f>IF($C21="","",$C21-$F21-$G21)</f>
+        <v>15927</v>
+      </c>
+      <c r="I21" s="80">
+        <f>IF($C21="","",ROUND(($H21+$D21)*B15,0))</f>
+        <v>1662</v>
+      </c>
+      <c r="J21" s="80">
+        <f>IF($C21="","",$H21-$I21)</f>
+        <v>14265</v>
+      </c>
+      <c r="K21" s="80">
+        <f>IF($C21="","",$J21-$E21)</f>
+        <v>14265</v>
+      </c>
+      <c r="L21" s="80">
+        <f>IF($C21="","",ROUND($C21*B16,0))</f>
+        <v>554</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="80" t="n">
+        <v>2</v>
+      </c>
+      <c r="B22" s="81" t="inlineStr">
+        <is>
+          <t>NEAGU VLAD-FLORIAN</t>
+        </is>
+      </c>
+      <c r="C22" s="81" t="n">
+        <v>12513</v>
+      </c>
+      <c r="D22" s="81" t="n">
+        <v>480</v>
+      </c>
+      <c r="E22" s="81" t="n">
+        <v>0</v>
+      </c>
+      <c r="F22" s="80">
+        <f>IF($C22="","",ROUND($C22*B13,0))</f>
+        <v>3128</v>
+      </c>
+      <c r="G22" s="80">
+        <f>IF($C22="","",ROUND(($C22+$D22)*B14,0))</f>
+        <v>1299</v>
+      </c>
+      <c r="H22" s="80">
+        <f>IF($C22="","",$C22-$F22-$G22)</f>
+        <v>8086</v>
+      </c>
+      <c r="I22" s="80">
+        <f>IF($C22="","",ROUND(($H22+$D22)*B15,0))</f>
+        <v>857</v>
+      </c>
+      <c r="J22" s="80">
+        <f>IF($C22="","",$H22-$I22)</f>
+        <v>7229</v>
+      </c>
+      <c r="K22" s="80">
+        <f>IF($C22="","",$J22-$E22)</f>
+        <v>7229</v>
+      </c>
+      <c r="L22" s="80">
+        <f>IF($C22="","",ROUND($C22*B16,0))</f>
+        <v>282</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="80" t="n">
+        <v>3</v>
+      </c>
+      <c r="B23" s="81" t="inlineStr">
+        <is>
+          <t>POPESCU IOANA-GABRIELA</t>
+        </is>
+      </c>
+      <c r="C23" s="81" t="n">
+        <v>9627</v>
+      </c>
+      <c r="D23" s="81" t="n">
+        <v>690</v>
+      </c>
+      <c r="E23" s="81" t="n">
+        <v>0</v>
+      </c>
+      <c r="F23" s="80">
+        <f>IF($C23="","",ROUND($C23*B13,0))</f>
+        <v>2407</v>
+      </c>
+      <c r="G23" s="80">
+        <f>IF($C23="","",ROUND(($C23+$D23)*B14,0))</f>
+        <v>1032</v>
+      </c>
+      <c r="H23" s="80">
+        <f>IF($C23="","",$C23-$F23-$G23)</f>
+        <v>6188</v>
+      </c>
+      <c r="I23" s="80">
+        <f>IF($C23="","",ROUND(($H23+$D23)*B15,0))</f>
+        <v>688</v>
+      </c>
+      <c r="J23" s="80">
+        <f>IF($C23="","",$H23-$I23)</f>
+        <v>5500</v>
+      </c>
+      <c r="K23" s="80">
+        <f>IF($C23="","",$J23-$E23)</f>
+        <v>5500</v>
+      </c>
+      <c r="L23" s="80">
+        <f>IF($C23="","",ROUND($C23*B16,0))</f>
+        <v>217</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="80" t="n">
+        <v>4</v>
+      </c>
+      <c r="B24" s="81" t="inlineStr">
+        <is>
+          <t>SASCAU COSMIN-BOGDAN</t>
+        </is>
+      </c>
+      <c r="C24" s="81" t="n">
+        <v>24127</v>
+      </c>
+      <c r="D24" s="81" t="n">
+        <v>690</v>
+      </c>
+      <c r="E24" s="81" t="n">
+        <v>0</v>
+      </c>
+      <c r="F24" s="80">
+        <f>IF($C24="","",ROUND($C24*B13,0))</f>
+        <v>6032</v>
+      </c>
+      <c r="G24" s="80">
+        <f>IF($C24="","",ROUND(($C24+$D24)*B14,0))</f>
+        <v>2482</v>
+      </c>
+      <c r="H24" s="80">
+        <f>IF($C24="","",$C24-$F24-$G24)</f>
+        <v>15613</v>
+      </c>
+      <c r="I24" s="80">
+        <f>IF($C24="","",ROUND(($H24+$D24)*B15,0))</f>
+        <v>1630</v>
+      </c>
+      <c r="J24" s="80">
+        <f>IF($C24="","",$H24-$I24)</f>
+        <v>13983</v>
+      </c>
+      <c r="K24" s="80">
+        <f>IF($C24="","",$J24-$E24)</f>
+        <v>13983</v>
+      </c>
+      <c r="L24" s="80">
+        <f>IF($C24="","",ROUND($C24*B16,0))</f>
+        <v>543</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="80" t="n">
+        <v>5</v>
+      </c>
+      <c r="B25" s="81" t="inlineStr"/>
+      <c r="C25" s="81" t="n"/>
+      <c r="D25" s="81" t="n"/>
+      <c r="E25" s="81" t="n"/>
+      <c r="F25" s="80">
+        <f>IF($C25="","",ROUND($C25*B13,0))</f>
+        <v/>
+      </c>
+      <c r="G25" s="80">
+        <f>IF($C25="","",ROUND(($C25+$D25)*B14,0))</f>
+        <v/>
+      </c>
+      <c r="H25" s="80">
+        <f>IF($C25="","",$C25-$F25-$G25)</f>
+        <v/>
+      </c>
+      <c r="I25" s="80">
+        <f>IF($C25="","",ROUND(($H25+$D25)*B15,0))</f>
+        <v/>
+      </c>
+      <c r="J25" s="80">
+        <f>IF($C25="","",$H25-$I25)</f>
+        <v/>
+      </c>
+      <c r="K25" s="80">
+        <f>IF($C25="","",$J25-$E25)</f>
+        <v/>
+      </c>
+      <c r="L25" s="80">
+        <f>IF($C25="","",ROUND($C25*B16,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="80" t="n">
+        <v>6</v>
+      </c>
+      <c r="B26" s="81" t="inlineStr"/>
+      <c r="C26" s="81" t="n"/>
+      <c r="D26" s="81" t="n"/>
+      <c r="E26" s="81" t="n"/>
+      <c r="F26" s="80">
+        <f>IF($C26="","",ROUND($C26*B13,0))</f>
+        <v/>
+      </c>
+      <c r="G26" s="80">
+        <f>IF($C26="","",ROUND(($C26+$D26)*B14,0))</f>
+        <v/>
+      </c>
+      <c r="H26" s="80">
+        <f>IF($C26="","",$C26-$F26-$G26)</f>
+        <v/>
+      </c>
+      <c r="I26" s="80">
+        <f>IF($C26="","",ROUND(($H26+$D26)*B15,0))</f>
+        <v/>
+      </c>
+      <c r="J26" s="80">
+        <f>IF($C26="","",$H26-$I26)</f>
+        <v/>
+      </c>
+      <c r="K26" s="80">
+        <f>IF($C26="","",$J26-$E26)</f>
+        <v/>
+      </c>
+      <c r="L26" s="80">
+        <f>IF($C26="","",ROUND($C26*B16,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="80" t="n">
+        <v>7</v>
+      </c>
+      <c r="B27" s="81" t="inlineStr"/>
+      <c r="C27" s="81" t="n"/>
+      <c r="D27" s="81" t="n"/>
+      <c r="E27" s="81" t="n"/>
+      <c r="F27" s="80">
+        <f>IF($C27="","",ROUND($C27*B13,0))</f>
+        <v/>
+      </c>
+      <c r="G27" s="80">
+        <f>IF($C27="","",ROUND(($C27+$D27)*B14,0))</f>
+        <v/>
+      </c>
+      <c r="H27" s="80">
+        <f>IF($C27="","",$C27-$F27-$G27)</f>
+        <v/>
+      </c>
+      <c r="I27" s="80">
+        <f>IF($C27="","",ROUND(($H27+$D27)*B15,0))</f>
+        <v/>
+      </c>
+      <c r="J27" s="80">
+        <f>IF($C27="","",$H27-$I27)</f>
+        <v/>
+      </c>
+      <c r="K27" s="80">
+        <f>IF($C27="","",$J27-$E27)</f>
+        <v/>
+      </c>
+      <c r="L27" s="80">
+        <f>IF($C27="","",ROUND($C27*B16,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="80" t="n">
+        <v>8</v>
+      </c>
+      <c r="B28" s="81" t="inlineStr"/>
+      <c r="C28" s="81" t="n"/>
+      <c r="D28" s="81" t="n"/>
+      <c r="E28" s="81" t="n"/>
+      <c r="F28" s="80">
+        <f>IF($C28="","",ROUND($C28*B13,0))</f>
+        <v/>
+      </c>
+      <c r="G28" s="80">
+        <f>IF($C28="","",ROUND(($C28+$D28)*B14,0))</f>
+        <v/>
+      </c>
+      <c r="H28" s="80">
+        <f>IF($C28="","",$C28-$F28-$G28)</f>
+        <v/>
+      </c>
+      <c r="I28" s="80">
+        <f>IF($C28="","",ROUND(($H28+$D28)*B15,0))</f>
+        <v/>
+      </c>
+      <c r="J28" s="80">
+        <f>IF($C28="","",$H28-$I28)</f>
+        <v/>
+      </c>
+      <c r="K28" s="80">
+        <f>IF($C28="","",$J28-$E28)</f>
+        <v/>
+      </c>
+      <c r="L28" s="80">
+        <f>IF($C28="","",ROUND($C28*B16,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="82" t="inlineStr"/>
+      <c r="B29" s="82" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="C29" s="82">
+        <f>SUM(C21:C28)</f>
+        <v>70877</v>
+      </c>
+      <c r="D29" s="82">
+        <f>SUM(D21:D28)</f>
+        <v>2550</v>
+      </c>
+      <c r="E29" s="82">
+        <f>SUM(E21:E28)</f>
+        <v>0</v>
+      </c>
+      <c r="F29" s="82">
+        <f>SUM(F21:F28)</f>
+        <v>17720</v>
+      </c>
+      <c r="G29" s="82">
+        <f>SUM(G21:G28)</f>
+        <v>7343</v>
+      </c>
+      <c r="H29" s="82">
+        <f>SUM(H21:H28)</f>
+        <v>45814</v>
+      </c>
+      <c r="I29" s="82">
+        <f>SUM(I21:I28)</f>
+        <v>4837</v>
+      </c>
+      <c r="J29" s="82">
+        <f>SUM(J21:J28)</f>
+        <v>40977</v>
+      </c>
+      <c r="K29" s="82">
+        <f>SUM(K21:K28)</f>
+        <v>40977</v>
+      </c>
+      <c r="L29" s="82">
+        <f>SUM(L21:L28)</f>
+        <v>1596</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="79" t="inlineStr">
+        <is>
+          <t>4. Conturi</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="80" t="inlineStr">
+        <is>
+          <t>Cont cheltuieli cu salariile</t>
+        </is>
+      </c>
+      <c r="B32" s="81" t="n">
+        <v>641</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="80" t="inlineStr">
+        <is>
+          <t>Cont personal — salarii datorate</t>
+        </is>
+      </c>
+      <c r="B33" s="81" t="n">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="80" t="inlineStr">
+        <is>
+          <t>Cont avansuri acordate personalului</t>
+        </is>
+      </c>
+      <c r="B34" s="81" t="n">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="80" t="inlineStr">
+        <is>
+          <t>Cont CAS reținut</t>
+        </is>
+      </c>
+      <c r="B35" s="81" t="n">
+        <v>4315</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="80" t="inlineStr">
+        <is>
+          <t>Cont CASS reținut</t>
+        </is>
+      </c>
+      <c r="B36" s="81" t="n">
+        <v>4316</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="80" t="inlineStr">
+        <is>
+          <t>Cont impozit pe venit reținut</t>
+        </is>
+      </c>
+      <c r="B37" s="81" t="n">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="80" t="inlineStr">
+        <is>
+          <t>Cont cheltuieli cu CAM</t>
+        </is>
+      </c>
+      <c r="B38" s="81" t="n">
+        <v>646</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="80" t="inlineStr">
+        <is>
+          <t>Cont CAM datorat bugetului</t>
+        </is>
+      </c>
+      <c r="B39" s="81" t="n">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="80" t="inlineStr">
+        <is>
+          <t>Cont cheltuieli cu tichetele</t>
+        </is>
+      </c>
+      <c r="B40" s="81" t="n">
+        <v>642</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="80" t="inlineStr">
+        <is>
+          <t>Cont tichete în gestiune</t>
+        </is>
+      </c>
+      <c r="B41" s="81" t="n">
+        <v>5328</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="80" t="inlineStr">
+        <is>
+          <t>Cont trezorerie</t>
+        </is>
+      </c>
+      <c r="B42" s="81" t="inlineStr">
+        <is>
+          <t>5121</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="79" t="inlineStr">
+        <is>
+          <t>5. Controale</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="80" t="inlineStr">
+        <is>
+          <t>Check brut = net + rețineri</t>
+        </is>
+      </c>
+      <c r="B45" s="80">
+        <f>$C$29-($J$29+$F$29+$G$29+$I$29)</f>
+        <v>0</v>
+      </c>
+      <c r="C45" s="80" t="str">
+        <f>IF(ABS(B45)&lt;0.51,"OK — brutul se descompune integral","EROARE — rotunjirile nu se închid")</f>
+        <v>OK — brutul se descompune integral</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="80" t="inlineStr">
+        <is>
+          <t>Check total de plată = net − avans</t>
+        </is>
+      </c>
+      <c r="B46" s="80">
+        <f>$K$29-($J$29-$E$29)</f>
+        <v>0</v>
+      </c>
+      <c r="C46" s="80" t="str">
+        <f>IF(ABS(B46)&lt;0.01,"OK","EROARE")</f>
+        <v>OK</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="80" t="inlineStr">
+        <is>
+          <t>Reminder bază CASS</t>
+        </is>
+      </c>
+      <c r="B47" s="80">
+        <f>$D$29</f>
+        <v>2550</v>
+      </c>
+      <c r="C47" s="80" t="str">
+        <f>"Tichetele intră în baza CASS și în baza impozitului, dar NU în baza CAS. Dacă softul le tratează altfel, diferența apare aici."</f>
+        <v>Tichetele intră în baza CASS și în baza impozitului, dar NU în baza CAS. Dacă softul le tratează altfel, diferența apare aici.</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="80" t="inlineStr">
+        <is>
+          <t>Reminder deducere personală</t>
+        </is>
+      </c>
+      <c r="B48" s="80" t="str">
+        <f>"—"</f>
+        <v>—</v>
+      </c>
+      <c r="C48" s="80" t="str">
+        <f>"Modulul NU calculează deducerea personală. La salarii mici devine "&amp;"obligatorie — vezi Reguli_SALARII, tabelul C."</f>
+        <v>Modulul NU calculează deducerea personală. La salarii mici devine obligatorie — vezi Reguli_SALARII, tabelul C.</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="79" t="inlineStr">
+        <is>
+          <t>6. Sufix generat</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="80" t="inlineStr">
+        <is>
+          <t>Sufix</t>
+        </is>
+      </c>
+      <c r="B51" s="80" t="str">
+        <f>" - " &amp; B7</f>
+        <v> - 2026-07</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet49.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F26"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="26" customWidth="1" style="40" min="1" max="1"/>
+    <col width="30" customWidth="1" style="40" min="2" max="2"/>
+    <col width="14" customWidth="1" style="40" min="3" max="3"/>
+    <col width="40" customWidth="1" style="40" min="4" max="4"/>
+    <col width="22" customWidth="1" style="40" min="5" max="5"/>
+    <col width="54" customWidth="1" style="40" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="77" t="inlineStr">
+        <is>
+          <t>MOD_SALARII — Reguli (tabele fixe)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="78" t="inlineStr">
+        <is>
+          <t>Regula fiscală e dată, nu formulă. Se editează doar când se schimbă legea.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="79" t="inlineStr">
+        <is>
+          <t>Tabel A — Contribuții și baze</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="82" t="inlineStr">
+        <is>
+          <t>Element</t>
+        </is>
+      </c>
+      <c r="B5" s="82" t="inlineStr">
+        <is>
+          <t>Bază de calcul</t>
+        </is>
+      </c>
+      <c r="C5" s="82" t="inlineStr">
+        <is>
+          <t>Cotă</t>
+        </is>
+      </c>
+      <c r="D5" s="82" t="inlineStr">
+        <is>
+          <t>Cine suportă</t>
+        </is>
+      </c>
+      <c r="E5" s="82" t="inlineStr">
+        <is>
+          <t>Cont</t>
+        </is>
+      </c>
+      <c r="F5" s="82" t="inlineStr">
+        <is>
+          <t>Temei</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="80" t="inlineStr">
+        <is>
+          <t>CAS — pensie</t>
+        </is>
+      </c>
+      <c r="B6" s="80" t="inlineStr">
+        <is>
+          <t>salariul brut</t>
+        </is>
+      </c>
+      <c r="C6" s="80" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+      <c r="D6" s="80" t="inlineStr">
+        <is>
+          <t>angajatul (reținut)</t>
+        </is>
+      </c>
+      <c r="E6" s="80" t="inlineStr">
+        <is>
+          <t>4315</t>
+        </is>
+      </c>
+      <c r="F6" s="80" t="inlineStr">
+        <is>
+          <t>art. 138 Cod fiscal</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="80" t="inlineStr">
+        <is>
+          <t>CASS — sănătate</t>
+        </is>
+      </c>
+      <c r="B7" s="80" t="inlineStr">
+        <is>
+          <t>brut + tichete de masă</t>
+        </is>
+      </c>
+      <c r="C7" s="80" t="inlineStr">
+        <is>
+          <t>10%</t>
+        </is>
+      </c>
+      <c r="D7" s="80" t="inlineStr">
+        <is>
+          <t>angajatul (reținut)</t>
+        </is>
+      </c>
+      <c r="E7" s="80" t="inlineStr">
+        <is>
+          <t>4316</t>
+        </is>
+      </c>
+      <c r="F7" s="80" t="inlineStr">
+        <is>
+          <t>art. 156 CF; tichetele intră în bază din 2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="80" t="inlineStr">
+        <is>
+          <t>Impozit pe venit</t>
+        </is>
+      </c>
+      <c r="B8" s="80" t="inlineStr">
+        <is>
+          <t>venit net + tichete</t>
+        </is>
+      </c>
+      <c r="C8" s="80" t="inlineStr">
+        <is>
+          <t>10%</t>
+        </is>
+      </c>
+      <c r="D8" s="80" t="inlineStr">
+        <is>
+          <t>angajatul (reținut)</t>
+        </is>
+      </c>
+      <c r="E8" s="80" t="inlineStr">
+        <is>
+          <t>444</t>
+        </is>
+      </c>
+      <c r="F8" s="80" t="inlineStr">
+        <is>
+          <t>art. 78 CF</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="80" t="inlineStr">
+        <is>
+          <t>CAM — asigurare de muncă</t>
+        </is>
+      </c>
+      <c r="B9" s="80" t="inlineStr">
+        <is>
+          <t>salariul brut</t>
+        </is>
+      </c>
+      <c r="C9" s="80" t="inlineStr">
+        <is>
+          <t>2,25%</t>
+        </is>
+      </c>
+      <c r="D9" s="80" t="inlineStr">
+        <is>
+          <t>angajatorul (cheltuială)</t>
+        </is>
+      </c>
+      <c r="E9" s="80" t="inlineStr">
+        <is>
+          <t>436</t>
+        </is>
+      </c>
+      <c r="F9" s="80" t="inlineStr">
+        <is>
+          <t>art. 220^3 CF</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="80" t="inlineStr">
+        <is>
+          <t>Tichete de masă</t>
+        </is>
+      </c>
+      <c r="B10" s="80" t="inlineStr">
+        <is>
+          <t>valoare nominală</t>
+        </is>
+      </c>
+      <c r="C10" s="80" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D10" s="80" t="inlineStr">
+        <is>
+          <t>angajatorul (cheltuială)</t>
+        </is>
+      </c>
+      <c r="E10" s="80" t="inlineStr">
+        <is>
+          <t>642 / 5328</t>
+        </is>
+      </c>
+      <c r="F10" s="80" t="inlineStr">
+        <is>
+          <t>nu intră în baza CAS; intră în CASS și impozit</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="79" t="inlineStr">
+        <is>
+          <t>Tabel B — Ordinea înregistrărilor</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="82" t="inlineStr">
+        <is>
+          <t>Moment</t>
+        </is>
+      </c>
+      <c r="B13" s="82" t="inlineStr">
+        <is>
+          <t>Ce se înregistrează</t>
+        </is>
+      </c>
+      <c r="C13" s="82" t="inlineStr">
+        <is>
+          <t>Data</t>
+        </is>
+      </c>
+      <c r="D13" s="82" t="inlineStr"/>
+      <c r="E13" s="82" t="inlineStr"/>
+      <c r="F13" s="82" t="inlineStr">
+        <is>
+          <t>Observație</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="80" t="inlineStr">
+        <is>
+          <t>Avans</t>
+        </is>
+      </c>
+      <c r="B14" s="80" t="inlineStr">
+        <is>
+          <t>425 = 5121</t>
+        </is>
+      </c>
+      <c r="C14" s="80" t="inlineStr">
+        <is>
+          <t>în cursul lunii</t>
+        </is>
+      </c>
+      <c r="D14" s="80" t="inlineStr"/>
+      <c r="E14" s="80" t="inlineStr"/>
+      <c r="F14" s="80" t="inlineStr">
+        <is>
+          <t>Doar dacă există avans acordat</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="80" t="inlineStr">
+        <is>
+          <t>Închiderea lunii</t>
+        </is>
+      </c>
+      <c r="B15" s="80" t="inlineStr">
+        <is>
+          <t>641 = 421; 421 = 4315/4316/444; 646 = 436; 642 = 5328</t>
+        </is>
+      </c>
+      <c r="C15" s="80" t="inlineStr">
+        <is>
+          <t>ultima zi a lunii</t>
+        </is>
+      </c>
+      <c r="D15" s="80" t="inlineStr"/>
+      <c r="E15" s="80" t="inlineStr"/>
+      <c r="F15" s="80" t="inlineStr">
+        <is>
+          <t>Costul aparține lunii lucrate</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="80" t="inlineStr">
+        <is>
+          <t>Stingerea avansului</t>
+        </is>
+      </c>
+      <c r="B16" s="80" t="inlineStr">
+        <is>
+          <t>421 = 425</t>
+        </is>
+      </c>
+      <c r="C16" s="80" t="inlineStr">
+        <is>
+          <t>ultima zi a lunii</t>
+        </is>
+      </c>
+      <c r="D16" s="80" t="inlineStr"/>
+      <c r="E16" s="80" t="inlineStr"/>
+      <c r="F16" s="80" t="inlineStr">
+        <is>
+          <t>Diminuează datoria salarială cu avansul deja plătit</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="80" t="inlineStr">
+        <is>
+          <t>Plăți</t>
+        </is>
+      </c>
+      <c r="B17" s="80" t="inlineStr">
+        <is>
+          <t>421 = 5121; 4315/4316/444 = 5121; 436 = 5121</t>
+        </is>
+      </c>
+      <c r="C17" s="80" t="inlineStr">
+        <is>
+          <t>luna următoare</t>
+        </is>
+      </c>
+      <c r="D17" s="80" t="inlineStr"/>
+      <c r="E17" s="80" t="inlineStr"/>
+      <c r="F17" s="80" t="inlineStr">
+        <is>
+          <t>Termenul legal: 25 a lunii următoare</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="79" t="inlineStr">
+        <is>
+          <t>Tabel C — LIMITĂRI DECLARATE ale modulului</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="78" t="inlineStr">
+        <is>
+          <t>Enumerate explicit ca să nu fie luate drept acoperite. Fiecare cere ajustare manuală înainte de folosire la un client căruia i se aplică.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="82" t="inlineStr">
+        <is>
+          <t>Ce NU tratează</t>
+        </is>
+      </c>
+      <c r="B21" s="82" t="inlineStr">
+        <is>
+          <t>De ce</t>
+        </is>
+      </c>
+      <c r="C21" s="82" t="inlineStr">
+        <is>
+          <t>Ce faci</t>
+        </is>
+      </c>
+      <c r="D21" s="82" t="inlineStr"/>
+      <c r="E21" s="82" t="inlineStr"/>
+      <c r="F21" s="82" t="inlineStr">
+        <is>
+          <t>Efect dacă îl ignori</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="80" t="inlineStr">
+        <is>
+          <t>Deducerea personală</t>
+        </is>
+      </c>
+      <c r="B22" s="80" t="inlineStr">
+        <is>
+          <t>Cei 4 angajați din statul-sursă sunt peste plafonul de acordare, deci mecanismul nu apare în fișier și nu a fost inventat.</t>
+        </is>
+      </c>
+      <c r="C22" s="80" t="inlineStr">
+        <is>
+          <t>La salarii mici: calculează deducerea și scade-o din baza impozitului.</t>
+        </is>
+      </c>
+      <c r="D22" s="80" t="inlineStr"/>
+      <c r="E22" s="80" t="inlineStr"/>
+      <c r="F22" s="80" t="inlineStr">
+        <is>
+          <t>Impozit supraevaluat, net subevaluat</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="80" t="inlineStr">
+        <is>
+          <t>Facilități sectoriale (construcții, IT, agricultură, alimentar)</t>
+        </is>
+      </c>
+      <c r="B23" s="80" t="inlineStr">
+        <is>
+          <t>Cotele și scutirile diferă pe sector și se schimbă des.</t>
+        </is>
+      </c>
+      <c r="C23" s="80" t="inlineStr">
+        <is>
+          <t>Ajustează cotele din Parametri și verifică scutirea de CASS/impozit.</t>
+        </is>
+      </c>
+      <c r="D23" s="80" t="inlineStr"/>
+      <c r="E23" s="80" t="inlineStr"/>
+      <c r="F23" s="80" t="inlineStr">
+        <is>
+          <t>Contribuții calculate greșit în ambele sensuri</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="80" t="inlineStr">
+        <is>
+          <t>Scutiri (handicap, studenți)</t>
+        </is>
+      </c>
+      <c r="B24" s="80" t="inlineStr">
+        <is>
+          <t>Regim special, pe document justificativ.</t>
+        </is>
+      </c>
+      <c r="C24" s="80" t="inlineStr">
+        <is>
+          <t>Tratează separat angajatul respectiv.</t>
+        </is>
+      </c>
+      <c r="D24" s="80" t="inlineStr"/>
+      <c r="E24" s="80" t="inlineStr"/>
+      <c r="F24" s="80" t="inlineStr">
+        <is>
+          <t>Impozit reținut nedatorat</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="80" t="inlineStr">
+        <is>
+          <t>Pilonul II / pensii facultative</t>
+        </is>
+      </c>
+      <c r="B25" s="80" t="inlineStr">
+        <is>
+          <t>Rețineri opționale, pe cerere.</t>
+        </is>
+      </c>
+      <c r="C25" s="80" t="inlineStr">
+        <is>
+          <t>Adaugă coloană de reținere și cont 4315 analitic.</t>
+        </is>
+      </c>
+      <c r="D25" s="80" t="inlineStr"/>
+      <c r="E25" s="80" t="inlineStr"/>
+      <c r="F25" s="80" t="inlineStr">
+        <is>
+          <t>Netul plătit nu corespunde statului</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="80" t="inlineStr">
+        <is>
+          <t>Concedii medicale (FNUASS)</t>
+        </is>
+      </c>
+      <c r="B26" s="80" t="inlineStr">
+        <is>
+          <t>Recuperarea de la buget are mecanism propriu.</t>
+        </is>
+      </c>
+      <c r="C26" s="80" t="inlineStr">
+        <is>
+          <t>Tratează prin 4382 / 4315 analitic.</t>
+        </is>
+      </c>
+      <c r="D26" s="80" t="inlineStr"/>
+      <c r="E26" s="80" t="inlineStr"/>
+      <c r="F26" s="80" t="inlineStr">
+        <is>
+          <t>Cheltuiala rămâne umflată</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr filterMode="0">
@@ -19227,6 +20618,4089 @@
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet50.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G44"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" style="40" min="1" max="1"/>
+    <col width="14" customWidth="1" style="40" min="2" max="2"/>
+    <col width="14" customWidth="1" style="40" min="3" max="3"/>
+    <col width="46" customWidth="1" style="40" min="4" max="4"/>
+    <col width="14" customWidth="1" style="40" min="5" max="5"/>
+    <col width="14" customWidth="1" style="40" min="6" max="6"/>
+    <col width="46" customWidth="1" style="40" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="77" t="inlineStr">
+        <is>
+          <t>MOD_SALARII — Jurnale (generate automat)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="78" t="inlineStr">
+        <is>
+          <t>Notele sunt agregate pe lună. Fișele individuale rămân în registrul din Declarații. Fiecare bloc are rând de Check.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="79" t="inlineStr">
+        <is>
+          <t>Bloc 1 — Plata avansului</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="80" t="inlineStr">
+        <is>
+          <t>Data jurnal:</t>
+        </is>
+      </c>
+      <c r="B5" s="80" t="str">
+        <f>Declarații_SALARII!B10</f>
+        <v>2026-07-20</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="82" t="inlineStr">
+        <is>
+          <t>Nr</t>
+        </is>
+      </c>
+      <c r="B7" s="82" t="inlineStr">
+        <is>
+          <t>Cont Dr</t>
+        </is>
+      </c>
+      <c r="C7" s="82" t="inlineStr">
+        <is>
+          <t>Sumă Dr</t>
+        </is>
+      </c>
+      <c r="D7" s="82" t="inlineStr">
+        <is>
+          <t>Descriere Dr</t>
+        </is>
+      </c>
+      <c r="E7" s="82" t="inlineStr">
+        <is>
+          <t>Cont Cr</t>
+        </is>
+      </c>
+      <c r="F7" s="82" t="inlineStr">
+        <is>
+          <t>Sumă Cr</t>
+        </is>
+      </c>
+      <c r="G7" s="82" t="inlineStr">
+        <is>
+          <t>Descriere Cr</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="80" t="n">
+        <v>1</v>
+      </c>
+      <c r="B8" s="80">
+        <f>Declarații_SALARII!B34</f>
+        <v>425</v>
+      </c>
+      <c r="C8" s="80">
+        <f>Declarații_SALARII!$E$29</f>
+        <v>0</v>
+      </c>
+      <c r="D8" s="80" t="str">
+        <f>"Avans acordat personalului" &amp; Declarații_SALARII!B51</f>
+        <v>Avans acordat personalului - 2026-07</v>
+      </c>
+      <c r="E8" s="80" t="str">
+        <f>Declarații_SALARII!B42</f>
+        <v>5121</v>
+      </c>
+      <c r="F8" s="80">
+        <f>Declarații_SALARII!$E$29</f>
+        <v>0</v>
+      </c>
+      <c r="G8" s="80" t="str">
+        <f>"Plata avansului din bancă" &amp; Declarații_SALARII!B51</f>
+        <v>Plata avansului din bancă - 2026-07</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="80" t="inlineStr">
+        <is>
+          <t>Check Σ (structural)</t>
+        </is>
+      </c>
+      <c r="B10" s="80">
+        <f>C8-F8</f>
+        <v>0</v>
+      </c>
+      <c r="C10" s="80" t="str">
+        <f>IF(ABS(B10)&lt;0.01,"OK — nota se închide","EROARE")</f>
+        <v>OK — nota se închide</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="80" t="inlineStr">
+        <is>
+          <t>Bloc activ?</t>
+        </is>
+      </c>
+      <c r="B11" s="80">
+        <f>Declarații_SALARII!$E$29</f>
+        <v>0</v>
+      </c>
+      <c r="C11" s="80" t="str">
+        <f>IF(B11&gt;0,"ACTIV — există avans","INACTIV — fără avans în această lună")</f>
+        <v>INACTIV — fără avans în această lună</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="79" t="inlineStr">
+        <is>
+          <t>Bloc 2 — Costurile lunii</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="80" t="inlineStr">
+        <is>
+          <t>Data jurnal:</t>
+        </is>
+      </c>
+      <c r="B14" s="80" t="str">
+        <f>Declarații_SALARII!B8</f>
+        <v>2026-07-31</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="82" t="inlineStr">
+        <is>
+          <t>Nr</t>
+        </is>
+      </c>
+      <c r="B16" s="82" t="inlineStr">
+        <is>
+          <t>Cont Dr</t>
+        </is>
+      </c>
+      <c r="C16" s="82" t="inlineStr">
+        <is>
+          <t>Sumă Dr</t>
+        </is>
+      </c>
+      <c r="D16" s="82" t="inlineStr">
+        <is>
+          <t>Descriere Dr</t>
+        </is>
+      </c>
+      <c r="E16" s="82" t="inlineStr">
+        <is>
+          <t>Cont Cr</t>
+        </is>
+      </c>
+      <c r="F16" s="82" t="inlineStr">
+        <is>
+          <t>Sumă Cr</t>
+        </is>
+      </c>
+      <c r="G16" s="82" t="inlineStr">
+        <is>
+          <t>Descriere Cr</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="80" t="n">
+        <v>1</v>
+      </c>
+      <c r="B17" s="80">
+        <f>Declarații_SALARII!B32</f>
+        <v>641</v>
+      </c>
+      <c r="C17" s="80">
+        <f>Declarații_SALARII!$C$29</f>
+        <v>70877</v>
+      </c>
+      <c r="D17" s="80" t="str">
+        <f>"Cheltuieli cu salariile" &amp; Declarații_SALARII!B51</f>
+        <v>Cheltuieli cu salariile - 2026-07</v>
+      </c>
+      <c r="E17" s="80">
+        <f>Declarații_SALARII!B33</f>
+        <v>421</v>
+      </c>
+      <c r="F17" s="80">
+        <f>Declarații_SALARII!$C$29</f>
+        <v>70877</v>
+      </c>
+      <c r="G17" s="80" t="str">
+        <f>"Salarii brute datorate personalului" &amp; Declarații_SALARII!B51</f>
+        <v>Salarii brute datorate personalului - 2026-07</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="80" t="n">
+        <v>2</v>
+      </c>
+      <c r="B18" s="80">
+        <f>Declarații_SALARII!B33</f>
+        <v>421</v>
+      </c>
+      <c r="C18" s="80">
+        <f>Declarații_SALARII!$F$29+Declarații_SALARII!$G$29+Declarații_SALARII!$I$29</f>
+        <v>29900</v>
+      </c>
+      <c r="D18" s="80" t="str">
+        <f>"Rețineri din salarii: CAS, CASS, impozit" &amp; Declarații_SALARII!B51</f>
+        <v>Rețineri din salarii: CAS, CASS, impozit - 2026-07</v>
+      </c>
+      <c r="E18" s="80">
+        <f>Declarații_SALARII!B35</f>
+        <v>4315</v>
+      </c>
+      <c r="F18" s="80">
+        <f>Declarații_SALARII!$F$29</f>
+        <v>17720</v>
+      </c>
+      <c r="G18" s="80" t="str">
+        <f>"CAS reținut, datorat bugetului" &amp; Declarații_SALARII!B51</f>
+        <v>CAS reținut, datorat bugetului - 2026-07</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="80" t="n">
+        <v>3</v>
+      </c>
+      <c r="E19" s="80">
+        <f>Declarații_SALARII!B36</f>
+        <v>4316</v>
+      </c>
+      <c r="F19" s="80">
+        <f>Declarații_SALARII!$G$29</f>
+        <v>7343</v>
+      </c>
+      <c r="G19" s="80" t="str">
+        <f>"CASS reținut, datorat bugetului" &amp; Declarații_SALARII!B51</f>
+        <v>CASS reținut, datorat bugetului - 2026-07</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="80" t="n">
+        <v>4</v>
+      </c>
+      <c r="E20" s="80">
+        <f>Declarații_SALARII!B37</f>
+        <v>444</v>
+      </c>
+      <c r="F20" s="80">
+        <f>Declarații_SALARII!$I$29</f>
+        <v>4837</v>
+      </c>
+      <c r="G20" s="80" t="str">
+        <f>"Impozit pe venit reținut, datorat bugetului" &amp; Declarații_SALARII!B51</f>
+        <v>Impozit pe venit reținut, datorat bugetului - 2026-07</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="80" t="n">
+        <v>5</v>
+      </c>
+      <c r="B21" s="80">
+        <f>Declarații_SALARII!B38</f>
+        <v>646</v>
+      </c>
+      <c r="C21" s="80">
+        <f>Declarații_SALARII!$L$29</f>
+        <v>1596</v>
+      </c>
+      <c r="D21" s="80" t="str">
+        <f>"Cheltuieli cu CAM" &amp; Declarații_SALARII!B51</f>
+        <v>Cheltuieli cu CAM - 2026-07</v>
+      </c>
+      <c r="E21" s="80">
+        <f>Declarații_SALARII!B39</f>
+        <v>436</v>
+      </c>
+      <c r="F21" s="80">
+        <f>Declarații_SALARII!$L$29</f>
+        <v>1596</v>
+      </c>
+      <c r="G21" s="80" t="str">
+        <f>"CAM datorat bugetului" &amp; Declarații_SALARII!B51</f>
+        <v>CAM datorat bugetului - 2026-07</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="80" t="n">
+        <v>6</v>
+      </c>
+      <c r="B22" s="80">
+        <f>Declarații_SALARII!B40</f>
+        <v>642</v>
+      </c>
+      <c r="C22" s="80">
+        <f>Declarații_SALARII!$D$29</f>
+        <v>2550</v>
+      </c>
+      <c r="D22" s="80" t="str">
+        <f>"Cheltuieli cu tichetele de masă" &amp; Declarații_SALARII!B51</f>
+        <v>Cheltuieli cu tichetele de masă - 2026-07</v>
+      </c>
+      <c r="E22" s="80">
+        <f>Declarații_SALARII!B41</f>
+        <v>5328</v>
+      </c>
+      <c r="F22" s="80">
+        <f>Declarații_SALARII!$D$29</f>
+        <v>2550</v>
+      </c>
+      <c r="G22" s="80" t="str">
+        <f>"Descărcarea tichetelor din gestiune" &amp; Declarații_SALARII!B51</f>
+        <v>Descărcarea tichetelor din gestiune - 2026-07</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="80" t="n">
+        <v>7</v>
+      </c>
+      <c r="B23" s="80">
+        <f>Declarații_SALARII!B33</f>
+        <v>421</v>
+      </c>
+      <c r="C23" s="80">
+        <f>Declarații_SALARII!$E$29</f>
+        <v>0</v>
+      </c>
+      <c r="D23" s="80" t="str">
+        <f>"Diminuarea datoriei salariale cu avansul acordat" &amp; Declarații_SALARII!B51</f>
+        <v>Diminuarea datoriei salariale cu avansul acordat - 2026-07</v>
+      </c>
+      <c r="E23" s="80">
+        <f>Declarații_SALARII!B34</f>
+        <v>425</v>
+      </c>
+      <c r="F23" s="80">
+        <f>Declarații_SALARII!$E$29</f>
+        <v>0</v>
+      </c>
+      <c r="G23" s="80" t="str">
+        <f>"Stingerea avansului acordat personalului" &amp; Declarații_SALARII!B51</f>
+        <v>Stingerea avansului acordat personalului - 2026-07</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="80" t="inlineStr">
+        <is>
+          <t>Total Dr</t>
+        </is>
+      </c>
+      <c r="B25" s="80">
+        <f>SUM(C17:C23)</f>
+        <v>104923</v>
+      </c>
+      <c r="C25" s="80" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="80" t="inlineStr">
+        <is>
+          <t>Total Cr</t>
+        </is>
+      </c>
+      <c r="B26" s="80">
+        <f>SUM(F17:F23)</f>
+        <v>104923</v>
+      </c>
+      <c r="C26" s="80" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="80" t="inlineStr">
+        <is>
+          <t>Check Σ (structural)</t>
+        </is>
+      </c>
+      <c r="B27" s="80">
+        <f>SUM(C17:C23)-SUM(F17:F23)</f>
+        <v>0</v>
+      </c>
+      <c r="C27" s="80" t="str">
+        <f>IF(ABS(B27)&lt;0.01,"OK — notele se închid","EROARE")</f>
+        <v>OK — notele se închid</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="80" t="inlineStr">
+        <is>
+          <t>Check sold 421 după bloc</t>
+        </is>
+      </c>
+      <c r="B28" s="80">
+        <f>Declarații_SALARII!$C$29-(Declarații_SALARII!$F$29+Declarații_SALARII!$G$29+Declarații_SALARII!$I$29+Declarații_SALARII!$E$29)</f>
+        <v>40977</v>
+      </c>
+      <c r="C28" s="80" t="str">
+        <f>IF(ABS(B28-Declarații_SALARII!$K$29)&lt;0.51,"OK — soldul 421 = total de plată","EROARE — 421 nu corespunde netului")</f>
+        <v>OK — soldul 421 = total de plată</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="79" t="inlineStr">
+        <is>
+          <t>Bloc 3 — Plăți</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="80" t="inlineStr">
+        <is>
+          <t>Data jurnal:</t>
+        </is>
+      </c>
+      <c r="B31" s="80" t="str">
+        <f>Declarații_SALARII!B9</f>
+        <v>2026-08-10</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="82" t="inlineStr">
+        <is>
+          <t>Nr</t>
+        </is>
+      </c>
+      <c r="B33" s="82" t="inlineStr">
+        <is>
+          <t>Cont Dr</t>
+        </is>
+      </c>
+      <c r="C33" s="82" t="inlineStr">
+        <is>
+          <t>Sumă Dr</t>
+        </is>
+      </c>
+      <c r="D33" s="82" t="inlineStr">
+        <is>
+          <t>Descriere Dr</t>
+        </is>
+      </c>
+      <c r="E33" s="82" t="inlineStr">
+        <is>
+          <t>Cont Cr</t>
+        </is>
+      </c>
+      <c r="F33" s="82" t="inlineStr">
+        <is>
+          <t>Sumă Cr</t>
+        </is>
+      </c>
+      <c r="G33" s="82" t="inlineStr">
+        <is>
+          <t>Descriere Cr</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="80" t="n">
+        <v>1</v>
+      </c>
+      <c r="B34" s="80">
+        <f>Declarații_SALARII!B33</f>
+        <v>421</v>
+      </c>
+      <c r="C34" s="80">
+        <f>Declarații_SALARII!$K$29</f>
+        <v>40977</v>
+      </c>
+      <c r="D34" s="80" t="str">
+        <f>"Plata salariilor nete" &amp; Declarații_SALARII!B51</f>
+        <v>Plata salariilor nete - 2026-07</v>
+      </c>
+      <c r="E34" s="80" t="str">
+        <f>Declarații_SALARII!B42</f>
+        <v>5121</v>
+      </c>
+      <c r="F34" s="80">
+        <f>Declarații_SALARII!$K$29</f>
+        <v>40977</v>
+      </c>
+      <c r="G34" s="80" t="str">
+        <f>"Plata salariilor nete din bancă" &amp; Declarații_SALARII!B51</f>
+        <v>Plata salariilor nete din bancă - 2026-07</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="80" t="n">
+        <v>2</v>
+      </c>
+      <c r="B35" s="80">
+        <f>Declarații_SALARII!B35</f>
+        <v>4315</v>
+      </c>
+      <c r="C35" s="80">
+        <f>Declarații_SALARII!$F$29</f>
+        <v>17720</v>
+      </c>
+      <c r="D35" s="80" t="str">
+        <f>"Stingerea datoriei CAS" &amp; Declarații_SALARII!B51</f>
+        <v>Stingerea datoriei CAS - 2026-07</v>
+      </c>
+      <c r="E35" s="80" t="str">
+        <f>Declarații_SALARII!B42</f>
+        <v>5121</v>
+      </c>
+      <c r="F35" s="80">
+        <f>Declarații_SALARII!$F$29+Declarații_SALARII!$G$29+Declarații_SALARII!$I$29</f>
+        <v>29900</v>
+      </c>
+      <c r="G35" s="80" t="str">
+        <f>"Plata CAS, CASS și impozit din bancă" &amp; Declarații_SALARII!B51</f>
+        <v>Plata CAS, CASS și impozit din bancă - 2026-07</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="80" t="n">
+        <v>3</v>
+      </c>
+      <c r="B36" s="80">
+        <f>Declarații_SALARII!B36</f>
+        <v>4316</v>
+      </c>
+      <c r="C36" s="80">
+        <f>Declarații_SALARII!$G$29</f>
+        <v>7343</v>
+      </c>
+      <c r="D36" s="80" t="str">
+        <f>"Stingerea datoriei CASS" &amp; Declarații_SALARII!B51</f>
+        <v>Stingerea datoriei CASS - 2026-07</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="80" t="n">
+        <v>4</v>
+      </c>
+      <c r="B37" s="80">
+        <f>Declarații_SALARII!B37</f>
+        <v>444</v>
+      </c>
+      <c r="C37" s="80">
+        <f>Declarații_SALARII!$I$29</f>
+        <v>4837</v>
+      </c>
+      <c r="D37" s="80" t="str">
+        <f>"Stingerea datoriei de impozit" &amp; Declarații_SALARII!B51</f>
+        <v>Stingerea datoriei de impozit - 2026-07</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="80" t="n">
+        <v>5</v>
+      </c>
+      <c r="B38" s="80">
+        <f>Declarații_SALARII!B39</f>
+        <v>436</v>
+      </c>
+      <c r="C38" s="80">
+        <f>Declarații_SALARII!$L$29</f>
+        <v>1596</v>
+      </c>
+      <c r="D38" s="80" t="str">
+        <f>"Stingerea datoriei CAM" &amp; Declarații_SALARII!B51</f>
+        <v>Stingerea datoriei CAM - 2026-07</v>
+      </c>
+      <c r="E38" s="80" t="str">
+        <f>Declarații_SALARII!B42</f>
+        <v>5121</v>
+      </c>
+      <c r="F38" s="80">
+        <f>Declarații_SALARII!$L$29</f>
+        <v>1596</v>
+      </c>
+      <c r="G38" s="80" t="str">
+        <f>"Plata CAM din bancă" &amp; Declarații_SALARII!B51</f>
+        <v>Plata CAM din bancă - 2026-07</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="80" t="inlineStr">
+        <is>
+          <t>Total Dr</t>
+        </is>
+      </c>
+      <c r="B40" s="80">
+        <f>SUM(C34:C38)</f>
+        <v>72473</v>
+      </c>
+      <c r="C40" s="80" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="80" t="inlineStr">
+        <is>
+          <t>Total Cr</t>
+        </is>
+      </c>
+      <c r="B41" s="80">
+        <f>SUM(F34:F38)</f>
+        <v>72473</v>
+      </c>
+      <c r="C41" s="80" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="80" t="inlineStr">
+        <is>
+          <t>Check Σ (structural)</t>
+        </is>
+      </c>
+      <c r="B42" s="80">
+        <f>SUM(C34:C38)-SUM(F34:F38)</f>
+        <v>0</v>
+      </c>
+      <c r="C42" s="80" t="str">
+        <f>IF(ABS(B42)&lt;0.01,"OK — notele se închid","EROARE")</f>
+        <v>OK — notele se închid</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="78" t="inlineStr">
+        <is>
+          <t>Stare terminală așteptată: 421 = 0, 425 = 0, 4315/4316/444/436 = 0 după plăți; 641, 642 și 646 se închid pe 121 la finalul exercițiului (vezi fluxul de închidere a exercițiului).</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet51.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="6" customWidth="1" style="40" min="1" max="1"/>
+    <col width="26" customWidth="1" style="40" min="2" max="2"/>
+    <col width="12" customWidth="1" style="40" min="3" max="3"/>
+    <col width="12" customWidth="1" style="40" min="4" max="4"/>
+    <col width="12" customWidth="1" style="40" min="5" max="5"/>
+    <col width="14" customWidth="1" style="40" min="6" max="6"/>
+    <col width="48" customWidth="1" style="40" min="7" max="7"/>
+    <col width="20" customWidth="1" style="40" min="8" max="8"/>
+    <col width="9" customWidth="1" style="40" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="77" t="inlineStr">
+        <is>
+          <t>MOD_SALARII — Notă pentru import (1 rând = 1 înregistrare)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="78" t="inlineStr">
+        <is>
+          <t>Filtrează pe Include = DA. Echilibrul se verifică pe bloc în Jurnale, nu pe totalul listei.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="82" t="inlineStr">
+        <is>
+          <t>Nr</t>
+        </is>
+      </c>
+      <c r="B4" s="82" t="inlineStr">
+        <is>
+          <t>Bloc</t>
+        </is>
+      </c>
+      <c r="C4" s="82" t="inlineStr">
+        <is>
+          <t>Data</t>
+        </is>
+      </c>
+      <c r="D4" s="82" t="inlineStr">
+        <is>
+          <t>Cont Dr</t>
+        </is>
+      </c>
+      <c r="E4" s="82" t="inlineStr">
+        <is>
+          <t>Cont Cr</t>
+        </is>
+      </c>
+      <c r="F4" s="82" t="inlineStr">
+        <is>
+          <t>Sumă</t>
+        </is>
+      </c>
+      <c r="G4" s="82" t="inlineStr">
+        <is>
+          <t>Descriere</t>
+        </is>
+      </c>
+      <c r="H4" s="82" t="inlineStr">
+        <is>
+          <t>Document</t>
+        </is>
+      </c>
+      <c r="I4" s="82" t="inlineStr">
+        <is>
+          <t>Include</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="80" t="n">
+        <v>1</v>
+      </c>
+      <c r="B5" s="80" t="inlineStr">
+        <is>
+          <t>Bloc 1 — Avans</t>
+        </is>
+      </c>
+      <c r="C5" s="80" t="str">
+        <f>Declarații_SALARII!B10</f>
+        <v>2026-07-20</v>
+      </c>
+      <c r="D5" s="80">
+        <f>Jurnale_SALARII!B8</f>
+        <v>425</v>
+      </c>
+      <c r="E5" s="80" t="str">
+        <f>Jurnale_SALARII!E8</f>
+        <v>5121</v>
+      </c>
+      <c r="F5" s="80">
+        <f>Jurnale_SALARII!C8</f>
+        <v>0</v>
+      </c>
+      <c r="G5" s="80" t="str">
+        <f>Jurnale_SALARII!D8</f>
+        <v>Avans acordat personalului - 2026-07</v>
+      </c>
+      <c r="H5" s="80" t="inlineStr">
+        <is>
+          <t>Stat de plată</t>
+        </is>
+      </c>
+      <c r="I5" s="80" t="str">
+        <f>IF(N(F5)&gt;0,"DA","NU")</f>
+        <v>NU</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="80" t="n">
+        <v>2</v>
+      </c>
+      <c r="B6" s="80" t="inlineStr">
+        <is>
+          <t>Bloc 2 — Costuri</t>
+        </is>
+      </c>
+      <c r="C6" s="80" t="str">
+        <f>Declarații_SALARII!B8</f>
+        <v>2026-07-31</v>
+      </c>
+      <c r="D6" s="80">
+        <f>Jurnale_SALARII!B17</f>
+        <v>641</v>
+      </c>
+      <c r="E6" s="80">
+        <f>Jurnale_SALARII!E17</f>
+        <v>421</v>
+      </c>
+      <c r="F6" s="80">
+        <f>Jurnale_SALARII!C17</f>
+        <v>70877</v>
+      </c>
+      <c r="G6" s="80" t="str">
+        <f>Jurnale_SALARII!D17</f>
+        <v>Cheltuieli cu salariile - 2026-07</v>
+      </c>
+      <c r="H6" s="80" t="inlineStr">
+        <is>
+          <t>Stat de plată</t>
+        </is>
+      </c>
+      <c r="I6" s="80" t="str">
+        <f>IF(N(F6)&gt;0,"DA","NU")</f>
+        <v>DA</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="80" t="n">
+        <v>3</v>
+      </c>
+      <c r="B7" s="80" t="inlineStr">
+        <is>
+          <t>Bloc 2 — Costuri</t>
+        </is>
+      </c>
+      <c r="C7" s="80" t="str">
+        <f>Declarații_SALARII!B8</f>
+        <v>2026-07-31</v>
+      </c>
+      <c r="D7" s="80">
+        <f>Jurnale_SALARII!B18</f>
+        <v>421</v>
+      </c>
+      <c r="E7" s="80">
+        <f>Jurnale_SALARII!E18</f>
+        <v>4315</v>
+      </c>
+      <c r="F7" s="80">
+        <f>Jurnale_SALARII!C18</f>
+        <v>29900</v>
+      </c>
+      <c r="G7" s="80" t="str">
+        <f>Jurnale_SALARII!D18</f>
+        <v>Rețineri din salarii: CAS, CASS, impozit - 2026-07</v>
+      </c>
+      <c r="H7" s="80" t="inlineStr">
+        <is>
+          <t>Stat de plată</t>
+        </is>
+      </c>
+      <c r="I7" s="80" t="str">
+        <f>IF(N(F7)&gt;0,"DA","NU")</f>
+        <v>DA</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="80" t="n">
+        <v>4</v>
+      </c>
+      <c r="B8" s="80" t="inlineStr">
+        <is>
+          <t>Bloc 2 — Costuri</t>
+        </is>
+      </c>
+      <c r="C8" s="80" t="str">
+        <f>Declarații_SALARII!B8</f>
+        <v>2026-07-31</v>
+      </c>
+      <c r="D8" s="80">
+        <f>Jurnale_SALARII!B19</f>
+        <v>0</v>
+      </c>
+      <c r="E8" s="80">
+        <f>Jurnale_SALARII!E19</f>
+        <v>4316</v>
+      </c>
+      <c r="F8" s="80">
+        <f>Jurnale_SALARII!C19</f>
+        <v>0</v>
+      </c>
+      <c r="G8" s="80">
+        <f>Jurnale_SALARII!D19</f>
+        <v>0</v>
+      </c>
+      <c r="H8" s="80" t="inlineStr">
+        <is>
+          <t>Stat de plată</t>
+        </is>
+      </c>
+      <c r="I8" s="80" t="str">
+        <f>IF(N(F8)&gt;0,"DA","NU")</f>
+        <v>NU</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="80" t="n">
+        <v>5</v>
+      </c>
+      <c r="B9" s="80" t="inlineStr">
+        <is>
+          <t>Bloc 2 — Costuri</t>
+        </is>
+      </c>
+      <c r="C9" s="80" t="str">
+        <f>Declarații_SALARII!B8</f>
+        <v>2026-07-31</v>
+      </c>
+      <c r="D9" s="80">
+        <f>Jurnale_SALARII!B20</f>
+        <v>0</v>
+      </c>
+      <c r="E9" s="80">
+        <f>Jurnale_SALARII!E20</f>
+        <v>444</v>
+      </c>
+      <c r="F9" s="80">
+        <f>Jurnale_SALARII!C20</f>
+        <v>0</v>
+      </c>
+      <c r="G9" s="80">
+        <f>Jurnale_SALARII!D20</f>
+        <v>0</v>
+      </c>
+      <c r="H9" s="80" t="inlineStr">
+        <is>
+          <t>Stat de plată</t>
+        </is>
+      </c>
+      <c r="I9" s="80" t="str">
+        <f>IF(N(F9)&gt;0,"DA","NU")</f>
+        <v>NU</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="80" t="n">
+        <v>6</v>
+      </c>
+      <c r="B10" s="80" t="inlineStr">
+        <is>
+          <t>Bloc 2 — Costuri</t>
+        </is>
+      </c>
+      <c r="C10" s="80" t="str">
+        <f>Declarații_SALARII!B8</f>
+        <v>2026-07-31</v>
+      </c>
+      <c r="D10" s="80">
+        <f>Jurnale_SALARII!B21</f>
+        <v>646</v>
+      </c>
+      <c r="E10" s="80">
+        <f>Jurnale_SALARII!E21</f>
+        <v>436</v>
+      </c>
+      <c r="F10" s="80">
+        <f>Jurnale_SALARII!C21</f>
+        <v>1596</v>
+      </c>
+      <c r="G10" s="80" t="str">
+        <f>Jurnale_SALARII!D21</f>
+        <v>Cheltuieli cu CAM - 2026-07</v>
+      </c>
+      <c r="H10" s="80" t="inlineStr">
+        <is>
+          <t>Stat de plată</t>
+        </is>
+      </c>
+      <c r="I10" s="80" t="str">
+        <f>IF(N(F10)&gt;0,"DA","NU")</f>
+        <v>DA</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="80" t="n">
+        <v>7</v>
+      </c>
+      <c r="B11" s="80" t="inlineStr">
+        <is>
+          <t>Bloc 2 — Costuri</t>
+        </is>
+      </c>
+      <c r="C11" s="80" t="str">
+        <f>Declarații_SALARII!B8</f>
+        <v>2026-07-31</v>
+      </c>
+      <c r="D11" s="80">
+        <f>Jurnale_SALARII!B22</f>
+        <v>642</v>
+      </c>
+      <c r="E11" s="80">
+        <f>Jurnale_SALARII!E22</f>
+        <v>5328</v>
+      </c>
+      <c r="F11" s="80">
+        <f>Jurnale_SALARII!C22</f>
+        <v>2550</v>
+      </c>
+      <c r="G11" s="80" t="str">
+        <f>Jurnale_SALARII!D22</f>
+        <v>Cheltuieli cu tichetele de masă - 2026-07</v>
+      </c>
+      <c r="H11" s="80" t="inlineStr">
+        <is>
+          <t>Stat de plată</t>
+        </is>
+      </c>
+      <c r="I11" s="80" t="str">
+        <f>IF(N(F11)&gt;0,"DA","NU")</f>
+        <v>DA</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="80" t="n">
+        <v>8</v>
+      </c>
+      <c r="B12" s="80" t="inlineStr">
+        <is>
+          <t>Bloc 2 — Costuri</t>
+        </is>
+      </c>
+      <c r="C12" s="80" t="str">
+        <f>Declarații_SALARII!B8</f>
+        <v>2026-07-31</v>
+      </c>
+      <c r="D12" s="80">
+        <f>Jurnale_SALARII!B23</f>
+        <v>421</v>
+      </c>
+      <c r="E12" s="80">
+        <f>Jurnale_SALARII!E23</f>
+        <v>425</v>
+      </c>
+      <c r="F12" s="80">
+        <f>Jurnale_SALARII!C23</f>
+        <v>0</v>
+      </c>
+      <c r="G12" s="80" t="str">
+        <f>Jurnale_SALARII!D23</f>
+        <v>Diminuarea datoriei salariale cu avansul acordat - 2026-07</v>
+      </c>
+      <c r="H12" s="80" t="inlineStr">
+        <is>
+          <t>Stat de plată</t>
+        </is>
+      </c>
+      <c r="I12" s="80" t="str">
+        <f>IF(N(F12)&gt;0,"DA","NU")</f>
+        <v>NU</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="80" t="n">
+        <v>9</v>
+      </c>
+      <c r="B13" s="80" t="inlineStr">
+        <is>
+          <t>Bloc 3 — Plăți</t>
+        </is>
+      </c>
+      <c r="C13" s="80" t="str">
+        <f>Declarații_SALARII!B9</f>
+        <v>2026-08-10</v>
+      </c>
+      <c r="D13" s="80">
+        <f>Jurnale_SALARII!B34</f>
+        <v>421</v>
+      </c>
+      <c r="E13" s="80" t="str">
+        <f>Jurnale_SALARII!E34</f>
+        <v>5121</v>
+      </c>
+      <c r="F13" s="80">
+        <f>Jurnale_SALARII!C34</f>
+        <v>40977</v>
+      </c>
+      <c r="G13" s="80" t="str">
+        <f>Jurnale_SALARII!D34</f>
+        <v>Plata salariilor nete - 2026-07</v>
+      </c>
+      <c r="H13" s="80" t="inlineStr">
+        <is>
+          <t>Stat de plată</t>
+        </is>
+      </c>
+      <c r="I13" s="80" t="str">
+        <f>IF(N(F13)&gt;0,"DA","NU")</f>
+        <v>DA</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="80" t="n">
+        <v>10</v>
+      </c>
+      <c r="B14" s="80" t="inlineStr">
+        <is>
+          <t>Bloc 3 — Plăți</t>
+        </is>
+      </c>
+      <c r="C14" s="80" t="str">
+        <f>Declarații_SALARII!B9</f>
+        <v>2026-08-10</v>
+      </c>
+      <c r="D14" s="80">
+        <f>Jurnale_SALARII!B35</f>
+        <v>4315</v>
+      </c>
+      <c r="E14" s="80" t="str">
+        <f>Jurnale_SALARII!E35</f>
+        <v>5121</v>
+      </c>
+      <c r="F14" s="80">
+        <f>Jurnale_SALARII!C35</f>
+        <v>17720</v>
+      </c>
+      <c r="G14" s="80" t="str">
+        <f>Jurnale_SALARII!D35</f>
+        <v>Stingerea datoriei CAS - 2026-07</v>
+      </c>
+      <c r="H14" s="80" t="inlineStr">
+        <is>
+          <t>Stat de plată</t>
+        </is>
+      </c>
+      <c r="I14" s="80" t="str">
+        <f>IF(N(F14)&gt;0,"DA","NU")</f>
+        <v>DA</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="80" t="n">
+        <v>11</v>
+      </c>
+      <c r="B15" s="80" t="inlineStr">
+        <is>
+          <t>Bloc 3 — Plăți</t>
+        </is>
+      </c>
+      <c r="C15" s="80" t="str">
+        <f>Declarații_SALARII!B9</f>
+        <v>2026-08-10</v>
+      </c>
+      <c r="D15" s="80">
+        <f>Jurnale_SALARII!B36</f>
+        <v>4316</v>
+      </c>
+      <c r="E15" s="80">
+        <f>Jurnale_SALARII!E36</f>
+        <v>0</v>
+      </c>
+      <c r="F15" s="80">
+        <f>Jurnale_SALARII!C36</f>
+        <v>7343</v>
+      </c>
+      <c r="G15" s="80" t="str">
+        <f>Jurnale_SALARII!D36</f>
+        <v>Stingerea datoriei CASS - 2026-07</v>
+      </c>
+      <c r="H15" s="80" t="inlineStr">
+        <is>
+          <t>Stat de plată</t>
+        </is>
+      </c>
+      <c r="I15" s="80" t="str">
+        <f>IF(N(F15)&gt;0,"DA","NU")</f>
+        <v>DA</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="80" t="n">
+        <v>12</v>
+      </c>
+      <c r="B16" s="80" t="inlineStr">
+        <is>
+          <t>Bloc 3 — Plăți</t>
+        </is>
+      </c>
+      <c r="C16" s="80" t="str">
+        <f>Declarații_SALARII!B9</f>
+        <v>2026-08-10</v>
+      </c>
+      <c r="D16" s="80">
+        <f>Jurnale_SALARII!B37</f>
+        <v>444</v>
+      </c>
+      <c r="E16" s="80">
+        <f>Jurnale_SALARII!E37</f>
+        <v>0</v>
+      </c>
+      <c r="F16" s="80">
+        <f>Jurnale_SALARII!C37</f>
+        <v>4837</v>
+      </c>
+      <c r="G16" s="80" t="str">
+        <f>Jurnale_SALARII!D37</f>
+        <v>Stingerea datoriei de impozit - 2026-07</v>
+      </c>
+      <c r="H16" s="80" t="inlineStr">
+        <is>
+          <t>Stat de plată</t>
+        </is>
+      </c>
+      <c r="I16" s="80" t="str">
+        <f>IF(N(F16)&gt;0,"DA","NU")</f>
+        <v>DA</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="80" t="n">
+        <v>13</v>
+      </c>
+      <c r="B17" s="80" t="inlineStr">
+        <is>
+          <t>Bloc 3 — Plăți</t>
+        </is>
+      </c>
+      <c r="C17" s="80" t="str">
+        <f>Declarații_SALARII!B9</f>
+        <v>2026-08-10</v>
+      </c>
+      <c r="D17" s="80">
+        <f>Jurnale_SALARII!B38</f>
+        <v>436</v>
+      </c>
+      <c r="E17" s="80" t="str">
+        <f>Jurnale_SALARII!E38</f>
+        <v>5121</v>
+      </c>
+      <c r="F17" s="80">
+        <f>Jurnale_SALARII!C38</f>
+        <v>1596</v>
+      </c>
+      <c r="G17" s="80" t="str">
+        <f>Jurnale_SALARII!D38</f>
+        <v>Stingerea datoriei CAM - 2026-07</v>
+      </c>
+      <c r="H17" s="80" t="inlineStr">
+        <is>
+          <t>Stat de plată</t>
+        </is>
+      </c>
+      <c r="I17" s="80" t="str">
+        <f>IF(N(F17)&gt;0,"DA","NU")</f>
+        <v>DA</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="80" t="inlineStr">
+        <is>
+          <t>Rânduri de importat (Include=DA)</t>
+        </is>
+      </c>
+      <c r="B19" s="80">
+        <f>COUNTIF(I5:I17,"DA")</f>
+        <v>9</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet52.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C30"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="40" customWidth="1" style="40" min="1" max="1"/>
+    <col width="22" customWidth="1" style="40" min="2" max="2"/>
+    <col width="58" customWidth="1" style="40" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="77" t="inlineStr">
+        <is>
+          <t>MOD_DECONT — Declarații (input)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="78" t="inlineStr">
+        <is>
+          <t>Antetul și politica de conturi se completează o dată. Liniile propriu-zise se lipesc în foaia Registru_DECONT. Valorile implicite sunt cele din decontul real din 31.07.2026, ca modulul să poată fi verificat contra lui.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="79" t="inlineStr">
+        <is>
+          <t>1. Antet</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="80" t="inlineStr">
+        <is>
+          <t>Societate</t>
+        </is>
+      </c>
+      <c r="B5" s="80" t="str">
+        <f>Parametri!B5</f>
+        <v>SC EXEMPLU SRL</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="80" t="inlineStr">
+        <is>
+          <t>Titular decont</t>
+        </is>
+      </c>
+      <c r="B6" s="81" t="inlineStr">
+        <is>
+          <t>CHIRIACESCU DIANA</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="80" t="inlineStr">
+        <is>
+          <t>Data decontului</t>
+        </is>
+      </c>
+      <c r="B7" s="81" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="80" t="inlineStr">
+        <is>
+          <t>Data plății / restituirii</t>
+        </is>
+      </c>
+      <c r="B8" s="81" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="79" t="inlineStr">
+        <is>
+          <t>2. Declarații fiscale</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="80" t="inlineStr">
+        <is>
+          <t>Societate plătitoare de TVA (DA / NU)</t>
+        </is>
+      </c>
+      <c r="B11" s="81" t="inlineStr">
+        <is>
+          <t>DA</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="80" t="inlineStr">
+        <is>
+          <t>Cotă TVA standard</t>
+        </is>
+      </c>
+      <c r="B12" s="80">
+        <f>Parametri!B10</f>
+        <v>0.21</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="80" t="inlineStr">
+        <is>
+          <t>Cotă TVA redusă</t>
+        </is>
+      </c>
+      <c r="B13" s="80">
+        <f>Parametri!B11</f>
+        <v>0.11</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="80" t="inlineStr">
+        <is>
+          <t>Procent deducere TVA vehicule</t>
+        </is>
+      </c>
+      <c r="B14" s="80">
+        <f>Parametri!B19</f>
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="79" t="inlineStr">
+        <is>
+          <t>3. Politica de conturi (comutatoare)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="80" t="inlineStr">
+        <is>
+          <t>Cont datorie față de titular</t>
+        </is>
+      </c>
+      <c r="B17" s="81" t="inlineStr">
+        <is>
+          <t>542</t>
+        </is>
+      </c>
+      <c r="C17" s="78" t="inlineStr">
+        <is>
+          <t>542 avansuri de trezorerie / 462 creditori / 4281 alte datorii</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="80" t="inlineStr">
+        <is>
+          <t>Cont avans de trezorerie</t>
+        </is>
+      </c>
+      <c r="B18" s="81" t="inlineStr">
+        <is>
+          <t>542</t>
+        </is>
+      </c>
+      <c r="C18" s="78" t="inlineStr">
+        <is>
+          <t>542 / 425</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="80" t="inlineStr">
+        <is>
+          <t>Cont transport și parcare</t>
+        </is>
+      </c>
+      <c r="B19" s="81" t="inlineStr">
+        <is>
+          <t>625</t>
+        </is>
+      </c>
+      <c r="C19" s="78" t="inlineStr">
+        <is>
+          <t>624 / 625 — comutator; 625 e convenția din decontul-sursă</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="80" t="inlineStr">
+        <is>
+          <t>Cont masă în deplasare</t>
+        </is>
+      </c>
+      <c r="B20" s="81" t="inlineStr">
+        <is>
+          <t>625</t>
+        </is>
+      </c>
+      <c r="C20" s="78" t="inlineStr">
+        <is>
+          <t>625 / 6231 / 6588 — comutator</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="80" t="inlineStr">
+        <is>
+          <t>Cont TVA deductibilă</t>
+        </is>
+      </c>
+      <c r="B21" s="81" t="n">
+        <v>4426</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="80" t="inlineStr">
+        <is>
+          <t>Cont trezorerie pentru plăți</t>
+        </is>
+      </c>
+      <c r="B22" s="81" t="inlineStr">
+        <is>
+          <t>5121</t>
+        </is>
+      </c>
+      <c r="C22" s="78" t="inlineStr">
+        <is>
+          <t>5121 / 5311</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="79" t="inlineStr">
+        <is>
+          <t>4. Avans și control</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="80" t="inlineStr">
+        <is>
+          <t>Avans primit (declarat în decont)</t>
+        </is>
+      </c>
+      <c r="B25" s="81" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="80" t="inlineStr">
+        <is>
+          <t>Sold cont avans din balanță</t>
+        </is>
+      </c>
+      <c r="B26" s="81" t="n">
+        <v>0</v>
+      </c>
+      <c r="C26" s="78" t="inlineStr">
+        <is>
+          <t>Din fișa contului, la data decontului</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="80" t="inlineStr">
+        <is>
+          <t>Verdict control avans</t>
+        </is>
+      </c>
+      <c r="B27" s="80">
+        <f>B26-B25</f>
+        <v>0</v>
+      </c>
+      <c r="C27" s="80" t="str">
+        <f>IF(ABS(B27)&lt;0.01,"OK — avansul declarat corespunde balanței","ATENȚIE — declarația titularului nu corespunde evidenței contabile")</f>
+        <v>OK — avansul declarat corespunde balanței</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="79" t="inlineStr">
+        <is>
+          <t>5. Sufix generat</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="80" t="inlineStr">
+        <is>
+          <t>Sufix</t>
+        </is>
+      </c>
+      <c r="B30" s="80" t="str">
+        <f>" - decont " &amp; B6 &amp; " " &amp; B7</f>
+        <v> - decont CHIRIACESCU DIANA 2026-07-31</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet53.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H29"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" style="40" min="1" max="1"/>
+    <col width="40" customWidth="1" style="40" min="2" max="2"/>
+    <col width="10" customWidth="1" style="40" min="3" max="3"/>
+    <col width="12" customWidth="1" style="40" min="4" max="4"/>
+    <col width="24" customWidth="1" style="40" min="5" max="5"/>
+    <col width="12" customWidth="1" style="40" min="6" max="6"/>
+    <col width="22" customWidth="1" style="40" min="7" max="7"/>
+    <col width="52" customWidth="1" style="40" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="77" t="inlineStr">
+        <is>
+          <t>MOD_DECONT — Reguli (tabele fixe)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="78" t="inlineStr">
+        <is>
+          <t>Regula fiscală e dată, nu formulă. Motorul din Registru caută în tabelele astea; se editează doar când se schimbă legea sau politica firmei.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="79" t="inlineStr">
+        <is>
+          <t>Tabel A — Natura cheltuielii</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="82" t="inlineStr">
+        <is>
+          <t>Cod</t>
+        </is>
+      </c>
+      <c r="B5" s="82" t="inlineStr">
+        <is>
+          <t>Denumire</t>
+        </is>
+      </c>
+      <c r="C5" s="82" t="inlineStr">
+        <is>
+          <t>Cont</t>
+        </is>
+      </c>
+      <c r="D5" s="82" t="inlineStr">
+        <is>
+          <t>Cotă TVA</t>
+        </is>
+      </c>
+      <c r="E5" s="82" t="inlineStr">
+        <is>
+          <t>Regim TVA</t>
+        </is>
+      </c>
+      <c r="F5" s="82" t="inlineStr">
+        <is>
+          <t>% deducere</t>
+        </is>
+      </c>
+      <c r="G5" s="82" t="inlineStr">
+        <is>
+          <t>Impozit pe profit</t>
+        </is>
+      </c>
+      <c r="H5" s="82" t="inlineStr">
+        <is>
+          <t>Temei / observație</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="80" t="inlineStr">
+        <is>
+          <t>TRANSP_INT</t>
+        </is>
+      </c>
+      <c r="B6" s="80" t="inlineStr">
+        <is>
+          <t>Transport aerian internațional de persoane</t>
+        </is>
+      </c>
+      <c r="C6" s="80" t="str">
+        <f>Declarații_DECONT!B19</f>
+        <v>625</v>
+      </c>
+      <c r="D6" s="80" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" s="80" t="inlineStr">
+        <is>
+          <t>Scutit cu drept de deducere</t>
+        </is>
+      </c>
+      <c r="F6" s="80" t="n">
+        <v>1</v>
+      </c>
+      <c r="G6" s="80" t="inlineStr">
+        <is>
+          <t>Deductibil</t>
+        </is>
+      </c>
+      <c r="H6" s="80" t="inlineStr">
+        <is>
+          <t>art. 294 alin. (1) — scutire cu drept de deducere, TVA zero</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="80" t="inlineStr">
+        <is>
+          <t>TRANSP_INTERN</t>
+        </is>
+      </c>
+      <c r="B7" s="80" t="inlineStr">
+        <is>
+          <t>Transport intern de persoane</t>
+        </is>
+      </c>
+      <c r="C7" s="80" t="str">
+        <f>Declarații_DECONT!B19</f>
+        <v>625</v>
+      </c>
+      <c r="D7" s="80">
+        <f>Declarații_DECONT!B13</f>
+        <v>0.11</v>
+      </c>
+      <c r="E7" s="80" t="inlineStr">
+        <is>
+          <t>Taxabil</t>
+        </is>
+      </c>
+      <c r="F7" s="80" t="n">
+        <v>1</v>
+      </c>
+      <c r="G7" s="80" t="inlineStr">
+        <is>
+          <t>Deductibil</t>
+        </is>
+      </c>
+      <c r="H7" s="80" t="inlineStr">
+        <is>
+          <t>cotă redusă pentru transportul de persoane</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="80" t="inlineStr">
+        <is>
+          <t>PARCARE</t>
+        </is>
+      </c>
+      <c r="B8" s="80" t="inlineStr">
+        <is>
+          <t>Parcare, taxe de drum</t>
+        </is>
+      </c>
+      <c r="C8" s="80" t="str">
+        <f>Declarații_DECONT!B19</f>
+        <v>625</v>
+      </c>
+      <c r="D8" s="80">
+        <f>Declarații_DECONT!B12</f>
+        <v>0.21</v>
+      </c>
+      <c r="E8" s="80" t="inlineStr">
+        <is>
+          <t>Taxabil</t>
+        </is>
+      </c>
+      <c r="F8" s="80" t="n">
+        <v>1</v>
+      </c>
+      <c r="G8" s="80" t="inlineStr">
+        <is>
+          <t>Deductibil</t>
+        </is>
+      </c>
+      <c r="H8" s="80" t="inlineStr">
+        <is>
+          <t>cotă standard</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="80" t="inlineStr">
+        <is>
+          <t>TAXI</t>
+        </is>
+      </c>
+      <c r="B9" s="80" t="inlineStr">
+        <is>
+          <t>Taxi, transfer aeroport</t>
+        </is>
+      </c>
+      <c r="C9" s="80" t="str">
+        <f>Declarații_DECONT!B19</f>
+        <v>625</v>
+      </c>
+      <c r="D9" s="80">
+        <f>Declarații_DECONT!B13</f>
+        <v>0.11</v>
+      </c>
+      <c r="E9" s="80" t="inlineStr">
+        <is>
+          <t>Taxabil</t>
+        </is>
+      </c>
+      <c r="F9" s="80" t="n">
+        <v>1</v>
+      </c>
+      <c r="G9" s="80" t="inlineStr">
+        <is>
+          <t>Deductibil</t>
+        </is>
+      </c>
+      <c r="H9" s="80" t="inlineStr">
+        <is>
+          <t>transport de persoane</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="80" t="inlineStr">
+        <is>
+          <t>CAZARE</t>
+        </is>
+      </c>
+      <c r="B10" s="80" t="inlineStr">
+        <is>
+          <t>Cazare hotelieră</t>
+        </is>
+      </c>
+      <c r="C10" s="80" t="str">
+        <f>Declarații_DECONT!B20</f>
+        <v>625</v>
+      </c>
+      <c r="D10" s="80">
+        <f>Declarații_DECONT!B13</f>
+        <v>0.11</v>
+      </c>
+      <c r="E10" s="80" t="inlineStr">
+        <is>
+          <t>Taxabil</t>
+        </is>
+      </c>
+      <c r="F10" s="80" t="n">
+        <v>1</v>
+      </c>
+      <c r="G10" s="80" t="inlineStr">
+        <is>
+          <t>Deductibil</t>
+        </is>
+      </c>
+      <c r="H10" s="80" t="inlineStr">
+        <is>
+          <t>cotă redusă HoReCa</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="80" t="inlineStr">
+        <is>
+          <t>MASA</t>
+        </is>
+      </c>
+      <c r="B11" s="80" t="inlineStr">
+        <is>
+          <t>Masă în deplasare</t>
+        </is>
+      </c>
+      <c r="C11" s="80" t="str">
+        <f>Declarații_DECONT!B20</f>
+        <v>625</v>
+      </c>
+      <c r="D11" s="80">
+        <f>Declarații_DECONT!B13</f>
+        <v>0.11</v>
+      </c>
+      <c r="E11" s="80" t="inlineStr">
+        <is>
+          <t>Taxabil</t>
+        </is>
+      </c>
+      <c r="F11" s="80" t="n">
+        <v>1</v>
+      </c>
+      <c r="G11" s="80" t="inlineStr">
+        <is>
+          <t>Deductibil</t>
+        </is>
+      </c>
+      <c r="H11" s="80" t="inlineStr">
+        <is>
+          <t>restaurant/catering; dacă se acordă diurnă, comută pe 6588</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="80" t="inlineStr">
+        <is>
+          <t>PROTOCOL</t>
+        </is>
+      </c>
+      <c r="B12" s="80" t="inlineStr">
+        <is>
+          <t>Protocol cu partener / client</t>
+        </is>
+      </c>
+      <c r="C12" s="80" t="inlineStr">
+        <is>
+          <t>6231</t>
+        </is>
+      </c>
+      <c r="D12" s="80">
+        <f>Declarații_DECONT!B13</f>
+        <v>0.11</v>
+      </c>
+      <c r="E12" s="80" t="inlineStr">
+        <is>
+          <t>Taxabil</t>
+        </is>
+      </c>
+      <c r="F12" s="80" t="n">
+        <v>1</v>
+      </c>
+      <c r="G12" s="80" t="inlineStr">
+        <is>
+          <t>Deductibil limitat 2%</t>
+        </is>
+      </c>
+      <c r="H12" s="80" t="inlineStr">
+        <is>
+          <t>limita de 2% din profitul contabil</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="80" t="inlineStr">
+        <is>
+          <t>COMBUSTIBIL</t>
+        </is>
+      </c>
+      <c r="B13" s="80" t="inlineStr">
+        <is>
+          <t>Combustibil auto</t>
+        </is>
+      </c>
+      <c r="C13" s="80" t="inlineStr">
+        <is>
+          <t>6022</t>
+        </is>
+      </c>
+      <c r="D13" s="80">
+        <f>Declarații_DECONT!B12</f>
+        <v>0.21</v>
+      </c>
+      <c r="E13" s="80" t="inlineStr">
+        <is>
+          <t>Taxabil</t>
+        </is>
+      </c>
+      <c r="F13" s="80">
+        <f>Declarații_DECONT!B14</f>
+        <v>0.5</v>
+      </c>
+      <c r="G13" s="80" t="inlineStr">
+        <is>
+          <t>Deductibil limitat 50%</t>
+        </is>
+      </c>
+      <c r="H13" s="80" t="inlineStr">
+        <is>
+          <t>art. 298 — deducere TVA 50% fără utilizare exclusivă</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="80" t="inlineStr">
+        <is>
+          <t>SERVICII</t>
+        </is>
+      </c>
+      <c r="B14" s="80" t="inlineStr">
+        <is>
+          <t>Alte servicii executate de terți</t>
+        </is>
+      </c>
+      <c r="C14" s="80" t="inlineStr">
+        <is>
+          <t>628</t>
+        </is>
+      </c>
+      <c r="D14" s="80">
+        <f>Declarații_DECONT!B12</f>
+        <v>0.21</v>
+      </c>
+      <c r="E14" s="80" t="inlineStr">
+        <is>
+          <t>Taxabil</t>
+        </is>
+      </c>
+      <c r="F14" s="80" t="n">
+        <v>1</v>
+      </c>
+      <c r="G14" s="80" t="inlineStr">
+        <is>
+          <t>Deductibil</t>
+        </is>
+      </c>
+      <c r="H14" s="80" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="80" t="inlineStr">
+        <is>
+          <t>MATERIALE</t>
+        </is>
+      </c>
+      <c r="B15" s="80" t="inlineStr">
+        <is>
+          <t>Materiale consumabile</t>
+        </is>
+      </c>
+      <c r="C15" s="80" t="inlineStr">
+        <is>
+          <t>6028</t>
+        </is>
+      </c>
+      <c r="D15" s="80">
+        <f>Declarații_DECONT!B12</f>
+        <v>0.21</v>
+      </c>
+      <c r="E15" s="80" t="inlineStr">
+        <is>
+          <t>Taxabil</t>
+        </is>
+      </c>
+      <c r="F15" s="80" t="n">
+        <v>1</v>
+      </c>
+      <c r="G15" s="80" t="inlineStr">
+        <is>
+          <t>Deductibil</t>
+        </is>
+      </c>
+      <c r="H15" s="80" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="80" t="inlineStr">
+        <is>
+          <t>PERSONAL</t>
+        </is>
+      </c>
+      <c r="B16" s="80" t="inlineStr">
+        <is>
+          <t>Cheltuială personală / nejustificată</t>
+        </is>
+      </c>
+      <c r="C16" s="80" t="inlineStr">
+        <is>
+          <t>6588</t>
+        </is>
+      </c>
+      <c r="D16" s="80" t="n">
+        <v>0</v>
+      </c>
+      <c r="E16" s="80" t="inlineStr">
+        <is>
+          <t>Fără drept de deducere</t>
+        </is>
+      </c>
+      <c r="F16" s="80" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" s="80" t="inlineStr">
+        <is>
+          <t>Nedeductibil</t>
+        </is>
+      </c>
+      <c r="H16" s="80" t="inlineStr">
+        <is>
+          <t>nu se acceptă la deducere fiscală</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="79" t="inlineStr">
+        <is>
+          <t>Tabel B — Matricea dreptului de deducere</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="78" t="inlineStr">
+        <is>
+          <t>Cheia e perechea „tip document | CUI pe document”. Aici se decide dacă TVA se deduce și dacă cheltuiala se acceptă la decont.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="82" t="inlineStr">
+        <is>
+          <t>Cheie</t>
+        </is>
+      </c>
+      <c r="B20" s="82" t="inlineStr">
+        <is>
+          <t>Tip document</t>
+        </is>
+      </c>
+      <c r="C20" s="82" t="inlineStr">
+        <is>
+          <t>CUI pe document</t>
+        </is>
+      </c>
+      <c r="D20" s="82" t="inlineStr">
+        <is>
+          <t>Deducere TVA</t>
+        </is>
+      </c>
+      <c r="E20" s="82" t="inlineStr">
+        <is>
+          <t>Cheltuială acceptată</t>
+        </is>
+      </c>
+      <c r="F20" s="82" t="inlineStr"/>
+      <c r="G20" s="82" t="inlineStr"/>
+      <c r="H20" s="82" t="inlineStr">
+        <is>
+          <t>Motivare</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="80" t="inlineStr">
+        <is>
+          <t>Factura|DA</t>
+        </is>
+      </c>
+      <c r="B21" s="80" t="inlineStr">
+        <is>
+          <t>Factura</t>
+        </is>
+      </c>
+      <c r="C21" s="80" t="inlineStr">
+        <is>
+          <t>DA</t>
+        </is>
+      </c>
+      <c r="D21" s="80" t="inlineStr">
+        <is>
+          <t>DA</t>
+        </is>
+      </c>
+      <c r="E21" s="80" t="inlineStr">
+        <is>
+          <t>DA</t>
+        </is>
+      </c>
+      <c r="H21" s="80" t="inlineStr">
+        <is>
+          <t>Factură completă conform art. 319 — TVA deductibil</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="80" t="inlineStr">
+        <is>
+          <t>Factura|NU</t>
+        </is>
+      </c>
+      <c r="B22" s="80" t="inlineStr">
+        <is>
+          <t>Factura</t>
+        </is>
+      </c>
+      <c r="C22" s="80" t="inlineStr">
+        <is>
+          <t>NU</t>
+        </is>
+      </c>
+      <c r="D22" s="80" t="inlineStr">
+        <is>
+          <t>NU</t>
+        </is>
+      </c>
+      <c r="E22" s="80" t="inlineStr">
+        <is>
+          <t>DA</t>
+        </is>
+      </c>
+      <c r="H22" s="80" t="inlineStr">
+        <is>
+          <t>Lipsesc datele cumpărătorului — TVA nedeductibil, cheltuiala rămâne acceptată</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="80" t="inlineStr">
+        <is>
+          <t>Bon fiscal|DA</t>
+        </is>
+      </c>
+      <c r="B23" s="80" t="inlineStr">
+        <is>
+          <t>Bon fiscal</t>
+        </is>
+      </c>
+      <c r="C23" s="80" t="inlineStr">
+        <is>
+          <t>DA</t>
+        </is>
+      </c>
+      <c r="D23" s="80" t="inlineStr">
+        <is>
+          <t>DA</t>
+        </is>
+      </c>
+      <c r="E23" s="80" t="inlineStr">
+        <is>
+          <t>DA</t>
+        </is>
+      </c>
+      <c r="H23" s="80" t="inlineStr">
+        <is>
+          <t>Factură simplificată — deducere permisă sub plafonul de 100 EUR</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="80" t="inlineStr">
+        <is>
+          <t>Bon fiscal|NU</t>
+        </is>
+      </c>
+      <c r="B24" s="80" t="inlineStr">
+        <is>
+          <t>Bon fiscal</t>
+        </is>
+      </c>
+      <c r="C24" s="80" t="inlineStr">
+        <is>
+          <t>NU</t>
+        </is>
+      </c>
+      <c r="D24" s="80" t="inlineStr">
+        <is>
+          <t>NU</t>
+        </is>
+      </c>
+      <c r="E24" s="80" t="inlineStr">
+        <is>
+          <t>DA</t>
+        </is>
+      </c>
+      <c r="H24" s="80" t="inlineStr">
+        <is>
+          <t>Bon fără CUI — TVA nedeductibil; justificare cu ordin de deplasare</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="80" t="inlineStr">
+        <is>
+          <t>Lipsa document|DA</t>
+        </is>
+      </c>
+      <c r="B25" s="80" t="inlineStr">
+        <is>
+          <t>Lipsa document</t>
+        </is>
+      </c>
+      <c r="C25" s="80" t="inlineStr">
+        <is>
+          <t>DA</t>
+        </is>
+      </c>
+      <c r="D25" s="80" t="inlineStr">
+        <is>
+          <t>NU</t>
+        </is>
+      </c>
+      <c r="E25" s="80" t="inlineStr">
+        <is>
+          <t>NU</t>
+        </is>
+      </c>
+      <c r="H25" s="80" t="inlineStr">
+        <is>
+          <t>Fără document justificativ — decontul nu se acceptă</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="80" t="inlineStr">
+        <is>
+          <t>Lipsa document|NU</t>
+        </is>
+      </c>
+      <c r="B26" s="80" t="inlineStr">
+        <is>
+          <t>Lipsa document</t>
+        </is>
+      </c>
+      <c r="C26" s="80" t="inlineStr">
+        <is>
+          <t>NU</t>
+        </is>
+      </c>
+      <c r="D26" s="80" t="inlineStr">
+        <is>
+          <t>NU</t>
+        </is>
+      </c>
+      <c r="E26" s="80" t="inlineStr">
+        <is>
+          <t>NU</t>
+        </is>
+      </c>
+      <c r="H26" s="80" t="inlineStr">
+        <is>
+          <t>Fără document justificativ — decontul nu se acceptă</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="79" t="inlineStr">
+        <is>
+          <t>Tabel C — Limitare cunoscută</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="80" t="inlineStr">
+        <is>
+          <t>Liniile fără document justificativ nu se înregistrează pe cheltuială. Dacă suma se plătește totuși titularului, ea devine avantaj de natură salarială și se impozitează prin statul de plată (impozit + contribuții) — tratament care ține de MOD_SALARII. Modulul le ține separat, nu le calculează.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet54.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:P24"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="5" customWidth="1" style="40" min="1" max="1"/>
+    <col width="28" customWidth="1" style="40" min="2" max="2"/>
+    <col width="12" customWidth="1" style="40" min="3" max="3"/>
+    <col width="12" customWidth="1" style="40" min="4" max="4"/>
+    <col width="14" customWidth="1" style="40" min="5" max="5"/>
+    <col width="12" customWidth="1" style="40" min="6" max="6"/>
+    <col width="10" customWidth="1" style="40" min="7" max="7"/>
+    <col width="10" customWidth="1" style="40" min="8" max="8"/>
+    <col width="10" customWidth="1" style="40" min="9" max="9"/>
+    <col width="10" customWidth="1" style="40" min="10" max="10"/>
+    <col width="10" customWidth="1" style="40" min="11" max="11"/>
+    <col width="14" customWidth="1" style="40" min="12" max="12"/>
+    <col width="14" customWidth="1" style="40" min="13" max="13"/>
+    <col width="14" customWidth="1" style="40" min="14" max="14"/>
+    <col width="18" customWidth="1" style="40" min="15" max="15"/>
+    <col width="56" customWidth="1" style="40" min="16" max="16"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="77" t="inlineStr">
+        <is>
+          <t>MOD_DECONT — Registrul liniilor</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="78" t="inlineStr">
+        <is>
+          <t>Completează galben coloanele B–G. Coloanele H–P sunt formule: contul, cota, regimul și dreptul de deducere se citesc din Reguli. Coloana „Regula aplicată” spune de ce a ieșit așa.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="82" t="inlineStr">
+        <is>
+          <t>Nr.</t>
+        </is>
+      </c>
+      <c r="B4" s="82" t="inlineStr">
+        <is>
+          <t>Furnizor</t>
+        </is>
+      </c>
+      <c r="C4" s="82" t="inlineStr">
+        <is>
+          <t>Data doc.</t>
+        </is>
+      </c>
+      <c r="D4" s="82" t="inlineStr">
+        <is>
+          <t>Sumă brută</t>
+        </is>
+      </c>
+      <c r="E4" s="82" t="inlineStr">
+        <is>
+          <t>Natura chelt.</t>
+        </is>
+      </c>
+      <c r="F4" s="82" t="inlineStr">
+        <is>
+          <t>Tip document</t>
+        </is>
+      </c>
+      <c r="G4" s="82" t="inlineStr">
+        <is>
+          <t>CUI pe doc.</t>
+        </is>
+      </c>
+      <c r="H4" s="82" t="inlineStr">
+        <is>
+          <t>Cont</t>
+        </is>
+      </c>
+      <c r="I4" s="82" t="inlineStr">
+        <is>
+          <t>Cotă</t>
+        </is>
+      </c>
+      <c r="J4" s="82" t="inlineStr">
+        <is>
+          <t>% ded.</t>
+        </is>
+      </c>
+      <c r="K4" s="82" t="inlineStr">
+        <is>
+          <t>Deducere TVA</t>
+        </is>
+      </c>
+      <c r="L4" s="82" t="inlineStr">
+        <is>
+          <t>Acceptat</t>
+        </is>
+      </c>
+      <c r="M4" s="82" t="inlineStr">
+        <is>
+          <t>Bază cheltuială</t>
+        </is>
+      </c>
+      <c r="N4" s="82" t="inlineStr">
+        <is>
+          <t>TVA deductibil</t>
+        </is>
+      </c>
+      <c r="O4" s="82" t="inlineStr">
+        <is>
+          <t>Impozit pe profit</t>
+        </is>
+      </c>
+      <c r="P4" s="82" t="inlineStr">
+        <is>
+          <t>Regula aplicată</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="80" t="n">
+        <v>1</v>
+      </c>
+      <c r="B5" s="81" t="inlineStr">
+        <is>
+          <t>WIZZ AIR MALTA LIMITED</t>
+        </is>
+      </c>
+      <c r="C5" s="81" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="D5" s="81" t="n">
+        <v>1780.38</v>
+      </c>
+      <c r="E5" s="81" t="inlineStr">
+        <is>
+          <t>TRANSP_INT</t>
+        </is>
+      </c>
+      <c r="F5" s="81" t="inlineStr">
+        <is>
+          <t>Factura</t>
+        </is>
+      </c>
+      <c r="G5" s="81" t="inlineStr">
+        <is>
+          <t>DA</t>
+        </is>
+      </c>
+      <c r="H5" s="80" t="str">
+        <f>IF($D5="","",IFERROR(VLOOKUP($E5,Reguli_DECONT!$A$6:$H$16,3,FALSE),"?"))</f>
+        <v>625</v>
+      </c>
+      <c r="I5" s="80">
+        <f>IF($D5="","",IFERROR(VLOOKUP($E5,Reguli_DECONT!$A$6:$H$16,4,FALSE),0))</f>
+        <v>0</v>
+      </c>
+      <c r="J5" s="80">
+        <f>IF($D5="","",IFERROR(VLOOKUP($E5,Reguli_DECONT!$A$6:$H$16,6,FALSE),0))</f>
+        <v>1</v>
+      </c>
+      <c r="K5" s="80" t="str">
+        <f>IF($D5="","",IF(Declarații_DECONT!B11&lt;&gt;"DA","NU",IFERROR(VLOOKUP($F5&amp;"|"&amp;$G5,Reguli_DECONT!$A$21:$H$26,4,FALSE),"NU")))</f>
+        <v>DA</v>
+      </c>
+      <c r="L5" s="80" t="str">
+        <f>IF($D5="","",IFERROR(VLOOKUP($F5&amp;"|"&amp;$G5,Reguli_DECONT!$A$21:$H$26,5,FALSE),"NU"))</f>
+        <v>DA</v>
+      </c>
+      <c r="M5" s="80">
+        <f>IF($D5="","",IF($L5&lt;&gt;"DA",0,$D5-$N5))</f>
+        <v>1780.38</v>
+      </c>
+      <c r="N5" s="80">
+        <f>IF($D5="","",IF($L5&lt;&gt;"DA",0,IF($K5&lt;&gt;"DA",0,ROUND($D5*$I5/(1+$I5)*$J5,2))))</f>
+        <v>0</v>
+      </c>
+      <c r="O5" s="80" t="str">
+        <f>IF($D5="","",IFERROR(VLOOKUP($E5,Reguli_DECONT!$A$6:$H$16,7,FALSE),"?"))</f>
+        <v>Deductibil</v>
+      </c>
+      <c r="P5" s="78" t="str">
+        <f>IF($D5="","",IFERROR(VLOOKUP($F5&amp;"|"&amp;$G5,Reguli_DECONT!$A$21:$H$26,8,FALSE),"cod de natură necunoscut"))</f>
+        <v>Factură completă conform art. 319 — TVA deductibil</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="80" t="n">
+        <v>2</v>
+      </c>
+      <c r="B6" s="81" t="inlineStr">
+        <is>
+          <t>WIZZ AIR MALTA LIMITED</t>
+        </is>
+      </c>
+      <c r="C6" s="81" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="D6" s="81" t="n">
+        <v>1720.38</v>
+      </c>
+      <c r="E6" s="81" t="inlineStr">
+        <is>
+          <t>TRANSP_INT</t>
+        </is>
+      </c>
+      <c r="F6" s="81" t="inlineStr">
+        <is>
+          <t>Factura</t>
+        </is>
+      </c>
+      <c r="G6" s="81" t="inlineStr">
+        <is>
+          <t>DA</t>
+        </is>
+      </c>
+      <c r="H6" s="80" t="str">
+        <f>IF($D6="","",IFERROR(VLOOKUP($E6,Reguli_DECONT!$A$6:$H$16,3,FALSE),"?"))</f>
+        <v>625</v>
+      </c>
+      <c r="I6" s="80">
+        <f>IF($D6="","",IFERROR(VLOOKUP($E6,Reguli_DECONT!$A$6:$H$16,4,FALSE),0))</f>
+        <v>0</v>
+      </c>
+      <c r="J6" s="80">
+        <f>IF($D6="","",IFERROR(VLOOKUP($E6,Reguli_DECONT!$A$6:$H$16,6,FALSE),0))</f>
+        <v>1</v>
+      </c>
+      <c r="K6" s="80" t="str">
+        <f>IF($D6="","",IF(Declarații_DECONT!B11&lt;&gt;"DA","NU",IFERROR(VLOOKUP($F6&amp;"|"&amp;$G6,Reguli_DECONT!$A$21:$H$26,4,FALSE),"NU")))</f>
+        <v>DA</v>
+      </c>
+      <c r="L6" s="80" t="str">
+        <f>IF($D6="","",IFERROR(VLOOKUP($F6&amp;"|"&amp;$G6,Reguli_DECONT!$A$21:$H$26,5,FALSE),"NU"))</f>
+        <v>DA</v>
+      </c>
+      <c r="M6" s="80">
+        <f>IF($D6="","",IF($L6&lt;&gt;"DA",0,$D6-$N6))</f>
+        <v>1720.38</v>
+      </c>
+      <c r="N6" s="80">
+        <f>IF($D6="","",IF($L6&lt;&gt;"DA",0,IF($K6&lt;&gt;"DA",0,ROUND($D6*$I6/(1+$I6)*$J6,2))))</f>
+        <v>0</v>
+      </c>
+      <c r="O6" s="80" t="str">
+        <f>IF($D6="","",IFERROR(VLOOKUP($E6,Reguli_DECONT!$A$6:$H$16,7,FALSE),"?"))</f>
+        <v>Deductibil</v>
+      </c>
+      <c r="P6" s="78" t="str">
+        <f>IF($D6="","",IFERROR(VLOOKUP($F6&amp;"|"&amp;$G6,Reguli_DECONT!$A$21:$H$26,8,FALSE),"cod de natură necunoscut"))</f>
+        <v>Factură completă conform art. 319 — TVA deductibil</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="80" t="n">
+        <v>3</v>
+      </c>
+      <c r="B7" s="81" t="inlineStr">
+        <is>
+          <t>CITY CAFÉ EXPRESS</t>
+        </is>
+      </c>
+      <c r="C7" s="81" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="D7" s="81" t="n">
+        <v>38</v>
+      </c>
+      <c r="E7" s="81" t="inlineStr">
+        <is>
+          <t>MASA</t>
+        </is>
+      </c>
+      <c r="F7" s="81" t="inlineStr">
+        <is>
+          <t>Bon fiscal</t>
+        </is>
+      </c>
+      <c r="G7" s="81" t="inlineStr">
+        <is>
+          <t>NU</t>
+        </is>
+      </c>
+      <c r="H7" s="80" t="str">
+        <f>IF($D7="","",IFERROR(VLOOKUP($E7,Reguli_DECONT!$A$6:$H$16,3,FALSE),"?"))</f>
+        <v>625</v>
+      </c>
+      <c r="I7" s="80">
+        <f>IF($D7="","",IFERROR(VLOOKUP($E7,Reguli_DECONT!$A$6:$H$16,4,FALSE),0))</f>
+        <v>0.11</v>
+      </c>
+      <c r="J7" s="80">
+        <f>IF($D7="","",IFERROR(VLOOKUP($E7,Reguli_DECONT!$A$6:$H$16,6,FALSE),0))</f>
+        <v>1</v>
+      </c>
+      <c r="K7" s="80" t="str">
+        <f>IF($D7="","",IF(Declarații_DECONT!B11&lt;&gt;"DA","NU",IFERROR(VLOOKUP($F7&amp;"|"&amp;$G7,Reguli_DECONT!$A$21:$H$26,4,FALSE),"NU")))</f>
+        <v>NU</v>
+      </c>
+      <c r="L7" s="80" t="str">
+        <f>IF($D7="","",IFERROR(VLOOKUP($F7&amp;"|"&amp;$G7,Reguli_DECONT!$A$21:$H$26,5,FALSE),"NU"))</f>
+        <v>DA</v>
+      </c>
+      <c r="M7" s="80">
+        <f>IF($D7="","",IF($L7&lt;&gt;"DA",0,$D7-$N7))</f>
+        <v>38</v>
+      </c>
+      <c r="N7" s="80">
+        <f>IF($D7="","",IF($L7&lt;&gt;"DA",0,IF($K7&lt;&gt;"DA",0,ROUND($D7*$I7/(1+$I7)*$J7,2))))</f>
+        <v>0</v>
+      </c>
+      <c r="O7" s="80" t="str">
+        <f>IF($D7="","",IFERROR(VLOOKUP($E7,Reguli_DECONT!$A$6:$H$16,7,FALSE),"?"))</f>
+        <v>Deductibil</v>
+      </c>
+      <c r="P7" s="78" t="str">
+        <f>IF($D7="","",IFERROR(VLOOKUP($F7&amp;"|"&amp;$G7,Reguli_DECONT!$A$21:$H$26,8,FALSE),"cod de natură necunoscut"))</f>
+        <v>Bon fără CUI — TVA nedeductibil; justificare cu ordin de deplasare</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="80" t="n">
+        <v>4</v>
+      </c>
+      <c r="B8" s="81" t="inlineStr">
+        <is>
+          <t>OLIMPIA PARKING</t>
+        </is>
+      </c>
+      <c r="C8" s="81" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="D8" s="81" t="n">
+        <v>200</v>
+      </c>
+      <c r="E8" s="81" t="inlineStr">
+        <is>
+          <t>PARCARE</t>
+        </is>
+      </c>
+      <c r="F8" s="81" t="inlineStr">
+        <is>
+          <t>Bon fiscal</t>
+        </is>
+      </c>
+      <c r="G8" s="81" t="inlineStr">
+        <is>
+          <t>NU</t>
+        </is>
+      </c>
+      <c r="H8" s="80" t="str">
+        <f>IF($D8="","",IFERROR(VLOOKUP($E8,Reguli_DECONT!$A$6:$H$16,3,FALSE),"?"))</f>
+        <v>625</v>
+      </c>
+      <c r="I8" s="80">
+        <f>IF($D8="","",IFERROR(VLOOKUP($E8,Reguli_DECONT!$A$6:$H$16,4,FALSE),0))</f>
+        <v>0.21</v>
+      </c>
+      <c r="J8" s="80">
+        <f>IF($D8="","",IFERROR(VLOOKUP($E8,Reguli_DECONT!$A$6:$H$16,6,FALSE),0))</f>
+        <v>1</v>
+      </c>
+      <c r="K8" s="80" t="str">
+        <f>IF($D8="","",IF(Declarații_DECONT!B11&lt;&gt;"DA","NU",IFERROR(VLOOKUP($F8&amp;"|"&amp;$G8,Reguli_DECONT!$A$21:$H$26,4,FALSE),"NU")))</f>
+        <v>NU</v>
+      </c>
+      <c r="L8" s="80" t="str">
+        <f>IF($D8="","",IFERROR(VLOOKUP($F8&amp;"|"&amp;$G8,Reguli_DECONT!$A$21:$H$26,5,FALSE),"NU"))</f>
+        <v>DA</v>
+      </c>
+      <c r="M8" s="80">
+        <f>IF($D8="","",IF($L8&lt;&gt;"DA",0,$D8-$N8))</f>
+        <v>200</v>
+      </c>
+      <c r="N8" s="80">
+        <f>IF($D8="","",IF($L8&lt;&gt;"DA",0,IF($K8&lt;&gt;"DA",0,ROUND($D8*$I8/(1+$I8)*$J8,2))))</f>
+        <v>0</v>
+      </c>
+      <c r="O8" s="80" t="str">
+        <f>IF($D8="","",IFERROR(VLOOKUP($E8,Reguli_DECONT!$A$6:$H$16,7,FALSE),"?"))</f>
+        <v>Deductibil</v>
+      </c>
+      <c r="P8" s="78" t="str">
+        <f>IF($D8="","",IFERROR(VLOOKUP($F8&amp;"|"&amp;$G8,Reguli_DECONT!$A$21:$H$26,8,FALSE),"cod de natură necunoscut"))</f>
+        <v>Bon fără CUI — TVA nedeductibil; justificare cu ordin de deplasare</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="80" t="n">
+        <v>5</v>
+      </c>
+      <c r="B9" s="81" t="inlineStr">
+        <is>
+          <t>OLIMPIA PARKING</t>
+        </is>
+      </c>
+      <c r="C9" s="81" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="D9" s="81" t="n">
+        <v>200</v>
+      </c>
+      <c r="E9" s="81" t="inlineStr">
+        <is>
+          <t>PARCARE</t>
+        </is>
+      </c>
+      <c r="F9" s="81" t="inlineStr">
+        <is>
+          <t>Bon fiscal</t>
+        </is>
+      </c>
+      <c r="G9" s="81" t="inlineStr">
+        <is>
+          <t>NU</t>
+        </is>
+      </c>
+      <c r="H9" s="80" t="str">
+        <f>IF($D9="","",IFERROR(VLOOKUP($E9,Reguli_DECONT!$A$6:$H$16,3,FALSE),"?"))</f>
+        <v>625</v>
+      </c>
+      <c r="I9" s="80">
+        <f>IF($D9="","",IFERROR(VLOOKUP($E9,Reguli_DECONT!$A$6:$H$16,4,FALSE),0))</f>
+        <v>0.21</v>
+      </c>
+      <c r="J9" s="80">
+        <f>IF($D9="","",IFERROR(VLOOKUP($E9,Reguli_DECONT!$A$6:$H$16,6,FALSE),0))</f>
+        <v>1</v>
+      </c>
+      <c r="K9" s="80" t="str">
+        <f>IF($D9="","",IF(Declarații_DECONT!B11&lt;&gt;"DA","NU",IFERROR(VLOOKUP($F9&amp;"|"&amp;$G9,Reguli_DECONT!$A$21:$H$26,4,FALSE),"NU")))</f>
+        <v>NU</v>
+      </c>
+      <c r="L9" s="80" t="str">
+        <f>IF($D9="","",IFERROR(VLOOKUP($F9&amp;"|"&amp;$G9,Reguli_DECONT!$A$21:$H$26,5,FALSE),"NU"))</f>
+        <v>DA</v>
+      </c>
+      <c r="M9" s="80">
+        <f>IF($D9="","",IF($L9&lt;&gt;"DA",0,$D9-$N9))</f>
+        <v>200</v>
+      </c>
+      <c r="N9" s="80">
+        <f>IF($D9="","",IF($L9&lt;&gt;"DA",0,IF($K9&lt;&gt;"DA",0,ROUND($D9*$I9/(1+$I9)*$J9,2))))</f>
+        <v>0</v>
+      </c>
+      <c r="O9" s="80" t="str">
+        <f>IF($D9="","",IFERROR(VLOOKUP($E9,Reguli_DECONT!$A$6:$H$16,7,FALSE),"?"))</f>
+        <v>Deductibil</v>
+      </c>
+      <c r="P9" s="78" t="str">
+        <f>IF($D9="","",IFERROR(VLOOKUP($F9&amp;"|"&amp;$G9,Reguli_DECONT!$A$21:$H$26,8,FALSE),"cod de natură necunoscut"))</f>
+        <v>Bon fără CUI — TVA nedeductibil; justificare cu ordin de deplasare</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="80" t="n">
+        <v>6</v>
+      </c>
+      <c r="B10" s="81" t="inlineStr"/>
+      <c r="C10" s="81" t="n"/>
+      <c r="D10" s="81" t="n"/>
+      <c r="E10" s="81" t="inlineStr"/>
+      <c r="F10" s="81" t="inlineStr"/>
+      <c r="G10" s="81" t="inlineStr"/>
+      <c r="H10" s="80">
+        <f>IF($D10="","",IFERROR(VLOOKUP($E10,Reguli_DECONT!$A$6:$H$16,3,FALSE),"?"))</f>
+        <v/>
+      </c>
+      <c r="I10" s="80">
+        <f>IF($D10="","",IFERROR(VLOOKUP($E10,Reguli_DECONT!$A$6:$H$16,4,FALSE),0))</f>
+        <v/>
+      </c>
+      <c r="J10" s="80">
+        <f>IF($D10="","",IFERROR(VLOOKUP($E10,Reguli_DECONT!$A$6:$H$16,6,FALSE),0))</f>
+        <v/>
+      </c>
+      <c r="K10" s="80">
+        <f>IF($D10="","",IF(Declarații_DECONT!B11&lt;&gt;"DA","NU",IFERROR(VLOOKUP($F10&amp;"|"&amp;$G10,Reguli_DECONT!$A$21:$H$26,4,FALSE),"NU")))</f>
+        <v/>
+      </c>
+      <c r="L10" s="80">
+        <f>IF($D10="","",IFERROR(VLOOKUP($F10&amp;"|"&amp;$G10,Reguli_DECONT!$A$21:$H$26,5,FALSE),"NU"))</f>
+        <v/>
+      </c>
+      <c r="M10" s="80">
+        <f>IF($D10="","",IF($L10&lt;&gt;"DA",0,$D10-$N10))</f>
+        <v/>
+      </c>
+      <c r="N10" s="80">
+        <f>IF($D10="","",IF($L10&lt;&gt;"DA",0,IF($K10&lt;&gt;"DA",0,ROUND($D10*$I10/(1+$I10)*$J10,2))))</f>
+        <v/>
+      </c>
+      <c r="O10" s="80">
+        <f>IF($D10="","",IFERROR(VLOOKUP($E10,Reguli_DECONT!$A$6:$H$16,7,FALSE),"?"))</f>
+        <v/>
+      </c>
+      <c r="P10" s="78">
+        <f>IF($D10="","",IFERROR(VLOOKUP($F10&amp;"|"&amp;$G10,Reguli_DECONT!$A$21:$H$26,8,FALSE),"cod de natură necunoscut"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="80" t="n">
+        <v>7</v>
+      </c>
+      <c r="B11" s="81" t="inlineStr"/>
+      <c r="C11" s="81" t="n"/>
+      <c r="D11" s="81" t="n"/>
+      <c r="E11" s="81" t="inlineStr"/>
+      <c r="F11" s="81" t="inlineStr"/>
+      <c r="G11" s="81" t="inlineStr"/>
+      <c r="H11" s="80">
+        <f>IF($D11="","",IFERROR(VLOOKUP($E11,Reguli_DECONT!$A$6:$H$16,3,FALSE),"?"))</f>
+        <v/>
+      </c>
+      <c r="I11" s="80">
+        <f>IF($D11="","",IFERROR(VLOOKUP($E11,Reguli_DECONT!$A$6:$H$16,4,FALSE),0))</f>
+        <v/>
+      </c>
+      <c r="J11" s="80">
+        <f>IF($D11="","",IFERROR(VLOOKUP($E11,Reguli_DECONT!$A$6:$H$16,6,FALSE),0))</f>
+        <v/>
+      </c>
+      <c r="K11" s="80">
+        <f>IF($D11="","",IF(Declarații_DECONT!B11&lt;&gt;"DA","NU",IFERROR(VLOOKUP($F11&amp;"|"&amp;$G11,Reguli_DECONT!$A$21:$H$26,4,FALSE),"NU")))</f>
+        <v/>
+      </c>
+      <c r="L11" s="80">
+        <f>IF($D11="","",IFERROR(VLOOKUP($F11&amp;"|"&amp;$G11,Reguli_DECONT!$A$21:$H$26,5,FALSE),"NU"))</f>
+        <v/>
+      </c>
+      <c r="M11" s="80">
+        <f>IF($D11="","",IF($L11&lt;&gt;"DA",0,$D11-$N11))</f>
+        <v/>
+      </c>
+      <c r="N11" s="80">
+        <f>IF($D11="","",IF($L11&lt;&gt;"DA",0,IF($K11&lt;&gt;"DA",0,ROUND($D11*$I11/(1+$I11)*$J11,2))))</f>
+        <v/>
+      </c>
+      <c r="O11" s="80">
+        <f>IF($D11="","",IFERROR(VLOOKUP($E11,Reguli_DECONT!$A$6:$H$16,7,FALSE),"?"))</f>
+        <v/>
+      </c>
+      <c r="P11" s="78">
+        <f>IF($D11="","",IFERROR(VLOOKUP($F11&amp;"|"&amp;$G11,Reguli_DECONT!$A$21:$H$26,8,FALSE),"cod de natură necunoscut"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="80" t="n">
+        <v>8</v>
+      </c>
+      <c r="B12" s="81" t="inlineStr"/>
+      <c r="C12" s="81" t="n"/>
+      <c r="D12" s="81" t="n"/>
+      <c r="E12" s="81" t="inlineStr"/>
+      <c r="F12" s="81" t="inlineStr"/>
+      <c r="G12" s="81" t="inlineStr"/>
+      <c r="H12" s="80">
+        <f>IF($D12="","",IFERROR(VLOOKUP($E12,Reguli_DECONT!$A$6:$H$16,3,FALSE),"?"))</f>
+        <v/>
+      </c>
+      <c r="I12" s="80">
+        <f>IF($D12="","",IFERROR(VLOOKUP($E12,Reguli_DECONT!$A$6:$H$16,4,FALSE),0))</f>
+        <v/>
+      </c>
+      <c r="J12" s="80">
+        <f>IF($D12="","",IFERROR(VLOOKUP($E12,Reguli_DECONT!$A$6:$H$16,6,FALSE),0))</f>
+        <v/>
+      </c>
+      <c r="K12" s="80">
+        <f>IF($D12="","",IF(Declarații_DECONT!B11&lt;&gt;"DA","NU",IFERROR(VLOOKUP($F12&amp;"|"&amp;$G12,Reguli_DECONT!$A$21:$H$26,4,FALSE),"NU")))</f>
+        <v/>
+      </c>
+      <c r="L12" s="80">
+        <f>IF($D12="","",IFERROR(VLOOKUP($F12&amp;"|"&amp;$G12,Reguli_DECONT!$A$21:$H$26,5,FALSE),"NU"))</f>
+        <v/>
+      </c>
+      <c r="M12" s="80">
+        <f>IF($D12="","",IF($L12&lt;&gt;"DA",0,$D12-$N12))</f>
+        <v/>
+      </c>
+      <c r="N12" s="80">
+        <f>IF($D12="","",IF($L12&lt;&gt;"DA",0,IF($K12&lt;&gt;"DA",0,ROUND($D12*$I12/(1+$I12)*$J12,2))))</f>
+        <v/>
+      </c>
+      <c r="O12" s="80">
+        <f>IF($D12="","",IFERROR(VLOOKUP($E12,Reguli_DECONT!$A$6:$H$16,7,FALSE),"?"))</f>
+        <v/>
+      </c>
+      <c r="P12" s="78">
+        <f>IF($D12="","",IFERROR(VLOOKUP($F12&amp;"|"&amp;$G12,Reguli_DECONT!$A$21:$H$26,8,FALSE),"cod de natură necunoscut"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="80" t="n">
+        <v>9</v>
+      </c>
+      <c r="B13" s="81" t="inlineStr"/>
+      <c r="C13" s="81" t="n"/>
+      <c r="D13" s="81" t="n"/>
+      <c r="E13" s="81" t="inlineStr"/>
+      <c r="F13" s="81" t="inlineStr"/>
+      <c r="G13" s="81" t="inlineStr"/>
+      <c r="H13" s="80">
+        <f>IF($D13="","",IFERROR(VLOOKUP($E13,Reguli_DECONT!$A$6:$H$16,3,FALSE),"?"))</f>
+        <v/>
+      </c>
+      <c r="I13" s="80">
+        <f>IF($D13="","",IFERROR(VLOOKUP($E13,Reguli_DECONT!$A$6:$H$16,4,FALSE),0))</f>
+        <v/>
+      </c>
+      <c r="J13" s="80">
+        <f>IF($D13="","",IFERROR(VLOOKUP($E13,Reguli_DECONT!$A$6:$H$16,6,FALSE),0))</f>
+        <v/>
+      </c>
+      <c r="K13" s="80">
+        <f>IF($D13="","",IF(Declarații_DECONT!B11&lt;&gt;"DA","NU",IFERROR(VLOOKUP($F13&amp;"|"&amp;$G13,Reguli_DECONT!$A$21:$H$26,4,FALSE),"NU")))</f>
+        <v/>
+      </c>
+      <c r="L13" s="80">
+        <f>IF($D13="","",IFERROR(VLOOKUP($F13&amp;"|"&amp;$G13,Reguli_DECONT!$A$21:$H$26,5,FALSE),"NU"))</f>
+        <v/>
+      </c>
+      <c r="M13" s="80">
+        <f>IF($D13="","",IF($L13&lt;&gt;"DA",0,$D13-$N13))</f>
+        <v/>
+      </c>
+      <c r="N13" s="80">
+        <f>IF($D13="","",IF($L13&lt;&gt;"DA",0,IF($K13&lt;&gt;"DA",0,ROUND($D13*$I13/(1+$I13)*$J13,2))))</f>
+        <v/>
+      </c>
+      <c r="O13" s="80">
+        <f>IF($D13="","",IFERROR(VLOOKUP($E13,Reguli_DECONT!$A$6:$H$16,7,FALSE),"?"))</f>
+        <v/>
+      </c>
+      <c r="P13" s="78">
+        <f>IF($D13="","",IFERROR(VLOOKUP($F13&amp;"|"&amp;$G13,Reguli_DECONT!$A$21:$H$26,8,FALSE),"cod de natură necunoscut"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="80" t="n">
+        <v>10</v>
+      </c>
+      <c r="B14" s="81" t="inlineStr"/>
+      <c r="C14" s="81" t="n"/>
+      <c r="D14" s="81" t="n"/>
+      <c r="E14" s="81" t="inlineStr"/>
+      <c r="F14" s="81" t="inlineStr"/>
+      <c r="G14" s="81" t="inlineStr"/>
+      <c r="H14" s="80">
+        <f>IF($D14="","",IFERROR(VLOOKUP($E14,Reguli_DECONT!$A$6:$H$16,3,FALSE),"?"))</f>
+        <v/>
+      </c>
+      <c r="I14" s="80">
+        <f>IF($D14="","",IFERROR(VLOOKUP($E14,Reguli_DECONT!$A$6:$H$16,4,FALSE),0))</f>
+        <v/>
+      </c>
+      <c r="J14" s="80">
+        <f>IF($D14="","",IFERROR(VLOOKUP($E14,Reguli_DECONT!$A$6:$H$16,6,FALSE),0))</f>
+        <v/>
+      </c>
+      <c r="K14" s="80">
+        <f>IF($D14="","",IF(Declarații_DECONT!B11&lt;&gt;"DA","NU",IFERROR(VLOOKUP($F14&amp;"|"&amp;$G14,Reguli_DECONT!$A$21:$H$26,4,FALSE),"NU")))</f>
+        <v/>
+      </c>
+      <c r="L14" s="80">
+        <f>IF($D14="","",IFERROR(VLOOKUP($F14&amp;"|"&amp;$G14,Reguli_DECONT!$A$21:$H$26,5,FALSE),"NU"))</f>
+        <v/>
+      </c>
+      <c r="M14" s="80">
+        <f>IF($D14="","",IF($L14&lt;&gt;"DA",0,$D14-$N14))</f>
+        <v/>
+      </c>
+      <c r="N14" s="80">
+        <f>IF($D14="","",IF($L14&lt;&gt;"DA",0,IF($K14&lt;&gt;"DA",0,ROUND($D14*$I14/(1+$I14)*$J14,2))))</f>
+        <v/>
+      </c>
+      <c r="O14" s="80">
+        <f>IF($D14="","",IFERROR(VLOOKUP($E14,Reguli_DECONT!$A$6:$H$16,7,FALSE),"?"))</f>
+        <v/>
+      </c>
+      <c r="P14" s="78">
+        <f>IF($D14="","",IFERROR(VLOOKUP($F14&amp;"|"&amp;$G14,Reguli_DECONT!$A$21:$H$26,8,FALSE),"cod de natură necunoscut"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="82" t="inlineStr"/>
+      <c r="B15" s="82" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="C15" s="82" t="inlineStr"/>
+      <c r="D15" s="82">
+        <f>SUM(D5:D14)</f>
+        <v>3938.76</v>
+      </c>
+      <c r="E15" s="82" t="inlineStr"/>
+      <c r="F15" s="82" t="inlineStr"/>
+      <c r="G15" s="82" t="inlineStr"/>
+      <c r="H15" s="82" t="inlineStr"/>
+      <c r="I15" s="82" t="inlineStr"/>
+      <c r="J15" s="82" t="inlineStr"/>
+      <c r="K15" s="82" t="inlineStr"/>
+      <c r="L15" s="82" t="inlineStr"/>
+      <c r="M15" s="82">
+        <f>SUM(M5:M14)</f>
+        <v>3938.76</v>
+      </c>
+      <c r="N15" s="82">
+        <f>SUM(N5:N14)</f>
+        <v>0</v>
+      </c>
+      <c r="O15" s="82" t="inlineStr"/>
+      <c r="P15" s="82" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="79" t="inlineStr">
+        <is>
+          <t>Recapitulație</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="80" t="inlineStr">
+        <is>
+          <t>Total datorat titularului (bază + TVA dedus)</t>
+        </is>
+      </c>
+      <c r="B18" s="80">
+        <f>Registru_DECONT!$M$15+Registru_DECONT!$N$15</f>
+        <v>3938.76</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="80" t="inlineStr">
+        <is>
+          <t>Total neacceptat (fără document justificativ)</t>
+        </is>
+      </c>
+      <c r="B19" s="80">
+        <f>Registru_DECONT!$D$15-(Registru_DECONT!$M$15+Registru_DECONT!$N$15)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="80" t="inlineStr">
+        <is>
+          <t>Avans acordat</t>
+        </is>
+      </c>
+      <c r="B20" s="80">
+        <f>Declarații_DECONT!B25</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="80" t="inlineStr">
+        <is>
+          <t>De plătit titularului (+) / de restituit (−)</t>
+        </is>
+      </c>
+      <c r="B21" s="80">
+        <f>Registru_DECONT!$B$18-Declarații_DECONT!B25</f>
+        <v>3938.76</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="80" t="inlineStr">
+        <is>
+          <t>Check Σ linii</t>
+        </is>
+      </c>
+      <c r="B23" s="80">
+        <f>Registru_DECONT!$D$15-(Registru_DECONT!$M$15+Registru_DECONT!$N$15)-Registru_DECONT!$B$19</f>
+        <v>0</v>
+      </c>
+      <c r="C23" s="80" t="str">
+        <f>IF(ABS(B23)&lt;0.01,"OK — brut = acceptat + neacceptat","EROARE")</f>
+        <v>OK — brut = acceptat + neacceptat</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="80" t="inlineStr">
+        <is>
+          <t>Check linii fără document</t>
+        </is>
+      </c>
+      <c r="B24" s="80">
+        <f>Registru_DECONT!$B$19</f>
+        <v>0</v>
+      </c>
+      <c r="C24" s="80" t="str">
+        <f>IF(B24&lt;0.01,"OK — toate liniile au document justificativ","ATENȚIE — sumă fără document: nu se trece pe cheltuială. Dacă se plătește, devine avantaj salarial — vezi MOD_SALARII")</f>
+        <v>OK — toate liniile au document justificativ</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet55.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G34"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" style="40" min="1" max="1"/>
+    <col width="14" customWidth="1" style="40" min="2" max="2"/>
+    <col width="14" customWidth="1" style="40" min="3" max="3"/>
+    <col width="46" customWidth="1" style="40" min="4" max="4"/>
+    <col width="14" customWidth="1" style="40" min="5" max="5"/>
+    <col width="14" customWidth="1" style="40" min="6" max="6"/>
+    <col width="46" customWidth="1" style="40" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="77" t="inlineStr">
+        <is>
+          <t>MOD_DECONT — Jurnale (generate automat)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="78" t="inlineStr">
+        <is>
+          <t>Cheltuielile se înregistrează agregat, pe contul dominant din decont. Pentru deconturi cu naturi multiple, folosește NotaExport, unde fiecare linie își poartă contul propriu.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="79" t="inlineStr">
+        <is>
+          <t>Bloc 1 — Acordarea avansului</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="80" t="inlineStr">
+        <is>
+          <t>Data jurnal:</t>
+        </is>
+      </c>
+      <c r="B5" s="80" t="str">
+        <f>Declarații_DECONT!B7</f>
+        <v>2026-07-31</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="82" t="inlineStr">
+        <is>
+          <t>Nr</t>
+        </is>
+      </c>
+      <c r="B7" s="82" t="inlineStr">
+        <is>
+          <t>Cont Dr</t>
+        </is>
+      </c>
+      <c r="C7" s="82" t="inlineStr">
+        <is>
+          <t>Sumă Dr</t>
+        </is>
+      </c>
+      <c r="D7" s="82" t="inlineStr">
+        <is>
+          <t>Descriere Dr</t>
+        </is>
+      </c>
+      <c r="E7" s="82" t="inlineStr">
+        <is>
+          <t>Cont Cr</t>
+        </is>
+      </c>
+      <c r="F7" s="82" t="inlineStr">
+        <is>
+          <t>Sumă Cr</t>
+        </is>
+      </c>
+      <c r="G7" s="82" t="inlineStr">
+        <is>
+          <t>Descriere Cr</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="80" t="n">
+        <v>1</v>
+      </c>
+      <c r="B8" s="80" t="str">
+        <f>Declarații_DECONT!B18</f>
+        <v>542</v>
+      </c>
+      <c r="C8" s="80">
+        <f>Declarații_DECONT!B25</f>
+        <v>0</v>
+      </c>
+      <c r="D8" s="80" t="str">
+        <f>"Avans de trezorerie acordat" &amp; Declarații_DECONT!B30</f>
+        <v>Avans de trezorerie acordat - decont CHIRIACESCU DIANA 2026-07-31</v>
+      </c>
+      <c r="E8" s="80" t="str">
+        <f>Declarații_DECONT!B22</f>
+        <v>5121</v>
+      </c>
+      <c r="F8" s="80">
+        <f>Declarații_DECONT!B25</f>
+        <v>0</v>
+      </c>
+      <c r="G8" s="80" t="str">
+        <f>"Plata avansului de trezorerie" &amp; Declarații_DECONT!B30</f>
+        <v>Plata avansului de trezorerie - decont CHIRIACESCU DIANA 2026-07-31</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="80" t="inlineStr">
+        <is>
+          <t>Check Σ (structural)</t>
+        </is>
+      </c>
+      <c r="B10" s="80">
+        <f>C8-F8</f>
+        <v>0</v>
+      </c>
+      <c r="C10" s="80" t="str">
+        <f>IF(ABS(B10)&lt;0.01,"OK — nota se închide","EROARE")</f>
+        <v>OK — nota se închide</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="80" t="inlineStr">
+        <is>
+          <t>Bloc activ?</t>
+        </is>
+      </c>
+      <c r="B11" s="80">
+        <f>Declarații_DECONT!B25</f>
+        <v>0</v>
+      </c>
+      <c r="C11" s="80" t="str">
+        <f>IF(B11&gt;0,"ACTIV — există avans","INACTIV — decont fără avans")</f>
+        <v>INACTIV — decont fără avans</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="79" t="inlineStr">
+        <is>
+          <t>Bloc 2 — Cheltuielile din decont</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="80" t="inlineStr">
+        <is>
+          <t>Data jurnal:</t>
+        </is>
+      </c>
+      <c r="B14" s="80" t="str">
+        <f>Declarații_DECONT!B7</f>
+        <v>2026-07-31</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="82" t="inlineStr">
+        <is>
+          <t>Nr</t>
+        </is>
+      </c>
+      <c r="B16" s="82" t="inlineStr">
+        <is>
+          <t>Cont Dr</t>
+        </is>
+      </c>
+      <c r="C16" s="82" t="inlineStr">
+        <is>
+          <t>Sumă Dr</t>
+        </is>
+      </c>
+      <c r="D16" s="82" t="inlineStr">
+        <is>
+          <t>Descriere Dr</t>
+        </is>
+      </c>
+      <c r="E16" s="82" t="inlineStr">
+        <is>
+          <t>Cont Cr</t>
+        </is>
+      </c>
+      <c r="F16" s="82" t="inlineStr">
+        <is>
+          <t>Sumă Cr</t>
+        </is>
+      </c>
+      <c r="G16" s="82" t="inlineStr">
+        <is>
+          <t>Descriere Cr</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="80" t="n">
+        <v>1</v>
+      </c>
+      <c r="B17" s="80" t="str">
+        <f>Declarații_DECONT!B19</f>
+        <v>625</v>
+      </c>
+      <c r="C17" s="80">
+        <f>Registru_DECONT!$M$15</f>
+        <v>3938.76</v>
+      </c>
+      <c r="D17" s="80" t="str">
+        <f>"Cheltuieli din decont, bază fără TVA dedus" &amp; Declarații_DECONT!B30</f>
+        <v>Cheltuieli din decont, bază fără TVA dedus - decont CHIRIACESCU DIANA 2026-07-31</v>
+      </c>
+      <c r="E17" s="80" t="str">
+        <f>Declarații_DECONT!B17</f>
+        <v>542</v>
+      </c>
+      <c r="F17" s="80">
+        <f>Registru_DECONT!$B$18</f>
+        <v>3938.76</v>
+      </c>
+      <c r="G17" s="80" t="str">
+        <f>"Datorie față de titularul de decont" &amp; Declarații_DECONT!B30</f>
+        <v>Datorie față de titularul de decont - decont CHIRIACESCU DIANA 2026-07-31</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="80" t="n">
+        <v>2</v>
+      </c>
+      <c r="B18" s="80">
+        <f>Declarații_DECONT!B21</f>
+        <v>4426</v>
+      </c>
+      <c r="C18" s="80">
+        <f>Registru_DECONT!$N$15</f>
+        <v>0</v>
+      </c>
+      <c r="D18" s="80" t="str">
+        <f>"TVA deductibilă din decont" &amp; Declarații_DECONT!B30</f>
+        <v>TVA deductibilă din decont - decont CHIRIACESCU DIANA 2026-07-31</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="80" t="inlineStr">
+        <is>
+          <t>Total Dr</t>
+        </is>
+      </c>
+      <c r="B20" s="80">
+        <f>SUM(C17:C18)</f>
+        <v>3938.76</v>
+      </c>
+      <c r="C20" s="80" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="80" t="inlineStr">
+        <is>
+          <t>Total Cr</t>
+        </is>
+      </c>
+      <c r="B21" s="80">
+        <f>SUM(F17:F18)</f>
+        <v>3938.76</v>
+      </c>
+      <c r="C21" s="80" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="80" t="inlineStr">
+        <is>
+          <t>Check Σ (structural)</t>
+        </is>
+      </c>
+      <c r="B22" s="80">
+        <f>SUM(C17:C18)-SUM(F17:F18)</f>
+        <v>0</v>
+      </c>
+      <c r="C22" s="80" t="str">
+        <f>IF(ABS(B22)&lt;0.01,"OK — nota se închide","EROARE")</f>
+        <v>OK — nota se închide</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="80" t="inlineStr">
+        <is>
+          <t>Check contul de cheltuială</t>
+        </is>
+      </c>
+      <c r="B23" s="80" t="str">
+        <f>Declarații_DECONT!B19</f>
+        <v>625</v>
+      </c>
+      <c r="C23" s="80" t="str">
+        <f>"Bloc agregat pe contul dominant. Dacă decontul are naturi multiple, importă din NotaExport, unde fiecare linie poartă contul ei."</f>
+        <v>Bloc agregat pe contul dominant. Dacă decontul are naturi multiple, importă din NotaExport, unde fiecare linie poartă contul ei.</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="79" t="inlineStr">
+        <is>
+          <t>Bloc 3 — Regularizarea avansului și plata</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="80" t="inlineStr">
+        <is>
+          <t>Data jurnal:</t>
+        </is>
+      </c>
+      <c r="B26" s="80" t="str">
+        <f>Declarații_DECONT!B8</f>
+        <v>2026-08-05</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="82" t="inlineStr">
+        <is>
+          <t>Nr</t>
+        </is>
+      </c>
+      <c r="B28" s="82" t="inlineStr">
+        <is>
+          <t>Cont Dr</t>
+        </is>
+      </c>
+      <c r="C28" s="82" t="inlineStr">
+        <is>
+          <t>Sumă Dr</t>
+        </is>
+      </c>
+      <c r="D28" s="82" t="inlineStr">
+        <is>
+          <t>Descriere Dr</t>
+        </is>
+      </c>
+      <c r="E28" s="82" t="inlineStr">
+        <is>
+          <t>Cont Cr</t>
+        </is>
+      </c>
+      <c r="F28" s="82" t="inlineStr">
+        <is>
+          <t>Sumă Cr</t>
+        </is>
+      </c>
+      <c r="G28" s="82" t="inlineStr">
+        <is>
+          <t>Descriere Cr</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="80" t="n">
+        <v>1</v>
+      </c>
+      <c r="B29" s="80" t="str">
+        <f>Declarații_DECONT!B17</f>
+        <v>542</v>
+      </c>
+      <c r="C29" s="80">
+        <f>Registru_DECONT!$B$21</f>
+        <v>3938.76</v>
+      </c>
+      <c r="D29" s="80" t="str">
+        <f>"Plata diferenței către titular" &amp; Declarații_DECONT!B30</f>
+        <v>Plata diferenței către titular - decont CHIRIACESCU DIANA 2026-07-31</v>
+      </c>
+      <c r="E29" s="80" t="str">
+        <f>Declarații_DECONT!B22</f>
+        <v>5121</v>
+      </c>
+      <c r="F29" s="80">
+        <f>Registru_DECONT!$B$21</f>
+        <v>3938.76</v>
+      </c>
+      <c r="G29" s="80" t="str">
+        <f>"Plata din trezorerie" &amp; Declarații_DECONT!B30</f>
+        <v>Plata din trezorerie - decont CHIRIACESCU DIANA 2026-07-31</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="80" t="inlineStr">
+        <is>
+          <t>Check Σ (structural)</t>
+        </is>
+      </c>
+      <c r="B31" s="80">
+        <f>SUM(C29:C29)-SUM(F29:F29)</f>
+        <v>0</v>
+      </c>
+      <c r="C31" s="80" t="str">
+        <f>IF(ABS(B31)&lt;0.01,"OK — nota se închide","EROARE")</f>
+        <v>OK — nota se închide</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="80" t="inlineStr">
+        <is>
+          <t>Sensul plății</t>
+        </is>
+      </c>
+      <c r="B32" s="80">
+        <f>Registru_DECONT!$B$21</f>
+        <v>3938.76</v>
+      </c>
+      <c r="C32" s="80" t="str">
+        <f>IF(B32&gt;=0,"Se plătește titularului","Titularul restituie diferența — inversează sensul notei")</f>
+        <v>Se plătește titularului</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="78" t="inlineStr">
+        <is>
+          <t>Stare terminală așteptată: contul de avans = 0, contul de datorie față de titular = 0 după plată.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet56.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I17"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="6" customWidth="1" style="40" min="1" max="1"/>
+    <col width="24" customWidth="1" style="40" min="2" max="2"/>
+    <col width="12" customWidth="1" style="40" min="3" max="3"/>
+    <col width="12" customWidth="1" style="40" min="4" max="4"/>
+    <col width="12" customWidth="1" style="40" min="5" max="5"/>
+    <col width="14" customWidth="1" style="40" min="6" max="6"/>
+    <col width="48" customWidth="1" style="40" min="7" max="7"/>
+    <col width="22" customWidth="1" style="40" min="8" max="8"/>
+    <col width="9" customWidth="1" style="40" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="77" t="inlineStr">
+        <is>
+          <t>MOD_DECONT — Notă pentru import (1 rând = 1 înregistrare)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="78" t="inlineStr">
+        <is>
+          <t>Aici fiecare linie de decont își păstrează contul propriu, spre deosebire de blocul agregat din Jurnale. Filtrează pe Include = DA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="82" t="inlineStr">
+        <is>
+          <t>Nr</t>
+        </is>
+      </c>
+      <c r="B4" s="82" t="inlineStr">
+        <is>
+          <t>Bloc</t>
+        </is>
+      </c>
+      <c r="C4" s="82" t="inlineStr">
+        <is>
+          <t>Data</t>
+        </is>
+      </c>
+      <c r="D4" s="82" t="inlineStr">
+        <is>
+          <t>Cont Dr</t>
+        </is>
+      </c>
+      <c r="E4" s="82" t="inlineStr">
+        <is>
+          <t>Cont Cr</t>
+        </is>
+      </c>
+      <c r="F4" s="82" t="inlineStr">
+        <is>
+          <t>Sumă</t>
+        </is>
+      </c>
+      <c r="G4" s="82" t="inlineStr">
+        <is>
+          <t>Descriere</t>
+        </is>
+      </c>
+      <c r="H4" s="82" t="inlineStr">
+        <is>
+          <t>Document</t>
+        </is>
+      </c>
+      <c r="I4" s="82" t="inlineStr">
+        <is>
+          <t>Include</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="80" t="n">
+        <v>1</v>
+      </c>
+      <c r="B5" s="80" t="inlineStr">
+        <is>
+          <t>Bloc 2 — Cheltuieli pe linie</t>
+        </is>
+      </c>
+      <c r="C5" s="80" t="str">
+        <f>Declarații_DECONT!B7</f>
+        <v>2026-07-31</v>
+      </c>
+      <c r="D5" s="80" t="str">
+        <f>Registru_DECONT!$H$5</f>
+        <v>625</v>
+      </c>
+      <c r="E5" s="80" t="str">
+        <f>Declarații_DECONT!B17</f>
+        <v>542</v>
+      </c>
+      <c r="F5" s="80">
+        <f>Registru_DECONT!$M$5</f>
+        <v>1780.38</v>
+      </c>
+      <c r="G5" s="80" t="str">
+        <f>IF(Registru_DECONT!$B$5="","",Registru_DECONT!$B$5 &amp; " — " &amp; Registru_DECONT!$P$5)</f>
+        <v>WIZZ AIR MALTA LIMITED — Factură completă conform art. 319 — TVA deductibil</v>
+      </c>
+      <c r="H5" s="80" t="inlineStr">
+        <is>
+          <t>Decont de cheltuieli</t>
+        </is>
+      </c>
+      <c r="I5" s="80" t="str">
+        <f>IF(N(F5)&gt;0,"DA","NU")</f>
+        <v>DA</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="80" t="n">
+        <v>2</v>
+      </c>
+      <c r="B6" s="80" t="inlineStr">
+        <is>
+          <t>Bloc 2 — Cheltuieli pe linie</t>
+        </is>
+      </c>
+      <c r="C6" s="80" t="str">
+        <f>Declarații_DECONT!B7</f>
+        <v>2026-07-31</v>
+      </c>
+      <c r="D6" s="80" t="str">
+        <f>Registru_DECONT!$H$6</f>
+        <v>625</v>
+      </c>
+      <c r="E6" s="80" t="str">
+        <f>Declarații_DECONT!B17</f>
+        <v>542</v>
+      </c>
+      <c r="F6" s="80">
+        <f>Registru_DECONT!$M$6</f>
+        <v>1720.38</v>
+      </c>
+      <c r="G6" s="80" t="str">
+        <f>IF(Registru_DECONT!$B$6="","",Registru_DECONT!$B$6 &amp; " — " &amp; Registru_DECONT!$P$6)</f>
+        <v>WIZZ AIR MALTA LIMITED — Factură completă conform art. 319 — TVA deductibil</v>
+      </c>
+      <c r="H6" s="80" t="inlineStr">
+        <is>
+          <t>Decont de cheltuieli</t>
+        </is>
+      </c>
+      <c r="I6" s="80" t="str">
+        <f>IF(N(F6)&gt;0,"DA","NU")</f>
+        <v>DA</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="80" t="n">
+        <v>3</v>
+      </c>
+      <c r="B7" s="80" t="inlineStr">
+        <is>
+          <t>Bloc 2 — Cheltuieli pe linie</t>
+        </is>
+      </c>
+      <c r="C7" s="80" t="str">
+        <f>Declarații_DECONT!B7</f>
+        <v>2026-07-31</v>
+      </c>
+      <c r="D7" s="80" t="str">
+        <f>Registru_DECONT!$H$7</f>
+        <v>625</v>
+      </c>
+      <c r="E7" s="80" t="str">
+        <f>Declarații_DECONT!B17</f>
+        <v>542</v>
+      </c>
+      <c r="F7" s="80">
+        <f>Registru_DECONT!$M$7</f>
+        <v>38</v>
+      </c>
+      <c r="G7" s="80" t="str">
+        <f>IF(Registru_DECONT!$B$7="","",Registru_DECONT!$B$7 &amp; " — " &amp; Registru_DECONT!$P$7)</f>
+        <v>CITY CAFÉ EXPRESS — Bon fără CUI — TVA nedeductibil; justificare cu ordin de deplasare</v>
+      </c>
+      <c r="H7" s="80" t="inlineStr">
+        <is>
+          <t>Decont de cheltuieli</t>
+        </is>
+      </c>
+      <c r="I7" s="80" t="str">
+        <f>IF(N(F7)&gt;0,"DA","NU")</f>
+        <v>DA</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="80" t="n">
+        <v>4</v>
+      </c>
+      <c r="B8" s="80" t="inlineStr">
+        <is>
+          <t>Bloc 2 — Cheltuieli pe linie</t>
+        </is>
+      </c>
+      <c r="C8" s="80" t="str">
+        <f>Declarații_DECONT!B7</f>
+        <v>2026-07-31</v>
+      </c>
+      <c r="D8" s="80" t="str">
+        <f>Registru_DECONT!$H$8</f>
+        <v>625</v>
+      </c>
+      <c r="E8" s="80" t="str">
+        <f>Declarații_DECONT!B17</f>
+        <v>542</v>
+      </c>
+      <c r="F8" s="80">
+        <f>Registru_DECONT!$M$8</f>
+        <v>200</v>
+      </c>
+      <c r="G8" s="80" t="str">
+        <f>IF(Registru_DECONT!$B$8="","",Registru_DECONT!$B$8 &amp; " — " &amp; Registru_DECONT!$P$8)</f>
+        <v>OLIMPIA PARKING — Bon fără CUI — TVA nedeductibil; justificare cu ordin de deplasare</v>
+      </c>
+      <c r="H8" s="80" t="inlineStr">
+        <is>
+          <t>Decont de cheltuieli</t>
+        </is>
+      </c>
+      <c r="I8" s="80" t="str">
+        <f>IF(N(F8)&gt;0,"DA","NU")</f>
+        <v>DA</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="80" t="n">
+        <v>5</v>
+      </c>
+      <c r="B9" s="80" t="inlineStr">
+        <is>
+          <t>Bloc 2 — Cheltuieli pe linie</t>
+        </is>
+      </c>
+      <c r="C9" s="80" t="str">
+        <f>Declarații_DECONT!B7</f>
+        <v>2026-07-31</v>
+      </c>
+      <c r="D9" s="80" t="str">
+        <f>Registru_DECONT!$H$9</f>
+        <v>625</v>
+      </c>
+      <c r="E9" s="80" t="str">
+        <f>Declarații_DECONT!B17</f>
+        <v>542</v>
+      </c>
+      <c r="F9" s="80">
+        <f>Registru_DECONT!$M$9</f>
+        <v>200</v>
+      </c>
+      <c r="G9" s="80" t="str">
+        <f>IF(Registru_DECONT!$B$9="","",Registru_DECONT!$B$9 &amp; " — " &amp; Registru_DECONT!$P$9)</f>
+        <v>OLIMPIA PARKING — Bon fără CUI — TVA nedeductibil; justificare cu ordin de deplasare</v>
+      </c>
+      <c r="H9" s="80" t="inlineStr">
+        <is>
+          <t>Decont de cheltuieli</t>
+        </is>
+      </c>
+      <c r="I9" s="80" t="str">
+        <f>IF(N(F9)&gt;0,"DA","NU")</f>
+        <v>DA</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="80" t="n">
+        <v>6</v>
+      </c>
+      <c r="B10" s="80" t="inlineStr">
+        <is>
+          <t>Bloc 2 — Cheltuieli pe linie</t>
+        </is>
+      </c>
+      <c r="C10" s="80" t="str">
+        <f>Declarații_DECONT!B7</f>
+        <v>2026-07-31</v>
+      </c>
+      <c r="D10" s="80">
+        <f>Registru_DECONT!$H$10</f>
+        <v/>
+      </c>
+      <c r="E10" s="80" t="str">
+        <f>Declarații_DECONT!B17</f>
+        <v>542</v>
+      </c>
+      <c r="F10" s="80">
+        <f>Registru_DECONT!$M$10</f>
+        <v/>
+      </c>
+      <c r="G10" s="80">
+        <f>IF(Registru_DECONT!$B$10="","",Registru_DECONT!$B$10 &amp; " — " &amp; Registru_DECONT!$P$10)</f>
+        <v/>
+      </c>
+      <c r="H10" s="80" t="inlineStr">
+        <is>
+          <t>Decont de cheltuieli</t>
+        </is>
+      </c>
+      <c r="I10" s="80" t="str">
+        <f>IF(N(F10)&gt;0,"DA","NU")</f>
+        <v>NU</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="80" t="n">
+        <v>7</v>
+      </c>
+      <c r="B11" s="80" t="inlineStr">
+        <is>
+          <t>Bloc 2 — Cheltuieli pe linie</t>
+        </is>
+      </c>
+      <c r="C11" s="80" t="str">
+        <f>Declarații_DECONT!B7</f>
+        <v>2026-07-31</v>
+      </c>
+      <c r="D11" s="80">
+        <f>Registru_DECONT!$H$11</f>
+        <v/>
+      </c>
+      <c r="E11" s="80" t="str">
+        <f>Declarații_DECONT!B17</f>
+        <v>542</v>
+      </c>
+      <c r="F11" s="80">
+        <f>Registru_DECONT!$M$11</f>
+        <v/>
+      </c>
+      <c r="G11" s="80">
+        <f>IF(Registru_DECONT!$B$11="","",Registru_DECONT!$B$11 &amp; " — " &amp; Registru_DECONT!$P$11)</f>
+        <v/>
+      </c>
+      <c r="H11" s="80" t="inlineStr">
+        <is>
+          <t>Decont de cheltuieli</t>
+        </is>
+      </c>
+      <c r="I11" s="80" t="str">
+        <f>IF(N(F11)&gt;0,"DA","NU")</f>
+        <v>NU</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="80" t="n">
+        <v>8</v>
+      </c>
+      <c r="B12" s="80" t="inlineStr">
+        <is>
+          <t>Bloc 2 — Cheltuieli pe linie</t>
+        </is>
+      </c>
+      <c r="C12" s="80" t="str">
+        <f>Declarații_DECONT!B7</f>
+        <v>2026-07-31</v>
+      </c>
+      <c r="D12" s="80">
+        <f>Registru_DECONT!$H$12</f>
+        <v/>
+      </c>
+      <c r="E12" s="80" t="str">
+        <f>Declarații_DECONT!B17</f>
+        <v>542</v>
+      </c>
+      <c r="F12" s="80">
+        <f>Registru_DECONT!$M$12</f>
+        <v/>
+      </c>
+      <c r="G12" s="80">
+        <f>IF(Registru_DECONT!$B$12="","",Registru_DECONT!$B$12 &amp; " — " &amp; Registru_DECONT!$P$12)</f>
+        <v/>
+      </c>
+      <c r="H12" s="80" t="inlineStr">
+        <is>
+          <t>Decont de cheltuieli</t>
+        </is>
+      </c>
+      <c r="I12" s="80" t="str">
+        <f>IF(N(F12)&gt;0,"DA","NU")</f>
+        <v>NU</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="80" t="n">
+        <v>9</v>
+      </c>
+      <c r="B13" s="80" t="inlineStr">
+        <is>
+          <t>Bloc 2 — Cheltuieli pe linie</t>
+        </is>
+      </c>
+      <c r="C13" s="80" t="str">
+        <f>Declarații_DECONT!B7</f>
+        <v>2026-07-31</v>
+      </c>
+      <c r="D13" s="80">
+        <f>Registru_DECONT!$H$13</f>
+        <v/>
+      </c>
+      <c r="E13" s="80" t="str">
+        <f>Declarații_DECONT!B17</f>
+        <v>542</v>
+      </c>
+      <c r="F13" s="80">
+        <f>Registru_DECONT!$M$13</f>
+        <v/>
+      </c>
+      <c r="G13" s="80">
+        <f>IF(Registru_DECONT!$B$13="","",Registru_DECONT!$B$13 &amp; " — " &amp; Registru_DECONT!$P$13)</f>
+        <v/>
+      </c>
+      <c r="H13" s="80" t="inlineStr">
+        <is>
+          <t>Decont de cheltuieli</t>
+        </is>
+      </c>
+      <c r="I13" s="80" t="str">
+        <f>IF(N(F13)&gt;0,"DA","NU")</f>
+        <v>NU</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="80" t="n">
+        <v>10</v>
+      </c>
+      <c r="B14" s="80" t="inlineStr">
+        <is>
+          <t>Bloc 2 — Cheltuieli pe linie</t>
+        </is>
+      </c>
+      <c r="C14" s="80" t="str">
+        <f>Declarații_DECONT!B7</f>
+        <v>2026-07-31</v>
+      </c>
+      <c r="D14" s="80">
+        <f>Registru_DECONT!$H$14</f>
+        <v/>
+      </c>
+      <c r="E14" s="80" t="str">
+        <f>Declarații_DECONT!B17</f>
+        <v>542</v>
+      </c>
+      <c r="F14" s="80">
+        <f>Registru_DECONT!$M$14</f>
+        <v/>
+      </c>
+      <c r="G14" s="80">
+        <f>IF(Registru_DECONT!$B$14="","",Registru_DECONT!$B$14 &amp; " — " &amp; Registru_DECONT!$P$14)</f>
+        <v/>
+      </c>
+      <c r="H14" s="80" t="inlineStr">
+        <is>
+          <t>Decont de cheltuieli</t>
+        </is>
+      </c>
+      <c r="I14" s="80" t="str">
+        <f>IF(N(F14)&gt;0,"DA","NU")</f>
+        <v>NU</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="80" t="inlineStr">
+        <is>
+          <t>Rânduri de importat (Include=DA)</t>
+        </is>
+      </c>
+      <c r="B16" s="80">
+        <f>COUNTIF(I5:I14,"DA")</f>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="80" t="inlineStr">
+        <is>
+          <t>Check total linii vs. registru</t>
+        </is>
+      </c>
+      <c r="B17" s="80">
+        <f>SUM(F5:F14)-Registru_DECONT!$M$15</f>
+        <v>0</v>
+      </c>
+      <c r="C17" s="80" t="str">
+        <f>IF(ABS(B17)&lt;0.01,"OK — suma liniilor = baza din registru","EROARE")</f>
+        <v>OK — suma liniilor = baza din registru</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 

--- a/dist/Module_Declarative_Fluxuri.xlsx
+++ b/dist/Module_Declarative_Fluxuri.xlsx
@@ -1,80 +1,80 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Instructiuni" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Parametri" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="CatalogModule" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Declarații_INCHIDERE_TVA" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Reguli_INCHIDERE_TVA" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Jurnale_INCHIDERE_TVA" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="NotaExport_INCHIDERE_TVA" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="Declarații_APROV_TRANZIT" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="Reguli_APROV_TRANZIT" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="Jurnale_APROV_TRANZIT" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="NotaExport_APROV_TRANZIT" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="Declarații_INTERMEDIAR" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="Reguli_INTERMEDIAR" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet name="Jurnale_INTERMEDIAR" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet name="NotaExport_INTERMEDIAR" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet name="Declarații_INCHIDERE_EX" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet name="Reguli_INCHIDERE_EX" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet name="Jurnale_INCHIDERE_EX" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet name="NotaExport_INCHIDERE_EX" sheetId="19" state="visible" r:id="rId19"/>
-    <sheet name="Declarații_NEUTRALIZARE" sheetId="20" state="visible" r:id="rId20"/>
-    <sheet name="Reguli_NEUTRALIZARE" sheetId="21" state="visible" r:id="rId21"/>
-    <sheet name="Jurnale_NEUTRALIZARE" sheetId="22" state="visible" r:id="rId22"/>
-    <sheet name="NotaExport_NEUTRALIZARE" sheetId="23" state="visible" r:id="rId23"/>
-    <sheet name="Declarații_AMANUNT" sheetId="24" state="visible" r:id="rId24"/>
-    <sheet name="Reguli_AMANUNT" sheetId="25" state="visible" r:id="rId25"/>
-    <sheet name="Jurnale_AMANUNT" sheetId="26" state="visible" r:id="rId26"/>
-    <sheet name="NotaExport_AMANUNT" sheetId="27" state="visible" r:id="rId27"/>
-    <sheet name="Declarații_TVA_INC" sheetId="28" state="visible" r:id="rId28"/>
-    <sheet name="Reguli_TVA_INC" sheetId="29" state="visible" r:id="rId29"/>
-    <sheet name="Jurnale_TVA_INC" sheetId="30" state="visible" r:id="rId30"/>
-    <sheet name="NotaExport_TVA_INC" sheetId="31" state="visible" r:id="rId31"/>
-    <sheet name="Declarații_CAPITALURI" sheetId="32" state="visible" r:id="rId32"/>
-    <sheet name="Reguli_CAPITALURI" sheetId="33" state="visible" r:id="rId33"/>
-    <sheet name="Jurnale_CAPITALURI" sheetId="34" state="visible" r:id="rId34"/>
-    <sheet name="NotaExport_CAPITALURI" sheetId="35" state="visible" r:id="rId35"/>
-    <sheet name="Declarații_CREDIT_VALUTA" sheetId="36" state="visible" r:id="rId36"/>
-    <sheet name="Reguli_CREDIT_VALUTA" sheetId="37" state="visible" r:id="rId37"/>
-    <sheet name="Jurnale_CREDIT_VALUTA" sheetId="38" state="visible" r:id="rId38"/>
-    <sheet name="NotaExport_CREDIT_VALUTA" sheetId="39" state="visible" r:id="rId39"/>
-    <sheet name="Declarații_PROVIZION" sheetId="40" state="visible" r:id="rId40"/>
-    <sheet name="Reguli_PROVIZION" sheetId="41" state="visible" r:id="rId41"/>
-    <sheet name="Jurnale_PROVIZION" sheetId="42" state="visible" r:id="rId42"/>
-    <sheet name="NotaExport_PROVIZION" sheetId="43" state="visible" r:id="rId43"/>
-    <sheet name="Declarații_LEASING_FIN" sheetId="44" state="visible" r:id="rId44"/>
-    <sheet name="Reguli_LEASING_FIN" sheetId="45" state="visible" r:id="rId45"/>
-    <sheet name="Jurnale_LEASING_FIN" sheetId="46" state="visible" r:id="rId46"/>
-    <sheet name="NotaExport_LEASING_FIN" sheetId="47" state="visible" r:id="rId47"/>
-    <sheet name="Declarații_IMOBILIZARI" sheetId="48" state="visible" r:id="rId48"/>
-    <sheet name="Reguli_IMOBILIZARI" sheetId="49" state="visible" r:id="rId49"/>
-    <sheet name="Jurnale_IMOBILIZARI" sheetId="50" state="visible" r:id="rId50"/>
-    <sheet name="NotaExport_IMOBILIZARI" sheetId="51" state="visible" r:id="rId51"/>
-    <sheet name="Declarații_SUBVENTIE" sheetId="52" state="visible" r:id="rId52"/>
-    <sheet name="Reguli_SUBVENTIE" sheetId="53" state="visible" r:id="rId53"/>
-    <sheet name="Jurnale_SUBVENTIE" sheetId="54" state="visible" r:id="rId54"/>
-    <sheet name="NotaExport_SUBVENTIE" sheetId="55" state="visible" r:id="rId55"/>
-    <sheet name="Declarații_IESIRE_MF" sheetId="56" state="visible" r:id="rId56"/>
-    <sheet name="Reguli_IESIRE_MF" sheetId="57" state="visible" r:id="rId57"/>
-    <sheet name="Jurnale_IESIRE_MF" sheetId="58" state="visible" r:id="rId58"/>
-    <sheet name="NotaExport_IESIRE_MF" sheetId="59" state="visible" r:id="rId59"/>
-    <sheet name="Declarații_SALARII" sheetId="60" state="visible" r:id="rId60"/>
-    <sheet name="Reguli_SALARII" sheetId="61" state="visible" r:id="rId61"/>
-    <sheet name="Jurnale_SALARII" sheetId="62" state="visible" r:id="rId62"/>
-    <sheet name="NotaExport_SALARII" sheetId="63" state="visible" r:id="rId63"/>
-    <sheet name="Declarații_DECONT" sheetId="64" state="visible" r:id="rId64"/>
-    <sheet name="Reguli_DECONT" sheetId="65" state="visible" r:id="rId65"/>
-    <sheet name="Registru_DECONT" sheetId="66" state="visible" r:id="rId66"/>
-    <sheet name="Jurnale_DECONT" sheetId="67" state="visible" r:id="rId67"/>
-    <sheet name="NotaExport_DECONT" sheetId="68" state="visible" r:id="rId68"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instructiuni" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Parametri" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CatalogModule" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Declarații_INCHIDERE_TVA" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reguli_INCHIDERE_TVA" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Jurnale_INCHIDERE_TVA" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NotaExport_INCHIDERE_TVA" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Declarații_APROV_TRANZIT" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reguli_APROV_TRANZIT" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Jurnale_APROV_TRANZIT" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NotaExport_APROV_TRANZIT" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Declarații_INTERMEDIAR" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reguli_INTERMEDIAR" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Jurnale_INTERMEDIAR" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NotaExport_INTERMEDIAR" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Declarații_INCHIDERE_EX" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reguli_INCHIDERE_EX" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Jurnale_INCHIDERE_EX" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NotaExport_INCHIDERE_EX" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Declarații_NEUTRALIZARE" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reguli_NEUTRALIZARE" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Jurnale_NEUTRALIZARE" sheetId="22" state="visible" r:id="rId22"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NotaExport_NEUTRALIZARE" sheetId="23" state="visible" r:id="rId23"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Declarații_AMANUNT" sheetId="24" state="visible" r:id="rId24"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reguli_AMANUNT" sheetId="25" state="visible" r:id="rId25"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Jurnale_AMANUNT" sheetId="26" state="visible" r:id="rId26"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NotaExport_AMANUNT" sheetId="27" state="visible" r:id="rId27"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Declarații_TVA_INC" sheetId="28" state="visible" r:id="rId28"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reguli_TVA_INC" sheetId="29" state="visible" r:id="rId29"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Jurnale_TVA_INC" sheetId="30" state="visible" r:id="rId30"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NotaExport_TVA_INC" sheetId="31" state="visible" r:id="rId31"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Declarații_CAPITALURI" sheetId="32" state="visible" r:id="rId32"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reguli_CAPITALURI" sheetId="33" state="visible" r:id="rId33"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Jurnale_CAPITALURI" sheetId="34" state="visible" r:id="rId34"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NotaExport_CAPITALURI" sheetId="35" state="visible" r:id="rId35"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Declarații_CREDIT_VALUTA" sheetId="36" state="visible" r:id="rId36"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reguli_CREDIT_VALUTA" sheetId="37" state="visible" r:id="rId37"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Jurnale_CREDIT_VALUTA" sheetId="38" state="visible" r:id="rId38"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NotaExport_CREDIT_VALUTA" sheetId="39" state="visible" r:id="rId39"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Declarații_PROVIZION" sheetId="40" state="visible" r:id="rId40"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reguli_PROVIZION" sheetId="41" state="visible" r:id="rId41"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Jurnale_PROVIZION" sheetId="42" state="visible" r:id="rId42"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NotaExport_PROVIZION" sheetId="43" state="visible" r:id="rId43"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Declarații_LEASING_FIN" sheetId="44" state="visible" r:id="rId44"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reguli_LEASING_FIN" sheetId="45" state="visible" r:id="rId45"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Jurnale_LEASING_FIN" sheetId="46" state="visible" r:id="rId46"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NotaExport_LEASING_FIN" sheetId="47" state="visible" r:id="rId47"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Declarații_IMOBILIZARI" sheetId="48" state="visible" r:id="rId48"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reguli_IMOBILIZARI" sheetId="49" state="visible" r:id="rId49"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Jurnale_IMOBILIZARI" sheetId="50" state="visible" r:id="rId50"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NotaExport_IMOBILIZARI" sheetId="51" state="visible" r:id="rId51"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Declarații_SUBVENTIE" sheetId="52" state="visible" r:id="rId52"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reguli_SUBVENTIE" sheetId="53" state="visible" r:id="rId53"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Jurnale_SUBVENTIE" sheetId="54" state="visible" r:id="rId54"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NotaExport_SUBVENTIE" sheetId="55" state="visible" r:id="rId55"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Declarații_IESIRE_MF" sheetId="56" state="visible" r:id="rId56"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reguli_IESIRE_MF" sheetId="57" state="visible" r:id="rId57"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Jurnale_IESIRE_MF" sheetId="58" state="visible" r:id="rId58"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NotaExport_IESIRE_MF" sheetId="59" state="visible" r:id="rId59"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Declarații_SALARII" sheetId="60" state="visible" r:id="rId60"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reguli_SALARII" sheetId="61" state="visible" r:id="rId61"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Jurnale_SALARII" sheetId="62" state="visible" r:id="rId62"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NotaExport_SALARII" sheetId="63" state="visible" r:id="rId63"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Declarații_DECONT" sheetId="64" state="visible" r:id="rId64"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reguli_DECONT" sheetId="65" state="visible" r:id="rId65"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Registru_DECONT" sheetId="66" state="visible" r:id="rId66"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Jurnale_DECONT" sheetId="67" state="visible" r:id="rId67"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NotaExport_DECONT" sheetId="68" state="visible" r:id="rId68"/>
   </sheets>
   <definedNames>
     <definedName name="param_proc_rezerva">Parametri!$B$18</definedName>

--- a/dist/Module_Declarative_Fluxuri.xlsx
+++ b/dist/Module_Declarative_Fluxuri.xlsx
@@ -75,6 +75,10 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Registru_DECONT" sheetId="66" state="visible" r:id="rId66"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Jurnale_DECONT" sheetId="67" state="visible" r:id="rId67"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NotaExport_DECONT" sheetId="68" state="visible" r:id="rId68"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Declarații_INCHIDERE_LUNARA" sheetId="69" state="visible" r:id="rId69"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reguli_INCHIDERE_LUNARA" sheetId="70" state="visible" r:id="rId70"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Verificări_INCHIDERE_LUNARA" sheetId="71" state="visible" r:id="rId71"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Abateri_INCHIDERE_LUNARA" sheetId="72" state="visible" r:id="rId72"/>
   </sheets>
   <definedNames>
     <definedName name="param_proc_rezerva">Parametri!$B$18</definedName>
@@ -8810,7 +8814,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:H29"/>
+  <dimension ref="A1:H30"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="8" customWidth="1" style="39" min="1" max="1"/>
@@ -9558,43 +9562,85 @@
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="42" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="58" t="inlineStr">
+        <is>
+          <t>NU</t>
+        </is>
+      </c>
+      <c r="B23" s="59" t="inlineStr">
+        <is>
+          <t>MOD_INCHIDERE_LUNARA</t>
+        </is>
+      </c>
+      <c r="C23" s="59" t="inlineStr">
+        <is>
+          <t>F-422, F-413</t>
+        </is>
+      </c>
+      <c r="D23" s="59" t="inlineStr">
+        <is>
+          <t>Lunar, pe balanța de verificare</t>
+        </is>
+      </c>
+      <c r="E23" s="59" t="inlineStr">
+        <is>
+          <t>Rulaj debitor, rulaj creditor și sold pentru conturile cu cadență; restul de plată de pe stat; soldul din decontul de TVA</t>
+        </is>
+      </c>
+      <c r="F23" s="59" t="inlineStr">
+        <is>
+          <t>Verifică solduri, nu documente — vezi Reguli, tabelul C</t>
+        </is>
+      </c>
+      <c r="G23" s="59" t="inlineStr">
+        <is>
+          <t>V1 Obligații lunare (rulaj = sold); V2 Datoria față de salariați; V3 Conturi care trebuie golite; V4 Verificarea CAM pe cifre</t>
+        </is>
+      </c>
+      <c r="H23" s="59" t="inlineStr">
+        <is>
+          <t>IMPLEMENTAT</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="42" t="inlineStr">
         <is>
           <t>REGULĂ DE SUMONARE</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="43" t="inlineStr">
-        <is>
-          <t>1. În CatalogModule setezi Activ=DA doar pe modulele necesare lunii.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="43" t="inlineStr">
         <is>
-          <t>2. Completezi variabilele din foaia Declarații_Modul (galben).</t>
+          <t>1. În CatalogModule setezi Activ=DA doar pe modulele necesare lunii.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="43" t="inlineStr">
         <is>
-          <t>3. Jurnalele și NotaExport se populează automat doar pentru modulele active.</t>
+          <t>2. Completezi variabilele din foaia Declarații_Modul (galben).</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="43" t="inlineStr">
         <is>
-          <t>4. Verifici Check=0 pe fiecare bloc; filtrezi NotaExport pe Include=DA și imporți.</t>
+          <t>3. Jurnalele și NotaExport se populează automat doar pentru modulele active.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="43" t="inlineStr">
+        <is>
+          <t>4. Verifici Check=0 pe fiecare bloc; filtrezi NotaExport pe Include=DA și imporți.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="43" t="inlineStr">
         <is>
           <t>Nu se creează conturi noi din modul — se folosesc doar conturile din politica declarată + planul de conturi pe rol.</t>
         </is>
@@ -9604,9 +9650,9 @@
   <mergeCells count="9">
     <mergeCell ref="A3:H3"/>
     <mergeCell ref="A26:H26"/>
+    <mergeCell ref="A30:H30"/>
     <mergeCell ref="A29:H29"/>
     <mergeCell ref="A25:H25"/>
-    <mergeCell ref="A24:H24"/>
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="A28:H28"/>
     <mergeCell ref="A1:H1"/>
@@ -30060,6 +30106,409 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet69.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E35"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" style="40" min="1" max="1"/>
+    <col width="44" customWidth="1" style="40" min="2" max="2"/>
+    <col width="16" customWidth="1" style="40" min="3" max="3"/>
+    <col width="16" customWidth="1" style="40" min="4" max="4"/>
+    <col width="16" customWidth="1" style="40" min="5" max="5"/>
+    <col width="46" customWidth="1" style="40" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="78" t="inlineStr">
+        <is>
+          <t>MOD_INCHIDERE_LUNARA — Declarații (input din balanță)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="79" t="inlineStr">
+        <is>
+          <t>Completează galben, din balanța de verificare a lunii: rulajul debitor, rulajul creditor și soldul final, pentru fiecare cont. Valorile implicite sunt luna-exemplu din F-422 (brut 50.000), care se reconciliază — înlocuiește-le cu ale clientului.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="80" t="inlineStr">
+        <is>
+          <t>1. Antet</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="81" t="inlineStr">
+        <is>
+          <t>Luna verificată</t>
+        </is>
+      </c>
+      <c r="B5" s="82" t="inlineStr">
+        <is>
+          <t>iulie 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="81" t="inlineStr">
+        <is>
+          <t>Societate</t>
+        </is>
+      </c>
+      <c r="B6" s="81" t="str">
+        <f>Parametri!B5</f>
+        <v>SC EXEMPLU SRL</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="80" t="inlineStr">
+        <is>
+          <t>2. Obligații constituite lunar și achitate în luna următoare</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="79" t="inlineStr">
+        <is>
+          <t>Regula: la sfârșitul lunii, soldul creditor = rulajul creditor al lunii. Un sold mai mare înseamnă restanță, iar mărimea ei spune de cât timp.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="83" t="inlineStr">
+        <is>
+          <t>Cont</t>
+        </is>
+      </c>
+      <c r="B10" s="83" t="inlineStr">
+        <is>
+          <t>Denumire</t>
+        </is>
+      </c>
+      <c r="C10" s="83" t="inlineStr">
+        <is>
+          <t>Rulaj debitor</t>
+        </is>
+      </c>
+      <c r="D10" s="83" t="inlineStr">
+        <is>
+          <t>Rulaj creditor</t>
+        </is>
+      </c>
+      <c r="E10" s="83" t="inlineStr">
+        <is>
+          <t>Sold creditor</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="81" t="inlineStr">
+        <is>
+          <t>444</t>
+        </is>
+      </c>
+      <c r="B11" s="81" t="inlineStr">
+        <is>
+          <t>Impozit pe venituri din salarii</t>
+        </is>
+      </c>
+      <c r="C11" s="81" t="n">
+        <v>3250</v>
+      </c>
+      <c r="D11" s="81" t="n">
+        <v>3250</v>
+      </c>
+      <c r="E11" s="81" t="n">
+        <v>3250</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="81" t="inlineStr">
+        <is>
+          <t>4315</t>
+        </is>
+      </c>
+      <c r="B12" s="81" t="inlineStr">
+        <is>
+          <t>CAS — contribuția de asigurări sociale</t>
+        </is>
+      </c>
+      <c r="C12" s="81" t="n">
+        <v>12500</v>
+      </c>
+      <c r="D12" s="81" t="n">
+        <v>12500</v>
+      </c>
+      <c r="E12" s="81" t="n">
+        <v>12500</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="81" t="inlineStr">
+        <is>
+          <t>4316</t>
+        </is>
+      </c>
+      <c r="B13" s="81" t="inlineStr">
+        <is>
+          <t>CASS — asigurări sociale de sănătate</t>
+        </is>
+      </c>
+      <c r="C13" s="81" t="n">
+        <v>5000</v>
+      </c>
+      <c r="D13" s="81" t="n">
+        <v>5000</v>
+      </c>
+      <c r="E13" s="81" t="n">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="81" t="inlineStr">
+        <is>
+          <t>436</t>
+        </is>
+      </c>
+      <c r="B14" s="81" t="inlineStr">
+        <is>
+          <t>CAM — contribuția asiguratorie pentru muncă</t>
+        </is>
+      </c>
+      <c r="C14" s="81" t="n">
+        <v>1125</v>
+      </c>
+      <c r="D14" s="81" t="n">
+        <v>1125</v>
+      </c>
+      <c r="E14" s="81" t="n">
+        <v>1125</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="81" t="inlineStr">
+        <is>
+          <t>427</t>
+        </is>
+      </c>
+      <c r="B15" s="81" t="inlineStr">
+        <is>
+          <t>Rețineri din salarii datorate terților</t>
+        </is>
+      </c>
+      <c r="C15" s="81" t="n">
+        <v>0</v>
+      </c>
+      <c r="D15" s="81" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" s="81" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="80" t="inlineStr">
+        <is>
+          <t>3. Datoria față de salariați</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="81" t="inlineStr">
+        <is>
+          <t>Sold creditor 421 — salarii datorate</t>
+        </is>
+      </c>
+      <c r="B18" s="82" t="n">
+        <v>29250</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="81" t="inlineStr">
+        <is>
+          <t>Sold creditor 423 — ajutoare materiale</t>
+        </is>
+      </c>
+      <c r="B19" s="82" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="81" t="inlineStr">
+        <is>
+          <t>Rest de plată din statul de plată</t>
+        </is>
+      </c>
+      <c r="B20" s="82" t="n">
+        <v>29250</v>
+      </c>
+      <c r="C20" s="79" t="inlineStr">
+        <is>
+          <t>Se ia din stat, nu din balanță — asta e tot rostul corelației</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="80" t="inlineStr">
+        <is>
+          <t>4. Baza CAM</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="81" t="inlineStr">
+        <is>
+          <t>Rulaj creditor 421 — brutul realizat al lunii</t>
+        </is>
+      </c>
+      <c r="B23" s="82" t="n">
+        <v>50000</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="81" t="inlineStr">
+        <is>
+          <t>Cota CAM</t>
+        </is>
+      </c>
+      <c r="B24" s="81">
+        <f>param_cota_cam</f>
+        <v>0.0225</v>
+      </c>
+      <c r="C24" s="79" t="inlineStr">
+        <is>
+          <t>Din Parametri; 2,25% aplicat la fondul de salarii</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="80" t="inlineStr">
+        <is>
+          <t>5. Conturi de tranzit — trebuie golite</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="83" t="inlineStr">
+        <is>
+          <t>Cont</t>
+        </is>
+      </c>
+      <c r="B27" s="83" t="inlineStr">
+        <is>
+          <t>Denumire</t>
+        </is>
+      </c>
+      <c r="C27" s="83" t="inlineStr">
+        <is>
+          <t>Sold la sfârșitul lunii</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="81" t="inlineStr">
+        <is>
+          <t>473</t>
+        </is>
+      </c>
+      <c r="B28" s="81" t="inlineStr">
+        <is>
+          <t>Decontări din operațiuni în curs de clarificare</t>
+        </is>
+      </c>
+      <c r="C28" s="81" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="81" t="inlineStr">
+        <is>
+          <t>581</t>
+        </is>
+      </c>
+      <c r="B29" s="81" t="inlineStr">
+        <is>
+          <t>Viramente interne</t>
+        </is>
+      </c>
+      <c r="C29" s="81" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="81" t="inlineStr">
+        <is>
+          <t>542</t>
+        </is>
+      </c>
+      <c r="B30" s="81" t="inlineStr">
+        <is>
+          <t>Avansuri de trezorerie</t>
+        </is>
+      </c>
+      <c r="C30" s="81" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="81" t="inlineStr">
+        <is>
+          <t>4382</t>
+        </is>
+      </c>
+      <c r="B31" s="81" t="inlineStr">
+        <is>
+          <t>Alte creanțe sociale (de recuperat de la FNUASS)</t>
+        </is>
+      </c>
+      <c r="C31" s="81" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="80" t="inlineStr">
+        <is>
+          <t>6. TVA</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="81" t="inlineStr">
+        <is>
+          <t>Sold 4423 din balanță</t>
+        </is>
+      </c>
+      <c r="B34" s="82" t="n">
+        <v>5250</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="81" t="inlineStr">
+        <is>
+          <t>Sold de plată din decontul de TVA</t>
+        </is>
+      </c>
+      <c r="B35" s="82" t="n">
+        <v>5250</v>
+      </c>
+      <c r="C35" s="79" t="inlineStr">
+        <is>
+          <t>Soldul, nu rulajul lunii. La rambursare, atenția merge pe soldul cu care pleci</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr filterMode="0">
@@ -30289,6 +30738,1227 @@
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet70.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D22"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" style="40" min="1" max="1"/>
+    <col width="52" customWidth="1" style="40" min="2" max="2"/>
+    <col width="52" customWidth="1" style="40" min="3" max="3"/>
+    <col width="52" customWidth="1" style="40" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="78" t="inlineStr">
+        <is>
+          <t>MOD_INCHIDERE_LUNARA — Reguli</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="79" t="inlineStr">
+        <is>
+          <t>Tabele fixe. Se editează doar când se schimbă legea sau când o corelație nouă intră în workbook-ul de plan.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="80" t="inlineStr">
+        <is>
+          <t>Tabelul A — corelațiile verificate și ce le rupe</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="83" t="inlineStr">
+        <is>
+          <t>Cod</t>
+        </is>
+      </c>
+      <c r="B5" s="83" t="inlineStr">
+        <is>
+          <t>Corelația</t>
+        </is>
+      </c>
+      <c r="C5" s="83" t="inlineStr">
+        <is>
+          <t>Ce o rupe LEGITIM</t>
+        </is>
+      </c>
+      <c r="D5" s="83" t="inlineStr">
+        <is>
+          <t>Ce o rupe SUSPECT</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="81" t="inlineStr">
+        <is>
+          <t>C-24</t>
+        </is>
+      </c>
+      <c r="B6" s="81" t="inlineStr">
+        <is>
+          <t>sold C 421 + sold C 423 = rest de plată din stat</t>
+        </is>
+      </c>
+      <c r="C6" s="81" t="inlineStr">
+        <is>
+          <t>Avans pe 425, nescăzut încă · drepturi neridicate mutate pe 426</t>
+        </is>
+      </c>
+      <c r="D6" s="81" t="inlineStr">
+        <is>
+          <t>Plată înregistrată pe alt cont decât 421 · salarii restante nereclasificate</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="81" t="inlineStr">
+        <is>
+          <t>C-25</t>
+        </is>
+      </c>
+      <c r="B7" s="81" t="inlineStr">
+        <is>
+          <t>rulaj C 444 = sold C 444</t>
+        </is>
+      </c>
+      <c r="C7" s="81" t="inlineStr">
+        <is>
+          <t>Rectificativă pe o lună anterioară · plată în avans</t>
+        </is>
+      </c>
+      <c r="D7" s="81" t="inlineStr">
+        <is>
+          <t>Sold &gt; rulaj constant = stopaj la sursă nevirat. Peste 30 de zile, penal</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="81" t="inlineStr">
+        <is>
+          <t>C-26</t>
+        </is>
+      </c>
+      <c r="B8" s="81" t="inlineStr">
+        <is>
+          <t>rulaj C 4315/4316/436 = soldurile lor</t>
+        </is>
+      </c>
+      <c r="C8" s="81" t="inlineStr">
+        <is>
+          <t>Rectificativă · eșalonare la plată aprobată de ANAF</t>
+        </is>
+      </c>
+      <c r="D8" s="81" t="inlineStr">
+        <is>
+          <t>Contribuții restante · bază de calcul care nu corespunde brutului</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="81" t="inlineStr">
+        <is>
+          <t>C-27</t>
+        </is>
+      </c>
+      <c r="B9" s="81" t="inlineStr">
+        <is>
+          <t>cota CAM × rulaj C 421 = rulaj C 436</t>
+        </is>
+      </c>
+      <c r="C9" s="81" t="inlineStr">
+        <is>
+          <t>Luni cu concedii medicale: CAM nu se datorează pe partea din FNUASS (art. 220^5) · categorii cu cotă redusă</t>
+        </is>
+      </c>
+      <c r="D9" s="81" t="inlineStr">
+        <is>
+          <t>Sporuri sau prime omise din fondul de salarii · CAM înregistrat invers</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="81" t="inlineStr">
+        <is>
+          <t>C-28</t>
+        </is>
+      </c>
+      <c r="B10" s="81" t="inlineStr">
+        <is>
+          <t>rulaj C 427 = sold C 427</t>
+        </is>
+      </c>
+      <c r="C10" s="81" t="inlineStr">
+        <is>
+          <t>Poprire înființată la final de lună, cu virare în luna următoare</t>
+        </is>
+      </c>
+      <c r="D10" s="81" t="inlineStr">
+        <is>
+          <t>Sold care persistă = bani opriți din salariul altcuiva și nevirați</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="81" t="inlineStr">
+        <is>
+          <t>C-29</t>
+        </is>
+      </c>
+      <c r="B11" s="81" t="inlineStr">
+        <is>
+          <t>sold 4423 din balanță = sold din decontul de TVA</t>
+        </is>
+      </c>
+      <c r="C11" s="81" t="inlineStr">
+        <is>
+          <t>Sume din decizii de impunere, pe analitic distinct (F-421)</t>
+        </is>
+      </c>
+      <c r="D11" s="81" t="inlineStr">
+        <is>
+          <t>TVA neachitat din perioade precedente, omis din decont</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="81" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="B12" s="81" t="inlineStr">
+        <is>
+          <t>sold 473, 581, 542, 4382 = 0</t>
+        </is>
+      </c>
+      <c r="C12" s="81" t="inlineStr">
+        <is>
+          <t>Operațiune de final de lună, închisă în primele zile ale lunii următoare</t>
+        </is>
+      </c>
+      <c r="D12" s="81" t="inlineStr">
+        <is>
+          <t>Sold care se reportează = operațiune neterminată, ascunsă în balanță</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="80" t="inlineStr">
+        <is>
+          <t>Tabelul B — cadențele, din foaia „Închideri periodice”</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="79" t="inlineStr">
+        <is>
+          <t>Lista nu se rescrie aici: e aceeași cu cea din workbook-ul de plan, care o derivă din stările terminale ale fluxurilor (poarta 17).</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="80" t="inlineStr">
+        <is>
+          <t>Tabelul C — LIMITĂRI DECLARATE</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="83" t="inlineStr">
+        <is>
+          <t>Ce NU face modulul</t>
+        </is>
+      </c>
+      <c r="B18" s="83" t="inlineStr">
+        <is>
+          <t>De ce contează</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="81" t="inlineStr">
+        <is>
+          <t>Verifică solduri, nu documente</t>
+        </is>
+      </c>
+      <c r="B19" s="81" t="inlineStr">
+        <is>
+          <t>Nu poate spune dacă statul de plată e corect întocmit — doar dacă balanța se potrivește cu el. Un stat greșit, reflectat fidel în balanță, trece.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="81" t="inlineStr">
+        <is>
+          <t>Restul de plată se introduce manual</t>
+        </is>
+      </c>
+      <c r="B20" s="81" t="inlineStr">
+        <is>
+          <t>Vine din stat, nu din balanță. Dacă îl copiezi din balanță, corelația devine tautologie și nu mai verifică nimic.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="81" t="inlineStr">
+        <is>
+          <t>Conturile fără corelație declarată nu apar</t>
+        </is>
+      </c>
+      <c r="B21" s="81" t="inlineStr">
+        <is>
+          <t>455, 461, 462, 5187 au cadență, dar niciun flux nu le declară starea terminală. Golul e declarat în `date/inchideri.py`, nu ascuns aici.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="81" t="inlineStr">
+        <is>
+          <t>O singură lună odată</t>
+        </is>
+      </c>
+      <c r="B22" s="81" t="inlineStr">
+        <is>
+          <t>Restanța se vede ca diferență sold − rulaj, dar vechimea ei se află doar comparând mai multe luni. Aici se vede CĂ există, nu de când.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet71.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F29"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" style="40" min="1" max="1"/>
+    <col width="46" customWidth="1" style="40" min="2" max="2"/>
+    <col width="16" customWidth="1" style="40" min="3" max="3"/>
+    <col width="16" customWidth="1" style="40" min="4" max="4"/>
+    <col width="16" customWidth="1" style="40" min="5" max="5"/>
+    <col width="40" customWidth="1" style="40" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="78" t="inlineStr">
+        <is>
+          <t>MOD_INCHIDERE_LUNARA — Verificări</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="79" t="inlineStr">
+        <is>
+          <t>O linie pe corelație, calculată din Declarații. Coloana „Diferență” e ce contează: zero înseamnă că se potrivește.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="80" t="inlineStr">
+        <is>
+          <t>V1 — obligații lunare: rulaj creditor = sold creditor</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="83" t="inlineStr">
+        <is>
+          <t>Cod</t>
+        </is>
+      </c>
+      <c r="B5" s="83" t="inlineStr">
+        <is>
+          <t>Ce verifică</t>
+        </is>
+      </c>
+      <c r="C5" s="83" t="inlineStr">
+        <is>
+          <t>Rulaj C</t>
+        </is>
+      </c>
+      <c r="D5" s="83" t="inlineStr">
+        <is>
+          <t>Sold C</t>
+        </is>
+      </c>
+      <c r="E5" s="83" t="inlineStr">
+        <is>
+          <t>Diferență</t>
+        </is>
+      </c>
+      <c r="F5" s="83" t="inlineStr">
+        <is>
+          <t>Verdict</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="81" t="inlineStr">
+        <is>
+          <t>C-25</t>
+        </is>
+      </c>
+      <c r="B6" s="81" t="inlineStr">
+        <is>
+          <t>444 — Impozit pe venituri din salarii</t>
+        </is>
+      </c>
+      <c r="C6" s="81">
+        <f>Declarații_INCHIDERE_LUNARA!D11</f>
+        <v>3250</v>
+      </c>
+      <c r="D6" s="81">
+        <f>Declarații_INCHIDERE_LUNARA!E11</f>
+        <v>3250</v>
+      </c>
+      <c r="E6" s="81">
+        <f>Declarații_INCHIDERE_LUNARA!E11-Declarații_INCHIDERE_LUNARA!D11</f>
+        <v>0</v>
+      </c>
+      <c r="F6" s="81" t="str">
+        <f>IF(ABS(E6)&lt;0.01,"OK","ATENȚIE — sold peste rulaj: restanță de "&amp;TEXT(E6,"#,##0")&amp;" lei")</f>
+        <v>OK</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="81" t="inlineStr">
+        <is>
+          <t>C-26</t>
+        </is>
+      </c>
+      <c r="B7" s="81" t="inlineStr">
+        <is>
+          <t>4315 — CAS — contribuția de asigurări sociale</t>
+        </is>
+      </c>
+      <c r="C7" s="81">
+        <f>Declarații_INCHIDERE_LUNARA!D12</f>
+        <v>12500</v>
+      </c>
+      <c r="D7" s="81">
+        <f>Declarații_INCHIDERE_LUNARA!E12</f>
+        <v>12500</v>
+      </c>
+      <c r="E7" s="81">
+        <f>Declarații_INCHIDERE_LUNARA!E12-Declarații_INCHIDERE_LUNARA!D12</f>
+        <v>0</v>
+      </c>
+      <c r="F7" s="81" t="str">
+        <f>IF(ABS(E7)&lt;0.01,"OK","ATENȚIE — sold peste rulaj: restanță de "&amp;TEXT(E7,"#,##0")&amp;" lei")</f>
+        <v>OK</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="81" t="inlineStr">
+        <is>
+          <t>C-26</t>
+        </is>
+      </c>
+      <c r="B8" s="81" t="inlineStr">
+        <is>
+          <t>4316 — CASS — asigurări sociale de sănătate</t>
+        </is>
+      </c>
+      <c r="C8" s="81">
+        <f>Declarații_INCHIDERE_LUNARA!D13</f>
+        <v>5000</v>
+      </c>
+      <c r="D8" s="81">
+        <f>Declarații_INCHIDERE_LUNARA!E13</f>
+        <v>5000</v>
+      </c>
+      <c r="E8" s="81">
+        <f>Declarații_INCHIDERE_LUNARA!E13-Declarații_INCHIDERE_LUNARA!D13</f>
+        <v>0</v>
+      </c>
+      <c r="F8" s="81" t="str">
+        <f>IF(ABS(E8)&lt;0.01,"OK","ATENȚIE — sold peste rulaj: restanță de "&amp;TEXT(E8,"#,##0")&amp;" lei")</f>
+        <v>OK</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="81" t="inlineStr">
+        <is>
+          <t>C-26</t>
+        </is>
+      </c>
+      <c r="B9" s="81" t="inlineStr">
+        <is>
+          <t>436 — CAM — contribuția asiguratorie pentru muncă</t>
+        </is>
+      </c>
+      <c r="C9" s="81">
+        <f>Declarații_INCHIDERE_LUNARA!D14</f>
+        <v>1125</v>
+      </c>
+      <c r="D9" s="81">
+        <f>Declarații_INCHIDERE_LUNARA!E14</f>
+        <v>1125</v>
+      </c>
+      <c r="E9" s="81">
+        <f>Declarații_INCHIDERE_LUNARA!E14-Declarații_INCHIDERE_LUNARA!D14</f>
+        <v>0</v>
+      </c>
+      <c r="F9" s="81" t="str">
+        <f>IF(ABS(E9)&lt;0.01,"OK","ATENȚIE — sold peste rulaj: restanță de "&amp;TEXT(E9,"#,##0")&amp;" lei")</f>
+        <v>OK</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="81" t="inlineStr">
+        <is>
+          <t>C-28</t>
+        </is>
+      </c>
+      <c r="B10" s="81" t="inlineStr">
+        <is>
+          <t>427 — Rețineri din salarii datorate terților</t>
+        </is>
+      </c>
+      <c r="C10" s="81">
+        <f>Declarații_INCHIDERE_LUNARA!D15</f>
+        <v>0</v>
+      </c>
+      <c r="D10" s="81">
+        <f>Declarații_INCHIDERE_LUNARA!E15</f>
+        <v>0</v>
+      </c>
+      <c r="E10" s="81">
+        <f>Declarații_INCHIDERE_LUNARA!E15-Declarații_INCHIDERE_LUNARA!D15</f>
+        <v>0</v>
+      </c>
+      <c r="F10" s="81" t="str">
+        <f>IF(ABS(E10)&lt;0.01,"OK","ATENȚIE — sold peste rulaj: restanță de "&amp;TEXT(E10,"#,##0")&amp;" lei")</f>
+        <v>OK</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="80" t="inlineStr">
+        <is>
+          <t>V2 — datoria față de salariați</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="83" t="inlineStr">
+        <is>
+          <t>Cod</t>
+        </is>
+      </c>
+      <c r="B13" s="83" t="inlineStr">
+        <is>
+          <t>Ce verifică</t>
+        </is>
+      </c>
+      <c r="C13" s="83" t="inlineStr">
+        <is>
+          <t>Din balanță</t>
+        </is>
+      </c>
+      <c r="D13" s="83" t="inlineStr">
+        <is>
+          <t>Din stat</t>
+        </is>
+      </c>
+      <c r="E13" s="83" t="inlineStr">
+        <is>
+          <t>Diferență</t>
+        </is>
+      </c>
+      <c r="F13" s="83" t="inlineStr">
+        <is>
+          <t>Verdict</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="81" t="inlineStr">
+        <is>
+          <t>C-24</t>
+        </is>
+      </c>
+      <c r="B14" s="81" t="inlineStr">
+        <is>
+          <t>421 + 423 = rest de plată de pe stat</t>
+        </is>
+      </c>
+      <c r="C14" s="81">
+        <f>Declarații_INCHIDERE_LUNARA!B18+Declarații_INCHIDERE_LUNARA!B19</f>
+        <v>29250</v>
+      </c>
+      <c r="D14" s="81">
+        <f>Declarații_INCHIDERE_LUNARA!B20</f>
+        <v>29250</v>
+      </c>
+      <c r="E14" s="81">
+        <f>Declarații_INCHIDERE_LUNARA!B18+Declarații_INCHIDERE_LUNARA!B19-Declarații_INCHIDERE_LUNARA!B20</f>
+        <v>0</v>
+      </c>
+      <c r="F14" s="81" t="str">
+        <f>IF(ABS(E14)&lt;0.01,"OK","ATENȚIE — balanța nu corespunde statului")</f>
+        <v>OK</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="80" t="inlineStr">
+        <is>
+          <t>V3 — conturi de tranzit, care trebuie golite</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="83" t="inlineStr">
+        <is>
+          <t>Cod</t>
+        </is>
+      </c>
+      <c r="B17" s="83" t="inlineStr">
+        <is>
+          <t>Ce verifică</t>
+        </is>
+      </c>
+      <c r="C17" s="83" t="inlineStr">
+        <is>
+          <t>Sold</t>
+        </is>
+      </c>
+      <c r="D17" s="83" t="inlineStr">
+        <is>
+          <t>Așteptat</t>
+        </is>
+      </c>
+      <c r="E17" s="83" t="inlineStr">
+        <is>
+          <t>Diferență</t>
+        </is>
+      </c>
+      <c r="F17" s="83" t="inlineStr">
+        <is>
+          <t>Verdict</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="81" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="B18" s="81" t="inlineStr">
+        <is>
+          <t>473 — Decontări din operațiuni în curs de clarificare</t>
+        </is>
+      </c>
+      <c r="C18" s="81">
+        <f>Declarații_INCHIDERE_LUNARA!C28</f>
+        <v>0</v>
+      </c>
+      <c r="D18" s="81" t="n">
+        <v>0</v>
+      </c>
+      <c r="E18" s="81">
+        <f>Declarații_INCHIDERE_LUNARA!C28</f>
+        <v>0</v>
+      </c>
+      <c r="F18" s="81" t="str">
+        <f>IF(ABS(E18)&lt;0.01,"OK","ATENȚIE — operațiune neterminată, ascunsă în balanță")</f>
+        <v>OK</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="81" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="B19" s="81" t="inlineStr">
+        <is>
+          <t>581 — Viramente interne</t>
+        </is>
+      </c>
+      <c r="C19" s="81">
+        <f>Declarații_INCHIDERE_LUNARA!C29</f>
+        <v>0</v>
+      </c>
+      <c r="D19" s="81" t="n">
+        <v>0</v>
+      </c>
+      <c r="E19" s="81">
+        <f>Declarații_INCHIDERE_LUNARA!C29</f>
+        <v>0</v>
+      </c>
+      <c r="F19" s="81" t="str">
+        <f>IF(ABS(E19)&lt;0.01,"OK","ATENȚIE — operațiune neterminată, ascunsă în balanță")</f>
+        <v>OK</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="81" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="B20" s="81" t="inlineStr">
+        <is>
+          <t>542 — Avansuri de trezorerie</t>
+        </is>
+      </c>
+      <c r="C20" s="81">
+        <f>Declarații_INCHIDERE_LUNARA!C30</f>
+        <v>0</v>
+      </c>
+      <c r="D20" s="81" t="n">
+        <v>0</v>
+      </c>
+      <c r="E20" s="81">
+        <f>Declarații_INCHIDERE_LUNARA!C30</f>
+        <v>0</v>
+      </c>
+      <c r="F20" s="81" t="str">
+        <f>IF(ABS(E20)&lt;0.01,"OK","ATENȚIE — operațiune neterminată, ascunsă în balanță")</f>
+        <v>OK</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="81" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="B21" s="81" t="inlineStr">
+        <is>
+          <t>4382 — Alte creanțe sociale (de recuperat de la FNUASS)</t>
+        </is>
+      </c>
+      <c r="C21" s="81">
+        <f>Declarații_INCHIDERE_LUNARA!C31</f>
+        <v>0</v>
+      </c>
+      <c r="D21" s="81" t="n">
+        <v>0</v>
+      </c>
+      <c r="E21" s="81">
+        <f>Declarații_INCHIDERE_LUNARA!C31</f>
+        <v>0</v>
+      </c>
+      <c r="F21" s="81" t="str">
+        <f>IF(ABS(E21)&lt;0.01,"OK","ATENȚIE — operațiune neterminată, ascunsă în balanță")</f>
+        <v>OK</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="80" t="inlineStr">
+        <is>
+          <t>V4 — CAM pe cifre și TVA</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="83" t="inlineStr">
+        <is>
+          <t>Cod</t>
+        </is>
+      </c>
+      <c r="B24" s="83" t="inlineStr">
+        <is>
+          <t>Ce verifică</t>
+        </is>
+      </c>
+      <c r="C24" s="83" t="inlineStr">
+        <is>
+          <t>Calculat</t>
+        </is>
+      </c>
+      <c r="D24" s="83" t="inlineStr">
+        <is>
+          <t>Din balanță</t>
+        </is>
+      </c>
+      <c r="E24" s="83" t="inlineStr">
+        <is>
+          <t>Diferență</t>
+        </is>
+      </c>
+      <c r="F24" s="83" t="inlineStr">
+        <is>
+          <t>Verdict</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="81" t="inlineStr">
+        <is>
+          <t>C-27</t>
+        </is>
+      </c>
+      <c r="B25" s="81" t="inlineStr">
+        <is>
+          <t>cota CAM × brut = rulaj C 436</t>
+        </is>
+      </c>
+      <c r="C25" s="81">
+        <f>ROUND(Declarații_INCHIDERE_LUNARA!B23*param_cota_cam,2)</f>
+        <v>1125</v>
+      </c>
+      <c r="D25" s="81">
+        <f>Declarații_INCHIDERE_LUNARA!D14</f>
+        <v>1125</v>
+      </c>
+      <c r="E25" s="81">
+        <f>Declarații_INCHIDERE_LUNARA!D14-ROUND(Declarații_INCHIDERE_LUNARA!B23*param_cota_cam,2)</f>
+        <v>0</v>
+      </c>
+      <c r="F25" s="81" t="str">
+        <f>IF(ABS(E25)&lt;0.01,"OK","ATENȚIE — bază de calcul greșită sau concedii medicale (vezi Reguli A)")</f>
+        <v>OK</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="81" t="inlineStr">
+        <is>
+          <t>C-29</t>
+        </is>
+      </c>
+      <c r="B26" s="81" t="inlineStr">
+        <is>
+          <t>sold 4423 din balanță = sold din decont</t>
+        </is>
+      </c>
+      <c r="C26" s="81">
+        <f>Declarații_INCHIDERE_LUNARA!B34</f>
+        <v>5250</v>
+      </c>
+      <c r="D26" s="81">
+        <f>Declarații_INCHIDERE_LUNARA!B35</f>
+        <v>5250</v>
+      </c>
+      <c r="E26" s="81">
+        <f>Declarații_INCHIDERE_LUNARA!B34-Declarații_INCHIDERE_LUNARA!B35</f>
+        <v>0</v>
+      </c>
+      <c r="F26" s="81" t="str">
+        <f>IF(ABS(E26)&lt;0.01,"OK","ATENȚIE — decontul și balanța nu spun același lucru")</f>
+        <v>OK</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="80" t="inlineStr">
+        <is>
+          <t>Control final</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="81" t="inlineStr">
+        <is>
+          <t>Check — toate corelațiile lunii</t>
+        </is>
+      </c>
+      <c r="B29" s="81">
+        <f>ABS(E6)+ABS(E7)+ABS(E8)+ABS(E9)+ABS(E10)+ABS(E14)+ABS(E18)+ABS(E19)+ABS(E20)+ABS(E21)+ABS(E25)+ABS(E26)</f>
+        <v>0</v>
+      </c>
+      <c r="C29" s="81" t="str">
+        <f>IF(ABS(B29)&lt;0.01,"OK — luna se reconciliază pe toate corelațiile","EROARE — vezi foaia Abateri")</f>
+        <v>OK — luna se reconciliază pe toate corelațiile</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet72.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E18"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" style="40" min="1" max="1"/>
+    <col width="12" customWidth="1" style="40" min="2" max="2"/>
+    <col width="46" customWidth="1" style="40" min="3" max="3"/>
+    <col width="16" customWidth="1" style="40" min="4" max="4"/>
+    <col width="56" customWidth="1" style="40" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="78" t="inlineStr">
+        <is>
+          <t>MOD_INCHIDERE_LUNARA — Abateri</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="79" t="inlineStr">
+        <is>
+          <t>Coloana „Include” spune DA doar unde corelația nu s-a potrivit. Lista e completă: dacă toate sunt NU, luna e curată.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="83" t="inlineStr">
+        <is>
+          <t>Include</t>
+        </is>
+      </c>
+      <c r="B4" s="83" t="inlineStr">
+        <is>
+          <t>Cod</t>
+        </is>
+      </c>
+      <c r="C4" s="83" t="inlineStr">
+        <is>
+          <t>Ce nu s-a potrivit</t>
+        </is>
+      </c>
+      <c r="D4" s="83" t="inlineStr">
+        <is>
+          <t>Diferență</t>
+        </is>
+      </c>
+      <c r="E4" s="83" t="inlineStr">
+        <is>
+          <t>Ce se face</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="81" t="str">
+        <f>IF(ABS(Verificări_INCHIDERE_LUNARA!E6)&lt;0.01,"NU","DA")</f>
+        <v>NU</v>
+      </c>
+      <c r="B5" s="81" t="inlineStr">
+        <is>
+          <t>C-25</t>
+        </is>
+      </c>
+      <c r="C5" s="81" t="inlineStr">
+        <is>
+          <t>444 Impozit pe venituri din salarii</t>
+        </is>
+      </c>
+      <c r="D5" s="81">
+        <f>Verificări_INCHIDERE_LUNARA!E6</f>
+        <v>0</v>
+      </c>
+      <c r="E5" s="81" t="inlineStr">
+        <is>
+          <t>Se verifică fișa de plătitor din SPV. Stopaj nevirat peste 30 de zile = răspundere penală, nu întârziere.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="81" t="str">
+        <f>IF(ABS(Verificări_INCHIDERE_LUNARA!E7)&lt;0.01,"NU","DA")</f>
+        <v>NU</v>
+      </c>
+      <c r="B6" s="81" t="inlineStr">
+        <is>
+          <t>C-26</t>
+        </is>
+      </c>
+      <c r="C6" s="81" t="inlineStr">
+        <is>
+          <t>4315 CAS — contribuția de asigurări sociale</t>
+        </is>
+      </c>
+      <c r="D6" s="81">
+        <f>Verificări_INCHIDERE_LUNARA!E7</f>
+        <v>0</v>
+      </c>
+      <c r="E6" s="81" t="inlineStr">
+        <is>
+          <t>Se confruntă cu D112. Dacă e eșalonare, se notează; altfel e restanță.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="81" t="str">
+        <f>IF(ABS(Verificări_INCHIDERE_LUNARA!E8)&lt;0.01,"NU","DA")</f>
+        <v>NU</v>
+      </c>
+      <c r="B7" s="81" t="inlineStr">
+        <is>
+          <t>C-26</t>
+        </is>
+      </c>
+      <c r="C7" s="81" t="inlineStr">
+        <is>
+          <t>4316 CASS — asigurări sociale de sănătate</t>
+        </is>
+      </c>
+      <c r="D7" s="81">
+        <f>Verificări_INCHIDERE_LUNARA!E8</f>
+        <v>0</v>
+      </c>
+      <c r="E7" s="81" t="inlineStr">
+        <is>
+          <t>Se confruntă cu D112. Dacă e eșalonare, se notează; altfel e restanță.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="81" t="str">
+        <f>IF(ABS(Verificări_INCHIDERE_LUNARA!E9)&lt;0.01,"NU","DA")</f>
+        <v>NU</v>
+      </c>
+      <c r="B8" s="81" t="inlineStr">
+        <is>
+          <t>C-26</t>
+        </is>
+      </c>
+      <c r="C8" s="81" t="inlineStr">
+        <is>
+          <t>436 CAM — contribuția asiguratorie pentru muncă</t>
+        </is>
+      </c>
+      <c r="D8" s="81">
+        <f>Verificări_INCHIDERE_LUNARA!E9</f>
+        <v>0</v>
+      </c>
+      <c r="E8" s="81" t="inlineStr">
+        <is>
+          <t>Se confruntă cu D112. Dacă e eșalonare, se notează; altfel e restanță.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="81" t="str">
+        <f>IF(ABS(Verificări_INCHIDERE_LUNARA!E10)&lt;0.01,"NU","DA")</f>
+        <v>NU</v>
+      </c>
+      <c r="B9" s="81" t="inlineStr">
+        <is>
+          <t>C-28</t>
+        </is>
+      </c>
+      <c r="C9" s="81" t="inlineStr">
+        <is>
+          <t>427 Rețineri din salarii datorate terților</t>
+        </is>
+      </c>
+      <c r="D9" s="81">
+        <f>Verificări_INCHIDERE_LUNARA!E10</f>
+        <v>0</v>
+      </c>
+      <c r="E9" s="81" t="inlineStr">
+        <is>
+          <t>Se virează imediat. Banii sunt ai salariatului, opriți pentru altcineva.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="81" t="str">
+        <f>IF(ABS(Verificări_INCHIDERE_LUNARA!E14)&lt;0.01,"NU","DA")</f>
+        <v>NU</v>
+      </c>
+      <c r="B10" s="81" t="inlineStr">
+        <is>
+          <t>C-24</t>
+        </is>
+      </c>
+      <c r="C10" s="81" t="inlineStr">
+        <is>
+          <t>421 + 423 vs. stat</t>
+        </is>
+      </c>
+      <c r="D10" s="81">
+        <f>Verificări_INCHIDERE_LUNARA!E14</f>
+        <v>0</v>
+      </c>
+      <c r="E10" s="81" t="inlineStr">
+        <is>
+          <t>Se scot statele lună de lună și se caută luna în care s-a rupt. Cauza tipică: plată pe alt cont decât 421.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="81" t="str">
+        <f>IF(ABS(Verificări_INCHIDERE_LUNARA!E18)&lt;0.01,"NU","DA")</f>
+        <v>NU</v>
+      </c>
+      <c r="B11" s="81" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C11" s="81" t="inlineStr">
+        <is>
+          <t>473 sold zero</t>
+        </is>
+      </c>
+      <c r="D11" s="81">
+        <f>Verificări_INCHIDERE_LUNARA!E18</f>
+        <v>0</v>
+      </c>
+      <c r="E11" s="81" t="inlineStr">
+        <is>
+          <t>Se identifică operațiunea neterminată și se închide. Un sold reportat pe un cont de tranzit ascunde ceva.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="81" t="str">
+        <f>IF(ABS(Verificări_INCHIDERE_LUNARA!E19)&lt;0.01,"NU","DA")</f>
+        <v>NU</v>
+      </c>
+      <c r="B12" s="81" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C12" s="81" t="inlineStr">
+        <is>
+          <t>581 sold zero</t>
+        </is>
+      </c>
+      <c r="D12" s="81">
+        <f>Verificări_INCHIDERE_LUNARA!E19</f>
+        <v>0</v>
+      </c>
+      <c r="E12" s="81" t="inlineStr">
+        <is>
+          <t>Se identifică operațiunea neterminată și se închide. Un sold reportat pe un cont de tranzit ascunde ceva.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="81" t="str">
+        <f>IF(ABS(Verificări_INCHIDERE_LUNARA!E20)&lt;0.01,"NU","DA")</f>
+        <v>NU</v>
+      </c>
+      <c r="B13" s="81" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C13" s="81" t="inlineStr">
+        <is>
+          <t>542 sold zero</t>
+        </is>
+      </c>
+      <c r="D13" s="81">
+        <f>Verificări_INCHIDERE_LUNARA!E20</f>
+        <v>0</v>
+      </c>
+      <c r="E13" s="81" t="inlineStr">
+        <is>
+          <t>Se identifică operațiunea neterminată și se închide. Un sold reportat pe un cont de tranzit ascunde ceva.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="81" t="str">
+        <f>IF(ABS(Verificări_INCHIDERE_LUNARA!E21)&lt;0.01,"NU","DA")</f>
+        <v>NU</v>
+      </c>
+      <c r="B14" s="81" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C14" s="81" t="inlineStr">
+        <is>
+          <t>4382 sold zero</t>
+        </is>
+      </c>
+      <c r="D14" s="81">
+        <f>Verificări_INCHIDERE_LUNARA!E21</f>
+        <v>0</v>
+      </c>
+      <c r="E14" s="81" t="inlineStr">
+        <is>
+          <t>Se identifică operațiunea neterminată și se închide. Un sold reportat pe un cont de tranzit ascunde ceva.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="81" t="str">
+        <f>IF(ABS(Verificări_INCHIDERE_LUNARA!E25)&lt;0.01,"NU","DA")</f>
+        <v>NU</v>
+      </c>
+      <c r="B15" s="81" t="inlineStr">
+        <is>
+          <t>C-27</t>
+        </is>
+      </c>
+      <c r="C15" s="81" t="inlineStr">
+        <is>
+          <t>CAM pe cifre</t>
+        </is>
+      </c>
+      <c r="D15" s="81">
+        <f>Verificări_INCHIDERE_LUNARA!E25</f>
+        <v>0</v>
+      </c>
+      <c r="E15" s="81" t="inlineStr">
+        <is>
+          <t>Se verifică dacă luna are concedii medicale — CAM nu se datorează pe partea din FNUASS. Altfel, bază de calcul incompletă.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="81" t="str">
+        <f>IF(ABS(Verificări_INCHIDERE_LUNARA!E26)&lt;0.01,"NU","DA")</f>
+        <v>NU</v>
+      </c>
+      <c r="B16" s="81" t="inlineStr">
+        <is>
+          <t>C-29</t>
+        </is>
+      </c>
+      <c r="C16" s="81" t="inlineStr">
+        <is>
+          <t>4423 vs. decont</t>
+        </is>
+      </c>
+      <c r="D16" s="81">
+        <f>Verificări_INCHIDERE_LUNARA!E26</f>
+        <v>0</v>
+      </c>
+      <c r="E16" s="81" t="inlineStr">
+        <is>
+          <t>Se verifică dacă e sumă din decizie de impunere (analitic distinct) sau TVA neachitat din perioade precedente, omis din decont.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="81" t="inlineStr">
+        <is>
+          <t>Check — număr de abateri</t>
+        </is>
+      </c>
+      <c r="B18" s="81">
+        <f>COUNTIF(A5:A16,"DA")</f>
+        <v>0</v>
+      </c>
+      <c r="C18" s="81" t="str">
+        <f>IF(B18=0,"OK — nicio abatere","ATENȚIE — "&amp;B18&amp;" corelații nu se potrivesc")</f>
+        <v>OK — nicio abatere</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 

--- a/dist/Module_Declarative_Fluxuri.xlsx
+++ b/dist/Module_Declarative_Fluxuri.xlsx
@@ -71,18 +71,22 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reguli_TVA_INC" sheetId="62" state="visible" r:id="rId62"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Jurnale_TVA_INC" sheetId="63" state="visible" r:id="rId63"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NotaExport_TVA_INC" sheetId="64" state="visible" r:id="rId64"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Declarații_NEUTRALIZARE" sheetId="65" state="visible" r:id="rId65"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reguli_NEUTRALIZARE" sheetId="66" state="visible" r:id="rId66"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Jurnale_NEUTRALIZARE" sheetId="67" state="visible" r:id="rId67"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NotaExport_NEUTRALIZARE" sheetId="68" state="visible" r:id="rId68"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Declarații_AMANUNT" sheetId="69" state="visible" r:id="rId69"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reguli_AMANUNT" sheetId="70" state="visible" r:id="rId70"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Jurnale_AMANUNT" sheetId="71" state="visible" r:id="rId71"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NotaExport_AMANUNT" sheetId="72" state="visible" r:id="rId72"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Declarații_INCHIDERE_LUNARA" sheetId="73" state="visible" r:id="rId73"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reguli_INCHIDERE_LUNARA" sheetId="74" state="visible" r:id="rId74"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Verificări_INCHIDERE_LUNARA" sheetId="75" state="visible" r:id="rId75"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Abateri_INCHIDERE_LUNARA" sheetId="76" state="visible" r:id="rId76"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Declarații_TAXARE_INVERSA" sheetId="65" state="visible" r:id="rId65"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reguli_TAXARE_INVERSA" sheetId="66" state="visible" r:id="rId66"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Jurnale_TAXARE_INVERSA" sheetId="67" state="visible" r:id="rId67"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NotaExport_TAXARE_INVERSA" sheetId="68" state="visible" r:id="rId68"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Declarații_NEUTRALIZARE" sheetId="69" state="visible" r:id="rId69"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reguli_NEUTRALIZARE" sheetId="70" state="visible" r:id="rId70"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Jurnale_NEUTRALIZARE" sheetId="71" state="visible" r:id="rId71"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NotaExport_NEUTRALIZARE" sheetId="72" state="visible" r:id="rId72"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Declarații_AMANUNT" sheetId="73" state="visible" r:id="rId73"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reguli_AMANUNT" sheetId="74" state="visible" r:id="rId74"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Jurnale_AMANUNT" sheetId="75" state="visible" r:id="rId75"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NotaExport_AMANUNT" sheetId="76" state="visible" r:id="rId76"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Declarații_INCHIDERE_LUNARA" sheetId="77" state="visible" r:id="rId77"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reguli_INCHIDERE_LUNARA" sheetId="78" state="visible" r:id="rId78"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Verificări_INCHIDERE_LUNARA" sheetId="79" state="visible" r:id="rId79"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Abateri_INCHIDERE_LUNARA" sheetId="80" state="visible" r:id="rId80"/>
   </sheets>
   <definedNames>
     <definedName name="param_proc_rezerva">Parametri!$B$18</definedName>
@@ -828,7 +832,7 @@
     <row r="4" ht="15" customHeight="1" s="40">
       <c r="A4" s="43" t="inlineStr">
         <is>
-          <t>Cele 18 module declarative care execută fluxurile din „Plan de conturi”. Fluxul explică de ce; modulul face înregistrarea. Completezi câteva variabile într-o foaie de input și ies jurnalele și nota de export.</t>
+          <t>Cele 19 module declarative care execută fluxurile din „Plan de conturi”. Fluxul explică de ce; modulul face înregistrarea. Completezi câteva variabile într-o foaie de input și ies jurnalele și nota de export.</t>
         </is>
       </c>
     </row>
@@ -10951,7 +10955,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:H31"/>
+  <dimension ref="A1:H32"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="8" customWidth="1" style="39" min="1" max="1"/>
@@ -11742,84 +11746,126 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="62" t="inlineStr">
+      <c r="A24" s="60" t="inlineStr">
+        <is>
+          <t>NU</t>
+        </is>
+      </c>
+      <c r="B24" s="61" t="inlineStr">
+        <is>
+          <t>MOD_TAXARE_INVERSA</t>
+        </is>
+      </c>
+      <c r="C24" s="61" t="inlineStr">
+        <is>
+          <t>F-303, F-402</t>
+        </is>
+      </c>
+      <c r="D24" s="61" t="inlineStr">
+        <is>
+          <t>Pe factură</t>
+        </is>
+      </c>
+      <c r="E24" s="61" t="inlineStr">
+        <is>
+          <t>Valoare (sau valută × curs), cota TVA, tipul operațiunii, partenerul</t>
+        </is>
+      </c>
+      <c r="F24" s="61" t="inlineStr">
+        <is>
+          <t>4426 = 4427 exact; D390 doar la intracomunitar</t>
+        </is>
+      </c>
+      <c r="G24" s="61" t="inlineStr">
+        <is>
+          <t>A Achiziție intracomunitară; B Taxare inversă internă</t>
+        </is>
+      </c>
+      <c r="H24" s="61" t="inlineStr">
+        <is>
+          <t>IMPLEMENTAT</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="62" t="inlineStr">
         <is>
           <t>DA</t>
         </is>
       </c>
-      <c r="B24" s="61" t="inlineStr">
+      <c r="B25" s="61" t="inlineStr">
         <is>
           <t>MOD_INCHIDERE_LUNARA</t>
         </is>
       </c>
-      <c r="C24" s="61" t="inlineStr">
+      <c r="C25" s="61" t="inlineStr">
         <is>
           <t>F-422, F-413</t>
         </is>
       </c>
-      <c r="D24" s="61" t="inlineStr">
+      <c r="D25" s="61" t="inlineStr">
         <is>
           <t>Lunar, pe balanța de verificare</t>
         </is>
       </c>
-      <c r="E24" s="61" t="inlineStr">
+      <c r="E25" s="61" t="inlineStr">
         <is>
           <t>Rulaj debitor, rulaj creditor și sold pentru conturile cu cadență; restul de plată de pe stat; soldul din decontul de TVA</t>
         </is>
       </c>
-      <c r="F24" s="61" t="inlineStr">
+      <c r="F25" s="61" t="inlineStr">
         <is>
           <t>Verifică solduri, nu documente — vezi Reguli, tabelul C</t>
         </is>
       </c>
-      <c r="G24" s="61" t="inlineStr">
+      <c r="G25" s="61" t="inlineStr">
         <is>
           <t>V1 Obligații lunare (rulaj = sold); V2 Datoria față de salariați; V3 Conturi care trebuie golite; V4 Verificarea CAM pe cifre</t>
         </is>
       </c>
-      <c r="H24" s="61" t="inlineStr">
+      <c r="H25" s="61" t="inlineStr">
         <is>
           <t>IMPLEMENTAT</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="63" t="inlineStr">
+    <row r="27">
+      <c r="A27" s="63" t="inlineStr">
         <is>
           <t>REGULĂ DE SUMONARE</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="46" t="inlineStr">
-        <is>
-          <t>1. În CatalogModule setezi Activ=DA doar pe modulele necesare lunii.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="46" t="inlineStr">
         <is>
-          <t>2. Completezi variabilele din foaia Declarații_Modul (galben).</t>
+          <t>1. În CatalogModule setezi Activ=DA doar pe modulele necesare lunii.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="46" t="inlineStr">
         <is>
-          <t>3. Jurnalele și NotaExport se populează automat doar pentru modulele active.</t>
+          <t>2. Completezi variabilele din foaia Declarații_Modul (galben).</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="46" t="inlineStr">
         <is>
-          <t>4. Verifici Check=0 pe fiecare bloc; filtrezi NotaExport pe Include=DA și imporți.</t>
+          <t>3. Jurnalele și NotaExport se populează automat doar pentru modulele active.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="46" t="inlineStr">
+        <is>
+          <t>4. Verifici Check=0 pe fiecare bloc; filtrezi NotaExport pe Include=DA și imporți.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="46" t="inlineStr">
         <is>
           <t>Nu se creează conturi noi din modul — se folosesc doar conturile din politica declarată + planul de conturi pe rol.</t>
         </is>
@@ -11828,12 +11874,12 @@
   </sheetData>
   <mergeCells count="9">
     <mergeCell ref="A3:H3"/>
-    <mergeCell ref="A26:H26"/>
     <mergeCell ref="A30:H30"/>
     <mergeCell ref="A29:H29"/>
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="A28:H28"/>
     <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A32:H32"/>
     <mergeCell ref="A27:H27"/>
     <mergeCell ref="A31:H31"/>
   </mergeCells>
@@ -28476,25 +28522,25 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B41"/>
+  <dimension ref="A1:C46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="40" customWidth="1" style="40" min="1" max="1"/>
-    <col width="42" customWidth="1" style="40" min="2" max="2"/>
-    <col width="52" customWidth="1" style="40" min="3" max="3"/>
+    <col width="46" customWidth="1" style="40" min="1" max="1"/>
+    <col width="24" customWidth="1" style="40" min="2" max="2"/>
+    <col width="58" customWidth="1" style="40" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="41" t="inlineStr">
         <is>
-          <t>MOD_NEUTRALIZARE — Declarații (input)</t>
+          <t>MOD_TAXARE_INVERSA — Declarații (input)</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="44" t="inlineStr">
         <is>
-          <t>Acoperă F-311 (bunuri/711), F-312 (servicii/712), F-209 (imobilizări/722). Alege tipul — conturile și lanțul se adaptează. Principiu: costurile lovesc cls.6, apoi contul de venit de producție capitalizează și neutralizează.</t>
+          <t>Două cazuri, același mecanism. Pune DA pe cel care s-a întâmplat — pot fi și amândouă în aceeași lună, pe facturi diferite.</t>
         </is>
       </c>
     </row>
@@ -28530,7 +28576,7 @@
     <row r="7">
       <c r="A7" s="43" t="inlineStr">
         <is>
-          <t>Luna / proiect</t>
+          <t>Luna (AAAA-LL)</t>
         </is>
       </c>
       <c r="B7" s="64" t="inlineStr">
@@ -28542,287 +28588,368 @@
     <row r="8">
       <c r="A8" s="43" t="inlineStr">
         <is>
-          <t>Data costuri (B1)</t>
+          <t>Data jurnal</t>
         </is>
       </c>
       <c r="B8" s="64" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-31</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="43" t="inlineStr">
         <is>
-          <t>Data finalizare stoc (B2-B3)</t>
-        </is>
-      </c>
-      <c r="B9" s="64" t="inlineStr">
-        <is>
-          <t>2026-07-20</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="43" t="inlineStr">
-        <is>
-          <t>Data vânzare / recepție MF (B4)</t>
-        </is>
-      </c>
-      <c r="B10" s="64" t="inlineStr">
-        <is>
-          <t>2026-07-25</t>
+          <t>Cota TVA</t>
+        </is>
+      </c>
+      <c r="B9" s="64" t="n">
+        <v>0.21</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="42" t="inlineStr">
+        <is>
+          <t>2. Cazul A — Achiziție intracomunitară</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="42" t="inlineStr">
-        <is>
-          <t>2. Tip producție (poartă principală)</t>
+      <c r="A12" s="43" t="inlineStr">
+        <is>
+          <t>Se aplică? (DA/NU)</t>
+        </is>
+      </c>
+      <c r="B12" s="64" t="inlineStr">
+        <is>
+          <t>DA</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="43" t="inlineStr">
         <is>
-          <t>Tip (BUNURI / SERVICII / MF)</t>
+          <t>Furnizor UE</t>
         </is>
       </c>
       <c r="B13" s="64" t="inlineStr">
         <is>
-          <t>BUNURI</t>
+          <t>Furnizor UE DEMO</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="43" t="inlineStr">
         <is>
-          <t>Cont venit neutralizare (auto)</t>
-        </is>
-      </c>
-      <c r="B14" s="43">
-        <f>IF(B13="BUNURI",711,IF(B13="SERVICII",712,IF(B13="MF",722,"?")))</f>
-        <v>711</v>
+          <t>Cod TVA valid în VIES? (DA/NU)</t>
+        </is>
+      </c>
+      <c r="B14" s="64" t="inlineStr">
+        <is>
+          <t>DA</t>
+        </is>
+      </c>
+      <c r="C14" s="44" t="inlineStr">
+        <is>
+          <t>Verificat la DATA operațiunii, nu azi — VIES arată starea curentă</t>
+        </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="43" t="inlineStr">
         <is>
-          <t>Cont stoc intermediar (auto)</t>
-        </is>
-      </c>
-      <c r="B15" s="43">
-        <f>IF(B13="BUNURI",331,IF(B13="SERVICII",332,IF(B13="MF",231,"?")))</f>
-        <v>331</v>
+          <t>Valoare în valută</t>
+        </is>
+      </c>
+      <c r="B15" s="64" t="n">
+        <v>15000</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="43" t="inlineStr">
         <is>
-          <t>Cont stoc final (auto)</t>
-        </is>
-      </c>
-      <c r="B16" s="43">
-        <f>IF(B13="BUNURI",345,IF(B13="SERVICII","(nu e cazul — se stinge la livrare)",IF(B13="MF",213,"?")))</f>
-        <v>345</v>
+          <t>Curs la data facturii</t>
+        </is>
+      </c>
+      <c r="B16" s="64" t="n">
+        <v>4.97</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="43" t="inlineStr">
         <is>
-          <t>Cont venit vânzare (auto)</t>
+          <t>Valoare în lei (auto)</t>
         </is>
       </c>
       <c r="B17" s="43">
-        <f>IF(B13="BUNURI",701,IF(B13="SERVICII",704,IF(B13="MF","(nu e vânzare — e activ)","?")))</f>
-        <v>701</v>
+        <f>ROUND(B15*B16,2)</f>
+        <v>74550</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="43" t="inlineStr">
+        <is>
+          <t>TVA autolichidată (din autofactură)</t>
+        </is>
+      </c>
+      <c r="B18" s="64" t="n">
+        <v>15655.5</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="42" t="inlineStr">
-        <is>
-          <t>3. Costuri (cls.6)</t>
-        </is>
+      <c r="A19" s="43" t="inlineStr">
+        <is>
+          <t>TVA recalculată (auto)</t>
+        </is>
+      </c>
+      <c r="B19" s="43">
+        <f>ROUND(B17*B9,2)</f>
+        <v>15655.5</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="43" t="inlineStr">
         <is>
-          <t>Cost materiale (→ 601)</t>
-        </is>
-      </c>
-      <c r="B20" s="64" t="n">
-        <v>4500</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="43" t="inlineStr">
-        <is>
-          <t>Cost manoperă (→ 641)</t>
-        </is>
-      </c>
-      <c r="B21" s="64" t="n">
-        <v>0</v>
+          <t>Marfa e în tranzit? (DA = 327, NU = 371)</t>
+        </is>
+      </c>
+      <c r="B20" s="64" t="inlineStr">
+        <is>
+          <t>NU</t>
+        </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="43" t="inlineStr">
-        <is>
-          <t>Alte costuri (→ 6xx)</t>
-        </is>
-      </c>
-      <c r="B22" s="64" t="n">
-        <v>0</v>
+      <c r="A22" s="42" t="inlineStr">
+        <is>
+          <t>3. Cazul B — Taxare inversă internă</t>
+        </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="43" t="inlineStr">
         <is>
-          <t>Cost total</t>
-        </is>
-      </c>
-      <c r="B23" s="43">
-        <f>B20+B21+B22</f>
-        <v>4500</v>
+          <t>Se aplică? (DA/NU)</t>
+        </is>
+      </c>
+      <c r="B23" s="64" t="inlineStr">
+        <is>
+          <t>DA</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="43" t="inlineStr">
+        <is>
+          <t>Furnizor RO (plătitor de TVA)</t>
+        </is>
+      </c>
+      <c r="B24" s="64" t="inlineStr">
+        <is>
+          <t>Furnizor RO DEMO</t>
+        </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="42" t="inlineStr">
-        <is>
-          <t>4. Vânzare (doar BUNURI / SERVICII)</t>
+      <c r="A25" s="43" t="inlineStr">
+        <is>
+          <t>Operațiunea din art. 331 CF</t>
+        </is>
+      </c>
+      <c r="B25" s="64" t="inlineStr">
+        <is>
+          <t>Cereale</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="43" t="inlineStr">
         <is>
-          <t>Preț vânzare (fără TVA)</t>
+          <t>Valoare fără TVA</t>
         </is>
       </c>
       <c r="B26" s="64" t="n">
-        <v>7000</v>
+        <v>10000</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="43" t="inlineStr">
         <is>
-          <t>Cota TVA</t>
+          <t>TVA autolichidată (din autofactură)</t>
         </is>
       </c>
       <c r="B27" s="64" t="n">
-        <v>0.21</v>
+        <v>2100</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="43" t="inlineStr">
         <is>
-          <t>TVA</t>
+          <t>TVA recalculată (auto)</t>
         </is>
       </c>
       <c r="B28" s="43">
-        <f>IF(OR(B13="BUNURI",B13="SERVICII"),B26*B27,0)</f>
-        <v>1470</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="43" t="inlineStr">
-        <is>
-          <t>Total factură</t>
-        </is>
-      </c>
-      <c r="B29" s="43">
-        <f>B26+B28</f>
-        <v>8470</v>
+        <f>ROUND(B26*B9,2)</f>
+        <v>2100</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="42" t="inlineStr">
+        <is>
+          <t>4. Conturi</t>
+        </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="42" t="inlineStr">
-        <is>
-          <t>5. Conturi suplimentare</t>
+      <c r="A31" s="43" t="inlineStr">
+        <is>
+          <t>Cont stoc / cheltuială</t>
+        </is>
+      </c>
+      <c r="B31" s="64" t="inlineStr">
+        <is>
+          <t>371</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="43" t="inlineStr">
         <is>
-          <t>Cont materii prime</t>
+          <t>Cont tranzit (32x)</t>
         </is>
       </c>
       <c r="B32" s="64" t="inlineStr">
         <is>
-          <t>301</t>
+          <t>327</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="43" t="inlineStr">
         <is>
-          <t>Cont client</t>
+          <t>Cont furnizor UE</t>
         </is>
       </c>
       <c r="B33" s="64" t="inlineStr">
         <is>
-          <t>411.RO</t>
+          <t>401.UE</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="43" t="inlineStr">
         <is>
+          <t>Cont furnizor RO</t>
+        </is>
+      </c>
+      <c r="B34" s="64" t="inlineStr">
+        <is>
+          <t>401.RO</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="43" t="inlineStr">
+        <is>
+          <t>Cont TVA deductibilă</t>
+        </is>
+      </c>
+      <c r="B35" s="64" t="inlineStr">
+        <is>
+          <t>4426</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="43" t="inlineStr">
+        <is>
           <t>Cont TVA colectată</t>
         </is>
       </c>
-      <c r="B34" s="64" t="inlineStr">
+      <c r="B36" s="64" t="inlineStr">
         <is>
           <t>4427</t>
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="42" t="inlineStr">
-        <is>
-          <t>6. Sufix</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="43" t="inlineStr">
+    <row r="38">
+      <c r="A38" s="42" t="inlineStr">
+        <is>
+          <t>5. Sufix</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="43" t="inlineStr">
         <is>
           <t>Sufix</t>
         </is>
       </c>
-      <c r="B37" s="43" t="str">
-        <f>"— " &amp; B7 &amp; " — " &amp; B13 &amp; " — " &amp; B14</f>
-        <v>— 2026-07 — BUNURI — 711</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="42" t="inlineStr">
-        <is>
-          <t>7. Control</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="43" t="inlineStr">
-        <is>
-          <t>Marjă (vânzare − cost)</t>
-        </is>
-      </c>
-      <c r="B40" s="43">
-        <f>IF(OR(B13="BUNURI",B13="SERVICII"),B26-B23,"n/a (MF)")</f>
-        <v>2500</v>
+      <c r="B39" s="43" t="str">
+        <f>"— taxare inversă " &amp; B7</f>
+        <v>— taxare inversă 2026-07</v>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="43" t="inlineStr">
-        <is>
-          <t>Notă principiu</t>
-        </is>
-      </c>
-      <c r="B41" s="43" t="inlineStr">
-        <is>
-          <t>Costurile lovesc cls.6; contul de venit de producție (711/712/722) capitalizează și neutralizează. Descărcarea la vânzare (bunuri) e prin 711=345, nu prin 607.</t>
+      <c r="A41" s="42" t="inlineStr">
+        <is>
+          <t>6. Control</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="43" t="inlineStr">
+        <is>
+          <t>Modul activ?</t>
+        </is>
+      </c>
+      <c r="B42" s="43" t="str">
+        <f>IF(INDEX(CatalogModule!$A$1:$A$200,MATCH("MOD_TAXARE_INVERSA",CatalogModule!$B$1:$B$200,0))="DA","ACTIV","INACTIV")</f>
+        <v>INACTIV</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="43" t="inlineStr">
+        <is>
+          <t>Verificare: TVA de pe autofactură = cotă × bază</t>
+        </is>
+      </c>
+      <c r="B43" s="43" t="str">
+        <f>IF(AND(OR(B12&lt;&gt;"DA",ABS(B18-B19)&lt;0.01),OR(B23&lt;&gt;"DA",ABS(B27-B28)&lt;0.01)),"OK — TVA corect calculată pe ambele cazuri","EROARE — TVA de pe autofactură nu corespunde cotei")</f>
+        <v>OK — TVA corect calculată pe ambele cazuri</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="43" t="inlineStr">
+        <is>
+          <t>Verificare: intracomunitar fără cod VIES valid</t>
+        </is>
+      </c>
+      <c r="B44" s="43" t="str">
+        <f>IF(AND(B12="DA",B14&lt;&gt;"DA"),"ATENȚIE — fără cod VIES valid, operațiunea NU e scutită la furnizor și nu poate fi declarată în D390","OK")</f>
+        <v>OK</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="43" t="inlineStr">
+        <is>
+          <t>Declarații de depus (auto)</t>
+        </is>
+      </c>
+      <c r="B45" s="43" t="str">
+        <f>IF(B12="DA","D300 + D390 + D394","") &amp; IF(AND(B12="DA",B23="DA")," · ","") &amp; IF(B23="DA","D300 + D394 (fără D390)","")</f>
+        <v>D300 + D390 + D394 · D300 + D394 (fără D390)</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="43" t="inlineStr">
+        <is>
+          <t>Derogare art. 331 CF</t>
+        </is>
+      </c>
+      <c r="B46" s="43" t="inlineStr">
+        <is>
+          <t>Taxarea inversă INTERNĂ se aplică pe baza unei derogări UE care expiră la 31.12.2026. La 21.08.2026 nu era publicată o prelungire — reverifică înainte de prima factură din 2027.</t>
         </is>
       </c>
     </row>
@@ -28837,240 +28964,279 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F21"/>
+  <dimension ref="A1:E26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" style="40" min="1" max="1"/>
-    <col width="20" customWidth="1" style="40" min="2" max="2"/>
-    <col width="20" customWidth="1" style="40" min="3" max="3"/>
-    <col width="26" customWidth="1" style="40" min="4" max="4"/>
-    <col width="30" customWidth="1" style="40" min="5" max="5"/>
-    <col width="26" customWidth="1" style="40" min="6" max="6"/>
+    <col width="30" customWidth="1" style="40" min="1" max="1"/>
+    <col width="44" customWidth="1" style="40" min="2" max="2"/>
+    <col width="16" customWidth="1" style="40" min="3" max="3"/>
+    <col width="44" customWidth="1" style="40" min="4" max="4"/>
+    <col width="48" customWidth="1" style="40" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="41" t="inlineStr">
         <is>
-          <t>MOD_NEUTRALIZARE — Reguli (tabele fixe)</t>
+          <t>MOD_TAXARE_INVERSA — Reguli (tabele fixe)</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="44" t="inlineStr">
         <is>
-          <t>Principiul comun F-311 / F-312 / F-209: cost → cls.6 → stoc intermediar = venit neutralizare → stoc final / livrare. 711/712/722 nu se stinge greșit în stocul final fără pasul de obținere.</t>
+          <t>Regula e dată, nu formulă. Mecanismul contabil e identic în ambele cazuri; diferă partenerul și declarația.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="42" t="inlineStr">
         <is>
-          <t>Tabel A — Lanț pe tip</t>
+          <t>Tabel A — Cele două cazuri</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="65" t="inlineStr">
         <is>
-          <t>Tip</t>
+          <t>Caz</t>
         </is>
       </c>
       <c r="B5" s="65" t="inlineStr">
         <is>
-          <t>Cost →</t>
+          <t>Partener</t>
         </is>
       </c>
       <c r="C5" s="65" t="inlineStr">
         <is>
-          <t>Stoc intermediar</t>
+          <t>Cont furnizor</t>
         </is>
       </c>
       <c r="D5" s="65" t="inlineStr">
         <is>
-          <t>Venit neut.</t>
+          <t>Ce declară</t>
         </is>
       </c>
       <c r="E5" s="65" t="inlineStr">
         <is>
-          <t>Stoc final / livrare</t>
-        </is>
-      </c>
-      <c r="F5" s="65" t="inlineStr">
-        <is>
-          <t>Descărcare la vânzare</t>
+          <t>Condiție</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="43" t="inlineStr">
         <is>
-          <t>BUNURI</t>
+          <t>Achiziție intracomunitară</t>
         </is>
       </c>
       <c r="B6" s="43" t="inlineStr">
         <is>
-          <t>601=301</t>
+          <t>Persoană impozabilă din alt stat membru</t>
         </is>
       </c>
       <c r="C6" s="43" t="inlineStr">
         <is>
-          <t>331=711</t>
+          <t>401.UE</t>
         </is>
       </c>
       <c r="D6" s="43" t="inlineStr">
         <is>
-          <t>711=331 apoi 345=711</t>
+          <t>D300 (casete taxare inversă) + D390 + D394</t>
         </is>
       </c>
       <c r="E6" s="43" t="inlineStr">
         <is>
-          <t>345</t>
-        </is>
-      </c>
-      <c r="F6" s="43" t="inlineStr">
-        <is>
-          <t>711=345 (NU 607)</t>
+          <t>Cod de TVA valid în VIES la data operațiunii</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="43" t="inlineStr">
         <is>
-          <t>SERVICII</t>
+          <t>Taxare inversă internă</t>
         </is>
       </c>
       <c r="B7" s="43" t="inlineStr">
         <is>
-          <t>641/601=…</t>
+          <t>Plătitor de TVA din România</t>
         </is>
       </c>
       <c r="C7" s="43" t="inlineStr">
         <is>
-          <t>332=712</t>
+          <t>401.RO</t>
         </is>
       </c>
       <c r="D7" s="43" t="inlineStr">
         <is>
-          <t>712=332</t>
+          <t>D300 (casete taxare inversă) + D394, FĂRĂ D390</t>
         </is>
       </c>
       <c r="E7" s="43" t="inlineStr">
         <is>
-          <t>(nu e stoc final)</t>
-        </is>
-      </c>
-      <c r="F7" s="43" t="inlineStr">
-        <is>
-          <t>712 stins la livrare</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="43" t="inlineStr">
-        <is>
-          <t>MF</t>
-        </is>
-      </c>
-      <c r="B8" s="43" t="inlineStr">
-        <is>
-          <t>601=301, 641=421</t>
-        </is>
-      </c>
-      <c r="C8" s="43" t="inlineStr">
-        <is>
-          <t>231=722</t>
-        </is>
-      </c>
-      <c r="D8" s="43" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E8" s="43" t="inlineStr">
-        <is>
-          <t>213=231</t>
-        </is>
-      </c>
-      <c r="F8" s="43" t="inlineStr">
-        <is>
-          <t>(nu e vânzare — e activ)</t>
+          <t>Bunul sau serviciul e pe lista art. 331 CF</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="42" t="inlineStr">
+        <is>
+          <t>Tabel B — Operațiuni cu taxare inversă internă (art. 331 CF)</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="42" t="inlineStr">
-        <is>
-          <t>Tabel B — Porți de calitate</t>
+      <c r="A10" s="65" t="inlineStr">
+        <is>
+          <t>Operațiune</t>
+        </is>
+      </c>
+      <c r="B10" s="65" t="inlineStr">
+        <is>
+          <t>Prag</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="44" t="inlineStr">
-        <is>
-          <t>• ΣD=ΣC pe fiecare bloc</t>
+      <c r="A11" s="43" t="inlineStr">
+        <is>
+          <t>Cereale și plante tehnice</t>
+        </is>
+      </c>
+      <c r="B11" s="43" t="inlineStr">
+        <is>
+          <t>fără prag valoric</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="44" t="inlineStr">
-        <is>
-          <t>• Cont venit neutralizare: rulaj D = rulaj C la final (sold 0)</t>
+      <c r="A12" s="43" t="inlineStr">
+        <is>
+          <t>Certificate de emisii de gaze cu efect de seră</t>
+        </is>
+      </c>
+      <c r="B12" s="43" t="inlineStr">
+        <is>
+          <t>fără prag valoric</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="44" t="inlineStr">
-        <is>
-          <t>• Stoc intermediar sold 0 după finalizare</t>
+      <c r="A13" s="43" t="inlineStr">
+        <is>
+          <t>Energie electrică și gaze naturale către comercianți persoane impozabile</t>
+        </is>
+      </c>
+      <c r="B13" s="43" t="inlineStr">
+        <is>
+          <t>fără prag valoric</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="44" t="inlineStr">
-        <is>
-          <t>• Pentru BUNURI: 345 un singur D și un singur C; descărcare prin 711, nu 607</t>
+      <c r="A14" s="43" t="inlineStr">
+        <is>
+          <t>Certificate verzi</t>
+        </is>
+      </c>
+      <c r="B14" s="43" t="inlineStr">
+        <is>
+          <t>fără prag valoric</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="44" t="inlineStr">
-        <is>
-          <t>• Pentru MF: impact net pe 121 din capitalizare = 0 (cheltuieli = 722)</t>
+      <c r="A15" s="43" t="inlineStr">
+        <is>
+          <t>Telefoane mobile</t>
+        </is>
+      </c>
+      <c r="B15" s="43" t="inlineStr">
+        <is>
+          <t>doar dacă valoarea fără TVA de pe factură ≥ 22.500 lei</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="43" t="inlineStr">
+        <is>
+          <t>Dispozitive cu circuite integrate</t>
+        </is>
+      </c>
+      <c r="B16" s="43" t="inlineStr">
+        <is>
+          <t>doar dacă valoarea fără TVA de pe factură ≥ 22.500 lei</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="42" t="inlineStr">
-        <is>
-          <t>Tabel C — Ce NU se face</t>
+      <c r="A17" s="43" t="inlineStr">
+        <is>
+          <t>Console de jocuri</t>
+        </is>
+      </c>
+      <c r="B17" s="43" t="inlineStr">
+        <is>
+          <t>doar dacă valoarea fără TVA de pe factură ≥ 22.500 lei</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="44" t="inlineStr">
-        <is>
-          <t>• 345 creditat de două ori fără un debit de obținere (eroarea F-311 veche)</t>
+      <c r="A18" s="43" t="inlineStr">
+        <is>
+          <t>Tablete și laptopuri</t>
+        </is>
+      </c>
+      <c r="B18" s="43" t="inlineStr">
+        <is>
+          <t>doar dacă valoarea fără TVA de pe factură ≥ 22.500 lei</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="44" t="inlineStr">
         <is>
-          <t>• 722 = 231 (ar stinge activul — eroare F-209 veche); corect e 231 = 722</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="44" t="inlineStr">
-        <is>
-          <t>• 607 la descărcarea produselor finite (607 e doar mărfuri)</t>
+          <t>Derogarea Consiliului UE pe baza căreia se aplică art. 331 expiră la 31.12.2026. Verificat la 21.08.2026: nicio prelungire publicată. Nu se presupune prelungirea automată.</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="44" t="inlineStr">
-        <is>
-          <t>• „711 sau 712” la servicii — pentru servicii e strict 712</t>
+      <c r="A21" s="42" t="inlineStr">
+        <is>
+          <t>Tabel C — Porți de calitate</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="44" t="inlineStr">
+        <is>
+          <t>• 4426 și 4427 primesc EXACT aceeași sumă — netul pe operațiune e zero</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="44" t="inlineStr">
+        <is>
+          <t>• D390 doar la intracomunitar; un partener intern trecut acolo se vede la ANAF prin necorelare cu VIES</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="44" t="inlineStr">
+        <is>
+          <t>• Codul VIES se verifică la DATA operațiunii, nu la data când te uiți</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="44" t="inlineStr">
+        <is>
+          <t>• Fără TVA plătită efectiv: autolichidarea nu produce flux de trezorerie</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="44" t="inlineStr">
+        <is>
+          <t>• La închiderea lunară, sumele astea intră în 4426/4427 ca oricare altele și se anulează reciproc — vezi MOD_INCHIDERE_TVA</t>
         </is>
       </c>
     </row>
@@ -29085,36 +29251,36 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G35"/>
+  <dimension ref="A1:G22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="14" customWidth="1" style="40" min="1" max="1"/>
-    <col width="20" customWidth="1" style="40" min="2" max="2"/>
+    <col width="30" customWidth="1" style="40" min="1" max="1"/>
+    <col width="16" customWidth="1" style="40" min="2" max="2"/>
     <col width="14" customWidth="1" style="40" min="3" max="3"/>
-    <col width="52" customWidth="1" style="40" min="4" max="4"/>
-    <col width="20" customWidth="1" style="40" min="5" max="5"/>
+    <col width="50" customWidth="1" style="40" min="4" max="4"/>
+    <col width="16" customWidth="1" style="40" min="5" max="5"/>
     <col width="14" customWidth="1" style="40" min="6" max="6"/>
-    <col width="52" customWidth="1" style="40" min="7" max="7"/>
+    <col width="50" customWidth="1" style="40" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="41" t="inlineStr">
         <is>
-          <t>MOD_NEUTRALIZARE — Jurnale (generate automat)</t>
+          <t>MOD_TAXARE_INVERSA — Jurnale (generate automat)</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="44" t="inlineStr">
         <is>
-          <t>Lanțul se adaptează după Tip. Pentru MF, blocul de vânzare rămâne 0. Pentru SERVICII, stocul final e gol.</t>
+          <t>Fiecare caz iese cu zero dacă nu e activat. Pasul de autolichidare are aceeași sumă pe ambele părți — asta e chiar mecanismul, nu o coincidență.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="42" t="inlineStr">
         <is>
-          <t>Bloc 1 — Costuri pe cls.6</t>
+          <t>Bloc A — Achiziție intracomunitară</t>
         </is>
       </c>
     </row>
@@ -29125,8 +29291,8 @@
         </is>
       </c>
       <c r="B5" s="43" t="str">
-        <f>Declarații_NEUTRALIZARE!B8</f>
-        <v>2026-07-05</v>
+        <f>Declarații_TAXARE_INVERSA!B8</f>
+        <v>2026-07-31</v>
       </c>
     </row>
     <row r="6">
@@ -29170,94 +29336,95 @@
       <c r="A7" s="43" t="n">
         <v>1</v>
       </c>
-      <c r="B7" s="43" t="inlineStr">
-        <is>
-          <t>601</t>
-        </is>
+      <c r="B7" s="43" t="str">
+        <f>IF(Declarații_TAXARE_INVERSA!B20="DA",Declarații_TAXARE_INVERSA!B32,Declarații_TAXARE_INVERSA!B31)</f>
+        <v>371</v>
       </c>
       <c r="C7" s="43">
-        <f>Declarații_NEUTRALIZARE!B20</f>
-        <v>4500</v>
+        <f>IF(Declarații_TAXARE_INVERSA!B12="DA",Declarații_TAXARE_INVERSA!B17,0)</f>
+        <v>74550</v>
       </c>
       <c r="D7" s="43" t="str">
-        <f>"Consum materiale " &amp; Declarații_NEUTRALIZARE!B37</f>
-        <v>Consum materiale — 2026-07 — BUNURI — 711</v>
+        <f>"Achiziție intracomunitară " &amp; Declarații_TAXARE_INVERSA!B13 &amp; " " &amp; Declarații_TAXARE_INVERSA!B39</f>
+        <v>Achiziție intracomunitară Furnizor UE DEMO — taxare inversă 2026-07</v>
       </c>
       <c r="E7" s="43" t="str">
-        <f>Declarații_NEUTRALIZARE!B32</f>
-        <v>301</v>
+        <f>Declarații_TAXARE_INVERSA!B33</f>
+        <v>401.UE</v>
       </c>
       <c r="F7" s="43">
-        <f>Declarații_NEUTRALIZARE!B20</f>
-        <v>4500</v>
+        <f>IF(Declarații_TAXARE_INVERSA!B12="DA",Declarații_TAXARE_INVERSA!B17,0)</f>
+        <v>74550</v>
       </c>
       <c r="G7" s="43" t="str">
-        <f>"Stingere stoc materii " &amp; Declarații_NEUTRALIZARE!B37</f>
-        <v>Stingere stoc materii — 2026-07 — BUNURI — 711</v>
+        <f>"Datorie furnizor UE " &amp; Declarații_TAXARE_INVERSA!B39</f>
+        <v>Datorie furnizor UE — taxare inversă 2026-07</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="43" t="n">
+      <c r="A8" s="43" t="inlineStr">
+        <is>
+          <t>Check A1 (factura)</t>
+        </is>
+      </c>
+      <c r="B8" s="43">
+        <f>C7-F7</f>
+        <v>0</v>
+      </c>
+      <c r="C8" s="43" t="str">
+        <f>IF(ABS(B8)&lt;0.01,"OK","EROARE")</f>
+        <v>OK</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="43" t="n">
         <v>2</v>
       </c>
-      <c r="B8" s="43" t="inlineStr">
-        <is>
-          <t>641</t>
-        </is>
-      </c>
-      <c r="C8" s="43">
-        <f>Declarații_NEUTRALIZARE!B21</f>
+      <c r="B9" s="43" t="str">
+        <f>Declarații_TAXARE_INVERSA!B35</f>
+        <v>4426</v>
+      </c>
+      <c r="C9" s="43">
+        <f>IF(Declarații_TAXARE_INVERSA!B12="DA",Declarații_TAXARE_INVERSA!B18,0)</f>
+        <v>15655.5</v>
+      </c>
+      <c r="D9" s="43" t="str">
+        <f>"TVA deductibilă prin autolichidare " &amp; Declarații_TAXARE_INVERSA!B39</f>
+        <v>TVA deductibilă prin autolichidare — taxare inversă 2026-07</v>
+      </c>
+      <c r="E9" s="43" t="str">
+        <f>Declarații_TAXARE_INVERSA!B36</f>
+        <v>4427</v>
+      </c>
+      <c r="F9" s="43">
+        <f>IF(Declarații_TAXARE_INVERSA!B12="DA",Declarații_TAXARE_INVERSA!B18,0)</f>
+        <v>15655.5</v>
+      </c>
+      <c r="G9" s="43" t="str">
+        <f>"TVA colectată prin autolichidare " &amp; Declarații_TAXARE_INVERSA!B39</f>
+        <v>TVA colectată prin autolichidare — taxare inversă 2026-07</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="43" t="inlineStr">
+        <is>
+          <t>Check A2 (autolichidare = cotă × bază)</t>
+        </is>
+      </c>
+      <c r="B10" s="43">
+        <f>C9-IF(Declarații_TAXARE_INVERSA!B12="DA",Declarații_TAXARE_INVERSA!B19,0)</f>
         <v>0</v>
       </c>
-      <c r="D8" s="43" t="str">
-        <f>"Manoperă pe proiect " &amp; Declarații_NEUTRALIZARE!B37</f>
-        <v>Manoperă pe proiect — 2026-07 — BUNURI — 711</v>
-      </c>
-      <c r="E8" s="43" t="inlineStr">
-        <is>
-          <t>421</t>
-        </is>
-      </c>
-      <c r="F8" s="43">
-        <f>Declarații_NEUTRALIZARE!B21</f>
-        <v>0</v>
-      </c>
-      <c r="G8" s="43" t="str">
-        <f>"Datorie salarii " &amp; Declarații_NEUTRALIZARE!B37</f>
-        <v>Datorie salarii — 2026-07 — BUNURI — 711</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="43" t="inlineStr">
-        <is>
-          <t>Check B1</t>
-        </is>
-      </c>
-      <c r="B9" s="43">
-        <f>(C7+C8)-(F7+F8)</f>
-        <v>0</v>
-      </c>
-      <c r="C9" s="43" t="str">
-        <f>IF(ABS(B9)&lt;0.01,"OK","EROARE")</f>
-        <v>OK</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="42" t="inlineStr">
-        <is>
-          <t>Bloc 2 — Stoc intermediar = venit neutralizare (pas revelator)</t>
-        </is>
+      <c r="C10" s="43" t="str">
+        <f>IF(ABS(B10)&lt;0.01,"OK — 4426 = 4427 = cotă × bază","EROARE — suma din notă nu e cotă × bază")</f>
+        <v>OK — 4426 = 4427 = cotă × bază</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="43" t="inlineStr">
-        <is>
-          <t>Data:</t>
-        </is>
-      </c>
-      <c r="B12" s="43" t="str">
-        <f>Declarații_NEUTRALIZARE!B9</f>
-        <v>2026-07-20</v>
+      <c r="A12" s="42" t="inlineStr">
+        <is>
+          <t>Bloc B — Taxare inversă internă</t>
+        </is>
       </c>
     </row>
     <row r="13">
@@ -29301,35 +29468,35 @@
       <c r="A14" s="43" t="n">
         <v>1</v>
       </c>
-      <c r="B14" s="43">
-        <f>Declarații_NEUTRALIZARE!B15</f>
-        <v>331</v>
+      <c r="B14" s="43" t="str">
+        <f>Declarații_TAXARE_INVERSA!B31</f>
+        <v>371</v>
       </c>
       <c r="C14" s="43">
-        <f>Declarații_NEUTRALIZARE!B23</f>
-        <v>4500</v>
+        <f>IF(Declarații_TAXARE_INVERSA!B23="DA",Declarații_TAXARE_INVERSA!B26,0)</f>
+        <v>10000</v>
       </c>
       <c r="D14" s="43" t="str">
-        <f>"Stoc intermediar (PN/servicii/MF în curs) " &amp; Declarații_NEUTRALIZARE!B37</f>
-        <v>Stoc intermediar (PN/servicii/MF în curs) — 2026-07 — BUNURI — 711</v>
-      </c>
-      <c r="E14" s="43">
-        <f>Declarații_NEUTRALIZARE!B14</f>
-        <v>711</v>
+        <f>"Achiziție cu taxare inversă (" &amp; Declarații_TAXARE_INVERSA!B25 &amp; ") " &amp; Declarații_TAXARE_INVERSA!B39</f>
+        <v>Achiziție cu taxare inversă (Cereale) — taxare inversă 2026-07</v>
+      </c>
+      <c r="E14" s="43" t="str">
+        <f>Declarații_TAXARE_INVERSA!B34</f>
+        <v>401.RO</v>
       </c>
       <c r="F14" s="43">
-        <f>Declarații_NEUTRALIZARE!B23</f>
-        <v>4500</v>
+        <f>IF(Declarații_TAXARE_INVERSA!B23="DA",Declarații_TAXARE_INVERSA!B26,0)</f>
+        <v>10000</v>
       </c>
       <c r="G14" s="43" t="str">
-        <f>"Venit producție / neutralizare " &amp; Declarații_NEUTRALIZARE!B37</f>
-        <v>Venit producție / neutralizare — 2026-07 — BUNURI — 711</v>
+        <f>"Datorie furnizor RO " &amp; Declarații_TAXARE_INVERSA!B39</f>
+        <v>Datorie furnizor RO — taxare inversă 2026-07</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="43" t="inlineStr">
         <is>
-          <t>Check B2</t>
+          <t>Check B1 (factura)</t>
         </is>
       </c>
       <c r="B15" s="43">
@@ -29341,311 +29508,76 @@
         <v>OK</v>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" s="43" t="n">
+        <v>2</v>
+      </c>
+      <c r="B16" s="43" t="str">
+        <f>Declarații_TAXARE_INVERSA!B35</f>
+        <v>4426</v>
+      </c>
+      <c r="C16" s="43">
+        <f>IF(Declarații_TAXARE_INVERSA!B23="DA",Declarații_TAXARE_INVERSA!B27,0)</f>
+        <v>2100</v>
+      </c>
+      <c r="D16" s="43" t="str">
+        <f>"TVA deductibilă prin autolichidare " &amp; Declarații_TAXARE_INVERSA!B39</f>
+        <v>TVA deductibilă prin autolichidare — taxare inversă 2026-07</v>
+      </c>
+      <c r="E16" s="43" t="str">
+        <f>Declarații_TAXARE_INVERSA!B36</f>
+        <v>4427</v>
+      </c>
+      <c r="F16" s="43">
+        <f>IF(Declarații_TAXARE_INVERSA!B23="DA",Declarații_TAXARE_INVERSA!B27,0)</f>
+        <v>2100</v>
+      </c>
+      <c r="G16" s="43" t="str">
+        <f>"TVA colectată prin autolichidare " &amp; Declarații_TAXARE_INVERSA!B39</f>
+        <v>TVA colectată prin autolichidare — taxare inversă 2026-07</v>
+      </c>
+    </row>
     <row r="17">
-      <c r="A17" s="42" t="inlineStr">
-        <is>
-          <t>Bloc 3 — Finalizare (obținere stoc final / stingere intermediar)</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="43" t="inlineStr">
-        <is>
-          <t>Data:</t>
-        </is>
-      </c>
-      <c r="B18" s="43" t="str">
-        <f>Declarații_NEUTRALIZARE!B9</f>
-        <v>2026-07-20</v>
+      <c r="A17" s="43" t="inlineStr">
+        <is>
+          <t>Check B2 (autolichidare = cotă × bază)</t>
+        </is>
+      </c>
+      <c r="B17" s="43">
+        <f>C16-IF(Declarații_TAXARE_INVERSA!B23="DA",Declarații_TAXARE_INVERSA!B28,0)</f>
+        <v>0</v>
+      </c>
+      <c r="C17" s="43" t="str">
+        <f>IF(ABS(B17)&lt;0.01,"OK — 4426 = 4427 = cotă × bază","EROARE — suma din notă nu e cotă × bază")</f>
+        <v>OK — 4426 = 4427 = cotă × bază</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="65" t="inlineStr">
-        <is>
-          <t>Nr</t>
-        </is>
-      </c>
-      <c r="B19" s="65" t="inlineStr">
-        <is>
-          <t>Cont Dr</t>
-        </is>
-      </c>
-      <c r="C19" s="65" t="inlineStr">
-        <is>
-          <t>Sumă Dr</t>
-        </is>
-      </c>
-      <c r="D19" s="65" t="inlineStr">
-        <is>
-          <t>Descriere Dr</t>
-        </is>
-      </c>
-      <c r="E19" s="65" t="inlineStr">
-        <is>
-          <t>Cont Cr</t>
-        </is>
-      </c>
-      <c r="F19" s="65" t="inlineStr">
-        <is>
-          <t>Sumă Cr</t>
-        </is>
-      </c>
-      <c r="G19" s="65" t="inlineStr">
-        <is>
-          <t>Descriere Cr</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="43" t="n">
-        <v>1</v>
-      </c>
-      <c r="B20" s="43">
-        <f>IF(Declarații_NEUTRALIZARE!B13="BUNURI",Declarații_NEUTRALIZARE!B14,IF(Declarații_NEUTRALIZARE!B13="SERVICII",Declarații_NEUTRALIZARE!B14,Declarații_NEUTRALIZARE!B16))</f>
-        <v>711</v>
-      </c>
-      <c r="C20" s="43">
-        <f>Declarații_NEUTRALIZARE!B23</f>
-        <v>4500</v>
-      </c>
-      <c r="D20" s="43" t="str">
-        <f>IF(Declarații_NEUTRALIZARE!B13="BUNURI","Reluare PN (711 debitat #1) ",IF(Declarații_NEUTRALIZARE!B13="SERVICII","Stingere servicii în curs ","Transfer MF final ")) &amp; Declarații_NEUTRALIZARE!B37</f>
-        <v>Reluare PN (711 debitat #1) — 2026-07 — BUNURI — 711</v>
-      </c>
-      <c r="E20" s="43">
-        <f>IF(Declarații_NEUTRALIZARE!B13="MF",Declarații_NEUTRALIZARE!B15,Declarații_NEUTRALIZARE!B15)</f>
-        <v>331</v>
-      </c>
-      <c r="F20" s="43">
-        <f>Declarații_NEUTRALIZARE!B23</f>
-        <v>4500</v>
-      </c>
-      <c r="G20" s="43" t="str">
-        <f>"Stingere stoc intermediar " &amp; Declarații_NEUTRALIZARE!B37</f>
-        <v>Stingere stoc intermediar — 2026-07 — BUNURI — 711</v>
+      <c r="A19" s="43" t="inlineStr">
+        <is>
+          <t>Check global</t>
+        </is>
+      </c>
+      <c r="B19" s="43">
+        <f>ABS(B8)+ABS(B10)+ABS(B15)+ABS(B17)</f>
+        <v>0</v>
+      </c>
+      <c r="C19" s="43" t="str">
+        <f>IF(B19&lt;0.01,"OK — toate blocurile se închid","EROARE — cel puțin un bloc dezechilibrat")</f>
+        <v>OK — toate blocurile se închid</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="43" t="n">
-        <v>2</v>
-      </c>
-      <c r="B21" s="43">
-        <f>IF(Declarații_NEUTRALIZARE!B13="BUNURI",Declarații_NEUTRALIZARE!B16,0)</f>
-        <v>345</v>
-      </c>
-      <c r="C21" s="43">
-        <f>IF(Declarații_NEUTRALIZARE!B13="BUNURI",Declarații_NEUTRALIZARE!B23,0)</f>
-        <v>4500</v>
-      </c>
-      <c r="D21" s="43" t="str">
-        <f>IF(Declarații_NEUTRALIZARE!B13="BUNURI","Obținere produs finit (345=711) " &amp; Declarații_NEUTRALIZARE!B37,"")</f>
-        <v>Obținere produs finit (345=711) — 2026-07 — BUNURI — 711</v>
-      </c>
-      <c r="E21" s="43">
-        <f>IF(Declarații_NEUTRALIZARE!B13="BUNURI",Declarații_NEUTRALIZARE!B14,0)</f>
-        <v>711</v>
-      </c>
-      <c r="F21" s="43">
-        <f>IF(Declarații_NEUTRALIZARE!B13="BUNURI",Declarații_NEUTRALIZARE!B23,0)</f>
-        <v>4500</v>
-      </c>
-      <c r="G21" s="43" t="str">
-        <f>IF(Declarații_NEUTRALIZARE!B13="BUNURI","Neutralizare (711 creditat #2) " &amp; Declarații_NEUTRALIZARE!B37,"")</f>
-        <v>Neutralizare (711 creditat #2) — 2026-07 — BUNURI — 711</v>
+      <c r="A21" s="42" t="inlineStr">
+        <is>
+          <t>Stare terminală</t>
+        </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="43" t="inlineStr">
-        <is>
-          <t>Check B3</t>
-        </is>
-      </c>
-      <c r="B22" s="43">
-        <f>(C20+C21)-(F20+F21)</f>
-        <v>0</v>
-      </c>
-      <c r="C22" s="43" t="str">
-        <f>IF(ABS(B22)&lt;0.01,"OK","EROARE")</f>
-        <v>OK</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="42" t="inlineStr">
-        <is>
-          <t>Bloc 4 — Vânzare + descărcare (BUNURI/SERVICII; 0 pentru MF)</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="43" t="inlineStr">
-        <is>
-          <t>Data:</t>
-        </is>
-      </c>
-      <c r="B25" s="43" t="str">
-        <f>Declarații_NEUTRALIZARE!B10</f>
-        <v>2026-07-25</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="65" t="inlineStr">
-        <is>
-          <t>Nr</t>
-        </is>
-      </c>
-      <c r="B26" s="65" t="inlineStr">
-        <is>
-          <t>Cont Dr</t>
-        </is>
-      </c>
-      <c r="C26" s="65" t="inlineStr">
-        <is>
-          <t>Sumă Dr</t>
-        </is>
-      </c>
-      <c r="D26" s="65" t="inlineStr">
-        <is>
-          <t>Descriere Dr</t>
-        </is>
-      </c>
-      <c r="E26" s="65" t="inlineStr">
-        <is>
-          <t>Cont Cr</t>
-        </is>
-      </c>
-      <c r="F26" s="65" t="inlineStr">
-        <is>
-          <t>Sumă Cr</t>
-        </is>
-      </c>
-      <c r="G26" s="65" t="inlineStr">
-        <is>
-          <t>Descriere Cr</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="43" t="n">
-        <v>1</v>
-      </c>
-      <c r="B27" s="43" t="str">
-        <f>IF(OR(Declarații_NEUTRALIZARE!B13="BUNURI",Declarații_NEUTRALIZARE!B13="SERVICII"),Declarații_NEUTRALIZARE!B33,0)</f>
-        <v>411.RO</v>
-      </c>
-      <c r="C27" s="43">
-        <f>IF(OR(Declarații_NEUTRALIZARE!B13="BUNURI",Declarații_NEUTRALIZARE!B13="SERVICII"),Declarații_NEUTRALIZARE!B29,0)</f>
-        <v>8470</v>
-      </c>
-      <c r="D27" s="43" t="str">
-        <f>"Creanță client " &amp; Declarații_NEUTRALIZARE!B37</f>
-        <v>Creanță client — 2026-07 — BUNURI — 711</v>
-      </c>
-      <c r="E27" s="43">
-        <f>IF(OR(Declarații_NEUTRALIZARE!B13="BUNURI",Declarații_NEUTRALIZARE!B13="SERVICII"),Declarații_NEUTRALIZARE!B17,0)</f>
-        <v>701</v>
-      </c>
-      <c r="F27" s="43">
-        <f>IF(OR(Declarații_NEUTRALIZARE!B13="BUNURI",Declarații_NEUTRALIZARE!B13="SERVICII"),Declarații_NEUTRALIZARE!B26,0)</f>
-        <v>7000</v>
-      </c>
-      <c r="G27" s="43" t="str">
-        <f>"Venit din vânzare " &amp; Declarații_NEUTRALIZARE!B37</f>
-        <v>Venit din vânzare — 2026-07 — BUNURI — 711</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="43" t="n">
-        <v>2</v>
-      </c>
-      <c r="B28" s="43" t="n">
-        <v>0</v>
-      </c>
-      <c r="C28" s="43" t="n">
-        <v>0</v>
-      </c>
-      <c r="E28" s="43" t="str">
-        <f>IF(OR(Declarații_NEUTRALIZARE!B13="BUNURI",Declarații_NEUTRALIZARE!B13="SERVICII"),Declarații_NEUTRALIZARE!B34,0)</f>
-        <v>4427</v>
-      </c>
-      <c r="F28" s="43">
-        <f>IF(OR(Declarații_NEUTRALIZARE!B13="BUNURI",Declarații_NEUTRALIZARE!B13="SERVICII"),Declarații_NEUTRALIZARE!B28,0)</f>
-        <v>1470</v>
-      </c>
-      <c r="G28" s="43" t="str">
-        <f>"TVA colectată " &amp; Declarații_NEUTRALIZARE!B37</f>
-        <v>TVA colectată — 2026-07 — BUNURI — 711</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="43" t="n">
-        <v>3</v>
-      </c>
-      <c r="B29" s="43">
-        <f>IF(Declarații_NEUTRALIZARE!B13="BUNURI",Declarații_NEUTRALIZARE!B14,IF(Declarații_NEUTRALIZARE!B13="SERVICII",Declarații_NEUTRALIZARE!B14,0))</f>
-        <v>711</v>
-      </c>
-      <c r="C29" s="43">
-        <f>IF(OR(Declarații_NEUTRALIZARE!B13="BUNURI",Declarații_NEUTRALIZARE!B13="SERVICII"),Declarații_NEUTRALIZARE!B23,0)</f>
-        <v>4500</v>
-      </c>
-      <c r="D29" s="43" t="str">
-        <f>IF(Declarații_NEUTRALIZARE!B13="BUNURI","Descărcare PF prin 711 (NU 607) ",IF(Declarații_NEUTRALIZARE!B13="SERVICII","Stingere 712 la livrare ","")) &amp; Declarații_NEUTRALIZARE!B37</f>
-        <v>Descărcare PF prin 711 (NU 607) — 2026-07 — BUNURI — 711</v>
-      </c>
-      <c r="E29" s="43">
-        <f>IF(Declarații_NEUTRALIZARE!B13="BUNURI",Declarații_NEUTRALIZARE!B16,0)</f>
-        <v>345</v>
-      </c>
-      <c r="F29" s="43">
-        <f>IF(Declarații_NEUTRALIZARE!B13="BUNURI",Declarații_NEUTRALIZARE!B23,0)</f>
-        <v>4500</v>
-      </c>
-      <c r="G29" s="43" t="str">
-        <f>IF(Declarații_NEUTRALIZARE!B13="BUNURI","Stingere stoc PF " &amp; Declarații_NEUTRALIZARE!B37,"")</f>
-        <v>Stingere stoc PF — 2026-07 — BUNURI — 711</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="43" t="inlineStr">
-        <is>
-          <t>Check B4</t>
-        </is>
-      </c>
-      <c r="B30" s="43">
-        <f>(C27+C28+C29)-(F27+F28+F29)</f>
-        <v>0</v>
-      </c>
-      <c r="C30" s="43" t="str">
-        <f>IF(ABS(B30)&lt;0.01,"OK","EROARE")</f>
-        <v>OK</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="43" t="inlineStr">
-        <is>
-          <t>Check global</t>
-        </is>
-      </c>
-      <c r="B32" s="43">
-        <f>ABS(B9)+ABS(B15)+ABS(B22)+ABS(B30)</f>
-        <v>0</v>
-      </c>
-      <c r="C32" s="43" t="str">
-        <f>IF(B32&lt;0.01,"OK — toate blocurile se închid","EROARE — cel puțin un bloc dezechilibrat")</f>
-        <v>OK — toate blocurile se închid</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="42" t="inlineStr">
-        <is>
-          <t>Stare terminală</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="44" t="inlineStr">
-        <is>
-          <t>Cont venit neut. sold 0 | Stoc intermediar 0 | Pentru BUNURI: 345 sold 0, descărcare prin 711 | Pentru MF: 213=cost, impact 121 din capitalizare = 0</t>
+      <c r="A22" s="44" t="inlineStr">
+        <is>
+          <t>Nicio TVA de plată suplimentară din operațiunile astea: 4426 și 4427 s-au mișcat cu aceeași sumă și se anulează la închiderea lunară. Ce rămâne e raportarea: D300 la ambele, D390 doar la intracomunitar.</t>
         </is>
       </c>
     </row>
@@ -29660,16 +29592,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I15"/>
+  <dimension ref="A1:I11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" style="40" min="1" max="1"/>
-    <col width="18" customWidth="1" style="40" min="2" max="2"/>
+    <col width="26" customWidth="1" style="40" min="2" max="2"/>
     <col width="14" customWidth="1" style="40" min="3" max="3"/>
-    <col width="16" customWidth="1" style="40" min="4" max="4"/>
-    <col width="16" customWidth="1" style="40" min="5" max="5"/>
+    <col width="12" customWidth="1" style="40" min="4" max="4"/>
+    <col width="12" customWidth="1" style="40" min="5" max="5"/>
     <col width="14" customWidth="1" style="40" min="6" max="6"/>
-    <col width="52" customWidth="1" style="40" min="7" max="7"/>
+    <col width="50" customWidth="1" style="40" min="7" max="7"/>
     <col width="24" customWidth="1" style="40" min="8" max="8"/>
     <col width="10" customWidth="1" style="40" min="9" max="9"/>
   </cols>
@@ -29677,14 +29609,14 @@
     <row r="1">
       <c r="A1" s="41" t="inlineStr">
         <is>
-          <t>MOD_NEUTRALIZARE — Notă pentru import</t>
+          <t>MOD_TAXARE_INVERSA — Notă pentru import</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="44" t="inlineStr">
         <is>
-          <t>Filtrează Include=DA. Rândurile cu sumă 0 (ex. manoperă 0, sau blocuri MF fără vânzare) apar ca NU.</t>
+          <t>Filtrează Include=DA. Cazurile neactivate ies cu sumă 0 și apar ca NU.</t>
         </is>
       </c>
     </row>
@@ -29741,32 +29673,32 @@
       </c>
       <c r="B5" s="43" t="inlineStr">
         <is>
-          <t>B1 Costuri</t>
+          <t>A Intracomunitar — factura</t>
         </is>
       </c>
       <c r="C5" s="43" t="str">
-        <f>Declarații_NEUTRALIZARE!B8</f>
-        <v>2026-07-05</v>
+        <f>Declarații_TAXARE_INVERSA!B8</f>
+        <v>2026-07-31</v>
       </c>
       <c r="D5" s="43" t="str">
-        <f>Jurnale_NEUTRALIZARE!B7</f>
-        <v>601</v>
+        <f>Jurnale_TAXARE_INVERSA!B7</f>
+        <v>371</v>
       </c>
       <c r="E5" s="43" t="str">
-        <f>Jurnale_NEUTRALIZARE!E7</f>
-        <v>301</v>
+        <f>Jurnale_TAXARE_INVERSA!E7</f>
+        <v>401.UE</v>
       </c>
       <c r="F5" s="43">
-        <f>Jurnale_NEUTRALIZARE!C7</f>
-        <v>4500</v>
+        <f>Jurnale_TAXARE_INVERSA!C7</f>
+        <v>74550</v>
       </c>
       <c r="G5" s="43" t="str">
-        <f>Jurnale_NEUTRALIZARE!D7</f>
-        <v>Consum materiale — 2026-07 — BUNURI — 711</v>
+        <f>Jurnale_TAXARE_INVERSA!D7</f>
+        <v>Achiziție intracomunitară Furnizor UE DEMO — taxare inversă 2026-07</v>
       </c>
       <c r="H5" s="43" t="inlineStr">
         <is>
-          <t>Producție / neutralizare</t>
+          <t>Factură furnizor UE</t>
         </is>
       </c>
       <c r="I5" s="43" t="str">
@@ -29780,37 +29712,37 @@
       </c>
       <c r="B6" s="43" t="inlineStr">
         <is>
-          <t>B1 Costuri</t>
+          <t>A Intracomunitar — autolichidare</t>
         </is>
       </c>
       <c r="C6" s="43" t="str">
-        <f>Declarații_NEUTRALIZARE!B8</f>
-        <v>2026-07-05</v>
+        <f>Declarații_TAXARE_INVERSA!B8</f>
+        <v>2026-07-31</v>
       </c>
       <c r="D6" s="43" t="str">
-        <f>Jurnale_NEUTRALIZARE!B8</f>
-        <v>641</v>
+        <f>Jurnale_TAXARE_INVERSA!B9</f>
+        <v>4426</v>
       </c>
       <c r="E6" s="43" t="str">
-        <f>Jurnale_NEUTRALIZARE!E8</f>
-        <v>421</v>
+        <f>Jurnale_TAXARE_INVERSA!E9</f>
+        <v>4427</v>
       </c>
       <c r="F6" s="43">
-        <f>Jurnale_NEUTRALIZARE!C8</f>
-        <v>0</v>
+        <f>Jurnale_TAXARE_INVERSA!C9</f>
+        <v>15655.5</v>
       </c>
       <c r="G6" s="43" t="str">
-        <f>Jurnale_NEUTRALIZARE!D8</f>
-        <v>Manoperă pe proiect — 2026-07 — BUNURI — 711</v>
+        <f>Jurnale_TAXARE_INVERSA!D9</f>
+        <v>TVA deductibilă prin autolichidare — taxare inversă 2026-07</v>
       </c>
       <c r="H6" s="43" t="inlineStr">
         <is>
-          <t>Producție / neutralizare</t>
+          <t>Autofactură</t>
         </is>
       </c>
       <c r="I6" s="43" t="str">
         <f>IF(AND(ISNUMBER(F6),F6&gt;0),"DA","NU")</f>
-        <v>NU</v>
+        <v>DA</v>
       </c>
     </row>
     <row r="7">
@@ -29819,32 +29751,32 @@
       </c>
       <c r="B7" s="43" t="inlineStr">
         <is>
-          <t>B2 Neutralizare</t>
+          <t>B Intern — factura</t>
         </is>
       </c>
       <c r="C7" s="43" t="str">
-        <f>Declarații_NEUTRALIZARE!B9</f>
-        <v>2026-07-20</v>
-      </c>
-      <c r="D7" s="43">
-        <f>Jurnale_NEUTRALIZARE!B14</f>
-        <v>331</v>
-      </c>
-      <c r="E7" s="43">
-        <f>Jurnale_NEUTRALIZARE!E14</f>
-        <v>711</v>
+        <f>Declarații_TAXARE_INVERSA!B8</f>
+        <v>2026-07-31</v>
+      </c>
+      <c r="D7" s="43" t="str">
+        <f>Jurnale_TAXARE_INVERSA!B14</f>
+        <v>371</v>
+      </c>
+      <c r="E7" s="43" t="str">
+        <f>Jurnale_TAXARE_INVERSA!E14</f>
+        <v>401.RO</v>
       </c>
       <c r="F7" s="43">
-        <f>Jurnale_NEUTRALIZARE!C14</f>
-        <v>4500</v>
+        <f>Jurnale_TAXARE_INVERSA!C14</f>
+        <v>10000</v>
       </c>
       <c r="G7" s="43" t="str">
-        <f>Jurnale_NEUTRALIZARE!D14</f>
-        <v>Stoc intermediar (PN/servicii/MF în curs) — 2026-07 — BUNURI — 711</v>
+        <f>Jurnale_TAXARE_INVERSA!D14</f>
+        <v>Achiziție cu taxare inversă (Cereale) — taxare inversă 2026-07</v>
       </c>
       <c r="H7" s="43" t="inlineStr">
         <is>
-          <t>Producție / neutralizare</t>
+          <t>Factură (mențiune taxare inversă)</t>
         </is>
       </c>
       <c r="I7" s="43" t="str">
@@ -29858,32 +29790,32 @@
       </c>
       <c r="B8" s="43" t="inlineStr">
         <is>
-          <t>B3 Finalizare</t>
+          <t>B Intern — autolichidare</t>
         </is>
       </c>
       <c r="C8" s="43" t="str">
-        <f>Declarații_NEUTRALIZARE!B9</f>
-        <v>2026-07-20</v>
-      </c>
-      <c r="D8" s="43">
-        <f>Jurnale_NEUTRALIZARE!B20</f>
-        <v>711</v>
-      </c>
-      <c r="E8" s="43">
-        <f>Jurnale_NEUTRALIZARE!E20</f>
-        <v>331</v>
+        <f>Declarații_TAXARE_INVERSA!B8</f>
+        <v>2026-07-31</v>
+      </c>
+      <c r="D8" s="43" t="str">
+        <f>Jurnale_TAXARE_INVERSA!B16</f>
+        <v>4426</v>
+      </c>
+      <c r="E8" s="43" t="str">
+        <f>Jurnale_TAXARE_INVERSA!E16</f>
+        <v>4427</v>
       </c>
       <c r="F8" s="43">
-        <f>Jurnale_NEUTRALIZARE!C20</f>
-        <v>4500</v>
+        <f>Jurnale_TAXARE_INVERSA!C16</f>
+        <v>2100</v>
       </c>
       <c r="G8" s="43" t="str">
-        <f>Jurnale_NEUTRALIZARE!D20</f>
-        <v>Reluare PN (711 debitat #1) — 2026-07 — BUNURI — 711</v>
+        <f>Jurnale_TAXARE_INVERSA!D16</f>
+        <v>TVA deductibilă prin autolichidare — taxare inversă 2026-07</v>
       </c>
       <c r="H8" s="43" t="inlineStr">
         <is>
-          <t>Producție / neutralizare</t>
+          <t>Autofactură</t>
         </is>
       </c>
       <c r="I8" s="43" t="str">
@@ -29891,185 +29823,29 @@
         <v>DA</v>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="43" t="n">
-        <v>5</v>
-      </c>
-      <c r="B9" s="43" t="inlineStr">
-        <is>
-          <t>B3 Finalizare</t>
-        </is>
-      </c>
-      <c r="C9" s="43" t="str">
-        <f>Declarații_NEUTRALIZARE!B9</f>
-        <v>2026-07-20</v>
-      </c>
-      <c r="D9" s="43">
-        <f>Jurnale_NEUTRALIZARE!B21</f>
-        <v>345</v>
-      </c>
-      <c r="E9" s="43">
-        <f>Jurnale_NEUTRALIZARE!E21</f>
-        <v>711</v>
-      </c>
-      <c r="F9" s="43">
-        <f>Jurnale_NEUTRALIZARE!C21</f>
-        <v>4500</v>
-      </c>
-      <c r="G9" s="43" t="str">
-        <f>Jurnale_NEUTRALIZARE!D21</f>
-        <v>Obținere produs finit (345=711) — 2026-07 — BUNURI — 711</v>
-      </c>
-      <c r="H9" s="43" t="inlineStr">
-        <is>
-          <t>Producție / neutralizare</t>
-        </is>
-      </c>
-      <c r="I9" s="43" t="str">
-        <f>IF(AND(ISNUMBER(F9),F9&gt;0),"DA","NU")</f>
-        <v>DA</v>
-      </c>
-    </row>
     <row r="10">
-      <c r="A10" s="43" t="n">
-        <v>6</v>
-      </c>
-      <c r="B10" s="43" t="inlineStr">
-        <is>
-          <t>B4 Vânzare</t>
-        </is>
-      </c>
-      <c r="C10" s="43" t="str">
-        <f>Declarații_NEUTRALIZARE!B10</f>
-        <v>2026-07-25</v>
-      </c>
-      <c r="D10" s="43" t="str">
-        <f>Jurnale_NEUTRALIZARE!B27</f>
-        <v>411.RO</v>
-      </c>
-      <c r="E10" s="43">
-        <f>Jurnale_NEUTRALIZARE!E27</f>
-        <v>701</v>
-      </c>
-      <c r="F10" s="43">
-        <f>Jurnale_NEUTRALIZARE!F27</f>
-        <v>7000</v>
-      </c>
-      <c r="G10" s="43" t="str">
-        <f>Jurnale_NEUTRALIZARE!D27</f>
-        <v>Creanță client — 2026-07 — BUNURI — 711</v>
-      </c>
-      <c r="H10" s="43" t="inlineStr">
-        <is>
-          <t>Producție / neutralizare</t>
-        </is>
-      </c>
-      <c r="I10" s="43" t="str">
-        <f>IF(AND(ISNUMBER(F10),F10&gt;0),"DA","NU")</f>
-        <v>DA</v>
+      <c r="A10" s="43" t="inlineStr">
+        <is>
+          <t>Rânduri de importat</t>
+        </is>
+      </c>
+      <c r="B10" s="43">
+        <f>COUNTIF(I5:I8,"DA")</f>
+        <v>4</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="43" t="n">
-        <v>7</v>
-      </c>
-      <c r="B11" s="43" t="inlineStr">
-        <is>
-          <t>B4 TVA</t>
-        </is>
+      <c r="A11" s="43" t="inlineStr">
+        <is>
+          <t>Check global</t>
+        </is>
+      </c>
+      <c r="B11" s="43">
+        <f>Jurnale_TAXARE_INVERSA!B19</f>
+        <v>0</v>
       </c>
       <c r="C11" s="43" t="str">
-        <f>Declarații_NEUTRALIZARE!B10</f>
-        <v>2026-07-25</v>
-      </c>
-      <c r="D11" s="43" t="str">
-        <f>Jurnale_NEUTRALIZARE!B27</f>
-        <v>411.RO</v>
-      </c>
-      <c r="E11" s="43" t="str">
-        <f>Jurnale_NEUTRALIZARE!E28</f>
-        <v>4427</v>
-      </c>
-      <c r="F11" s="43">
-        <f>Jurnale_NEUTRALIZARE!F28</f>
-        <v>1470</v>
-      </c>
-      <c r="G11" s="43" t="str">
-        <f>Jurnale_NEUTRALIZARE!G28</f>
-        <v>TVA colectată — 2026-07 — BUNURI — 711</v>
-      </c>
-      <c r="H11" s="43" t="inlineStr">
-        <is>
-          <t>Producție / neutralizare</t>
-        </is>
-      </c>
-      <c r="I11" s="43" t="str">
-        <f>IF(AND(ISNUMBER(F11),F11&gt;0),"DA","NU")</f>
-        <v>DA</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="43" t="n">
-        <v>8</v>
-      </c>
-      <c r="B12" s="43" t="inlineStr">
-        <is>
-          <t>B4 Descărcare</t>
-        </is>
-      </c>
-      <c r="C12" s="43" t="str">
-        <f>Declarații_NEUTRALIZARE!B10</f>
-        <v>2026-07-25</v>
-      </c>
-      <c r="D12" s="43">
-        <f>Jurnale_NEUTRALIZARE!B29</f>
-        <v>711</v>
-      </c>
-      <c r="E12" s="43">
-        <f>Jurnale_NEUTRALIZARE!E29</f>
-        <v>345</v>
-      </c>
-      <c r="F12" s="43">
-        <f>Jurnale_NEUTRALIZARE!C29</f>
-        <v>4500</v>
-      </c>
-      <c r="G12" s="43" t="str">
-        <f>Jurnale_NEUTRALIZARE!D29</f>
-        <v>Descărcare PF prin 711 (NU 607) — 2026-07 — BUNURI — 711</v>
-      </c>
-      <c r="H12" s="43" t="inlineStr">
-        <is>
-          <t>Producție / neutralizare</t>
-        </is>
-      </c>
-      <c r="I12" s="43" t="str">
-        <f>IF(AND(ISNUMBER(F12),F12&gt;0),"DA","NU")</f>
-        <v>DA</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="43" t="inlineStr">
-        <is>
-          <t>Rânduri de importat</t>
-        </is>
-      </c>
-      <c r="B14" s="43">
-        <f>COUNTIF(I5:I12,"DA")</f>
-        <v>7</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="43" t="inlineStr">
-        <is>
-          <t>Check global</t>
-        </is>
-      </c>
-      <c r="B15" s="43">
-        <f>Jurnale_NEUTRALIZARE!B32</f>
-        <v>0</v>
-      </c>
-      <c r="C15" s="43" t="str">
-        <f>IF(ABS(B15)&lt;0.01,"OK","EROARE")</f>
+        <f>IF(ABS(B11)&lt;0.01,"OK","EROARE")</f>
         <v>OK</v>
       </c>
     </row>
@@ -30084,25 +29860,25 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B40"/>
+  <dimension ref="A1:B41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="36" customWidth="1" style="40" min="1" max="1"/>
-    <col width="26" customWidth="1" style="40" min="2" max="2"/>
+    <col width="40" customWidth="1" style="40" min="1" max="1"/>
+    <col width="42" customWidth="1" style="40" min="2" max="2"/>
     <col width="52" customWidth="1" style="40" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="41" t="inlineStr">
         <is>
-          <t>MOD_VANZ_AMANUNT — Declarații (input)</t>
+          <t>MOD_NEUTRALIZARE — Declarații (input)</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="44" t="inlineStr">
         <is>
-          <t>Gestiune amănunt la PVA. Corelații: 371×c/(100+c)=4428 și 707−607=rulaj D 378. Completează galben.</t>
+          <t>Acoperă F-311 (bunuri/711), F-312 (servicii/712), F-209 (imobilizări/722). Alege tipul — conturile și lanțul se adaptează. Principiu: costurile lovesc cls.6, apoi contul de venit de producție capitalizează și neutralizează.</t>
         </is>
       </c>
     </row>
@@ -30127,19 +29903,18 @@
     <row r="6">
       <c r="A6" s="43" t="inlineStr">
         <is>
-          <t>Gestiune (analitic)</t>
-        </is>
-      </c>
-      <c r="B6" s="64" t="inlineStr">
-        <is>
-          <t>AM.21</t>
-        </is>
+          <t>CUI</t>
+        </is>
+      </c>
+      <c r="B6" s="43" t="str">
+        <f>Parametri!B6</f>
+        <v>RO00000000</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="43" t="inlineStr">
         <is>
-          <t>Luna</t>
+          <t>Luna / proiect</t>
         </is>
       </c>
       <c r="B7" s="64" t="inlineStr">
@@ -30151,7 +29926,7 @@
     <row r="8">
       <c r="A8" s="43" t="inlineStr">
         <is>
-          <t>Data aprovizionare</t>
+          <t>Data costuri (B1)</t>
         </is>
       </c>
       <c r="B8" s="64" t="inlineStr">
@@ -30163,301 +29938,276 @@
     <row r="9">
       <c r="A9" s="43" t="inlineStr">
         <is>
-          <t>Data vânzare (Z-report)</t>
+          <t>Data finalizare stoc (B2-B3)</t>
         </is>
       </c>
       <c r="B9" s="64" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="42" t="inlineStr">
-        <is>
-          <t>2. Aprovizionare</t>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="43" t="inlineStr">
+        <is>
+          <t>Data vânzare / recepție MF (B4)</t>
+        </is>
+      </c>
+      <c r="B10" s="64" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="43" t="inlineStr">
-        <is>
-          <t>Cost (fără TVA)</t>
-        </is>
-      </c>
-      <c r="B12" s="64" t="n">
-        <v>10000</v>
+      <c r="A12" s="42" t="inlineStr">
+        <is>
+          <t>2. Tip producție (poartă principală)</t>
+        </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="43" t="inlineStr">
         <is>
-          <t>Adaos %</t>
-        </is>
-      </c>
-      <c r="B13" s="64" t="n">
-        <v>0.3</v>
+          <t>Tip (BUNURI / SERVICII / MF)</t>
+        </is>
+      </c>
+      <c r="B13" s="64" t="inlineStr">
+        <is>
+          <t>BUNURI</t>
+        </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="43" t="inlineStr">
         <is>
-          <t>Cotă TVA</t>
-        </is>
-      </c>
-      <c r="B14" s="64" t="n">
-        <v>0.21</v>
+          <t>Cont venit neutralizare (auto)</t>
+        </is>
+      </c>
+      <c r="B14" s="43">
+        <f>IF(B13="BUNURI",711,IF(B13="SERVICII",712,IF(B13="MF",722,"?")))</f>
+        <v>711</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="43" t="inlineStr">
         <is>
-          <t>Adaos (lei)</t>
+          <t>Cont stoc intermediar (auto)</t>
         </is>
       </c>
       <c r="B15" s="43">
-        <f>B12*B13</f>
-        <v>3000</v>
+        <f>IF(B13="BUNURI",331,IF(B13="SERVICII",332,IF(B13="MF",231,"?")))</f>
+        <v>331</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="43" t="inlineStr">
         <is>
-          <t>Bază PVA (cost+adaos)</t>
+          <t>Cont stoc final (auto)</t>
         </is>
       </c>
       <c r="B16" s="43">
-        <f>B12+B15</f>
-        <v>13000</v>
+        <f>IF(B13="BUNURI",345,IF(B13="SERVICII","(nu e cazul — se stinge la livrare)",IF(B13="MF",213,"?")))</f>
+        <v>345</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="43" t="inlineStr">
         <is>
-          <t>TVA în PVA</t>
+          <t>Cont venit vânzare (auto)</t>
         </is>
       </c>
       <c r="B17" s="43">
-        <f>B16*B14</f>
-        <v>2730</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="43" t="inlineStr">
-        <is>
-          <t>PVA total (371)</t>
-        </is>
-      </c>
-      <c r="B18" s="43">
-        <f>B16+B17</f>
-        <v>15730</v>
+        <f>IF(B13="BUNURI",701,IF(B13="SERVICII",704,IF(B13="MF","(nu e vânzare — e activ)","?")))</f>
+        <v>701</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="43" t="inlineStr">
-        <is>
-          <t>TVA deductibilă (pe cost)</t>
-        </is>
-      </c>
-      <c r="B19" s="43">
-        <f>B12*B14</f>
-        <v>2100</v>
+      <c r="A19" s="42" t="inlineStr">
+        <is>
+          <t>3. Costuri (cls.6)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="43" t="inlineStr">
+        <is>
+          <t>Cost materiale (→ 601)</t>
+        </is>
+      </c>
+      <c r="B20" s="64" t="n">
+        <v>4500</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="42" t="inlineStr">
-        <is>
-          <t>3. Conturi</t>
-        </is>
+      <c r="A21" s="43" t="inlineStr">
+        <is>
+          <t>Cost manoperă (→ 641)</t>
+        </is>
+      </c>
+      <c r="B21" s="64" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="43" t="inlineStr">
         <is>
-          <t>Cont stoc (371.gest.cotă)</t>
-        </is>
-      </c>
-      <c r="B22" s="64" t="inlineStr">
-        <is>
-          <t>371.AM.21</t>
-        </is>
+          <t>Alte costuri (→ 6xx)</t>
+        </is>
+      </c>
+      <c r="B22" s="64" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="43" t="inlineStr">
         <is>
-          <t>Cont adaos (378)</t>
-        </is>
-      </c>
-      <c r="B23" s="64" t="inlineStr">
-        <is>
-          <t>378.AM.21</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="43" t="inlineStr">
-        <is>
-          <t>Cont TVA neexigibilă (4428)</t>
-        </is>
-      </c>
-      <c r="B24" s="64" t="inlineStr">
-        <is>
-          <t>4428.AM</t>
-        </is>
+          <t>Cost total</t>
+        </is>
+      </c>
+      <c r="B23" s="43">
+        <f>B20+B21+B22</f>
+        <v>4500</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="43" t="inlineStr">
-        <is>
-          <t>Cont furnizor</t>
-        </is>
-      </c>
-      <c r="B25" s="64" t="inlineStr">
-        <is>
-          <t>401.RO</t>
+      <c r="A25" s="42" t="inlineStr">
+        <is>
+          <t>4. Vânzare (doar BUNURI / SERVICII)</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="43" t="inlineStr">
         <is>
-          <t>Cont TVA deductibilă</t>
-        </is>
-      </c>
-      <c r="B26" s="64" t="inlineStr">
-        <is>
-          <t>4426</t>
-        </is>
+          <t>Preț vânzare (fără TVA)</t>
+        </is>
+      </c>
+      <c r="B26" s="64" t="n">
+        <v>7000</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="43" t="inlineStr">
         <is>
-          <t>Cont cheltuială (607)</t>
-        </is>
-      </c>
-      <c r="B27" s="64" t="inlineStr">
-        <is>
-          <t>607</t>
-        </is>
+          <t>Cota TVA</t>
+        </is>
+      </c>
+      <c r="B27" s="64" t="n">
+        <v>0.21</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="43" t="inlineStr">
         <is>
-          <t>Cont venit (707)</t>
-        </is>
-      </c>
-      <c r="B28" s="64" t="inlineStr">
-        <is>
-          <t>707</t>
-        </is>
+          <t>TVA</t>
+        </is>
+      </c>
+      <c r="B28" s="43">
+        <f>IF(OR(B13="BUNURI",B13="SERVICII"),B26*B27,0)</f>
+        <v>1470</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="43" t="inlineStr">
         <is>
-          <t>Cont TVA colectată</t>
-        </is>
-      </c>
-      <c r="B29" s="64" t="inlineStr">
-        <is>
-          <t>4427</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="43" t="inlineStr">
-        <is>
-          <t>Cont casă / bancă</t>
-        </is>
-      </c>
-      <c r="B30" s="64" t="inlineStr">
-        <is>
-          <t>531.1</t>
-        </is>
+          <t>Total factură</t>
+        </is>
+      </c>
+      <c r="B29" s="43">
+        <f>B26+B28</f>
+        <v>8470</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="43" t="inlineStr">
-        <is>
-          <t>Cont TVA de plată</t>
-        </is>
-      </c>
-      <c r="B31" s="64" t="inlineStr">
-        <is>
-          <t>4423</t>
+      <c r="A31" s="42" t="inlineStr">
+        <is>
+          <t>5. Conturi suplimentare</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="43" t="inlineStr">
+        <is>
+          <t>Cont materii prime</t>
+        </is>
+      </c>
+      <c r="B32" s="64" t="inlineStr">
+        <is>
+          <t>301</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="42" t="inlineStr">
-        <is>
-          <t>4. Corelații (auto)</t>
+      <c r="A33" s="43" t="inlineStr">
+        <is>
+          <t>Cont client</t>
+        </is>
+      </c>
+      <c r="B33" s="64" t="inlineStr">
+        <is>
+          <t>411.RO</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="43" t="inlineStr">
         <is>
-          <t>Corelație 1: 371×c/(100+c) =?</t>
-        </is>
-      </c>
-      <c r="B34" s="43">
-        <f>B18*B14/(1+B14)</f>
-        <v>2730</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="43" t="inlineStr">
-        <is>
-          <t>Trebuie = 4428</t>
-        </is>
-      </c>
-      <c r="B35" s="43" t="str">
-        <f>IF(ABS(B34-B17)&lt;0.01,"OK — corelație 1 ține","EROARE")</f>
-        <v>OK — corelație 1 ține</v>
+          <t>Cont TVA colectată</t>
+        </is>
+      </c>
+      <c r="B34" s="64" t="inlineStr">
+        <is>
+          <t>4427</t>
+        </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="43" t="inlineStr">
-        <is>
-          <t>Corelație 2: 707−607 =?</t>
-        </is>
-      </c>
-      <c r="B36" s="43">
-        <f>B16-B12</f>
-        <v>3000</v>
+      <c r="A36" s="42" t="inlineStr">
+        <is>
+          <t>6. Sufix</t>
+        </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="43" t="inlineStr">
         <is>
-          <t>Trebuie = adaos (rulaj D 378)</t>
+          <t>Sufix</t>
         </is>
       </c>
       <c r="B37" s="43" t="str">
-        <f>IF(ABS(B36-B15)&lt;0.01,"OK — corelație 2 ține","EROARE")</f>
-        <v>OK — corelație 2 ține</v>
+        <f>"— " &amp; B7 &amp; " — " &amp; B13 &amp; " — " &amp; B14</f>
+        <v>— 2026-07 — BUNURI — 711</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="42" t="inlineStr">
         <is>
-          <t>5. Sufix</t>
+          <t>7. Control</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="43" t="inlineStr">
         <is>
-          <t>Sufix</t>
-        </is>
-      </c>
-      <c r="B40" s="43" t="str">
-        <f>"— amănunt " &amp; B6 &amp; " — " &amp; B7</f>
-        <v>— amănunt AM.21 — 2026-07</v>
+          <t>Marjă (vânzare − cost)</t>
+        </is>
+      </c>
+      <c r="B40" s="43">
+        <f>IF(OR(B13="BUNURI",B13="SERVICII"),B26-B23,"n/a (MF)")</f>
+        <v>2500</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="43" t="inlineStr">
+        <is>
+          <t>Notă principiu</t>
+        </is>
+      </c>
+      <c r="B41" s="43" t="inlineStr">
+        <is>
+          <t>Costurile lovesc cls.6; contul de venit de producție (711/712/722) capitalizează și neutralizează. Descărcarea la vânzare (bunuri) e prin 711=345, nu prin 607.</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -30856,6 +30606,1640 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:F21"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" style="40" min="1" max="1"/>
+    <col width="20" customWidth="1" style="40" min="2" max="2"/>
+    <col width="20" customWidth="1" style="40" min="3" max="3"/>
+    <col width="26" customWidth="1" style="40" min="4" max="4"/>
+    <col width="30" customWidth="1" style="40" min="5" max="5"/>
+    <col width="26" customWidth="1" style="40" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="41" t="inlineStr">
+        <is>
+          <t>MOD_NEUTRALIZARE — Reguli (tabele fixe)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="44" t="inlineStr">
+        <is>
+          <t>Principiul comun F-311 / F-312 / F-209: cost → cls.6 → stoc intermediar = venit neutralizare → stoc final / livrare. 711/712/722 nu se stinge greșit în stocul final fără pasul de obținere.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="42" t="inlineStr">
+        <is>
+          <t>Tabel A — Lanț pe tip</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="65" t="inlineStr">
+        <is>
+          <t>Tip</t>
+        </is>
+      </c>
+      <c r="B5" s="65" t="inlineStr">
+        <is>
+          <t>Cost →</t>
+        </is>
+      </c>
+      <c r="C5" s="65" t="inlineStr">
+        <is>
+          <t>Stoc intermediar</t>
+        </is>
+      </c>
+      <c r="D5" s="65" t="inlineStr">
+        <is>
+          <t>Venit neut.</t>
+        </is>
+      </c>
+      <c r="E5" s="65" t="inlineStr">
+        <is>
+          <t>Stoc final / livrare</t>
+        </is>
+      </c>
+      <c r="F5" s="65" t="inlineStr">
+        <is>
+          <t>Descărcare la vânzare</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="43" t="inlineStr">
+        <is>
+          <t>BUNURI</t>
+        </is>
+      </c>
+      <c r="B6" s="43" t="inlineStr">
+        <is>
+          <t>601=301</t>
+        </is>
+      </c>
+      <c r="C6" s="43" t="inlineStr">
+        <is>
+          <t>331=711</t>
+        </is>
+      </c>
+      <c r="D6" s="43" t="inlineStr">
+        <is>
+          <t>711=331 apoi 345=711</t>
+        </is>
+      </c>
+      <c r="E6" s="43" t="inlineStr">
+        <is>
+          <t>345</t>
+        </is>
+      </c>
+      <c r="F6" s="43" t="inlineStr">
+        <is>
+          <t>711=345 (NU 607)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="43" t="inlineStr">
+        <is>
+          <t>SERVICII</t>
+        </is>
+      </c>
+      <c r="B7" s="43" t="inlineStr">
+        <is>
+          <t>641/601=…</t>
+        </is>
+      </c>
+      <c r="C7" s="43" t="inlineStr">
+        <is>
+          <t>332=712</t>
+        </is>
+      </c>
+      <c r="D7" s="43" t="inlineStr">
+        <is>
+          <t>712=332</t>
+        </is>
+      </c>
+      <c r="E7" s="43" t="inlineStr">
+        <is>
+          <t>(nu e stoc final)</t>
+        </is>
+      </c>
+      <c r="F7" s="43" t="inlineStr">
+        <is>
+          <t>712 stins la livrare</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="43" t="inlineStr">
+        <is>
+          <t>MF</t>
+        </is>
+      </c>
+      <c r="B8" s="43" t="inlineStr">
+        <is>
+          <t>601=301, 641=421</t>
+        </is>
+      </c>
+      <c r="C8" s="43" t="inlineStr">
+        <is>
+          <t>231=722</t>
+        </is>
+      </c>
+      <c r="D8" s="43" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E8" s="43" t="inlineStr">
+        <is>
+          <t>213=231</t>
+        </is>
+      </c>
+      <c r="F8" s="43" t="inlineStr">
+        <is>
+          <t>(nu e vânzare — e activ)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="42" t="inlineStr">
+        <is>
+          <t>Tabel B — Porți de calitate</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="44" t="inlineStr">
+        <is>
+          <t>• ΣD=ΣC pe fiecare bloc</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="44" t="inlineStr">
+        <is>
+          <t>• Cont venit neutralizare: rulaj D = rulaj C la final (sold 0)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="44" t="inlineStr">
+        <is>
+          <t>• Stoc intermediar sold 0 după finalizare</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="44" t="inlineStr">
+        <is>
+          <t>• Pentru BUNURI: 345 un singur D și un singur C; descărcare prin 711, nu 607</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="44" t="inlineStr">
+        <is>
+          <t>• Pentru MF: impact net pe 121 din capitalizare = 0 (cheltuieli = 722)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="42" t="inlineStr">
+        <is>
+          <t>Tabel C — Ce NU se face</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="44" t="inlineStr">
+        <is>
+          <t>• 345 creditat de două ori fără un debit de obținere (eroarea F-311 veche)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="44" t="inlineStr">
+        <is>
+          <t>• 722 = 231 (ar stinge activul — eroare F-209 veche); corect e 231 = 722</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="44" t="inlineStr">
+        <is>
+          <t>• 607 la descărcarea produselor finite (607 e doar mărfuri)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="44" t="inlineStr">
+        <is>
+          <t>• „711 sau 712” la servicii — pentru servicii e strict 712</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet71.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G35"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" style="40" min="1" max="1"/>
+    <col width="20" customWidth="1" style="40" min="2" max="2"/>
+    <col width="14" customWidth="1" style="40" min="3" max="3"/>
+    <col width="52" customWidth="1" style="40" min="4" max="4"/>
+    <col width="20" customWidth="1" style="40" min="5" max="5"/>
+    <col width="14" customWidth="1" style="40" min="6" max="6"/>
+    <col width="52" customWidth="1" style="40" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="41" t="inlineStr">
+        <is>
+          <t>MOD_NEUTRALIZARE — Jurnale (generate automat)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="44" t="inlineStr">
+        <is>
+          <t>Lanțul se adaptează după Tip. Pentru MF, blocul de vânzare rămâne 0. Pentru SERVICII, stocul final e gol.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="42" t="inlineStr">
+        <is>
+          <t>Bloc 1 — Costuri pe cls.6</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="43" t="inlineStr">
+        <is>
+          <t>Data:</t>
+        </is>
+      </c>
+      <c r="B5" s="43" t="str">
+        <f>Declarații_NEUTRALIZARE!B8</f>
+        <v>2026-07-05</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="65" t="inlineStr">
+        <is>
+          <t>Nr</t>
+        </is>
+      </c>
+      <c r="B6" s="65" t="inlineStr">
+        <is>
+          <t>Cont Dr</t>
+        </is>
+      </c>
+      <c r="C6" s="65" t="inlineStr">
+        <is>
+          <t>Sumă Dr</t>
+        </is>
+      </c>
+      <c r="D6" s="65" t="inlineStr">
+        <is>
+          <t>Descriere Dr</t>
+        </is>
+      </c>
+      <c r="E6" s="65" t="inlineStr">
+        <is>
+          <t>Cont Cr</t>
+        </is>
+      </c>
+      <c r="F6" s="65" t="inlineStr">
+        <is>
+          <t>Sumă Cr</t>
+        </is>
+      </c>
+      <c r="G6" s="65" t="inlineStr">
+        <is>
+          <t>Descriere Cr</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="43" t="n">
+        <v>1</v>
+      </c>
+      <c r="B7" s="43" t="inlineStr">
+        <is>
+          <t>601</t>
+        </is>
+      </c>
+      <c r="C7" s="43">
+        <f>Declarații_NEUTRALIZARE!B20</f>
+        <v>4500</v>
+      </c>
+      <c r="D7" s="43" t="str">
+        <f>"Consum materiale " &amp; Declarații_NEUTRALIZARE!B37</f>
+        <v>Consum materiale — 2026-07 — BUNURI — 711</v>
+      </c>
+      <c r="E7" s="43" t="str">
+        <f>Declarații_NEUTRALIZARE!B32</f>
+        <v>301</v>
+      </c>
+      <c r="F7" s="43">
+        <f>Declarații_NEUTRALIZARE!B20</f>
+        <v>4500</v>
+      </c>
+      <c r="G7" s="43" t="str">
+        <f>"Stingere stoc materii " &amp; Declarații_NEUTRALIZARE!B37</f>
+        <v>Stingere stoc materii — 2026-07 — BUNURI — 711</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="43" t="n">
+        <v>2</v>
+      </c>
+      <c r="B8" s="43" t="inlineStr">
+        <is>
+          <t>641</t>
+        </is>
+      </c>
+      <c r="C8" s="43">
+        <f>Declarații_NEUTRALIZARE!B21</f>
+        <v>0</v>
+      </c>
+      <c r="D8" s="43" t="str">
+        <f>"Manoperă pe proiect " &amp; Declarații_NEUTRALIZARE!B37</f>
+        <v>Manoperă pe proiect — 2026-07 — BUNURI — 711</v>
+      </c>
+      <c r="E8" s="43" t="inlineStr">
+        <is>
+          <t>421</t>
+        </is>
+      </c>
+      <c r="F8" s="43">
+        <f>Declarații_NEUTRALIZARE!B21</f>
+        <v>0</v>
+      </c>
+      <c r="G8" s="43" t="str">
+        <f>"Datorie salarii " &amp; Declarații_NEUTRALIZARE!B37</f>
+        <v>Datorie salarii — 2026-07 — BUNURI — 711</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="43" t="inlineStr">
+        <is>
+          <t>Check B1</t>
+        </is>
+      </c>
+      <c r="B9" s="43">
+        <f>(C7+C8)-(F7+F8)</f>
+        <v>0</v>
+      </c>
+      <c r="C9" s="43" t="str">
+        <f>IF(ABS(B9)&lt;0.01,"OK","EROARE")</f>
+        <v>OK</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="42" t="inlineStr">
+        <is>
+          <t>Bloc 2 — Stoc intermediar = venit neutralizare (pas revelator)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="43" t="inlineStr">
+        <is>
+          <t>Data:</t>
+        </is>
+      </c>
+      <c r="B12" s="43" t="str">
+        <f>Declarații_NEUTRALIZARE!B9</f>
+        <v>2026-07-20</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="65" t="inlineStr">
+        <is>
+          <t>Nr</t>
+        </is>
+      </c>
+      <c r="B13" s="65" t="inlineStr">
+        <is>
+          <t>Cont Dr</t>
+        </is>
+      </c>
+      <c r="C13" s="65" t="inlineStr">
+        <is>
+          <t>Sumă Dr</t>
+        </is>
+      </c>
+      <c r="D13" s="65" t="inlineStr">
+        <is>
+          <t>Descriere Dr</t>
+        </is>
+      </c>
+      <c r="E13" s="65" t="inlineStr">
+        <is>
+          <t>Cont Cr</t>
+        </is>
+      </c>
+      <c r="F13" s="65" t="inlineStr">
+        <is>
+          <t>Sumă Cr</t>
+        </is>
+      </c>
+      <c r="G13" s="65" t="inlineStr">
+        <is>
+          <t>Descriere Cr</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="43" t="n">
+        <v>1</v>
+      </c>
+      <c r="B14" s="43">
+        <f>Declarații_NEUTRALIZARE!B15</f>
+        <v>331</v>
+      </c>
+      <c r="C14" s="43">
+        <f>Declarații_NEUTRALIZARE!B23</f>
+        <v>4500</v>
+      </c>
+      <c r="D14" s="43" t="str">
+        <f>"Stoc intermediar (PN/servicii/MF în curs) " &amp; Declarații_NEUTRALIZARE!B37</f>
+        <v>Stoc intermediar (PN/servicii/MF în curs) — 2026-07 — BUNURI — 711</v>
+      </c>
+      <c r="E14" s="43">
+        <f>Declarații_NEUTRALIZARE!B14</f>
+        <v>711</v>
+      </c>
+      <c r="F14" s="43">
+        <f>Declarații_NEUTRALIZARE!B23</f>
+        <v>4500</v>
+      </c>
+      <c r="G14" s="43" t="str">
+        <f>"Venit producție / neutralizare " &amp; Declarații_NEUTRALIZARE!B37</f>
+        <v>Venit producție / neutralizare — 2026-07 — BUNURI — 711</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="43" t="inlineStr">
+        <is>
+          <t>Check B2</t>
+        </is>
+      </c>
+      <c r="B15" s="43">
+        <f>C14-F14</f>
+        <v>0</v>
+      </c>
+      <c r="C15" s="43" t="str">
+        <f>IF(ABS(B15)&lt;0.01,"OK","EROARE")</f>
+        <v>OK</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="42" t="inlineStr">
+        <is>
+          <t>Bloc 3 — Finalizare (obținere stoc final / stingere intermediar)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="43" t="inlineStr">
+        <is>
+          <t>Data:</t>
+        </is>
+      </c>
+      <c r="B18" s="43" t="str">
+        <f>Declarații_NEUTRALIZARE!B9</f>
+        <v>2026-07-20</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="65" t="inlineStr">
+        <is>
+          <t>Nr</t>
+        </is>
+      </c>
+      <c r="B19" s="65" t="inlineStr">
+        <is>
+          <t>Cont Dr</t>
+        </is>
+      </c>
+      <c r="C19" s="65" t="inlineStr">
+        <is>
+          <t>Sumă Dr</t>
+        </is>
+      </c>
+      <c r="D19" s="65" t="inlineStr">
+        <is>
+          <t>Descriere Dr</t>
+        </is>
+      </c>
+      <c r="E19" s="65" t="inlineStr">
+        <is>
+          <t>Cont Cr</t>
+        </is>
+      </c>
+      <c r="F19" s="65" t="inlineStr">
+        <is>
+          <t>Sumă Cr</t>
+        </is>
+      </c>
+      <c r="G19" s="65" t="inlineStr">
+        <is>
+          <t>Descriere Cr</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="43" t="n">
+        <v>1</v>
+      </c>
+      <c r="B20" s="43">
+        <f>IF(Declarații_NEUTRALIZARE!B13="BUNURI",Declarații_NEUTRALIZARE!B14,IF(Declarații_NEUTRALIZARE!B13="SERVICII",Declarații_NEUTRALIZARE!B14,Declarații_NEUTRALIZARE!B16))</f>
+        <v>711</v>
+      </c>
+      <c r="C20" s="43">
+        <f>Declarații_NEUTRALIZARE!B23</f>
+        <v>4500</v>
+      </c>
+      <c r="D20" s="43" t="str">
+        <f>IF(Declarații_NEUTRALIZARE!B13="BUNURI","Reluare PN (711 debitat #1) ",IF(Declarații_NEUTRALIZARE!B13="SERVICII","Stingere servicii în curs ","Transfer MF final ")) &amp; Declarații_NEUTRALIZARE!B37</f>
+        <v>Reluare PN (711 debitat #1) — 2026-07 — BUNURI — 711</v>
+      </c>
+      <c r="E20" s="43">
+        <f>IF(Declarații_NEUTRALIZARE!B13="MF",Declarații_NEUTRALIZARE!B15,Declarații_NEUTRALIZARE!B15)</f>
+        <v>331</v>
+      </c>
+      <c r="F20" s="43">
+        <f>Declarații_NEUTRALIZARE!B23</f>
+        <v>4500</v>
+      </c>
+      <c r="G20" s="43" t="str">
+        <f>"Stingere stoc intermediar " &amp; Declarații_NEUTRALIZARE!B37</f>
+        <v>Stingere stoc intermediar — 2026-07 — BUNURI — 711</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="43" t="n">
+        <v>2</v>
+      </c>
+      <c r="B21" s="43">
+        <f>IF(Declarații_NEUTRALIZARE!B13="BUNURI",Declarații_NEUTRALIZARE!B16,0)</f>
+        <v>345</v>
+      </c>
+      <c r="C21" s="43">
+        <f>IF(Declarații_NEUTRALIZARE!B13="BUNURI",Declarații_NEUTRALIZARE!B23,0)</f>
+        <v>4500</v>
+      </c>
+      <c r="D21" s="43" t="str">
+        <f>IF(Declarații_NEUTRALIZARE!B13="BUNURI","Obținere produs finit (345=711) " &amp; Declarații_NEUTRALIZARE!B37,"")</f>
+        <v>Obținere produs finit (345=711) — 2026-07 — BUNURI — 711</v>
+      </c>
+      <c r="E21" s="43">
+        <f>IF(Declarații_NEUTRALIZARE!B13="BUNURI",Declarații_NEUTRALIZARE!B14,0)</f>
+        <v>711</v>
+      </c>
+      <c r="F21" s="43">
+        <f>IF(Declarații_NEUTRALIZARE!B13="BUNURI",Declarații_NEUTRALIZARE!B23,0)</f>
+        <v>4500</v>
+      </c>
+      <c r="G21" s="43" t="str">
+        <f>IF(Declarații_NEUTRALIZARE!B13="BUNURI","Neutralizare (711 creditat #2) " &amp; Declarații_NEUTRALIZARE!B37,"")</f>
+        <v>Neutralizare (711 creditat #2) — 2026-07 — BUNURI — 711</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="43" t="inlineStr">
+        <is>
+          <t>Check B3</t>
+        </is>
+      </c>
+      <c r="B22" s="43">
+        <f>(C20+C21)-(F20+F21)</f>
+        <v>0</v>
+      </c>
+      <c r="C22" s="43" t="str">
+        <f>IF(ABS(B22)&lt;0.01,"OK","EROARE")</f>
+        <v>OK</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="42" t="inlineStr">
+        <is>
+          <t>Bloc 4 — Vânzare + descărcare (BUNURI/SERVICII; 0 pentru MF)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="43" t="inlineStr">
+        <is>
+          <t>Data:</t>
+        </is>
+      </c>
+      <c r="B25" s="43" t="str">
+        <f>Declarații_NEUTRALIZARE!B10</f>
+        <v>2026-07-25</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="65" t="inlineStr">
+        <is>
+          <t>Nr</t>
+        </is>
+      </c>
+      <c r="B26" s="65" t="inlineStr">
+        <is>
+          <t>Cont Dr</t>
+        </is>
+      </c>
+      <c r="C26" s="65" t="inlineStr">
+        <is>
+          <t>Sumă Dr</t>
+        </is>
+      </c>
+      <c r="D26" s="65" t="inlineStr">
+        <is>
+          <t>Descriere Dr</t>
+        </is>
+      </c>
+      <c r="E26" s="65" t="inlineStr">
+        <is>
+          <t>Cont Cr</t>
+        </is>
+      </c>
+      <c r="F26" s="65" t="inlineStr">
+        <is>
+          <t>Sumă Cr</t>
+        </is>
+      </c>
+      <c r="G26" s="65" t="inlineStr">
+        <is>
+          <t>Descriere Cr</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="43" t="n">
+        <v>1</v>
+      </c>
+      <c r="B27" s="43" t="str">
+        <f>IF(OR(Declarații_NEUTRALIZARE!B13="BUNURI",Declarații_NEUTRALIZARE!B13="SERVICII"),Declarații_NEUTRALIZARE!B33,0)</f>
+        <v>411.RO</v>
+      </c>
+      <c r="C27" s="43">
+        <f>IF(OR(Declarații_NEUTRALIZARE!B13="BUNURI",Declarații_NEUTRALIZARE!B13="SERVICII"),Declarații_NEUTRALIZARE!B29,0)</f>
+        <v>8470</v>
+      </c>
+      <c r="D27" s="43" t="str">
+        <f>"Creanță client " &amp; Declarații_NEUTRALIZARE!B37</f>
+        <v>Creanță client — 2026-07 — BUNURI — 711</v>
+      </c>
+      <c r="E27" s="43">
+        <f>IF(OR(Declarații_NEUTRALIZARE!B13="BUNURI",Declarații_NEUTRALIZARE!B13="SERVICII"),Declarații_NEUTRALIZARE!B17,0)</f>
+        <v>701</v>
+      </c>
+      <c r="F27" s="43">
+        <f>IF(OR(Declarații_NEUTRALIZARE!B13="BUNURI",Declarații_NEUTRALIZARE!B13="SERVICII"),Declarații_NEUTRALIZARE!B26,0)</f>
+        <v>7000</v>
+      </c>
+      <c r="G27" s="43" t="str">
+        <f>"Venit din vânzare " &amp; Declarații_NEUTRALIZARE!B37</f>
+        <v>Venit din vânzare — 2026-07 — BUNURI — 711</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="43" t="n">
+        <v>2</v>
+      </c>
+      <c r="B28" s="43" t="n">
+        <v>0</v>
+      </c>
+      <c r="C28" s="43" t="n">
+        <v>0</v>
+      </c>
+      <c r="E28" s="43" t="str">
+        <f>IF(OR(Declarații_NEUTRALIZARE!B13="BUNURI",Declarații_NEUTRALIZARE!B13="SERVICII"),Declarații_NEUTRALIZARE!B34,0)</f>
+        <v>4427</v>
+      </c>
+      <c r="F28" s="43">
+        <f>IF(OR(Declarații_NEUTRALIZARE!B13="BUNURI",Declarații_NEUTRALIZARE!B13="SERVICII"),Declarații_NEUTRALIZARE!B28,0)</f>
+        <v>1470</v>
+      </c>
+      <c r="G28" s="43" t="str">
+        <f>"TVA colectată " &amp; Declarații_NEUTRALIZARE!B37</f>
+        <v>TVA colectată — 2026-07 — BUNURI — 711</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="43" t="n">
+        <v>3</v>
+      </c>
+      <c r="B29" s="43">
+        <f>IF(Declarații_NEUTRALIZARE!B13="BUNURI",Declarații_NEUTRALIZARE!B14,IF(Declarații_NEUTRALIZARE!B13="SERVICII",Declarații_NEUTRALIZARE!B14,0))</f>
+        <v>711</v>
+      </c>
+      <c r="C29" s="43">
+        <f>IF(OR(Declarații_NEUTRALIZARE!B13="BUNURI",Declarații_NEUTRALIZARE!B13="SERVICII"),Declarații_NEUTRALIZARE!B23,0)</f>
+        <v>4500</v>
+      </c>
+      <c r="D29" s="43" t="str">
+        <f>IF(Declarații_NEUTRALIZARE!B13="BUNURI","Descărcare PF prin 711 (NU 607) ",IF(Declarații_NEUTRALIZARE!B13="SERVICII","Stingere 712 la livrare ","")) &amp; Declarații_NEUTRALIZARE!B37</f>
+        <v>Descărcare PF prin 711 (NU 607) — 2026-07 — BUNURI — 711</v>
+      </c>
+      <c r="E29" s="43">
+        <f>IF(Declarații_NEUTRALIZARE!B13="BUNURI",Declarații_NEUTRALIZARE!B16,0)</f>
+        <v>345</v>
+      </c>
+      <c r="F29" s="43">
+        <f>IF(Declarații_NEUTRALIZARE!B13="BUNURI",Declarații_NEUTRALIZARE!B23,0)</f>
+        <v>4500</v>
+      </c>
+      <c r="G29" s="43" t="str">
+        <f>IF(Declarații_NEUTRALIZARE!B13="BUNURI","Stingere stoc PF " &amp; Declarații_NEUTRALIZARE!B37,"")</f>
+        <v>Stingere stoc PF — 2026-07 — BUNURI — 711</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="43" t="inlineStr">
+        <is>
+          <t>Check B4</t>
+        </is>
+      </c>
+      <c r="B30" s="43">
+        <f>(C27+C28+C29)-(F27+F28+F29)</f>
+        <v>0</v>
+      </c>
+      <c r="C30" s="43" t="str">
+        <f>IF(ABS(B30)&lt;0.01,"OK","EROARE")</f>
+        <v>OK</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="43" t="inlineStr">
+        <is>
+          <t>Check global</t>
+        </is>
+      </c>
+      <c r="B32" s="43">
+        <f>ABS(B9)+ABS(B15)+ABS(B22)+ABS(B30)</f>
+        <v>0</v>
+      </c>
+      <c r="C32" s="43" t="str">
+        <f>IF(B32&lt;0.01,"OK — toate blocurile se închid","EROARE — cel puțin un bloc dezechilibrat")</f>
+        <v>OK — toate blocurile se închid</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="42" t="inlineStr">
+        <is>
+          <t>Stare terminală</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="44" t="inlineStr">
+        <is>
+          <t>Cont venit neut. sold 0 | Stoc intermediar 0 | Pentru BUNURI: 345 sold 0, descărcare prin 711 | Pentru MF: 213=cost, impact 121 din capitalizare = 0</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet72.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="6" customWidth="1" style="40" min="1" max="1"/>
+    <col width="18" customWidth="1" style="40" min="2" max="2"/>
+    <col width="14" customWidth="1" style="40" min="3" max="3"/>
+    <col width="16" customWidth="1" style="40" min="4" max="4"/>
+    <col width="16" customWidth="1" style="40" min="5" max="5"/>
+    <col width="14" customWidth="1" style="40" min="6" max="6"/>
+    <col width="52" customWidth="1" style="40" min="7" max="7"/>
+    <col width="24" customWidth="1" style="40" min="8" max="8"/>
+    <col width="10" customWidth="1" style="40" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="41" t="inlineStr">
+        <is>
+          <t>MOD_NEUTRALIZARE — Notă pentru import</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="44" t="inlineStr">
+        <is>
+          <t>Filtrează Include=DA. Rândurile cu sumă 0 (ex. manoperă 0, sau blocuri MF fără vânzare) apar ca NU.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="65" t="inlineStr">
+        <is>
+          <t>Nr</t>
+        </is>
+      </c>
+      <c r="B4" s="65" t="inlineStr">
+        <is>
+          <t>Bloc</t>
+        </is>
+      </c>
+      <c r="C4" s="65" t="inlineStr">
+        <is>
+          <t>Data</t>
+        </is>
+      </c>
+      <c r="D4" s="65" t="inlineStr">
+        <is>
+          <t>Cont Dr</t>
+        </is>
+      </c>
+      <c r="E4" s="65" t="inlineStr">
+        <is>
+          <t>Cont Cr</t>
+        </is>
+      </c>
+      <c r="F4" s="65" t="inlineStr">
+        <is>
+          <t>Sumă</t>
+        </is>
+      </c>
+      <c r="G4" s="65" t="inlineStr">
+        <is>
+          <t>Descriere</t>
+        </is>
+      </c>
+      <c r="H4" s="65" t="inlineStr">
+        <is>
+          <t>Document</t>
+        </is>
+      </c>
+      <c r="I4" s="65" t="inlineStr">
+        <is>
+          <t>Include</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="43" t="n">
+        <v>1</v>
+      </c>
+      <c r="B5" s="43" t="inlineStr">
+        <is>
+          <t>B1 Costuri</t>
+        </is>
+      </c>
+      <c r="C5" s="43" t="str">
+        <f>Declarații_NEUTRALIZARE!B8</f>
+        <v>2026-07-05</v>
+      </c>
+      <c r="D5" s="43" t="str">
+        <f>Jurnale_NEUTRALIZARE!B7</f>
+        <v>601</v>
+      </c>
+      <c r="E5" s="43" t="str">
+        <f>Jurnale_NEUTRALIZARE!E7</f>
+        <v>301</v>
+      </c>
+      <c r="F5" s="43">
+        <f>Jurnale_NEUTRALIZARE!C7</f>
+        <v>4500</v>
+      </c>
+      <c r="G5" s="43" t="str">
+        <f>Jurnale_NEUTRALIZARE!D7</f>
+        <v>Consum materiale — 2026-07 — BUNURI — 711</v>
+      </c>
+      <c r="H5" s="43" t="inlineStr">
+        <is>
+          <t>Producție / neutralizare</t>
+        </is>
+      </c>
+      <c r="I5" s="43" t="str">
+        <f>IF(AND(ISNUMBER(F5),F5&gt;0),"DA","NU")</f>
+        <v>DA</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="43" t="n">
+        <v>2</v>
+      </c>
+      <c r="B6" s="43" t="inlineStr">
+        <is>
+          <t>B1 Costuri</t>
+        </is>
+      </c>
+      <c r="C6" s="43" t="str">
+        <f>Declarații_NEUTRALIZARE!B8</f>
+        <v>2026-07-05</v>
+      </c>
+      <c r="D6" s="43" t="str">
+        <f>Jurnale_NEUTRALIZARE!B8</f>
+        <v>641</v>
+      </c>
+      <c r="E6" s="43" t="str">
+        <f>Jurnale_NEUTRALIZARE!E8</f>
+        <v>421</v>
+      </c>
+      <c r="F6" s="43">
+        <f>Jurnale_NEUTRALIZARE!C8</f>
+        <v>0</v>
+      </c>
+      <c r="G6" s="43" t="str">
+        <f>Jurnale_NEUTRALIZARE!D8</f>
+        <v>Manoperă pe proiect — 2026-07 — BUNURI — 711</v>
+      </c>
+      <c r="H6" s="43" t="inlineStr">
+        <is>
+          <t>Producție / neutralizare</t>
+        </is>
+      </c>
+      <c r="I6" s="43" t="str">
+        <f>IF(AND(ISNUMBER(F6),F6&gt;0),"DA","NU")</f>
+        <v>NU</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="43" t="n">
+        <v>3</v>
+      </c>
+      <c r="B7" s="43" t="inlineStr">
+        <is>
+          <t>B2 Neutralizare</t>
+        </is>
+      </c>
+      <c r="C7" s="43" t="str">
+        <f>Declarații_NEUTRALIZARE!B9</f>
+        <v>2026-07-20</v>
+      </c>
+      <c r="D7" s="43">
+        <f>Jurnale_NEUTRALIZARE!B14</f>
+        <v>331</v>
+      </c>
+      <c r="E7" s="43">
+        <f>Jurnale_NEUTRALIZARE!E14</f>
+        <v>711</v>
+      </c>
+      <c r="F7" s="43">
+        <f>Jurnale_NEUTRALIZARE!C14</f>
+        <v>4500</v>
+      </c>
+      <c r="G7" s="43" t="str">
+        <f>Jurnale_NEUTRALIZARE!D14</f>
+        <v>Stoc intermediar (PN/servicii/MF în curs) — 2026-07 — BUNURI — 711</v>
+      </c>
+      <c r="H7" s="43" t="inlineStr">
+        <is>
+          <t>Producție / neutralizare</t>
+        </is>
+      </c>
+      <c r="I7" s="43" t="str">
+        <f>IF(AND(ISNUMBER(F7),F7&gt;0),"DA","NU")</f>
+        <v>DA</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="43" t="n">
+        <v>4</v>
+      </c>
+      <c r="B8" s="43" t="inlineStr">
+        <is>
+          <t>B3 Finalizare</t>
+        </is>
+      </c>
+      <c r="C8" s="43" t="str">
+        <f>Declarații_NEUTRALIZARE!B9</f>
+        <v>2026-07-20</v>
+      </c>
+      <c r="D8" s="43">
+        <f>Jurnale_NEUTRALIZARE!B20</f>
+        <v>711</v>
+      </c>
+      <c r="E8" s="43">
+        <f>Jurnale_NEUTRALIZARE!E20</f>
+        <v>331</v>
+      </c>
+      <c r="F8" s="43">
+        <f>Jurnale_NEUTRALIZARE!C20</f>
+        <v>4500</v>
+      </c>
+      <c r="G8" s="43" t="str">
+        <f>Jurnale_NEUTRALIZARE!D20</f>
+        <v>Reluare PN (711 debitat #1) — 2026-07 — BUNURI — 711</v>
+      </c>
+      <c r="H8" s="43" t="inlineStr">
+        <is>
+          <t>Producție / neutralizare</t>
+        </is>
+      </c>
+      <c r="I8" s="43" t="str">
+        <f>IF(AND(ISNUMBER(F8),F8&gt;0),"DA","NU")</f>
+        <v>DA</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="43" t="n">
+        <v>5</v>
+      </c>
+      <c r="B9" s="43" t="inlineStr">
+        <is>
+          <t>B3 Finalizare</t>
+        </is>
+      </c>
+      <c r="C9" s="43" t="str">
+        <f>Declarații_NEUTRALIZARE!B9</f>
+        <v>2026-07-20</v>
+      </c>
+      <c r="D9" s="43">
+        <f>Jurnale_NEUTRALIZARE!B21</f>
+        <v>345</v>
+      </c>
+      <c r="E9" s="43">
+        <f>Jurnale_NEUTRALIZARE!E21</f>
+        <v>711</v>
+      </c>
+      <c r="F9" s="43">
+        <f>Jurnale_NEUTRALIZARE!C21</f>
+        <v>4500</v>
+      </c>
+      <c r="G9" s="43" t="str">
+        <f>Jurnale_NEUTRALIZARE!D21</f>
+        <v>Obținere produs finit (345=711) — 2026-07 — BUNURI — 711</v>
+      </c>
+      <c r="H9" s="43" t="inlineStr">
+        <is>
+          <t>Producție / neutralizare</t>
+        </is>
+      </c>
+      <c r="I9" s="43" t="str">
+        <f>IF(AND(ISNUMBER(F9),F9&gt;0),"DA","NU")</f>
+        <v>DA</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="43" t="n">
+        <v>6</v>
+      </c>
+      <c r="B10" s="43" t="inlineStr">
+        <is>
+          <t>B4 Vânzare</t>
+        </is>
+      </c>
+      <c r="C10" s="43" t="str">
+        <f>Declarații_NEUTRALIZARE!B10</f>
+        <v>2026-07-25</v>
+      </c>
+      <c r="D10" s="43" t="str">
+        <f>Jurnale_NEUTRALIZARE!B27</f>
+        <v>411.RO</v>
+      </c>
+      <c r="E10" s="43">
+        <f>Jurnale_NEUTRALIZARE!E27</f>
+        <v>701</v>
+      </c>
+      <c r="F10" s="43">
+        <f>Jurnale_NEUTRALIZARE!F27</f>
+        <v>7000</v>
+      </c>
+      <c r="G10" s="43" t="str">
+        <f>Jurnale_NEUTRALIZARE!D27</f>
+        <v>Creanță client — 2026-07 — BUNURI — 711</v>
+      </c>
+      <c r="H10" s="43" t="inlineStr">
+        <is>
+          <t>Producție / neutralizare</t>
+        </is>
+      </c>
+      <c r="I10" s="43" t="str">
+        <f>IF(AND(ISNUMBER(F10),F10&gt;0),"DA","NU")</f>
+        <v>DA</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="43" t="n">
+        <v>7</v>
+      </c>
+      <c r="B11" s="43" t="inlineStr">
+        <is>
+          <t>B4 TVA</t>
+        </is>
+      </c>
+      <c r="C11" s="43" t="str">
+        <f>Declarații_NEUTRALIZARE!B10</f>
+        <v>2026-07-25</v>
+      </c>
+      <c r="D11" s="43" t="str">
+        <f>Jurnale_NEUTRALIZARE!B27</f>
+        <v>411.RO</v>
+      </c>
+      <c r="E11" s="43" t="str">
+        <f>Jurnale_NEUTRALIZARE!E28</f>
+        <v>4427</v>
+      </c>
+      <c r="F11" s="43">
+        <f>Jurnale_NEUTRALIZARE!F28</f>
+        <v>1470</v>
+      </c>
+      <c r="G11" s="43" t="str">
+        <f>Jurnale_NEUTRALIZARE!G28</f>
+        <v>TVA colectată — 2026-07 — BUNURI — 711</v>
+      </c>
+      <c r="H11" s="43" t="inlineStr">
+        <is>
+          <t>Producție / neutralizare</t>
+        </is>
+      </c>
+      <c r="I11" s="43" t="str">
+        <f>IF(AND(ISNUMBER(F11),F11&gt;0),"DA","NU")</f>
+        <v>DA</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="43" t="n">
+        <v>8</v>
+      </c>
+      <c r="B12" s="43" t="inlineStr">
+        <is>
+          <t>B4 Descărcare</t>
+        </is>
+      </c>
+      <c r="C12" s="43" t="str">
+        <f>Declarații_NEUTRALIZARE!B10</f>
+        <v>2026-07-25</v>
+      </c>
+      <c r="D12" s="43">
+        <f>Jurnale_NEUTRALIZARE!B29</f>
+        <v>711</v>
+      </c>
+      <c r="E12" s="43">
+        <f>Jurnale_NEUTRALIZARE!E29</f>
+        <v>345</v>
+      </c>
+      <c r="F12" s="43">
+        <f>Jurnale_NEUTRALIZARE!C29</f>
+        <v>4500</v>
+      </c>
+      <c r="G12" s="43" t="str">
+        <f>Jurnale_NEUTRALIZARE!D29</f>
+        <v>Descărcare PF prin 711 (NU 607) — 2026-07 — BUNURI — 711</v>
+      </c>
+      <c r="H12" s="43" t="inlineStr">
+        <is>
+          <t>Producție / neutralizare</t>
+        </is>
+      </c>
+      <c r="I12" s="43" t="str">
+        <f>IF(AND(ISNUMBER(F12),F12&gt;0),"DA","NU")</f>
+        <v>DA</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="43" t="inlineStr">
+        <is>
+          <t>Rânduri de importat</t>
+        </is>
+      </c>
+      <c r="B14" s="43">
+        <f>COUNTIF(I5:I12,"DA")</f>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="43" t="inlineStr">
+        <is>
+          <t>Check global</t>
+        </is>
+      </c>
+      <c r="B15" s="43">
+        <f>Jurnale_NEUTRALIZARE!B32</f>
+        <v>0</v>
+      </c>
+      <c r="C15" s="43" t="str">
+        <f>IF(ABS(B15)&lt;0.01,"OK","EROARE")</f>
+        <v>OK</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet73.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B40"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="36" customWidth="1" style="40" min="1" max="1"/>
+    <col width="26" customWidth="1" style="40" min="2" max="2"/>
+    <col width="52" customWidth="1" style="40" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="41" t="inlineStr">
+        <is>
+          <t>MOD_VANZ_AMANUNT — Declarații (input)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="44" t="inlineStr">
+        <is>
+          <t>Gestiune amănunt la PVA. Corelații: 371×c/(100+c)=4428 și 707−607=rulaj D 378. Completează galben.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="42" t="inlineStr">
+        <is>
+          <t>1. Antet</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="43" t="inlineStr">
+        <is>
+          <t>Societate</t>
+        </is>
+      </c>
+      <c r="B5" s="43" t="str">
+        <f>Parametri!B5</f>
+        <v>SC EXEMPLU SRL</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="43" t="inlineStr">
+        <is>
+          <t>Gestiune (analitic)</t>
+        </is>
+      </c>
+      <c r="B6" s="64" t="inlineStr">
+        <is>
+          <t>AM.21</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="43" t="inlineStr">
+        <is>
+          <t>Luna</t>
+        </is>
+      </c>
+      <c r="B7" s="64" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="43" t="inlineStr">
+        <is>
+          <t>Data aprovizionare</t>
+        </is>
+      </c>
+      <c r="B8" s="64" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="43" t="inlineStr">
+        <is>
+          <t>Data vânzare (Z-report)</t>
+        </is>
+      </c>
+      <c r="B9" s="64" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="42" t="inlineStr">
+        <is>
+          <t>2. Aprovizionare</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="43" t="inlineStr">
+        <is>
+          <t>Cost (fără TVA)</t>
+        </is>
+      </c>
+      <c r="B12" s="64" t="n">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="43" t="inlineStr">
+        <is>
+          <t>Adaos %</t>
+        </is>
+      </c>
+      <c r="B13" s="64" t="n">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="43" t="inlineStr">
+        <is>
+          <t>Cotă TVA</t>
+        </is>
+      </c>
+      <c r="B14" s="64" t="n">
+        <v>0.21</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="43" t="inlineStr">
+        <is>
+          <t>Adaos (lei)</t>
+        </is>
+      </c>
+      <c r="B15" s="43">
+        <f>B12*B13</f>
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="43" t="inlineStr">
+        <is>
+          <t>Bază PVA (cost+adaos)</t>
+        </is>
+      </c>
+      <c r="B16" s="43">
+        <f>B12+B15</f>
+        <v>13000</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="43" t="inlineStr">
+        <is>
+          <t>TVA în PVA</t>
+        </is>
+      </c>
+      <c r="B17" s="43">
+        <f>B16*B14</f>
+        <v>2730</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="43" t="inlineStr">
+        <is>
+          <t>PVA total (371)</t>
+        </is>
+      </c>
+      <c r="B18" s="43">
+        <f>B16+B17</f>
+        <v>15730</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="43" t="inlineStr">
+        <is>
+          <t>TVA deductibilă (pe cost)</t>
+        </is>
+      </c>
+      <c r="B19" s="43">
+        <f>B12*B14</f>
+        <v>2100</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="42" t="inlineStr">
+        <is>
+          <t>3. Conturi</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="43" t="inlineStr">
+        <is>
+          <t>Cont stoc (371.gest.cotă)</t>
+        </is>
+      </c>
+      <c r="B22" s="64" t="inlineStr">
+        <is>
+          <t>371.AM.21</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="43" t="inlineStr">
+        <is>
+          <t>Cont adaos (378)</t>
+        </is>
+      </c>
+      <c r="B23" s="64" t="inlineStr">
+        <is>
+          <t>378.AM.21</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="43" t="inlineStr">
+        <is>
+          <t>Cont TVA neexigibilă (4428)</t>
+        </is>
+      </c>
+      <c r="B24" s="64" t="inlineStr">
+        <is>
+          <t>4428.AM</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="43" t="inlineStr">
+        <is>
+          <t>Cont furnizor</t>
+        </is>
+      </c>
+      <c r="B25" s="64" t="inlineStr">
+        <is>
+          <t>401.RO</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="43" t="inlineStr">
+        <is>
+          <t>Cont TVA deductibilă</t>
+        </is>
+      </c>
+      <c r="B26" s="64" t="inlineStr">
+        <is>
+          <t>4426</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="43" t="inlineStr">
+        <is>
+          <t>Cont cheltuială (607)</t>
+        </is>
+      </c>
+      <c r="B27" s="64" t="inlineStr">
+        <is>
+          <t>607</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="43" t="inlineStr">
+        <is>
+          <t>Cont venit (707)</t>
+        </is>
+      </c>
+      <c r="B28" s="64" t="inlineStr">
+        <is>
+          <t>707</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="43" t="inlineStr">
+        <is>
+          <t>Cont TVA colectată</t>
+        </is>
+      </c>
+      <c r="B29" s="64" t="inlineStr">
+        <is>
+          <t>4427</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="43" t="inlineStr">
+        <is>
+          <t>Cont casă / bancă</t>
+        </is>
+      </c>
+      <c r="B30" s="64" t="inlineStr">
+        <is>
+          <t>531.1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="43" t="inlineStr">
+        <is>
+          <t>Cont TVA de plată</t>
+        </is>
+      </c>
+      <c r="B31" s="64" t="inlineStr">
+        <is>
+          <t>4423</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="42" t="inlineStr">
+        <is>
+          <t>4. Corelații (auto)</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="43" t="inlineStr">
+        <is>
+          <t>Corelație 1: 371×c/(100+c) =?</t>
+        </is>
+      </c>
+      <c r="B34" s="43">
+        <f>B18*B14/(1+B14)</f>
+        <v>2730</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="43" t="inlineStr">
+        <is>
+          <t>Trebuie = 4428</t>
+        </is>
+      </c>
+      <c r="B35" s="43" t="str">
+        <f>IF(ABS(B34-B17)&lt;0.01,"OK — corelație 1 ține","EROARE")</f>
+        <v>OK — corelație 1 ține</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="43" t="inlineStr">
+        <is>
+          <t>Corelație 2: 707−607 =?</t>
+        </is>
+      </c>
+      <c r="B36" s="43">
+        <f>B16-B12</f>
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="43" t="inlineStr">
+        <is>
+          <t>Trebuie = adaos (rulaj D 378)</t>
+        </is>
+      </c>
+      <c r="B37" s="43" t="str">
+        <f>IF(ABS(B36-B15)&lt;0.01,"OK — corelație 2 ține","EROARE")</f>
+        <v>OK — corelație 2 ține</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="42" t="inlineStr">
+        <is>
+          <t>5. Sufix</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="43" t="inlineStr">
+        <is>
+          <t>Sufix</t>
+        </is>
+      </c>
+      <c r="B40" s="43" t="str">
+        <f>"— amănunt " &amp; B6 &amp; " — " &amp; B7</f>
+        <v>— amănunt AM.21 — 2026-07</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet74.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:F22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -31243,7 +32627,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet71.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet75.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -31907,7 +33291,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet72.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet76.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -32441,7 +33825,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet73.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet77.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -32844,7 +34228,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet74.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet78.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -33142,7 +34526,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet75.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet79.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -33681,383 +35065,6 @@
       <c r="C29" s="43" t="str">
         <f>IF(ABS(B29)&lt;0.01,"OK — luna se reconciliază pe toate corelațiile","EROARE — vezi foaia Abateri")</f>
         <v>OK — luna se reconciliază pe toate corelațiile</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet76.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:E18"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="10" customWidth="1" style="40" min="1" max="1"/>
-    <col width="12" customWidth="1" style="40" min="2" max="2"/>
-    <col width="46" customWidth="1" style="40" min="3" max="3"/>
-    <col width="16" customWidth="1" style="40" min="4" max="4"/>
-    <col width="56" customWidth="1" style="40" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="41" t="inlineStr">
-        <is>
-          <t>MOD_INCHIDERE_LUNARA — Abateri</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="44" t="inlineStr">
-        <is>
-          <t>Coloana „Include” spune DA doar unde corelația nu s-a potrivit. Lista e completă: dacă toate sunt NU, luna e curată.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="65" t="inlineStr">
-        <is>
-          <t>Include</t>
-        </is>
-      </c>
-      <c r="B4" s="65" t="inlineStr">
-        <is>
-          <t>Cod</t>
-        </is>
-      </c>
-      <c r="C4" s="65" t="inlineStr">
-        <is>
-          <t>Ce nu s-a potrivit</t>
-        </is>
-      </c>
-      <c r="D4" s="65" t="inlineStr">
-        <is>
-          <t>Diferență</t>
-        </is>
-      </c>
-      <c r="E4" s="65" t="inlineStr">
-        <is>
-          <t>Ce se face</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="43" t="str">
-        <f>IF(ABS(Verificări_INCHIDERE_LUNARA!E6)&lt;0.01,"NU","DA")</f>
-        <v>NU</v>
-      </c>
-      <c r="B5" s="43" t="inlineStr">
-        <is>
-          <t>C-25</t>
-        </is>
-      </c>
-      <c r="C5" s="43" t="inlineStr">
-        <is>
-          <t>444 Impozit pe venituri din salarii</t>
-        </is>
-      </c>
-      <c r="D5" s="43">
-        <f>Verificări_INCHIDERE_LUNARA!E6</f>
-        <v>0</v>
-      </c>
-      <c r="E5" s="43" t="inlineStr">
-        <is>
-          <t>Se verifică fișa de plătitor din SPV. Stopaj nevirat peste 30 de zile = răspundere penală, nu întârziere.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="43" t="str">
-        <f>IF(ABS(Verificări_INCHIDERE_LUNARA!E7)&lt;0.01,"NU","DA")</f>
-        <v>NU</v>
-      </c>
-      <c r="B6" s="43" t="inlineStr">
-        <is>
-          <t>C-26</t>
-        </is>
-      </c>
-      <c r="C6" s="43" t="inlineStr">
-        <is>
-          <t>4315 CAS — contribuția de asigurări sociale</t>
-        </is>
-      </c>
-      <c r="D6" s="43">
-        <f>Verificări_INCHIDERE_LUNARA!E7</f>
-        <v>0</v>
-      </c>
-      <c r="E6" s="43" t="inlineStr">
-        <is>
-          <t>Se confruntă cu D112. Dacă e eșalonare, se notează; altfel e restanță.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="43" t="str">
-        <f>IF(ABS(Verificări_INCHIDERE_LUNARA!E8)&lt;0.01,"NU","DA")</f>
-        <v>NU</v>
-      </c>
-      <c r="B7" s="43" t="inlineStr">
-        <is>
-          <t>C-26</t>
-        </is>
-      </c>
-      <c r="C7" s="43" t="inlineStr">
-        <is>
-          <t>4316 CASS — asigurări sociale de sănătate</t>
-        </is>
-      </c>
-      <c r="D7" s="43">
-        <f>Verificări_INCHIDERE_LUNARA!E8</f>
-        <v>0</v>
-      </c>
-      <c r="E7" s="43" t="inlineStr">
-        <is>
-          <t>Se confruntă cu D112. Dacă e eșalonare, se notează; altfel e restanță.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="43" t="str">
-        <f>IF(ABS(Verificări_INCHIDERE_LUNARA!E9)&lt;0.01,"NU","DA")</f>
-        <v>NU</v>
-      </c>
-      <c r="B8" s="43" t="inlineStr">
-        <is>
-          <t>C-26</t>
-        </is>
-      </c>
-      <c r="C8" s="43" t="inlineStr">
-        <is>
-          <t>436 CAM — contribuția asiguratorie pentru muncă</t>
-        </is>
-      </c>
-      <c r="D8" s="43">
-        <f>Verificări_INCHIDERE_LUNARA!E9</f>
-        <v>0</v>
-      </c>
-      <c r="E8" s="43" t="inlineStr">
-        <is>
-          <t>Se confruntă cu D112. Dacă e eșalonare, se notează; altfel e restanță.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="43" t="str">
-        <f>IF(ABS(Verificări_INCHIDERE_LUNARA!E10)&lt;0.01,"NU","DA")</f>
-        <v>NU</v>
-      </c>
-      <c r="B9" s="43" t="inlineStr">
-        <is>
-          <t>C-28</t>
-        </is>
-      </c>
-      <c r="C9" s="43" t="inlineStr">
-        <is>
-          <t>427 Rețineri din salarii datorate terților</t>
-        </is>
-      </c>
-      <c r="D9" s="43">
-        <f>Verificări_INCHIDERE_LUNARA!E10</f>
-        <v>0</v>
-      </c>
-      <c r="E9" s="43" t="inlineStr">
-        <is>
-          <t>Se virează imediat. Banii sunt ai salariatului, opriți pentru altcineva.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="43" t="str">
-        <f>IF(ABS(Verificări_INCHIDERE_LUNARA!E14)&lt;0.01,"NU","DA")</f>
-        <v>NU</v>
-      </c>
-      <c r="B10" s="43" t="inlineStr">
-        <is>
-          <t>C-24</t>
-        </is>
-      </c>
-      <c r="C10" s="43" t="inlineStr">
-        <is>
-          <t>421 + 423 vs. stat</t>
-        </is>
-      </c>
-      <c r="D10" s="43">
-        <f>Verificări_INCHIDERE_LUNARA!E14</f>
-        <v>0</v>
-      </c>
-      <c r="E10" s="43" t="inlineStr">
-        <is>
-          <t>Se scot statele lună de lună și se caută luna în care s-a rupt. Cauza tipică: plată pe alt cont decât 421.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="43" t="str">
-        <f>IF(ABS(Verificări_INCHIDERE_LUNARA!E18)&lt;0.01,"NU","DA")</f>
-        <v>NU</v>
-      </c>
-      <c r="B11" s="43" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C11" s="43" t="inlineStr">
-        <is>
-          <t>473 sold zero</t>
-        </is>
-      </c>
-      <c r="D11" s="43">
-        <f>Verificări_INCHIDERE_LUNARA!E18</f>
-        <v>0</v>
-      </c>
-      <c r="E11" s="43" t="inlineStr">
-        <is>
-          <t>Se identifică operațiunea neterminată și se închide. Un sold reportat pe un cont de tranzit ascunde ceva.</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="43" t="str">
-        <f>IF(ABS(Verificări_INCHIDERE_LUNARA!E19)&lt;0.01,"NU","DA")</f>
-        <v>NU</v>
-      </c>
-      <c r="B12" s="43" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C12" s="43" t="inlineStr">
-        <is>
-          <t>581 sold zero</t>
-        </is>
-      </c>
-      <c r="D12" s="43">
-        <f>Verificări_INCHIDERE_LUNARA!E19</f>
-        <v>0</v>
-      </c>
-      <c r="E12" s="43" t="inlineStr">
-        <is>
-          <t>Se identifică operațiunea neterminată și se închide. Un sold reportat pe un cont de tranzit ascunde ceva.</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="43" t="str">
-        <f>IF(ABS(Verificări_INCHIDERE_LUNARA!E20)&lt;0.01,"NU","DA")</f>
-        <v>NU</v>
-      </c>
-      <c r="B13" s="43" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C13" s="43" t="inlineStr">
-        <is>
-          <t>542 sold zero</t>
-        </is>
-      </c>
-      <c r="D13" s="43">
-        <f>Verificări_INCHIDERE_LUNARA!E20</f>
-        <v>0</v>
-      </c>
-      <c r="E13" s="43" t="inlineStr">
-        <is>
-          <t>Se identifică operațiunea neterminată și se închide. Un sold reportat pe un cont de tranzit ascunde ceva.</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="43" t="str">
-        <f>IF(ABS(Verificări_INCHIDERE_LUNARA!E21)&lt;0.01,"NU","DA")</f>
-        <v>NU</v>
-      </c>
-      <c r="B14" s="43" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C14" s="43" t="inlineStr">
-        <is>
-          <t>4382 sold zero</t>
-        </is>
-      </c>
-      <c r="D14" s="43">
-        <f>Verificări_INCHIDERE_LUNARA!E21</f>
-        <v>0</v>
-      </c>
-      <c r="E14" s="43" t="inlineStr">
-        <is>
-          <t>Se identifică operațiunea neterminată și se închide. Un sold reportat pe un cont de tranzit ascunde ceva.</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="43" t="str">
-        <f>IF(ABS(Verificări_INCHIDERE_LUNARA!E25)&lt;0.01,"NU","DA")</f>
-        <v>NU</v>
-      </c>
-      <c r="B15" s="43" t="inlineStr">
-        <is>
-          <t>C-27</t>
-        </is>
-      </c>
-      <c r="C15" s="43" t="inlineStr">
-        <is>
-          <t>CAM pe cifre</t>
-        </is>
-      </c>
-      <c r="D15" s="43">
-        <f>Verificări_INCHIDERE_LUNARA!E25</f>
-        <v>0</v>
-      </c>
-      <c r="E15" s="43" t="inlineStr">
-        <is>
-          <t>Se verifică dacă luna are concedii medicale — CAM nu se datorează pe partea din FNUASS. Altfel, bază de calcul incompletă.</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="43" t="str">
-        <f>IF(ABS(Verificări_INCHIDERE_LUNARA!E26)&lt;0.01,"NU","DA")</f>
-        <v>NU</v>
-      </c>
-      <c r="B16" s="43" t="inlineStr">
-        <is>
-          <t>C-29</t>
-        </is>
-      </c>
-      <c r="C16" s="43" t="inlineStr">
-        <is>
-          <t>4423 vs. decont</t>
-        </is>
-      </c>
-      <c r="D16" s="43">
-        <f>Verificări_INCHIDERE_LUNARA!E26</f>
-        <v>0</v>
-      </c>
-      <c r="E16" s="43" t="inlineStr">
-        <is>
-          <t>Se verifică dacă e sumă din decizie de impunere (analitic distinct) sau TVA neachitat din perioade precedente, omis din decont.</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="43" t="inlineStr">
-        <is>
-          <t>Check — număr de abateri</t>
-        </is>
-      </c>
-      <c r="B18" s="43">
-        <f>COUNTIF(A5:A16,"DA")</f>
-        <v>0</v>
-      </c>
-      <c r="C18" s="43" t="str">
-        <f>IF(B18=0,"OK — nicio abatere","ATENȚIE — "&amp;B18&amp;" corelații nu se potrivesc")</f>
-        <v>OK — nicio abatere</v>
       </c>
     </row>
   </sheetData>
@@ -34579,6 +35586,383 @@
       <c r="B54" s="43" t="str">
         <f>" - " &amp; B6 &amp; " - " &amp; B7</f>
         <v> - CR-2026-001 - 2026-07</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet80.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E18"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" style="40" min="1" max="1"/>
+    <col width="12" customWidth="1" style="40" min="2" max="2"/>
+    <col width="46" customWidth="1" style="40" min="3" max="3"/>
+    <col width="16" customWidth="1" style="40" min="4" max="4"/>
+    <col width="56" customWidth="1" style="40" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="41" t="inlineStr">
+        <is>
+          <t>MOD_INCHIDERE_LUNARA — Abateri</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="44" t="inlineStr">
+        <is>
+          <t>Coloana „Include” spune DA doar unde corelația nu s-a potrivit. Lista e completă: dacă toate sunt NU, luna e curată.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="65" t="inlineStr">
+        <is>
+          <t>Include</t>
+        </is>
+      </c>
+      <c r="B4" s="65" t="inlineStr">
+        <is>
+          <t>Cod</t>
+        </is>
+      </c>
+      <c r="C4" s="65" t="inlineStr">
+        <is>
+          <t>Ce nu s-a potrivit</t>
+        </is>
+      </c>
+      <c r="D4" s="65" t="inlineStr">
+        <is>
+          <t>Diferență</t>
+        </is>
+      </c>
+      <c r="E4" s="65" t="inlineStr">
+        <is>
+          <t>Ce se face</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="43" t="str">
+        <f>IF(ABS(Verificări_INCHIDERE_LUNARA!E6)&lt;0.01,"NU","DA")</f>
+        <v>NU</v>
+      </c>
+      <c r="B5" s="43" t="inlineStr">
+        <is>
+          <t>C-25</t>
+        </is>
+      </c>
+      <c r="C5" s="43" t="inlineStr">
+        <is>
+          <t>444 Impozit pe venituri din salarii</t>
+        </is>
+      </c>
+      <c r="D5" s="43">
+        <f>Verificări_INCHIDERE_LUNARA!E6</f>
+        <v>0</v>
+      </c>
+      <c r="E5" s="43" t="inlineStr">
+        <is>
+          <t>Se verifică fișa de plătitor din SPV. Stopaj nevirat peste 30 de zile = răspundere penală, nu întârziere.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="43" t="str">
+        <f>IF(ABS(Verificări_INCHIDERE_LUNARA!E7)&lt;0.01,"NU","DA")</f>
+        <v>NU</v>
+      </c>
+      <c r="B6" s="43" t="inlineStr">
+        <is>
+          <t>C-26</t>
+        </is>
+      </c>
+      <c r="C6" s="43" t="inlineStr">
+        <is>
+          <t>4315 CAS — contribuția de asigurări sociale</t>
+        </is>
+      </c>
+      <c r="D6" s="43">
+        <f>Verificări_INCHIDERE_LUNARA!E7</f>
+        <v>0</v>
+      </c>
+      <c r="E6" s="43" t="inlineStr">
+        <is>
+          <t>Se confruntă cu D112. Dacă e eșalonare, se notează; altfel e restanță.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="43" t="str">
+        <f>IF(ABS(Verificări_INCHIDERE_LUNARA!E8)&lt;0.01,"NU","DA")</f>
+        <v>NU</v>
+      </c>
+      <c r="B7" s="43" t="inlineStr">
+        <is>
+          <t>C-26</t>
+        </is>
+      </c>
+      <c r="C7" s="43" t="inlineStr">
+        <is>
+          <t>4316 CASS — asigurări sociale de sănătate</t>
+        </is>
+      </c>
+      <c r="D7" s="43">
+        <f>Verificări_INCHIDERE_LUNARA!E8</f>
+        <v>0</v>
+      </c>
+      <c r="E7" s="43" t="inlineStr">
+        <is>
+          <t>Se confruntă cu D112. Dacă e eșalonare, se notează; altfel e restanță.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="43" t="str">
+        <f>IF(ABS(Verificări_INCHIDERE_LUNARA!E9)&lt;0.01,"NU","DA")</f>
+        <v>NU</v>
+      </c>
+      <c r="B8" s="43" t="inlineStr">
+        <is>
+          <t>C-26</t>
+        </is>
+      </c>
+      <c r="C8" s="43" t="inlineStr">
+        <is>
+          <t>436 CAM — contribuția asiguratorie pentru muncă</t>
+        </is>
+      </c>
+      <c r="D8" s="43">
+        <f>Verificări_INCHIDERE_LUNARA!E9</f>
+        <v>0</v>
+      </c>
+      <c r="E8" s="43" t="inlineStr">
+        <is>
+          <t>Se confruntă cu D112. Dacă e eșalonare, se notează; altfel e restanță.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="43" t="str">
+        <f>IF(ABS(Verificări_INCHIDERE_LUNARA!E10)&lt;0.01,"NU","DA")</f>
+        <v>NU</v>
+      </c>
+      <c r="B9" s="43" t="inlineStr">
+        <is>
+          <t>C-28</t>
+        </is>
+      </c>
+      <c r="C9" s="43" t="inlineStr">
+        <is>
+          <t>427 Rețineri din salarii datorate terților</t>
+        </is>
+      </c>
+      <c r="D9" s="43">
+        <f>Verificări_INCHIDERE_LUNARA!E10</f>
+        <v>0</v>
+      </c>
+      <c r="E9" s="43" t="inlineStr">
+        <is>
+          <t>Se virează imediat. Banii sunt ai salariatului, opriți pentru altcineva.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="43" t="str">
+        <f>IF(ABS(Verificări_INCHIDERE_LUNARA!E14)&lt;0.01,"NU","DA")</f>
+        <v>NU</v>
+      </c>
+      <c r="B10" s="43" t="inlineStr">
+        <is>
+          <t>C-24</t>
+        </is>
+      </c>
+      <c r="C10" s="43" t="inlineStr">
+        <is>
+          <t>421 + 423 vs. stat</t>
+        </is>
+      </c>
+      <c r="D10" s="43">
+        <f>Verificări_INCHIDERE_LUNARA!E14</f>
+        <v>0</v>
+      </c>
+      <c r="E10" s="43" t="inlineStr">
+        <is>
+          <t>Se scot statele lună de lună și se caută luna în care s-a rupt. Cauza tipică: plată pe alt cont decât 421.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="43" t="str">
+        <f>IF(ABS(Verificări_INCHIDERE_LUNARA!E18)&lt;0.01,"NU","DA")</f>
+        <v>NU</v>
+      </c>
+      <c r="B11" s="43" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C11" s="43" t="inlineStr">
+        <is>
+          <t>473 sold zero</t>
+        </is>
+      </c>
+      <c r="D11" s="43">
+        <f>Verificări_INCHIDERE_LUNARA!E18</f>
+        <v>0</v>
+      </c>
+      <c r="E11" s="43" t="inlineStr">
+        <is>
+          <t>Se identifică operațiunea neterminată și se închide. Un sold reportat pe un cont de tranzit ascunde ceva.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="43" t="str">
+        <f>IF(ABS(Verificări_INCHIDERE_LUNARA!E19)&lt;0.01,"NU","DA")</f>
+        <v>NU</v>
+      </c>
+      <c r="B12" s="43" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C12" s="43" t="inlineStr">
+        <is>
+          <t>581 sold zero</t>
+        </is>
+      </c>
+      <c r="D12" s="43">
+        <f>Verificări_INCHIDERE_LUNARA!E19</f>
+        <v>0</v>
+      </c>
+      <c r="E12" s="43" t="inlineStr">
+        <is>
+          <t>Se identifică operațiunea neterminată și se închide. Un sold reportat pe un cont de tranzit ascunde ceva.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="43" t="str">
+        <f>IF(ABS(Verificări_INCHIDERE_LUNARA!E20)&lt;0.01,"NU","DA")</f>
+        <v>NU</v>
+      </c>
+      <c r="B13" s="43" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C13" s="43" t="inlineStr">
+        <is>
+          <t>542 sold zero</t>
+        </is>
+      </c>
+      <c r="D13" s="43">
+        <f>Verificări_INCHIDERE_LUNARA!E20</f>
+        <v>0</v>
+      </c>
+      <c r="E13" s="43" t="inlineStr">
+        <is>
+          <t>Se identifică operațiunea neterminată și se închide. Un sold reportat pe un cont de tranzit ascunde ceva.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="43" t="str">
+        <f>IF(ABS(Verificări_INCHIDERE_LUNARA!E21)&lt;0.01,"NU","DA")</f>
+        <v>NU</v>
+      </c>
+      <c r="B14" s="43" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C14" s="43" t="inlineStr">
+        <is>
+          <t>4382 sold zero</t>
+        </is>
+      </c>
+      <c r="D14" s="43">
+        <f>Verificări_INCHIDERE_LUNARA!E21</f>
+        <v>0</v>
+      </c>
+      <c r="E14" s="43" t="inlineStr">
+        <is>
+          <t>Se identifică operațiunea neterminată și se închide. Un sold reportat pe un cont de tranzit ascunde ceva.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="43" t="str">
+        <f>IF(ABS(Verificări_INCHIDERE_LUNARA!E25)&lt;0.01,"NU","DA")</f>
+        <v>NU</v>
+      </c>
+      <c r="B15" s="43" t="inlineStr">
+        <is>
+          <t>C-27</t>
+        </is>
+      </c>
+      <c r="C15" s="43" t="inlineStr">
+        <is>
+          <t>CAM pe cifre</t>
+        </is>
+      </c>
+      <c r="D15" s="43">
+        <f>Verificări_INCHIDERE_LUNARA!E25</f>
+        <v>0</v>
+      </c>
+      <c r="E15" s="43" t="inlineStr">
+        <is>
+          <t>Se verifică dacă luna are concedii medicale — CAM nu se datorează pe partea din FNUASS. Altfel, bază de calcul incompletă.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="43" t="str">
+        <f>IF(ABS(Verificări_INCHIDERE_LUNARA!E26)&lt;0.01,"NU","DA")</f>
+        <v>NU</v>
+      </c>
+      <c r="B16" s="43" t="inlineStr">
+        <is>
+          <t>C-29</t>
+        </is>
+      </c>
+      <c r="C16" s="43" t="inlineStr">
+        <is>
+          <t>4423 vs. decont</t>
+        </is>
+      </c>
+      <c r="D16" s="43">
+        <f>Verificări_INCHIDERE_LUNARA!E26</f>
+        <v>0</v>
+      </c>
+      <c r="E16" s="43" t="inlineStr">
+        <is>
+          <t>Se verifică dacă e sumă din decizie de impunere (analitic distinct) sau TVA neachitat din perioade precedente, omis din decont.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="43" t="inlineStr">
+        <is>
+          <t>Check — număr de abateri</t>
+        </is>
+      </c>
+      <c r="B18" s="43">
+        <f>COUNTIF(A5:A16,"DA")</f>
+        <v>0</v>
+      </c>
+      <c r="C18" s="43" t="str">
+        <f>IF(B18=0,"OK — nicio abatere","ATENȚIE — "&amp;B18&amp;" corelații nu se potrivesc")</f>
+        <v>OK — nicio abatere</v>
       </c>
     </row>
   </sheetData>

--- a/dist/Module_Declarative_Fluxuri.xlsx
+++ b/dist/Module_Declarative_Fluxuri.xlsx
@@ -75,18 +75,22 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reguli_TAXARE_INVERSA" sheetId="66" state="visible" r:id="rId66"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Jurnale_TAXARE_INVERSA" sheetId="67" state="visible" r:id="rId67"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NotaExport_TAXARE_INVERSA" sheetId="68" state="visible" r:id="rId68"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Declarații_NEUTRALIZARE" sheetId="69" state="visible" r:id="rId69"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reguli_NEUTRALIZARE" sheetId="70" state="visible" r:id="rId70"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Jurnale_NEUTRALIZARE" sheetId="71" state="visible" r:id="rId71"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NotaExport_NEUTRALIZARE" sheetId="72" state="visible" r:id="rId72"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Declarații_AMANUNT" sheetId="73" state="visible" r:id="rId73"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reguli_AMANUNT" sheetId="74" state="visible" r:id="rId74"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Jurnale_AMANUNT" sheetId="75" state="visible" r:id="rId75"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NotaExport_AMANUNT" sheetId="76" state="visible" r:id="rId76"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Declarații_INCHIDERE_LUNARA" sheetId="77" state="visible" r:id="rId77"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reguli_INCHIDERE_LUNARA" sheetId="78" state="visible" r:id="rId78"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Verificări_INCHIDERE_LUNARA" sheetId="79" state="visible" r:id="rId79"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Abateri_INCHIDERE_LUNARA" sheetId="80" state="visible" r:id="rId80"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Declarații_FARA_DOCUMENT" sheetId="69" state="visible" r:id="rId69"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reguli_FARA_DOCUMENT" sheetId="70" state="visible" r:id="rId70"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Jurnale_FARA_DOCUMENT" sheetId="71" state="visible" r:id="rId71"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NotaExport_FARA_DOCUMENT" sheetId="72" state="visible" r:id="rId72"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Declarații_NEUTRALIZARE" sheetId="73" state="visible" r:id="rId73"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reguli_NEUTRALIZARE" sheetId="74" state="visible" r:id="rId74"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Jurnale_NEUTRALIZARE" sheetId="75" state="visible" r:id="rId75"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NotaExport_NEUTRALIZARE" sheetId="76" state="visible" r:id="rId76"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Declarații_AMANUNT" sheetId="77" state="visible" r:id="rId77"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reguli_AMANUNT" sheetId="78" state="visible" r:id="rId78"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Jurnale_AMANUNT" sheetId="79" state="visible" r:id="rId79"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NotaExport_AMANUNT" sheetId="80" state="visible" r:id="rId80"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Declarații_INCHIDERE_LUNARA" sheetId="81" state="visible" r:id="rId81"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reguli_INCHIDERE_LUNARA" sheetId="82" state="visible" r:id="rId82"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Verificări_INCHIDERE_LUNARA" sheetId="83" state="visible" r:id="rId83"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Abateri_INCHIDERE_LUNARA" sheetId="84" state="visible" r:id="rId84"/>
   </sheets>
   <definedNames>
     <definedName name="param_proc_rezerva">Parametri!$B$18</definedName>
@@ -832,7 +836,7 @@
     <row r="4" ht="15" customHeight="1" s="40">
       <c r="A4" s="43" t="inlineStr">
         <is>
-          <t>Cele 19 module declarative care execută fluxurile din „Plan de conturi”. Fluxul explică de ce; modulul face înregistrarea. Completezi câteva variabile într-o foaie de input și ies jurnalele și nota de export.</t>
+          <t>Cele 20 module declarative care execută fluxurile din „Plan de conturi”. Fluxul explică de ce; modulul face înregistrarea. Completezi câteva variabile într-o foaie de input și ies jurnalele și nota de export.</t>
         </is>
       </c>
     </row>
@@ -10955,7 +10959,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:H32"/>
+  <dimension ref="A1:H33"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="8" customWidth="1" style="39" min="1" max="1"/>
@@ -11788,84 +11792,126 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="62" t="inlineStr">
+      <c r="A25" s="60" t="inlineStr">
+        <is>
+          <t>NU</t>
+        </is>
+      </c>
+      <c r="B25" s="61" t="inlineStr">
+        <is>
+          <t>MOD_FARA_DOCUMENT</t>
+        </is>
+      </c>
+      <c r="C25" s="61" t="inlineStr">
+        <is>
+          <t>F-406</t>
+        </is>
+      </c>
+      <c r="D25" s="61" t="inlineStr">
+        <is>
+          <t>Pe eveniment</t>
+        </is>
+      </c>
+      <c r="E25" s="61" t="inlineStr">
+        <is>
+          <t>Valoare factură și cota, pentru vehicul; costul lipsei la inventar</t>
+        </is>
+      </c>
+      <c r="F25" s="61" t="inlineStr">
+        <is>
+          <t>Procentul de deducere vine din param_proc_vehicul; 4427 se creditează la lipsă</t>
+        </is>
+      </c>
+      <c r="G25" s="61" t="inlineStr">
+        <is>
+          <t>A Vehicul cu regim mixt (50%); B Lipsă la inventar nejustificată</t>
+        </is>
+      </c>
+      <c r="H25" s="61" t="inlineStr">
+        <is>
+          <t>IMPLEMENTAT</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="62" t="inlineStr">
         <is>
           <t>DA</t>
         </is>
       </c>
-      <c r="B25" s="61" t="inlineStr">
+      <c r="B26" s="61" t="inlineStr">
         <is>
           <t>MOD_INCHIDERE_LUNARA</t>
         </is>
       </c>
-      <c r="C25" s="61" t="inlineStr">
+      <c r="C26" s="61" t="inlineStr">
         <is>
           <t>F-422, F-413</t>
         </is>
       </c>
-      <c r="D25" s="61" t="inlineStr">
+      <c r="D26" s="61" t="inlineStr">
         <is>
           <t>Lunar, pe balanța de verificare</t>
         </is>
       </c>
-      <c r="E25" s="61" t="inlineStr">
+      <c r="E26" s="61" t="inlineStr">
         <is>
           <t>Rulaj debitor, rulaj creditor și sold pentru conturile cu cadență; restul de plată de pe stat; soldul din decontul de TVA</t>
         </is>
       </c>
-      <c r="F25" s="61" t="inlineStr">
+      <c r="F26" s="61" t="inlineStr">
         <is>
           <t>Verifică solduri, nu documente — vezi Reguli, tabelul C</t>
         </is>
       </c>
-      <c r="G25" s="61" t="inlineStr">
+      <c r="G26" s="61" t="inlineStr">
         <is>
           <t>V1 Obligații lunare (rulaj = sold); V2 Datoria față de salariați; V3 Conturi care trebuie golite; V4 Verificarea CAM pe cifre</t>
         </is>
       </c>
-      <c r="H25" s="61" t="inlineStr">
+      <c r="H26" s="61" t="inlineStr">
         <is>
           <t>IMPLEMENTAT</t>
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="63" t="inlineStr">
+    <row r="28">
+      <c r="A28" s="63" t="inlineStr">
         <is>
           <t>REGULĂ DE SUMONARE</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="46" t="inlineStr">
-        <is>
-          <t>1. În CatalogModule setezi Activ=DA doar pe modulele necesare lunii.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="46" t="inlineStr">
         <is>
-          <t>2. Completezi variabilele din foaia Declarații_Modul (galben).</t>
+          <t>1. În CatalogModule setezi Activ=DA doar pe modulele necesare lunii.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="46" t="inlineStr">
         <is>
-          <t>3. Jurnalele și NotaExport se populează automat doar pentru modulele active.</t>
+          <t>2. Completezi variabilele din foaia Declarații_Modul (galben).</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="46" t="inlineStr">
         <is>
-          <t>4. Verifici Check=0 pe fiecare bloc; filtrezi NotaExport pe Include=DA și imporți.</t>
+          <t>3. Jurnalele și NotaExport se populează automat doar pentru modulele active.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="46" t="inlineStr">
+        <is>
+          <t>4. Verifici Check=0 pe fiecare bloc; filtrezi NotaExport pe Include=DA și imporți.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="46" t="inlineStr">
         <is>
           <t>Nu se creează conturi noi din modul — se folosesc doar conturile din politica declarată + planul de conturi pe rol.</t>
         </is>
@@ -11878,9 +11924,9 @@
     <mergeCell ref="A29:H29"/>
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="A28:H28"/>
+    <mergeCell ref="A33:H33"/>
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="A32:H32"/>
-    <mergeCell ref="A27:H27"/>
     <mergeCell ref="A31:H31"/>
   </mergeCells>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
@@ -29860,25 +29906,25 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B41"/>
+  <dimension ref="A1:C42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="40" customWidth="1" style="40" min="1" max="1"/>
-    <col width="42" customWidth="1" style="40" min="2" max="2"/>
-    <col width="52" customWidth="1" style="40" min="3" max="3"/>
+    <col width="50" customWidth="1" style="40" min="1" max="1"/>
+    <col width="22" customWidth="1" style="40" min="2" max="2"/>
+    <col width="58" customWidth="1" style="40" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="41" t="inlineStr">
         <is>
-          <t>MOD_NEUTRALIZARE — Declarații (input)</t>
+          <t>MOD_FARA_DOCUMENT — Declarații (input)</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="44" t="inlineStr">
         <is>
-          <t>Acoperă F-311 (bunuri/711), F-312 (servicii/712), F-209 (imobilizări/722). Alege tipul — conturile și lanțul se adaptează. Principiu: costurile lovesc cls.6, apoi contul de venit de producție capitalizează și neutralizează.</t>
+          <t>Două cazuri independente. Pune DA pe cel care s-a întâmplat — de obicei primul se aplică lunar, al doilea doar după inventar.</t>
         </is>
       </c>
     </row>
@@ -29914,7 +29960,7 @@
     <row r="7">
       <c r="A7" s="43" t="inlineStr">
         <is>
-          <t>Luna / proiect</t>
+          <t>Luna (AAAA-LL)</t>
         </is>
       </c>
       <c r="B7" s="64" t="inlineStr">
@@ -29926,234 +29972,270 @@
     <row r="8">
       <c r="A8" s="43" t="inlineStr">
         <is>
-          <t>Data costuri (B1)</t>
+          <t>Data jurnal</t>
         </is>
       </c>
       <c r="B8" s="64" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-31</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="43" t="inlineStr">
         <is>
-          <t>Data finalizare stoc (B2-B3)</t>
-        </is>
-      </c>
-      <c r="B9" s="64" t="inlineStr">
-        <is>
-          <t>2026-07-20</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="43" t="inlineStr">
-        <is>
-          <t>Data vânzare / recepție MF (B4)</t>
-        </is>
-      </c>
-      <c r="B10" s="64" t="inlineStr">
-        <is>
-          <t>2026-07-25</t>
+          <t>Cota TVA</t>
+        </is>
+      </c>
+      <c r="B9" s="64" t="n">
+        <v>0.21</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="42" t="inlineStr">
+        <is>
+          <t>2. Cazul A — Vehicul cu regim mixt (deducere 50%)</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="42" t="inlineStr">
-        <is>
-          <t>2. Tip producție (poartă principală)</t>
+      <c r="A12" s="43" t="inlineStr">
+        <is>
+          <t>Se aplică? (DA/NU)</t>
+        </is>
+      </c>
+      <c r="B12" s="64" t="inlineStr">
+        <is>
+          <t>DA</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="43" t="inlineStr">
         <is>
-          <t>Tip (BUNURI / SERVICII / MF)</t>
+          <t>Regim (MIXT / EXCLUSIV / EXCEPTAT)</t>
         </is>
       </c>
       <c r="B13" s="64" t="inlineStr">
         <is>
-          <t>BUNURI</t>
+          <t>MIXT</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="43" t="inlineStr">
         <is>
-          <t>Cont venit neutralizare (auto)</t>
-        </is>
-      </c>
-      <c r="B14" s="43">
-        <f>IF(B13="BUNURI",711,IF(B13="SERVICII",712,IF(B13="MF",722,"?")))</f>
-        <v>711</v>
+          <t>Valoare factură fără TVA</t>
+        </is>
+      </c>
+      <c r="B14" s="64" t="n">
+        <v>1000</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="43" t="inlineStr">
         <is>
-          <t>Cont stoc intermediar (auto)</t>
+          <t>TVA de pe factură (auto)</t>
         </is>
       </c>
       <c r="B15" s="43">
-        <f>IF(B13="BUNURI",331,IF(B13="SERVICII",332,IF(B13="MF",231,"?")))</f>
-        <v>331</v>
+        <f>ROUND(B14*B9,2)</f>
+        <v>210</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="43" t="inlineStr">
         <is>
-          <t>Cont stoc final (auto)</t>
+          <t>Procent de deducere (auto)</t>
         </is>
       </c>
       <c r="B16" s="43">
-        <f>IF(B13="BUNURI",345,IF(B13="SERVICII","(nu e cazul — se stinge la livrare)",IF(B13="MF",213,"?")))</f>
-        <v>345</v>
+        <f>IF(B13="MIXT",param_proc_vehicul,1)</f>
+        <v>0.5</v>
+      </c>
+      <c r="C16" s="44" t="inlineStr">
+        <is>
+          <t>La MIXT vine din param_proc_vehicul; la EXCLUSIV și EXCEPTAT se deduce integral</t>
+        </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="43" t="inlineStr">
         <is>
-          <t>Cont venit vânzare (auto)</t>
+          <t>TVA deductibilă (auto)</t>
         </is>
       </c>
       <c r="B17" s="43">
-        <f>IF(B13="BUNURI",701,IF(B13="SERVICII",704,IF(B13="MF","(nu e vânzare — e activ)","?")))</f>
-        <v>701</v>
+        <f>ROUND(B15*B16,2)</f>
+        <v>105</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="43" t="inlineStr">
+        <is>
+          <t>TVA nedeductibilă (auto)</t>
+        </is>
+      </c>
+      <c r="B18" s="43">
+        <f>B15-B17</f>
+        <v>105</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="42" t="inlineStr">
-        <is>
-          <t>3. Costuri (cls.6)</t>
+      <c r="A19" s="43" t="inlineStr">
+        <is>
+          <t>Cheltuială = net + TVA nedeductibilă (auto)</t>
+        </is>
+      </c>
+      <c r="B19" s="43">
+        <f>B14+B18</f>
+        <v>1105</v>
+      </c>
+      <c r="C19" s="44" t="inlineStr">
+        <is>
+          <t>TVA nedeductibilă NU se pierde: se incorporează în cheltuială</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="43" t="inlineStr">
         <is>
-          <t>Cost materiale (→ 601)</t>
-        </is>
-      </c>
-      <c r="B20" s="64" t="n">
-        <v>4500</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="43" t="inlineStr">
-        <is>
-          <t>Cost manoperă (→ 641)</t>
-        </is>
-      </c>
-      <c r="B21" s="64" t="n">
-        <v>0</v>
+          <t>Total factură (auto)</t>
+        </is>
+      </c>
+      <c r="B20" s="43">
+        <f>B14+B15</f>
+        <v>1210</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="43" t="inlineStr">
-        <is>
-          <t>Alte costuri (→ 6xx)</t>
-        </is>
-      </c>
-      <c r="B22" s="64" t="n">
-        <v>0</v>
+      <c r="A22" s="42" t="inlineStr">
+        <is>
+          <t>3. Cazul B — Lipsă la inventar</t>
+        </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="43" t="inlineStr">
         <is>
-          <t>Cost total</t>
-        </is>
-      </c>
-      <c r="B23" s="43">
-        <f>B20+B21+B22</f>
-        <v>4500</v>
+          <t>Se aplică? (DA/NU)</t>
+        </is>
+      </c>
+      <c r="B23" s="64" t="inlineStr">
+        <is>
+          <t>DA</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="43" t="inlineStr">
+        <is>
+          <t>Lipsa e JUSTIFICATĂ? (DA/NU)</t>
+        </is>
+      </c>
+      <c r="B24" s="64" t="inlineStr">
+        <is>
+          <t>NU</t>
+        </is>
+      </c>
+      <c r="C24" s="44" t="inlineStr">
+        <is>
+          <t>Calamitate, perisabilități în limita legală, casare documentată. Nejustificată = se colectează TVA</t>
+        </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="42" t="inlineStr">
-        <is>
-          <t>4. Vânzare (doar BUNURI / SERVICII)</t>
-        </is>
+      <c r="A25" s="43" t="inlineStr">
+        <is>
+          <t>Costul bunului lipsă</t>
+        </is>
+      </c>
+      <c r="B25" s="64" t="n">
+        <v>1200</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="43" t="inlineStr">
         <is>
-          <t>Preț vânzare (fără TVA)</t>
-        </is>
-      </c>
-      <c r="B26" s="64" t="n">
-        <v>7000</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="43" t="inlineStr">
-        <is>
-          <t>Cota TVA</t>
-        </is>
-      </c>
-      <c r="B27" s="64" t="n">
-        <v>0.21</v>
+          <t>TVA de colectat (auto)</t>
+        </is>
+      </c>
+      <c r="B26" s="43">
+        <f>IF(B24="DA",0,ROUND(B25*B9,2))</f>
+        <v>252</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="43" t="inlineStr">
-        <is>
-          <t>TVA</t>
-        </is>
-      </c>
-      <c r="B28" s="43">
-        <f>IF(OR(B13="BUNURI",B13="SERVICII"),B26*B27,0)</f>
-        <v>1470</v>
+      <c r="A28" s="42" t="inlineStr">
+        <is>
+          <t>4. Conturi</t>
+        </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="43" t="inlineStr">
         <is>
-          <t>Total factură</t>
-        </is>
-      </c>
-      <c r="B29" s="43">
-        <f>B26+B28</f>
-        <v>8470</v>
+          <t>Cheltuială cu serviciile (628)</t>
+        </is>
+      </c>
+      <c r="B29" s="64" t="inlineStr">
+        <is>
+          <t>628</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="43" t="inlineStr">
+        <is>
+          <t>Alte cheltuieli de exploatare (658)</t>
+        </is>
+      </c>
+      <c r="B30" s="64" t="inlineStr">
+        <is>
+          <t>658</t>
+        </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="42" t="inlineStr">
-        <is>
-          <t>5. Conturi suplimentare</t>
+      <c r="A31" s="43" t="inlineStr">
+        <is>
+          <t>Furnizor</t>
+        </is>
+      </c>
+      <c r="B31" s="64" t="inlineStr">
+        <is>
+          <t>401</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="43" t="inlineStr">
         <is>
-          <t>Cont materii prime</t>
+          <t>Cont stoc</t>
         </is>
       </c>
       <c r="B32" s="64" t="inlineStr">
         <is>
-          <t>301</t>
+          <t>371</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="43" t="inlineStr">
         <is>
-          <t>Cont client</t>
+          <t>TVA deductibilă</t>
         </is>
       </c>
       <c r="B33" s="64" t="inlineStr">
         <is>
-          <t>411.RO</t>
+          <t>4426</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="43" t="inlineStr">
         <is>
-          <t>Cont TVA colectată</t>
+          <t>TVA colectată</t>
         </is>
       </c>
       <c r="B34" s="64" t="inlineStr">
@@ -30165,7 +30247,7 @@
     <row r="36">
       <c r="A36" s="42" t="inlineStr">
         <is>
-          <t>6. Sufix</t>
+          <t>5. Sufix</t>
         </is>
       </c>
     </row>
@@ -30176,38 +30258,48 @@
         </is>
       </c>
       <c r="B37" s="43" t="str">
-        <f>"— " &amp; B7 &amp; " — " &amp; B13 &amp; " — " &amp; B14</f>
-        <v>— 2026-07 — BUNURI — 711</v>
+        <f>"— fără document " &amp; B7</f>
+        <v>— fără document 2026-07</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="42" t="inlineStr">
         <is>
-          <t>7. Control</t>
+          <t>6. Control</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="43" t="inlineStr">
         <is>
-          <t>Marjă (vânzare − cost)</t>
-        </is>
-      </c>
-      <c r="B40" s="43">
-        <f>IF(OR(B13="BUNURI",B13="SERVICII"),B26-B23,"n/a (MF)")</f>
-        <v>2500</v>
+          <t>Modul activ?</t>
+        </is>
+      </c>
+      <c r="B40" s="43" t="str">
+        <f>IF(INDEX(CatalogModule!$A$1:$A$200,MATCH("MOD_FARA_DOCUMENT",CatalogModule!$B$1:$B$200,0))="DA","ACTIV","INACTIV")</f>
+        <v>INACTIV</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="43" t="inlineStr">
         <is>
-          <t>Notă principiu</t>
-        </is>
-      </c>
-      <c r="B41" s="43" t="inlineStr">
-        <is>
-          <t>Costurile lovesc cls.6; contul de venit de producție (711/712/722) capitalizează și neutralizează. Descărcarea la vânzare (bunuri) e prin 711=345, nu prin 607.</t>
-        </is>
+          <t>Verificare: cheltuială + TVA dedusă = total factură</t>
+        </is>
+      </c>
+      <c r="B41" s="43" t="str">
+        <f>IF(OR(B12&lt;&gt;"DA",ABS((B19+B17)-B20)&lt;0.01),"OK — TVA nedeductibilă e în cheltuială, nimic nu se pierde","EROARE — nota nu acoperă totalul facturii")</f>
+        <v>OK — TVA nedeductibilă e în cheltuială, nimic nu se pierde</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="43" t="inlineStr">
+        <is>
+          <t>Regula de sens la lipsă</t>
+        </is>
+      </c>
+      <c r="B42" s="43" t="str">
+        <f>IF(AND(B23="DA",B24&lt;&gt;"DA"),"4427 se CREDITEAZĂ — colectezi, nu storna deducerea","—")</f>
+        <v>4427 se CREDITEAZĂ — colectezi, nu storna deducerea</v>
       </c>
     </row>
   </sheetData>
@@ -30606,6 +30698,1191 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:D21"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="54" customWidth="1" style="40" min="1" max="1"/>
+    <col width="32" customWidth="1" style="40" min="2" max="2"/>
+    <col width="44" customWidth="1" style="40" min="3" max="3"/>
+    <col width="52" customWidth="1" style="40" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="41" t="inlineStr">
+        <is>
+          <t>MOD_FARA_DOCUMENT — Reguli (tabele fixe)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="44" t="inlineStr">
+        <is>
+          <t>Regula e dată, nu formulă. Se editează doar când se schimbă legea.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="42" t="inlineStr">
+        <is>
+          <t>Tabel A — Regimuri și tratamente</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="65" t="inlineStr">
+        <is>
+          <t>Caz</t>
+        </is>
+      </c>
+      <c r="B5" s="65" t="inlineStr">
+        <is>
+          <t>TVA</t>
+        </is>
+      </c>
+      <c r="C5" s="65" t="inlineStr">
+        <is>
+          <t>Partea nedeductibilă</t>
+        </is>
+      </c>
+      <c r="D5" s="65" t="inlineStr">
+        <is>
+          <t>Temei / condiție</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="43" t="inlineStr">
+        <is>
+          <t>Vehicul cu regim MIXT (personal + business)</t>
+        </is>
+      </c>
+      <c r="B6" s="43" t="inlineStr">
+        <is>
+          <t>se deduce 50%</t>
+        </is>
+      </c>
+      <c r="C6" s="43" t="inlineStr">
+        <is>
+          <t>jumătatea nedeductibilă intră în cheltuială</t>
+        </is>
+      </c>
+      <c r="D6" s="43" t="inlineStr">
+        <is>
+          <t>art. 298 CF (TVA) și art. 25 alin. (3) lit. l) CF (cheltuieli)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="43" t="inlineStr">
+        <is>
+          <t>Vehicul folosit EXCLUSIV în scop economic</t>
+        </is>
+      </c>
+      <c r="B7" s="43" t="inlineStr">
+        <is>
+          <t>se deduce 100%</t>
+        </is>
+      </c>
+      <c r="C7" s="43" t="inlineStr">
+        <is>
+          <t>nimic — TVA e integral deductibilă</t>
+        </is>
+      </c>
+      <c r="D7" s="43" t="inlineStr">
+        <is>
+          <t>cere foaie de parcurs care să dovedească utilizarea exclusivă</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="43" t="inlineStr">
+        <is>
+          <t>Vehicul EXCEPTAT (taxi, școală de șoferi, intervenție, agenți de vânzări…)</t>
+        </is>
+      </c>
+      <c r="B8" s="43" t="inlineStr">
+        <is>
+          <t>se deduce 100%</t>
+        </is>
+      </c>
+      <c r="C8" s="43" t="inlineStr">
+        <is>
+          <t>nimic</t>
+        </is>
+      </c>
+      <c r="D8" s="43" t="inlineStr">
+        <is>
+          <t>art. 298 alin. (2) CF — enumerare limitativă</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="43" t="inlineStr">
+        <is>
+          <t>Lipsă la inventar NEJUSTIFICATĂ</t>
+        </is>
+      </c>
+      <c r="B9" s="43" t="inlineStr">
+        <is>
+          <t>se COLECTEAZĂ pe valoarea bunului</t>
+        </is>
+      </c>
+      <c r="C9" s="43" t="inlineStr">
+        <is>
+          <t>cheltuiala e valoarea bunului; TVA colectată e separată</t>
+        </is>
+      </c>
+      <c r="D9" s="43" t="inlineStr">
+        <is>
+          <t>bunul se tratează ca livrat către sine</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="43" t="inlineStr">
+        <is>
+          <t>Lipsă JUSTIFICATĂ (calamitate, perisabilități în limită, casare documentată)</t>
+        </is>
+      </c>
+      <c r="B10" s="43" t="inlineStr">
+        <is>
+          <t>nu se colectează</t>
+        </is>
+      </c>
+      <c r="C10" s="43" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D10" s="43" t="inlineStr">
+        <is>
+          <t>trebuie documentată, altfel intră la nejustificată</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="42" t="inlineStr">
+        <is>
+          <t>Tabel B — Cele două principii</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="44" t="inlineStr">
+        <is>
+          <t>(1) TVA nedeductibilă se INCORPOREAZĂ în cheltuială. Nu se pierde și nu rămâne pe 4426 — acolo ar produce un sold care nu se închide la finalul lunii.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="44" t="inlineStr">
+        <is>
+          <t>(2) La lipsă nejustificată, 4427 se CREDITEAZĂ. Legea nu cere anularea deducerii, cere COLECTAREA: bunul se tratează ca livrat. Debitarea lui 4427 ar reduce TVA-ul colectat al lunii — exact invers decât trebuie.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="42" t="inlineStr">
+        <is>
+          <t>Tabel C — Porți de calitate</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="44" t="inlineStr">
+        <is>
+          <t>• ΣDr = ΣCr pe fiecare bloc</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="44" t="inlineStr">
+        <is>
+          <t>• Cheltuială + TVA dedusă = totalul facturii (1.105 + 105 = 1.210)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="44" t="inlineStr">
+        <is>
+          <t>• La regim MIXT se deduce exact procentul din param_proc_vehicul, nu unul scris în celulă</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="44" t="inlineStr">
+        <is>
+          <t>• La lipsă nejustificată, suma stă pe CREDITUL lui 4427</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="44" t="inlineStr">
+        <is>
+          <t>• Limitarea de 50% la TVA nu se cumulează cu plafonul de amortizare auto — sunt două mecanisme diferite (vezi param_plafon_amo_auto)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet71.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G21"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="38" customWidth="1" style="40" min="1" max="1"/>
+    <col width="16" customWidth="1" style="40" min="2" max="2"/>
+    <col width="14" customWidth="1" style="40" min="3" max="3"/>
+    <col width="52" customWidth="1" style="40" min="4" max="4"/>
+    <col width="16" customWidth="1" style="40" min="5" max="5"/>
+    <col width="14" customWidth="1" style="40" min="6" max="6"/>
+    <col width="52" customWidth="1" style="40" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="41" t="inlineStr">
+        <is>
+          <t>MOD_FARA_DOCUMENT — Jurnale (generate automat)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="44" t="inlineStr">
+        <is>
+          <t>Blocul A e un articol compus: două debite (cheltuiala majorată și TVA dedusă) contra unui singur credit, totalul facturii.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="42" t="inlineStr">
+        <is>
+          <t>Bloc A — Vehicul cu regim mixt</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="43" t="inlineStr">
+        <is>
+          <t>Data:</t>
+        </is>
+      </c>
+      <c r="B5" s="43" t="str">
+        <f>Declarații_FARA_DOCUMENT!B8</f>
+        <v>2026-07-31</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="65" t="inlineStr">
+        <is>
+          <t>Nr</t>
+        </is>
+      </c>
+      <c r="B6" s="65" t="inlineStr">
+        <is>
+          <t>Cont Dr</t>
+        </is>
+      </c>
+      <c r="C6" s="65" t="inlineStr">
+        <is>
+          <t>Sumă Dr</t>
+        </is>
+      </c>
+      <c r="D6" s="65" t="inlineStr">
+        <is>
+          <t>Descriere Dr</t>
+        </is>
+      </c>
+      <c r="E6" s="65" t="inlineStr">
+        <is>
+          <t>Cont Cr</t>
+        </is>
+      </c>
+      <c r="F6" s="65" t="inlineStr">
+        <is>
+          <t>Sumă Cr</t>
+        </is>
+      </c>
+      <c r="G6" s="65" t="inlineStr">
+        <is>
+          <t>Descriere Cr</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="43" t="n">
+        <v>1</v>
+      </c>
+      <c r="B7" s="43" t="str">
+        <f>Declarații_FARA_DOCUMENT!B29</f>
+        <v>628</v>
+      </c>
+      <c r="C7" s="43">
+        <f>IF(Declarații_FARA_DOCUMENT!B12="DA",Declarații_FARA_DOCUMENT!B19,0)</f>
+        <v>1105</v>
+      </c>
+      <c r="D7" s="43" t="str">
+        <f>"Cheltuială + TVA nedeductibilă " &amp; Declarații_FARA_DOCUMENT!B37</f>
+        <v>Cheltuială + TVA nedeductibilă — fără document 2026-07</v>
+      </c>
+      <c r="E7" s="43" t="str">
+        <f>Declarații_FARA_DOCUMENT!B31</f>
+        <v>401</v>
+      </c>
+      <c r="F7" s="43">
+        <f>IF(Declarații_FARA_DOCUMENT!B12="DA",Declarații_FARA_DOCUMENT!B20,0)</f>
+        <v>1210</v>
+      </c>
+      <c r="G7" s="43" t="str">
+        <f>"Datorie furnizor (total factură) " &amp; Declarații_FARA_DOCUMENT!B37</f>
+        <v>Datorie furnizor (total factură) — fără document 2026-07</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="43" t="n">
+        <v>2</v>
+      </c>
+      <c r="B8" s="43" t="str">
+        <f>Declarații_FARA_DOCUMENT!B33</f>
+        <v>4426</v>
+      </c>
+      <c r="C8" s="43">
+        <f>IF(Declarații_FARA_DOCUMENT!B12="DA",Declarații_FARA_DOCUMENT!B17,0)</f>
+        <v>105</v>
+      </c>
+      <c r="D8" s="43" t="str">
+        <f>"TVA deductibilă (procentul admis) " &amp; Declarații_FARA_DOCUMENT!B37</f>
+        <v>TVA deductibilă (procentul admis) — fără document 2026-07</v>
+      </c>
+      <c r="E8" s="43" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" s="43" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="43" t="inlineStr">
+        <is>
+          <t>Check A (cheltuială + TVA dedusă = total)</t>
+        </is>
+      </c>
+      <c r="B9" s="43">
+        <f>(C7+C8)-F7</f>
+        <v>0</v>
+      </c>
+      <c r="C9" s="43" t="str">
+        <f>IF(ABS(B9)&lt;0.01,"OK — nimic nu se pierde","EROARE")</f>
+        <v>OK — nimic nu se pierde</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="42" t="inlineStr">
+        <is>
+          <t>Bloc B — Lipsă la inventar nejustificată</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="65" t="inlineStr">
+        <is>
+          <t>Nr</t>
+        </is>
+      </c>
+      <c r="B12" s="65" t="inlineStr">
+        <is>
+          <t>Cont Dr</t>
+        </is>
+      </c>
+      <c r="C12" s="65" t="inlineStr">
+        <is>
+          <t>Sumă Dr</t>
+        </is>
+      </c>
+      <c r="D12" s="65" t="inlineStr">
+        <is>
+          <t>Descriere Dr</t>
+        </is>
+      </c>
+      <c r="E12" s="65" t="inlineStr">
+        <is>
+          <t>Cont Cr</t>
+        </is>
+      </c>
+      <c r="F12" s="65" t="inlineStr">
+        <is>
+          <t>Sumă Cr</t>
+        </is>
+      </c>
+      <c r="G12" s="65" t="inlineStr">
+        <is>
+          <t>Descriere Cr</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="43" t="n">
+        <v>1</v>
+      </c>
+      <c r="B13" s="43" t="str">
+        <f>Declarații_FARA_DOCUMENT!B30</f>
+        <v>658</v>
+      </c>
+      <c r="C13" s="43">
+        <f>IF(Declarații_FARA_DOCUMENT!B23="DA",Declarații_FARA_DOCUMENT!B25,0)</f>
+        <v>1200</v>
+      </c>
+      <c r="D13" s="43" t="str">
+        <f>"Cheltuială cu lipsa la inventar " &amp; Declarații_FARA_DOCUMENT!B37</f>
+        <v>Cheltuială cu lipsa la inventar — fără document 2026-07</v>
+      </c>
+      <c r="E13" s="43" t="str">
+        <f>Declarații_FARA_DOCUMENT!B32</f>
+        <v>371</v>
+      </c>
+      <c r="F13" s="43">
+        <f>IF(Declarații_FARA_DOCUMENT!B23="DA",Declarații_FARA_DOCUMENT!B25,0)</f>
+        <v>1200</v>
+      </c>
+      <c r="G13" s="43" t="str">
+        <f>"Descărcarea stocului lipsă " &amp; Declarații_FARA_DOCUMENT!B37</f>
+        <v>Descărcarea stocului lipsă — fără document 2026-07</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="43" t="inlineStr">
+        <is>
+          <t>Check B1 (descărcarea stocului)</t>
+        </is>
+      </c>
+      <c r="B14" s="43">
+        <f>C13-F13</f>
+        <v>0</v>
+      </c>
+      <c r="C14" s="43" t="str">
+        <f>IF(ABS(B14)&lt;0.01,"OK","EROARE")</f>
+        <v>OK</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="43" t="n">
+        <v>2</v>
+      </c>
+      <c r="B15" s="43" t="str">
+        <f>Declarații_FARA_DOCUMENT!B30</f>
+        <v>658</v>
+      </c>
+      <c r="C15" s="43">
+        <f>IF(Declarații_FARA_DOCUMENT!B23="DA",Declarații_FARA_DOCUMENT!B26,0)</f>
+        <v>252</v>
+      </c>
+      <c r="D15" s="43" t="str">
+        <f>"TVA colectată pe lipsă (NU stornare de deducere) " &amp; Declarații_FARA_DOCUMENT!B37</f>
+        <v>TVA colectată pe lipsă (NU stornare de deducere) — fără document 2026-07</v>
+      </c>
+      <c r="E15" s="43" t="str">
+        <f>Declarații_FARA_DOCUMENT!B34</f>
+        <v>4427</v>
+      </c>
+      <c r="F15" s="43">
+        <f>IF(Declarații_FARA_DOCUMENT!B23="DA",Declarații_FARA_DOCUMENT!B26,0)</f>
+        <v>252</v>
+      </c>
+      <c r="G15" s="43" t="str">
+        <f>"TVA colectată — bunul se tratează ca livrat " &amp; Declarații_FARA_DOCUMENT!B37</f>
+        <v>TVA colectată — bunul se tratează ca livrat — fără document 2026-07</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="43" t="inlineStr">
+        <is>
+          <t>Check B2 (4427 pe partea de CREDIT)</t>
+        </is>
+      </c>
+      <c r="B16" s="43">
+        <f>IF(E15=Declarații_FARA_DOCUMENT!B34,0,1)</f>
+        <v>0</v>
+      </c>
+      <c r="C16" s="43" t="str">
+        <f>IF(B16=0,"OK — 4427 creditat, cum trebuie","EROARE — 4427 nu e pe credit: la lipsă se colectează, nu se stornează deducerea")</f>
+        <v>OK — 4427 creditat, cum trebuie</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="43" t="inlineStr">
+        <is>
+          <t>Check global</t>
+        </is>
+      </c>
+      <c r="B18" s="43">
+        <f>ABS(B9)+ABS(B14)+ABS(B16)</f>
+        <v>0</v>
+      </c>
+      <c r="C18" s="43" t="str">
+        <f>IF(B18&lt;0.01,"OK — toate blocurile se închid","EROARE — cel puțin un bloc dezechilibrat")</f>
+        <v>OK — toate blocurile se închid</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="42" t="inlineStr">
+        <is>
+          <t>Stare terminală</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="44" t="inlineStr">
+        <is>
+          <t>Pe 4426 intră doar partea deductibilă; restul e cost și nu mai apare nicăieri ca TVA. Pe 4427 intră TVA-ul colectat pe lipsă, care majorează TVA-ul de plată al lunii — nu îl reduce.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet72.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="6" customWidth="1" style="40" min="1" max="1"/>
+    <col width="30" customWidth="1" style="40" min="2" max="2"/>
+    <col width="14" customWidth="1" style="40" min="3" max="3"/>
+    <col width="12" customWidth="1" style="40" min="4" max="4"/>
+    <col width="12" customWidth="1" style="40" min="5" max="5"/>
+    <col width="14" customWidth="1" style="40" min="6" max="6"/>
+    <col width="52" customWidth="1" style="40" min="7" max="7"/>
+    <col width="26" customWidth="1" style="40" min="8" max="8"/>
+    <col width="10" customWidth="1" style="40" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="41" t="inlineStr">
+        <is>
+          <t>MOD_FARA_DOCUMENT — Notă pentru import</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="44" t="inlineStr">
+        <is>
+          <t>Filtrează Include=DA. Cazurile neactivate ies cu sumă 0 și apar ca NU.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="65" t="inlineStr">
+        <is>
+          <t>Nr</t>
+        </is>
+      </c>
+      <c r="B4" s="65" t="inlineStr">
+        <is>
+          <t>Bloc</t>
+        </is>
+      </c>
+      <c r="C4" s="65" t="inlineStr">
+        <is>
+          <t>Data</t>
+        </is>
+      </c>
+      <c r="D4" s="65" t="inlineStr">
+        <is>
+          <t>Cont Dr</t>
+        </is>
+      </c>
+      <c r="E4" s="65" t="inlineStr">
+        <is>
+          <t>Cont Cr</t>
+        </is>
+      </c>
+      <c r="F4" s="65" t="inlineStr">
+        <is>
+          <t>Sumă</t>
+        </is>
+      </c>
+      <c r="G4" s="65" t="inlineStr">
+        <is>
+          <t>Descriere</t>
+        </is>
+      </c>
+      <c r="H4" s="65" t="inlineStr">
+        <is>
+          <t>Document</t>
+        </is>
+      </c>
+      <c r="I4" s="65" t="inlineStr">
+        <is>
+          <t>Include</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="43" t="n">
+        <v>1</v>
+      </c>
+      <c r="B5" s="43" t="inlineStr">
+        <is>
+          <t>A Auto — cheltuiala</t>
+        </is>
+      </c>
+      <c r="C5" s="43" t="str">
+        <f>Declarații_FARA_DOCUMENT!B8</f>
+        <v>2026-07-31</v>
+      </c>
+      <c r="D5" s="43" t="str">
+        <f>Jurnale_FARA_DOCUMENT!B7</f>
+        <v>628</v>
+      </c>
+      <c r="E5" s="43" t="str">
+        <f>Jurnale_FARA_DOCUMENT!E7</f>
+        <v>401</v>
+      </c>
+      <c r="F5" s="43">
+        <f>Jurnale_FARA_DOCUMENT!C7</f>
+        <v>1105</v>
+      </c>
+      <c r="G5" s="43" t="str">
+        <f>Jurnale_FARA_DOCUMENT!D7</f>
+        <v>Cheltuială + TVA nedeductibilă — fără document 2026-07</v>
+      </c>
+      <c r="H5" s="43" t="inlineStr">
+        <is>
+          <t>Factură</t>
+        </is>
+      </c>
+      <c r="I5" s="43" t="str">
+        <f>IF(AND(ISNUMBER(F5),F5&gt;0),"DA","NU")</f>
+        <v>DA</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="43" t="n">
+        <v>2</v>
+      </c>
+      <c r="B6" s="43" t="inlineStr">
+        <is>
+          <t>A Auto — TVA dedusă</t>
+        </is>
+      </c>
+      <c r="C6" s="43" t="str">
+        <f>Declarații_FARA_DOCUMENT!B8</f>
+        <v>2026-07-31</v>
+      </c>
+      <c r="D6" s="43" t="str">
+        <f>Jurnale_FARA_DOCUMENT!B8</f>
+        <v>4426</v>
+      </c>
+      <c r="E6" s="43" t="str">
+        <f>Jurnale_FARA_DOCUMENT!E7</f>
+        <v>401</v>
+      </c>
+      <c r="F6" s="43">
+        <f>Jurnale_FARA_DOCUMENT!C8</f>
+        <v>105</v>
+      </c>
+      <c r="G6" s="43" t="str">
+        <f>Jurnale_FARA_DOCUMENT!D8</f>
+        <v>TVA deductibilă (procentul admis) — fără document 2026-07</v>
+      </c>
+      <c r="H6" s="43" t="inlineStr">
+        <is>
+          <t>Factură</t>
+        </is>
+      </c>
+      <c r="I6" s="43" t="str">
+        <f>IF(AND(ISNUMBER(F6),F6&gt;0),"DA","NU")</f>
+        <v>DA</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="43" t="n">
+        <v>3</v>
+      </c>
+      <c r="B7" s="43" t="inlineStr">
+        <is>
+          <t>B Lipsă — cheltuiala</t>
+        </is>
+      </c>
+      <c r="C7" s="43" t="str">
+        <f>Declarații_FARA_DOCUMENT!B8</f>
+        <v>2026-07-31</v>
+      </c>
+      <c r="D7" s="43" t="str">
+        <f>Jurnale_FARA_DOCUMENT!B13</f>
+        <v>658</v>
+      </c>
+      <c r="E7" s="43" t="str">
+        <f>Jurnale_FARA_DOCUMENT!E13</f>
+        <v>371</v>
+      </c>
+      <c r="F7" s="43">
+        <f>Jurnale_FARA_DOCUMENT!C13</f>
+        <v>1200</v>
+      </c>
+      <c r="G7" s="43" t="str">
+        <f>Jurnale_FARA_DOCUMENT!D13</f>
+        <v>Cheltuială cu lipsa la inventar — fără document 2026-07</v>
+      </c>
+      <c r="H7" s="43" t="inlineStr">
+        <is>
+          <t>Proces-verbal inventar</t>
+        </is>
+      </c>
+      <c r="I7" s="43" t="str">
+        <f>IF(AND(ISNUMBER(F7),F7&gt;0),"DA","NU")</f>
+        <v>DA</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="43" t="n">
+        <v>4</v>
+      </c>
+      <c r="B8" s="43" t="inlineStr">
+        <is>
+          <t>B Lipsă — TVA colectată</t>
+        </is>
+      </c>
+      <c r="C8" s="43" t="str">
+        <f>Declarații_FARA_DOCUMENT!B8</f>
+        <v>2026-07-31</v>
+      </c>
+      <c r="D8" s="43" t="str">
+        <f>Jurnale_FARA_DOCUMENT!B15</f>
+        <v>658</v>
+      </c>
+      <c r="E8" s="43" t="str">
+        <f>Jurnale_FARA_DOCUMENT!E15</f>
+        <v>4427</v>
+      </c>
+      <c r="F8" s="43">
+        <f>Jurnale_FARA_DOCUMENT!C15</f>
+        <v>252</v>
+      </c>
+      <c r="G8" s="43" t="str">
+        <f>Jurnale_FARA_DOCUMENT!D15</f>
+        <v>TVA colectată pe lipsă (NU stornare de deducere) — fără document 2026-07</v>
+      </c>
+      <c r="H8" s="43" t="inlineStr">
+        <is>
+          <t>Proces-verbal inventar</t>
+        </is>
+      </c>
+      <c r="I8" s="43" t="str">
+        <f>IF(AND(ISNUMBER(F8),F8&gt;0),"DA","NU")</f>
+        <v>DA</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="43" t="inlineStr">
+        <is>
+          <t>Rânduri de importat</t>
+        </is>
+      </c>
+      <c r="B10" s="43">
+        <f>COUNTIF(I5:I8,"DA")</f>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="43" t="inlineStr">
+        <is>
+          <t>Check global</t>
+        </is>
+      </c>
+      <c r="B11" s="43">
+        <f>Jurnale_FARA_DOCUMENT!B18</f>
+        <v>0</v>
+      </c>
+      <c r="C11" s="43" t="str">
+        <f>IF(ABS(B11)&lt;0.01,"OK","EROARE")</f>
+        <v>OK</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet73.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B41"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="40" customWidth="1" style="40" min="1" max="1"/>
+    <col width="42" customWidth="1" style="40" min="2" max="2"/>
+    <col width="52" customWidth="1" style="40" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="41" t="inlineStr">
+        <is>
+          <t>MOD_NEUTRALIZARE — Declarații (input)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="44" t="inlineStr">
+        <is>
+          <t>Acoperă F-311 (bunuri/711), F-312 (servicii/712), F-209 (imobilizări/722). Alege tipul — conturile și lanțul se adaptează. Principiu: costurile lovesc cls.6, apoi contul de venit de producție capitalizează și neutralizează.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="42" t="inlineStr">
+        <is>
+          <t>1. Antet</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="43" t="inlineStr">
+        <is>
+          <t>Societate</t>
+        </is>
+      </c>
+      <c r="B5" s="43" t="str">
+        <f>Parametri!B5</f>
+        <v>SC EXEMPLU SRL</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="43" t="inlineStr">
+        <is>
+          <t>CUI</t>
+        </is>
+      </c>
+      <c r="B6" s="43" t="str">
+        <f>Parametri!B6</f>
+        <v>RO00000000</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="43" t="inlineStr">
+        <is>
+          <t>Luna / proiect</t>
+        </is>
+      </c>
+      <c r="B7" s="64" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="43" t="inlineStr">
+        <is>
+          <t>Data costuri (B1)</t>
+        </is>
+      </c>
+      <c r="B8" s="64" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="43" t="inlineStr">
+        <is>
+          <t>Data finalizare stoc (B2-B3)</t>
+        </is>
+      </c>
+      <c r="B9" s="64" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="43" t="inlineStr">
+        <is>
+          <t>Data vânzare / recepție MF (B4)</t>
+        </is>
+      </c>
+      <c r="B10" s="64" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="42" t="inlineStr">
+        <is>
+          <t>2. Tip producție (poartă principală)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="43" t="inlineStr">
+        <is>
+          <t>Tip (BUNURI / SERVICII / MF)</t>
+        </is>
+      </c>
+      <c r="B13" s="64" t="inlineStr">
+        <is>
+          <t>BUNURI</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="43" t="inlineStr">
+        <is>
+          <t>Cont venit neutralizare (auto)</t>
+        </is>
+      </c>
+      <c r="B14" s="43">
+        <f>IF(B13="BUNURI",711,IF(B13="SERVICII",712,IF(B13="MF",722,"?")))</f>
+        <v>711</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="43" t="inlineStr">
+        <is>
+          <t>Cont stoc intermediar (auto)</t>
+        </is>
+      </c>
+      <c r="B15" s="43">
+        <f>IF(B13="BUNURI",331,IF(B13="SERVICII",332,IF(B13="MF",231,"?")))</f>
+        <v>331</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="43" t="inlineStr">
+        <is>
+          <t>Cont stoc final (auto)</t>
+        </is>
+      </c>
+      <c r="B16" s="43">
+        <f>IF(B13="BUNURI",345,IF(B13="SERVICII","(nu e cazul — se stinge la livrare)",IF(B13="MF",213,"?")))</f>
+        <v>345</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="43" t="inlineStr">
+        <is>
+          <t>Cont venit vânzare (auto)</t>
+        </is>
+      </c>
+      <c r="B17" s="43">
+        <f>IF(B13="BUNURI",701,IF(B13="SERVICII",704,IF(B13="MF","(nu e vânzare — e activ)","?")))</f>
+        <v>701</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="42" t="inlineStr">
+        <is>
+          <t>3. Costuri (cls.6)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="43" t="inlineStr">
+        <is>
+          <t>Cost materiale (→ 601)</t>
+        </is>
+      </c>
+      <c r="B20" s="64" t="n">
+        <v>4500</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="43" t="inlineStr">
+        <is>
+          <t>Cost manoperă (→ 641)</t>
+        </is>
+      </c>
+      <c r="B21" s="64" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="43" t="inlineStr">
+        <is>
+          <t>Alte costuri (→ 6xx)</t>
+        </is>
+      </c>
+      <c r="B22" s="64" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="43" t="inlineStr">
+        <is>
+          <t>Cost total</t>
+        </is>
+      </c>
+      <c r="B23" s="43">
+        <f>B20+B21+B22</f>
+        <v>4500</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="42" t="inlineStr">
+        <is>
+          <t>4. Vânzare (doar BUNURI / SERVICII)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="43" t="inlineStr">
+        <is>
+          <t>Preț vânzare (fără TVA)</t>
+        </is>
+      </c>
+      <c r="B26" s="64" t="n">
+        <v>7000</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="43" t="inlineStr">
+        <is>
+          <t>Cota TVA</t>
+        </is>
+      </c>
+      <c r="B27" s="64" t="n">
+        <v>0.21</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="43" t="inlineStr">
+        <is>
+          <t>TVA</t>
+        </is>
+      </c>
+      <c r="B28" s="43">
+        <f>IF(OR(B13="BUNURI",B13="SERVICII"),B26*B27,0)</f>
+        <v>1470</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="43" t="inlineStr">
+        <is>
+          <t>Total factură</t>
+        </is>
+      </c>
+      <c r="B29" s="43">
+        <f>B26+B28</f>
+        <v>8470</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="42" t="inlineStr">
+        <is>
+          <t>5. Conturi suplimentare</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="43" t="inlineStr">
+        <is>
+          <t>Cont materii prime</t>
+        </is>
+      </c>
+      <c r="B32" s="64" t="inlineStr">
+        <is>
+          <t>301</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="43" t="inlineStr">
+        <is>
+          <t>Cont client</t>
+        </is>
+      </c>
+      <c r="B33" s="64" t="inlineStr">
+        <is>
+          <t>411.RO</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="43" t="inlineStr">
+        <is>
+          <t>Cont TVA colectată</t>
+        </is>
+      </c>
+      <c r="B34" s="64" t="inlineStr">
+        <is>
+          <t>4427</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="42" t="inlineStr">
+        <is>
+          <t>6. Sufix</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="43" t="inlineStr">
+        <is>
+          <t>Sufix</t>
+        </is>
+      </c>
+      <c r="B37" s="43" t="str">
+        <f>"— " &amp; B7 &amp; " — " &amp; B13 &amp; " — " &amp; B14</f>
+        <v>— 2026-07 — BUNURI — 711</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="42" t="inlineStr">
+        <is>
+          <t>7. Control</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="43" t="inlineStr">
+        <is>
+          <t>Marjă (vânzare − cost)</t>
+        </is>
+      </c>
+      <c r="B40" s="43">
+        <f>IF(OR(B13="BUNURI",B13="SERVICII"),B26-B23,"n/a (MF)")</f>
+        <v>2500</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="43" t="inlineStr">
+        <is>
+          <t>Notă principiu</t>
+        </is>
+      </c>
+      <c r="B41" s="43" t="inlineStr">
+        <is>
+          <t>Costurile lovesc cls.6; contul de venit de producție (711/712/722) capitalizează și neutralizează. Descărcarea la vânzare (bunuri) e prin 711=345, nu prin 607.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet74.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:F21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -30848,7 +32125,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet71.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet75.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -31423,7 +32700,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet72.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet76.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -31847,7 +33124,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet73.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet77.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -32234,7 +33511,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet74.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet78.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -32627,7 +33904,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet75.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet79.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -33291,7 +34568,528 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet76.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C54"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="46" customWidth="1" style="40" min="1" max="1"/>
+    <col width="20" customWidth="1" style="40" min="2" max="2"/>
+    <col width="62" customWidth="1" style="40" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="41" t="inlineStr">
+        <is>
+          <t>MOD_CREDIT_VALUTA — Declarații (input)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="44" t="inlineStr">
+        <is>
+          <t>Valorile implicite reproduc monografia din F-107. Rata și dobânda se iau din SCADENȚAR, nu din extras — extrasul le arată deseori cumulat.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="42" t="inlineStr">
+        <is>
+          <t>1. Antet</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="43" t="inlineStr">
+        <is>
+          <t>Societate</t>
+        </is>
+      </c>
+      <c r="B5" s="43" t="str">
+        <f>Parametri!B5</f>
+        <v>SC EXEMPLU SRL</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="43" t="inlineStr">
+        <is>
+          <t>Număr contract de credit</t>
+        </is>
+      </c>
+      <c r="B6" s="64" t="inlineStr">
+        <is>
+          <t>CR-2026-001</t>
+        </is>
+      </c>
+      <c r="C6" s="44" t="inlineStr">
+        <is>
+          <t>1621 se ține analitic pe contract și pe valută</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="43" t="inlineStr">
+        <is>
+          <t>Luna (AAAA-LL)</t>
+        </is>
+      </c>
+      <c r="B7" s="64" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="43" t="inlineStr">
+        <is>
+          <t>Data plății ratei</t>
+        </is>
+      </c>
+      <c r="B8" s="64" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="43" t="inlineStr">
+        <is>
+          <t>Data reevaluării (ultima zi bancară a lunii)</t>
+        </is>
+      </c>
+      <c r="B9" s="64" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="43" t="inlineStr">
+        <is>
+          <t>Valuta</t>
+        </is>
+      </c>
+      <c r="B10" s="64" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="42" t="inlineStr">
+        <is>
+          <t>2. Soldul de la care pornim</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="43" t="inlineStr">
+        <is>
+          <t>Sold inițial, în valută</t>
+        </is>
+      </c>
+      <c r="B13" s="64" t="n">
+        <v>20000</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="43" t="inlineStr">
+        <is>
+          <t>Cursul la care e înregistrat soldul</t>
+        </is>
+      </c>
+      <c r="B14" s="64" t="n">
+        <v>4.97</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="43" t="inlineStr">
+        <is>
+          <t>Sold inițial, în lei</t>
+        </is>
+      </c>
+      <c r="B15" s="43">
+        <f>ROUND(B13*B14,2)</f>
+        <v>99400</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="42" t="inlineStr">
+        <is>
+          <t>3. Mișcările lunii (din SCADENȚAR)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="43" t="inlineStr">
+        <is>
+          <t>Rata de capital, în valută</t>
+        </is>
+      </c>
+      <c r="B18" s="64" t="n">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="43" t="inlineStr">
+        <is>
+          <t>Dobânda, în valută</t>
+        </is>
+      </c>
+      <c r="B19" s="64" t="n">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="43" t="inlineStr">
+        <is>
+          <t>Cursul de la data plății</t>
+        </is>
+      </c>
+      <c r="B20" s="64" t="n">
+        <v>4.99</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="43" t="inlineStr">
+        <is>
+          <t>Comisioane bancare, în lei</t>
+        </is>
+      </c>
+      <c r="B21" s="64" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="42" t="inlineStr">
+        <is>
+          <t>4. Reevaluarea de la finalul lunii</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="43" t="inlineStr">
+        <is>
+          <t>Curs BNR la data reevaluării</t>
+        </is>
+      </c>
+      <c r="B24" s="64" t="n">
+        <v>5.01</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="42" t="inlineStr">
+        <is>
+          <t>5. Calcul automat (nu edita)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="43" t="inlineStr">
+        <is>
+          <t>Rata, la cursul de înregistrare</t>
+        </is>
+      </c>
+      <c r="B27" s="43">
+        <f>ROUND(B18*B14,2)</f>
+        <v>24850</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="43" t="inlineStr">
+        <is>
+          <t>Rata, la cursul de plată</t>
+        </is>
+      </c>
+      <c r="B28" s="43">
+        <f>ROUND(B18*B20,2)</f>
+        <v>24950</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="43" t="inlineStr">
+        <is>
+          <t>MOMENTUL 1 — diferența la plată</t>
+        </is>
+      </c>
+      <c r="B29" s="43">
+        <f>B28-B27</f>
+        <v>100</v>
+      </c>
+      <c r="C29" s="44" t="inlineStr">
+        <is>
+          <t>Pozitiv = nefavorabil (665); negativ = favorabil (765)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="43" t="inlineStr">
+        <is>
+          <t>Dobânda, în lei</t>
+        </is>
+      </c>
+      <c r="B30" s="43">
+        <f>ROUND(B19*B20,2)</f>
+        <v>998</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="43" t="inlineStr">
+        <is>
+          <t>Sold rămas, în valută</t>
+        </is>
+      </c>
+      <c r="B31" s="43">
+        <f>B13-B18</f>
+        <v>15000</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="43" t="inlineStr">
+        <is>
+          <t>Sold rămas, la cursul de înregistrare</t>
+        </is>
+      </c>
+      <c r="B32" s="43">
+        <f>ROUND(B31*B14,2)</f>
+        <v>74550</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="43" t="inlineStr">
+        <is>
+          <t>Sold rămas, la cursul BNR</t>
+        </is>
+      </c>
+      <c r="B33" s="43">
+        <f>ROUND(B31*B24,2)</f>
+        <v>75150</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="43" t="inlineStr">
+        <is>
+          <t>MOMENTUL 2 — diferența din reevaluare</t>
+        </is>
+      </c>
+      <c r="B34" s="43">
+        <f>B33-B32</f>
+        <v>600</v>
+      </c>
+      <c r="C34" s="44" t="inlineStr">
+        <is>
+          <t>Pozitiv = datoria crește = nefavorabil (665)</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="42" t="inlineStr">
+        <is>
+          <t>6. Conturi</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="43" t="inlineStr">
+        <is>
+          <t>Cont credit (162x)</t>
+        </is>
+      </c>
+      <c r="B37" s="64" t="inlineStr">
+        <is>
+          <t>1621</t>
+        </is>
+      </c>
+      <c r="C37" s="44" t="inlineStr">
+        <is>
+          <t>1621…1627 sunt sintetice DISTINCTE, nu analitice ale aceluiași cont</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="43" t="inlineStr">
+        <is>
+          <t>Cont dobândă neajunsă la scadență</t>
+        </is>
+      </c>
+      <c r="B38" s="64" t="n">
+        <v>1682</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="43" t="inlineStr">
+        <is>
+          <t>Cont trezorerie în valută</t>
+        </is>
+      </c>
+      <c r="B39" s="64" t="inlineStr">
+        <is>
+          <t>5124</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="43" t="inlineStr">
+        <is>
+          <t>Cont trezorerie în lei</t>
+        </is>
+      </c>
+      <c r="B40" s="64" t="inlineStr">
+        <is>
+          <t>5121</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="43" t="inlineStr">
+        <is>
+          <t>Cont cheltuială cu dobânda</t>
+        </is>
+      </c>
+      <c r="B41" s="64" t="n">
+        <v>666</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="43" t="inlineStr">
+        <is>
+          <t>Cont cheltuială cu serviciile bancare</t>
+        </is>
+      </c>
+      <c r="B42" s="64" t="n">
+        <v>627</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="43" t="inlineStr">
+        <is>
+          <t>Cont diferențe nefavorabile</t>
+        </is>
+      </c>
+      <c r="B43" s="64" t="n">
+        <v>665</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="43" t="inlineStr">
+        <is>
+          <t>Cont diferențe favorabile</t>
+        </is>
+      </c>
+      <c r="B44" s="64" t="n">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="42" t="inlineStr">
+        <is>
+          <t>7. Controale</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="43" t="inlineStr">
+        <is>
+          <t>Check FINAL: sold lei = sold valută × curs BNR</t>
+        </is>
+      </c>
+      <c r="B47" s="43">
+        <f>B32+B34-B33</f>
+        <v>0</v>
+      </c>
+      <c r="C47" s="43" t="str">
+        <f>IF(ABS(B47)&lt;0.01,"OK — soldul în lei corespunde soldului în valută","EROARE — una dintre cele două diferențe de curs lipsește")</f>
+        <v>OK — soldul în lei corespunde soldului în valută</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="43" t="inlineStr">
+        <is>
+          <t>Check cele două momente sunt distincte</t>
+        </is>
+      </c>
+      <c r="B48" s="43">
+        <f>B29+B34</f>
+        <v>700</v>
+      </c>
+      <c r="C48" s="43" t="str">
+        <f>"Momentul 1 (la plată): " &amp; TEXT(B29,"0.00") &amp; " lei · Momentul 2 (reevaluare): " &amp; TEXT(B34,"0.00") &amp; " lei"</f>
+        <v>Momentul 1 (la plată): 100.00 lei · Momentul 2 (reevaluare): 600.00 lei</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="43" t="inlineStr">
+        <is>
+          <t>Reminder: rata și dobânda vin din scadențar</t>
+        </is>
+      </c>
+      <c r="B49" s="43">
+        <f>B18+B19</f>
+        <v>5200</v>
+      </c>
+      <c r="C49" s="43" t="str">
+        <f>"Extrasul arată deseori B18+B19 cumulat. Dacă le înregistrezi așa, ajungi cu 1621 pe debit sau cu sold rămas la finalul creditului."</f>
+        <v>Extrasul arată deseori B18+B19 cumulat. Dacă le înregistrezi așa, ajungi cu 1621 pe debit sau cu sold rămas la finalul creditului.</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="43" t="inlineStr">
+        <is>
+          <t>Reminder: reevaluarea e LUNARĂ</t>
+        </is>
+      </c>
+      <c r="B50" s="43" t="str">
+        <f>B9</f>
+        <v>2026-07-31</v>
+      </c>
+      <c r="C50" s="43" t="str">
+        <f>"Obligatorie lunar (OMFP 1802/2014), nu trimestrial. Verifică și soldul ÎN VALUTĂ, nu doar în lei."</f>
+        <v>Obligatorie lunar (OMFP 1802/2014), nu trimestrial. Verifică și soldul ÎN VALUTĂ, nu doar în lei.</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="43" t="inlineStr">
+        <is>
+          <t>Reminder bilanț</t>
+        </is>
+      </c>
+      <c r="B51" s="43">
+        <f>B31</f>
+        <v>15000</v>
+      </c>
+      <c r="C51" s="43" t="str">
+        <f>"Reclasifică porțiunea scadentă în ≤ 12 luni pentru bilanț, prin analitic sau cont dedicat. Dobânda calculată și neajunsă la scadență stă pe 1682."</f>
+        <v>Reclasifică porțiunea scadentă în ≤ 12 luni pentru bilanț, prin analitic sau cont dedicat. Dobânda calculată și neajunsă la scadență stă pe 1682.</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="42" t="inlineStr">
+        <is>
+          <t>8. Sufix generat</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="43" t="inlineStr">
+        <is>
+          <t>Sufix</t>
+        </is>
+      </c>
+      <c r="B54" s="43" t="str">
+        <f>" - " &amp; B6 &amp; " - " &amp; B7</f>
+        <v> - CR-2026-001 - 2026-07</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet80.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -33825,7 +35623,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet77.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet81.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -34228,7 +36026,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet78.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet82.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -34526,7 +36324,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet79.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet83.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -35072,528 +36870,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:C54"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="46" customWidth="1" style="40" min="1" max="1"/>
-    <col width="20" customWidth="1" style="40" min="2" max="2"/>
-    <col width="62" customWidth="1" style="40" min="3" max="3"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="41" t="inlineStr">
-        <is>
-          <t>MOD_CREDIT_VALUTA — Declarații (input)</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="44" t="inlineStr">
-        <is>
-          <t>Valorile implicite reproduc monografia din F-107. Rata și dobânda se iau din SCADENȚAR, nu din extras — extrasul le arată deseori cumulat.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="42" t="inlineStr">
-        <is>
-          <t>1. Antet</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="43" t="inlineStr">
-        <is>
-          <t>Societate</t>
-        </is>
-      </c>
-      <c r="B5" s="43" t="str">
-        <f>Parametri!B5</f>
-        <v>SC EXEMPLU SRL</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="43" t="inlineStr">
-        <is>
-          <t>Număr contract de credit</t>
-        </is>
-      </c>
-      <c r="B6" s="64" t="inlineStr">
-        <is>
-          <t>CR-2026-001</t>
-        </is>
-      </c>
-      <c r="C6" s="44" t="inlineStr">
-        <is>
-          <t>1621 se ține analitic pe contract și pe valută</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="43" t="inlineStr">
-        <is>
-          <t>Luna (AAAA-LL)</t>
-        </is>
-      </c>
-      <c r="B7" s="64" t="inlineStr">
-        <is>
-          <t>2026-07</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="43" t="inlineStr">
-        <is>
-          <t>Data plății ratei</t>
-        </is>
-      </c>
-      <c r="B8" s="64" t="inlineStr">
-        <is>
-          <t>2026-07-15</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="43" t="inlineStr">
-        <is>
-          <t>Data reevaluării (ultima zi bancară a lunii)</t>
-        </is>
-      </c>
-      <c r="B9" s="64" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="43" t="inlineStr">
-        <is>
-          <t>Valuta</t>
-        </is>
-      </c>
-      <c r="B10" s="64" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="42" t="inlineStr">
-        <is>
-          <t>2. Soldul de la care pornim</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="43" t="inlineStr">
-        <is>
-          <t>Sold inițial, în valută</t>
-        </is>
-      </c>
-      <c r="B13" s="64" t="n">
-        <v>20000</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="43" t="inlineStr">
-        <is>
-          <t>Cursul la care e înregistrat soldul</t>
-        </is>
-      </c>
-      <c r="B14" s="64" t="n">
-        <v>4.97</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="43" t="inlineStr">
-        <is>
-          <t>Sold inițial, în lei</t>
-        </is>
-      </c>
-      <c r="B15" s="43">
-        <f>ROUND(B13*B14,2)</f>
-        <v>99400</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="42" t="inlineStr">
-        <is>
-          <t>3. Mișcările lunii (din SCADENȚAR)</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="43" t="inlineStr">
-        <is>
-          <t>Rata de capital, în valută</t>
-        </is>
-      </c>
-      <c r="B18" s="64" t="n">
-        <v>5000</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="43" t="inlineStr">
-        <is>
-          <t>Dobânda, în valută</t>
-        </is>
-      </c>
-      <c r="B19" s="64" t="n">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="43" t="inlineStr">
-        <is>
-          <t>Cursul de la data plății</t>
-        </is>
-      </c>
-      <c r="B20" s="64" t="n">
-        <v>4.99</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="43" t="inlineStr">
-        <is>
-          <t>Comisioane bancare, în lei</t>
-        </is>
-      </c>
-      <c r="B21" s="64" t="n">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="42" t="inlineStr">
-        <is>
-          <t>4. Reevaluarea de la finalul lunii</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="43" t="inlineStr">
-        <is>
-          <t>Curs BNR la data reevaluării</t>
-        </is>
-      </c>
-      <c r="B24" s="64" t="n">
-        <v>5.01</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="42" t="inlineStr">
-        <is>
-          <t>5. Calcul automat (nu edita)</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="43" t="inlineStr">
-        <is>
-          <t>Rata, la cursul de înregistrare</t>
-        </is>
-      </c>
-      <c r="B27" s="43">
-        <f>ROUND(B18*B14,2)</f>
-        <v>24850</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="43" t="inlineStr">
-        <is>
-          <t>Rata, la cursul de plată</t>
-        </is>
-      </c>
-      <c r="B28" s="43">
-        <f>ROUND(B18*B20,2)</f>
-        <v>24950</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="43" t="inlineStr">
-        <is>
-          <t>MOMENTUL 1 — diferența la plată</t>
-        </is>
-      </c>
-      <c r="B29" s="43">
-        <f>B28-B27</f>
-        <v>100</v>
-      </c>
-      <c r="C29" s="44" t="inlineStr">
-        <is>
-          <t>Pozitiv = nefavorabil (665); negativ = favorabil (765)</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="43" t="inlineStr">
-        <is>
-          <t>Dobânda, în lei</t>
-        </is>
-      </c>
-      <c r="B30" s="43">
-        <f>ROUND(B19*B20,2)</f>
-        <v>998</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="43" t="inlineStr">
-        <is>
-          <t>Sold rămas, în valută</t>
-        </is>
-      </c>
-      <c r="B31" s="43">
-        <f>B13-B18</f>
-        <v>15000</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="43" t="inlineStr">
-        <is>
-          <t>Sold rămas, la cursul de înregistrare</t>
-        </is>
-      </c>
-      <c r="B32" s="43">
-        <f>ROUND(B31*B14,2)</f>
-        <v>74550</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="43" t="inlineStr">
-        <is>
-          <t>Sold rămas, la cursul BNR</t>
-        </is>
-      </c>
-      <c r="B33" s="43">
-        <f>ROUND(B31*B24,2)</f>
-        <v>75150</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="43" t="inlineStr">
-        <is>
-          <t>MOMENTUL 2 — diferența din reevaluare</t>
-        </is>
-      </c>
-      <c r="B34" s="43">
-        <f>B33-B32</f>
-        <v>600</v>
-      </c>
-      <c r="C34" s="44" t="inlineStr">
-        <is>
-          <t>Pozitiv = datoria crește = nefavorabil (665)</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="42" t="inlineStr">
-        <is>
-          <t>6. Conturi</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="43" t="inlineStr">
-        <is>
-          <t>Cont credit (162x)</t>
-        </is>
-      </c>
-      <c r="B37" s="64" t="inlineStr">
-        <is>
-          <t>1621</t>
-        </is>
-      </c>
-      <c r="C37" s="44" t="inlineStr">
-        <is>
-          <t>1621…1627 sunt sintetice DISTINCTE, nu analitice ale aceluiași cont</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="43" t="inlineStr">
-        <is>
-          <t>Cont dobândă neajunsă la scadență</t>
-        </is>
-      </c>
-      <c r="B38" s="64" t="n">
-        <v>1682</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="43" t="inlineStr">
-        <is>
-          <t>Cont trezorerie în valută</t>
-        </is>
-      </c>
-      <c r="B39" s="64" t="inlineStr">
-        <is>
-          <t>5124</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="43" t="inlineStr">
-        <is>
-          <t>Cont trezorerie în lei</t>
-        </is>
-      </c>
-      <c r="B40" s="64" t="inlineStr">
-        <is>
-          <t>5121</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="43" t="inlineStr">
-        <is>
-          <t>Cont cheltuială cu dobânda</t>
-        </is>
-      </c>
-      <c r="B41" s="64" t="n">
-        <v>666</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="43" t="inlineStr">
-        <is>
-          <t>Cont cheltuială cu serviciile bancare</t>
-        </is>
-      </c>
-      <c r="B42" s="64" t="n">
-        <v>627</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="43" t="inlineStr">
-        <is>
-          <t>Cont diferențe nefavorabile</t>
-        </is>
-      </c>
-      <c r="B43" s="64" t="n">
-        <v>665</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="43" t="inlineStr">
-        <is>
-          <t>Cont diferențe favorabile</t>
-        </is>
-      </c>
-      <c r="B44" s="64" t="n">
-        <v>765</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="42" t="inlineStr">
-        <is>
-          <t>7. Controale</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="43" t="inlineStr">
-        <is>
-          <t>Check FINAL: sold lei = sold valută × curs BNR</t>
-        </is>
-      </c>
-      <c r="B47" s="43">
-        <f>B32+B34-B33</f>
-        <v>0</v>
-      </c>
-      <c r="C47" s="43" t="str">
-        <f>IF(ABS(B47)&lt;0.01,"OK — soldul în lei corespunde soldului în valută","EROARE — una dintre cele două diferențe de curs lipsește")</f>
-        <v>OK — soldul în lei corespunde soldului în valută</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="43" t="inlineStr">
-        <is>
-          <t>Check cele două momente sunt distincte</t>
-        </is>
-      </c>
-      <c r="B48" s="43">
-        <f>B29+B34</f>
-        <v>700</v>
-      </c>
-      <c r="C48" s="43" t="str">
-        <f>"Momentul 1 (la plată): " &amp; TEXT(B29,"0.00") &amp; " lei · Momentul 2 (reevaluare): " &amp; TEXT(B34,"0.00") &amp; " lei"</f>
-        <v>Momentul 1 (la plată): 100.00 lei · Momentul 2 (reevaluare): 600.00 lei</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="43" t="inlineStr">
-        <is>
-          <t>Reminder: rata și dobânda vin din scadențar</t>
-        </is>
-      </c>
-      <c r="B49" s="43">
-        <f>B18+B19</f>
-        <v>5200</v>
-      </c>
-      <c r="C49" s="43" t="str">
-        <f>"Extrasul arată deseori B18+B19 cumulat. Dacă le înregistrezi așa, ajungi cu 1621 pe debit sau cu sold rămas la finalul creditului."</f>
-        <v>Extrasul arată deseori B18+B19 cumulat. Dacă le înregistrezi așa, ajungi cu 1621 pe debit sau cu sold rămas la finalul creditului.</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="43" t="inlineStr">
-        <is>
-          <t>Reminder: reevaluarea e LUNARĂ</t>
-        </is>
-      </c>
-      <c r="B50" s="43" t="str">
-        <f>B9</f>
-        <v>2026-07-31</v>
-      </c>
-      <c r="C50" s="43" t="str">
-        <f>"Obligatorie lunar (OMFP 1802/2014), nu trimestrial. Verifică și soldul ÎN VALUTĂ, nu doar în lei."</f>
-        <v>Obligatorie lunar (OMFP 1802/2014), nu trimestrial. Verifică și soldul ÎN VALUTĂ, nu doar în lei.</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="43" t="inlineStr">
-        <is>
-          <t>Reminder bilanț</t>
-        </is>
-      </c>
-      <c r="B51" s="43">
-        <f>B31</f>
-        <v>15000</v>
-      </c>
-      <c r="C51" s="43" t="str">
-        <f>"Reclasifică porțiunea scadentă în ≤ 12 luni pentru bilanț, prin analitic sau cont dedicat. Dobânda calculată și neajunsă la scadență stă pe 1682."</f>
-        <v>Reclasifică porțiunea scadentă în ≤ 12 luni pentru bilanț, prin analitic sau cont dedicat. Dobânda calculată și neajunsă la scadență stă pe 1682.</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="42" t="inlineStr">
-        <is>
-          <t>8. Sufix generat</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="43" t="inlineStr">
-        <is>
-          <t>Sufix</t>
-        </is>
-      </c>
-      <c r="B54" s="43" t="str">
-        <f>" - " &amp; B6 &amp; " - " &amp; B7</f>
-        <v> - CR-2026-001 - 2026-07</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet80.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet84.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>

--- a/dist/Module_Declarative_Fluxuri.xlsx
+++ b/dist/Module_Declarative_Fluxuri.xlsx
@@ -63,34 +63,38 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reguli_APROV_TRANZIT" sheetId="54" state="visible" r:id="rId54"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Jurnale_APROV_TRANZIT" sheetId="55" state="visible" r:id="rId55"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NotaExport_APROV_TRANZIT" sheetId="56" state="visible" r:id="rId56"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Declarații_INCHIDERE_EX" sheetId="57" state="visible" r:id="rId57"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reguli_INCHIDERE_EX" sheetId="58" state="visible" r:id="rId58"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Jurnale_INCHIDERE_EX" sheetId="59" state="visible" r:id="rId59"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NotaExport_INCHIDERE_EX" sheetId="60" state="visible" r:id="rId60"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Declarații_TVA_INC" sheetId="61" state="visible" r:id="rId61"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reguli_TVA_INC" sheetId="62" state="visible" r:id="rId62"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Jurnale_TVA_INC" sheetId="63" state="visible" r:id="rId63"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NotaExport_TVA_INC" sheetId="64" state="visible" r:id="rId64"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Declarații_TAXARE_INVERSA" sheetId="65" state="visible" r:id="rId65"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reguli_TAXARE_INVERSA" sheetId="66" state="visible" r:id="rId66"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Jurnale_TAXARE_INVERSA" sheetId="67" state="visible" r:id="rId67"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NotaExport_TAXARE_INVERSA" sheetId="68" state="visible" r:id="rId68"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Declarații_FARA_DOCUMENT" sheetId="69" state="visible" r:id="rId69"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reguli_FARA_DOCUMENT" sheetId="70" state="visible" r:id="rId70"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Jurnale_FARA_DOCUMENT" sheetId="71" state="visible" r:id="rId71"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NotaExport_FARA_DOCUMENT" sheetId="72" state="visible" r:id="rId72"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Declarații_NEUTRALIZARE" sheetId="73" state="visible" r:id="rId73"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reguli_NEUTRALIZARE" sheetId="74" state="visible" r:id="rId74"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Jurnale_NEUTRALIZARE" sheetId="75" state="visible" r:id="rId75"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NotaExport_NEUTRALIZARE" sheetId="76" state="visible" r:id="rId76"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Declarații_AMANUNT" sheetId="77" state="visible" r:id="rId77"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reguli_AMANUNT" sheetId="78" state="visible" r:id="rId78"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Jurnale_AMANUNT" sheetId="79" state="visible" r:id="rId79"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NotaExport_AMANUNT" sheetId="80" state="visible" r:id="rId80"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Declarații_INCHIDERE_LUNARA" sheetId="81" state="visible" r:id="rId81"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reguli_INCHIDERE_LUNARA" sheetId="82" state="visible" r:id="rId82"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Verificări_INCHIDERE_LUNARA" sheetId="83" state="visible" r:id="rId83"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Abateri_INCHIDERE_LUNARA" sheetId="84" state="visible" r:id="rId84"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Declarații_IMPORT" sheetId="57" state="visible" r:id="rId57"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reguli_IMPORT" sheetId="58" state="visible" r:id="rId58"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Jurnale_IMPORT" sheetId="59" state="visible" r:id="rId59"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NotaExport_IMPORT" sheetId="60" state="visible" r:id="rId60"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Declarații_INCHIDERE_EX" sheetId="61" state="visible" r:id="rId61"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reguli_INCHIDERE_EX" sheetId="62" state="visible" r:id="rId62"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Jurnale_INCHIDERE_EX" sheetId="63" state="visible" r:id="rId63"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NotaExport_INCHIDERE_EX" sheetId="64" state="visible" r:id="rId64"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Declarații_TVA_INC" sheetId="65" state="visible" r:id="rId65"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reguli_TVA_INC" sheetId="66" state="visible" r:id="rId66"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Jurnale_TVA_INC" sheetId="67" state="visible" r:id="rId67"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NotaExport_TVA_INC" sheetId="68" state="visible" r:id="rId68"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Declarații_TAXARE_INVERSA" sheetId="69" state="visible" r:id="rId69"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reguli_TAXARE_INVERSA" sheetId="70" state="visible" r:id="rId70"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Jurnale_TAXARE_INVERSA" sheetId="71" state="visible" r:id="rId71"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NotaExport_TAXARE_INVERSA" sheetId="72" state="visible" r:id="rId72"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Declarații_FARA_DOCUMENT" sheetId="73" state="visible" r:id="rId73"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reguli_FARA_DOCUMENT" sheetId="74" state="visible" r:id="rId74"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Jurnale_FARA_DOCUMENT" sheetId="75" state="visible" r:id="rId75"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NotaExport_FARA_DOCUMENT" sheetId="76" state="visible" r:id="rId76"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Declarații_NEUTRALIZARE" sheetId="77" state="visible" r:id="rId77"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reguli_NEUTRALIZARE" sheetId="78" state="visible" r:id="rId78"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Jurnale_NEUTRALIZARE" sheetId="79" state="visible" r:id="rId79"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NotaExport_NEUTRALIZARE" sheetId="80" state="visible" r:id="rId80"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Declarații_AMANUNT" sheetId="81" state="visible" r:id="rId81"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reguli_AMANUNT" sheetId="82" state="visible" r:id="rId82"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Jurnale_AMANUNT" sheetId="83" state="visible" r:id="rId83"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NotaExport_AMANUNT" sheetId="84" state="visible" r:id="rId84"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Declarații_INCHIDERE_LUNARA" sheetId="85" state="visible" r:id="rId85"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reguli_INCHIDERE_LUNARA" sheetId="86" state="visible" r:id="rId86"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Verificări_INCHIDERE_LUNARA" sheetId="87" state="visible" r:id="rId87"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Abateri_INCHIDERE_LUNARA" sheetId="88" state="visible" r:id="rId88"/>
   </sheets>
   <definedNames>
     <definedName name="param_proc_rezerva">Parametri!$B$18</definedName>
@@ -836,7 +840,7 @@
     <row r="4" ht="15" customHeight="1" s="40">
       <c r="A4" s="43" t="inlineStr">
         <is>
-          <t>Cele 20 module declarative care execută fluxurile din „Plan de conturi”. Fluxul explică de ce; modulul face înregistrarea. Completezi câteva variabile într-o foaie de input și ies jurnalele și nota de export.</t>
+          <t>Cele 21 module declarative care execută fluxurile din „Plan de conturi”. Fluxul explică de ce; modulul face înregistrarea. Completezi câteva variabile într-o foaie de input și ies jurnalele și nota de export.</t>
         </is>
       </c>
     </row>
@@ -10959,7 +10963,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:H33"/>
+  <dimension ref="A1:H34"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="8" customWidth="1" style="39" min="1" max="1"/>
@@ -11757,32 +11761,32 @@
       </c>
       <c r="B24" s="61" t="inlineStr">
         <is>
-          <t>MOD_TAXARE_INVERSA</t>
+          <t>MOD_IMPORT</t>
         </is>
       </c>
       <c r="C24" s="61" t="inlineStr">
         <is>
-          <t>F-303, F-402</t>
+          <t>F-319, F-320</t>
         </is>
       </c>
       <c r="D24" s="61" t="inlineStr">
         <is>
-          <t>Pe factură</t>
+          <t>Pe declarație vamală</t>
         </is>
       </c>
       <c r="E24" s="61" t="inlineStr">
         <is>
-          <t>Valoare (sau valută × curs), cota TVA, tipul operațiunii, partenerul</t>
+          <t>Valoarea mărfii, taxele vamale, transportul intern, cota TVA, calea (comisionar sau plată directă)</t>
         </is>
       </c>
       <c r="F24" s="61" t="inlineStr">
         <is>
-          <t>4426 = 4427 exact; D390 doar la intracomunitar</t>
+          <t>Baza TVA = marfă + taxe vamale, fără transportul intern; 446.VAMA sold 0</t>
         </is>
       </c>
       <c r="G24" s="61" t="inlineStr">
         <is>
-          <t>A Achiziție intracomunitară; B Taxare inversă internă</t>
+          <t>A Import prin comisionar (446.VAMA); B Import cu plată directă în vamă</t>
         </is>
       </c>
       <c r="H24" s="61" t="inlineStr">
@@ -11799,119 +11803,161 @@
       </c>
       <c r="B25" s="61" t="inlineStr">
         <is>
+          <t>MOD_TAXARE_INVERSA</t>
+        </is>
+      </c>
+      <c r="C25" s="61" t="inlineStr">
+        <is>
+          <t>F-303, F-402</t>
+        </is>
+      </c>
+      <c r="D25" s="61" t="inlineStr">
+        <is>
+          <t>Pe factură</t>
+        </is>
+      </c>
+      <c r="E25" s="61" t="inlineStr">
+        <is>
+          <t>Valoare (sau valută × curs), cota TVA, tipul operațiunii, partenerul</t>
+        </is>
+      </c>
+      <c r="F25" s="61" t="inlineStr">
+        <is>
+          <t>4426 = 4427 exact; D390 doar la intracomunitar</t>
+        </is>
+      </c>
+      <c r="G25" s="61" t="inlineStr">
+        <is>
+          <t>A Achiziție intracomunitară; B Taxare inversă internă</t>
+        </is>
+      </c>
+      <c r="H25" s="61" t="inlineStr">
+        <is>
+          <t>IMPLEMENTAT</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="60" t="inlineStr">
+        <is>
+          <t>NU</t>
+        </is>
+      </c>
+      <c r="B26" s="61" t="inlineStr">
+        <is>
           <t>MOD_FARA_DOCUMENT</t>
         </is>
       </c>
-      <c r="C25" s="61" t="inlineStr">
+      <c r="C26" s="61" t="inlineStr">
         <is>
           <t>F-406</t>
         </is>
       </c>
-      <c r="D25" s="61" t="inlineStr">
+      <c r="D26" s="61" t="inlineStr">
         <is>
           <t>Pe eveniment</t>
         </is>
       </c>
-      <c r="E25" s="61" t="inlineStr">
+      <c r="E26" s="61" t="inlineStr">
         <is>
           <t>Valoare factură și cota, pentru vehicul; costul lipsei la inventar</t>
         </is>
       </c>
-      <c r="F25" s="61" t="inlineStr">
+      <c r="F26" s="61" t="inlineStr">
         <is>
           <t>Procentul de deducere vine din param_proc_vehicul; 4427 se creditează la lipsă</t>
         </is>
       </c>
-      <c r="G25" s="61" t="inlineStr">
+      <c r="G26" s="61" t="inlineStr">
         <is>
           <t>A Vehicul cu regim mixt (50%); B Lipsă la inventar nejustificată</t>
         </is>
       </c>
-      <c r="H25" s="61" t="inlineStr">
+      <c r="H26" s="61" t="inlineStr">
         <is>
           <t>IMPLEMENTAT</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="62" t="inlineStr">
+    <row r="27">
+      <c r="A27" s="62" t="inlineStr">
         <is>
           <t>DA</t>
         </is>
       </c>
-      <c r="B26" s="61" t="inlineStr">
+      <c r="B27" s="61" t="inlineStr">
         <is>
           <t>MOD_INCHIDERE_LUNARA</t>
         </is>
       </c>
-      <c r="C26" s="61" t="inlineStr">
+      <c r="C27" s="61" t="inlineStr">
         <is>
           <t>F-422, F-413</t>
         </is>
       </c>
-      <c r="D26" s="61" t="inlineStr">
+      <c r="D27" s="61" t="inlineStr">
         <is>
           <t>Lunar, pe balanța de verificare</t>
         </is>
       </c>
-      <c r="E26" s="61" t="inlineStr">
+      <c r="E27" s="61" t="inlineStr">
         <is>
           <t>Rulaj debitor, rulaj creditor și sold pentru conturile cu cadență; restul de plată de pe stat; soldul din decontul de TVA</t>
         </is>
       </c>
-      <c r="F26" s="61" t="inlineStr">
+      <c r="F27" s="61" t="inlineStr">
         <is>
           <t>Verifică solduri, nu documente — vezi Reguli, tabelul C</t>
         </is>
       </c>
-      <c r="G26" s="61" t="inlineStr">
+      <c r="G27" s="61" t="inlineStr">
         <is>
           <t>V1 Obligații lunare (rulaj = sold); V2 Datoria față de salariați; V3 Conturi care trebuie golite; V4 Verificarea CAM pe cifre</t>
         </is>
       </c>
-      <c r="H26" s="61" t="inlineStr">
+      <c r="H27" s="61" t="inlineStr">
         <is>
           <t>IMPLEMENTAT</t>
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="63" t="inlineStr">
+    <row r="29">
+      <c r="A29" s="63" t="inlineStr">
         <is>
           <t>REGULĂ DE SUMONARE</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="46" t="inlineStr">
-        <is>
-          <t>1. În CatalogModule setezi Activ=DA doar pe modulele necesare lunii.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="46" t="inlineStr">
         <is>
-          <t>2. Completezi variabilele din foaia Declarații_Modul (galben).</t>
+          <t>1. În CatalogModule setezi Activ=DA doar pe modulele necesare lunii.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="46" t="inlineStr">
         <is>
-          <t>3. Jurnalele și NotaExport se populează automat doar pentru modulele active.</t>
+          <t>2. Completezi variabilele din foaia Declarații_Modul (galben).</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="46" t="inlineStr">
         <is>
-          <t>4. Verifici Check=0 pe fiecare bloc; filtrezi NotaExport pe Include=DA și imporți.</t>
+          <t>3. Jurnalele și NotaExport se populează automat doar pentru modulele active.</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="46" t="inlineStr">
+        <is>
+          <t>4. Verifici Check=0 pe fiecare bloc; filtrezi NotaExport pe Include=DA și imporți.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="46" t="inlineStr">
         <is>
           <t>Nu se creează conturi noi din modul — se folosesc doar conturile din politica declarată + planul de conturi pe rol.</t>
         </is>
@@ -11923,11 +11969,11 @@
     <mergeCell ref="A30:H30"/>
     <mergeCell ref="A29:H29"/>
     <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A28:H28"/>
     <mergeCell ref="A33:H33"/>
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="A32:H32"/>
     <mergeCell ref="A31:H31"/>
+    <mergeCell ref="A34:H34"/>
   </mergeCells>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -24885,25 +24931,25 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B38"/>
+  <dimension ref="A1:C47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="48" customWidth="1" style="40" min="1" max="1"/>
-    <col width="26" customWidth="1" style="40" min="2" max="2"/>
-    <col width="56" customWidth="1" style="40" min="3" max="3"/>
+    <col width="50" customWidth="1" style="40" min="1" max="1"/>
+    <col width="22" customWidth="1" style="40" min="2" max="2"/>
+    <col width="60" customWidth="1" style="40" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="41" t="inlineStr">
         <is>
-          <t>MOD_INCHIDERE_EX — Declarații (input)</t>
+          <t>MOD_IMPORT — Declarații (input)</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="44" t="inlineStr">
         <is>
-          <t>Modul anual. Completezi rulajele din balanță (sau totaluri din SAGA). Jurnalele închid cls.6 → 121, cls.7 → 121, calculează impozit / IMCA, repartizează 129 și reportează 117.</t>
+          <t>Două căi alternative. De regulă se aplică una singură pe un import — pune DA pe cea folosită.</t>
         </is>
       </c>
     </row>
@@ -24939,265 +24985,405 @@
     <row r="7">
       <c r="A7" s="43" t="inlineStr">
         <is>
-          <t>An exercițiu</t>
-        </is>
-      </c>
-      <c r="B7" s="64" t="n">
-        <v>2026</v>
+          <t>Luna (AAAA-LL)</t>
+        </is>
+      </c>
+      <c r="B7" s="64" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="43" t="inlineStr">
         <is>
-          <t>Data jurnal închidere (31.12)</t>
+          <t>Data jurnal (DVI)</t>
         </is>
       </c>
       <c r="B8" s="64" t="inlineStr">
         <is>
-          <t>2026-12-31</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="42" t="inlineStr">
-        <is>
-          <t>2. Rulaje de închis (din balanță / totaluri SAGA)</t>
-        </is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="43" t="inlineStr">
+        <is>
+          <t>Cota TVA</t>
+        </is>
+      </c>
+      <c r="B9" s="64" t="n">
+        <v>0.21</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="43" t="inlineStr">
-        <is>
-          <t>Total rulaj debitor cls.6 (cheltuieli)</t>
-        </is>
-      </c>
-      <c r="B11" s="64" t="n">
-        <v>185000</v>
+      <c r="A11" s="42" t="inlineStr">
+        <is>
+          <t>2. Calea A — Import prin comisionar</t>
+        </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="43" t="inlineStr">
         <is>
-          <t>Total rulaj creditor cls.7 (venituri)</t>
-        </is>
-      </c>
-      <c r="B12" s="64" t="n">
-        <v>245000</v>
+          <t>Se aplică? (DA/NU)</t>
+        </is>
+      </c>
+      <c r="B12" s="64" t="inlineStr">
+        <is>
+          <t>DA</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="43" t="inlineStr">
+        <is>
+          <t>Furnizor extern</t>
+        </is>
+      </c>
+      <c r="B13" s="64" t="inlineStr">
+        <is>
+          <t>Furnizor EXT DEMO</t>
+        </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="42" t="inlineStr">
-        <is>
-          <t>3. Impozit pe profit / IMCA</t>
+      <c r="A14" s="43" t="inlineStr">
+        <is>
+          <t>Comisionar vamal</t>
+        </is>
+      </c>
+      <c r="B14" s="64" t="inlineStr">
+        <is>
+          <t>Comisionar DEMO</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="43" t="inlineStr">
         <is>
-          <t>Regim (PROFIT / MICRO / IMCA)</t>
-        </is>
-      </c>
-      <c r="B15" s="64" t="inlineStr">
-        <is>
-          <t>PROFIT</t>
+          <t>Valoarea mărfii (lei)</t>
+        </is>
+      </c>
+      <c r="B15" s="64" t="n">
+        <v>100000</v>
+      </c>
+      <c r="C15" s="44" t="inlineStr">
+        <is>
+          <t>15.000–20.000 EUR × cursul de la data DVI</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="43" t="inlineStr">
         <is>
-          <t>Baza impozabilă (sau cifră afaceri IMCA)</t>
+          <t>Taxe vamale</t>
         </is>
       </c>
       <c r="B16" s="64" t="n">
-        <v>60000</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="43" t="inlineStr">
         <is>
-          <t>Cotă (0.16 / 0.01 / 0.03 etc.)</t>
+          <t>Transport INTERN (după vămuire)</t>
         </is>
       </c>
       <c r="B17" s="64" t="n">
-        <v>0.16</v>
+        <v>2000</v>
+      </c>
+      <c r="C17" s="44" t="inlineStr">
+        <is>
+          <t>Intră în COST, dar NU în baza TVA vamală</t>
+        </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="43" t="inlineStr">
         <is>
-          <t>Impozit calculat</t>
+          <t>Baza TVA vamală (auto) = marfă + taxe</t>
         </is>
       </c>
       <c r="B18" s="43">
-        <f>B16*B17</f>
-        <v>9600</v>
+        <f>B15+B16</f>
+        <v>103000</v>
+      </c>
+      <c r="C18" s="44" t="inlineStr">
+        <is>
+          <t>Fără transportul intern — acela are TVA-ul lui pe factura transportatorului</t>
+        </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="43" t="inlineStr">
         <is>
-          <t>Cont cheltuială impozit (691 / 697 / 4417)</t>
-        </is>
-      </c>
-      <c r="B19" s="64" t="inlineStr">
-        <is>
-          <t>691</t>
-        </is>
+          <t>TVA vamală (auto)</t>
+        </is>
+      </c>
+      <c r="B19" s="43">
+        <f>ROUND(B18*B9,2)</f>
+        <v>21630</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="43" t="inlineStr">
         <is>
-          <t>Cont datorie impozit (441 / 4417)</t>
-        </is>
-      </c>
-      <c r="B20" s="64" t="inlineStr">
-        <is>
-          <t>441</t>
-        </is>
+          <t>Costul final al stocului (auto)</t>
+        </is>
+      </c>
+      <c r="B20" s="43">
+        <f>B15+B16+B17</f>
+        <v>105000</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="42" t="inlineStr">
         <is>
-          <t>4. Repartizare rezultat</t>
+          <t>3. Calea B — Import cu plată directă în vamă</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="43" t="inlineStr">
         <is>
-          <t>Rezultat înainte de impozit (7−6)</t>
-        </is>
-      </c>
-      <c r="B23" s="43">
-        <f>B12-B11</f>
-        <v>60000</v>
+          <t>Se aplică? (DA/NU)</t>
+        </is>
+      </c>
+      <c r="B23" s="64" t="inlineStr">
+        <is>
+          <t>DA</t>
+        </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="43" t="inlineStr">
         <is>
-          <t>Rezultat net (după impozit)</t>
-        </is>
-      </c>
-      <c r="B24" s="43">
-        <f>B23-B18</f>
-        <v>50400</v>
+          <t>Furnizor extern</t>
+        </is>
+      </c>
+      <c r="B24" s="64" t="inlineStr">
+        <is>
+          <t>Furnizor EXT DEMO 2</t>
+        </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="43" t="inlineStr">
         <is>
-          <t>Repartizare la rezerve / dividende etc. (opțional)</t>
+          <t>Valoarea mărfii (lei)</t>
         </is>
       </c>
       <c r="B25" s="64" t="n">
-        <v>0</v>
+        <v>50000</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="43" t="inlineStr">
         <is>
-          <t>Reportat pe 117 (sold final 121/129)</t>
-        </is>
-      </c>
-      <c r="B26" s="43">
-        <f>B24-B25</f>
-        <v>50400</v>
+          <t>Taxe vamale (plătite direct)</t>
+        </is>
+      </c>
+      <c r="B26" s="64" t="n">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="43" t="inlineStr">
+        <is>
+          <t>Baza TVA vamală (auto) = marfă + taxe</t>
+        </is>
+      </c>
+      <c r="B27" s="43">
+        <f>B25+B26</f>
+        <v>52000</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="42" t="inlineStr">
-        <is>
-          <t>5. Politică conturi rezultat</t>
-        </is>
+      <c r="A28" s="43" t="inlineStr">
+        <is>
+          <t>TVA vamală (auto)</t>
+        </is>
+      </c>
+      <c r="B28" s="43">
+        <f>ROUND(B27*B9,2)</f>
+        <v>10920</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="43" t="inlineStr">
         <is>
-          <t>Cont profit și pierdere</t>
-        </is>
-      </c>
-      <c r="B29" s="64" t="inlineStr">
-        <is>
-          <t>121</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="43" t="inlineStr">
-        <is>
-          <t>Cont repartizare profit</t>
-        </is>
-      </c>
-      <c r="B30" s="64" t="inlineStr">
-        <is>
-          <t>129</t>
-        </is>
+          <t>Costul final al stocului (auto)</t>
+        </is>
+      </c>
+      <c r="B29" s="43">
+        <f>B25+B26</f>
+        <v>52000</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="43" t="inlineStr">
-        <is>
-          <t>Cont rezultat reportat</t>
-        </is>
-      </c>
-      <c r="B31" s="64" t="inlineStr">
-        <is>
-          <t>117</t>
+      <c r="A31" s="42" t="inlineStr">
+        <is>
+          <t>4. Conturi</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="43" t="inlineStr">
+        <is>
+          <t>Cont stoc</t>
+        </is>
+      </c>
+      <c r="B32" s="64" t="inlineStr">
+        <is>
+          <t>371</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="42" t="inlineStr">
-        <is>
-          <t>6. Sufix</t>
+      <c r="A33" s="43" t="inlineStr">
+        <is>
+          <t>Furnizor extern</t>
+        </is>
+      </c>
+      <c r="B33" s="64" t="inlineStr">
+        <is>
+          <t>401.EXT</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="43" t="inlineStr">
         <is>
-          <t>Sufix</t>
-        </is>
-      </c>
-      <c r="B34" s="43" t="str">
-        <f>"— închidere exercițiu " &amp; B7</f>
-        <v>— închidere exercițiu 2026</v>
+          <t>Intermediar TVA vamală</t>
+        </is>
+      </c>
+      <c r="B34" s="64" t="inlineStr">
+        <is>
+          <t>446.VAMA</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="43" t="inlineStr">
+        <is>
+          <t>Furnizor comisionar</t>
+        </is>
+      </c>
+      <c r="B35" s="64" t="inlineStr">
+        <is>
+          <t>401</t>
+        </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="42" t="inlineStr">
-        <is>
-          <t>7. Control</t>
+      <c r="A36" s="43" t="inlineStr">
+        <is>
+          <t>Furnizor intern / transport</t>
+        </is>
+      </c>
+      <c r="B36" s="64" t="inlineStr">
+        <is>
+          <t>401.RO</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="43" t="inlineStr">
         <is>
-          <t>Modul activ?</t>
-        </is>
-      </c>
-      <c r="B37" s="43" t="str">
-        <f>IF(INDEX(CatalogModule!$A$1:$A$200,MATCH("MOD_INCHIDERE_EX",CatalogModule!$B$1:$B$200,0))="DA","ACTIV","INACTIV")</f>
-        <v>INACTIV</v>
+          <t>TVA deductibilă</t>
+        </is>
+      </c>
+      <c r="B37" s="64" t="inlineStr">
+        <is>
+          <t>4426</t>
+        </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="43" t="inlineStr">
         <is>
-          <t>Notă</t>
-        </is>
-      </c>
-      <c r="B38" s="43" t="inlineStr">
-        <is>
-          <t>În practică se închid conturile de cheltuieli/venituri pe analitice (sau pe grupe). Aici se lucrează pe totaluri — un singur rând pe clasă.</t>
-        </is>
+          <t>Bancă</t>
+        </is>
+      </c>
+      <c r="B38" s="64" t="inlineStr">
+        <is>
+          <t>512.1</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="42" t="inlineStr">
+        <is>
+          <t>5. Sufix</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="43" t="inlineStr">
+        <is>
+          <t>Sufix</t>
+        </is>
+      </c>
+      <c r="B41" s="43" t="str">
+        <f>"— import " &amp; B7</f>
+        <v>— import 2026-07</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="42" t="inlineStr">
+        <is>
+          <t>6. Control</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="43" t="inlineStr">
+        <is>
+          <t>Modul activ?</t>
+        </is>
+      </c>
+      <c r="B44" s="43" t="str">
+        <f>IF(INDEX(CatalogModule!$A$1:$A$200,MATCH("MOD_IMPORT",CatalogModule!$B$1:$B$200,0))="DA","ACTIV","INACTIV")</f>
+        <v>INACTIV</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="43" t="inlineStr">
+        <is>
+          <t>Verificare: baza TVA exclude transportul intern</t>
+        </is>
+      </c>
+      <c r="B45" s="43" t="str">
+        <f>IF(OR(B12&lt;&gt;"DA",ABS(B18-(B20-B17))&lt;0.01),"OK — baza = marfă + taxe, fără transportul intern","EROARE — transportul intern a intrat în baza TVA")</f>
+        <v>OK — baza = marfă + taxe, fără transportul intern</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="43" t="inlineStr">
+        <is>
+          <t>Cât ar costa greșeala (informativ)</t>
+        </is>
+      </c>
+      <c r="B46" s="43" t="str">
+        <f>IF(B12="DA","TVA calculată pe cost în loc de bază: +" &amp; TEXT(ROUND(B17*B9,2),"0.00") &amp; " lei dedusă de două ori","—")</f>
+        <v>TVA calculată pe cost în loc de bază: +420.00 lei dedusă de două ori</v>
+      </c>
+      <c r="C46" s="44" t="inlineStr">
+        <is>
+          <t>Transportul intern are deja TVA pe factura transportatorului</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="43" t="inlineStr">
+        <is>
+          <t>Cale aleasă</t>
+        </is>
+      </c>
+      <c r="B47" s="43" t="str">
+        <f>IF(AND(B12="DA",B23="DA"),"ATENȚIE — de regulă un import merge pe o singură cale",IF(B12="DA","Prin comisionar — 446.VAMA se stinge",IF(B23="DA","Plată directă — fără intermediar","—")))</f>
+        <v>ATENȚIE — de regulă un import merge pe o singură cale</v>
       </c>
     </row>
   </sheetData>
@@ -25211,472 +25397,309 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F28"/>
+  <dimension ref="A1:D24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="8" customWidth="1" style="40" min="1" max="1"/>
-    <col width="30" customWidth="1" style="40" min="2" max="2"/>
-    <col width="16" customWidth="1" style="40" min="3" max="3"/>
-    <col width="18" customWidth="1" style="40" min="4" max="4"/>
-    <col width="20" customWidth="1" style="40" min="5" max="5"/>
-    <col width="48" customWidth="1" style="40" min="6" max="6"/>
+    <col width="44" customWidth="1" style="40" min="1" max="1"/>
+    <col width="16" customWidth="1" style="40" min="2" max="2"/>
+    <col width="22" customWidth="1" style="40" min="3" max="3"/>
+    <col width="58" customWidth="1" style="40" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="41" t="inlineStr">
         <is>
-          <t>MOD_INCHIDERE_EX — Reguli (tabele fixe)</t>
+          <t>MOD_IMPORT — Reguli (tabele fixe)</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="44" t="inlineStr">
         <is>
-          <t>Secvența de închidere e standard OMFP 1802. Detalierea pe conturi analitice se face în SAGA; modulul lucrează pe totaluri de clasă pentru generarea notei de principiu.</t>
+          <t>Regula e dată, nu formulă. Tabelul A e cel care se citește cel mai des: spune ce intră unde.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="42" t="inlineStr">
         <is>
-          <t>Tabel A — Secvența de închidere</t>
+          <t>Tabel A — Ce intră în cost și ce intră în baza TVA vamală</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="65" t="inlineStr">
         <is>
-          <t>Pas</t>
+          <t>Element</t>
         </is>
       </c>
       <c r="B5" s="65" t="inlineStr">
         <is>
-          <t>Bloc</t>
+          <t>În cost?</t>
         </is>
       </c>
       <c r="C5" s="65" t="inlineStr">
         <is>
-          <t>Cont Dr</t>
+          <t>În baza TVA?</t>
         </is>
       </c>
       <c r="D5" s="65" t="inlineStr">
         <is>
-          <t>Cont Cr</t>
-        </is>
-      </c>
-      <c r="E5" s="65" t="inlineStr">
-        <is>
-          <t>Sumă</t>
-        </is>
-      </c>
-      <c r="F5" s="65" t="inlineStr">
-        <is>
           <t>Observație</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="43" t="n">
-        <v>1</v>
+      <c r="A6" s="43" t="inlineStr">
+        <is>
+          <t>Valoarea mărfii de pe factura externă</t>
+        </is>
       </c>
       <c r="B6" s="43" t="inlineStr">
         <is>
-          <t>B1 Închidere cheltuieli</t>
+          <t>DA</t>
         </is>
       </c>
       <c r="C6" s="43" t="inlineStr">
         <is>
-          <t>121</t>
+          <t>DA</t>
         </is>
       </c>
       <c r="D6" s="43" t="inlineStr">
         <is>
-          <t>6xx (total)</t>
-        </is>
-      </c>
-      <c r="E6" s="43" t="inlineStr">
-        <is>
-          <t>Rulaj D cls.6</t>
-        </is>
-      </c>
-      <c r="F6" s="43" t="inlineStr">
-        <is>
-          <t>Neutralizare rezultat — cheltuieli</t>
+          <t>Convertită la cursul de la data DVI</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="43" t="n">
-        <v>2</v>
+      <c r="A7" s="43" t="inlineStr">
+        <is>
+          <t>Taxe vamale</t>
+        </is>
       </c>
       <c r="B7" s="43" t="inlineStr">
         <is>
-          <t>B2 Închidere venituri</t>
+          <t>DA</t>
         </is>
       </c>
       <c r="C7" s="43" t="inlineStr">
         <is>
-          <t>7xx (total)</t>
+          <t>DA</t>
         </is>
       </c>
       <c r="D7" s="43" t="inlineStr">
         <is>
-          <t>121</t>
-        </is>
-      </c>
-      <c r="E7" s="43" t="inlineStr">
-        <is>
-          <t>Rulaj C cls.7</t>
-        </is>
-      </c>
-      <c r="F7" s="43" t="inlineStr">
-        <is>
-          <t>Neutralizare rezultat — venituri</t>
+          <t>Sunt parte din baza de impozitare la import</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="43" t="n">
-        <v>3</v>
+      <c r="A8" s="43" t="inlineStr">
+        <is>
+          <t>Comisioane vamale, taxe de manipulare</t>
+        </is>
       </c>
       <c r="B8" s="43" t="inlineStr">
         <is>
-          <t>B3 Impozit</t>
+          <t>DA</t>
         </is>
       </c>
       <c r="C8" s="43" t="inlineStr">
         <is>
-          <t>691/697</t>
+          <t>DA</t>
         </is>
       </c>
       <c r="D8" s="43" t="inlineStr">
         <is>
-          <t>441/4417</t>
-        </is>
-      </c>
-      <c r="E8" s="43" t="inlineStr">
-        <is>
-          <t>Impozit calculat</t>
-        </is>
-      </c>
-      <c r="F8" s="43" t="inlineStr">
-        <is>
-          <t>Cheltuială cu impozitul → datorie</t>
+          <t>Dacă apar pe DVI, urmează același regim ca taxele</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="43" t="n">
-        <v>4</v>
+      <c r="A9" s="43" t="inlineStr">
+        <is>
+          <t>Transport EXTERN, până la frontieră</t>
+        </is>
       </c>
       <c r="B9" s="43" t="inlineStr">
         <is>
-          <t>B3b Închidere 691</t>
+          <t>DA</t>
         </is>
       </c>
       <c r="C9" s="43" t="inlineStr">
         <is>
-          <t>121</t>
+          <t>DA</t>
         </is>
       </c>
       <c r="D9" s="43" t="inlineStr">
         <is>
-          <t>691</t>
-        </is>
-      </c>
-      <c r="E9" s="43" t="inlineStr">
-        <is>
-          <t>Impozit</t>
-        </is>
-      </c>
-      <c r="F9" s="43" t="inlineStr">
-        <is>
-          <t>Impozitul intră în rezultatul net</t>
+          <t>Intră în baza vamală dacă e până la primul loc de destinație din UE</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="43" t="n">
-        <v>5</v>
+      <c r="A10" s="43" t="inlineStr">
+        <is>
+          <t>Transport INTERN, după vămuire</t>
+        </is>
       </c>
       <c r="B10" s="43" t="inlineStr">
         <is>
-          <t>B4 Repartizare (opțional)</t>
+          <t>DA</t>
         </is>
       </c>
       <c r="C10" s="43" t="inlineStr">
         <is>
-          <t>129</t>
+          <t>NU</t>
         </is>
       </c>
       <c r="D10" s="43" t="inlineStr">
         <is>
-          <t>106/457…</t>
-        </is>
-      </c>
-      <c r="E10" s="43" t="inlineStr">
-        <is>
-          <t>Sumă repartizată</t>
-        </is>
-      </c>
-      <c r="F10" s="43" t="inlineStr">
-        <is>
-          <t>Doar dacă AGA / decizie există</t>
+          <t>Cost de achiziție, dar are TVA-ul lui pe factura transportatorului</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="43" t="n">
-        <v>6</v>
+      <c r="A11" s="43" t="inlineStr">
+        <is>
+          <t>TVA-ul vamal însuși</t>
+        </is>
       </c>
       <c r="B11" s="43" t="inlineStr">
         <is>
-          <t>B5 Report</t>
+          <t>NU</t>
         </is>
       </c>
       <c r="C11" s="43" t="inlineStr">
         <is>
-          <t>121</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D11" s="43" t="inlineStr">
         <is>
-          <t>117</t>
-        </is>
-      </c>
-      <c r="E11" s="43" t="inlineStr">
-        <is>
-          <t>Sold final 121</t>
-        </is>
-      </c>
-      <c r="F11" s="43" t="inlineStr">
-        <is>
-          <t>Dacă profit; invers dacă pierdere</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="42" t="inlineStr">
-        <is>
-          <t>Tabel B — Conturi din plan pe rol</t>
+          <t>Merge pe 4426, nu în costul stocului</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="44" t="inlineStr">
+        <is>
+          <t>Cele două coloane NU coincid. Transportul intern e singurul element care intră în cost fără să intre în bază — acolo se face greșeala.</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="65" t="inlineStr">
-        <is>
-          <t>Cont</t>
-        </is>
-      </c>
-      <c r="B14" s="65" t="inlineStr">
-        <is>
-          <t>Denumire</t>
-        </is>
-      </c>
-      <c r="C14" s="65" t="inlineStr">
-        <is>
-          <t>Rol</t>
-        </is>
-      </c>
-      <c r="D14" s="65" t="inlineStr">
-        <is>
-          <t>Observație</t>
+      <c r="A14" s="42" t="inlineStr">
+        <is>
+          <t>Tabel B — Cele două căi</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="43" t="inlineStr">
-        <is>
-          <t>121</t>
-        </is>
-      </c>
-      <c r="B15" s="43" t="inlineStr">
-        <is>
-          <t>Profit sau pierdere</t>
-        </is>
-      </c>
-      <c r="C15" s="43" t="inlineStr">
-        <is>
-          <t>Colectare rezultat</t>
-        </is>
-      </c>
-      <c r="D15" s="43" t="inlineStr">
-        <is>
-          <t>Se închide anual; fără sold după report pe 117</t>
+      <c r="A15" s="65" t="inlineStr">
+        <is>
+          <t>Cale</t>
+        </is>
+      </c>
+      <c r="B15" s="65" t="inlineStr">
+        <is>
+          <t>Cine plătește TVA în vamă</t>
+        </is>
+      </c>
+      <c r="C15" s="65" t="inlineStr">
+        <is>
+          <t>Cont folosit</t>
+        </is>
+      </c>
+      <c r="D15" s="65" t="inlineStr">
+        <is>
+          <t>Stare terminală</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="43" t="inlineStr">
         <is>
-          <t>129</t>
+          <t>Prin comisionar</t>
         </is>
       </c>
       <c r="B16" s="43" t="inlineStr">
         <is>
-          <t>Repartizarea profitului</t>
+          <t>Comisionarul avansează TVA-ul</t>
         </is>
       </c>
       <c r="C16" s="43" t="inlineStr">
         <is>
-          <t>Colectare / tranzit</t>
+          <t>446.VAMA — intermediar, până la stingerea datoriei</t>
         </is>
       </c>
       <c r="D16" s="43" t="inlineStr">
         <is>
-          <t>Se folosește doar la repartizare formală</t>
+          <t>446.VAMA: rulaj D = rulaj C, sold 0</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="43" t="inlineStr">
         <is>
-          <t>117</t>
+          <t>Plată directă în vamă</t>
         </is>
       </c>
       <c r="B17" s="43" t="inlineStr">
         <is>
-          <t>Rezultatul reportat</t>
+          <t>Firma, din contul propriu</t>
         </is>
       </c>
       <c r="C17" s="43" t="inlineStr">
         <is>
-          <t>Patrimonial — Capital</t>
+          <t>Fără intermediar — direct 4426 = 512</t>
         </is>
       </c>
       <c r="D17" s="43" t="inlineStr">
         <is>
-          <t>Sold permanent până la acoperire / repartizare</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="43" t="inlineStr">
-        <is>
-          <t>691</t>
-        </is>
-      </c>
-      <c r="B18" s="43" t="inlineStr">
-        <is>
-          <t>Cheltuieli cu impozitul pe profit</t>
-        </is>
-      </c>
-      <c r="C18" s="43" t="inlineStr">
-        <is>
-          <t>Neutralizare rezultat</t>
-        </is>
-      </c>
-      <c r="D18" s="43" t="inlineStr">
-        <is>
-          <t>Se închide în 121</t>
+          <t>401.EXT rămâne doar cu valoarea mărfii</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="43" t="inlineStr">
-        <is>
-          <t>697</t>
-        </is>
-      </c>
-      <c r="B19" s="43" t="inlineStr">
-        <is>
-          <t>Cheltuieli cu impozitul pe venit micro</t>
-        </is>
-      </c>
-      <c r="C19" s="43" t="inlineStr">
-        <is>
-          <t>Neutralizare rezultat</t>
-        </is>
-      </c>
-      <c r="D19" s="43" t="inlineStr">
-        <is>
-          <t>Alternativă la 691</t>
+      <c r="A19" s="42" t="inlineStr">
+        <is>
+          <t>Tabel C — Porți de calitate</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="43" t="inlineStr">
-        <is>
-          <t>441</t>
-        </is>
-      </c>
-      <c r="B20" s="43" t="inlineStr">
-        <is>
-          <t>Impozit pe profit</t>
-        </is>
-      </c>
-      <c r="C20" s="43" t="inlineStr">
-        <is>
-          <t>Patrimonial — Datorie</t>
-        </is>
-      </c>
-      <c r="D20" s="43" t="inlineStr">
-        <is>
-          <t>Datorie către buget</t>
+      <c r="A20" s="44" t="inlineStr">
+        <is>
+          <t>• ΣDr = ΣCr pe fiecare bloc</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="43" t="inlineStr">
-        <is>
-          <t>4417</t>
-        </is>
-      </c>
-      <c r="B21" s="43" t="inlineStr">
-        <is>
-          <t>Impozit pe venit micro / alte impozite</t>
-        </is>
-      </c>
-      <c r="C21" s="43" t="inlineStr">
-        <is>
-          <t>Patrimonial — Datorie</t>
-        </is>
-      </c>
-      <c r="D21" s="43" t="inlineStr">
-        <is>
-          <t>Conform OMF actualizat</t>
+      <c r="A21" s="44" t="inlineStr">
+        <is>
+          <t>• Baza TVA vamală = valoarea mărfii + taxele vamale, NU costul complet</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="44" t="inlineStr">
+        <is>
+          <t>• 446.VAMA: rulaj debitor = rulaj creditor, sold 0. Un sold rămas înseamnă datorie nestinsă față de comisionarul care a avansat TVA-ul</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="42" t="inlineStr">
-        <is>
-          <t>Tabel C — Porți de calitate</t>
+      <c r="A23" s="44" t="inlineStr">
+        <is>
+          <t>• 401.EXT rămâne doar cu valoarea mărfii — taxele și TVA-ul nu se datorează furnizorului extern</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="44" t="inlineStr">
         <is>
-          <t>• ΣDr = ΣCr pe fiecare bloc</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="44" t="inlineStr">
-        <is>
-          <t>• După B1+B2: sold 6xx = 0, sold 7xx = 0</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="44" t="inlineStr">
-        <is>
-          <t>• Sold 121 înainte de report = rezultat net</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="44" t="inlineStr">
-        <is>
-          <t>• După B5: sold 121 = 0, sold 117 reflectă reportul</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="44" t="inlineStr">
-        <is>
-          <t>• Modulul nu înlocuiește D101 / declarația de impozit — produce doar nota contabilă</t>
+          <t>• TVA-ul vamal merge pe 4426 și se închide lunar ca oricare altul (vezi MOD_INCHIDERE_TVA); nu intră niciodată în costul stocului</t>
         </is>
       </c>
     </row>
@@ -25694,412 +25717,469 @@
   <dimension ref="A1:G30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="24" customWidth="1" style="40" min="1" max="1"/>
+    <col width="36" customWidth="1" style="40" min="1" max="1"/>
     <col width="16" customWidth="1" style="40" min="2" max="2"/>
     <col width="14" customWidth="1" style="40" min="3" max="3"/>
-    <col width="50" customWidth="1" style="40" min="4" max="4"/>
+    <col width="52" customWidth="1" style="40" min="4" max="4"/>
     <col width="16" customWidth="1" style="40" min="5" max="5"/>
     <col width="14" customWidth="1" style="40" min="6" max="6"/>
-    <col width="50" customWidth="1" style="40" min="7" max="7"/>
+    <col width="52" customWidth="1" style="40" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="41" t="inlineStr">
         <is>
-          <t>MOD_INCHIDERE_EX — Jurnale (generate automat)</t>
+          <t>MOD_IMPORT — Jurnale (generate automat)</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="44" t="inlineStr">
         <is>
-          <t>Toate sumele derivă din Declarații. În SAGA se detaliază pe conturi analitice; aici e nota de principiu pe totaluri de clasă.</t>
+          <t>Calea A are exact două note pentru TVA-ul vamal: una îl aduce pe 4426 prin intermediar, alta stinge intermediarul. Sărită a doua, 446.VAMA rămâne deschis la infinit.</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="43" t="inlineStr">
-        <is>
-          <t>Data jurnal:</t>
-        </is>
-      </c>
-      <c r="B4" s="43" t="str">
-        <f>Declarații_INCHIDERE_EX!B8</f>
-        <v>2026-12-31</v>
+      <c r="A4" s="42" t="inlineStr">
+        <is>
+          <t>Bloc A — Import prin comisionar</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="43" t="inlineStr">
+        <is>
+          <t>Data:</t>
+        </is>
+      </c>
+      <c r="B5" s="43" t="str">
+        <f>Declarații_IMPORT!B8</f>
+        <v>2026-07-31</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="42" t="inlineStr">
-        <is>
-          <t>Bloc 1 — Închidere cheltuieli (cls.6 → 121)</t>
+      <c r="A6" s="65" t="inlineStr">
+        <is>
+          <t>Nr</t>
+        </is>
+      </c>
+      <c r="B6" s="65" t="inlineStr">
+        <is>
+          <t>Cont Dr</t>
+        </is>
+      </c>
+      <c r="C6" s="65" t="inlineStr">
+        <is>
+          <t>Sumă Dr</t>
+        </is>
+      </c>
+      <c r="D6" s="65" t="inlineStr">
+        <is>
+          <t>Descriere Dr</t>
+        </is>
+      </c>
+      <c r="E6" s="65" t="inlineStr">
+        <is>
+          <t>Cont Cr</t>
+        </is>
+      </c>
+      <c r="F6" s="65" t="inlineStr">
+        <is>
+          <t>Sumă Cr</t>
+        </is>
+      </c>
+      <c r="G6" s="65" t="inlineStr">
+        <is>
+          <t>Descriere Cr</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="65" t="inlineStr">
-        <is>
-          <t>Nr</t>
-        </is>
-      </c>
-      <c r="B7" s="65" t="inlineStr">
-        <is>
-          <t>Cont Dr</t>
-        </is>
-      </c>
-      <c r="C7" s="65" t="inlineStr">
-        <is>
-          <t>Sumă Dr</t>
-        </is>
-      </c>
-      <c r="D7" s="65" t="inlineStr">
-        <is>
-          <t>Descriere Dr</t>
-        </is>
-      </c>
-      <c r="E7" s="65" t="inlineStr">
-        <is>
-          <t>Cont Cr</t>
-        </is>
-      </c>
-      <c r="F7" s="65" t="inlineStr">
-        <is>
-          <t>Sumă Cr</t>
-        </is>
-      </c>
-      <c r="G7" s="65" t="inlineStr">
-        <is>
-          <t>Descriere Cr</t>
-        </is>
+      <c r="A7" s="43" t="n">
+        <v>1</v>
+      </c>
+      <c r="B7" s="43" t="str">
+        <f>Declarații_IMPORT!B32</f>
+        <v>371</v>
+      </c>
+      <c r="C7" s="43">
+        <f>IF(Declarații_IMPORT!B12="DA",Declarații_IMPORT!B15,0)</f>
+        <v>100000</v>
+      </c>
+      <c r="D7" s="43" t="str">
+        <f>"Marfă din import (doar valoarea externă) " &amp; Declarații_IMPORT!B41</f>
+        <v>Marfă din import (doar valoarea externă) — import 2026-07</v>
+      </c>
+      <c r="E7" s="43" t="str">
+        <f>Declarații_IMPORT!B33</f>
+        <v>401.EXT</v>
+      </c>
+      <c r="F7" s="43">
+        <f>IF(Declarații_IMPORT!B12="DA",Declarații_IMPORT!B15,0)</f>
+        <v>100000</v>
+      </c>
+      <c r="G7" s="43" t="str">
+        <f>"Datorie furnizor extern " &amp; Declarații_IMPORT!B41</f>
+        <v>Datorie furnizor extern — import 2026-07</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="43" t="n">
-        <v>1</v>
-      </c>
-      <c r="B8" s="43" t="str">
-        <f>Declarații_INCHIDERE_EX!B29</f>
-        <v>121</v>
-      </c>
-      <c r="C8" s="43">
-        <f>Declarații_INCHIDERE_EX!B11</f>
-        <v>185000</v>
-      </c>
-      <c r="D8" s="43" t="str">
-        <f>"Închidere cheltuieli cls.6 " &amp; Declarații_INCHIDERE_EX!B34</f>
-        <v>Închidere cheltuieli cls.6 — închidere exercițiu 2026</v>
-      </c>
-      <c r="E8" s="43" t="inlineStr">
-        <is>
-          <t>6xx</t>
-        </is>
-      </c>
-      <c r="F8" s="43">
-        <f>Declarații_INCHIDERE_EX!B11</f>
-        <v>185000</v>
-      </c>
-      <c r="G8" s="43" t="str">
-        <f>"Stingere rulaj cheltuieli " &amp; Declarații_INCHIDERE_EX!B34</f>
-        <v>Stingere rulaj cheltuieli — închidere exercițiu 2026</v>
+      <c r="A8" s="43" t="inlineStr">
+        <is>
+          <t>Check A1 (factura externă)</t>
+        </is>
+      </c>
+      <c r="B8" s="43">
+        <f>C7-F7</f>
+        <v>0</v>
+      </c>
+      <c r="C8" s="43" t="str">
+        <f>IF(ABS(B8)&lt;0.01,"OK","EROARE")</f>
+        <v>OK</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="43" t="inlineStr">
-        <is>
-          <t>Check B1</t>
-        </is>
-      </c>
-      <c r="B9" s="43">
-        <f>C8-F8</f>
+      <c r="A9" s="43" t="n">
+        <v>2</v>
+      </c>
+      <c r="B9" s="43" t="str">
+        <f>Declarații_IMPORT!B37</f>
+        <v>4426</v>
+      </c>
+      <c r="C9" s="43">
+        <f>IF(Declarații_IMPORT!B12="DA",Declarații_IMPORT!B19,0)</f>
+        <v>21630</v>
+      </c>
+      <c r="D9" s="43" t="str">
+        <f>"TVA vamală, avansată de comisionar " &amp; Declarații_IMPORT!B41</f>
+        <v>TVA vamală, avansată de comisionar — import 2026-07</v>
+      </c>
+      <c r="E9" s="43" t="str">
+        <f>Declarații_IMPORT!B34</f>
+        <v>446.VAMA</v>
+      </c>
+      <c r="F9" s="43">
+        <f>IF(Declarații_IMPORT!B12="DA",Declarații_IMPORT!B19,0)</f>
+        <v>21630</v>
+      </c>
+      <c r="G9" s="43" t="str">
+        <f>"Intermediar 446.VAMA (pas revelator) " &amp; Declarații_IMPORT!B41</f>
+        <v>Intermediar 446.VAMA (pas revelator) — import 2026-07</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="43" t="inlineStr">
+        <is>
+          <t>Check A2 (TVA prin intermediar)</t>
+        </is>
+      </c>
+      <c r="B10" s="43">
+        <f>C9-F9</f>
         <v>0</v>
       </c>
-      <c r="C9" s="43" t="str">
-        <f>IF(ABS(B9)&lt;0.01,"OK","EROARE")</f>
+      <c r="C10" s="43" t="str">
+        <f>IF(ABS(B10)&lt;0.01,"OK","EROARE")</f>
         <v>OK</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="42" t="inlineStr">
-        <is>
-          <t>Bloc 2 — Închidere venituri (cls.7 → 121)</t>
-        </is>
+      <c r="A11" s="43" t="n">
+        <v>3</v>
+      </c>
+      <c r="B11" s="43" t="str">
+        <f>Declarații_IMPORT!B34</f>
+        <v>446.VAMA</v>
+      </c>
+      <c r="C11" s="43">
+        <f>IF(Declarații_IMPORT!B12="DA",Declarații_IMPORT!B19,0)</f>
+        <v>21630</v>
+      </c>
+      <c r="D11" s="43" t="str">
+        <f>"Stingerea intermediarului " &amp; Declarații_IMPORT!B41</f>
+        <v>Stingerea intermediarului — import 2026-07</v>
+      </c>
+      <c r="E11" s="43" t="str">
+        <f>Declarații_IMPORT!B35</f>
+        <v>401</v>
+      </c>
+      <c r="F11" s="43">
+        <f>IF(Declarații_IMPORT!B12="DA",Declarații_IMPORT!B19,0)</f>
+        <v>21630</v>
+      </c>
+      <c r="G11" s="43" t="str">
+        <f>"Datorie reală față de comisionar " &amp; Declarații_IMPORT!B41</f>
+        <v>Datorie reală față de comisionar — import 2026-07</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="65" t="inlineStr">
-        <is>
-          <t>Nr</t>
-        </is>
-      </c>
-      <c r="B12" s="65" t="inlineStr">
-        <is>
-          <t>Cont Dr</t>
-        </is>
-      </c>
-      <c r="C12" s="65" t="inlineStr">
-        <is>
-          <t>Sumă Dr</t>
-        </is>
-      </c>
-      <c r="D12" s="65" t="inlineStr">
-        <is>
-          <t>Descriere Dr</t>
-        </is>
-      </c>
-      <c r="E12" s="65" t="inlineStr">
-        <is>
-          <t>Cont Cr</t>
-        </is>
-      </c>
-      <c r="F12" s="65" t="inlineStr">
-        <is>
-          <t>Sumă Cr</t>
-        </is>
-      </c>
-      <c r="G12" s="65" t="inlineStr">
-        <is>
-          <t>Descriere Cr</t>
-        </is>
+      <c r="A12" s="43" t="inlineStr">
+        <is>
+          <t>Check A3 (stingerea intermediarului)</t>
+        </is>
+      </c>
+      <c r="B12" s="43">
+        <f>C11-F11</f>
+        <v>0</v>
+      </c>
+      <c r="C12" s="43" t="str">
+        <f>IF(ABS(B12)&lt;0.01,"OK","EROARE")</f>
+        <v>OK</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="43" t="n">
+        <v>4</v>
+      </c>
+      <c r="B13" s="43" t="str">
+        <f>Declarații_IMPORT!B32</f>
+        <v>371</v>
+      </c>
+      <c r="C13" s="43">
+        <f>IF(Declarații_IMPORT!B12="DA",Declarații_IMPORT!B16,0)</f>
+        <v>3000</v>
+      </c>
+      <c r="D13" s="43" t="str">
+        <f>"Taxe vamale în costul stocului " &amp; Declarații_IMPORT!B41</f>
+        <v>Taxe vamale în costul stocului — import 2026-07</v>
+      </c>
+      <c r="E13" s="43" t="str">
+        <f>Declarații_IMPORT!B36</f>
+        <v>401.RO</v>
+      </c>
+      <c r="F13" s="43">
+        <f>IF(Declarații_IMPORT!B12="DA",Declarații_IMPORT!B16,0)</f>
+        <v>3000</v>
+      </c>
+      <c r="G13" s="43" t="str">
+        <f>"Datorie taxe vamale " &amp; Declarații_IMPORT!B41</f>
+        <v>Datorie taxe vamale — import 2026-07</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="43" t="n">
+        <v>5</v>
+      </c>
+      <c r="B14" s="43" t="str">
+        <f>Declarații_IMPORT!B32</f>
+        <v>371</v>
+      </c>
+      <c r="C14" s="43">
+        <f>IF(Declarații_IMPORT!B12="DA",Declarații_IMPORT!B17,0)</f>
+        <v>2000</v>
+      </c>
+      <c r="D14" s="43" t="str">
+        <f>"Transport intern în cost (NU în baza TVA) " &amp; Declarații_IMPORT!B41</f>
+        <v>Transport intern în cost (NU în baza TVA) — import 2026-07</v>
+      </c>
+      <c r="E14" s="43" t="str">
+        <f>Declarații_IMPORT!B36</f>
+        <v>401.RO</v>
+      </c>
+      <c r="F14" s="43">
+        <f>IF(Declarații_IMPORT!B12="DA",Declarații_IMPORT!B17,0)</f>
+        <v>2000</v>
+      </c>
+      <c r="G14" s="43" t="str">
+        <f>"Datorie transportator " &amp; Declarații_IMPORT!B41</f>
+        <v>Datorie transportator — import 2026-07</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="43" t="inlineStr">
+        <is>
+          <t>Check A4 (taxe + transport în cost)</t>
+        </is>
+      </c>
+      <c r="B15" s="43">
+        <f>(C13+C14)-(F13+F14)</f>
+        <v>0</v>
+      </c>
+      <c r="C15" s="43" t="str">
+        <f>IF(ABS(B15)&lt;0.01,"OK","EROARE")</f>
+        <v>OK</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="43" t="inlineStr">
+        <is>
+          <t>Check A5 (446.VAMA sold 0)</t>
+        </is>
+      </c>
+      <c r="B16" s="43">
+        <f>F9-C11</f>
+        <v>0</v>
+      </c>
+      <c r="C16" s="43" t="str">
+        <f>IF(ABS(B16)&lt;0.01,"OK — 446.VAMA rulaj D = rulaj C, sold 0","EROARE — intermediarul rămâne deschis")</f>
+        <v>OK — 446.VAMA rulaj D = rulaj C, sold 0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="42" t="inlineStr">
+        <is>
+          <t>Bloc B — Import cu plată directă în vamă</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="65" t="inlineStr">
+        <is>
+          <t>Nr</t>
+        </is>
+      </c>
+      <c r="B19" s="65" t="inlineStr">
+        <is>
+          <t>Cont Dr</t>
+        </is>
+      </c>
+      <c r="C19" s="65" t="inlineStr">
+        <is>
+          <t>Sumă Dr</t>
+        </is>
+      </c>
+      <c r="D19" s="65" t="inlineStr">
+        <is>
+          <t>Descriere Dr</t>
+        </is>
+      </c>
+      <c r="E19" s="65" t="inlineStr">
+        <is>
+          <t>Cont Cr</t>
+        </is>
+      </c>
+      <c r="F19" s="65" t="inlineStr">
+        <is>
+          <t>Sumă Cr</t>
+        </is>
+      </c>
+      <c r="G19" s="65" t="inlineStr">
+        <is>
+          <t>Descriere Cr</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="43" t="n">
         <v>1</v>
       </c>
-      <c r="B13" s="43" t="inlineStr">
-        <is>
-          <t>7xx</t>
-        </is>
-      </c>
-      <c r="C13" s="43">
-        <f>Declarații_INCHIDERE_EX!B12</f>
-        <v>245000</v>
-      </c>
-      <c r="D13" s="43" t="str">
-        <f>"Închidere venituri cls.7 " &amp; Declarații_INCHIDERE_EX!B34</f>
-        <v>Închidere venituri cls.7 — închidere exercițiu 2026</v>
-      </c>
-      <c r="E13" s="43" t="str">
-        <f>Declarații_INCHIDERE_EX!B29</f>
-        <v>121</v>
-      </c>
-      <c r="F13" s="43">
-        <f>Declarații_INCHIDERE_EX!B12</f>
-        <v>245000</v>
-      </c>
-      <c r="G13" s="43" t="str">
-        <f>"Stingere rulaj venituri " &amp; Declarații_INCHIDERE_EX!B34</f>
-        <v>Stingere rulaj venituri — închidere exercițiu 2026</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="43" t="inlineStr">
-        <is>
-          <t>Check B2</t>
-        </is>
-      </c>
-      <c r="B14" s="43">
-        <f>C13-F13</f>
+      <c r="B20" s="43" t="str">
+        <f>Declarații_IMPORT!B32</f>
+        <v>371</v>
+      </c>
+      <c r="C20" s="43">
+        <f>IF(Declarații_IMPORT!B23="DA",Declarații_IMPORT!B25,0)</f>
+        <v>50000</v>
+      </c>
+      <c r="D20" s="43" t="str">
+        <f>"Marfă din import " &amp; Declarații_IMPORT!B41</f>
+        <v>Marfă din import — import 2026-07</v>
+      </c>
+      <c r="E20" s="43" t="str">
+        <f>Declarații_IMPORT!B33</f>
+        <v>401.EXT</v>
+      </c>
+      <c r="F20" s="43">
+        <f>IF(Declarații_IMPORT!B23="DA",Declarații_IMPORT!B25,0)</f>
+        <v>50000</v>
+      </c>
+      <c r="G20" s="43" t="str">
+        <f>"Datorie furnizor extern " &amp; Declarații_IMPORT!B41</f>
+        <v>Datorie furnizor extern — import 2026-07</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="43" t="inlineStr">
+        <is>
+          <t>Check B1 (factura externă)</t>
+        </is>
+      </c>
+      <c r="B21" s="43">
+        <f>C20-F20</f>
         <v>0</v>
       </c>
-      <c r="C14" s="43" t="str">
-        <f>IF(ABS(B14)&lt;0.01,"OK","EROARE")</f>
+      <c r="C21" s="43" t="str">
+        <f>IF(ABS(B21)&lt;0.01,"OK","EROARE")</f>
         <v>OK</v>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="42" t="inlineStr">
-        <is>
-          <t>Bloc 3 — Cheltuială cu impozitul + închiderea ei în 121</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="65" t="inlineStr">
-        <is>
-          <t>Nr</t>
-        </is>
-      </c>
-      <c r="B17" s="65" t="inlineStr">
-        <is>
-          <t>Cont Dr</t>
-        </is>
-      </c>
-      <c r="C17" s="65" t="inlineStr">
-        <is>
-          <t>Sumă Dr</t>
-        </is>
-      </c>
-      <c r="D17" s="65" t="inlineStr">
-        <is>
-          <t>Descriere Dr</t>
-        </is>
-      </c>
-      <c r="E17" s="65" t="inlineStr">
-        <is>
-          <t>Cont Cr</t>
-        </is>
-      </c>
-      <c r="F17" s="65" t="inlineStr">
-        <is>
-          <t>Sumă Cr</t>
-        </is>
-      </c>
-      <c r="G17" s="65" t="inlineStr">
-        <is>
-          <t>Descriere Cr</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="43" t="n">
-        <v>1</v>
-      </c>
-      <c r="B18" s="43" t="str">
-        <f>Declarații_INCHIDERE_EX!B19</f>
-        <v>691</v>
-      </c>
-      <c r="C18" s="43">
-        <f>Declarații_INCHIDERE_EX!B18</f>
-        <v>9600</v>
-      </c>
-      <c r="D18" s="43" t="str">
-        <f>"Cheltuială impozit " &amp; Declarații_INCHIDERE_EX!B34</f>
-        <v>Cheltuială impozit — închidere exercițiu 2026</v>
-      </c>
-      <c r="E18" s="43" t="str">
-        <f>Declarații_INCHIDERE_EX!B20</f>
-        <v>441</v>
-      </c>
-      <c r="F18" s="43">
-        <f>Declarații_INCHIDERE_EX!B18</f>
-        <v>9600</v>
-      </c>
-      <c r="G18" s="43" t="str">
-        <f>"Datorie impozit buget " &amp; Declarații_INCHIDERE_EX!B34</f>
-        <v>Datorie impozit buget — închidere exercițiu 2026</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="43" t="n">
+    <row r="22">
+      <c r="A22" s="43" t="n">
         <v>2</v>
       </c>
-      <c r="B19" s="43" t="str">
-        <f>Declarații_INCHIDERE_EX!B29</f>
-        <v>121</v>
-      </c>
-      <c r="C19" s="43">
-        <f>Declarații_INCHIDERE_EX!B18</f>
-        <v>9600</v>
-      </c>
-      <c r="D19" s="43" t="str">
-        <f>"Închidere cheltuială impozit în rezultat " &amp; Declarații_INCHIDERE_EX!B34</f>
-        <v>Închidere cheltuială impozit în rezultat — închidere exercițiu 2026</v>
-      </c>
-      <c r="E19" s="43" t="str">
-        <f>Declarații_INCHIDERE_EX!B19</f>
-        <v>691</v>
-      </c>
-      <c r="F19" s="43">
-        <f>Declarații_INCHIDERE_EX!B18</f>
-        <v>9600</v>
-      </c>
-      <c r="G19" s="43" t="str">
-        <f>"Stingere 691 " &amp; Declarații_INCHIDERE_EX!B34</f>
-        <v>Stingere 691 — închidere exercițiu 2026</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="43" t="inlineStr">
-        <is>
-          <t>Check B3</t>
-        </is>
-      </c>
-      <c r="B20" s="43">
-        <f>(C18+C19)-(F18+F19)</f>
+      <c r="B22" s="43" t="str">
+        <f>Declarații_IMPORT!B32</f>
+        <v>371</v>
+      </c>
+      <c r="C22" s="43">
+        <f>IF(Declarații_IMPORT!B23="DA",Declarații_IMPORT!B26,0)</f>
+        <v>2000</v>
+      </c>
+      <c r="D22" s="43" t="str">
+        <f>"Taxe vamale plătite direct, în cost " &amp; Declarații_IMPORT!B41</f>
+        <v>Taxe vamale plătite direct, în cost — import 2026-07</v>
+      </c>
+      <c r="E22" s="43" t="str">
+        <f>Declarații_IMPORT!B38</f>
+        <v>512.1</v>
+      </c>
+      <c r="F22" s="43">
+        <f>IF(Declarații_IMPORT!B23="DA",Declarații_IMPORT!B26,0)</f>
+        <v>2000</v>
+      </c>
+      <c r="G22" s="43" t="str">
+        <f>"Ieșire bancă " &amp; Declarații_IMPORT!B41</f>
+        <v>Ieșire bancă — import 2026-07</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="43" t="inlineStr">
+        <is>
+          <t>Check B2 (taxe vamale)</t>
+        </is>
+      </c>
+      <c r="B23" s="43">
+        <f>C22-F22</f>
         <v>0</v>
       </c>
-      <c r="C20" s="43" t="str">
-        <f>IF(ABS(B20)&lt;0.01,"OK","EROARE")</f>
+      <c r="C23" s="43" t="str">
+        <f>IF(ABS(B23)&lt;0.01,"OK","EROARE")</f>
         <v>OK</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="42" t="inlineStr">
-        <is>
-          <t>Bloc 4 — Report rezultat net pe 117</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="65" t="inlineStr">
-        <is>
-          <t>Nr</t>
-        </is>
-      </c>
-      <c r="B23" s="65" t="inlineStr">
-        <is>
-          <t>Cont Dr</t>
-        </is>
-      </c>
-      <c r="C23" s="65" t="inlineStr">
-        <is>
-          <t>Sumă Dr</t>
-        </is>
-      </c>
-      <c r="D23" s="65" t="inlineStr">
-        <is>
-          <t>Descriere Dr</t>
-        </is>
-      </c>
-      <c r="E23" s="65" t="inlineStr">
-        <is>
-          <t>Cont Cr</t>
-        </is>
-      </c>
-      <c r="F23" s="65" t="inlineStr">
-        <is>
-          <t>Sumă Cr</t>
-        </is>
-      </c>
-      <c r="G23" s="65" t="inlineStr">
-        <is>
-          <t>Descriere Cr</t>
-        </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="43" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B24" s="43" t="str">
-        <f>IF(Declarații_INCHIDERE_EX!B26&gt;=0,Declarații_INCHIDERE_EX!B29,Declarații_INCHIDERE_EX!B31)</f>
-        <v>121</v>
+        <f>Declarații_IMPORT!B37</f>
+        <v>4426</v>
       </c>
       <c r="C24" s="43">
-        <f>ABS(Declarații_INCHIDERE_EX!B26)</f>
-        <v>50400</v>
+        <f>IF(Declarații_IMPORT!B23="DA",Declarații_IMPORT!B28,0)</f>
+        <v>10920</v>
       </c>
       <c r="D24" s="43" t="str">
-        <f>IF(Declarații_INCHIDERE_EX!B26&gt;=0,"Report profit pe 117 ","Report pierdere pe 117 ") &amp; Declarații_INCHIDERE_EX!B34</f>
-        <v>Report profit pe 117 — închidere exercițiu 2026</v>
+        <f>"TVA vamală plătită direct " &amp; Declarații_IMPORT!B41</f>
+        <v>TVA vamală plătită direct — import 2026-07</v>
       </c>
       <c r="E24" s="43" t="str">
-        <f>IF(Declarații_INCHIDERE_EX!B26&gt;=0,Declarații_INCHIDERE_EX!B31,Declarații_INCHIDERE_EX!B29)</f>
-        <v>117</v>
+        <f>Declarații_IMPORT!B38</f>
+        <v>512.1</v>
       </c>
       <c r="F24" s="43">
-        <f>ABS(Declarații_INCHIDERE_EX!B26)</f>
-        <v>50400</v>
+        <f>IF(Declarații_IMPORT!B23="DA",Declarații_IMPORT!B28,0)</f>
+        <v>10920</v>
       </c>
       <c r="G24" s="43" t="str">
-        <f>IF(Declarații_INCHIDERE_EX!B26&gt;=0,"Rezultat reportat (profit) ","Rezultat reportat (pierdere) ") &amp; Declarații_INCHIDERE_EX!B34</f>
-        <v>Rezultat reportat (profit) — închidere exercițiu 2026</v>
+        <f>"Ieșire bancă " &amp; Declarații_IMPORT!B41</f>
+        <v>Ieșire bancă — import 2026-07</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="43" t="inlineStr">
         <is>
-          <t>Check B4</t>
+          <t>Check B3 (TVA vamală)</t>
         </is>
       </c>
       <c r="B25" s="43">
@@ -26112,32 +26192,32 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="42" t="inlineStr">
-        <is>
-          <t>Stare terminală așteptată</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="44" t="inlineStr">
-        <is>
-          <t>Sold 6xx=0 | Sold 7xx=0 | Sold 121=0 | Sold 691=0 | 441 = impozit datorat | 117 = rezultat net reportat</t>
+      <c r="A27" s="43" t="inlineStr">
+        <is>
+          <t>Check global</t>
+        </is>
+      </c>
+      <c r="B27" s="43">
+        <f>ABS(B8)+ABS(B10)+ABS(B12)+ABS(B15)+ABS(B16)+ABS(B21)+ABS(B23)+ABS(B25)</f>
+        <v>0</v>
+      </c>
+      <c r="C27" s="43" t="str">
+        <f>IF(B27&lt;0.01,"OK — toate blocurile se închid","EROARE — cel puțin un bloc dezechilibrat")</f>
+        <v>OK — toate blocurile se închid</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="42" t="inlineStr">
+        <is>
+          <t>Stare terminală</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="43" t="inlineStr">
-        <is>
-          <t>Check global</t>
-        </is>
-      </c>
-      <c r="B30" s="43">
-        <f>ABS(B9)+ABS(B14)+ABS(B20)+ABS(B25)</f>
-        <v>0</v>
-      </c>
-      <c r="C30" s="43" t="str">
-        <f>IF(B30&lt;0.01,"OK — toate blocurile se închid","EROARE — cel puțin un bloc dezechilibrat")</f>
-        <v>OK — toate blocurile se închid</v>
+      <c r="A30" s="44" t="inlineStr">
+        <is>
+          <t>Calea A: 446.VAMA sold 0, stoc la 105.000 (marfă + taxe + transport), TVA 21.630 pe 4426, datorie 100.000 către furnizorul extern și 21.630 către comisionar. Calea B: stoc 52.000, TVA 10.920 pe 4426, 401.EXT doar 50.000 — fără intermediar, pentru că nimeni n-a avansat nimic.</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -26685,6 +26765,1696 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:I15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="6" customWidth="1" style="40" min="1" max="1"/>
+    <col width="30" customWidth="1" style="40" min="2" max="2"/>
+    <col width="14" customWidth="1" style="40" min="3" max="3"/>
+    <col width="12" customWidth="1" style="40" min="4" max="4"/>
+    <col width="12" customWidth="1" style="40" min="5" max="5"/>
+    <col width="14" customWidth="1" style="40" min="6" max="6"/>
+    <col width="52" customWidth="1" style="40" min="7" max="7"/>
+    <col width="22" customWidth="1" style="40" min="8" max="8"/>
+    <col width="10" customWidth="1" style="40" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="41" t="inlineStr">
+        <is>
+          <t>MOD_IMPORT — Notă pentru import</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="44" t="inlineStr">
+        <is>
+          <t>Filtrează Include=DA. Calea neactivată iese cu sumă 0 și apare ca NU.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="65" t="inlineStr">
+        <is>
+          <t>Nr</t>
+        </is>
+      </c>
+      <c r="B4" s="65" t="inlineStr">
+        <is>
+          <t>Bloc</t>
+        </is>
+      </c>
+      <c r="C4" s="65" t="inlineStr">
+        <is>
+          <t>Data</t>
+        </is>
+      </c>
+      <c r="D4" s="65" t="inlineStr">
+        <is>
+          <t>Cont Dr</t>
+        </is>
+      </c>
+      <c r="E4" s="65" t="inlineStr">
+        <is>
+          <t>Cont Cr</t>
+        </is>
+      </c>
+      <c r="F4" s="65" t="inlineStr">
+        <is>
+          <t>Sumă</t>
+        </is>
+      </c>
+      <c r="G4" s="65" t="inlineStr">
+        <is>
+          <t>Descriere</t>
+        </is>
+      </c>
+      <c r="H4" s="65" t="inlineStr">
+        <is>
+          <t>Document</t>
+        </is>
+      </c>
+      <c r="I4" s="65" t="inlineStr">
+        <is>
+          <t>Include</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="43" t="n">
+        <v>1</v>
+      </c>
+      <c r="B5" s="43" t="inlineStr">
+        <is>
+          <t>A Comisionar — marfa</t>
+        </is>
+      </c>
+      <c r="C5" s="43" t="str">
+        <f>Declarații_IMPORT!B8</f>
+        <v>2026-07-31</v>
+      </c>
+      <c r="D5" s="43" t="str">
+        <f>Jurnale_IMPORT!B7</f>
+        <v>371</v>
+      </c>
+      <c r="E5" s="43" t="str">
+        <f>Jurnale_IMPORT!E7</f>
+        <v>401.EXT</v>
+      </c>
+      <c r="F5" s="43">
+        <f>Jurnale_IMPORT!C7</f>
+        <v>100000</v>
+      </c>
+      <c r="G5" s="43" t="str">
+        <f>Jurnale_IMPORT!D7</f>
+        <v>Marfă din import (doar valoarea externă) — import 2026-07</v>
+      </c>
+      <c r="H5" s="43" t="inlineStr">
+        <is>
+          <t>Factură externă</t>
+        </is>
+      </c>
+      <c r="I5" s="43" t="str">
+        <f>IF(AND(ISNUMBER(F5),F5&gt;0),"DA","NU")</f>
+        <v>DA</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="43" t="n">
+        <v>2</v>
+      </c>
+      <c r="B6" s="43" t="inlineStr">
+        <is>
+          <t>A Comisionar — TVA vamală</t>
+        </is>
+      </c>
+      <c r="C6" s="43" t="str">
+        <f>Declarații_IMPORT!B8</f>
+        <v>2026-07-31</v>
+      </c>
+      <c r="D6" s="43" t="str">
+        <f>Jurnale_IMPORT!B9</f>
+        <v>4426</v>
+      </c>
+      <c r="E6" s="43" t="str">
+        <f>Jurnale_IMPORT!E9</f>
+        <v>446.VAMA</v>
+      </c>
+      <c r="F6" s="43">
+        <f>Jurnale_IMPORT!C9</f>
+        <v>21630</v>
+      </c>
+      <c r="G6" s="43" t="str">
+        <f>Jurnale_IMPORT!D9</f>
+        <v>TVA vamală, avansată de comisionar — import 2026-07</v>
+      </c>
+      <c r="H6" s="43" t="inlineStr">
+        <is>
+          <t>DVI</t>
+        </is>
+      </c>
+      <c r="I6" s="43" t="str">
+        <f>IF(AND(ISNUMBER(F6),F6&gt;0),"DA","NU")</f>
+        <v>DA</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="43" t="n">
+        <v>3</v>
+      </c>
+      <c r="B7" s="43" t="inlineStr">
+        <is>
+          <t>A Comisionar — stingere 446</t>
+        </is>
+      </c>
+      <c r="C7" s="43" t="str">
+        <f>Declarații_IMPORT!B8</f>
+        <v>2026-07-31</v>
+      </c>
+      <c r="D7" s="43" t="str">
+        <f>Jurnale_IMPORT!B11</f>
+        <v>446.VAMA</v>
+      </c>
+      <c r="E7" s="43" t="str">
+        <f>Jurnale_IMPORT!E11</f>
+        <v>401</v>
+      </c>
+      <c r="F7" s="43">
+        <f>Jurnale_IMPORT!C11</f>
+        <v>21630</v>
+      </c>
+      <c r="G7" s="43" t="str">
+        <f>Jurnale_IMPORT!D11</f>
+        <v>Stingerea intermediarului — import 2026-07</v>
+      </c>
+      <c r="H7" s="43" t="inlineStr">
+        <is>
+          <t>Factură comisionar</t>
+        </is>
+      </c>
+      <c r="I7" s="43" t="str">
+        <f>IF(AND(ISNUMBER(F7),F7&gt;0),"DA","NU")</f>
+        <v>DA</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="43" t="n">
+        <v>4</v>
+      </c>
+      <c r="B8" s="43" t="inlineStr">
+        <is>
+          <t>A Comisionar — taxe vamale</t>
+        </is>
+      </c>
+      <c r="C8" s="43" t="str">
+        <f>Declarații_IMPORT!B8</f>
+        <v>2026-07-31</v>
+      </c>
+      <c r="D8" s="43" t="str">
+        <f>Jurnale_IMPORT!B13</f>
+        <v>371</v>
+      </c>
+      <c r="E8" s="43" t="str">
+        <f>Jurnale_IMPORT!E13</f>
+        <v>401.RO</v>
+      </c>
+      <c r="F8" s="43">
+        <f>Jurnale_IMPORT!C13</f>
+        <v>3000</v>
+      </c>
+      <c r="G8" s="43" t="str">
+        <f>Jurnale_IMPORT!D13</f>
+        <v>Taxe vamale în costul stocului — import 2026-07</v>
+      </c>
+      <c r="H8" s="43" t="inlineStr">
+        <is>
+          <t>DVI</t>
+        </is>
+      </c>
+      <c r="I8" s="43" t="str">
+        <f>IF(AND(ISNUMBER(F8),F8&gt;0),"DA","NU")</f>
+        <v>DA</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="43" t="n">
+        <v>5</v>
+      </c>
+      <c r="B9" s="43" t="inlineStr">
+        <is>
+          <t>A Comisionar — transport intern</t>
+        </is>
+      </c>
+      <c r="C9" s="43" t="str">
+        <f>Declarații_IMPORT!B8</f>
+        <v>2026-07-31</v>
+      </c>
+      <c r="D9" s="43" t="str">
+        <f>Jurnale_IMPORT!B14</f>
+        <v>371</v>
+      </c>
+      <c r="E9" s="43" t="str">
+        <f>Jurnale_IMPORT!E14</f>
+        <v>401.RO</v>
+      </c>
+      <c r="F9" s="43">
+        <f>Jurnale_IMPORT!C14</f>
+        <v>2000</v>
+      </c>
+      <c r="G9" s="43" t="str">
+        <f>Jurnale_IMPORT!D14</f>
+        <v>Transport intern în cost (NU în baza TVA) — import 2026-07</v>
+      </c>
+      <c r="H9" s="43" t="inlineStr">
+        <is>
+          <t>Factură transport</t>
+        </is>
+      </c>
+      <c r="I9" s="43" t="str">
+        <f>IF(AND(ISNUMBER(F9),F9&gt;0),"DA","NU")</f>
+        <v>DA</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="43" t="n">
+        <v>6</v>
+      </c>
+      <c r="B10" s="43" t="inlineStr">
+        <is>
+          <t>B Direct — marfa</t>
+        </is>
+      </c>
+      <c r="C10" s="43" t="str">
+        <f>Declarații_IMPORT!B8</f>
+        <v>2026-07-31</v>
+      </c>
+      <c r="D10" s="43" t="str">
+        <f>Jurnale_IMPORT!B20</f>
+        <v>371</v>
+      </c>
+      <c r="E10" s="43" t="str">
+        <f>Jurnale_IMPORT!E20</f>
+        <v>401.EXT</v>
+      </c>
+      <c r="F10" s="43">
+        <f>Jurnale_IMPORT!C20</f>
+        <v>50000</v>
+      </c>
+      <c r="G10" s="43" t="str">
+        <f>Jurnale_IMPORT!D20</f>
+        <v>Marfă din import — import 2026-07</v>
+      </c>
+      <c r="H10" s="43" t="inlineStr">
+        <is>
+          <t>Factură externă</t>
+        </is>
+      </c>
+      <c r="I10" s="43" t="str">
+        <f>IF(AND(ISNUMBER(F10),F10&gt;0),"DA","NU")</f>
+        <v>DA</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="43" t="n">
+        <v>7</v>
+      </c>
+      <c r="B11" s="43" t="inlineStr">
+        <is>
+          <t>B Direct — taxe vamale</t>
+        </is>
+      </c>
+      <c r="C11" s="43" t="str">
+        <f>Declarații_IMPORT!B8</f>
+        <v>2026-07-31</v>
+      </c>
+      <c r="D11" s="43" t="str">
+        <f>Jurnale_IMPORT!B22</f>
+        <v>371</v>
+      </c>
+      <c r="E11" s="43" t="str">
+        <f>Jurnale_IMPORT!E22</f>
+        <v>512.1</v>
+      </c>
+      <c r="F11" s="43">
+        <f>Jurnale_IMPORT!C22</f>
+        <v>2000</v>
+      </c>
+      <c r="G11" s="43" t="str">
+        <f>Jurnale_IMPORT!D22</f>
+        <v>Taxe vamale plătite direct, în cost — import 2026-07</v>
+      </c>
+      <c r="H11" s="43" t="inlineStr">
+        <is>
+          <t>DVI + extras</t>
+        </is>
+      </c>
+      <c r="I11" s="43" t="str">
+        <f>IF(AND(ISNUMBER(F11),F11&gt;0),"DA","NU")</f>
+        <v>DA</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="43" t="n">
+        <v>8</v>
+      </c>
+      <c r="B12" s="43" t="inlineStr">
+        <is>
+          <t>B Direct — TVA vamală</t>
+        </is>
+      </c>
+      <c r="C12" s="43" t="str">
+        <f>Declarații_IMPORT!B8</f>
+        <v>2026-07-31</v>
+      </c>
+      <c r="D12" s="43" t="str">
+        <f>Jurnale_IMPORT!B24</f>
+        <v>4426</v>
+      </c>
+      <c r="E12" s="43" t="str">
+        <f>Jurnale_IMPORT!E24</f>
+        <v>512.1</v>
+      </c>
+      <c r="F12" s="43">
+        <f>Jurnale_IMPORT!C24</f>
+        <v>10920</v>
+      </c>
+      <c r="G12" s="43" t="str">
+        <f>Jurnale_IMPORT!D24</f>
+        <v>TVA vamală plătită direct — import 2026-07</v>
+      </c>
+      <c r="H12" s="43" t="inlineStr">
+        <is>
+          <t>DVI + extras</t>
+        </is>
+      </c>
+      <c r="I12" s="43" t="str">
+        <f>IF(AND(ISNUMBER(F12),F12&gt;0),"DA","NU")</f>
+        <v>DA</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="43" t="inlineStr">
+        <is>
+          <t>Rânduri de importat</t>
+        </is>
+      </c>
+      <c r="B14" s="43">
+        <f>COUNTIF(I5:I12,"DA")</f>
+        <v>8</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="43" t="inlineStr">
+        <is>
+          <t>Check global</t>
+        </is>
+      </c>
+      <c r="B15" s="43">
+        <f>Jurnale_IMPORT!B27</f>
+        <v>0</v>
+      </c>
+      <c r="C15" s="43" t="str">
+        <f>IF(ABS(B15)&lt;0.01,"OK","EROARE")</f>
+        <v>OK</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet61.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B38"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="48" customWidth="1" style="40" min="1" max="1"/>
+    <col width="26" customWidth="1" style="40" min="2" max="2"/>
+    <col width="56" customWidth="1" style="40" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="41" t="inlineStr">
+        <is>
+          <t>MOD_INCHIDERE_EX — Declarații (input)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="44" t="inlineStr">
+        <is>
+          <t>Modul anual. Completezi rulajele din balanță (sau totaluri din SAGA). Jurnalele închid cls.6 → 121, cls.7 → 121, calculează impozit / IMCA, repartizează 129 și reportează 117.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="42" t="inlineStr">
+        <is>
+          <t>1. Antet</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="43" t="inlineStr">
+        <is>
+          <t>Societate</t>
+        </is>
+      </c>
+      <c r="B5" s="43" t="str">
+        <f>Parametri!B5</f>
+        <v>SC EXEMPLU SRL</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="43" t="inlineStr">
+        <is>
+          <t>CUI</t>
+        </is>
+      </c>
+      <c r="B6" s="43" t="str">
+        <f>Parametri!B6</f>
+        <v>RO00000000</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="43" t="inlineStr">
+        <is>
+          <t>An exercițiu</t>
+        </is>
+      </c>
+      <c r="B7" s="64" t="n">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="43" t="inlineStr">
+        <is>
+          <t>Data jurnal închidere (31.12)</t>
+        </is>
+      </c>
+      <c r="B8" s="64" t="inlineStr">
+        <is>
+          <t>2026-12-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="42" t="inlineStr">
+        <is>
+          <t>2. Rulaje de închis (din balanță / totaluri SAGA)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="43" t="inlineStr">
+        <is>
+          <t>Total rulaj debitor cls.6 (cheltuieli)</t>
+        </is>
+      </c>
+      <c r="B11" s="64" t="n">
+        <v>185000</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="43" t="inlineStr">
+        <is>
+          <t>Total rulaj creditor cls.7 (venituri)</t>
+        </is>
+      </c>
+      <c r="B12" s="64" t="n">
+        <v>245000</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="42" t="inlineStr">
+        <is>
+          <t>3. Impozit pe profit / IMCA</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="43" t="inlineStr">
+        <is>
+          <t>Regim (PROFIT / MICRO / IMCA)</t>
+        </is>
+      </c>
+      <c r="B15" s="64" t="inlineStr">
+        <is>
+          <t>PROFIT</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="43" t="inlineStr">
+        <is>
+          <t>Baza impozabilă (sau cifră afaceri IMCA)</t>
+        </is>
+      </c>
+      <c r="B16" s="64" t="n">
+        <v>60000</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="43" t="inlineStr">
+        <is>
+          <t>Cotă (0.16 / 0.01 / 0.03 etc.)</t>
+        </is>
+      </c>
+      <c r="B17" s="64" t="n">
+        <v>0.16</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="43" t="inlineStr">
+        <is>
+          <t>Impozit calculat</t>
+        </is>
+      </c>
+      <c r="B18" s="43">
+        <f>B16*B17</f>
+        <v>9600</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="43" t="inlineStr">
+        <is>
+          <t>Cont cheltuială impozit (691 / 697 / 4417)</t>
+        </is>
+      </c>
+      <c r="B19" s="64" t="inlineStr">
+        <is>
+          <t>691</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="43" t="inlineStr">
+        <is>
+          <t>Cont datorie impozit (441 / 4417)</t>
+        </is>
+      </c>
+      <c r="B20" s="64" t="inlineStr">
+        <is>
+          <t>441</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="42" t="inlineStr">
+        <is>
+          <t>4. Repartizare rezultat</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="43" t="inlineStr">
+        <is>
+          <t>Rezultat înainte de impozit (7−6)</t>
+        </is>
+      </c>
+      <c r="B23" s="43">
+        <f>B12-B11</f>
+        <v>60000</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="43" t="inlineStr">
+        <is>
+          <t>Rezultat net (după impozit)</t>
+        </is>
+      </c>
+      <c r="B24" s="43">
+        <f>B23-B18</f>
+        <v>50400</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="43" t="inlineStr">
+        <is>
+          <t>Repartizare la rezerve / dividende etc. (opțional)</t>
+        </is>
+      </c>
+      <c r="B25" s="64" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="43" t="inlineStr">
+        <is>
+          <t>Reportat pe 117 (sold final 121/129)</t>
+        </is>
+      </c>
+      <c r="B26" s="43">
+        <f>B24-B25</f>
+        <v>50400</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="42" t="inlineStr">
+        <is>
+          <t>5. Politică conturi rezultat</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="43" t="inlineStr">
+        <is>
+          <t>Cont profit și pierdere</t>
+        </is>
+      </c>
+      <c r="B29" s="64" t="inlineStr">
+        <is>
+          <t>121</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="43" t="inlineStr">
+        <is>
+          <t>Cont repartizare profit</t>
+        </is>
+      </c>
+      <c r="B30" s="64" t="inlineStr">
+        <is>
+          <t>129</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="43" t="inlineStr">
+        <is>
+          <t>Cont rezultat reportat</t>
+        </is>
+      </c>
+      <c r="B31" s="64" t="inlineStr">
+        <is>
+          <t>117</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="42" t="inlineStr">
+        <is>
+          <t>6. Sufix</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="43" t="inlineStr">
+        <is>
+          <t>Sufix</t>
+        </is>
+      </c>
+      <c r="B34" s="43" t="str">
+        <f>"— închidere exercițiu " &amp; B7</f>
+        <v>— închidere exercițiu 2026</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="42" t="inlineStr">
+        <is>
+          <t>7. Control</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="43" t="inlineStr">
+        <is>
+          <t>Modul activ?</t>
+        </is>
+      </c>
+      <c r="B37" s="43" t="str">
+        <f>IF(INDEX(CatalogModule!$A$1:$A$200,MATCH("MOD_INCHIDERE_EX",CatalogModule!$B$1:$B$200,0))="DA","ACTIV","INACTIV")</f>
+        <v>INACTIV</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="43" t="inlineStr">
+        <is>
+          <t>Notă</t>
+        </is>
+      </c>
+      <c r="B38" s="43" t="inlineStr">
+        <is>
+          <t>În practică se închid conturile de cheltuieli/venituri pe analitice (sau pe grupe). Aici se lucrează pe totaluri — un singur rând pe clasă.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet62.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F28"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" style="40" min="1" max="1"/>
+    <col width="30" customWidth="1" style="40" min="2" max="2"/>
+    <col width="16" customWidth="1" style="40" min="3" max="3"/>
+    <col width="18" customWidth="1" style="40" min="4" max="4"/>
+    <col width="20" customWidth="1" style="40" min="5" max="5"/>
+    <col width="48" customWidth="1" style="40" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="41" t="inlineStr">
+        <is>
+          <t>MOD_INCHIDERE_EX — Reguli (tabele fixe)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="44" t="inlineStr">
+        <is>
+          <t>Secvența de închidere e standard OMFP 1802. Detalierea pe conturi analitice se face în SAGA; modulul lucrează pe totaluri de clasă pentru generarea notei de principiu.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="42" t="inlineStr">
+        <is>
+          <t>Tabel A — Secvența de închidere</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="65" t="inlineStr">
+        <is>
+          <t>Pas</t>
+        </is>
+      </c>
+      <c r="B5" s="65" t="inlineStr">
+        <is>
+          <t>Bloc</t>
+        </is>
+      </c>
+      <c r="C5" s="65" t="inlineStr">
+        <is>
+          <t>Cont Dr</t>
+        </is>
+      </c>
+      <c r="D5" s="65" t="inlineStr">
+        <is>
+          <t>Cont Cr</t>
+        </is>
+      </c>
+      <c r="E5" s="65" t="inlineStr">
+        <is>
+          <t>Sumă</t>
+        </is>
+      </c>
+      <c r="F5" s="65" t="inlineStr">
+        <is>
+          <t>Observație</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="43" t="n">
+        <v>1</v>
+      </c>
+      <c r="B6" s="43" t="inlineStr">
+        <is>
+          <t>B1 Închidere cheltuieli</t>
+        </is>
+      </c>
+      <c r="C6" s="43" t="inlineStr">
+        <is>
+          <t>121</t>
+        </is>
+      </c>
+      <c r="D6" s="43" t="inlineStr">
+        <is>
+          <t>6xx (total)</t>
+        </is>
+      </c>
+      <c r="E6" s="43" t="inlineStr">
+        <is>
+          <t>Rulaj D cls.6</t>
+        </is>
+      </c>
+      <c r="F6" s="43" t="inlineStr">
+        <is>
+          <t>Neutralizare rezultat — cheltuieli</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="43" t="n">
+        <v>2</v>
+      </c>
+      <c r="B7" s="43" t="inlineStr">
+        <is>
+          <t>B2 Închidere venituri</t>
+        </is>
+      </c>
+      <c r="C7" s="43" t="inlineStr">
+        <is>
+          <t>7xx (total)</t>
+        </is>
+      </c>
+      <c r="D7" s="43" t="inlineStr">
+        <is>
+          <t>121</t>
+        </is>
+      </c>
+      <c r="E7" s="43" t="inlineStr">
+        <is>
+          <t>Rulaj C cls.7</t>
+        </is>
+      </c>
+      <c r="F7" s="43" t="inlineStr">
+        <is>
+          <t>Neutralizare rezultat — venituri</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="43" t="n">
+        <v>3</v>
+      </c>
+      <c r="B8" s="43" t="inlineStr">
+        <is>
+          <t>B3 Impozit</t>
+        </is>
+      </c>
+      <c r="C8" s="43" t="inlineStr">
+        <is>
+          <t>691/697</t>
+        </is>
+      </c>
+      <c r="D8" s="43" t="inlineStr">
+        <is>
+          <t>441/4417</t>
+        </is>
+      </c>
+      <c r="E8" s="43" t="inlineStr">
+        <is>
+          <t>Impozit calculat</t>
+        </is>
+      </c>
+      <c r="F8" s="43" t="inlineStr">
+        <is>
+          <t>Cheltuială cu impozitul → datorie</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="43" t="n">
+        <v>4</v>
+      </c>
+      <c r="B9" s="43" t="inlineStr">
+        <is>
+          <t>B3b Închidere 691</t>
+        </is>
+      </c>
+      <c r="C9" s="43" t="inlineStr">
+        <is>
+          <t>121</t>
+        </is>
+      </c>
+      <c r="D9" s="43" t="inlineStr">
+        <is>
+          <t>691</t>
+        </is>
+      </c>
+      <c r="E9" s="43" t="inlineStr">
+        <is>
+          <t>Impozit</t>
+        </is>
+      </c>
+      <c r="F9" s="43" t="inlineStr">
+        <is>
+          <t>Impozitul intră în rezultatul net</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="43" t="n">
+        <v>5</v>
+      </c>
+      <c r="B10" s="43" t="inlineStr">
+        <is>
+          <t>B4 Repartizare (opțional)</t>
+        </is>
+      </c>
+      <c r="C10" s="43" t="inlineStr">
+        <is>
+          <t>129</t>
+        </is>
+      </c>
+      <c r="D10" s="43" t="inlineStr">
+        <is>
+          <t>106/457…</t>
+        </is>
+      </c>
+      <c r="E10" s="43" t="inlineStr">
+        <is>
+          <t>Sumă repartizată</t>
+        </is>
+      </c>
+      <c r="F10" s="43" t="inlineStr">
+        <is>
+          <t>Doar dacă AGA / decizie există</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="43" t="n">
+        <v>6</v>
+      </c>
+      <c r="B11" s="43" t="inlineStr">
+        <is>
+          <t>B5 Report</t>
+        </is>
+      </c>
+      <c r="C11" s="43" t="inlineStr">
+        <is>
+          <t>121</t>
+        </is>
+      </c>
+      <c r="D11" s="43" t="inlineStr">
+        <is>
+          <t>117</t>
+        </is>
+      </c>
+      <c r="E11" s="43" t="inlineStr">
+        <is>
+          <t>Sold final 121</t>
+        </is>
+      </c>
+      <c r="F11" s="43" t="inlineStr">
+        <is>
+          <t>Dacă profit; invers dacă pierdere</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="42" t="inlineStr">
+        <is>
+          <t>Tabel B — Conturi din plan pe rol</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="65" t="inlineStr">
+        <is>
+          <t>Cont</t>
+        </is>
+      </c>
+      <c r="B14" s="65" t="inlineStr">
+        <is>
+          <t>Denumire</t>
+        </is>
+      </c>
+      <c r="C14" s="65" t="inlineStr">
+        <is>
+          <t>Rol</t>
+        </is>
+      </c>
+      <c r="D14" s="65" t="inlineStr">
+        <is>
+          <t>Observație</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="43" t="inlineStr">
+        <is>
+          <t>121</t>
+        </is>
+      </c>
+      <c r="B15" s="43" t="inlineStr">
+        <is>
+          <t>Profit sau pierdere</t>
+        </is>
+      </c>
+      <c r="C15" s="43" t="inlineStr">
+        <is>
+          <t>Colectare rezultat</t>
+        </is>
+      </c>
+      <c r="D15" s="43" t="inlineStr">
+        <is>
+          <t>Se închide anual; fără sold după report pe 117</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="43" t="inlineStr">
+        <is>
+          <t>129</t>
+        </is>
+      </c>
+      <c r="B16" s="43" t="inlineStr">
+        <is>
+          <t>Repartizarea profitului</t>
+        </is>
+      </c>
+      <c r="C16" s="43" t="inlineStr">
+        <is>
+          <t>Colectare / tranzit</t>
+        </is>
+      </c>
+      <c r="D16" s="43" t="inlineStr">
+        <is>
+          <t>Se folosește doar la repartizare formală</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="43" t="inlineStr">
+        <is>
+          <t>117</t>
+        </is>
+      </c>
+      <c r="B17" s="43" t="inlineStr">
+        <is>
+          <t>Rezultatul reportat</t>
+        </is>
+      </c>
+      <c r="C17" s="43" t="inlineStr">
+        <is>
+          <t>Patrimonial — Capital</t>
+        </is>
+      </c>
+      <c r="D17" s="43" t="inlineStr">
+        <is>
+          <t>Sold permanent până la acoperire / repartizare</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="43" t="inlineStr">
+        <is>
+          <t>691</t>
+        </is>
+      </c>
+      <c r="B18" s="43" t="inlineStr">
+        <is>
+          <t>Cheltuieli cu impozitul pe profit</t>
+        </is>
+      </c>
+      <c r="C18" s="43" t="inlineStr">
+        <is>
+          <t>Neutralizare rezultat</t>
+        </is>
+      </c>
+      <c r="D18" s="43" t="inlineStr">
+        <is>
+          <t>Se închide în 121</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="43" t="inlineStr">
+        <is>
+          <t>697</t>
+        </is>
+      </c>
+      <c r="B19" s="43" t="inlineStr">
+        <is>
+          <t>Cheltuieli cu impozitul pe venit micro</t>
+        </is>
+      </c>
+      <c r="C19" s="43" t="inlineStr">
+        <is>
+          <t>Neutralizare rezultat</t>
+        </is>
+      </c>
+      <c r="D19" s="43" t="inlineStr">
+        <is>
+          <t>Alternativă la 691</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="43" t="inlineStr">
+        <is>
+          <t>441</t>
+        </is>
+      </c>
+      <c r="B20" s="43" t="inlineStr">
+        <is>
+          <t>Impozit pe profit</t>
+        </is>
+      </c>
+      <c r="C20" s="43" t="inlineStr">
+        <is>
+          <t>Patrimonial — Datorie</t>
+        </is>
+      </c>
+      <c r="D20" s="43" t="inlineStr">
+        <is>
+          <t>Datorie către buget</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="43" t="inlineStr">
+        <is>
+          <t>4417</t>
+        </is>
+      </c>
+      <c r="B21" s="43" t="inlineStr">
+        <is>
+          <t>Impozit pe venit micro / alte impozite</t>
+        </is>
+      </c>
+      <c r="C21" s="43" t="inlineStr">
+        <is>
+          <t>Patrimonial — Datorie</t>
+        </is>
+      </c>
+      <c r="D21" s="43" t="inlineStr">
+        <is>
+          <t>Conform OMF actualizat</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="42" t="inlineStr">
+        <is>
+          <t>Tabel C — Porți de calitate</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="44" t="inlineStr">
+        <is>
+          <t>• ΣDr = ΣCr pe fiecare bloc</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="44" t="inlineStr">
+        <is>
+          <t>• După B1+B2: sold 6xx = 0, sold 7xx = 0</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="44" t="inlineStr">
+        <is>
+          <t>• Sold 121 înainte de report = rezultat net</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="44" t="inlineStr">
+        <is>
+          <t>• După B5: sold 121 = 0, sold 117 reflectă reportul</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="44" t="inlineStr">
+        <is>
+          <t>• Modulul nu înlocuiește D101 / declarația de impozit — produce doar nota contabilă</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet63.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G30"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="24" customWidth="1" style="40" min="1" max="1"/>
+    <col width="16" customWidth="1" style="40" min="2" max="2"/>
+    <col width="14" customWidth="1" style="40" min="3" max="3"/>
+    <col width="50" customWidth="1" style="40" min="4" max="4"/>
+    <col width="16" customWidth="1" style="40" min="5" max="5"/>
+    <col width="14" customWidth="1" style="40" min="6" max="6"/>
+    <col width="50" customWidth="1" style="40" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="41" t="inlineStr">
+        <is>
+          <t>MOD_INCHIDERE_EX — Jurnale (generate automat)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="44" t="inlineStr">
+        <is>
+          <t>Toate sumele derivă din Declarații. În SAGA se detaliază pe conturi analitice; aici e nota de principiu pe totaluri de clasă.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="43" t="inlineStr">
+        <is>
+          <t>Data jurnal:</t>
+        </is>
+      </c>
+      <c r="B4" s="43" t="str">
+        <f>Declarații_INCHIDERE_EX!B8</f>
+        <v>2026-12-31</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="42" t="inlineStr">
+        <is>
+          <t>Bloc 1 — Închidere cheltuieli (cls.6 → 121)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="65" t="inlineStr">
+        <is>
+          <t>Nr</t>
+        </is>
+      </c>
+      <c r="B7" s="65" t="inlineStr">
+        <is>
+          <t>Cont Dr</t>
+        </is>
+      </c>
+      <c r="C7" s="65" t="inlineStr">
+        <is>
+          <t>Sumă Dr</t>
+        </is>
+      </c>
+      <c r="D7" s="65" t="inlineStr">
+        <is>
+          <t>Descriere Dr</t>
+        </is>
+      </c>
+      <c r="E7" s="65" t="inlineStr">
+        <is>
+          <t>Cont Cr</t>
+        </is>
+      </c>
+      <c r="F7" s="65" t="inlineStr">
+        <is>
+          <t>Sumă Cr</t>
+        </is>
+      </c>
+      <c r="G7" s="65" t="inlineStr">
+        <is>
+          <t>Descriere Cr</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="43" t="n">
+        <v>1</v>
+      </c>
+      <c r="B8" s="43" t="str">
+        <f>Declarații_INCHIDERE_EX!B29</f>
+        <v>121</v>
+      </c>
+      <c r="C8" s="43">
+        <f>Declarații_INCHIDERE_EX!B11</f>
+        <v>185000</v>
+      </c>
+      <c r="D8" s="43" t="str">
+        <f>"Închidere cheltuieli cls.6 " &amp; Declarații_INCHIDERE_EX!B34</f>
+        <v>Închidere cheltuieli cls.6 — închidere exercițiu 2026</v>
+      </c>
+      <c r="E8" s="43" t="inlineStr">
+        <is>
+          <t>6xx</t>
+        </is>
+      </c>
+      <c r="F8" s="43">
+        <f>Declarații_INCHIDERE_EX!B11</f>
+        <v>185000</v>
+      </c>
+      <c r="G8" s="43" t="str">
+        <f>"Stingere rulaj cheltuieli " &amp; Declarații_INCHIDERE_EX!B34</f>
+        <v>Stingere rulaj cheltuieli — închidere exercițiu 2026</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="43" t="inlineStr">
+        <is>
+          <t>Check B1</t>
+        </is>
+      </c>
+      <c r="B9" s="43">
+        <f>C8-F8</f>
+        <v>0</v>
+      </c>
+      <c r="C9" s="43" t="str">
+        <f>IF(ABS(B9)&lt;0.01,"OK","EROARE")</f>
+        <v>OK</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="42" t="inlineStr">
+        <is>
+          <t>Bloc 2 — Închidere venituri (cls.7 → 121)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="65" t="inlineStr">
+        <is>
+          <t>Nr</t>
+        </is>
+      </c>
+      <c r="B12" s="65" t="inlineStr">
+        <is>
+          <t>Cont Dr</t>
+        </is>
+      </c>
+      <c r="C12" s="65" t="inlineStr">
+        <is>
+          <t>Sumă Dr</t>
+        </is>
+      </c>
+      <c r="D12" s="65" t="inlineStr">
+        <is>
+          <t>Descriere Dr</t>
+        </is>
+      </c>
+      <c r="E12" s="65" t="inlineStr">
+        <is>
+          <t>Cont Cr</t>
+        </is>
+      </c>
+      <c r="F12" s="65" t="inlineStr">
+        <is>
+          <t>Sumă Cr</t>
+        </is>
+      </c>
+      <c r="G12" s="65" t="inlineStr">
+        <is>
+          <t>Descriere Cr</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="43" t="n">
+        <v>1</v>
+      </c>
+      <c r="B13" s="43" t="inlineStr">
+        <is>
+          <t>7xx</t>
+        </is>
+      </c>
+      <c r="C13" s="43">
+        <f>Declarații_INCHIDERE_EX!B12</f>
+        <v>245000</v>
+      </c>
+      <c r="D13" s="43" t="str">
+        <f>"Închidere venituri cls.7 " &amp; Declarații_INCHIDERE_EX!B34</f>
+        <v>Închidere venituri cls.7 — închidere exercițiu 2026</v>
+      </c>
+      <c r="E13" s="43" t="str">
+        <f>Declarații_INCHIDERE_EX!B29</f>
+        <v>121</v>
+      </c>
+      <c r="F13" s="43">
+        <f>Declarații_INCHIDERE_EX!B12</f>
+        <v>245000</v>
+      </c>
+      <c r="G13" s="43" t="str">
+        <f>"Stingere rulaj venituri " &amp; Declarații_INCHIDERE_EX!B34</f>
+        <v>Stingere rulaj venituri — închidere exercițiu 2026</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="43" t="inlineStr">
+        <is>
+          <t>Check B2</t>
+        </is>
+      </c>
+      <c r="B14" s="43">
+        <f>C13-F13</f>
+        <v>0</v>
+      </c>
+      <c r="C14" s="43" t="str">
+        <f>IF(ABS(B14)&lt;0.01,"OK","EROARE")</f>
+        <v>OK</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="42" t="inlineStr">
+        <is>
+          <t>Bloc 3 — Cheltuială cu impozitul + închiderea ei în 121</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="65" t="inlineStr">
+        <is>
+          <t>Nr</t>
+        </is>
+      </c>
+      <c r="B17" s="65" t="inlineStr">
+        <is>
+          <t>Cont Dr</t>
+        </is>
+      </c>
+      <c r="C17" s="65" t="inlineStr">
+        <is>
+          <t>Sumă Dr</t>
+        </is>
+      </c>
+      <c r="D17" s="65" t="inlineStr">
+        <is>
+          <t>Descriere Dr</t>
+        </is>
+      </c>
+      <c r="E17" s="65" t="inlineStr">
+        <is>
+          <t>Cont Cr</t>
+        </is>
+      </c>
+      <c r="F17" s="65" t="inlineStr">
+        <is>
+          <t>Sumă Cr</t>
+        </is>
+      </c>
+      <c r="G17" s="65" t="inlineStr">
+        <is>
+          <t>Descriere Cr</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="43" t="n">
+        <v>1</v>
+      </c>
+      <c r="B18" s="43" t="str">
+        <f>Declarații_INCHIDERE_EX!B19</f>
+        <v>691</v>
+      </c>
+      <c r="C18" s="43">
+        <f>Declarații_INCHIDERE_EX!B18</f>
+        <v>9600</v>
+      </c>
+      <c r="D18" s="43" t="str">
+        <f>"Cheltuială impozit " &amp; Declarații_INCHIDERE_EX!B34</f>
+        <v>Cheltuială impozit — închidere exercițiu 2026</v>
+      </c>
+      <c r="E18" s="43" t="str">
+        <f>Declarații_INCHIDERE_EX!B20</f>
+        <v>441</v>
+      </c>
+      <c r="F18" s="43">
+        <f>Declarații_INCHIDERE_EX!B18</f>
+        <v>9600</v>
+      </c>
+      <c r="G18" s="43" t="str">
+        <f>"Datorie impozit buget " &amp; Declarații_INCHIDERE_EX!B34</f>
+        <v>Datorie impozit buget — închidere exercițiu 2026</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="43" t="n">
+        <v>2</v>
+      </c>
+      <c r="B19" s="43" t="str">
+        <f>Declarații_INCHIDERE_EX!B29</f>
+        <v>121</v>
+      </c>
+      <c r="C19" s="43">
+        <f>Declarații_INCHIDERE_EX!B18</f>
+        <v>9600</v>
+      </c>
+      <c r="D19" s="43" t="str">
+        <f>"Închidere cheltuială impozit în rezultat " &amp; Declarații_INCHIDERE_EX!B34</f>
+        <v>Închidere cheltuială impozit în rezultat — închidere exercițiu 2026</v>
+      </c>
+      <c r="E19" s="43" t="str">
+        <f>Declarații_INCHIDERE_EX!B19</f>
+        <v>691</v>
+      </c>
+      <c r="F19" s="43">
+        <f>Declarații_INCHIDERE_EX!B18</f>
+        <v>9600</v>
+      </c>
+      <c r="G19" s="43" t="str">
+        <f>"Stingere 691 " &amp; Declarații_INCHIDERE_EX!B34</f>
+        <v>Stingere 691 — închidere exercițiu 2026</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="43" t="inlineStr">
+        <is>
+          <t>Check B3</t>
+        </is>
+      </c>
+      <c r="B20" s="43">
+        <f>(C18+C19)-(F18+F19)</f>
+        <v>0</v>
+      </c>
+      <c r="C20" s="43" t="str">
+        <f>IF(ABS(B20)&lt;0.01,"OK","EROARE")</f>
+        <v>OK</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="42" t="inlineStr">
+        <is>
+          <t>Bloc 4 — Report rezultat net pe 117</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="65" t="inlineStr">
+        <is>
+          <t>Nr</t>
+        </is>
+      </c>
+      <c r="B23" s="65" t="inlineStr">
+        <is>
+          <t>Cont Dr</t>
+        </is>
+      </c>
+      <c r="C23" s="65" t="inlineStr">
+        <is>
+          <t>Sumă Dr</t>
+        </is>
+      </c>
+      <c r="D23" s="65" t="inlineStr">
+        <is>
+          <t>Descriere Dr</t>
+        </is>
+      </c>
+      <c r="E23" s="65" t="inlineStr">
+        <is>
+          <t>Cont Cr</t>
+        </is>
+      </c>
+      <c r="F23" s="65" t="inlineStr">
+        <is>
+          <t>Sumă Cr</t>
+        </is>
+      </c>
+      <c r="G23" s="65" t="inlineStr">
+        <is>
+          <t>Descriere Cr</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="43" t="n">
+        <v>1</v>
+      </c>
+      <c r="B24" s="43" t="str">
+        <f>IF(Declarații_INCHIDERE_EX!B26&gt;=0,Declarații_INCHIDERE_EX!B29,Declarații_INCHIDERE_EX!B31)</f>
+        <v>121</v>
+      </c>
+      <c r="C24" s="43">
+        <f>ABS(Declarații_INCHIDERE_EX!B26)</f>
+        <v>50400</v>
+      </c>
+      <c r="D24" s="43" t="str">
+        <f>IF(Declarații_INCHIDERE_EX!B26&gt;=0,"Report profit pe 117 ","Report pierdere pe 117 ") &amp; Declarații_INCHIDERE_EX!B34</f>
+        <v>Report profit pe 117 — închidere exercițiu 2026</v>
+      </c>
+      <c r="E24" s="43" t="str">
+        <f>IF(Declarații_INCHIDERE_EX!B26&gt;=0,Declarații_INCHIDERE_EX!B31,Declarații_INCHIDERE_EX!B29)</f>
+        <v>117</v>
+      </c>
+      <c r="F24" s="43">
+        <f>ABS(Declarații_INCHIDERE_EX!B26)</f>
+        <v>50400</v>
+      </c>
+      <c r="G24" s="43" t="str">
+        <f>IF(Declarații_INCHIDERE_EX!B26&gt;=0,"Rezultat reportat (profit) ","Rezultat reportat (pierdere) ") &amp; Declarații_INCHIDERE_EX!B34</f>
+        <v>Rezultat reportat (profit) — închidere exercițiu 2026</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="43" t="inlineStr">
+        <is>
+          <t>Check B4</t>
+        </is>
+      </c>
+      <c r="B25" s="43">
+        <f>C24-F24</f>
+        <v>0</v>
+      </c>
+      <c r="C25" s="43" t="str">
+        <f>IF(ABS(B25)&lt;0.01,"OK","EROARE")</f>
+        <v>OK</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="42" t="inlineStr">
+        <is>
+          <t>Stare terminală așteptată</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="44" t="inlineStr">
+        <is>
+          <t>Sold 6xx=0 | Sold 7xx=0 | Sold 121=0 | Sold 691=0 | 441 = impozit datorat | 117 = rezultat net reportat</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="43" t="inlineStr">
+        <is>
+          <t>Check global</t>
+        </is>
+      </c>
+      <c r="B30" s="43">
+        <f>ABS(B9)+ABS(B14)+ABS(B20)+ABS(B25)</f>
+        <v>0</v>
+      </c>
+      <c r="C30" s="43" t="str">
+        <f>IF(B30&lt;0.01,"OK — toate blocurile se închid","EROARE — cel puțin un bloc dezechilibrat")</f>
+        <v>OK — toate blocurile se închid</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet64.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:I12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -26986,7 +28756,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet61.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet65.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -27306,7 +29076,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet62.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet66.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -27596,7 +29366,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet63.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet67.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -28148,7 +29918,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet64.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet68.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -28562,7 +30332,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet65.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet69.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -28997,1309 +30767,6 @@
         <is>
           <t>Taxarea inversă INTERNĂ se aplică pe baza unei derogări UE care expiră la 31.12.2026. La 21.08.2026 nu era publicată o prelungire — reverifică înainte de prima factură din 2027.</t>
         </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet66.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:E26"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="30" customWidth="1" style="40" min="1" max="1"/>
-    <col width="44" customWidth="1" style="40" min="2" max="2"/>
-    <col width="16" customWidth="1" style="40" min="3" max="3"/>
-    <col width="44" customWidth="1" style="40" min="4" max="4"/>
-    <col width="48" customWidth="1" style="40" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="41" t="inlineStr">
-        <is>
-          <t>MOD_TAXARE_INVERSA — Reguli (tabele fixe)</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="44" t="inlineStr">
-        <is>
-          <t>Regula e dată, nu formulă. Mecanismul contabil e identic în ambele cazuri; diferă partenerul și declarația.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="42" t="inlineStr">
-        <is>
-          <t>Tabel A — Cele două cazuri</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="65" t="inlineStr">
-        <is>
-          <t>Caz</t>
-        </is>
-      </c>
-      <c r="B5" s="65" t="inlineStr">
-        <is>
-          <t>Partener</t>
-        </is>
-      </c>
-      <c r="C5" s="65" t="inlineStr">
-        <is>
-          <t>Cont furnizor</t>
-        </is>
-      </c>
-      <c r="D5" s="65" t="inlineStr">
-        <is>
-          <t>Ce declară</t>
-        </is>
-      </c>
-      <c r="E5" s="65" t="inlineStr">
-        <is>
-          <t>Condiție</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="43" t="inlineStr">
-        <is>
-          <t>Achiziție intracomunitară</t>
-        </is>
-      </c>
-      <c r="B6" s="43" t="inlineStr">
-        <is>
-          <t>Persoană impozabilă din alt stat membru</t>
-        </is>
-      </c>
-      <c r="C6" s="43" t="inlineStr">
-        <is>
-          <t>401.UE</t>
-        </is>
-      </c>
-      <c r="D6" s="43" t="inlineStr">
-        <is>
-          <t>D300 (casete taxare inversă) + D390 + D394</t>
-        </is>
-      </c>
-      <c r="E6" s="43" t="inlineStr">
-        <is>
-          <t>Cod de TVA valid în VIES la data operațiunii</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="43" t="inlineStr">
-        <is>
-          <t>Taxare inversă internă</t>
-        </is>
-      </c>
-      <c r="B7" s="43" t="inlineStr">
-        <is>
-          <t>Plătitor de TVA din România</t>
-        </is>
-      </c>
-      <c r="C7" s="43" t="inlineStr">
-        <is>
-          <t>401.RO</t>
-        </is>
-      </c>
-      <c r="D7" s="43" t="inlineStr">
-        <is>
-          <t>D300 (casete taxare inversă) + D394, FĂRĂ D390</t>
-        </is>
-      </c>
-      <c r="E7" s="43" t="inlineStr">
-        <is>
-          <t>Bunul sau serviciul e pe lista art. 331 CF</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="42" t="inlineStr">
-        <is>
-          <t>Tabel B — Operațiuni cu taxare inversă internă (art. 331 CF)</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="65" t="inlineStr">
-        <is>
-          <t>Operațiune</t>
-        </is>
-      </c>
-      <c r="B10" s="65" t="inlineStr">
-        <is>
-          <t>Prag</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="43" t="inlineStr">
-        <is>
-          <t>Cereale și plante tehnice</t>
-        </is>
-      </c>
-      <c r="B11" s="43" t="inlineStr">
-        <is>
-          <t>fără prag valoric</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="43" t="inlineStr">
-        <is>
-          <t>Certificate de emisii de gaze cu efect de seră</t>
-        </is>
-      </c>
-      <c r="B12" s="43" t="inlineStr">
-        <is>
-          <t>fără prag valoric</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="43" t="inlineStr">
-        <is>
-          <t>Energie electrică și gaze naturale către comercianți persoane impozabile</t>
-        </is>
-      </c>
-      <c r="B13" s="43" t="inlineStr">
-        <is>
-          <t>fără prag valoric</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="43" t="inlineStr">
-        <is>
-          <t>Certificate verzi</t>
-        </is>
-      </c>
-      <c r="B14" s="43" t="inlineStr">
-        <is>
-          <t>fără prag valoric</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="43" t="inlineStr">
-        <is>
-          <t>Telefoane mobile</t>
-        </is>
-      </c>
-      <c r="B15" s="43" t="inlineStr">
-        <is>
-          <t>doar dacă valoarea fără TVA de pe factură ≥ 22.500 lei</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="43" t="inlineStr">
-        <is>
-          <t>Dispozitive cu circuite integrate</t>
-        </is>
-      </c>
-      <c r="B16" s="43" t="inlineStr">
-        <is>
-          <t>doar dacă valoarea fără TVA de pe factură ≥ 22.500 lei</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="43" t="inlineStr">
-        <is>
-          <t>Console de jocuri</t>
-        </is>
-      </c>
-      <c r="B17" s="43" t="inlineStr">
-        <is>
-          <t>doar dacă valoarea fără TVA de pe factură ≥ 22.500 lei</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="43" t="inlineStr">
-        <is>
-          <t>Tablete și laptopuri</t>
-        </is>
-      </c>
-      <c r="B18" s="43" t="inlineStr">
-        <is>
-          <t>doar dacă valoarea fără TVA de pe factură ≥ 22.500 lei</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="44" t="inlineStr">
-        <is>
-          <t>Derogarea Consiliului UE pe baza căreia se aplică art. 331 expiră la 31.12.2026. Verificat la 21.08.2026: nicio prelungire publicată. Nu se presupune prelungirea automată.</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="42" t="inlineStr">
-        <is>
-          <t>Tabel C — Porți de calitate</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="44" t="inlineStr">
-        <is>
-          <t>• 4426 și 4427 primesc EXACT aceeași sumă — netul pe operațiune e zero</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="44" t="inlineStr">
-        <is>
-          <t>• D390 doar la intracomunitar; un partener intern trecut acolo se vede la ANAF prin necorelare cu VIES</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="44" t="inlineStr">
-        <is>
-          <t>• Codul VIES se verifică la DATA operațiunii, nu la data când te uiți</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="44" t="inlineStr">
-        <is>
-          <t>• Fără TVA plătită efectiv: autolichidarea nu produce flux de trezorerie</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="44" t="inlineStr">
-        <is>
-          <t>• La închiderea lunară, sumele astea intră în 4426/4427 ca oricare altele și se anulează reciproc — vezi MOD_INCHIDERE_TVA</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet67.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:G22"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="30" customWidth="1" style="40" min="1" max="1"/>
-    <col width="16" customWidth="1" style="40" min="2" max="2"/>
-    <col width="14" customWidth="1" style="40" min="3" max="3"/>
-    <col width="50" customWidth="1" style="40" min="4" max="4"/>
-    <col width="16" customWidth="1" style="40" min="5" max="5"/>
-    <col width="14" customWidth="1" style="40" min="6" max="6"/>
-    <col width="50" customWidth="1" style="40" min="7" max="7"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="41" t="inlineStr">
-        <is>
-          <t>MOD_TAXARE_INVERSA — Jurnale (generate automat)</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="44" t="inlineStr">
-        <is>
-          <t>Fiecare caz iese cu zero dacă nu e activat. Pasul de autolichidare are aceeași sumă pe ambele părți — asta e chiar mecanismul, nu o coincidență.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="42" t="inlineStr">
-        <is>
-          <t>Bloc A — Achiziție intracomunitară</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="43" t="inlineStr">
-        <is>
-          <t>Data:</t>
-        </is>
-      </c>
-      <c r="B5" s="43" t="str">
-        <f>Declarații_TAXARE_INVERSA!B8</f>
-        <v>2026-07-31</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="65" t="inlineStr">
-        <is>
-          <t>Nr</t>
-        </is>
-      </c>
-      <c r="B6" s="65" t="inlineStr">
-        <is>
-          <t>Cont Dr</t>
-        </is>
-      </c>
-      <c r="C6" s="65" t="inlineStr">
-        <is>
-          <t>Sumă Dr</t>
-        </is>
-      </c>
-      <c r="D6" s="65" t="inlineStr">
-        <is>
-          <t>Descriere Dr</t>
-        </is>
-      </c>
-      <c r="E6" s="65" t="inlineStr">
-        <is>
-          <t>Cont Cr</t>
-        </is>
-      </c>
-      <c r="F6" s="65" t="inlineStr">
-        <is>
-          <t>Sumă Cr</t>
-        </is>
-      </c>
-      <c r="G6" s="65" t="inlineStr">
-        <is>
-          <t>Descriere Cr</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="43" t="n">
-        <v>1</v>
-      </c>
-      <c r="B7" s="43" t="str">
-        <f>IF(Declarații_TAXARE_INVERSA!B20="DA",Declarații_TAXARE_INVERSA!B32,Declarații_TAXARE_INVERSA!B31)</f>
-        <v>371</v>
-      </c>
-      <c r="C7" s="43">
-        <f>IF(Declarații_TAXARE_INVERSA!B12="DA",Declarații_TAXARE_INVERSA!B17,0)</f>
-        <v>74550</v>
-      </c>
-      <c r="D7" s="43" t="str">
-        <f>"Achiziție intracomunitară " &amp; Declarații_TAXARE_INVERSA!B13 &amp; " " &amp; Declarații_TAXARE_INVERSA!B39</f>
-        <v>Achiziție intracomunitară Furnizor UE DEMO — taxare inversă 2026-07</v>
-      </c>
-      <c r="E7" s="43" t="str">
-        <f>Declarații_TAXARE_INVERSA!B33</f>
-        <v>401.UE</v>
-      </c>
-      <c r="F7" s="43">
-        <f>IF(Declarații_TAXARE_INVERSA!B12="DA",Declarații_TAXARE_INVERSA!B17,0)</f>
-        <v>74550</v>
-      </c>
-      <c r="G7" s="43" t="str">
-        <f>"Datorie furnizor UE " &amp; Declarații_TAXARE_INVERSA!B39</f>
-        <v>Datorie furnizor UE — taxare inversă 2026-07</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="43" t="inlineStr">
-        <is>
-          <t>Check A1 (factura)</t>
-        </is>
-      </c>
-      <c r="B8" s="43">
-        <f>C7-F7</f>
-        <v>0</v>
-      </c>
-      <c r="C8" s="43" t="str">
-        <f>IF(ABS(B8)&lt;0.01,"OK","EROARE")</f>
-        <v>OK</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="43" t="n">
-        <v>2</v>
-      </c>
-      <c r="B9" s="43" t="str">
-        <f>Declarații_TAXARE_INVERSA!B35</f>
-        <v>4426</v>
-      </c>
-      <c r="C9" s="43">
-        <f>IF(Declarații_TAXARE_INVERSA!B12="DA",Declarații_TAXARE_INVERSA!B18,0)</f>
-        <v>15655.5</v>
-      </c>
-      <c r="D9" s="43" t="str">
-        <f>"TVA deductibilă prin autolichidare " &amp; Declarații_TAXARE_INVERSA!B39</f>
-        <v>TVA deductibilă prin autolichidare — taxare inversă 2026-07</v>
-      </c>
-      <c r="E9" s="43" t="str">
-        <f>Declarații_TAXARE_INVERSA!B36</f>
-        <v>4427</v>
-      </c>
-      <c r="F9" s="43">
-        <f>IF(Declarații_TAXARE_INVERSA!B12="DA",Declarații_TAXARE_INVERSA!B18,0)</f>
-        <v>15655.5</v>
-      </c>
-      <c r="G9" s="43" t="str">
-        <f>"TVA colectată prin autolichidare " &amp; Declarații_TAXARE_INVERSA!B39</f>
-        <v>TVA colectată prin autolichidare — taxare inversă 2026-07</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="43" t="inlineStr">
-        <is>
-          <t>Check A2 (autolichidare = cotă × bază)</t>
-        </is>
-      </c>
-      <c r="B10" s="43">
-        <f>C9-IF(Declarații_TAXARE_INVERSA!B12="DA",Declarații_TAXARE_INVERSA!B19,0)</f>
-        <v>0</v>
-      </c>
-      <c r="C10" s="43" t="str">
-        <f>IF(ABS(B10)&lt;0.01,"OK — 4426 = 4427 = cotă × bază","EROARE — suma din notă nu e cotă × bază")</f>
-        <v>OK — 4426 = 4427 = cotă × bază</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="42" t="inlineStr">
-        <is>
-          <t>Bloc B — Taxare inversă internă</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="65" t="inlineStr">
-        <is>
-          <t>Nr</t>
-        </is>
-      </c>
-      <c r="B13" s="65" t="inlineStr">
-        <is>
-          <t>Cont Dr</t>
-        </is>
-      </c>
-      <c r="C13" s="65" t="inlineStr">
-        <is>
-          <t>Sumă Dr</t>
-        </is>
-      </c>
-      <c r="D13" s="65" t="inlineStr">
-        <is>
-          <t>Descriere Dr</t>
-        </is>
-      </c>
-      <c r="E13" s="65" t="inlineStr">
-        <is>
-          <t>Cont Cr</t>
-        </is>
-      </c>
-      <c r="F13" s="65" t="inlineStr">
-        <is>
-          <t>Sumă Cr</t>
-        </is>
-      </c>
-      <c r="G13" s="65" t="inlineStr">
-        <is>
-          <t>Descriere Cr</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="43" t="n">
-        <v>1</v>
-      </c>
-      <c r="B14" s="43" t="str">
-        <f>Declarații_TAXARE_INVERSA!B31</f>
-        <v>371</v>
-      </c>
-      <c r="C14" s="43">
-        <f>IF(Declarații_TAXARE_INVERSA!B23="DA",Declarații_TAXARE_INVERSA!B26,0)</f>
-        <v>10000</v>
-      </c>
-      <c r="D14" s="43" t="str">
-        <f>"Achiziție cu taxare inversă (" &amp; Declarații_TAXARE_INVERSA!B25 &amp; ") " &amp; Declarații_TAXARE_INVERSA!B39</f>
-        <v>Achiziție cu taxare inversă (Cereale) — taxare inversă 2026-07</v>
-      </c>
-      <c r="E14" s="43" t="str">
-        <f>Declarații_TAXARE_INVERSA!B34</f>
-        <v>401.RO</v>
-      </c>
-      <c r="F14" s="43">
-        <f>IF(Declarații_TAXARE_INVERSA!B23="DA",Declarații_TAXARE_INVERSA!B26,0)</f>
-        <v>10000</v>
-      </c>
-      <c r="G14" s="43" t="str">
-        <f>"Datorie furnizor RO " &amp; Declarații_TAXARE_INVERSA!B39</f>
-        <v>Datorie furnizor RO — taxare inversă 2026-07</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="43" t="inlineStr">
-        <is>
-          <t>Check B1 (factura)</t>
-        </is>
-      </c>
-      <c r="B15" s="43">
-        <f>C14-F14</f>
-        <v>0</v>
-      </c>
-      <c r="C15" s="43" t="str">
-        <f>IF(ABS(B15)&lt;0.01,"OK","EROARE")</f>
-        <v>OK</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="43" t="n">
-        <v>2</v>
-      </c>
-      <c r="B16" s="43" t="str">
-        <f>Declarații_TAXARE_INVERSA!B35</f>
-        <v>4426</v>
-      </c>
-      <c r="C16" s="43">
-        <f>IF(Declarații_TAXARE_INVERSA!B23="DA",Declarații_TAXARE_INVERSA!B27,0)</f>
-        <v>2100</v>
-      </c>
-      <c r="D16" s="43" t="str">
-        <f>"TVA deductibilă prin autolichidare " &amp; Declarații_TAXARE_INVERSA!B39</f>
-        <v>TVA deductibilă prin autolichidare — taxare inversă 2026-07</v>
-      </c>
-      <c r="E16" s="43" t="str">
-        <f>Declarații_TAXARE_INVERSA!B36</f>
-        <v>4427</v>
-      </c>
-      <c r="F16" s="43">
-        <f>IF(Declarații_TAXARE_INVERSA!B23="DA",Declarații_TAXARE_INVERSA!B27,0)</f>
-        <v>2100</v>
-      </c>
-      <c r="G16" s="43" t="str">
-        <f>"TVA colectată prin autolichidare " &amp; Declarații_TAXARE_INVERSA!B39</f>
-        <v>TVA colectată prin autolichidare — taxare inversă 2026-07</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="43" t="inlineStr">
-        <is>
-          <t>Check B2 (autolichidare = cotă × bază)</t>
-        </is>
-      </c>
-      <c r="B17" s="43">
-        <f>C16-IF(Declarații_TAXARE_INVERSA!B23="DA",Declarații_TAXARE_INVERSA!B28,0)</f>
-        <v>0</v>
-      </c>
-      <c r="C17" s="43" t="str">
-        <f>IF(ABS(B17)&lt;0.01,"OK — 4426 = 4427 = cotă × bază","EROARE — suma din notă nu e cotă × bază")</f>
-        <v>OK — 4426 = 4427 = cotă × bază</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="43" t="inlineStr">
-        <is>
-          <t>Check global</t>
-        </is>
-      </c>
-      <c r="B19" s="43">
-        <f>ABS(B8)+ABS(B10)+ABS(B15)+ABS(B17)</f>
-        <v>0</v>
-      </c>
-      <c r="C19" s="43" t="str">
-        <f>IF(B19&lt;0.01,"OK — toate blocurile se închid","EROARE — cel puțin un bloc dezechilibrat")</f>
-        <v>OK — toate blocurile se închid</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="42" t="inlineStr">
-        <is>
-          <t>Stare terminală</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="44" t="inlineStr">
-        <is>
-          <t>Nicio TVA de plată suplimentară din operațiunile astea: 4426 și 4427 s-au mișcat cu aceeași sumă și se anulează la închiderea lunară. Ce rămâne e raportarea: D300 la ambele, D390 doar la intracomunitar.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet68.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:I11"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="6" customWidth="1" style="40" min="1" max="1"/>
-    <col width="26" customWidth="1" style="40" min="2" max="2"/>
-    <col width="14" customWidth="1" style="40" min="3" max="3"/>
-    <col width="12" customWidth="1" style="40" min="4" max="4"/>
-    <col width="12" customWidth="1" style="40" min="5" max="5"/>
-    <col width="14" customWidth="1" style="40" min="6" max="6"/>
-    <col width="50" customWidth="1" style="40" min="7" max="7"/>
-    <col width="24" customWidth="1" style="40" min="8" max="8"/>
-    <col width="10" customWidth="1" style="40" min="9" max="9"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="41" t="inlineStr">
-        <is>
-          <t>MOD_TAXARE_INVERSA — Notă pentru import</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="44" t="inlineStr">
-        <is>
-          <t>Filtrează Include=DA. Cazurile neactivate ies cu sumă 0 și apar ca NU.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="65" t="inlineStr">
-        <is>
-          <t>Nr</t>
-        </is>
-      </c>
-      <c r="B4" s="65" t="inlineStr">
-        <is>
-          <t>Bloc</t>
-        </is>
-      </c>
-      <c r="C4" s="65" t="inlineStr">
-        <is>
-          <t>Data</t>
-        </is>
-      </c>
-      <c r="D4" s="65" t="inlineStr">
-        <is>
-          <t>Cont Dr</t>
-        </is>
-      </c>
-      <c r="E4" s="65" t="inlineStr">
-        <is>
-          <t>Cont Cr</t>
-        </is>
-      </c>
-      <c r="F4" s="65" t="inlineStr">
-        <is>
-          <t>Sumă</t>
-        </is>
-      </c>
-      <c r="G4" s="65" t="inlineStr">
-        <is>
-          <t>Descriere</t>
-        </is>
-      </c>
-      <c r="H4" s="65" t="inlineStr">
-        <is>
-          <t>Document</t>
-        </is>
-      </c>
-      <c r="I4" s="65" t="inlineStr">
-        <is>
-          <t>Include</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="43" t="n">
-        <v>1</v>
-      </c>
-      <c r="B5" s="43" t="inlineStr">
-        <is>
-          <t>A Intracomunitar — factura</t>
-        </is>
-      </c>
-      <c r="C5" s="43" t="str">
-        <f>Declarații_TAXARE_INVERSA!B8</f>
-        <v>2026-07-31</v>
-      </c>
-      <c r="D5" s="43" t="str">
-        <f>Jurnale_TAXARE_INVERSA!B7</f>
-        <v>371</v>
-      </c>
-      <c r="E5" s="43" t="str">
-        <f>Jurnale_TAXARE_INVERSA!E7</f>
-        <v>401.UE</v>
-      </c>
-      <c r="F5" s="43">
-        <f>Jurnale_TAXARE_INVERSA!C7</f>
-        <v>74550</v>
-      </c>
-      <c r="G5" s="43" t="str">
-        <f>Jurnale_TAXARE_INVERSA!D7</f>
-        <v>Achiziție intracomunitară Furnizor UE DEMO — taxare inversă 2026-07</v>
-      </c>
-      <c r="H5" s="43" t="inlineStr">
-        <is>
-          <t>Factură furnizor UE</t>
-        </is>
-      </c>
-      <c r="I5" s="43" t="str">
-        <f>IF(AND(ISNUMBER(F5),F5&gt;0),"DA","NU")</f>
-        <v>DA</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="43" t="n">
-        <v>2</v>
-      </c>
-      <c r="B6" s="43" t="inlineStr">
-        <is>
-          <t>A Intracomunitar — autolichidare</t>
-        </is>
-      </c>
-      <c r="C6" s="43" t="str">
-        <f>Declarații_TAXARE_INVERSA!B8</f>
-        <v>2026-07-31</v>
-      </c>
-      <c r="D6" s="43" t="str">
-        <f>Jurnale_TAXARE_INVERSA!B9</f>
-        <v>4426</v>
-      </c>
-      <c r="E6" s="43" t="str">
-        <f>Jurnale_TAXARE_INVERSA!E9</f>
-        <v>4427</v>
-      </c>
-      <c r="F6" s="43">
-        <f>Jurnale_TAXARE_INVERSA!C9</f>
-        <v>15655.5</v>
-      </c>
-      <c r="G6" s="43" t="str">
-        <f>Jurnale_TAXARE_INVERSA!D9</f>
-        <v>TVA deductibilă prin autolichidare — taxare inversă 2026-07</v>
-      </c>
-      <c r="H6" s="43" t="inlineStr">
-        <is>
-          <t>Autofactură</t>
-        </is>
-      </c>
-      <c r="I6" s="43" t="str">
-        <f>IF(AND(ISNUMBER(F6),F6&gt;0),"DA","NU")</f>
-        <v>DA</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="43" t="n">
-        <v>3</v>
-      </c>
-      <c r="B7" s="43" t="inlineStr">
-        <is>
-          <t>B Intern — factura</t>
-        </is>
-      </c>
-      <c r="C7" s="43" t="str">
-        <f>Declarații_TAXARE_INVERSA!B8</f>
-        <v>2026-07-31</v>
-      </c>
-      <c r="D7" s="43" t="str">
-        <f>Jurnale_TAXARE_INVERSA!B14</f>
-        <v>371</v>
-      </c>
-      <c r="E7" s="43" t="str">
-        <f>Jurnale_TAXARE_INVERSA!E14</f>
-        <v>401.RO</v>
-      </c>
-      <c r="F7" s="43">
-        <f>Jurnale_TAXARE_INVERSA!C14</f>
-        <v>10000</v>
-      </c>
-      <c r="G7" s="43" t="str">
-        <f>Jurnale_TAXARE_INVERSA!D14</f>
-        <v>Achiziție cu taxare inversă (Cereale) — taxare inversă 2026-07</v>
-      </c>
-      <c r="H7" s="43" t="inlineStr">
-        <is>
-          <t>Factură (mențiune taxare inversă)</t>
-        </is>
-      </c>
-      <c r="I7" s="43" t="str">
-        <f>IF(AND(ISNUMBER(F7),F7&gt;0),"DA","NU")</f>
-        <v>DA</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="43" t="n">
-        <v>4</v>
-      </c>
-      <c r="B8" s="43" t="inlineStr">
-        <is>
-          <t>B Intern — autolichidare</t>
-        </is>
-      </c>
-      <c r="C8" s="43" t="str">
-        <f>Declarații_TAXARE_INVERSA!B8</f>
-        <v>2026-07-31</v>
-      </c>
-      <c r="D8" s="43" t="str">
-        <f>Jurnale_TAXARE_INVERSA!B16</f>
-        <v>4426</v>
-      </c>
-      <c r="E8" s="43" t="str">
-        <f>Jurnale_TAXARE_INVERSA!E16</f>
-        <v>4427</v>
-      </c>
-      <c r="F8" s="43">
-        <f>Jurnale_TAXARE_INVERSA!C16</f>
-        <v>2100</v>
-      </c>
-      <c r="G8" s="43" t="str">
-        <f>Jurnale_TAXARE_INVERSA!D16</f>
-        <v>TVA deductibilă prin autolichidare — taxare inversă 2026-07</v>
-      </c>
-      <c r="H8" s="43" t="inlineStr">
-        <is>
-          <t>Autofactură</t>
-        </is>
-      </c>
-      <c r="I8" s="43" t="str">
-        <f>IF(AND(ISNUMBER(F8),F8&gt;0),"DA","NU")</f>
-        <v>DA</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="43" t="inlineStr">
-        <is>
-          <t>Rânduri de importat</t>
-        </is>
-      </c>
-      <c r="B10" s="43">
-        <f>COUNTIF(I5:I8,"DA")</f>
-        <v>4</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="43" t="inlineStr">
-        <is>
-          <t>Check global</t>
-        </is>
-      </c>
-      <c r="B11" s="43">
-        <f>Jurnale_TAXARE_INVERSA!B19</f>
-        <v>0</v>
-      </c>
-      <c r="C11" s="43" t="str">
-        <f>IF(ABS(B11)&lt;0.01,"OK","EROARE")</f>
-        <v>OK</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet69.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:C42"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="50" customWidth="1" style="40" min="1" max="1"/>
-    <col width="22" customWidth="1" style="40" min="2" max="2"/>
-    <col width="58" customWidth="1" style="40" min="3" max="3"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="41" t="inlineStr">
-        <is>
-          <t>MOD_FARA_DOCUMENT — Declarații (input)</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="44" t="inlineStr">
-        <is>
-          <t>Două cazuri independente. Pune DA pe cel care s-a întâmplat — de obicei primul se aplică lunar, al doilea doar după inventar.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="42" t="inlineStr">
-        <is>
-          <t>1. Antet</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="43" t="inlineStr">
-        <is>
-          <t>Societate</t>
-        </is>
-      </c>
-      <c r="B5" s="43" t="str">
-        <f>Parametri!B5</f>
-        <v>SC EXEMPLU SRL</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="43" t="inlineStr">
-        <is>
-          <t>CUI</t>
-        </is>
-      </c>
-      <c r="B6" s="43" t="str">
-        <f>Parametri!B6</f>
-        <v>RO00000000</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="43" t="inlineStr">
-        <is>
-          <t>Luna (AAAA-LL)</t>
-        </is>
-      </c>
-      <c r="B7" s="64" t="inlineStr">
-        <is>
-          <t>2026-07</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="43" t="inlineStr">
-        <is>
-          <t>Data jurnal</t>
-        </is>
-      </c>
-      <c r="B8" s="64" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="43" t="inlineStr">
-        <is>
-          <t>Cota TVA</t>
-        </is>
-      </c>
-      <c r="B9" s="64" t="n">
-        <v>0.21</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="42" t="inlineStr">
-        <is>
-          <t>2. Cazul A — Vehicul cu regim mixt (deducere 50%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="43" t="inlineStr">
-        <is>
-          <t>Se aplică? (DA/NU)</t>
-        </is>
-      </c>
-      <c r="B12" s="64" t="inlineStr">
-        <is>
-          <t>DA</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="43" t="inlineStr">
-        <is>
-          <t>Regim (MIXT / EXCLUSIV / EXCEPTAT)</t>
-        </is>
-      </c>
-      <c r="B13" s="64" t="inlineStr">
-        <is>
-          <t>MIXT</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="43" t="inlineStr">
-        <is>
-          <t>Valoare factură fără TVA</t>
-        </is>
-      </c>
-      <c r="B14" s="64" t="n">
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="43" t="inlineStr">
-        <is>
-          <t>TVA de pe factură (auto)</t>
-        </is>
-      </c>
-      <c r="B15" s="43">
-        <f>ROUND(B14*B9,2)</f>
-        <v>210</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="43" t="inlineStr">
-        <is>
-          <t>Procent de deducere (auto)</t>
-        </is>
-      </c>
-      <c r="B16" s="43">
-        <f>IF(B13="MIXT",param_proc_vehicul,1)</f>
-        <v>0.5</v>
-      </c>
-      <c r="C16" s="44" t="inlineStr">
-        <is>
-          <t>La MIXT vine din param_proc_vehicul; la EXCLUSIV și EXCEPTAT se deduce integral</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="43" t="inlineStr">
-        <is>
-          <t>TVA deductibilă (auto)</t>
-        </is>
-      </c>
-      <c r="B17" s="43">
-        <f>ROUND(B15*B16,2)</f>
-        <v>105</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="43" t="inlineStr">
-        <is>
-          <t>TVA nedeductibilă (auto)</t>
-        </is>
-      </c>
-      <c r="B18" s="43">
-        <f>B15-B17</f>
-        <v>105</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="43" t="inlineStr">
-        <is>
-          <t>Cheltuială = net + TVA nedeductibilă (auto)</t>
-        </is>
-      </c>
-      <c r="B19" s="43">
-        <f>B14+B18</f>
-        <v>1105</v>
-      </c>
-      <c r="C19" s="44" t="inlineStr">
-        <is>
-          <t>TVA nedeductibilă NU se pierde: se incorporează în cheltuială</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="43" t="inlineStr">
-        <is>
-          <t>Total factură (auto)</t>
-        </is>
-      </c>
-      <c r="B20" s="43">
-        <f>B14+B15</f>
-        <v>1210</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="42" t="inlineStr">
-        <is>
-          <t>3. Cazul B — Lipsă la inventar</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="43" t="inlineStr">
-        <is>
-          <t>Se aplică? (DA/NU)</t>
-        </is>
-      </c>
-      <c r="B23" s="64" t="inlineStr">
-        <is>
-          <t>DA</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="43" t="inlineStr">
-        <is>
-          <t>Lipsa e JUSTIFICATĂ? (DA/NU)</t>
-        </is>
-      </c>
-      <c r="B24" s="64" t="inlineStr">
-        <is>
-          <t>NU</t>
-        </is>
-      </c>
-      <c r="C24" s="44" t="inlineStr">
-        <is>
-          <t>Calamitate, perisabilități în limita legală, casare documentată. Nejustificată = se colectează TVA</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="43" t="inlineStr">
-        <is>
-          <t>Costul bunului lipsă</t>
-        </is>
-      </c>
-      <c r="B25" s="64" t="n">
-        <v>1200</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="43" t="inlineStr">
-        <is>
-          <t>TVA de colectat (auto)</t>
-        </is>
-      </c>
-      <c r="B26" s="43">
-        <f>IF(B24="DA",0,ROUND(B25*B9,2))</f>
-        <v>252</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="42" t="inlineStr">
-        <is>
-          <t>4. Conturi</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="43" t="inlineStr">
-        <is>
-          <t>Cheltuială cu serviciile (628)</t>
-        </is>
-      </c>
-      <c r="B29" s="64" t="inlineStr">
-        <is>
-          <t>628</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="43" t="inlineStr">
-        <is>
-          <t>Alte cheltuieli de exploatare (658)</t>
-        </is>
-      </c>
-      <c r="B30" s="64" t="inlineStr">
-        <is>
-          <t>658</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="43" t="inlineStr">
-        <is>
-          <t>Furnizor</t>
-        </is>
-      </c>
-      <c r="B31" s="64" t="inlineStr">
-        <is>
-          <t>401</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="43" t="inlineStr">
-        <is>
-          <t>Cont stoc</t>
-        </is>
-      </c>
-      <c r="B32" s="64" t="inlineStr">
-        <is>
-          <t>371</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="43" t="inlineStr">
-        <is>
-          <t>TVA deductibilă</t>
-        </is>
-      </c>
-      <c r="B33" s="64" t="inlineStr">
-        <is>
-          <t>4426</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="43" t="inlineStr">
-        <is>
-          <t>TVA colectată</t>
-        </is>
-      </c>
-      <c r="B34" s="64" t="inlineStr">
-        <is>
-          <t>4427</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="42" t="inlineStr">
-        <is>
-          <t>5. Sufix</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="43" t="inlineStr">
-        <is>
-          <t>Sufix</t>
-        </is>
-      </c>
-      <c r="B37" s="43" t="str">
-        <f>"— fără document " &amp; B7</f>
-        <v>— fără document 2026-07</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="42" t="inlineStr">
-        <is>
-          <t>6. Control</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="43" t="inlineStr">
-        <is>
-          <t>Modul activ?</t>
-        </is>
-      </c>
-      <c r="B40" s="43" t="str">
-        <f>IF(INDEX(CatalogModule!$A$1:$A$200,MATCH("MOD_FARA_DOCUMENT",CatalogModule!$B$1:$B$200,0))="DA","ACTIV","INACTIV")</f>
-        <v>INACTIV</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="43" t="inlineStr">
-        <is>
-          <t>Verificare: cheltuială + TVA dedusă = total factură</t>
-        </is>
-      </c>
-      <c r="B41" s="43" t="str">
-        <f>IF(OR(B12&lt;&gt;"DA",ABS((B19+B17)-B20)&lt;0.01),"OK — TVA nedeductibilă e în cheltuială, nimic nu se pierde","EROARE — nota nu acoperă totalul facturii")</f>
-        <v>OK — TVA nedeductibilă e în cheltuială, nimic nu se pierde</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="43" t="inlineStr">
-        <is>
-          <t>Regula de sens la lipsă</t>
-        </is>
-      </c>
-      <c r="B42" s="43" t="str">
-        <f>IF(AND(B23="DA",B24&lt;&gt;"DA"),"4427 se CREDITEAZĂ — colectezi, nu storna deducerea","—")</f>
-        <v>4427 se CREDITEAZĂ — colectezi, nu storna deducerea</v>
       </c>
     </row>
   </sheetData>
@@ -30698,6 +31165,1309 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:E26"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" style="40" min="1" max="1"/>
+    <col width="44" customWidth="1" style="40" min="2" max="2"/>
+    <col width="16" customWidth="1" style="40" min="3" max="3"/>
+    <col width="44" customWidth="1" style="40" min="4" max="4"/>
+    <col width="48" customWidth="1" style="40" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="41" t="inlineStr">
+        <is>
+          <t>MOD_TAXARE_INVERSA — Reguli (tabele fixe)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="44" t="inlineStr">
+        <is>
+          <t>Regula e dată, nu formulă. Mecanismul contabil e identic în ambele cazuri; diferă partenerul și declarația.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="42" t="inlineStr">
+        <is>
+          <t>Tabel A — Cele două cazuri</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="65" t="inlineStr">
+        <is>
+          <t>Caz</t>
+        </is>
+      </c>
+      <c r="B5" s="65" t="inlineStr">
+        <is>
+          <t>Partener</t>
+        </is>
+      </c>
+      <c r="C5" s="65" t="inlineStr">
+        <is>
+          <t>Cont furnizor</t>
+        </is>
+      </c>
+      <c r="D5" s="65" t="inlineStr">
+        <is>
+          <t>Ce declară</t>
+        </is>
+      </c>
+      <c r="E5" s="65" t="inlineStr">
+        <is>
+          <t>Condiție</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="43" t="inlineStr">
+        <is>
+          <t>Achiziție intracomunitară</t>
+        </is>
+      </c>
+      <c r="B6" s="43" t="inlineStr">
+        <is>
+          <t>Persoană impozabilă din alt stat membru</t>
+        </is>
+      </c>
+      <c r="C6" s="43" t="inlineStr">
+        <is>
+          <t>401.UE</t>
+        </is>
+      </c>
+      <c r="D6" s="43" t="inlineStr">
+        <is>
+          <t>D300 (casete taxare inversă) + D390 + D394</t>
+        </is>
+      </c>
+      <c r="E6" s="43" t="inlineStr">
+        <is>
+          <t>Cod de TVA valid în VIES la data operațiunii</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="43" t="inlineStr">
+        <is>
+          <t>Taxare inversă internă</t>
+        </is>
+      </c>
+      <c r="B7" s="43" t="inlineStr">
+        <is>
+          <t>Plătitor de TVA din România</t>
+        </is>
+      </c>
+      <c r="C7" s="43" t="inlineStr">
+        <is>
+          <t>401.RO</t>
+        </is>
+      </c>
+      <c r="D7" s="43" t="inlineStr">
+        <is>
+          <t>D300 (casete taxare inversă) + D394, FĂRĂ D390</t>
+        </is>
+      </c>
+      <c r="E7" s="43" t="inlineStr">
+        <is>
+          <t>Bunul sau serviciul e pe lista art. 331 CF</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="42" t="inlineStr">
+        <is>
+          <t>Tabel B — Operațiuni cu taxare inversă internă (art. 331 CF)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="65" t="inlineStr">
+        <is>
+          <t>Operațiune</t>
+        </is>
+      </c>
+      <c r="B10" s="65" t="inlineStr">
+        <is>
+          <t>Prag</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="43" t="inlineStr">
+        <is>
+          <t>Cereale și plante tehnice</t>
+        </is>
+      </c>
+      <c r="B11" s="43" t="inlineStr">
+        <is>
+          <t>fără prag valoric</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="43" t="inlineStr">
+        <is>
+          <t>Certificate de emisii de gaze cu efect de seră</t>
+        </is>
+      </c>
+      <c r="B12" s="43" t="inlineStr">
+        <is>
+          <t>fără prag valoric</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="43" t="inlineStr">
+        <is>
+          <t>Energie electrică și gaze naturale către comercianți persoane impozabile</t>
+        </is>
+      </c>
+      <c r="B13" s="43" t="inlineStr">
+        <is>
+          <t>fără prag valoric</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="43" t="inlineStr">
+        <is>
+          <t>Certificate verzi</t>
+        </is>
+      </c>
+      <c r="B14" s="43" t="inlineStr">
+        <is>
+          <t>fără prag valoric</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="43" t="inlineStr">
+        <is>
+          <t>Telefoane mobile</t>
+        </is>
+      </c>
+      <c r="B15" s="43" t="inlineStr">
+        <is>
+          <t>doar dacă valoarea fără TVA de pe factură ≥ 22.500 lei</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="43" t="inlineStr">
+        <is>
+          <t>Dispozitive cu circuite integrate</t>
+        </is>
+      </c>
+      <c r="B16" s="43" t="inlineStr">
+        <is>
+          <t>doar dacă valoarea fără TVA de pe factură ≥ 22.500 lei</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="43" t="inlineStr">
+        <is>
+          <t>Console de jocuri</t>
+        </is>
+      </c>
+      <c r="B17" s="43" t="inlineStr">
+        <is>
+          <t>doar dacă valoarea fără TVA de pe factură ≥ 22.500 lei</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="43" t="inlineStr">
+        <is>
+          <t>Tablete și laptopuri</t>
+        </is>
+      </c>
+      <c r="B18" s="43" t="inlineStr">
+        <is>
+          <t>doar dacă valoarea fără TVA de pe factură ≥ 22.500 lei</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="44" t="inlineStr">
+        <is>
+          <t>Derogarea Consiliului UE pe baza căreia se aplică art. 331 expiră la 31.12.2026. Verificat la 21.08.2026: nicio prelungire publicată. Nu se presupune prelungirea automată.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="42" t="inlineStr">
+        <is>
+          <t>Tabel C — Porți de calitate</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="44" t="inlineStr">
+        <is>
+          <t>• 4426 și 4427 primesc EXACT aceeași sumă — netul pe operațiune e zero</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="44" t="inlineStr">
+        <is>
+          <t>• D390 doar la intracomunitar; un partener intern trecut acolo se vede la ANAF prin necorelare cu VIES</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="44" t="inlineStr">
+        <is>
+          <t>• Codul VIES se verifică la DATA operațiunii, nu la data când te uiți</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="44" t="inlineStr">
+        <is>
+          <t>• Fără TVA plătită efectiv: autolichidarea nu produce flux de trezorerie</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="44" t="inlineStr">
+        <is>
+          <t>• La închiderea lunară, sumele astea intră în 4426/4427 ca oricare altele și se anulează reciproc — vezi MOD_INCHIDERE_TVA</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet71.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G22"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" style="40" min="1" max="1"/>
+    <col width="16" customWidth="1" style="40" min="2" max="2"/>
+    <col width="14" customWidth="1" style="40" min="3" max="3"/>
+    <col width="50" customWidth="1" style="40" min="4" max="4"/>
+    <col width="16" customWidth="1" style="40" min="5" max="5"/>
+    <col width="14" customWidth="1" style="40" min="6" max="6"/>
+    <col width="50" customWidth="1" style="40" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="41" t="inlineStr">
+        <is>
+          <t>MOD_TAXARE_INVERSA — Jurnale (generate automat)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="44" t="inlineStr">
+        <is>
+          <t>Fiecare caz iese cu zero dacă nu e activat. Pasul de autolichidare are aceeași sumă pe ambele părți — asta e chiar mecanismul, nu o coincidență.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="42" t="inlineStr">
+        <is>
+          <t>Bloc A — Achiziție intracomunitară</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="43" t="inlineStr">
+        <is>
+          <t>Data:</t>
+        </is>
+      </c>
+      <c r="B5" s="43" t="str">
+        <f>Declarații_TAXARE_INVERSA!B8</f>
+        <v>2026-07-31</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="65" t="inlineStr">
+        <is>
+          <t>Nr</t>
+        </is>
+      </c>
+      <c r="B6" s="65" t="inlineStr">
+        <is>
+          <t>Cont Dr</t>
+        </is>
+      </c>
+      <c r="C6" s="65" t="inlineStr">
+        <is>
+          <t>Sumă Dr</t>
+        </is>
+      </c>
+      <c r="D6" s="65" t="inlineStr">
+        <is>
+          <t>Descriere Dr</t>
+        </is>
+      </c>
+      <c r="E6" s="65" t="inlineStr">
+        <is>
+          <t>Cont Cr</t>
+        </is>
+      </c>
+      <c r="F6" s="65" t="inlineStr">
+        <is>
+          <t>Sumă Cr</t>
+        </is>
+      </c>
+      <c r="G6" s="65" t="inlineStr">
+        <is>
+          <t>Descriere Cr</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="43" t="n">
+        <v>1</v>
+      </c>
+      <c r="B7" s="43" t="str">
+        <f>IF(Declarații_TAXARE_INVERSA!B20="DA",Declarații_TAXARE_INVERSA!B32,Declarații_TAXARE_INVERSA!B31)</f>
+        <v>371</v>
+      </c>
+      <c r="C7" s="43">
+        <f>IF(Declarații_TAXARE_INVERSA!B12="DA",Declarații_TAXARE_INVERSA!B17,0)</f>
+        <v>74550</v>
+      </c>
+      <c r="D7" s="43" t="str">
+        <f>"Achiziție intracomunitară " &amp; Declarații_TAXARE_INVERSA!B13 &amp; " " &amp; Declarații_TAXARE_INVERSA!B39</f>
+        <v>Achiziție intracomunitară Furnizor UE DEMO — taxare inversă 2026-07</v>
+      </c>
+      <c r="E7" s="43" t="str">
+        <f>Declarații_TAXARE_INVERSA!B33</f>
+        <v>401.UE</v>
+      </c>
+      <c r="F7" s="43">
+        <f>IF(Declarații_TAXARE_INVERSA!B12="DA",Declarații_TAXARE_INVERSA!B17,0)</f>
+        <v>74550</v>
+      </c>
+      <c r="G7" s="43" t="str">
+        <f>"Datorie furnizor UE " &amp; Declarații_TAXARE_INVERSA!B39</f>
+        <v>Datorie furnizor UE — taxare inversă 2026-07</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="43" t="inlineStr">
+        <is>
+          <t>Check A1 (factura)</t>
+        </is>
+      </c>
+      <c r="B8" s="43">
+        <f>C7-F7</f>
+        <v>0</v>
+      </c>
+      <c r="C8" s="43" t="str">
+        <f>IF(ABS(B8)&lt;0.01,"OK","EROARE")</f>
+        <v>OK</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="43" t="n">
+        <v>2</v>
+      </c>
+      <c r="B9" s="43" t="str">
+        <f>Declarații_TAXARE_INVERSA!B35</f>
+        <v>4426</v>
+      </c>
+      <c r="C9" s="43">
+        <f>IF(Declarații_TAXARE_INVERSA!B12="DA",Declarații_TAXARE_INVERSA!B18,0)</f>
+        <v>15655.5</v>
+      </c>
+      <c r="D9" s="43" t="str">
+        <f>"TVA deductibilă prin autolichidare " &amp; Declarații_TAXARE_INVERSA!B39</f>
+        <v>TVA deductibilă prin autolichidare — taxare inversă 2026-07</v>
+      </c>
+      <c r="E9" s="43" t="str">
+        <f>Declarații_TAXARE_INVERSA!B36</f>
+        <v>4427</v>
+      </c>
+      <c r="F9" s="43">
+        <f>IF(Declarații_TAXARE_INVERSA!B12="DA",Declarații_TAXARE_INVERSA!B18,0)</f>
+        <v>15655.5</v>
+      </c>
+      <c r="G9" s="43" t="str">
+        <f>"TVA colectată prin autolichidare " &amp; Declarații_TAXARE_INVERSA!B39</f>
+        <v>TVA colectată prin autolichidare — taxare inversă 2026-07</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="43" t="inlineStr">
+        <is>
+          <t>Check A2 (autolichidare = cotă × bază)</t>
+        </is>
+      </c>
+      <c r="B10" s="43">
+        <f>C9-IF(Declarații_TAXARE_INVERSA!B12="DA",Declarații_TAXARE_INVERSA!B19,0)</f>
+        <v>0</v>
+      </c>
+      <c r="C10" s="43" t="str">
+        <f>IF(ABS(B10)&lt;0.01,"OK — 4426 = 4427 = cotă × bază","EROARE — suma din notă nu e cotă × bază")</f>
+        <v>OK — 4426 = 4427 = cotă × bază</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="42" t="inlineStr">
+        <is>
+          <t>Bloc B — Taxare inversă internă</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="65" t="inlineStr">
+        <is>
+          <t>Nr</t>
+        </is>
+      </c>
+      <c r="B13" s="65" t="inlineStr">
+        <is>
+          <t>Cont Dr</t>
+        </is>
+      </c>
+      <c r="C13" s="65" t="inlineStr">
+        <is>
+          <t>Sumă Dr</t>
+        </is>
+      </c>
+      <c r="D13" s="65" t="inlineStr">
+        <is>
+          <t>Descriere Dr</t>
+        </is>
+      </c>
+      <c r="E13" s="65" t="inlineStr">
+        <is>
+          <t>Cont Cr</t>
+        </is>
+      </c>
+      <c r="F13" s="65" t="inlineStr">
+        <is>
+          <t>Sumă Cr</t>
+        </is>
+      </c>
+      <c r="G13" s="65" t="inlineStr">
+        <is>
+          <t>Descriere Cr</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="43" t="n">
+        <v>1</v>
+      </c>
+      <c r="B14" s="43" t="str">
+        <f>Declarații_TAXARE_INVERSA!B31</f>
+        <v>371</v>
+      </c>
+      <c r="C14" s="43">
+        <f>IF(Declarații_TAXARE_INVERSA!B23="DA",Declarații_TAXARE_INVERSA!B26,0)</f>
+        <v>10000</v>
+      </c>
+      <c r="D14" s="43" t="str">
+        <f>"Achiziție cu taxare inversă (" &amp; Declarații_TAXARE_INVERSA!B25 &amp; ") " &amp; Declarații_TAXARE_INVERSA!B39</f>
+        <v>Achiziție cu taxare inversă (Cereale) — taxare inversă 2026-07</v>
+      </c>
+      <c r="E14" s="43" t="str">
+        <f>Declarații_TAXARE_INVERSA!B34</f>
+        <v>401.RO</v>
+      </c>
+      <c r="F14" s="43">
+        <f>IF(Declarații_TAXARE_INVERSA!B23="DA",Declarații_TAXARE_INVERSA!B26,0)</f>
+        <v>10000</v>
+      </c>
+      <c r="G14" s="43" t="str">
+        <f>"Datorie furnizor RO " &amp; Declarații_TAXARE_INVERSA!B39</f>
+        <v>Datorie furnizor RO — taxare inversă 2026-07</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="43" t="inlineStr">
+        <is>
+          <t>Check B1 (factura)</t>
+        </is>
+      </c>
+      <c r="B15" s="43">
+        <f>C14-F14</f>
+        <v>0</v>
+      </c>
+      <c r="C15" s="43" t="str">
+        <f>IF(ABS(B15)&lt;0.01,"OK","EROARE")</f>
+        <v>OK</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="43" t="n">
+        <v>2</v>
+      </c>
+      <c r="B16" s="43" t="str">
+        <f>Declarații_TAXARE_INVERSA!B35</f>
+        <v>4426</v>
+      </c>
+      <c r="C16" s="43">
+        <f>IF(Declarații_TAXARE_INVERSA!B23="DA",Declarații_TAXARE_INVERSA!B27,0)</f>
+        <v>2100</v>
+      </c>
+      <c r="D16" s="43" t="str">
+        <f>"TVA deductibilă prin autolichidare " &amp; Declarații_TAXARE_INVERSA!B39</f>
+        <v>TVA deductibilă prin autolichidare — taxare inversă 2026-07</v>
+      </c>
+      <c r="E16" s="43" t="str">
+        <f>Declarații_TAXARE_INVERSA!B36</f>
+        <v>4427</v>
+      </c>
+      <c r="F16" s="43">
+        <f>IF(Declarații_TAXARE_INVERSA!B23="DA",Declarații_TAXARE_INVERSA!B27,0)</f>
+        <v>2100</v>
+      </c>
+      <c r="G16" s="43" t="str">
+        <f>"TVA colectată prin autolichidare " &amp; Declarații_TAXARE_INVERSA!B39</f>
+        <v>TVA colectată prin autolichidare — taxare inversă 2026-07</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="43" t="inlineStr">
+        <is>
+          <t>Check B2 (autolichidare = cotă × bază)</t>
+        </is>
+      </c>
+      <c r="B17" s="43">
+        <f>C16-IF(Declarații_TAXARE_INVERSA!B23="DA",Declarații_TAXARE_INVERSA!B28,0)</f>
+        <v>0</v>
+      </c>
+      <c r="C17" s="43" t="str">
+        <f>IF(ABS(B17)&lt;0.01,"OK — 4426 = 4427 = cotă × bază","EROARE — suma din notă nu e cotă × bază")</f>
+        <v>OK — 4426 = 4427 = cotă × bază</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="43" t="inlineStr">
+        <is>
+          <t>Check global</t>
+        </is>
+      </c>
+      <c r="B19" s="43">
+        <f>ABS(B8)+ABS(B10)+ABS(B15)+ABS(B17)</f>
+        <v>0</v>
+      </c>
+      <c r="C19" s="43" t="str">
+        <f>IF(B19&lt;0.01,"OK — toate blocurile se închid","EROARE — cel puțin un bloc dezechilibrat")</f>
+        <v>OK — toate blocurile se închid</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="42" t="inlineStr">
+        <is>
+          <t>Stare terminală</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="44" t="inlineStr">
+        <is>
+          <t>Nicio TVA de plată suplimentară din operațiunile astea: 4426 și 4427 s-au mișcat cu aceeași sumă și se anulează la închiderea lunară. Ce rămâne e raportarea: D300 la ambele, D390 doar la intracomunitar.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet72.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="6" customWidth="1" style="40" min="1" max="1"/>
+    <col width="26" customWidth="1" style="40" min="2" max="2"/>
+    <col width="14" customWidth="1" style="40" min="3" max="3"/>
+    <col width="12" customWidth="1" style="40" min="4" max="4"/>
+    <col width="12" customWidth="1" style="40" min="5" max="5"/>
+    <col width="14" customWidth="1" style="40" min="6" max="6"/>
+    <col width="50" customWidth="1" style="40" min="7" max="7"/>
+    <col width="24" customWidth="1" style="40" min="8" max="8"/>
+    <col width="10" customWidth="1" style="40" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="41" t="inlineStr">
+        <is>
+          <t>MOD_TAXARE_INVERSA — Notă pentru import</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="44" t="inlineStr">
+        <is>
+          <t>Filtrează Include=DA. Cazurile neactivate ies cu sumă 0 și apar ca NU.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="65" t="inlineStr">
+        <is>
+          <t>Nr</t>
+        </is>
+      </c>
+      <c r="B4" s="65" t="inlineStr">
+        <is>
+          <t>Bloc</t>
+        </is>
+      </c>
+      <c r="C4" s="65" t="inlineStr">
+        <is>
+          <t>Data</t>
+        </is>
+      </c>
+      <c r="D4" s="65" t="inlineStr">
+        <is>
+          <t>Cont Dr</t>
+        </is>
+      </c>
+      <c r="E4" s="65" t="inlineStr">
+        <is>
+          <t>Cont Cr</t>
+        </is>
+      </c>
+      <c r="F4" s="65" t="inlineStr">
+        <is>
+          <t>Sumă</t>
+        </is>
+      </c>
+      <c r="G4" s="65" t="inlineStr">
+        <is>
+          <t>Descriere</t>
+        </is>
+      </c>
+      <c r="H4" s="65" t="inlineStr">
+        <is>
+          <t>Document</t>
+        </is>
+      </c>
+      <c r="I4" s="65" t="inlineStr">
+        <is>
+          <t>Include</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="43" t="n">
+        <v>1</v>
+      </c>
+      <c r="B5" s="43" t="inlineStr">
+        <is>
+          <t>A Intracomunitar — factura</t>
+        </is>
+      </c>
+      <c r="C5" s="43" t="str">
+        <f>Declarații_TAXARE_INVERSA!B8</f>
+        <v>2026-07-31</v>
+      </c>
+      <c r="D5" s="43" t="str">
+        <f>Jurnale_TAXARE_INVERSA!B7</f>
+        <v>371</v>
+      </c>
+      <c r="E5" s="43" t="str">
+        <f>Jurnale_TAXARE_INVERSA!E7</f>
+        <v>401.UE</v>
+      </c>
+      <c r="F5" s="43">
+        <f>Jurnale_TAXARE_INVERSA!C7</f>
+        <v>74550</v>
+      </c>
+      <c r="G5" s="43" t="str">
+        <f>Jurnale_TAXARE_INVERSA!D7</f>
+        <v>Achiziție intracomunitară Furnizor UE DEMO — taxare inversă 2026-07</v>
+      </c>
+      <c r="H5" s="43" t="inlineStr">
+        <is>
+          <t>Factură furnizor UE</t>
+        </is>
+      </c>
+      <c r="I5" s="43" t="str">
+        <f>IF(AND(ISNUMBER(F5),F5&gt;0),"DA","NU")</f>
+        <v>DA</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="43" t="n">
+        <v>2</v>
+      </c>
+      <c r="B6" s="43" t="inlineStr">
+        <is>
+          <t>A Intracomunitar — autolichidare</t>
+        </is>
+      </c>
+      <c r="C6" s="43" t="str">
+        <f>Declarații_TAXARE_INVERSA!B8</f>
+        <v>2026-07-31</v>
+      </c>
+      <c r="D6" s="43" t="str">
+        <f>Jurnale_TAXARE_INVERSA!B9</f>
+        <v>4426</v>
+      </c>
+      <c r="E6" s="43" t="str">
+        <f>Jurnale_TAXARE_INVERSA!E9</f>
+        <v>4427</v>
+      </c>
+      <c r="F6" s="43">
+        <f>Jurnale_TAXARE_INVERSA!C9</f>
+        <v>15655.5</v>
+      </c>
+      <c r="G6" s="43" t="str">
+        <f>Jurnale_TAXARE_INVERSA!D9</f>
+        <v>TVA deductibilă prin autolichidare — taxare inversă 2026-07</v>
+      </c>
+      <c r="H6" s="43" t="inlineStr">
+        <is>
+          <t>Autofactură</t>
+        </is>
+      </c>
+      <c r="I6" s="43" t="str">
+        <f>IF(AND(ISNUMBER(F6),F6&gt;0),"DA","NU")</f>
+        <v>DA</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="43" t="n">
+        <v>3</v>
+      </c>
+      <c r="B7" s="43" t="inlineStr">
+        <is>
+          <t>B Intern — factura</t>
+        </is>
+      </c>
+      <c r="C7" s="43" t="str">
+        <f>Declarații_TAXARE_INVERSA!B8</f>
+        <v>2026-07-31</v>
+      </c>
+      <c r="D7" s="43" t="str">
+        <f>Jurnale_TAXARE_INVERSA!B14</f>
+        <v>371</v>
+      </c>
+      <c r="E7" s="43" t="str">
+        <f>Jurnale_TAXARE_INVERSA!E14</f>
+        <v>401.RO</v>
+      </c>
+      <c r="F7" s="43">
+        <f>Jurnale_TAXARE_INVERSA!C14</f>
+        <v>10000</v>
+      </c>
+      <c r="G7" s="43" t="str">
+        <f>Jurnale_TAXARE_INVERSA!D14</f>
+        <v>Achiziție cu taxare inversă (Cereale) — taxare inversă 2026-07</v>
+      </c>
+      <c r="H7" s="43" t="inlineStr">
+        <is>
+          <t>Factură (mențiune taxare inversă)</t>
+        </is>
+      </c>
+      <c r="I7" s="43" t="str">
+        <f>IF(AND(ISNUMBER(F7),F7&gt;0),"DA","NU")</f>
+        <v>DA</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="43" t="n">
+        <v>4</v>
+      </c>
+      <c r="B8" s="43" t="inlineStr">
+        <is>
+          <t>B Intern — autolichidare</t>
+        </is>
+      </c>
+      <c r="C8" s="43" t="str">
+        <f>Declarații_TAXARE_INVERSA!B8</f>
+        <v>2026-07-31</v>
+      </c>
+      <c r="D8" s="43" t="str">
+        <f>Jurnale_TAXARE_INVERSA!B16</f>
+        <v>4426</v>
+      </c>
+      <c r="E8" s="43" t="str">
+        <f>Jurnale_TAXARE_INVERSA!E16</f>
+        <v>4427</v>
+      </c>
+      <c r="F8" s="43">
+        <f>Jurnale_TAXARE_INVERSA!C16</f>
+        <v>2100</v>
+      </c>
+      <c r="G8" s="43" t="str">
+        <f>Jurnale_TAXARE_INVERSA!D16</f>
+        <v>TVA deductibilă prin autolichidare — taxare inversă 2026-07</v>
+      </c>
+      <c r="H8" s="43" t="inlineStr">
+        <is>
+          <t>Autofactură</t>
+        </is>
+      </c>
+      <c r="I8" s="43" t="str">
+        <f>IF(AND(ISNUMBER(F8),F8&gt;0),"DA","NU")</f>
+        <v>DA</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="43" t="inlineStr">
+        <is>
+          <t>Rânduri de importat</t>
+        </is>
+      </c>
+      <c r="B10" s="43">
+        <f>COUNTIF(I5:I8,"DA")</f>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="43" t="inlineStr">
+        <is>
+          <t>Check global</t>
+        </is>
+      </c>
+      <c r="B11" s="43">
+        <f>Jurnale_TAXARE_INVERSA!B19</f>
+        <v>0</v>
+      </c>
+      <c r="C11" s="43" t="str">
+        <f>IF(ABS(B11)&lt;0.01,"OK","EROARE")</f>
+        <v>OK</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet73.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C42"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="50" customWidth="1" style="40" min="1" max="1"/>
+    <col width="22" customWidth="1" style="40" min="2" max="2"/>
+    <col width="58" customWidth="1" style="40" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="41" t="inlineStr">
+        <is>
+          <t>MOD_FARA_DOCUMENT — Declarații (input)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="44" t="inlineStr">
+        <is>
+          <t>Două cazuri independente. Pune DA pe cel care s-a întâmplat — de obicei primul se aplică lunar, al doilea doar după inventar.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="42" t="inlineStr">
+        <is>
+          <t>1. Antet</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="43" t="inlineStr">
+        <is>
+          <t>Societate</t>
+        </is>
+      </c>
+      <c r="B5" s="43" t="str">
+        <f>Parametri!B5</f>
+        <v>SC EXEMPLU SRL</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="43" t="inlineStr">
+        <is>
+          <t>CUI</t>
+        </is>
+      </c>
+      <c r="B6" s="43" t="str">
+        <f>Parametri!B6</f>
+        <v>RO00000000</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="43" t="inlineStr">
+        <is>
+          <t>Luna (AAAA-LL)</t>
+        </is>
+      </c>
+      <c r="B7" s="64" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="43" t="inlineStr">
+        <is>
+          <t>Data jurnal</t>
+        </is>
+      </c>
+      <c r="B8" s="64" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="43" t="inlineStr">
+        <is>
+          <t>Cota TVA</t>
+        </is>
+      </c>
+      <c r="B9" s="64" t="n">
+        <v>0.21</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="42" t="inlineStr">
+        <is>
+          <t>2. Cazul A — Vehicul cu regim mixt (deducere 50%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="43" t="inlineStr">
+        <is>
+          <t>Se aplică? (DA/NU)</t>
+        </is>
+      </c>
+      <c r="B12" s="64" t="inlineStr">
+        <is>
+          <t>DA</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="43" t="inlineStr">
+        <is>
+          <t>Regim (MIXT / EXCLUSIV / EXCEPTAT)</t>
+        </is>
+      </c>
+      <c r="B13" s="64" t="inlineStr">
+        <is>
+          <t>MIXT</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="43" t="inlineStr">
+        <is>
+          <t>Valoare factură fără TVA</t>
+        </is>
+      </c>
+      <c r="B14" s="64" t="n">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="43" t="inlineStr">
+        <is>
+          <t>TVA de pe factură (auto)</t>
+        </is>
+      </c>
+      <c r="B15" s="43">
+        <f>ROUND(B14*B9,2)</f>
+        <v>210</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="43" t="inlineStr">
+        <is>
+          <t>Procent de deducere (auto)</t>
+        </is>
+      </c>
+      <c r="B16" s="43">
+        <f>IF(B13="MIXT",param_proc_vehicul,1)</f>
+        <v>0.5</v>
+      </c>
+      <c r="C16" s="44" t="inlineStr">
+        <is>
+          <t>La MIXT vine din param_proc_vehicul; la EXCLUSIV și EXCEPTAT se deduce integral</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="43" t="inlineStr">
+        <is>
+          <t>TVA deductibilă (auto)</t>
+        </is>
+      </c>
+      <c r="B17" s="43">
+        <f>ROUND(B15*B16,2)</f>
+        <v>105</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="43" t="inlineStr">
+        <is>
+          <t>TVA nedeductibilă (auto)</t>
+        </is>
+      </c>
+      <c r="B18" s="43">
+        <f>B15-B17</f>
+        <v>105</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="43" t="inlineStr">
+        <is>
+          <t>Cheltuială = net + TVA nedeductibilă (auto)</t>
+        </is>
+      </c>
+      <c r="B19" s="43">
+        <f>B14+B18</f>
+        <v>1105</v>
+      </c>
+      <c r="C19" s="44" t="inlineStr">
+        <is>
+          <t>TVA nedeductibilă NU se pierde: se incorporează în cheltuială</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="43" t="inlineStr">
+        <is>
+          <t>Total factură (auto)</t>
+        </is>
+      </c>
+      <c r="B20" s="43">
+        <f>B14+B15</f>
+        <v>1210</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="42" t="inlineStr">
+        <is>
+          <t>3. Cazul B — Lipsă la inventar</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="43" t="inlineStr">
+        <is>
+          <t>Se aplică? (DA/NU)</t>
+        </is>
+      </c>
+      <c r="B23" s="64" t="inlineStr">
+        <is>
+          <t>DA</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="43" t="inlineStr">
+        <is>
+          <t>Lipsa e JUSTIFICATĂ? (DA/NU)</t>
+        </is>
+      </c>
+      <c r="B24" s="64" t="inlineStr">
+        <is>
+          <t>NU</t>
+        </is>
+      </c>
+      <c r="C24" s="44" t="inlineStr">
+        <is>
+          <t>Calamitate, perisabilități în limita legală, casare documentată. Nejustificată = se colectează TVA</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="43" t="inlineStr">
+        <is>
+          <t>Costul bunului lipsă</t>
+        </is>
+      </c>
+      <c r="B25" s="64" t="n">
+        <v>1200</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="43" t="inlineStr">
+        <is>
+          <t>TVA de colectat (auto)</t>
+        </is>
+      </c>
+      <c r="B26" s="43">
+        <f>IF(B24="DA",0,ROUND(B25*B9,2))</f>
+        <v>252</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="42" t="inlineStr">
+        <is>
+          <t>4. Conturi</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="43" t="inlineStr">
+        <is>
+          <t>Cheltuială cu serviciile (628)</t>
+        </is>
+      </c>
+      <c r="B29" s="64" t="inlineStr">
+        <is>
+          <t>628</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="43" t="inlineStr">
+        <is>
+          <t>Alte cheltuieli de exploatare (658)</t>
+        </is>
+      </c>
+      <c r="B30" s="64" t="inlineStr">
+        <is>
+          <t>658</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="43" t="inlineStr">
+        <is>
+          <t>Furnizor</t>
+        </is>
+      </c>
+      <c r="B31" s="64" t="inlineStr">
+        <is>
+          <t>401</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="43" t="inlineStr">
+        <is>
+          <t>Cont stoc</t>
+        </is>
+      </c>
+      <c r="B32" s="64" t="inlineStr">
+        <is>
+          <t>371</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="43" t="inlineStr">
+        <is>
+          <t>TVA deductibilă</t>
+        </is>
+      </c>
+      <c r="B33" s="64" t="inlineStr">
+        <is>
+          <t>4426</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="43" t="inlineStr">
+        <is>
+          <t>TVA colectată</t>
+        </is>
+      </c>
+      <c r="B34" s="64" t="inlineStr">
+        <is>
+          <t>4427</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="42" t="inlineStr">
+        <is>
+          <t>5. Sufix</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="43" t="inlineStr">
+        <is>
+          <t>Sufix</t>
+        </is>
+      </c>
+      <c r="B37" s="43" t="str">
+        <f>"— fără document " &amp; B7</f>
+        <v>— fără document 2026-07</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="42" t="inlineStr">
+        <is>
+          <t>6. Control</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="43" t="inlineStr">
+        <is>
+          <t>Modul activ?</t>
+        </is>
+      </c>
+      <c r="B40" s="43" t="str">
+        <f>IF(INDEX(CatalogModule!$A$1:$A$200,MATCH("MOD_FARA_DOCUMENT",CatalogModule!$B$1:$B$200,0))="DA","ACTIV","INACTIV")</f>
+        <v>INACTIV</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="43" t="inlineStr">
+        <is>
+          <t>Verificare: cheltuială + TVA dedusă = total factură</t>
+        </is>
+      </c>
+      <c r="B41" s="43" t="str">
+        <f>IF(OR(B12&lt;&gt;"DA",ABS((B19+B17)-B20)&lt;0.01),"OK — TVA nedeductibilă e în cheltuială, nimic nu se pierde","EROARE — nota nu acoperă totalul facturii")</f>
+        <v>OK — TVA nedeductibilă e în cheltuială, nimic nu se pierde</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="43" t="inlineStr">
+        <is>
+          <t>Regula de sens la lipsă</t>
+        </is>
+      </c>
+      <c r="B42" s="43" t="str">
+        <f>IF(AND(B23="DA",B24&lt;&gt;"DA"),"4427 se CREDITEAZĂ — colectezi, nu storna deducerea","—")</f>
+        <v>4427 se CREDITEAZĂ — colectezi, nu storna deducerea</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet74.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:D21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -30928,7 +32698,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet71.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet75.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -31248,7 +33018,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet72.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet76.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -31516,7 +33286,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet73.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet77.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -31877,7 +33647,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet74.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet78.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -32125,7 +33895,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet75.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet79.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -32700,7 +34470,528 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet76.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C54"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="46" customWidth="1" style="40" min="1" max="1"/>
+    <col width="20" customWidth="1" style="40" min="2" max="2"/>
+    <col width="62" customWidth="1" style="40" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="41" t="inlineStr">
+        <is>
+          <t>MOD_CREDIT_VALUTA — Declarații (input)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="44" t="inlineStr">
+        <is>
+          <t>Valorile implicite reproduc monografia din F-107. Rata și dobânda se iau din SCADENȚAR, nu din extras — extrasul le arată deseori cumulat.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="42" t="inlineStr">
+        <is>
+          <t>1. Antet</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="43" t="inlineStr">
+        <is>
+          <t>Societate</t>
+        </is>
+      </c>
+      <c r="B5" s="43" t="str">
+        <f>Parametri!B5</f>
+        <v>SC EXEMPLU SRL</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="43" t="inlineStr">
+        <is>
+          <t>Număr contract de credit</t>
+        </is>
+      </c>
+      <c r="B6" s="64" t="inlineStr">
+        <is>
+          <t>CR-2026-001</t>
+        </is>
+      </c>
+      <c r="C6" s="44" t="inlineStr">
+        <is>
+          <t>1621 se ține analitic pe contract și pe valută</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="43" t="inlineStr">
+        <is>
+          <t>Luna (AAAA-LL)</t>
+        </is>
+      </c>
+      <c r="B7" s="64" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="43" t="inlineStr">
+        <is>
+          <t>Data plății ratei</t>
+        </is>
+      </c>
+      <c r="B8" s="64" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="43" t="inlineStr">
+        <is>
+          <t>Data reevaluării (ultima zi bancară a lunii)</t>
+        </is>
+      </c>
+      <c r="B9" s="64" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="43" t="inlineStr">
+        <is>
+          <t>Valuta</t>
+        </is>
+      </c>
+      <c r="B10" s="64" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="42" t="inlineStr">
+        <is>
+          <t>2. Soldul de la care pornim</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="43" t="inlineStr">
+        <is>
+          <t>Sold inițial, în valută</t>
+        </is>
+      </c>
+      <c r="B13" s="64" t="n">
+        <v>20000</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="43" t="inlineStr">
+        <is>
+          <t>Cursul la care e înregistrat soldul</t>
+        </is>
+      </c>
+      <c r="B14" s="64" t="n">
+        <v>4.97</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="43" t="inlineStr">
+        <is>
+          <t>Sold inițial, în lei</t>
+        </is>
+      </c>
+      <c r="B15" s="43">
+        <f>ROUND(B13*B14,2)</f>
+        <v>99400</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="42" t="inlineStr">
+        <is>
+          <t>3. Mișcările lunii (din SCADENȚAR)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="43" t="inlineStr">
+        <is>
+          <t>Rata de capital, în valută</t>
+        </is>
+      </c>
+      <c r="B18" s="64" t="n">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="43" t="inlineStr">
+        <is>
+          <t>Dobânda, în valută</t>
+        </is>
+      </c>
+      <c r="B19" s="64" t="n">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="43" t="inlineStr">
+        <is>
+          <t>Cursul de la data plății</t>
+        </is>
+      </c>
+      <c r="B20" s="64" t="n">
+        <v>4.99</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="43" t="inlineStr">
+        <is>
+          <t>Comisioane bancare, în lei</t>
+        </is>
+      </c>
+      <c r="B21" s="64" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="42" t="inlineStr">
+        <is>
+          <t>4. Reevaluarea de la finalul lunii</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="43" t="inlineStr">
+        <is>
+          <t>Curs BNR la data reevaluării</t>
+        </is>
+      </c>
+      <c r="B24" s="64" t="n">
+        <v>5.01</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="42" t="inlineStr">
+        <is>
+          <t>5. Calcul automat (nu edita)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="43" t="inlineStr">
+        <is>
+          <t>Rata, la cursul de înregistrare</t>
+        </is>
+      </c>
+      <c r="B27" s="43">
+        <f>ROUND(B18*B14,2)</f>
+        <v>24850</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="43" t="inlineStr">
+        <is>
+          <t>Rata, la cursul de plată</t>
+        </is>
+      </c>
+      <c r="B28" s="43">
+        <f>ROUND(B18*B20,2)</f>
+        <v>24950</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="43" t="inlineStr">
+        <is>
+          <t>MOMENTUL 1 — diferența la plată</t>
+        </is>
+      </c>
+      <c r="B29" s="43">
+        <f>B28-B27</f>
+        <v>100</v>
+      </c>
+      <c r="C29" s="44" t="inlineStr">
+        <is>
+          <t>Pozitiv = nefavorabil (665); negativ = favorabil (765)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="43" t="inlineStr">
+        <is>
+          <t>Dobânda, în lei</t>
+        </is>
+      </c>
+      <c r="B30" s="43">
+        <f>ROUND(B19*B20,2)</f>
+        <v>998</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="43" t="inlineStr">
+        <is>
+          <t>Sold rămas, în valută</t>
+        </is>
+      </c>
+      <c r="B31" s="43">
+        <f>B13-B18</f>
+        <v>15000</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="43" t="inlineStr">
+        <is>
+          <t>Sold rămas, la cursul de înregistrare</t>
+        </is>
+      </c>
+      <c r="B32" s="43">
+        <f>ROUND(B31*B14,2)</f>
+        <v>74550</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="43" t="inlineStr">
+        <is>
+          <t>Sold rămas, la cursul BNR</t>
+        </is>
+      </c>
+      <c r="B33" s="43">
+        <f>ROUND(B31*B24,2)</f>
+        <v>75150</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="43" t="inlineStr">
+        <is>
+          <t>MOMENTUL 2 — diferența din reevaluare</t>
+        </is>
+      </c>
+      <c r="B34" s="43">
+        <f>B33-B32</f>
+        <v>600</v>
+      </c>
+      <c r="C34" s="44" t="inlineStr">
+        <is>
+          <t>Pozitiv = datoria crește = nefavorabil (665)</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="42" t="inlineStr">
+        <is>
+          <t>6. Conturi</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="43" t="inlineStr">
+        <is>
+          <t>Cont credit (162x)</t>
+        </is>
+      </c>
+      <c r="B37" s="64" t="inlineStr">
+        <is>
+          <t>1621</t>
+        </is>
+      </c>
+      <c r="C37" s="44" t="inlineStr">
+        <is>
+          <t>1621…1627 sunt sintetice DISTINCTE, nu analitice ale aceluiași cont</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="43" t="inlineStr">
+        <is>
+          <t>Cont dobândă neajunsă la scadență</t>
+        </is>
+      </c>
+      <c r="B38" s="64" t="n">
+        <v>1682</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="43" t="inlineStr">
+        <is>
+          <t>Cont trezorerie în valută</t>
+        </is>
+      </c>
+      <c r="B39" s="64" t="inlineStr">
+        <is>
+          <t>5124</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="43" t="inlineStr">
+        <is>
+          <t>Cont trezorerie în lei</t>
+        </is>
+      </c>
+      <c r="B40" s="64" t="inlineStr">
+        <is>
+          <t>5121</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="43" t="inlineStr">
+        <is>
+          <t>Cont cheltuială cu dobânda</t>
+        </is>
+      </c>
+      <c r="B41" s="64" t="n">
+        <v>666</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="43" t="inlineStr">
+        <is>
+          <t>Cont cheltuială cu serviciile bancare</t>
+        </is>
+      </c>
+      <c r="B42" s="64" t="n">
+        <v>627</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="43" t="inlineStr">
+        <is>
+          <t>Cont diferențe nefavorabile</t>
+        </is>
+      </c>
+      <c r="B43" s="64" t="n">
+        <v>665</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="43" t="inlineStr">
+        <is>
+          <t>Cont diferențe favorabile</t>
+        </is>
+      </c>
+      <c r="B44" s="64" t="n">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="42" t="inlineStr">
+        <is>
+          <t>7. Controale</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="43" t="inlineStr">
+        <is>
+          <t>Check FINAL: sold lei = sold valută × curs BNR</t>
+        </is>
+      </c>
+      <c r="B47" s="43">
+        <f>B32+B34-B33</f>
+        <v>0</v>
+      </c>
+      <c r="C47" s="43" t="str">
+        <f>IF(ABS(B47)&lt;0.01,"OK — soldul în lei corespunde soldului în valută","EROARE — una dintre cele două diferențe de curs lipsește")</f>
+        <v>OK — soldul în lei corespunde soldului în valută</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="43" t="inlineStr">
+        <is>
+          <t>Check cele două momente sunt distincte</t>
+        </is>
+      </c>
+      <c r="B48" s="43">
+        <f>B29+B34</f>
+        <v>700</v>
+      </c>
+      <c r="C48" s="43" t="str">
+        <f>"Momentul 1 (la plată): " &amp; TEXT(B29,"0.00") &amp; " lei · Momentul 2 (reevaluare): " &amp; TEXT(B34,"0.00") &amp; " lei"</f>
+        <v>Momentul 1 (la plată): 100.00 lei · Momentul 2 (reevaluare): 600.00 lei</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="43" t="inlineStr">
+        <is>
+          <t>Reminder: rata și dobânda vin din scadențar</t>
+        </is>
+      </c>
+      <c r="B49" s="43">
+        <f>B18+B19</f>
+        <v>5200</v>
+      </c>
+      <c r="C49" s="43" t="str">
+        <f>"Extrasul arată deseori B18+B19 cumulat. Dacă le înregistrezi așa, ajungi cu 1621 pe debit sau cu sold rămas la finalul creditului."</f>
+        <v>Extrasul arată deseori B18+B19 cumulat. Dacă le înregistrezi așa, ajungi cu 1621 pe debit sau cu sold rămas la finalul creditului.</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="43" t="inlineStr">
+        <is>
+          <t>Reminder: reevaluarea e LUNARĂ</t>
+        </is>
+      </c>
+      <c r="B50" s="43" t="str">
+        <f>B9</f>
+        <v>2026-07-31</v>
+      </c>
+      <c r="C50" s="43" t="str">
+        <f>"Obligatorie lunar (OMFP 1802/2014), nu trimestrial. Verifică și soldul ÎN VALUTĂ, nu doar în lei."</f>
+        <v>Obligatorie lunar (OMFP 1802/2014), nu trimestrial. Verifică și soldul ÎN VALUTĂ, nu doar în lei.</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="43" t="inlineStr">
+        <is>
+          <t>Reminder bilanț</t>
+        </is>
+      </c>
+      <c r="B51" s="43">
+        <f>B31</f>
+        <v>15000</v>
+      </c>
+      <c r="C51" s="43" t="str">
+        <f>"Reclasifică porțiunea scadentă în ≤ 12 luni pentru bilanț, prin analitic sau cont dedicat. Dobânda calculată și neajunsă la scadență stă pe 1682."</f>
+        <v>Reclasifică porțiunea scadentă în ≤ 12 luni pentru bilanț, prin analitic sau cont dedicat. Dobânda calculată și neajunsă la scadență stă pe 1682.</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="42" t="inlineStr">
+        <is>
+          <t>8. Sufix generat</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="43" t="inlineStr">
+        <is>
+          <t>Sufix</t>
+        </is>
+      </c>
+      <c r="B54" s="43" t="str">
+        <f>" - " &amp; B6 &amp; " - " &amp; B7</f>
+        <v> - CR-2026-001 - 2026-07</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet80.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -33124,7 +35415,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet77.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet81.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -33511,7 +35802,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet78.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet82.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -33904,7 +36195,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet79.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet83.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -34568,528 +36859,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:C54"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="46" customWidth="1" style="40" min="1" max="1"/>
-    <col width="20" customWidth="1" style="40" min="2" max="2"/>
-    <col width="62" customWidth="1" style="40" min="3" max="3"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="41" t="inlineStr">
-        <is>
-          <t>MOD_CREDIT_VALUTA — Declarații (input)</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="44" t="inlineStr">
-        <is>
-          <t>Valorile implicite reproduc monografia din F-107. Rata și dobânda se iau din SCADENȚAR, nu din extras — extrasul le arată deseori cumulat.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="42" t="inlineStr">
-        <is>
-          <t>1. Antet</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="43" t="inlineStr">
-        <is>
-          <t>Societate</t>
-        </is>
-      </c>
-      <c r="B5" s="43" t="str">
-        <f>Parametri!B5</f>
-        <v>SC EXEMPLU SRL</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="43" t="inlineStr">
-        <is>
-          <t>Număr contract de credit</t>
-        </is>
-      </c>
-      <c r="B6" s="64" t="inlineStr">
-        <is>
-          <t>CR-2026-001</t>
-        </is>
-      </c>
-      <c r="C6" s="44" t="inlineStr">
-        <is>
-          <t>1621 se ține analitic pe contract și pe valută</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="43" t="inlineStr">
-        <is>
-          <t>Luna (AAAA-LL)</t>
-        </is>
-      </c>
-      <c r="B7" s="64" t="inlineStr">
-        <is>
-          <t>2026-07</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="43" t="inlineStr">
-        <is>
-          <t>Data plății ratei</t>
-        </is>
-      </c>
-      <c r="B8" s="64" t="inlineStr">
-        <is>
-          <t>2026-07-15</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="43" t="inlineStr">
-        <is>
-          <t>Data reevaluării (ultima zi bancară a lunii)</t>
-        </is>
-      </c>
-      <c r="B9" s="64" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="43" t="inlineStr">
-        <is>
-          <t>Valuta</t>
-        </is>
-      </c>
-      <c r="B10" s="64" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="42" t="inlineStr">
-        <is>
-          <t>2. Soldul de la care pornim</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="43" t="inlineStr">
-        <is>
-          <t>Sold inițial, în valută</t>
-        </is>
-      </c>
-      <c r="B13" s="64" t="n">
-        <v>20000</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="43" t="inlineStr">
-        <is>
-          <t>Cursul la care e înregistrat soldul</t>
-        </is>
-      </c>
-      <c r="B14" s="64" t="n">
-        <v>4.97</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="43" t="inlineStr">
-        <is>
-          <t>Sold inițial, în lei</t>
-        </is>
-      </c>
-      <c r="B15" s="43">
-        <f>ROUND(B13*B14,2)</f>
-        <v>99400</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="42" t="inlineStr">
-        <is>
-          <t>3. Mișcările lunii (din SCADENȚAR)</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="43" t="inlineStr">
-        <is>
-          <t>Rata de capital, în valută</t>
-        </is>
-      </c>
-      <c r="B18" s="64" t="n">
-        <v>5000</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="43" t="inlineStr">
-        <is>
-          <t>Dobânda, în valută</t>
-        </is>
-      </c>
-      <c r="B19" s="64" t="n">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="43" t="inlineStr">
-        <is>
-          <t>Cursul de la data plății</t>
-        </is>
-      </c>
-      <c r="B20" s="64" t="n">
-        <v>4.99</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="43" t="inlineStr">
-        <is>
-          <t>Comisioane bancare, în lei</t>
-        </is>
-      </c>
-      <c r="B21" s="64" t="n">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="42" t="inlineStr">
-        <is>
-          <t>4. Reevaluarea de la finalul lunii</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="43" t="inlineStr">
-        <is>
-          <t>Curs BNR la data reevaluării</t>
-        </is>
-      </c>
-      <c r="B24" s="64" t="n">
-        <v>5.01</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="42" t="inlineStr">
-        <is>
-          <t>5. Calcul automat (nu edita)</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="43" t="inlineStr">
-        <is>
-          <t>Rata, la cursul de înregistrare</t>
-        </is>
-      </c>
-      <c r="B27" s="43">
-        <f>ROUND(B18*B14,2)</f>
-        <v>24850</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="43" t="inlineStr">
-        <is>
-          <t>Rata, la cursul de plată</t>
-        </is>
-      </c>
-      <c r="B28" s="43">
-        <f>ROUND(B18*B20,2)</f>
-        <v>24950</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="43" t="inlineStr">
-        <is>
-          <t>MOMENTUL 1 — diferența la plată</t>
-        </is>
-      </c>
-      <c r="B29" s="43">
-        <f>B28-B27</f>
-        <v>100</v>
-      </c>
-      <c r="C29" s="44" t="inlineStr">
-        <is>
-          <t>Pozitiv = nefavorabil (665); negativ = favorabil (765)</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="43" t="inlineStr">
-        <is>
-          <t>Dobânda, în lei</t>
-        </is>
-      </c>
-      <c r="B30" s="43">
-        <f>ROUND(B19*B20,2)</f>
-        <v>998</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="43" t="inlineStr">
-        <is>
-          <t>Sold rămas, în valută</t>
-        </is>
-      </c>
-      <c r="B31" s="43">
-        <f>B13-B18</f>
-        <v>15000</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="43" t="inlineStr">
-        <is>
-          <t>Sold rămas, la cursul de înregistrare</t>
-        </is>
-      </c>
-      <c r="B32" s="43">
-        <f>ROUND(B31*B14,2)</f>
-        <v>74550</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="43" t="inlineStr">
-        <is>
-          <t>Sold rămas, la cursul BNR</t>
-        </is>
-      </c>
-      <c r="B33" s="43">
-        <f>ROUND(B31*B24,2)</f>
-        <v>75150</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="43" t="inlineStr">
-        <is>
-          <t>MOMENTUL 2 — diferența din reevaluare</t>
-        </is>
-      </c>
-      <c r="B34" s="43">
-        <f>B33-B32</f>
-        <v>600</v>
-      </c>
-      <c r="C34" s="44" t="inlineStr">
-        <is>
-          <t>Pozitiv = datoria crește = nefavorabil (665)</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="42" t="inlineStr">
-        <is>
-          <t>6. Conturi</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="43" t="inlineStr">
-        <is>
-          <t>Cont credit (162x)</t>
-        </is>
-      </c>
-      <c r="B37" s="64" t="inlineStr">
-        <is>
-          <t>1621</t>
-        </is>
-      </c>
-      <c r="C37" s="44" t="inlineStr">
-        <is>
-          <t>1621…1627 sunt sintetice DISTINCTE, nu analitice ale aceluiași cont</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="43" t="inlineStr">
-        <is>
-          <t>Cont dobândă neajunsă la scadență</t>
-        </is>
-      </c>
-      <c r="B38" s="64" t="n">
-        <v>1682</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="43" t="inlineStr">
-        <is>
-          <t>Cont trezorerie în valută</t>
-        </is>
-      </c>
-      <c r="B39" s="64" t="inlineStr">
-        <is>
-          <t>5124</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="43" t="inlineStr">
-        <is>
-          <t>Cont trezorerie în lei</t>
-        </is>
-      </c>
-      <c r="B40" s="64" t="inlineStr">
-        <is>
-          <t>5121</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="43" t="inlineStr">
-        <is>
-          <t>Cont cheltuială cu dobânda</t>
-        </is>
-      </c>
-      <c r="B41" s="64" t="n">
-        <v>666</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="43" t="inlineStr">
-        <is>
-          <t>Cont cheltuială cu serviciile bancare</t>
-        </is>
-      </c>
-      <c r="B42" s="64" t="n">
-        <v>627</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="43" t="inlineStr">
-        <is>
-          <t>Cont diferențe nefavorabile</t>
-        </is>
-      </c>
-      <c r="B43" s="64" t="n">
-        <v>665</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="43" t="inlineStr">
-        <is>
-          <t>Cont diferențe favorabile</t>
-        </is>
-      </c>
-      <c r="B44" s="64" t="n">
-        <v>765</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="42" t="inlineStr">
-        <is>
-          <t>7. Controale</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="43" t="inlineStr">
-        <is>
-          <t>Check FINAL: sold lei = sold valută × curs BNR</t>
-        </is>
-      </c>
-      <c r="B47" s="43">
-        <f>B32+B34-B33</f>
-        <v>0</v>
-      </c>
-      <c r="C47" s="43" t="str">
-        <f>IF(ABS(B47)&lt;0.01,"OK — soldul în lei corespunde soldului în valută","EROARE — una dintre cele două diferențe de curs lipsește")</f>
-        <v>OK — soldul în lei corespunde soldului în valută</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="43" t="inlineStr">
-        <is>
-          <t>Check cele două momente sunt distincte</t>
-        </is>
-      </c>
-      <c r="B48" s="43">
-        <f>B29+B34</f>
-        <v>700</v>
-      </c>
-      <c r="C48" s="43" t="str">
-        <f>"Momentul 1 (la plată): " &amp; TEXT(B29,"0.00") &amp; " lei · Momentul 2 (reevaluare): " &amp; TEXT(B34,"0.00") &amp; " lei"</f>
-        <v>Momentul 1 (la plată): 100.00 lei · Momentul 2 (reevaluare): 600.00 lei</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="43" t="inlineStr">
-        <is>
-          <t>Reminder: rata și dobânda vin din scadențar</t>
-        </is>
-      </c>
-      <c r="B49" s="43">
-        <f>B18+B19</f>
-        <v>5200</v>
-      </c>
-      <c r="C49" s="43" t="str">
-        <f>"Extrasul arată deseori B18+B19 cumulat. Dacă le înregistrezi așa, ajungi cu 1621 pe debit sau cu sold rămas la finalul creditului."</f>
-        <v>Extrasul arată deseori B18+B19 cumulat. Dacă le înregistrezi așa, ajungi cu 1621 pe debit sau cu sold rămas la finalul creditului.</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="43" t="inlineStr">
-        <is>
-          <t>Reminder: reevaluarea e LUNARĂ</t>
-        </is>
-      </c>
-      <c r="B50" s="43" t="str">
-        <f>B9</f>
-        <v>2026-07-31</v>
-      </c>
-      <c r="C50" s="43" t="str">
-        <f>"Obligatorie lunar (OMFP 1802/2014), nu trimestrial. Verifică și soldul ÎN VALUTĂ, nu doar în lei."</f>
-        <v>Obligatorie lunar (OMFP 1802/2014), nu trimestrial. Verifică și soldul ÎN VALUTĂ, nu doar în lei.</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="43" t="inlineStr">
-        <is>
-          <t>Reminder bilanț</t>
-        </is>
-      </c>
-      <c r="B51" s="43">
-        <f>B31</f>
-        <v>15000</v>
-      </c>
-      <c r="C51" s="43" t="str">
-        <f>"Reclasifică porțiunea scadentă în ≤ 12 luni pentru bilanț, prin analitic sau cont dedicat. Dobânda calculată și neajunsă la scadență stă pe 1682."</f>
-        <v>Reclasifică porțiunea scadentă în ≤ 12 luni pentru bilanț, prin analitic sau cont dedicat. Dobânda calculată și neajunsă la scadență stă pe 1682.</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="42" t="inlineStr">
-        <is>
-          <t>8. Sufix generat</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="43" t="inlineStr">
-        <is>
-          <t>Sufix</t>
-        </is>
-      </c>
-      <c r="B54" s="43" t="str">
-        <f>" - " &amp; B6 &amp; " - " &amp; B7</f>
-        <v> - CR-2026-001 - 2026-07</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet80.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet84.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -35623,7 +37393,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet81.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet85.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -36026,7 +37796,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet82.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet86.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -36324,7 +38094,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet83.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet87.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -36870,7 +38640,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet84.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet88.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>

--- a/dist/Module_Declarative_Fluxuri.xlsx
+++ b/dist/Module_Declarative_Fluxuri.xlsx
@@ -83,18 +83,22 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reguli_FARA_DOCUMENT" sheetId="74" state="visible" r:id="rId74"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Jurnale_FARA_DOCUMENT" sheetId="75" state="visible" r:id="rId75"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NotaExport_FARA_DOCUMENT" sheetId="76" state="visible" r:id="rId76"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Declarații_NEUTRALIZARE" sheetId="77" state="visible" r:id="rId77"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reguli_NEUTRALIZARE" sheetId="78" state="visible" r:id="rId78"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Jurnale_NEUTRALIZARE" sheetId="79" state="visible" r:id="rId79"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NotaExport_NEUTRALIZARE" sheetId="80" state="visible" r:id="rId80"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Declarații_AMANUNT" sheetId="81" state="visible" r:id="rId81"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reguli_AMANUNT" sheetId="82" state="visible" r:id="rId82"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Jurnale_AMANUNT" sheetId="83" state="visible" r:id="rId83"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NotaExport_AMANUNT" sheetId="84" state="visible" r:id="rId84"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Declarații_INCHIDERE_LUNARA" sheetId="85" state="visible" r:id="rId85"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reguli_INCHIDERE_LUNARA" sheetId="86" state="visible" r:id="rId86"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Verificări_INCHIDERE_LUNARA" sheetId="87" state="visible" r:id="rId87"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Abateri_INCHIDERE_LUNARA" sheetId="88" state="visible" r:id="rId88"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Declarații_AVANSURI" sheetId="77" state="visible" r:id="rId77"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reguli_AVANSURI" sheetId="78" state="visible" r:id="rId78"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Jurnale_AVANSURI" sheetId="79" state="visible" r:id="rId79"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NotaExport_AVANSURI" sheetId="80" state="visible" r:id="rId80"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Declarații_NEUTRALIZARE" sheetId="81" state="visible" r:id="rId81"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reguli_NEUTRALIZARE" sheetId="82" state="visible" r:id="rId82"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Jurnale_NEUTRALIZARE" sheetId="83" state="visible" r:id="rId83"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NotaExport_NEUTRALIZARE" sheetId="84" state="visible" r:id="rId84"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Declarații_AMANUNT" sheetId="85" state="visible" r:id="rId85"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reguli_AMANUNT" sheetId="86" state="visible" r:id="rId86"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Jurnale_AMANUNT" sheetId="87" state="visible" r:id="rId87"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NotaExport_AMANUNT" sheetId="88" state="visible" r:id="rId88"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Declarații_INCHIDERE_LUNARA" sheetId="89" state="visible" r:id="rId89"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reguli_INCHIDERE_LUNARA" sheetId="90" state="visible" r:id="rId90"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Verificări_INCHIDERE_LUNARA" sheetId="91" state="visible" r:id="rId91"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Abateri_INCHIDERE_LUNARA" sheetId="92" state="visible" r:id="rId92"/>
   </sheets>
   <definedNames>
     <definedName name="param_proc_rezerva">Parametri!$B$18</definedName>
@@ -840,7 +844,7 @@
     <row r="4" ht="15" customHeight="1" s="40">
       <c r="A4" s="43" t="inlineStr">
         <is>
-          <t>Cele 21 module declarative care execută fluxurile din „Plan de conturi”. Fluxul explică de ce; modulul face înregistrarea. Completezi câteva variabile într-o foaie de input și ies jurnalele și nota de export.</t>
+          <t>Cele 22 module declarative care execută fluxurile din „Plan de conturi”. Fluxul explică de ce; modulul face înregistrarea. Completezi câteva variabile într-o foaie de input și ies jurnalele și nota de export.</t>
         </is>
       </c>
     </row>
@@ -10963,7 +10967,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:H34"/>
+  <dimension ref="A1:H35"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="8" customWidth="1" style="39" min="1" max="1"/>
@@ -11880,84 +11884,126 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="62" t="inlineStr">
+      <c r="A27" s="60" t="inlineStr">
+        <is>
+          <t>NU</t>
+        </is>
+      </c>
+      <c r="B27" s="61" t="inlineStr">
+        <is>
+          <t>MOD_AVANSURI</t>
+        </is>
+      </c>
+      <c r="C27" s="61" t="inlineStr">
+        <is>
+          <t>F-410, F-415</t>
+        </is>
+      </c>
+      <c r="D27" s="61" t="inlineStr">
+        <is>
+          <t>Pe avans / pe extras</t>
+        </is>
+      </c>
+      <c r="E27" s="61" t="inlineStr">
+        <is>
+          <t>Avansul și factura finală, la client și la furnizor; suma încasată peste factură</t>
+        </is>
+      </c>
+      <c r="F27" s="61" t="inlineStr">
+        <is>
+          <t>TVA avans + rest = TVA totală; 419 și 409 se închid la zero</t>
+        </is>
+      </c>
+      <c r="G27" s="61" t="inlineStr">
+        <is>
+          <t>A Avans client; B Factură finală client; C Avans furnizor; D Recepție furnizor; E Supraîncasare</t>
+        </is>
+      </c>
+      <c r="H27" s="61" t="inlineStr">
+        <is>
+          <t>IMPLEMENTAT</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="62" t="inlineStr">
         <is>
           <t>DA</t>
         </is>
       </c>
-      <c r="B27" s="61" t="inlineStr">
+      <c r="B28" s="61" t="inlineStr">
         <is>
           <t>MOD_INCHIDERE_LUNARA</t>
         </is>
       </c>
-      <c r="C27" s="61" t="inlineStr">
+      <c r="C28" s="61" t="inlineStr">
         <is>
           <t>F-422, F-413</t>
         </is>
       </c>
-      <c r="D27" s="61" t="inlineStr">
+      <c r="D28" s="61" t="inlineStr">
         <is>
           <t>Lunar, pe balanța de verificare</t>
         </is>
       </c>
-      <c r="E27" s="61" t="inlineStr">
+      <c r="E28" s="61" t="inlineStr">
         <is>
           <t>Rulaj debitor, rulaj creditor și sold pentru conturile cu cadență; restul de plată de pe stat; soldul din decontul de TVA</t>
         </is>
       </c>
-      <c r="F27" s="61" t="inlineStr">
+      <c r="F28" s="61" t="inlineStr">
         <is>
           <t>Verifică solduri, nu documente — vezi Reguli, tabelul C</t>
         </is>
       </c>
-      <c r="G27" s="61" t="inlineStr">
+      <c r="G28" s="61" t="inlineStr">
         <is>
           <t>V1 Obligații lunare (rulaj = sold); V2 Datoria față de salariați; V3 Conturi care trebuie golite; V4 Verificarea CAM pe cifre</t>
         </is>
       </c>
-      <c r="H27" s="61" t="inlineStr">
+      <c r="H28" s="61" t="inlineStr">
         <is>
           <t>IMPLEMENTAT</t>
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="63" t="inlineStr">
+    <row r="30">
+      <c r="A30" s="63" t="inlineStr">
         <is>
           <t>REGULĂ DE SUMONARE</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="46" t="inlineStr">
-        <is>
-          <t>1. În CatalogModule setezi Activ=DA doar pe modulele necesare lunii.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="46" t="inlineStr">
         <is>
-          <t>2. Completezi variabilele din foaia Declarații_Modul (galben).</t>
+          <t>1. În CatalogModule setezi Activ=DA doar pe modulele necesare lunii.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="46" t="inlineStr">
         <is>
-          <t>3. Jurnalele și NotaExport se populează automat doar pentru modulele active.</t>
+          <t>2. Completezi variabilele din foaia Declarații_Modul (galben).</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="46" t="inlineStr">
         <is>
-          <t>4. Verifici Check=0 pe fiecare bloc; filtrezi NotaExport pe Include=DA și imporți.</t>
+          <t>3. Jurnalele și NotaExport se populează automat doar pentru modulele active.</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="46" t="inlineStr">
+        <is>
+          <t>4. Verifici Check=0 pe fiecare bloc; filtrezi NotaExport pe Include=DA și imporți.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="46" t="inlineStr">
         <is>
           <t>Nu se creează conturi noi din modul — se folosesc doar conturile din politica declarată + planul de conturi pe rol.</t>
         </is>
@@ -11967,7 +12013,7 @@
   <mergeCells count="9">
     <mergeCell ref="A3:H3"/>
     <mergeCell ref="A30:H30"/>
-    <mergeCell ref="A29:H29"/>
+    <mergeCell ref="A35:H35"/>
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="A33:H33"/>
     <mergeCell ref="A1:H1"/>
@@ -33292,25 +33338,25 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B41"/>
+  <dimension ref="A1:C67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="40" customWidth="1" style="40" min="1" max="1"/>
-    <col width="42" customWidth="1" style="40" min="2" max="2"/>
-    <col width="52" customWidth="1" style="40" min="3" max="3"/>
+    <col width="52" customWidth="1" style="40" min="1" max="1"/>
+    <col width="22" customWidth="1" style="40" min="2" max="2"/>
+    <col width="58" customWidth="1" style="40" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="41" t="inlineStr">
         <is>
-          <t>MOD_NEUTRALIZARE — Declarații (input)</t>
+          <t>MOD_AVANSURI — Declarații (input)</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="44" t="inlineStr">
         <is>
-          <t>Acoperă F-311 (bunuri/711), F-312 (servicii/712), F-209 (imobilizări/722). Alege tipul — conturile și lanțul se adaptează. Principiu: costurile lovesc cls.6, apoi contul de venit de producție capitalizează și neutralizează.</t>
+          <t>Trei situații independente: avans de la client, avans către furnizor, supraîncasare. Pune DA pe cele care s-au întâmplat.</t>
         </is>
       </c>
     </row>
@@ -33346,7 +33392,7 @@
     <row r="7">
       <c r="A7" s="43" t="inlineStr">
         <is>
-          <t>Luna / proiect</t>
+          <t>Luna (AAAA-LL)</t>
         </is>
       </c>
       <c r="B7" s="64" t="inlineStr">
@@ -33358,288 +33404,595 @@
     <row r="8">
       <c r="A8" s="43" t="inlineStr">
         <is>
-          <t>Data costuri (B1)</t>
+          <t>Data jurnal</t>
         </is>
       </c>
       <c r="B8" s="64" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-31</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="43" t="inlineStr">
         <is>
-          <t>Data finalizare stoc (B2-B3)</t>
-        </is>
-      </c>
-      <c r="B9" s="64" t="inlineStr">
-        <is>
-          <t>2026-07-20</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="43" t="inlineStr">
-        <is>
-          <t>Data vânzare / recepție MF (B4)</t>
-        </is>
-      </c>
-      <c r="B10" s="64" t="inlineStr">
-        <is>
-          <t>2026-07-25</t>
+          <t>Cota TVA</t>
+        </is>
+      </c>
+      <c r="B9" s="64" t="n">
+        <v>0.21</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="42" t="inlineStr">
+        <is>
+          <t>2. Avans de la CLIENT (blocurile A și B)</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="42" t="inlineStr">
-        <is>
-          <t>2. Tip producție (poartă principală)</t>
+      <c r="A12" s="43" t="inlineStr">
+        <is>
+          <t>Se aplică? (DA/NU)</t>
+        </is>
+      </c>
+      <c r="B12" s="64" t="inlineStr">
+        <is>
+          <t>DA</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="43" t="inlineStr">
         <is>
-          <t>Tip (BUNURI / SERVICII / MF)</t>
+          <t>Client</t>
         </is>
       </c>
       <c r="B13" s="64" t="inlineStr">
         <is>
-          <t>BUNURI</t>
+          <t>Client DEMO</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="43" t="inlineStr">
         <is>
-          <t>Cont venit neutralizare (auto)</t>
-        </is>
-      </c>
-      <c r="B14" s="43">
-        <f>IF(B13="BUNURI",711,IF(B13="SERVICII",712,IF(B13="MF",722,"?")))</f>
-        <v>711</v>
+          <t>Avans încasat, fără TVA</t>
+        </is>
+      </c>
+      <c r="B14" s="64" t="n">
+        <v>5000</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="43" t="inlineStr">
         <is>
-          <t>Cont stoc intermediar (auto)</t>
+          <t>TVA pe avans (auto)</t>
         </is>
       </c>
       <c r="B15" s="43">
-        <f>IF(B13="BUNURI",331,IF(B13="SERVICII",332,IF(B13="MF",231,"?")))</f>
-        <v>331</v>
+        <f>ROUND(B14*B9,2)</f>
+        <v>1050</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="43" t="inlineStr">
         <is>
-          <t>Cont stoc final (auto)</t>
+          <t>Total avans încasat (auto)</t>
         </is>
       </c>
       <c r="B16" s="43">
-        <f>IF(B13="BUNURI",345,IF(B13="SERVICII","(nu e cazul — se stinge la livrare)",IF(B13="MF",213,"?")))</f>
-        <v>345</v>
+        <f>B14+B15</f>
+        <v>6050</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="43" t="inlineStr">
         <is>
-          <t>Cont venit vânzare (auto)</t>
-        </is>
-      </c>
-      <c r="B17" s="43">
-        <f>IF(B13="BUNURI",701,IF(B13="SERVICII",704,IF(B13="MF","(nu e vânzare — e activ)","?")))</f>
-        <v>701</v>
+          <t>Factura finală, fără TVA</t>
+        </is>
+      </c>
+      <c r="B17" s="64" t="n">
+        <v>12000</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="43" t="inlineStr">
+        <is>
+          <t>TVA totală pe factură (auto)</t>
+        </is>
+      </c>
+      <c r="B18" s="43">
+        <f>ROUND(B17*B9,2)</f>
+        <v>2520</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="42" t="inlineStr">
-        <is>
-          <t>3. Costuri (cls.6)</t>
-        </is>
+      <c r="A19" s="43" t="inlineStr">
+        <is>
+          <t>Total factură (auto)</t>
+        </is>
+      </c>
+      <c r="B19" s="43">
+        <f>B17+B18</f>
+        <v>14520</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="43" t="inlineStr">
         <is>
-          <t>Cost materiale (→ 601)</t>
-        </is>
-      </c>
-      <c r="B20" s="64" t="n">
-        <v>4500</v>
+          <t>REST de TVA de colectat (auto)</t>
+        </is>
+      </c>
+      <c r="B20" s="43">
+        <f>B18-B15</f>
+        <v>1470</v>
+      </c>
+      <c r="C20" s="44" t="inlineStr">
+        <is>
+          <t>Doar diferența — TVA-ul avansului a fost deja colectat</t>
+        </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="43" t="inlineStr">
         <is>
-          <t>Cost manoperă (→ 641)</t>
-        </is>
-      </c>
-      <c r="B21" s="64" t="n">
-        <v>0</v>
+          <t>Rest de valoare (auto)</t>
+        </is>
+      </c>
+      <c r="B21" s="43">
+        <f>B17-B14</f>
+        <v>7000</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="43" t="inlineStr">
         <is>
-          <t>Alte costuri (→ 6xx)</t>
-        </is>
-      </c>
-      <c r="B22" s="64" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="43" t="inlineStr">
-        <is>
-          <t>Cost total</t>
-        </is>
-      </c>
-      <c r="B23" s="43">
-        <f>B20+B21+B22</f>
-        <v>4500</v>
+          <t>Rămâne de încasat pe 411 (auto)</t>
+        </is>
+      </c>
+      <c r="B22" s="43">
+        <f>B19-B16</f>
+        <v>8470</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="42" t="inlineStr">
+        <is>
+          <t>3. Avans către FURNIZOR (blocurile C și D)</t>
+        </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="42" t="inlineStr">
-        <is>
-          <t>4. Vânzare (doar BUNURI / SERVICII)</t>
+      <c r="A25" s="43" t="inlineStr">
+        <is>
+          <t>Se aplică? (DA/NU)</t>
+        </is>
+      </c>
+      <c r="B25" s="64" t="inlineStr">
+        <is>
+          <t>DA</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="43" t="inlineStr">
         <is>
-          <t>Preț vânzare (fără TVA)</t>
-        </is>
-      </c>
-      <c r="B26" s="64" t="n">
-        <v>7000</v>
+          <t>Furnizor</t>
+        </is>
+      </c>
+      <c r="B26" s="64" t="inlineStr">
+        <is>
+          <t>Furnizor DEMO</t>
+        </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="43" t="inlineStr">
         <is>
-          <t>Cota TVA</t>
+          <t>Avans plătit, fără TVA</t>
         </is>
       </c>
       <c r="B27" s="64" t="n">
-        <v>0.21</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="43" t="inlineStr">
         <is>
-          <t>TVA</t>
+          <t>TVA pe avans (auto)</t>
         </is>
       </c>
       <c r="B28" s="43">
-        <f>IF(OR(B13="BUNURI",B13="SERVICII"),B26*B27,0)</f>
-        <v>1470</v>
+        <f>ROUND(B27*B9,2)</f>
+        <v>630</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="43" t="inlineStr">
         <is>
-          <t>Total factură</t>
+          <t>Total avans plătit (auto)</t>
         </is>
       </c>
       <c r="B29" s="43">
-        <f>B26+B28</f>
-        <v>8470</v>
+        <f>B27+B28</f>
+        <v>3630</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="43" t="inlineStr">
+        <is>
+          <t>Factura de recepție, fără TVA</t>
+        </is>
+      </c>
+      <c r="B30" s="64" t="n">
+        <v>8000</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="42" t="inlineStr">
-        <is>
-          <t>5. Conturi suplimentare</t>
-        </is>
+      <c r="A31" s="43" t="inlineStr">
+        <is>
+          <t>TVA totală pe factură (auto)</t>
+        </is>
+      </c>
+      <c r="B31" s="43">
+        <f>ROUND(B30*B9,2)</f>
+        <v>1680</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="43" t="inlineStr">
         <is>
-          <t>Cont materii prime</t>
-        </is>
-      </c>
-      <c r="B32" s="64" t="inlineStr">
-        <is>
-          <t>301</t>
-        </is>
+          <t>Total factură (auto)</t>
+        </is>
+      </c>
+      <c r="B32" s="43">
+        <f>B30+B31</f>
+        <v>9680</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="43" t="inlineStr">
         <is>
-          <t>Cont client</t>
-        </is>
-      </c>
-      <c r="B33" s="64" t="inlineStr">
-        <is>
-          <t>411.RO</t>
-        </is>
+          <t>REST de TVA de dedus (auto)</t>
+        </is>
+      </c>
+      <c r="B33" s="43">
+        <f>B31-B28</f>
+        <v>1050</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="43" t="inlineStr">
         <is>
-          <t>Cont TVA colectată</t>
-        </is>
-      </c>
-      <c r="B34" s="64" t="inlineStr">
-        <is>
-          <t>4427</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="42" t="inlineStr">
-        <is>
-          <t>6. Sufix</t>
-        </is>
+          <t>Rest de valoare (auto)</t>
+        </is>
+      </c>
+      <c r="B34" s="43">
+        <f>B30-B27</f>
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="43" t="inlineStr">
+        <is>
+          <t>Rămâne de plătit pe 401 (auto)</t>
+        </is>
+      </c>
+      <c r="B35" s="43">
+        <f>B32-B29</f>
+        <v>6050</v>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="43" t="inlineStr">
-        <is>
-          <t>Sufix</t>
-        </is>
-      </c>
-      <c r="B37" s="43" t="str">
-        <f>"— " &amp; B7 &amp; " — " &amp; B13 &amp; " — " &amp; B14</f>
-        <v>— 2026-07 — BUNURI — 711</v>
+      <c r="A37" s="42" t="inlineStr">
+        <is>
+          <t>4. SUPRAÎNCASARE (blocul E)</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="43" t="inlineStr">
+        <is>
+          <t>Se aplică? (DA/NU)</t>
+        </is>
+      </c>
+      <c r="B38" s="64" t="inlineStr">
+        <is>
+          <t>DA</t>
+        </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="42" t="inlineStr">
-        <is>
-          <t>7. Control</t>
+      <c r="A39" s="43" t="inlineStr">
+        <is>
+          <t>Partener</t>
+        </is>
+      </c>
+      <c r="B39" s="64" t="inlineStr">
+        <is>
+          <t>Partener DEMO</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="43" t="inlineStr">
         <is>
-          <t>Marjă (vânzare − cost)</t>
-        </is>
-      </c>
-      <c r="B40" s="43">
-        <f>IF(OR(B13="BUNURI",B13="SERVICII"),B26-B23,"n/a (MF)")</f>
-        <v>2500</v>
+          <t>Factura emisă, TOTAL cu TVA</t>
+        </is>
+      </c>
+      <c r="B40" s="64" t="n">
+        <v>10000</v>
+      </c>
+      <c r="C40" s="44" t="inlineStr">
+        <is>
+          <t>Aici se introduce totalul, nu baza — așa vine de pe factură</t>
+        </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="43" t="inlineStr">
         <is>
-          <t>Notă principiu</t>
-        </is>
-      </c>
-      <c r="B41" s="43" t="inlineStr">
-        <is>
-          <t>Costurile lovesc cls.6; contul de venit de producție (711/712/722) capitalizează și neutralizează. Descărcarea la vânzare (bunuri) e prin 711=345, nu prin 607.</t>
-        </is>
+          <t>Baza facturii (auto)</t>
+        </is>
+      </c>
+      <c r="B41" s="43">
+        <f>ROUND(B40/(1+B9),2)</f>
+        <v>8264.46</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="43" t="inlineStr">
+        <is>
+          <t>TVA pe factură (auto)</t>
+        </is>
+      </c>
+      <c r="B42" s="43">
+        <f>B40-B41</f>
+        <v>1735.5400000000009</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="43" t="inlineStr">
+        <is>
+          <t>Suma încasată efectiv</t>
+        </is>
+      </c>
+      <c r="B43" s="64" t="n">
+        <v>15000</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="43" t="inlineStr">
+        <is>
+          <t>Diferența încasată în plus (auto)</t>
+        </is>
+      </c>
+      <c r="B44" s="43">
+        <f>B43-B40</f>
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="43" t="inlineStr">
+        <is>
+          <t>Din care bază de avans (auto)</t>
+        </is>
+      </c>
+      <c r="B45" s="43">
+        <f>ROUND(B44/(1+B9),2)</f>
+        <v>4132.23</v>
+      </c>
+      <c r="C45" s="44" t="inlineStr">
+        <is>
+          <t>Suma virată e TVA-inclusivă: se împarte la 1 + cotă</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="43" t="inlineStr">
+        <is>
+          <t>Din care TVA de colectat (auto)</t>
+        </is>
+      </c>
+      <c r="B46" s="43">
+        <f>B44-B45</f>
+        <v>867.7700000000004</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="42" t="inlineStr">
+        <is>
+          <t>5. Conturi</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="43" t="inlineStr">
+        <is>
+          <t>Clienți</t>
+        </is>
+      </c>
+      <c r="B49" s="64" t="inlineStr">
+        <is>
+          <t>4111</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="43" t="inlineStr">
+        <is>
+          <t>Clienți-creditori (avansuri încasate)</t>
+        </is>
+      </c>
+      <c r="B50" s="64" t="inlineStr">
+        <is>
+          <t>419</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="43" t="inlineStr">
+        <is>
+          <t>Furnizori-debitori (avansuri plătite)</t>
+        </is>
+      </c>
+      <c r="B51" s="64" t="inlineStr">
+        <is>
+          <t>409</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="43" t="inlineStr">
+        <is>
+          <t>Furnizori</t>
+        </is>
+      </c>
+      <c r="B52" s="64" t="inlineStr">
+        <is>
+          <t>401.RO</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="43" t="inlineStr">
+        <is>
+          <t>Venit</t>
+        </is>
+      </c>
+      <c r="B53" s="64" t="inlineStr">
+        <is>
+          <t>707</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="43" t="inlineStr">
+        <is>
+          <t>Cont stoc / cheltuială</t>
+        </is>
+      </c>
+      <c r="B54" s="64" t="inlineStr">
+        <is>
+          <t>371</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="43" t="inlineStr">
+        <is>
+          <t>TVA deductibilă</t>
+        </is>
+      </c>
+      <c r="B55" s="64" t="inlineStr">
+        <is>
+          <t>4426</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="43" t="inlineStr">
+        <is>
+          <t>TVA colectată</t>
+        </is>
+      </c>
+      <c r="B56" s="64" t="inlineStr">
+        <is>
+          <t>4427</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="43" t="inlineStr">
+        <is>
+          <t>Bancă</t>
+        </is>
+      </c>
+      <c r="B57" s="64" t="inlineStr">
+        <is>
+          <t>5121</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="42" t="inlineStr">
+        <is>
+          <t>6. Sufix</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="43" t="inlineStr">
+        <is>
+          <t>Sufix</t>
+        </is>
+      </c>
+      <c r="B60" s="43" t="str">
+        <f>"— avansuri " &amp; B7</f>
+        <v>— avansuri 2026-07</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="42" t="inlineStr">
+        <is>
+          <t>7. Control</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="43" t="inlineStr">
+        <is>
+          <t>Modul activ?</t>
+        </is>
+      </c>
+      <c r="B63" s="43" t="str">
+        <f>IF(INDEX(CatalogModule!$A$1:$A$200,MATCH("MOD_AVANSURI",CatalogModule!$B$1:$B$200,0))="DA","ACTIV","INACTIV")</f>
+        <v>INACTIV</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="43" t="inlineStr">
+        <is>
+          <t>Verificare: TVA avans + rest = TVA totală (client)</t>
+        </is>
+      </c>
+      <c r="B64" s="43" t="str">
+        <f>IF(OR(B12&lt;&gt;"DA",ABS((B15+B20)-B18)&lt;0.01),"OK — TVA nu se colectează de două ori","EROARE — TVA recolectată pe toată factura")</f>
+        <v>OK — TVA nu se colectează de două ori</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="43" t="inlineStr">
+        <is>
+          <t>Verificare: TVA avans + rest = TVA totală (furnizor)</t>
+        </is>
+      </c>
+      <c r="B65" s="43" t="str">
+        <f>IF(OR(B25&lt;&gt;"DA",ABS((B28+B33)-B31)&lt;0.01),"OK — TVA nu se deduce de două ori","EROARE — TVA redusă pe toată factura")</f>
+        <v>OK — TVA nu se deduce de două ori</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="43" t="inlineStr">
+        <is>
+          <t>Verificare: TVA extrasă corect din suma încasată</t>
+        </is>
+      </c>
+      <c r="B66" s="43" t="str">
+        <f>IF(OR(B38&lt;&gt;"DA",ABS(B46-ROUND(B44*B9/(1+B9),2))&lt;0.01),"OK — TVA extrasă din suma încasată","EROARE — diferența pusă integral pe 419, TVA necolectată")</f>
+        <v>OK — TVA extrasă din suma încasată</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="43" t="inlineStr">
+        <is>
+          <t>Atenție la 472</t>
+        </is>
+      </c>
+      <c r="B67" s="43" t="str">
+        <f>IF(B38="DA","Diferența NU merge pe 472: nu e venit în avans, e datorie față de partener. Merge pe 419.","—")</f>
+        <v>Diferența NU merge pe 472: nu e venit în avans, e datorie față de partener. Merge pe 419.</v>
       </c>
     </row>
   </sheetData>
@@ -33653,240 +34006,218 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F21"/>
+  <dimension ref="A1:C24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" style="40" min="1" max="1"/>
-    <col width="20" customWidth="1" style="40" min="2" max="2"/>
-    <col width="20" customWidth="1" style="40" min="3" max="3"/>
-    <col width="26" customWidth="1" style="40" min="4" max="4"/>
-    <col width="30" customWidth="1" style="40" min="5" max="5"/>
-    <col width="26" customWidth="1" style="40" min="6" max="6"/>
+    <col width="42" customWidth="1" style="40" min="1" max="1"/>
+    <col width="34" customWidth="1" style="40" min="2" max="2"/>
+    <col width="62" customWidth="1" style="40" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="41" t="inlineStr">
         <is>
-          <t>MOD_NEUTRALIZARE — Reguli (tabele fixe)</t>
+          <t>MOD_AVANSURI — Reguli (tabele fixe)</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="44" t="inlineStr">
         <is>
-          <t>Principiul comun F-311 / F-312 / F-209: cost → cls.6 → stoc intermediar = venit neutralizare → stoc final / livrare. 711/712/722 nu se stinge greșit în stocul final fără pasul de obținere.</t>
+          <t>Regula e dată, nu formulă. Tabelul A răspunde la singura întrebare care se pune în practică: unde merge suma.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="42" t="inlineStr">
         <is>
-          <t>Tabel A — Lanț pe tip</t>
+          <t>Tabel A — Unde merge suma, și de ce nu altundeva</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="65" t="inlineStr">
         <is>
-          <t>Tip</t>
+          <t>Situație</t>
         </is>
       </c>
       <c r="B5" s="65" t="inlineStr">
         <is>
-          <t>Cost →</t>
+          <t>Unde merge</t>
         </is>
       </c>
       <c r="C5" s="65" t="inlineStr">
         <is>
-          <t>Stoc intermediar</t>
-        </is>
-      </c>
-      <c r="D5" s="65" t="inlineStr">
-        <is>
-          <t>Venit neut.</t>
-        </is>
-      </c>
-      <c r="E5" s="65" t="inlineStr">
-        <is>
-          <t>Stoc final / livrare</t>
-        </is>
-      </c>
-      <c r="F5" s="65" t="inlineStr">
-        <is>
-          <t>Descărcare la vânzare</t>
+          <t>De ce NU altundeva</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="43" t="inlineStr">
         <is>
-          <t>BUNURI</t>
+          <t>Avans încasat de la client</t>
         </is>
       </c>
       <c r="B6" s="43" t="inlineStr">
         <is>
-          <t>601=301</t>
+          <t>419 + 4427</t>
         </is>
       </c>
       <c r="C6" s="43" t="inlineStr">
         <is>
-          <t>331=711</t>
-        </is>
-      </c>
-      <c r="D6" s="43" t="inlineStr">
-        <is>
-          <t>711=331 apoi 345=711</t>
-        </is>
-      </c>
-      <c r="E6" s="43" t="inlineStr">
-        <is>
-          <t>345</t>
-        </is>
-      </c>
-      <c r="F6" s="43" t="inlineStr">
-        <is>
-          <t>711=345 (NU 607)</t>
+          <t>Nu 704/707: nu s-a livrat nimic. Datorie, nu venit.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="43" t="inlineStr">
         <is>
-          <t>SERVICII</t>
+          <t>Avans plătit furnizorului</t>
         </is>
       </c>
       <c r="B7" s="43" t="inlineStr">
         <is>
-          <t>641/601=…</t>
+          <t>409 + 4426</t>
         </is>
       </c>
       <c r="C7" s="43" t="inlineStr">
         <is>
-          <t>332=712</t>
-        </is>
-      </c>
-      <c r="D7" s="43" t="inlineStr">
-        <is>
-          <t>712=332</t>
-        </is>
-      </c>
-      <c r="E7" s="43" t="inlineStr">
-        <is>
-          <t>(nu e stoc final)</t>
-        </is>
-      </c>
-      <c r="F7" s="43" t="inlineStr">
-        <is>
-          <t>712 stins la livrare</t>
+          <t>Nu 6xx și nu 3xx: nu s-a primit nimic. Creanță, nu cost.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="43" t="inlineStr">
         <is>
-          <t>MF</t>
+          <t>Încasare peste valoarea facturii</t>
         </is>
       </c>
       <c r="B8" s="43" t="inlineStr">
         <is>
-          <t>601=301, 641=421</t>
+          <t>419 + 4427, pe diferență</t>
         </is>
       </c>
       <c r="C8" s="43" t="inlineStr">
         <is>
-          <t>231=722</t>
-        </is>
-      </c>
-      <c r="D8" s="43" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E8" s="43" t="inlineStr">
-        <is>
-          <t>213=231</t>
-        </is>
-      </c>
-      <c r="F8" s="43" t="inlineStr">
-        <is>
-          <t>(nu e vânzare — e activ)</t>
+          <t>Nu 472 (nu e venit în avans) și nu 758. E datorie față de partener.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="43" t="inlineStr">
+        <is>
+          <t>Sold creditor rămas pe 4111</t>
+        </is>
+      </c>
+      <c r="B9" s="43" t="inlineStr">
+        <is>
+          <t>se reclasifică pe 419</t>
+        </is>
+      </c>
+      <c r="C9" s="43" t="inlineStr">
+        <is>
+          <t>Un cont de activ cu sold contrar naturii lui = avans neînregistrat (C-23).</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="42" t="inlineStr">
-        <is>
-          <t>Tabel B — Porți de calitate</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="44" t="inlineStr">
-        <is>
-          <t>• ΣD=ΣC pe fiecare bloc</t>
+      <c r="A10" s="43" t="inlineStr">
+        <is>
+          <t>TVA din suma încasată peste factură</t>
+        </is>
+      </c>
+      <c r="B10" s="43" t="inlineStr">
+        <is>
+          <t>se extrage: sumă ÷ (1 + cotă)</t>
+        </is>
+      </c>
+      <c r="C10" s="43" t="inlineStr">
+        <is>
+          <t>Suma virată e TVA-inclusivă. Pusă integral pe 419, TVA rămâne necolectată.</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="44" t="inlineStr">
-        <is>
-          <t>• Cont venit neutralizare: rulaj D = rulaj C la final (sold 0)</t>
+      <c r="A12" s="42" t="inlineStr">
+        <is>
+          <t>Tabel B — Aritmetica avansului</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="44" t="inlineStr">
         <is>
-          <t>• Stoc intermediar sold 0 după finalizare</t>
+          <t>Avansul cu TVA se înregistrează INTEGRAL la primire sau la plată.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="44" t="inlineStr">
         <is>
-          <t>• Pentru BUNURI: 345 un singur D și un singur C; descărcare prin 711, nu 607</t>
+          <t>La factura finală se stinge capitalul avansului, se completează diferența de valoare și se adaugă doar RESTUL de TVA.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="44" t="inlineStr">
         <is>
-          <t>• Pentru MF: impact net pe 121 din capitalizare = 0 (cheltuieli = 722)</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="42" t="inlineStr">
-        <is>
-          <t>Tabel C — Ce NU se face</t>
+          <t>TVA avans + TVA rest = TVA totală a facturii. Cine recolectează TVA pe toată factura plătește de două ori pe aceeași bază.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="44" t="inlineStr">
+        <is>
+          <t>Suma încasată peste factură e TVA-inclusivă: se împarte la 1 + cotă ca să se separe baza de TVA.</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="44" t="inlineStr">
-        <is>
-          <t>• 345 creditat de două ori fără un debit de obținere (eroarea F-311 veche)</t>
+      <c r="A18" s="42" t="inlineStr">
+        <is>
+          <t>Tabel C — Porți de calitate</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="44" t="inlineStr">
         <is>
-          <t>• 722 = 231 (ar stinge activul — eroare F-209 veche); corect e 231 = 722</t>
+          <t>• ΣDr = ΣCr pe fiecare bloc</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="44" t="inlineStr">
         <is>
-          <t>• 607 la descărcarea produselor finite (607 e doar mărfuri)</t>
+          <t>• Sold 419 = 0 și sold 409 = 0 după livrare / recepție</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="44" t="inlineStr">
         <is>
-          <t>• „711 sau 712” la servicii — pentru servicii e strict 712</t>
+          <t>• Sold 4111 = 0 pe partenerul supraîncasat, după reclasificare</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="44" t="inlineStr">
+        <is>
+          <t>• Un sold CREDITOR pe 4111 e avans neînregistrat, nu eroare de încasare (C-23)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="44" t="inlineStr">
+        <is>
+          <t>• TVA-ul din supraîncasare se colectează chiar dacă banii se returnează luna următoare; dacă încasarea și restituirea se închid în aceeași lună, se neutralizează</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="44" t="inlineStr">
+        <is>
+          <t>• La regimul TVA la încasare, TVA-ul avansului trece prin 4428.INC — vezi MOD_TVA_INCASARE</t>
         </is>
       </c>
     </row>
@@ -33901,14 +34232,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G35"/>
+  <dimension ref="A1:G45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="14" customWidth="1" style="40" min="1" max="1"/>
-    <col width="20" customWidth="1" style="40" min="2" max="2"/>
+    <col width="40" customWidth="1" style="40" min="1" max="1"/>
+    <col width="16" customWidth="1" style="40" min="2" max="2"/>
     <col width="14" customWidth="1" style="40" min="3" max="3"/>
     <col width="52" customWidth="1" style="40" min="4" max="4"/>
-    <col width="20" customWidth="1" style="40" min="5" max="5"/>
+    <col width="16" customWidth="1" style="40" min="5" max="5"/>
     <col width="14" customWidth="1" style="40" min="6" max="6"/>
     <col width="52" customWidth="1" style="40" min="7" max="7"/>
   </cols>
@@ -33916,21 +34247,21 @@
     <row r="1">
       <c r="A1" s="41" t="inlineStr">
         <is>
-          <t>MOD_NEUTRALIZARE — Jurnale (generate automat)</t>
+          <t>MOD_AVANSURI — Jurnale (generate automat)</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="44" t="inlineStr">
         <is>
-          <t>Lanțul se adaptează după Tip. Pentru MF, blocul de vânzare rămâne 0. Pentru SERVICII, stocul final e gol.</t>
+          <t>Blocurile B și D sunt articole compuse: factura finală stinge avansul ȘI înregistrează restul, într-o singură notă.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="42" t="inlineStr">
         <is>
-          <t>Bloc 1 — Costuri pe cls.6</t>
+          <t>Bloc A — Avans încasat de la client</t>
         </is>
       </c>
     </row>
@@ -33941,8 +34272,8 @@
         </is>
       </c>
       <c r="B5" s="43" t="str">
-        <f>Declarații_NEUTRALIZARE!B8</f>
-        <v>2026-07-05</v>
+        <f>Declarații_AVANSURI!B8</f>
+        <v>2026-07-31</v>
       </c>
     </row>
     <row r="6">
@@ -33986,71 +34317,62 @@
       <c r="A7" s="43" t="n">
         <v>1</v>
       </c>
-      <c r="B7" s="43" t="inlineStr">
-        <is>
-          <t>601</t>
-        </is>
+      <c r="B7" s="43" t="str">
+        <f>Declarații_AVANSURI!B57</f>
+        <v>5121</v>
       </c>
       <c r="C7" s="43">
-        <f>Declarații_NEUTRALIZARE!B20</f>
-        <v>4500</v>
+        <f>IF(Declarații_AVANSURI!B12="DA",Declarații_AVANSURI!B16,0)</f>
+        <v>6050</v>
       </c>
       <c r="D7" s="43" t="str">
-        <f>"Consum materiale " &amp; Declarații_NEUTRALIZARE!B37</f>
-        <v>Consum materiale — 2026-07 — BUNURI — 711</v>
+        <f>"Încasare avans client " &amp; Declarații_AVANSURI!B13 &amp; " " &amp; Declarații_AVANSURI!B60</f>
+        <v>Încasare avans client Client DEMO — avansuri 2026-07</v>
       </c>
       <c r="E7" s="43" t="str">
-        <f>Declarații_NEUTRALIZARE!B32</f>
-        <v>301</v>
+        <f>Declarații_AVANSURI!B50</f>
+        <v>419</v>
       </c>
       <c r="F7" s="43">
-        <f>Declarații_NEUTRALIZARE!B20</f>
-        <v>4500</v>
+        <f>IF(Declarații_AVANSURI!B12="DA",Declarații_AVANSURI!B14,0)</f>
+        <v>5000</v>
       </c>
       <c r="G7" s="43" t="str">
-        <f>"Stingere stoc materii " &amp; Declarații_NEUTRALIZARE!B37</f>
-        <v>Stingere stoc materii — 2026-07 — BUNURI — 711</v>
+        <f>"Datorie din avans (bază) " &amp; Declarații_AVANSURI!B60</f>
+        <v>Datorie din avans (bază) — avansuri 2026-07</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="43" t="n">
         <v>2</v>
       </c>
-      <c r="B8" s="43" t="inlineStr">
-        <is>
-          <t>641</t>
-        </is>
-      </c>
-      <c r="C8" s="43">
-        <f>Declarații_NEUTRALIZARE!B21</f>
+      <c r="B8" s="43" t="n">
         <v>0</v>
       </c>
-      <c r="D8" s="43" t="str">
-        <f>"Manoperă pe proiect " &amp; Declarații_NEUTRALIZARE!B37</f>
-        <v>Manoperă pe proiect — 2026-07 — BUNURI — 711</v>
-      </c>
-      <c r="E8" s="43" t="inlineStr">
-        <is>
-          <t>421</t>
-        </is>
+      <c r="C8" s="43" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" s="43" t="str">
+        <f>Declarații_AVANSURI!B56</f>
+        <v>4427</v>
       </c>
       <c r="F8" s="43">
-        <f>Declarații_NEUTRALIZARE!B21</f>
-        <v>0</v>
+        <f>IF(Declarații_AVANSURI!B12="DA",Declarații_AVANSURI!B15,0)</f>
+        <v>1050</v>
       </c>
       <c r="G8" s="43" t="str">
-        <f>"Datorie salarii " &amp; Declarații_NEUTRALIZARE!B37</f>
-        <v>Datorie salarii — 2026-07 — BUNURI — 711</v>
+        <f>"TVA colectată pe avans " &amp; Declarații_AVANSURI!B60</f>
+        <v>TVA colectată pe avans — avansuri 2026-07</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="43" t="inlineStr">
         <is>
-          <t>Check B1</t>
+          <t>Check A</t>
         </is>
       </c>
       <c r="B9" s="43">
-        <f>(C7+C8)-(F7+F8)</f>
+        <f>C7-(F7+F8)</f>
         <v>0</v>
       </c>
       <c r="C9" s="43" t="str">
@@ -34061,95 +34383,113 @@
     <row r="11">
       <c r="A11" s="42" t="inlineStr">
         <is>
-          <t>Bloc 2 — Stoc intermediar = venit neutralizare (pas revelator)</t>
+          <t>Bloc B — Factura finală + stingerea avansului</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="43" t="inlineStr">
-        <is>
-          <t>Data:</t>
-        </is>
-      </c>
-      <c r="B12" s="43" t="str">
-        <f>Declarații_NEUTRALIZARE!B9</f>
-        <v>2026-07-20</v>
+      <c r="A12" s="65" t="inlineStr">
+        <is>
+          <t>Nr</t>
+        </is>
+      </c>
+      <c r="B12" s="65" t="inlineStr">
+        <is>
+          <t>Cont Dr</t>
+        </is>
+      </c>
+      <c r="C12" s="65" t="inlineStr">
+        <is>
+          <t>Sumă Dr</t>
+        </is>
+      </c>
+      <c r="D12" s="65" t="inlineStr">
+        <is>
+          <t>Descriere Dr</t>
+        </is>
+      </c>
+      <c r="E12" s="65" t="inlineStr">
+        <is>
+          <t>Cont Cr</t>
+        </is>
+      </c>
+      <c r="F12" s="65" t="inlineStr">
+        <is>
+          <t>Sumă Cr</t>
+        </is>
+      </c>
+      <c r="G12" s="65" t="inlineStr">
+        <is>
+          <t>Descriere Cr</t>
+        </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="65" t="inlineStr">
-        <is>
-          <t>Nr</t>
-        </is>
-      </c>
-      <c r="B13" s="65" t="inlineStr">
-        <is>
-          <t>Cont Dr</t>
-        </is>
-      </c>
-      <c r="C13" s="65" t="inlineStr">
-        <is>
-          <t>Sumă Dr</t>
-        </is>
-      </c>
-      <c r="D13" s="65" t="inlineStr">
-        <is>
-          <t>Descriere Dr</t>
-        </is>
-      </c>
-      <c r="E13" s="65" t="inlineStr">
-        <is>
-          <t>Cont Cr</t>
-        </is>
-      </c>
-      <c r="F13" s="65" t="inlineStr">
-        <is>
-          <t>Sumă Cr</t>
-        </is>
-      </c>
-      <c r="G13" s="65" t="inlineStr">
-        <is>
-          <t>Descriere Cr</t>
-        </is>
+      <c r="A13" s="43" t="n">
+        <v>1</v>
+      </c>
+      <c r="B13" s="43" t="str">
+        <f>Declarații_AVANSURI!B50</f>
+        <v>419</v>
+      </c>
+      <c r="C13" s="43">
+        <f>IF(Declarații_AVANSURI!B12="DA",Declarații_AVANSURI!B14,0)</f>
+        <v>5000</v>
+      </c>
+      <c r="D13" s="43" t="str">
+        <f>"Stingerea avansului (bază) " &amp; Declarații_AVANSURI!B60</f>
+        <v>Stingerea avansului (bază) — avansuri 2026-07</v>
+      </c>
+      <c r="E13" s="43" t="str">
+        <f>Declarații_AVANSURI!B53</f>
+        <v>707</v>
+      </c>
+      <c r="F13" s="43">
+        <f>IF(Declarații_AVANSURI!B12="DA",Declarații_AVANSURI!B17,0)</f>
+        <v>12000</v>
+      </c>
+      <c r="G13" s="43" t="str">
+        <f>"Venit din vânzare (total factură) " &amp; Declarații_AVANSURI!B60</f>
+        <v>Venit din vânzare (total factură) — avansuri 2026-07</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="43" t="n">
-        <v>1</v>
-      </c>
-      <c r="B14" s="43">
-        <f>Declarații_NEUTRALIZARE!B15</f>
-        <v>331</v>
+        <v>2</v>
+      </c>
+      <c r="B14" s="43" t="str">
+        <f>Declarații_AVANSURI!B49</f>
+        <v>4111</v>
       </c>
       <c r="C14" s="43">
-        <f>Declarații_NEUTRALIZARE!B23</f>
-        <v>4500</v>
+        <f>IF(Declarații_AVANSURI!B12="DA",Declarații_AVANSURI!B22,0)</f>
+        <v>8470</v>
       </c>
       <c r="D14" s="43" t="str">
-        <f>"Stoc intermediar (PN/servicii/MF în curs) " &amp; Declarații_NEUTRALIZARE!B37</f>
-        <v>Stoc intermediar (PN/servicii/MF în curs) — 2026-07 — BUNURI — 711</v>
-      </c>
-      <c r="E14" s="43">
-        <f>Declarații_NEUTRALIZARE!B14</f>
-        <v>711</v>
+        <f>"Rest de încasat de la client " &amp; Declarații_AVANSURI!B60</f>
+        <v>Rest de încasat de la client — avansuri 2026-07</v>
+      </c>
+      <c r="E14" s="43" t="str">
+        <f>Declarații_AVANSURI!B56</f>
+        <v>4427</v>
       </c>
       <c r="F14" s="43">
-        <f>Declarații_NEUTRALIZARE!B23</f>
-        <v>4500</v>
+        <f>IF(Declarații_AVANSURI!B12="DA",Declarații_AVANSURI!B20,0)</f>
+        <v>1470</v>
       </c>
       <c r="G14" s="43" t="str">
-        <f>"Venit producție / neutralizare " &amp; Declarații_NEUTRALIZARE!B37</f>
-        <v>Venit producție / neutralizare — 2026-07 — BUNURI — 711</v>
+        <f>"REST de TVA colectată (nu toată factura) " &amp; Declarații_AVANSURI!B60</f>
+        <v>REST de TVA colectată (nu toată factura) — avansuri 2026-07</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="43" t="inlineStr">
         <is>
-          <t>Check B2</t>
+          <t>Check B</t>
         </is>
       </c>
       <c r="B15" s="43">
-        <f>C14-F14</f>
+        <f>(C13+C14)-(F13+F14)</f>
         <v>0</v>
       </c>
       <c r="C15" s="43" t="str">
@@ -34157,22 +34497,26 @@
         <v>OK</v>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="42" t="inlineStr">
-        <is>
-          <t>Bloc 3 — Finalizare (obținere stoc final / stingere intermediar)</t>
-        </is>
+    <row r="16">
+      <c r="A16" s="43" t="inlineStr">
+        <is>
+          <t>Check B2 (419 se închide la zero)</t>
+        </is>
+      </c>
+      <c r="B16" s="43">
+        <f>F7-C13</f>
+        <v>0</v>
+      </c>
+      <c r="C16" s="43" t="str">
+        <f>IF(ABS(B16)&lt;0.01,"OK — sold 419 = 0","EROARE — avansul nu s-a stins integral")</f>
+        <v>OK — sold 419 = 0</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="43" t="inlineStr">
-        <is>
-          <t>Data:</t>
-        </is>
-      </c>
-      <c r="B18" s="43" t="str">
-        <f>Declarații_NEUTRALIZARE!B9</f>
-        <v>2026-07-20</v>
+      <c r="A18" s="42" t="inlineStr">
+        <is>
+          <t>Bloc C — Avans plătit furnizorului</t>
+        </is>
       </c>
     </row>
     <row r="19">
@@ -34216,68 +34560,62 @@
       <c r="A20" s="43" t="n">
         <v>1</v>
       </c>
-      <c r="B20" s="43">
-        <f>IF(Declarații_NEUTRALIZARE!B13="BUNURI",Declarații_NEUTRALIZARE!B14,IF(Declarații_NEUTRALIZARE!B13="SERVICII",Declarații_NEUTRALIZARE!B14,Declarații_NEUTRALIZARE!B16))</f>
-        <v>711</v>
+      <c r="B20" s="43" t="str">
+        <f>Declarații_AVANSURI!B51</f>
+        <v>409</v>
       </c>
       <c r="C20" s="43">
-        <f>Declarații_NEUTRALIZARE!B23</f>
-        <v>4500</v>
+        <f>IF(Declarații_AVANSURI!B25="DA",Declarații_AVANSURI!B27,0)</f>
+        <v>3000</v>
       </c>
       <c r="D20" s="43" t="str">
-        <f>IF(Declarații_NEUTRALIZARE!B13="BUNURI","Reluare PN (711 debitat #1) ",IF(Declarații_NEUTRALIZARE!B13="SERVICII","Stingere servicii în curs ","Transfer MF final ")) &amp; Declarații_NEUTRALIZARE!B37</f>
-        <v>Reluare PN (711 debitat #1) — 2026-07 — BUNURI — 711</v>
-      </c>
-      <c r="E20" s="43">
-        <f>IF(Declarații_NEUTRALIZARE!B13="MF",Declarații_NEUTRALIZARE!B15,Declarații_NEUTRALIZARE!B15)</f>
-        <v>331</v>
+        <f>"Avans plătit furnizorului (bază) " &amp; Declarații_AVANSURI!B60</f>
+        <v>Avans plătit furnizorului (bază) — avansuri 2026-07</v>
+      </c>
+      <c r="E20" s="43" t="str">
+        <f>Declarații_AVANSURI!B57</f>
+        <v>5121</v>
       </c>
       <c r="F20" s="43">
-        <f>Declarații_NEUTRALIZARE!B23</f>
-        <v>4500</v>
+        <f>IF(Declarații_AVANSURI!B25="DA",Declarații_AVANSURI!B29,0)</f>
+        <v>3630</v>
       </c>
       <c r="G20" s="43" t="str">
-        <f>"Stingere stoc intermediar " &amp; Declarații_NEUTRALIZARE!B37</f>
-        <v>Stingere stoc intermediar — 2026-07 — BUNURI — 711</v>
+        <f>"Ieșire bancă (total avans) " &amp; Declarații_AVANSURI!B60</f>
+        <v>Ieșire bancă (total avans) — avansuri 2026-07</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="43" t="n">
         <v>2</v>
       </c>
-      <c r="B21" s="43">
-        <f>IF(Declarații_NEUTRALIZARE!B13="BUNURI",Declarații_NEUTRALIZARE!B16,0)</f>
-        <v>345</v>
+      <c r="B21" s="43" t="str">
+        <f>Declarații_AVANSURI!B55</f>
+        <v>4426</v>
       </c>
       <c r="C21" s="43">
-        <f>IF(Declarații_NEUTRALIZARE!B13="BUNURI",Declarații_NEUTRALIZARE!B23,0)</f>
-        <v>4500</v>
+        <f>IF(Declarații_AVANSURI!B25="DA",Declarații_AVANSURI!B28,0)</f>
+        <v>630</v>
       </c>
       <c r="D21" s="43" t="str">
-        <f>IF(Declarații_NEUTRALIZARE!B13="BUNURI","Obținere produs finit (345=711) " &amp; Declarații_NEUTRALIZARE!B37,"")</f>
-        <v>Obținere produs finit (345=711) — 2026-07 — BUNURI — 711</v>
-      </c>
-      <c r="E21" s="43">
-        <f>IF(Declarații_NEUTRALIZARE!B13="BUNURI",Declarații_NEUTRALIZARE!B14,0)</f>
-        <v>711</v>
-      </c>
-      <c r="F21" s="43">
-        <f>IF(Declarații_NEUTRALIZARE!B13="BUNURI",Declarații_NEUTRALIZARE!B23,0)</f>
-        <v>4500</v>
-      </c>
-      <c r="G21" s="43" t="str">
-        <f>IF(Declarații_NEUTRALIZARE!B13="BUNURI","Neutralizare (711 creditat #2) " &amp; Declarații_NEUTRALIZARE!B37,"")</f>
-        <v>Neutralizare (711 creditat #2) — 2026-07 — BUNURI — 711</v>
+        <f>"TVA deductibilă pe avans " &amp; Declarații_AVANSURI!B60</f>
+        <v>TVA deductibilă pe avans — avansuri 2026-07</v>
+      </c>
+      <c r="E21" s="43" t="n">
+        <v>0</v>
+      </c>
+      <c r="F21" s="43" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="43" t="inlineStr">
         <is>
-          <t>Check B3</t>
+          <t>Check C</t>
         </is>
       </c>
       <c r="B22" s="43">
-        <f>(C20+C21)-(F20+F21)</f>
+        <f>(C20+C21)-F20</f>
         <v>0</v>
       </c>
       <c r="C22" s="43" t="str">
@@ -34288,180 +34626,383 @@
     <row r="24">
       <c r="A24" s="42" t="inlineStr">
         <is>
-          <t>Bloc 4 — Vânzare + descărcare (BUNURI/SERVICII; 0 pentru MF)</t>
+          <t>Bloc D — Recepție + stingerea avansului furnizor</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="43" t="inlineStr">
-        <is>
-          <t>Data:</t>
-        </is>
-      </c>
-      <c r="B25" s="43" t="str">
-        <f>Declarații_NEUTRALIZARE!B10</f>
-        <v>2026-07-25</v>
+      <c r="A25" s="65" t="inlineStr">
+        <is>
+          <t>Nr</t>
+        </is>
+      </c>
+      <c r="B25" s="65" t="inlineStr">
+        <is>
+          <t>Cont Dr</t>
+        </is>
+      </c>
+      <c r="C25" s="65" t="inlineStr">
+        <is>
+          <t>Sumă Dr</t>
+        </is>
+      </c>
+      <c r="D25" s="65" t="inlineStr">
+        <is>
+          <t>Descriere Dr</t>
+        </is>
+      </c>
+      <c r="E25" s="65" t="inlineStr">
+        <is>
+          <t>Cont Cr</t>
+        </is>
+      </c>
+      <c r="F25" s="65" t="inlineStr">
+        <is>
+          <t>Sumă Cr</t>
+        </is>
+      </c>
+      <c r="G25" s="65" t="inlineStr">
+        <is>
+          <t>Descriere Cr</t>
+        </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="65" t="inlineStr">
-        <is>
-          <t>Nr</t>
-        </is>
-      </c>
-      <c r="B26" s="65" t="inlineStr">
-        <is>
-          <t>Cont Dr</t>
-        </is>
-      </c>
-      <c r="C26" s="65" t="inlineStr">
-        <is>
-          <t>Sumă Dr</t>
-        </is>
-      </c>
-      <c r="D26" s="65" t="inlineStr">
-        <is>
-          <t>Descriere Dr</t>
-        </is>
-      </c>
-      <c r="E26" s="65" t="inlineStr">
-        <is>
-          <t>Cont Cr</t>
-        </is>
-      </c>
-      <c r="F26" s="65" t="inlineStr">
-        <is>
-          <t>Sumă Cr</t>
-        </is>
-      </c>
-      <c r="G26" s="65" t="inlineStr">
-        <is>
-          <t>Descriere Cr</t>
-        </is>
+      <c r="A26" s="43" t="n">
+        <v>1</v>
+      </c>
+      <c r="B26" s="43" t="str">
+        <f>Declarații_AVANSURI!B54</f>
+        <v>371</v>
+      </c>
+      <c r="C26" s="43">
+        <f>IF(Declarații_AVANSURI!B25="DA",Declarații_AVANSURI!B30,0)</f>
+        <v>8000</v>
+      </c>
+      <c r="D26" s="43" t="str">
+        <f>"Stoc recepționat (total factură) " &amp; Declarații_AVANSURI!B60</f>
+        <v>Stoc recepționat (total factură) — avansuri 2026-07</v>
+      </c>
+      <c r="E26" s="43" t="str">
+        <f>Declarații_AVANSURI!B51</f>
+        <v>409</v>
+      </c>
+      <c r="F26" s="43">
+        <f>IF(Declarații_AVANSURI!B25="DA",Declarații_AVANSURI!B27,0)</f>
+        <v>3000</v>
+      </c>
+      <c r="G26" s="43" t="str">
+        <f>"Stingerea avansului (bază) " &amp; Declarații_AVANSURI!B60</f>
+        <v>Stingerea avansului (bază) — avansuri 2026-07</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="43" t="n">
+        <v>2</v>
+      </c>
+      <c r="B27" s="43" t="str">
+        <f>Declarații_AVANSURI!B55</f>
+        <v>4426</v>
+      </c>
+      <c r="C27" s="43">
+        <f>IF(Declarații_AVANSURI!B25="DA",Declarații_AVANSURI!B33,0)</f>
+        <v>1050</v>
+      </c>
+      <c r="D27" s="43" t="str">
+        <f>"REST de TVA deductibilă " &amp; Declarații_AVANSURI!B60</f>
+        <v>REST de TVA deductibilă — avansuri 2026-07</v>
+      </c>
+      <c r="E27" s="43" t="str">
+        <f>Declarații_AVANSURI!B52</f>
+        <v>401.RO</v>
+      </c>
+      <c r="F27" s="43">
+        <f>IF(Declarații_AVANSURI!B25="DA",Declarații_AVANSURI!B35,0)</f>
+        <v>6050</v>
+      </c>
+      <c r="G27" s="43" t="str">
+        <f>"Rest de plătit furnizorului " &amp; Declarații_AVANSURI!B60</f>
+        <v>Rest de plătit furnizorului — avansuri 2026-07</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="43" t="inlineStr">
+        <is>
+          <t>Check D</t>
+        </is>
+      </c>
+      <c r="B28" s="43">
+        <f>(C26+C27)-(F26+F27)</f>
+        <v>0</v>
+      </c>
+      <c r="C28" s="43" t="str">
+        <f>IF(ABS(B28)&lt;0.01,"OK","EROARE")</f>
+        <v>OK</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="43" t="inlineStr">
+        <is>
+          <t>Check D2 (409 se închide la zero)</t>
+        </is>
+      </c>
+      <c r="B29" s="43">
+        <f>C20-F26</f>
+        <v>0</v>
+      </c>
+      <c r="C29" s="43" t="str">
+        <f>IF(ABS(B29)&lt;0.01,"OK — sold 409 = 0","EROARE — avansul nu s-a stins integral")</f>
+        <v>OK — sold 409 = 0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="42" t="inlineStr">
+        <is>
+          <t>Bloc E — Supraîncasare (pas revelator)</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="65" t="inlineStr">
+        <is>
+          <t>Nr</t>
+        </is>
+      </c>
+      <c r="B32" s="65" t="inlineStr">
+        <is>
+          <t>Cont Dr</t>
+        </is>
+      </c>
+      <c r="C32" s="65" t="inlineStr">
+        <is>
+          <t>Sumă Dr</t>
+        </is>
+      </c>
+      <c r="D32" s="65" t="inlineStr">
+        <is>
+          <t>Descriere Dr</t>
+        </is>
+      </c>
+      <c r="E32" s="65" t="inlineStr">
+        <is>
+          <t>Cont Cr</t>
+        </is>
+      </c>
+      <c r="F32" s="65" t="inlineStr">
+        <is>
+          <t>Sumă Cr</t>
+        </is>
+      </c>
+      <c r="G32" s="65" t="inlineStr">
+        <is>
+          <t>Descriere Cr</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="43" t="n">
         <v>1</v>
       </c>
-      <c r="B27" s="43" t="str">
-        <f>IF(OR(Declarații_NEUTRALIZARE!B13="BUNURI",Declarații_NEUTRALIZARE!B13="SERVICII"),Declarații_NEUTRALIZARE!B33,0)</f>
-        <v>411.RO</v>
-      </c>
-      <c r="C27" s="43">
-        <f>IF(OR(Declarații_NEUTRALIZARE!B13="BUNURI",Declarații_NEUTRALIZARE!B13="SERVICII"),Declarații_NEUTRALIZARE!B29,0)</f>
-        <v>8470</v>
-      </c>
-      <c r="D27" s="43" t="str">
-        <f>"Creanță client " &amp; Declarații_NEUTRALIZARE!B37</f>
-        <v>Creanță client — 2026-07 — BUNURI — 711</v>
-      </c>
-      <c r="E27" s="43">
-        <f>IF(OR(Declarații_NEUTRALIZARE!B13="BUNURI",Declarații_NEUTRALIZARE!B13="SERVICII"),Declarații_NEUTRALIZARE!B17,0)</f>
-        <v>701</v>
-      </c>
-      <c r="F27" s="43">
-        <f>IF(OR(Declarații_NEUTRALIZARE!B13="BUNURI",Declarații_NEUTRALIZARE!B13="SERVICII"),Declarații_NEUTRALIZARE!B26,0)</f>
-        <v>7000</v>
-      </c>
-      <c r="G27" s="43" t="str">
-        <f>"Venit din vânzare " &amp; Declarații_NEUTRALIZARE!B37</f>
-        <v>Venit din vânzare — 2026-07 — BUNURI — 711</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="43" t="n">
+      <c r="B33" s="43" t="str">
+        <f>Declarații_AVANSURI!B49</f>
+        <v>4111</v>
+      </c>
+      <c r="C33" s="43">
+        <f>IF(Declarații_AVANSURI!B38="DA",Declarații_AVANSURI!B40,0)</f>
+        <v>10000</v>
+      </c>
+      <c r="D33" s="43" t="str">
+        <f>"Factura emisă (total) " &amp; Declarații_AVANSURI!B60</f>
+        <v>Factura emisă (total) — avansuri 2026-07</v>
+      </c>
+      <c r="E33" s="43" t="str">
+        <f>Declarații_AVANSURI!B53</f>
+        <v>707</v>
+      </c>
+      <c r="F33" s="43">
+        <f>IF(Declarații_AVANSURI!B38="DA",Declarații_AVANSURI!B41,0)</f>
+        <v>8264.46</v>
+      </c>
+      <c r="G33" s="43" t="str">
+        <f>"Venit " &amp; Declarații_AVANSURI!B60</f>
+        <v>Venit — avansuri 2026-07</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="43" t="n">
         <v>2</v>
       </c>
-      <c r="B28" s="43" t="n">
+      <c r="B34" s="43" t="n">
         <v>0</v>
       </c>
-      <c r="C28" s="43" t="n">
+      <c r="C34" s="43" t="n">
         <v>0</v>
       </c>
-      <c r="E28" s="43" t="str">
-        <f>IF(OR(Declarații_NEUTRALIZARE!B13="BUNURI",Declarații_NEUTRALIZARE!B13="SERVICII"),Declarații_NEUTRALIZARE!B34,0)</f>
+      <c r="E34" s="43" t="str">
+        <f>Declarații_AVANSURI!B56</f>
         <v>4427</v>
       </c>
-      <c r="F28" s="43">
-        <f>IF(OR(Declarații_NEUTRALIZARE!B13="BUNURI",Declarații_NEUTRALIZARE!B13="SERVICII"),Declarații_NEUTRALIZARE!B28,0)</f>
-        <v>1470</v>
-      </c>
-      <c r="G28" s="43" t="str">
-        <f>"TVA colectată " &amp; Declarații_NEUTRALIZARE!B37</f>
-        <v>TVA colectată — 2026-07 — BUNURI — 711</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="43" t="n">
+      <c r="F34" s="43">
+        <f>IF(Declarații_AVANSURI!B38="DA",Declarații_AVANSURI!B42,0)</f>
+        <v>1735.5400000000009</v>
+      </c>
+      <c r="G34" s="43" t="str">
+        <f>"TVA colectată pe factură " &amp; Declarații_AVANSURI!B60</f>
+        <v>TVA colectată pe factură — avansuri 2026-07</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="43" t="inlineStr">
+        <is>
+          <t>Check E1 (factura)</t>
+        </is>
+      </c>
+      <c r="B35" s="43">
+        <f>C33-(F33+F34)</f>
+        <v>0</v>
+      </c>
+      <c r="C35" s="43" t="str">
+        <f>IF(ABS(B35)&lt;0.01,"OK","EROARE")</f>
+        <v>OK</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="43" t="n">
         <v>3</v>
       </c>
-      <c r="B29" s="43">
-        <f>IF(Declarații_NEUTRALIZARE!B13="BUNURI",Declarații_NEUTRALIZARE!B14,IF(Declarații_NEUTRALIZARE!B13="SERVICII",Declarații_NEUTRALIZARE!B14,0))</f>
-        <v>711</v>
-      </c>
-      <c r="C29" s="43">
-        <f>IF(OR(Declarații_NEUTRALIZARE!B13="BUNURI",Declarații_NEUTRALIZARE!B13="SERVICII"),Declarații_NEUTRALIZARE!B23,0)</f>
-        <v>4500</v>
-      </c>
-      <c r="D29" s="43" t="str">
-        <f>IF(Declarații_NEUTRALIZARE!B13="BUNURI","Descărcare PF prin 711 (NU 607) ",IF(Declarații_NEUTRALIZARE!B13="SERVICII","Stingere 712 la livrare ","")) &amp; Declarații_NEUTRALIZARE!B37</f>
-        <v>Descărcare PF prin 711 (NU 607) — 2026-07 — BUNURI — 711</v>
-      </c>
-      <c r="E29" s="43">
-        <f>IF(Declarații_NEUTRALIZARE!B13="BUNURI",Declarații_NEUTRALIZARE!B16,0)</f>
-        <v>345</v>
-      </c>
-      <c r="F29" s="43">
-        <f>IF(Declarații_NEUTRALIZARE!B13="BUNURI",Declarații_NEUTRALIZARE!B23,0)</f>
-        <v>4500</v>
-      </c>
-      <c r="G29" s="43" t="str">
-        <f>IF(Declarații_NEUTRALIZARE!B13="BUNURI","Stingere stoc PF " &amp; Declarații_NEUTRALIZARE!B37,"")</f>
-        <v>Stingere stoc PF — 2026-07 — BUNURI — 711</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="43" t="inlineStr">
-        <is>
-          <t>Check B4</t>
-        </is>
-      </c>
-      <c r="B30" s="43">
-        <f>(C27+C28+C29)-(F27+F28+F29)</f>
+      <c r="B36" s="43" t="str">
+        <f>Declarații_AVANSURI!B57</f>
+        <v>5121</v>
+      </c>
+      <c r="C36" s="43">
+        <f>IF(Declarații_AVANSURI!B38="DA",Declarații_AVANSURI!B43,0)</f>
+        <v>15000</v>
+      </c>
+      <c r="D36" s="43" t="str">
+        <f>"Încasare peste factură " &amp; Declarații_AVANSURI!B60</f>
+        <v>Încasare peste factură — avansuri 2026-07</v>
+      </c>
+      <c r="E36" s="43" t="str">
+        <f>Declarații_AVANSURI!B49</f>
+        <v>4111</v>
+      </c>
+      <c r="F36" s="43">
+        <f>IF(Declarații_AVANSURI!B38="DA",Declarații_AVANSURI!B43,0)</f>
+        <v>15000</v>
+      </c>
+      <c r="G36" s="43" t="str">
+        <f>"Creanța stinsă și depășită — 4111 trece pe credit " &amp; Declarații_AVANSURI!B60</f>
+        <v>Creanța stinsă și depășită — 4111 trece pe credit — avansuri 2026-07</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="43" t="inlineStr">
+        <is>
+          <t>Check E2 (încasarea)</t>
+        </is>
+      </c>
+      <c r="B37" s="43">
+        <f>C36-F36</f>
         <v>0</v>
       </c>
-      <c r="C30" s="43" t="str">
-        <f>IF(ABS(B30)&lt;0.01,"OK","EROARE")</f>
+      <c r="C37" s="43" t="str">
+        <f>IF(ABS(B37)&lt;0.01,"OK","EROARE")</f>
         <v>OK</v>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="43" t="inlineStr">
+    <row r="38">
+      <c r="A38" s="43" t="n">
+        <v>4</v>
+      </c>
+      <c r="B38" s="43" t="str">
+        <f>Declarații_AVANSURI!B49</f>
+        <v>4111</v>
+      </c>
+      <c r="C38" s="43">
+        <f>IF(Declarații_AVANSURI!B38="DA",Declarații_AVANSURI!B44,0)</f>
+        <v>5000</v>
+      </c>
+      <c r="D38" s="43" t="str">
+        <f>"Reclasificarea soldului creditor de pe 4111 " &amp; Declarații_AVANSURI!B60</f>
+        <v>Reclasificarea soldului creditor de pe 4111 — avansuri 2026-07</v>
+      </c>
+      <c r="E38" s="43" t="str">
+        <f>Declarații_AVANSURI!B50</f>
+        <v>419</v>
+      </c>
+      <c r="F38" s="43">
+        <f>IF(Declarații_AVANSURI!B38="DA",Declarații_AVANSURI!B45,0)</f>
+        <v>4132.23</v>
+      </c>
+      <c r="G38" s="43" t="str">
+        <f>"Avans identificat (bază) " &amp; Declarații_AVANSURI!B60</f>
+        <v>Avans identificat (bază) — avansuri 2026-07</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="43" t="n">
+        <v>5</v>
+      </c>
+      <c r="B39" s="43" t="n">
+        <v>0</v>
+      </c>
+      <c r="C39" s="43" t="n">
+        <v>0</v>
+      </c>
+      <c r="E39" s="43" t="str">
+        <f>Declarații_AVANSURI!B56</f>
+        <v>4427</v>
+      </c>
+      <c r="F39" s="43">
+        <f>IF(Declarații_AVANSURI!B38="DA",Declarații_AVANSURI!B46,0)</f>
+        <v>867.7700000000004</v>
+      </c>
+      <c r="G39" s="43" t="str">
+        <f>"TVA extrasă din suma încasată " &amp; Declarații_AVANSURI!B60</f>
+        <v>TVA extrasă din suma încasată — avansuri 2026-07</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="43" t="inlineStr">
+        <is>
+          <t>Check E3 (descompunerea diferenței)</t>
+        </is>
+      </c>
+      <c r="B40" s="43">
+        <f>C38-(F38+F39)</f>
+        <v>0</v>
+      </c>
+      <c r="C40" s="43" t="str">
+        <f>IF(ABS(B40)&lt;0.01,"OK — bază + TVA = diferența încasată","EROARE — TVA nu s-a extras din suma încasată")</f>
+        <v>OK — bază + TVA = diferența încasată</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="43" t="inlineStr">
         <is>
           <t>Check global</t>
         </is>
       </c>
-      <c r="B32" s="43">
-        <f>ABS(B9)+ABS(B15)+ABS(B22)+ABS(B30)</f>
+      <c r="B42" s="43">
+        <f>ABS(B9)+ABS(B15)+ABS(B16)+ABS(B22)+ABS(B28)+ABS(B29)+ABS(B35)+ABS(B37)+ABS(B40)</f>
         <v>0</v>
       </c>
-      <c r="C32" s="43" t="str">
-        <f>IF(B32&lt;0.01,"OK — toate blocurile se închid","EROARE — cel puțin un bloc dezechilibrat")</f>
+      <c r="C42" s="43" t="str">
+        <f>IF(B42&lt;0.01,"OK — toate blocurile se închid","EROARE — cel puțin un bloc dezechilibrat")</f>
         <v>OK — toate blocurile se închid</v>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="42" t="inlineStr">
+    <row r="44">
+      <c r="A44" s="42" t="inlineStr">
         <is>
           <t>Stare terminală</t>
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="44" t="inlineStr">
-        <is>
-          <t>Cont venit neut. sold 0 | Stoc intermediar 0 | Pentru BUNURI: 345 sold 0, descărcare prin 711 | Pentru MF: 213=cost, impact 121 din capitalizare = 0</t>
+    <row r="45">
+      <c r="A45" s="44" t="inlineStr">
+        <is>
+          <t>Sold 419 = 0 și sold 409 = 0 după livrare / recepție. La supraîncasare: sold 4111 = 0 pe partenerul respectiv, iar diferența stă pe 419 cu TVA-ul ei colectat. TVA pe avans regularizată în D300.</t>
         </is>
       </c>
     </row>
@@ -34997,6 +35538,1770 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:I19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="6" customWidth="1" style="40" min="1" max="1"/>
+    <col width="30" customWidth="1" style="40" min="2" max="2"/>
+    <col width="14" customWidth="1" style="40" min="3" max="3"/>
+    <col width="12" customWidth="1" style="40" min="4" max="4"/>
+    <col width="12" customWidth="1" style="40" min="5" max="5"/>
+    <col width="14" customWidth="1" style="40" min="6" max="6"/>
+    <col width="52" customWidth="1" style="40" min="7" max="7"/>
+    <col width="24" customWidth="1" style="40" min="8" max="8"/>
+    <col width="10" customWidth="1" style="40" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="41" t="inlineStr">
+        <is>
+          <t>MOD_AVANSURI — Notă pentru import</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="44" t="inlineStr">
+        <is>
+          <t>Filtrează Include=DA. Situațiile neactivate ies cu sumă 0 și apar ca NU.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="65" t="inlineStr">
+        <is>
+          <t>Nr</t>
+        </is>
+      </c>
+      <c r="B4" s="65" t="inlineStr">
+        <is>
+          <t>Bloc</t>
+        </is>
+      </c>
+      <c r="C4" s="65" t="inlineStr">
+        <is>
+          <t>Data</t>
+        </is>
+      </c>
+      <c r="D4" s="65" t="inlineStr">
+        <is>
+          <t>Cont Dr</t>
+        </is>
+      </c>
+      <c r="E4" s="65" t="inlineStr">
+        <is>
+          <t>Cont Cr</t>
+        </is>
+      </c>
+      <c r="F4" s="65" t="inlineStr">
+        <is>
+          <t>Sumă</t>
+        </is>
+      </c>
+      <c r="G4" s="65" t="inlineStr">
+        <is>
+          <t>Descriere</t>
+        </is>
+      </c>
+      <c r="H4" s="65" t="inlineStr">
+        <is>
+          <t>Document</t>
+        </is>
+      </c>
+      <c r="I4" s="65" t="inlineStr">
+        <is>
+          <t>Include</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="43" t="n">
+        <v>1</v>
+      </c>
+      <c r="B5" s="43" t="inlineStr">
+        <is>
+          <t>A Avans client — bază</t>
+        </is>
+      </c>
+      <c r="C5" s="43" t="str">
+        <f>Declarații_AVANSURI!B8</f>
+        <v>2026-07-31</v>
+      </c>
+      <c r="D5" s="43" t="str">
+        <f>Jurnale_AVANSURI!B7</f>
+        <v>5121</v>
+      </c>
+      <c r="E5" s="43" t="str">
+        <f>Jurnale_AVANSURI!E7</f>
+        <v>419</v>
+      </c>
+      <c r="F5" s="43">
+        <f>Jurnale_AVANSURI!F7</f>
+        <v>5000</v>
+      </c>
+      <c r="G5" s="43" t="str">
+        <f>Jurnale_AVANSURI!D7</f>
+        <v>Încasare avans client Client DEMO — avansuri 2026-07</v>
+      </c>
+      <c r="H5" s="43" t="inlineStr">
+        <is>
+          <t>Extras de cont</t>
+        </is>
+      </c>
+      <c r="I5" s="43" t="str">
+        <f>IF(AND(ISNUMBER(F5),F5&gt;0),"DA","NU")</f>
+        <v>DA</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="43" t="n">
+        <v>2</v>
+      </c>
+      <c r="B6" s="43" t="inlineStr">
+        <is>
+          <t>A Avans client — TVA</t>
+        </is>
+      </c>
+      <c r="C6" s="43" t="str">
+        <f>Declarații_AVANSURI!B8</f>
+        <v>2026-07-31</v>
+      </c>
+      <c r="D6" s="43" t="str">
+        <f>Jurnale_AVANSURI!B7</f>
+        <v>5121</v>
+      </c>
+      <c r="E6" s="43" t="str">
+        <f>Jurnale_AVANSURI!E8</f>
+        <v>4427</v>
+      </c>
+      <c r="F6" s="43">
+        <f>Jurnale_AVANSURI!F8</f>
+        <v>1050</v>
+      </c>
+      <c r="G6" s="43" t="str">
+        <f>Jurnale_AVANSURI!G8</f>
+        <v>TVA colectată pe avans — avansuri 2026-07</v>
+      </c>
+      <c r="H6" s="43" t="inlineStr">
+        <is>
+          <t>Extras de cont</t>
+        </is>
+      </c>
+      <c r="I6" s="43" t="str">
+        <f>IF(AND(ISNUMBER(F6),F6&gt;0),"DA","NU")</f>
+        <v>DA</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="43" t="n">
+        <v>3</v>
+      </c>
+      <c r="B7" s="43" t="inlineStr">
+        <is>
+          <t>B Factură finală — stingere avans</t>
+        </is>
+      </c>
+      <c r="C7" s="43" t="str">
+        <f>Declarații_AVANSURI!B8</f>
+        <v>2026-07-31</v>
+      </c>
+      <c r="D7" s="43" t="str">
+        <f>Jurnale_AVANSURI!B13</f>
+        <v>419</v>
+      </c>
+      <c r="E7" s="43" t="str">
+        <f>Jurnale_AVANSURI!E13</f>
+        <v>707</v>
+      </c>
+      <c r="F7" s="43">
+        <f>Jurnale_AVANSURI!C13</f>
+        <v>5000</v>
+      </c>
+      <c r="G7" s="43" t="str">
+        <f>Jurnale_AVANSURI!D13</f>
+        <v>Stingerea avansului (bază) — avansuri 2026-07</v>
+      </c>
+      <c r="H7" s="43" t="inlineStr">
+        <is>
+          <t>Factură</t>
+        </is>
+      </c>
+      <c r="I7" s="43" t="str">
+        <f>IF(AND(ISNUMBER(F7),F7&gt;0),"DA","NU")</f>
+        <v>DA</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="43" t="n">
+        <v>4</v>
+      </c>
+      <c r="B8" s="43" t="inlineStr">
+        <is>
+          <t>B Factură finală — rest creanță</t>
+        </is>
+      </c>
+      <c r="C8" s="43" t="str">
+        <f>Declarații_AVANSURI!B8</f>
+        <v>2026-07-31</v>
+      </c>
+      <c r="D8" s="43" t="str">
+        <f>Jurnale_AVANSURI!B14</f>
+        <v>4111</v>
+      </c>
+      <c r="E8" s="43" t="str">
+        <f>Jurnale_AVANSURI!E14</f>
+        <v>4427</v>
+      </c>
+      <c r="F8" s="43">
+        <f>Jurnale_AVANSURI!C14</f>
+        <v>8470</v>
+      </c>
+      <c r="G8" s="43" t="str">
+        <f>Jurnale_AVANSURI!D14</f>
+        <v>Rest de încasat de la client — avansuri 2026-07</v>
+      </c>
+      <c r="H8" s="43" t="inlineStr">
+        <is>
+          <t>Factură</t>
+        </is>
+      </c>
+      <c r="I8" s="43" t="str">
+        <f>IF(AND(ISNUMBER(F8),F8&gt;0),"DA","NU")</f>
+        <v>DA</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="43" t="n">
+        <v>5</v>
+      </c>
+      <c r="B9" s="43" t="inlineStr">
+        <is>
+          <t>C Avans furnizor — bază</t>
+        </is>
+      </c>
+      <c r="C9" s="43" t="str">
+        <f>Declarații_AVANSURI!B8</f>
+        <v>2026-07-31</v>
+      </c>
+      <c r="D9" s="43" t="str">
+        <f>Jurnale_AVANSURI!B20</f>
+        <v>409</v>
+      </c>
+      <c r="E9" s="43" t="str">
+        <f>Jurnale_AVANSURI!E20</f>
+        <v>5121</v>
+      </c>
+      <c r="F9" s="43">
+        <f>Jurnale_AVANSURI!C20</f>
+        <v>3000</v>
+      </c>
+      <c r="G9" s="43" t="str">
+        <f>Jurnale_AVANSURI!D20</f>
+        <v>Avans plătit furnizorului (bază) — avansuri 2026-07</v>
+      </c>
+      <c r="H9" s="43" t="inlineStr">
+        <is>
+          <t>Extras de cont</t>
+        </is>
+      </c>
+      <c r="I9" s="43" t="str">
+        <f>IF(AND(ISNUMBER(F9),F9&gt;0),"DA","NU")</f>
+        <v>DA</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="43" t="n">
+        <v>6</v>
+      </c>
+      <c r="B10" s="43" t="inlineStr">
+        <is>
+          <t>C Avans furnizor — TVA</t>
+        </is>
+      </c>
+      <c r="C10" s="43" t="str">
+        <f>Declarații_AVANSURI!B8</f>
+        <v>2026-07-31</v>
+      </c>
+      <c r="D10" s="43" t="str">
+        <f>Jurnale_AVANSURI!B21</f>
+        <v>4426</v>
+      </c>
+      <c r="E10" s="43" t="str">
+        <f>Jurnale_AVANSURI!E20</f>
+        <v>5121</v>
+      </c>
+      <c r="F10" s="43">
+        <f>Jurnale_AVANSURI!C21</f>
+        <v>630</v>
+      </c>
+      <c r="G10" s="43" t="str">
+        <f>Jurnale_AVANSURI!D21</f>
+        <v>TVA deductibilă pe avans — avansuri 2026-07</v>
+      </c>
+      <c r="H10" s="43" t="inlineStr">
+        <is>
+          <t>Extras de cont</t>
+        </is>
+      </c>
+      <c r="I10" s="43" t="str">
+        <f>IF(AND(ISNUMBER(F10),F10&gt;0),"DA","NU")</f>
+        <v>DA</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="43" t="n">
+        <v>7</v>
+      </c>
+      <c r="B11" s="43" t="inlineStr">
+        <is>
+          <t>D Recepție — stingere avans</t>
+        </is>
+      </c>
+      <c r="C11" s="43" t="str">
+        <f>Declarații_AVANSURI!B8</f>
+        <v>2026-07-31</v>
+      </c>
+      <c r="D11" s="43" t="str">
+        <f>Jurnale_AVANSURI!B26</f>
+        <v>371</v>
+      </c>
+      <c r="E11" s="43" t="str">
+        <f>Jurnale_AVANSURI!E26</f>
+        <v>409</v>
+      </c>
+      <c r="F11" s="43">
+        <f>Jurnale_AVANSURI!F26</f>
+        <v>3000</v>
+      </c>
+      <c r="G11" s="43" t="str">
+        <f>Jurnale_AVANSURI!D26</f>
+        <v>Stoc recepționat (total factură) — avansuri 2026-07</v>
+      </c>
+      <c r="H11" s="43" t="inlineStr">
+        <is>
+          <t>NIR</t>
+        </is>
+      </c>
+      <c r="I11" s="43" t="str">
+        <f>IF(AND(ISNUMBER(F11),F11&gt;0),"DA","NU")</f>
+        <v>DA</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="43" t="n">
+        <v>8</v>
+      </c>
+      <c r="B12" s="43" t="inlineStr">
+        <is>
+          <t>D Recepție — rest datorie</t>
+        </is>
+      </c>
+      <c r="C12" s="43" t="str">
+        <f>Declarații_AVANSURI!B8</f>
+        <v>2026-07-31</v>
+      </c>
+      <c r="D12" s="43" t="str">
+        <f>Jurnale_AVANSURI!B27</f>
+        <v>4426</v>
+      </c>
+      <c r="E12" s="43" t="str">
+        <f>Jurnale_AVANSURI!E27</f>
+        <v>401.RO</v>
+      </c>
+      <c r="F12" s="43">
+        <f>Jurnale_AVANSURI!C27</f>
+        <v>1050</v>
+      </c>
+      <c r="G12" s="43" t="str">
+        <f>Jurnale_AVANSURI!D27</f>
+        <v>REST de TVA deductibilă — avansuri 2026-07</v>
+      </c>
+      <c r="H12" s="43" t="inlineStr">
+        <is>
+          <t>NIR</t>
+        </is>
+      </c>
+      <c r="I12" s="43" t="str">
+        <f>IF(AND(ISNUMBER(F12),F12&gt;0),"DA","NU")</f>
+        <v>DA</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="43" t="n">
+        <v>9</v>
+      </c>
+      <c r="B13" s="43" t="inlineStr">
+        <is>
+          <t>E Supraîncasare — factura</t>
+        </is>
+      </c>
+      <c r="C13" s="43" t="str">
+        <f>Declarații_AVANSURI!B8</f>
+        <v>2026-07-31</v>
+      </c>
+      <c r="D13" s="43" t="str">
+        <f>Jurnale_AVANSURI!B33</f>
+        <v>4111</v>
+      </c>
+      <c r="E13" s="43" t="str">
+        <f>Jurnale_AVANSURI!E33</f>
+        <v>707</v>
+      </c>
+      <c r="F13" s="43">
+        <f>Jurnale_AVANSURI!F33</f>
+        <v>8264.46</v>
+      </c>
+      <c r="G13" s="43" t="str">
+        <f>Jurnale_AVANSURI!D33</f>
+        <v>Factura emisă (total) — avansuri 2026-07</v>
+      </c>
+      <c r="H13" s="43" t="inlineStr">
+        <is>
+          <t>Factură</t>
+        </is>
+      </c>
+      <c r="I13" s="43" t="str">
+        <f>IF(AND(ISNUMBER(F13),F13&gt;0),"DA","NU")</f>
+        <v>DA</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="43" t="n">
+        <v>10</v>
+      </c>
+      <c r="B14" s="43" t="inlineStr">
+        <is>
+          <t>E Supraîncasare — încasarea</t>
+        </is>
+      </c>
+      <c r="C14" s="43" t="str">
+        <f>Declarații_AVANSURI!B8</f>
+        <v>2026-07-31</v>
+      </c>
+      <c r="D14" s="43" t="str">
+        <f>Jurnale_AVANSURI!B36</f>
+        <v>5121</v>
+      </c>
+      <c r="E14" s="43" t="str">
+        <f>Jurnale_AVANSURI!E36</f>
+        <v>4111</v>
+      </c>
+      <c r="F14" s="43">
+        <f>Jurnale_AVANSURI!C36</f>
+        <v>15000</v>
+      </c>
+      <c r="G14" s="43" t="str">
+        <f>Jurnale_AVANSURI!D36</f>
+        <v>Încasare peste factură — avansuri 2026-07</v>
+      </c>
+      <c r="H14" s="43" t="inlineStr">
+        <is>
+          <t>Extras de cont</t>
+        </is>
+      </c>
+      <c r="I14" s="43" t="str">
+        <f>IF(AND(ISNUMBER(F14),F14&gt;0),"DA","NU")</f>
+        <v>DA</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="43" t="n">
+        <v>11</v>
+      </c>
+      <c r="B15" s="43" t="inlineStr">
+        <is>
+          <t>E Supraîncasare — reclasificare</t>
+        </is>
+      </c>
+      <c r="C15" s="43" t="str">
+        <f>Declarații_AVANSURI!B8</f>
+        <v>2026-07-31</v>
+      </c>
+      <c r="D15" s="43" t="str">
+        <f>Jurnale_AVANSURI!B38</f>
+        <v>4111</v>
+      </c>
+      <c r="E15" s="43" t="str">
+        <f>Jurnale_AVANSURI!E38</f>
+        <v>419</v>
+      </c>
+      <c r="F15" s="43">
+        <f>Jurnale_AVANSURI!F38</f>
+        <v>4132.23</v>
+      </c>
+      <c r="G15" s="43" t="str">
+        <f>Jurnale_AVANSURI!D38</f>
+        <v>Reclasificarea soldului creditor de pe 4111 — avansuri 2026-07</v>
+      </c>
+      <c r="H15" s="43" t="inlineStr">
+        <is>
+          <t>Notă contabilă</t>
+        </is>
+      </c>
+      <c r="I15" s="43" t="str">
+        <f>IF(AND(ISNUMBER(F15),F15&gt;0),"DA","NU")</f>
+        <v>DA</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="43" t="n">
+        <v>12</v>
+      </c>
+      <c r="B16" s="43" t="inlineStr">
+        <is>
+          <t>E Supraîncasare — TVA extrasă</t>
+        </is>
+      </c>
+      <c r="C16" s="43" t="str">
+        <f>Declarații_AVANSURI!B8</f>
+        <v>2026-07-31</v>
+      </c>
+      <c r="D16" s="43" t="str">
+        <f>Jurnale_AVANSURI!B38</f>
+        <v>4111</v>
+      </c>
+      <c r="E16" s="43" t="str">
+        <f>Jurnale_AVANSURI!E39</f>
+        <v>4427</v>
+      </c>
+      <c r="F16" s="43">
+        <f>Jurnale_AVANSURI!F39</f>
+        <v>867.7700000000004</v>
+      </c>
+      <c r="G16" s="43" t="str">
+        <f>Jurnale_AVANSURI!G39</f>
+        <v>TVA extrasă din suma încasată — avansuri 2026-07</v>
+      </c>
+      <c r="H16" s="43" t="inlineStr">
+        <is>
+          <t>Notă contabilă</t>
+        </is>
+      </c>
+      <c r="I16" s="43" t="str">
+        <f>IF(AND(ISNUMBER(F16),F16&gt;0),"DA","NU")</f>
+        <v>DA</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="43" t="inlineStr">
+        <is>
+          <t>Rânduri de importat</t>
+        </is>
+      </c>
+      <c r="B18" s="43">
+        <f>COUNTIF(I5:I16,"DA")</f>
+        <v>12</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="43" t="inlineStr">
+        <is>
+          <t>Check global</t>
+        </is>
+      </c>
+      <c r="B19" s="43">
+        <f>Jurnale_AVANSURI!B42</f>
+        <v>0</v>
+      </c>
+      <c r="C19" s="43" t="str">
+        <f>IF(ABS(B19)&lt;0.01,"OK","EROARE")</f>
+        <v>OK</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet81.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B41"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="40" customWidth="1" style="40" min="1" max="1"/>
+    <col width="42" customWidth="1" style="40" min="2" max="2"/>
+    <col width="52" customWidth="1" style="40" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="41" t="inlineStr">
+        <is>
+          <t>MOD_NEUTRALIZARE — Declarații (input)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="44" t="inlineStr">
+        <is>
+          <t>Acoperă F-311 (bunuri/711), F-312 (servicii/712), F-209 (imobilizări/722). Alege tipul — conturile și lanțul se adaptează. Principiu: costurile lovesc cls.6, apoi contul de venit de producție capitalizează și neutralizează.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="42" t="inlineStr">
+        <is>
+          <t>1. Antet</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="43" t="inlineStr">
+        <is>
+          <t>Societate</t>
+        </is>
+      </c>
+      <c r="B5" s="43" t="str">
+        <f>Parametri!B5</f>
+        <v>SC EXEMPLU SRL</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="43" t="inlineStr">
+        <is>
+          <t>CUI</t>
+        </is>
+      </c>
+      <c r="B6" s="43" t="str">
+        <f>Parametri!B6</f>
+        <v>RO00000000</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="43" t="inlineStr">
+        <is>
+          <t>Luna / proiect</t>
+        </is>
+      </c>
+      <c r="B7" s="64" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="43" t="inlineStr">
+        <is>
+          <t>Data costuri (B1)</t>
+        </is>
+      </c>
+      <c r="B8" s="64" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="43" t="inlineStr">
+        <is>
+          <t>Data finalizare stoc (B2-B3)</t>
+        </is>
+      </c>
+      <c r="B9" s="64" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="43" t="inlineStr">
+        <is>
+          <t>Data vânzare / recepție MF (B4)</t>
+        </is>
+      </c>
+      <c r="B10" s="64" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="42" t="inlineStr">
+        <is>
+          <t>2. Tip producție (poartă principală)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="43" t="inlineStr">
+        <is>
+          <t>Tip (BUNURI / SERVICII / MF)</t>
+        </is>
+      </c>
+      <c r="B13" s="64" t="inlineStr">
+        <is>
+          <t>BUNURI</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="43" t="inlineStr">
+        <is>
+          <t>Cont venit neutralizare (auto)</t>
+        </is>
+      </c>
+      <c r="B14" s="43">
+        <f>IF(B13="BUNURI",711,IF(B13="SERVICII",712,IF(B13="MF",722,"?")))</f>
+        <v>711</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="43" t="inlineStr">
+        <is>
+          <t>Cont stoc intermediar (auto)</t>
+        </is>
+      </c>
+      <c r="B15" s="43">
+        <f>IF(B13="BUNURI",331,IF(B13="SERVICII",332,IF(B13="MF",231,"?")))</f>
+        <v>331</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="43" t="inlineStr">
+        <is>
+          <t>Cont stoc final (auto)</t>
+        </is>
+      </c>
+      <c r="B16" s="43">
+        <f>IF(B13="BUNURI",345,IF(B13="SERVICII","(nu e cazul — se stinge la livrare)",IF(B13="MF",213,"?")))</f>
+        <v>345</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="43" t="inlineStr">
+        <is>
+          <t>Cont venit vânzare (auto)</t>
+        </is>
+      </c>
+      <c r="B17" s="43">
+        <f>IF(B13="BUNURI",701,IF(B13="SERVICII",704,IF(B13="MF","(nu e vânzare — e activ)","?")))</f>
+        <v>701</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="42" t="inlineStr">
+        <is>
+          <t>3. Costuri (cls.6)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="43" t="inlineStr">
+        <is>
+          <t>Cost materiale (→ 601)</t>
+        </is>
+      </c>
+      <c r="B20" s="64" t="n">
+        <v>4500</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="43" t="inlineStr">
+        <is>
+          <t>Cost manoperă (→ 641)</t>
+        </is>
+      </c>
+      <c r="B21" s="64" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="43" t="inlineStr">
+        <is>
+          <t>Alte costuri (→ 6xx)</t>
+        </is>
+      </c>
+      <c r="B22" s="64" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="43" t="inlineStr">
+        <is>
+          <t>Cost total</t>
+        </is>
+      </c>
+      <c r="B23" s="43">
+        <f>B20+B21+B22</f>
+        <v>4500</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="42" t="inlineStr">
+        <is>
+          <t>4. Vânzare (doar BUNURI / SERVICII)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="43" t="inlineStr">
+        <is>
+          <t>Preț vânzare (fără TVA)</t>
+        </is>
+      </c>
+      <c r="B26" s="64" t="n">
+        <v>7000</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="43" t="inlineStr">
+        <is>
+          <t>Cota TVA</t>
+        </is>
+      </c>
+      <c r="B27" s="64" t="n">
+        <v>0.21</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="43" t="inlineStr">
+        <is>
+          <t>TVA</t>
+        </is>
+      </c>
+      <c r="B28" s="43">
+        <f>IF(OR(B13="BUNURI",B13="SERVICII"),B26*B27,0)</f>
+        <v>1470</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="43" t="inlineStr">
+        <is>
+          <t>Total factură</t>
+        </is>
+      </c>
+      <c r="B29" s="43">
+        <f>B26+B28</f>
+        <v>8470</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="42" t="inlineStr">
+        <is>
+          <t>5. Conturi suplimentare</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="43" t="inlineStr">
+        <is>
+          <t>Cont materii prime</t>
+        </is>
+      </c>
+      <c r="B32" s="64" t="inlineStr">
+        <is>
+          <t>301</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="43" t="inlineStr">
+        <is>
+          <t>Cont client</t>
+        </is>
+      </c>
+      <c r="B33" s="64" t="inlineStr">
+        <is>
+          <t>411.RO</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="43" t="inlineStr">
+        <is>
+          <t>Cont TVA colectată</t>
+        </is>
+      </c>
+      <c r="B34" s="64" t="inlineStr">
+        <is>
+          <t>4427</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="42" t="inlineStr">
+        <is>
+          <t>6. Sufix</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="43" t="inlineStr">
+        <is>
+          <t>Sufix</t>
+        </is>
+      </c>
+      <c r="B37" s="43" t="str">
+        <f>"— " &amp; B7 &amp; " — " &amp; B13 &amp; " — " &amp; B14</f>
+        <v>— 2026-07 — BUNURI — 711</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="42" t="inlineStr">
+        <is>
+          <t>7. Control</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="43" t="inlineStr">
+        <is>
+          <t>Marjă (vânzare − cost)</t>
+        </is>
+      </c>
+      <c r="B40" s="43">
+        <f>IF(OR(B13="BUNURI",B13="SERVICII"),B26-B23,"n/a (MF)")</f>
+        <v>2500</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="43" t="inlineStr">
+        <is>
+          <t>Notă principiu</t>
+        </is>
+      </c>
+      <c r="B41" s="43" t="inlineStr">
+        <is>
+          <t>Costurile lovesc cls.6; contul de venit de producție (711/712/722) capitalizează și neutralizează. Descărcarea la vânzare (bunuri) e prin 711=345, nu prin 607.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet82.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F21"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" style="40" min="1" max="1"/>
+    <col width="20" customWidth="1" style="40" min="2" max="2"/>
+    <col width="20" customWidth="1" style="40" min="3" max="3"/>
+    <col width="26" customWidth="1" style="40" min="4" max="4"/>
+    <col width="30" customWidth="1" style="40" min="5" max="5"/>
+    <col width="26" customWidth="1" style="40" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="41" t="inlineStr">
+        <is>
+          <t>MOD_NEUTRALIZARE — Reguli (tabele fixe)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="44" t="inlineStr">
+        <is>
+          <t>Principiul comun F-311 / F-312 / F-209: cost → cls.6 → stoc intermediar = venit neutralizare → stoc final / livrare. 711/712/722 nu se stinge greșit în stocul final fără pasul de obținere.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="42" t="inlineStr">
+        <is>
+          <t>Tabel A — Lanț pe tip</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="65" t="inlineStr">
+        <is>
+          <t>Tip</t>
+        </is>
+      </c>
+      <c r="B5" s="65" t="inlineStr">
+        <is>
+          <t>Cost →</t>
+        </is>
+      </c>
+      <c r="C5" s="65" t="inlineStr">
+        <is>
+          <t>Stoc intermediar</t>
+        </is>
+      </c>
+      <c r="D5" s="65" t="inlineStr">
+        <is>
+          <t>Venit neut.</t>
+        </is>
+      </c>
+      <c r="E5" s="65" t="inlineStr">
+        <is>
+          <t>Stoc final / livrare</t>
+        </is>
+      </c>
+      <c r="F5" s="65" t="inlineStr">
+        <is>
+          <t>Descărcare la vânzare</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="43" t="inlineStr">
+        <is>
+          <t>BUNURI</t>
+        </is>
+      </c>
+      <c r="B6" s="43" t="inlineStr">
+        <is>
+          <t>601=301</t>
+        </is>
+      </c>
+      <c r="C6" s="43" t="inlineStr">
+        <is>
+          <t>331=711</t>
+        </is>
+      </c>
+      <c r="D6" s="43" t="inlineStr">
+        <is>
+          <t>711=331 apoi 345=711</t>
+        </is>
+      </c>
+      <c r="E6" s="43" t="inlineStr">
+        <is>
+          <t>345</t>
+        </is>
+      </c>
+      <c r="F6" s="43" t="inlineStr">
+        <is>
+          <t>711=345 (NU 607)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="43" t="inlineStr">
+        <is>
+          <t>SERVICII</t>
+        </is>
+      </c>
+      <c r="B7" s="43" t="inlineStr">
+        <is>
+          <t>641/601=…</t>
+        </is>
+      </c>
+      <c r="C7" s="43" t="inlineStr">
+        <is>
+          <t>332=712</t>
+        </is>
+      </c>
+      <c r="D7" s="43" t="inlineStr">
+        <is>
+          <t>712=332</t>
+        </is>
+      </c>
+      <c r="E7" s="43" t="inlineStr">
+        <is>
+          <t>(nu e stoc final)</t>
+        </is>
+      </c>
+      <c r="F7" s="43" t="inlineStr">
+        <is>
+          <t>712 stins la livrare</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="43" t="inlineStr">
+        <is>
+          <t>MF</t>
+        </is>
+      </c>
+      <c r="B8" s="43" t="inlineStr">
+        <is>
+          <t>601=301, 641=421</t>
+        </is>
+      </c>
+      <c r="C8" s="43" t="inlineStr">
+        <is>
+          <t>231=722</t>
+        </is>
+      </c>
+      <c r="D8" s="43" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E8" s="43" t="inlineStr">
+        <is>
+          <t>213=231</t>
+        </is>
+      </c>
+      <c r="F8" s="43" t="inlineStr">
+        <is>
+          <t>(nu e vânzare — e activ)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="42" t="inlineStr">
+        <is>
+          <t>Tabel B — Porți de calitate</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="44" t="inlineStr">
+        <is>
+          <t>• ΣD=ΣC pe fiecare bloc</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="44" t="inlineStr">
+        <is>
+          <t>• Cont venit neutralizare: rulaj D = rulaj C la final (sold 0)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="44" t="inlineStr">
+        <is>
+          <t>• Stoc intermediar sold 0 după finalizare</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="44" t="inlineStr">
+        <is>
+          <t>• Pentru BUNURI: 345 un singur D și un singur C; descărcare prin 711, nu 607</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="44" t="inlineStr">
+        <is>
+          <t>• Pentru MF: impact net pe 121 din capitalizare = 0 (cheltuieli = 722)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="42" t="inlineStr">
+        <is>
+          <t>Tabel C — Ce NU se face</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="44" t="inlineStr">
+        <is>
+          <t>• 345 creditat de două ori fără un debit de obținere (eroarea F-311 veche)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="44" t="inlineStr">
+        <is>
+          <t>• 722 = 231 (ar stinge activul — eroare F-209 veche); corect e 231 = 722</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="44" t="inlineStr">
+        <is>
+          <t>• 607 la descărcarea produselor finite (607 e doar mărfuri)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="44" t="inlineStr">
+        <is>
+          <t>• „711 sau 712” la servicii — pentru servicii e strict 712</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet83.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G35"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" style="40" min="1" max="1"/>
+    <col width="20" customWidth="1" style="40" min="2" max="2"/>
+    <col width="14" customWidth="1" style="40" min="3" max="3"/>
+    <col width="52" customWidth="1" style="40" min="4" max="4"/>
+    <col width="20" customWidth="1" style="40" min="5" max="5"/>
+    <col width="14" customWidth="1" style="40" min="6" max="6"/>
+    <col width="52" customWidth="1" style="40" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="41" t="inlineStr">
+        <is>
+          <t>MOD_NEUTRALIZARE — Jurnale (generate automat)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="44" t="inlineStr">
+        <is>
+          <t>Lanțul se adaptează după Tip. Pentru MF, blocul de vânzare rămâne 0. Pentru SERVICII, stocul final e gol.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="42" t="inlineStr">
+        <is>
+          <t>Bloc 1 — Costuri pe cls.6</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="43" t="inlineStr">
+        <is>
+          <t>Data:</t>
+        </is>
+      </c>
+      <c r="B5" s="43" t="str">
+        <f>Declarații_NEUTRALIZARE!B8</f>
+        <v>2026-07-05</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="65" t="inlineStr">
+        <is>
+          <t>Nr</t>
+        </is>
+      </c>
+      <c r="B6" s="65" t="inlineStr">
+        <is>
+          <t>Cont Dr</t>
+        </is>
+      </c>
+      <c r="C6" s="65" t="inlineStr">
+        <is>
+          <t>Sumă Dr</t>
+        </is>
+      </c>
+      <c r="D6" s="65" t="inlineStr">
+        <is>
+          <t>Descriere Dr</t>
+        </is>
+      </c>
+      <c r="E6" s="65" t="inlineStr">
+        <is>
+          <t>Cont Cr</t>
+        </is>
+      </c>
+      <c r="F6" s="65" t="inlineStr">
+        <is>
+          <t>Sumă Cr</t>
+        </is>
+      </c>
+      <c r="G6" s="65" t="inlineStr">
+        <is>
+          <t>Descriere Cr</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="43" t="n">
+        <v>1</v>
+      </c>
+      <c r="B7" s="43" t="inlineStr">
+        <is>
+          <t>601</t>
+        </is>
+      </c>
+      <c r="C7" s="43">
+        <f>Declarații_NEUTRALIZARE!B20</f>
+        <v>4500</v>
+      </c>
+      <c r="D7" s="43" t="str">
+        <f>"Consum materiale " &amp; Declarații_NEUTRALIZARE!B37</f>
+        <v>Consum materiale — 2026-07 — BUNURI — 711</v>
+      </c>
+      <c r="E7" s="43" t="str">
+        <f>Declarații_NEUTRALIZARE!B32</f>
+        <v>301</v>
+      </c>
+      <c r="F7" s="43">
+        <f>Declarații_NEUTRALIZARE!B20</f>
+        <v>4500</v>
+      </c>
+      <c r="G7" s="43" t="str">
+        <f>"Stingere stoc materii " &amp; Declarații_NEUTRALIZARE!B37</f>
+        <v>Stingere stoc materii — 2026-07 — BUNURI — 711</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="43" t="n">
+        <v>2</v>
+      </c>
+      <c r="B8" s="43" t="inlineStr">
+        <is>
+          <t>641</t>
+        </is>
+      </c>
+      <c r="C8" s="43">
+        <f>Declarații_NEUTRALIZARE!B21</f>
+        <v>0</v>
+      </c>
+      <c r="D8" s="43" t="str">
+        <f>"Manoperă pe proiect " &amp; Declarații_NEUTRALIZARE!B37</f>
+        <v>Manoperă pe proiect — 2026-07 — BUNURI — 711</v>
+      </c>
+      <c r="E8" s="43" t="inlineStr">
+        <is>
+          <t>421</t>
+        </is>
+      </c>
+      <c r="F8" s="43">
+        <f>Declarații_NEUTRALIZARE!B21</f>
+        <v>0</v>
+      </c>
+      <c r="G8" s="43" t="str">
+        <f>"Datorie salarii " &amp; Declarații_NEUTRALIZARE!B37</f>
+        <v>Datorie salarii — 2026-07 — BUNURI — 711</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="43" t="inlineStr">
+        <is>
+          <t>Check B1</t>
+        </is>
+      </c>
+      <c r="B9" s="43">
+        <f>(C7+C8)-(F7+F8)</f>
+        <v>0</v>
+      </c>
+      <c r="C9" s="43" t="str">
+        <f>IF(ABS(B9)&lt;0.01,"OK","EROARE")</f>
+        <v>OK</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="42" t="inlineStr">
+        <is>
+          <t>Bloc 2 — Stoc intermediar = venit neutralizare (pas revelator)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="43" t="inlineStr">
+        <is>
+          <t>Data:</t>
+        </is>
+      </c>
+      <c r="B12" s="43" t="str">
+        <f>Declarații_NEUTRALIZARE!B9</f>
+        <v>2026-07-20</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="65" t="inlineStr">
+        <is>
+          <t>Nr</t>
+        </is>
+      </c>
+      <c r="B13" s="65" t="inlineStr">
+        <is>
+          <t>Cont Dr</t>
+        </is>
+      </c>
+      <c r="C13" s="65" t="inlineStr">
+        <is>
+          <t>Sumă Dr</t>
+        </is>
+      </c>
+      <c r="D13" s="65" t="inlineStr">
+        <is>
+          <t>Descriere Dr</t>
+        </is>
+      </c>
+      <c r="E13" s="65" t="inlineStr">
+        <is>
+          <t>Cont Cr</t>
+        </is>
+      </c>
+      <c r="F13" s="65" t="inlineStr">
+        <is>
+          <t>Sumă Cr</t>
+        </is>
+      </c>
+      <c r="G13" s="65" t="inlineStr">
+        <is>
+          <t>Descriere Cr</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="43" t="n">
+        <v>1</v>
+      </c>
+      <c r="B14" s="43">
+        <f>Declarații_NEUTRALIZARE!B15</f>
+        <v>331</v>
+      </c>
+      <c r="C14" s="43">
+        <f>Declarații_NEUTRALIZARE!B23</f>
+        <v>4500</v>
+      </c>
+      <c r="D14" s="43" t="str">
+        <f>"Stoc intermediar (PN/servicii/MF în curs) " &amp; Declarații_NEUTRALIZARE!B37</f>
+        <v>Stoc intermediar (PN/servicii/MF în curs) — 2026-07 — BUNURI — 711</v>
+      </c>
+      <c r="E14" s="43">
+        <f>Declarații_NEUTRALIZARE!B14</f>
+        <v>711</v>
+      </c>
+      <c r="F14" s="43">
+        <f>Declarații_NEUTRALIZARE!B23</f>
+        <v>4500</v>
+      </c>
+      <c r="G14" s="43" t="str">
+        <f>"Venit producție / neutralizare " &amp; Declarații_NEUTRALIZARE!B37</f>
+        <v>Venit producție / neutralizare — 2026-07 — BUNURI — 711</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="43" t="inlineStr">
+        <is>
+          <t>Check B2</t>
+        </is>
+      </c>
+      <c r="B15" s="43">
+        <f>C14-F14</f>
+        <v>0</v>
+      </c>
+      <c r="C15" s="43" t="str">
+        <f>IF(ABS(B15)&lt;0.01,"OK","EROARE")</f>
+        <v>OK</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="42" t="inlineStr">
+        <is>
+          <t>Bloc 3 — Finalizare (obținere stoc final / stingere intermediar)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="43" t="inlineStr">
+        <is>
+          <t>Data:</t>
+        </is>
+      </c>
+      <c r="B18" s="43" t="str">
+        <f>Declarații_NEUTRALIZARE!B9</f>
+        <v>2026-07-20</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="65" t="inlineStr">
+        <is>
+          <t>Nr</t>
+        </is>
+      </c>
+      <c r="B19" s="65" t="inlineStr">
+        <is>
+          <t>Cont Dr</t>
+        </is>
+      </c>
+      <c r="C19" s="65" t="inlineStr">
+        <is>
+          <t>Sumă Dr</t>
+        </is>
+      </c>
+      <c r="D19" s="65" t="inlineStr">
+        <is>
+          <t>Descriere Dr</t>
+        </is>
+      </c>
+      <c r="E19" s="65" t="inlineStr">
+        <is>
+          <t>Cont Cr</t>
+        </is>
+      </c>
+      <c r="F19" s="65" t="inlineStr">
+        <is>
+          <t>Sumă Cr</t>
+        </is>
+      </c>
+      <c r="G19" s="65" t="inlineStr">
+        <is>
+          <t>Descriere Cr</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="43" t="n">
+        <v>1</v>
+      </c>
+      <c r="B20" s="43">
+        <f>IF(Declarații_NEUTRALIZARE!B13="BUNURI",Declarații_NEUTRALIZARE!B14,IF(Declarații_NEUTRALIZARE!B13="SERVICII",Declarații_NEUTRALIZARE!B14,Declarații_NEUTRALIZARE!B16))</f>
+        <v>711</v>
+      </c>
+      <c r="C20" s="43">
+        <f>Declarații_NEUTRALIZARE!B23</f>
+        <v>4500</v>
+      </c>
+      <c r="D20" s="43" t="str">
+        <f>IF(Declarații_NEUTRALIZARE!B13="BUNURI","Reluare PN (711 debitat #1) ",IF(Declarații_NEUTRALIZARE!B13="SERVICII","Stingere servicii în curs ","Transfer MF final ")) &amp; Declarații_NEUTRALIZARE!B37</f>
+        <v>Reluare PN (711 debitat #1) — 2026-07 — BUNURI — 711</v>
+      </c>
+      <c r="E20" s="43">
+        <f>IF(Declarații_NEUTRALIZARE!B13="MF",Declarații_NEUTRALIZARE!B15,Declarații_NEUTRALIZARE!B15)</f>
+        <v>331</v>
+      </c>
+      <c r="F20" s="43">
+        <f>Declarații_NEUTRALIZARE!B23</f>
+        <v>4500</v>
+      </c>
+      <c r="G20" s="43" t="str">
+        <f>"Stingere stoc intermediar " &amp; Declarații_NEUTRALIZARE!B37</f>
+        <v>Stingere stoc intermediar — 2026-07 — BUNURI — 711</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="43" t="n">
+        <v>2</v>
+      </c>
+      <c r="B21" s="43">
+        <f>IF(Declarații_NEUTRALIZARE!B13="BUNURI",Declarații_NEUTRALIZARE!B16,0)</f>
+        <v>345</v>
+      </c>
+      <c r="C21" s="43">
+        <f>IF(Declarații_NEUTRALIZARE!B13="BUNURI",Declarații_NEUTRALIZARE!B23,0)</f>
+        <v>4500</v>
+      </c>
+      <c r="D21" s="43" t="str">
+        <f>IF(Declarații_NEUTRALIZARE!B13="BUNURI","Obținere produs finit (345=711) " &amp; Declarații_NEUTRALIZARE!B37,"")</f>
+        <v>Obținere produs finit (345=711) — 2026-07 — BUNURI — 711</v>
+      </c>
+      <c r="E21" s="43">
+        <f>IF(Declarații_NEUTRALIZARE!B13="BUNURI",Declarații_NEUTRALIZARE!B14,0)</f>
+        <v>711</v>
+      </c>
+      <c r="F21" s="43">
+        <f>IF(Declarații_NEUTRALIZARE!B13="BUNURI",Declarații_NEUTRALIZARE!B23,0)</f>
+        <v>4500</v>
+      </c>
+      <c r="G21" s="43" t="str">
+        <f>IF(Declarații_NEUTRALIZARE!B13="BUNURI","Neutralizare (711 creditat #2) " &amp; Declarații_NEUTRALIZARE!B37,"")</f>
+        <v>Neutralizare (711 creditat #2) — 2026-07 — BUNURI — 711</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="43" t="inlineStr">
+        <is>
+          <t>Check B3</t>
+        </is>
+      </c>
+      <c r="B22" s="43">
+        <f>(C20+C21)-(F20+F21)</f>
+        <v>0</v>
+      </c>
+      <c r="C22" s="43" t="str">
+        <f>IF(ABS(B22)&lt;0.01,"OK","EROARE")</f>
+        <v>OK</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="42" t="inlineStr">
+        <is>
+          <t>Bloc 4 — Vânzare + descărcare (BUNURI/SERVICII; 0 pentru MF)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="43" t="inlineStr">
+        <is>
+          <t>Data:</t>
+        </is>
+      </c>
+      <c r="B25" s="43" t="str">
+        <f>Declarații_NEUTRALIZARE!B10</f>
+        <v>2026-07-25</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="65" t="inlineStr">
+        <is>
+          <t>Nr</t>
+        </is>
+      </c>
+      <c r="B26" s="65" t="inlineStr">
+        <is>
+          <t>Cont Dr</t>
+        </is>
+      </c>
+      <c r="C26" s="65" t="inlineStr">
+        <is>
+          <t>Sumă Dr</t>
+        </is>
+      </c>
+      <c r="D26" s="65" t="inlineStr">
+        <is>
+          <t>Descriere Dr</t>
+        </is>
+      </c>
+      <c r="E26" s="65" t="inlineStr">
+        <is>
+          <t>Cont Cr</t>
+        </is>
+      </c>
+      <c r="F26" s="65" t="inlineStr">
+        <is>
+          <t>Sumă Cr</t>
+        </is>
+      </c>
+      <c r="G26" s="65" t="inlineStr">
+        <is>
+          <t>Descriere Cr</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="43" t="n">
+        <v>1</v>
+      </c>
+      <c r="B27" s="43" t="str">
+        <f>IF(OR(Declarații_NEUTRALIZARE!B13="BUNURI",Declarații_NEUTRALIZARE!B13="SERVICII"),Declarații_NEUTRALIZARE!B33,0)</f>
+        <v>411.RO</v>
+      </c>
+      <c r="C27" s="43">
+        <f>IF(OR(Declarații_NEUTRALIZARE!B13="BUNURI",Declarații_NEUTRALIZARE!B13="SERVICII"),Declarații_NEUTRALIZARE!B29,0)</f>
+        <v>8470</v>
+      </c>
+      <c r="D27" s="43" t="str">
+        <f>"Creanță client " &amp; Declarații_NEUTRALIZARE!B37</f>
+        <v>Creanță client — 2026-07 — BUNURI — 711</v>
+      </c>
+      <c r="E27" s="43">
+        <f>IF(OR(Declarații_NEUTRALIZARE!B13="BUNURI",Declarații_NEUTRALIZARE!B13="SERVICII"),Declarații_NEUTRALIZARE!B17,0)</f>
+        <v>701</v>
+      </c>
+      <c r="F27" s="43">
+        <f>IF(OR(Declarații_NEUTRALIZARE!B13="BUNURI",Declarații_NEUTRALIZARE!B13="SERVICII"),Declarații_NEUTRALIZARE!B26,0)</f>
+        <v>7000</v>
+      </c>
+      <c r="G27" s="43" t="str">
+        <f>"Venit din vânzare " &amp; Declarații_NEUTRALIZARE!B37</f>
+        <v>Venit din vânzare — 2026-07 — BUNURI — 711</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="43" t="n">
+        <v>2</v>
+      </c>
+      <c r="B28" s="43" t="n">
+        <v>0</v>
+      </c>
+      <c r="C28" s="43" t="n">
+        <v>0</v>
+      </c>
+      <c r="E28" s="43" t="str">
+        <f>IF(OR(Declarații_NEUTRALIZARE!B13="BUNURI",Declarații_NEUTRALIZARE!B13="SERVICII"),Declarații_NEUTRALIZARE!B34,0)</f>
+        <v>4427</v>
+      </c>
+      <c r="F28" s="43">
+        <f>IF(OR(Declarații_NEUTRALIZARE!B13="BUNURI",Declarații_NEUTRALIZARE!B13="SERVICII"),Declarații_NEUTRALIZARE!B28,0)</f>
+        <v>1470</v>
+      </c>
+      <c r="G28" s="43" t="str">
+        <f>"TVA colectată " &amp; Declarații_NEUTRALIZARE!B37</f>
+        <v>TVA colectată — 2026-07 — BUNURI — 711</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="43" t="n">
+        <v>3</v>
+      </c>
+      <c r="B29" s="43">
+        <f>IF(Declarații_NEUTRALIZARE!B13="BUNURI",Declarații_NEUTRALIZARE!B14,IF(Declarații_NEUTRALIZARE!B13="SERVICII",Declarații_NEUTRALIZARE!B14,0))</f>
+        <v>711</v>
+      </c>
+      <c r="C29" s="43">
+        <f>IF(OR(Declarații_NEUTRALIZARE!B13="BUNURI",Declarații_NEUTRALIZARE!B13="SERVICII"),Declarații_NEUTRALIZARE!B23,0)</f>
+        <v>4500</v>
+      </c>
+      <c r="D29" s="43" t="str">
+        <f>IF(Declarații_NEUTRALIZARE!B13="BUNURI","Descărcare PF prin 711 (NU 607) ",IF(Declarații_NEUTRALIZARE!B13="SERVICII","Stingere 712 la livrare ","")) &amp; Declarații_NEUTRALIZARE!B37</f>
+        <v>Descărcare PF prin 711 (NU 607) — 2026-07 — BUNURI — 711</v>
+      </c>
+      <c r="E29" s="43">
+        <f>IF(Declarații_NEUTRALIZARE!B13="BUNURI",Declarații_NEUTRALIZARE!B16,0)</f>
+        <v>345</v>
+      </c>
+      <c r="F29" s="43">
+        <f>IF(Declarații_NEUTRALIZARE!B13="BUNURI",Declarații_NEUTRALIZARE!B23,0)</f>
+        <v>4500</v>
+      </c>
+      <c r="G29" s="43" t="str">
+        <f>IF(Declarații_NEUTRALIZARE!B13="BUNURI","Stingere stoc PF " &amp; Declarații_NEUTRALIZARE!B37,"")</f>
+        <v>Stingere stoc PF — 2026-07 — BUNURI — 711</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="43" t="inlineStr">
+        <is>
+          <t>Check B4</t>
+        </is>
+      </c>
+      <c r="B30" s="43">
+        <f>(C27+C28+C29)-(F27+F28+F29)</f>
+        <v>0</v>
+      </c>
+      <c r="C30" s="43" t="str">
+        <f>IF(ABS(B30)&lt;0.01,"OK","EROARE")</f>
+        <v>OK</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="43" t="inlineStr">
+        <is>
+          <t>Check global</t>
+        </is>
+      </c>
+      <c r="B32" s="43">
+        <f>ABS(B9)+ABS(B15)+ABS(B22)+ABS(B30)</f>
+        <v>0</v>
+      </c>
+      <c r="C32" s="43" t="str">
+        <f>IF(B32&lt;0.01,"OK — toate blocurile se închid","EROARE — cel puțin un bloc dezechilibrat")</f>
+        <v>OK — toate blocurile se închid</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="42" t="inlineStr">
+        <is>
+          <t>Stare terminală</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="44" t="inlineStr">
+        <is>
+          <t>Cont venit neut. sold 0 | Stoc intermediar 0 | Pentru BUNURI: 345 sold 0, descărcare prin 711 | Pentru MF: 213=cost, impact 121 din capitalizare = 0</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet84.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:I15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -35415,7 +37720,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet81.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet85.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -35802,7 +38107,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet82.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet86.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -36195,7 +38500,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet83.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet87.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -36859,7 +39164,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet84.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet88.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -37393,7 +39698,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet85.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet89.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -37789,1227 +40094,6 @@
         <is>
           <t>Soldul, nu rulajul lunii. La rambursare, atenția merge pe soldul cu care pleci</t>
         </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet86.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:D22"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="10" customWidth="1" style="40" min="1" max="1"/>
-    <col width="52" customWidth="1" style="40" min="2" max="2"/>
-    <col width="52" customWidth="1" style="40" min="3" max="3"/>
-    <col width="52" customWidth="1" style="40" min="4" max="4"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="41" t="inlineStr">
-        <is>
-          <t>MOD_INCHIDERE_LUNARA — Reguli</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="44" t="inlineStr">
-        <is>
-          <t>Tabele fixe. Se editează doar când se schimbă legea sau când o corelație nouă intră în workbook-ul de plan.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="42" t="inlineStr">
-        <is>
-          <t>Tabelul A — corelațiile verificate și ce le rupe</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="65" t="inlineStr">
-        <is>
-          <t>Cod</t>
-        </is>
-      </c>
-      <c r="B5" s="65" t="inlineStr">
-        <is>
-          <t>Corelația</t>
-        </is>
-      </c>
-      <c r="C5" s="65" t="inlineStr">
-        <is>
-          <t>Ce o rupe LEGITIM</t>
-        </is>
-      </c>
-      <c r="D5" s="65" t="inlineStr">
-        <is>
-          <t>Ce o rupe SUSPECT</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="43" t="inlineStr">
-        <is>
-          <t>C-24</t>
-        </is>
-      </c>
-      <c r="B6" s="43" t="inlineStr">
-        <is>
-          <t>sold C 421 + sold C 423 = rest de plată din stat</t>
-        </is>
-      </c>
-      <c r="C6" s="43" t="inlineStr">
-        <is>
-          <t>Avans pe 425, nescăzut încă · drepturi neridicate mutate pe 426</t>
-        </is>
-      </c>
-      <c r="D6" s="43" t="inlineStr">
-        <is>
-          <t>Plată înregistrată pe alt cont decât 421 · salarii restante nereclasificate</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="43" t="inlineStr">
-        <is>
-          <t>C-25</t>
-        </is>
-      </c>
-      <c r="B7" s="43" t="inlineStr">
-        <is>
-          <t>rulaj C 444 = sold C 444</t>
-        </is>
-      </c>
-      <c r="C7" s="43" t="inlineStr">
-        <is>
-          <t>Rectificativă pe o lună anterioară · plată în avans</t>
-        </is>
-      </c>
-      <c r="D7" s="43" t="inlineStr">
-        <is>
-          <t>Sold &gt; rulaj constant = stopaj la sursă nevirat. Peste 30 de zile, penal</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="43" t="inlineStr">
-        <is>
-          <t>C-26</t>
-        </is>
-      </c>
-      <c r="B8" s="43" t="inlineStr">
-        <is>
-          <t>rulaj C 4315/4316/436 = soldurile lor</t>
-        </is>
-      </c>
-      <c r="C8" s="43" t="inlineStr">
-        <is>
-          <t>Rectificativă · eșalonare la plată aprobată de ANAF</t>
-        </is>
-      </c>
-      <c r="D8" s="43" t="inlineStr">
-        <is>
-          <t>Contribuții restante · bază de calcul care nu corespunde brutului</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="43" t="inlineStr">
-        <is>
-          <t>C-27</t>
-        </is>
-      </c>
-      <c r="B9" s="43" t="inlineStr">
-        <is>
-          <t>cota CAM × rulaj C 421 = rulaj C 436</t>
-        </is>
-      </c>
-      <c r="C9" s="43" t="inlineStr">
-        <is>
-          <t>Luni cu concedii medicale: CAM nu se datorează pe partea din FNUASS (art. 220^5) · categorii cu cotă redusă</t>
-        </is>
-      </c>
-      <c r="D9" s="43" t="inlineStr">
-        <is>
-          <t>Sporuri sau prime omise din fondul de salarii · CAM înregistrat invers</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="43" t="inlineStr">
-        <is>
-          <t>C-28</t>
-        </is>
-      </c>
-      <c r="B10" s="43" t="inlineStr">
-        <is>
-          <t>rulaj C 427 = sold C 427</t>
-        </is>
-      </c>
-      <c r="C10" s="43" t="inlineStr">
-        <is>
-          <t>Poprire înființată la final de lună, cu virare în luna următoare</t>
-        </is>
-      </c>
-      <c r="D10" s="43" t="inlineStr">
-        <is>
-          <t>Sold care persistă = bani opriți din salariul altcuiva și nevirați</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="43" t="inlineStr">
-        <is>
-          <t>C-29</t>
-        </is>
-      </c>
-      <c r="B11" s="43" t="inlineStr">
-        <is>
-          <t>sold 4423 din balanță = sold din decontul de TVA</t>
-        </is>
-      </c>
-      <c r="C11" s="43" t="inlineStr">
-        <is>
-          <t>Sume din decizii de impunere, pe analitic distinct (F-421)</t>
-        </is>
-      </c>
-      <c r="D11" s="43" t="inlineStr">
-        <is>
-          <t>TVA neachitat din perioade precedente, omis din decont</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="43" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="B12" s="43" t="inlineStr">
-        <is>
-          <t>sold 473, 581, 542, 4382 = 0</t>
-        </is>
-      </c>
-      <c r="C12" s="43" t="inlineStr">
-        <is>
-          <t>Operațiune de final de lună, închisă în primele zile ale lunii următoare</t>
-        </is>
-      </c>
-      <c r="D12" s="43" t="inlineStr">
-        <is>
-          <t>Sold care se reportează = operațiune neterminată, ascunsă în balanță</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="42" t="inlineStr">
-        <is>
-          <t>Tabelul B — cadențele, din foaia „Închideri periodice”</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="44" t="inlineStr">
-        <is>
-          <t>Lista nu se rescrie aici: e aceeași cu cea din workbook-ul de plan, care o derivă din stările terminale ale fluxurilor (poarta 17).</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="42" t="inlineStr">
-        <is>
-          <t>Tabelul C — LIMITĂRI DECLARATE</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="65" t="inlineStr">
-        <is>
-          <t>Ce NU face modulul</t>
-        </is>
-      </c>
-      <c r="B18" s="65" t="inlineStr">
-        <is>
-          <t>De ce contează</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="43" t="inlineStr">
-        <is>
-          <t>Verifică solduri, nu documente</t>
-        </is>
-      </c>
-      <c r="B19" s="43" t="inlineStr">
-        <is>
-          <t>Nu poate spune dacă statul de plată e corect întocmit — doar dacă balanța se potrivește cu el. Un stat greșit, reflectat fidel în balanță, trece.</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="43" t="inlineStr">
-        <is>
-          <t>Restul de plată se introduce manual</t>
-        </is>
-      </c>
-      <c r="B20" s="43" t="inlineStr">
-        <is>
-          <t>Vine din stat, nu din balanță. Dacă îl copiezi din balanță, corelația devine tautologie și nu mai verifică nimic.</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="43" t="inlineStr">
-        <is>
-          <t>Conturile fără corelație declarată nu apar</t>
-        </is>
-      </c>
-      <c r="B21" s="43" t="inlineStr">
-        <is>
-          <t>455, 461, 462, 5187 au cadență, dar niciun flux nu le declară starea terminală. Golul e declarat în `date/inchideri.py`, nu ascuns aici.</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="43" t="inlineStr">
-        <is>
-          <t>O singură lună odată</t>
-        </is>
-      </c>
-      <c r="B22" s="43" t="inlineStr">
-        <is>
-          <t>Restanța se vede ca diferență sold − rulaj, dar vechimea ei se află doar comparând mai multe luni. Aici se vede CĂ există, nu de când.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet87.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:F29"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="10" customWidth="1" style="40" min="1" max="1"/>
-    <col width="46" customWidth="1" style="40" min="2" max="2"/>
-    <col width="16" customWidth="1" style="40" min="3" max="3"/>
-    <col width="16" customWidth="1" style="40" min="4" max="4"/>
-    <col width="16" customWidth="1" style="40" min="5" max="5"/>
-    <col width="40" customWidth="1" style="40" min="6" max="6"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="41" t="inlineStr">
-        <is>
-          <t>MOD_INCHIDERE_LUNARA — Verificări</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="44" t="inlineStr">
-        <is>
-          <t>O linie pe corelație, calculată din Declarații. Coloana „Diferență” e ce contează: zero înseamnă că se potrivește.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="42" t="inlineStr">
-        <is>
-          <t>V1 — obligații lunare: rulaj creditor = sold creditor</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="65" t="inlineStr">
-        <is>
-          <t>Cod</t>
-        </is>
-      </c>
-      <c r="B5" s="65" t="inlineStr">
-        <is>
-          <t>Ce verifică</t>
-        </is>
-      </c>
-      <c r="C5" s="65" t="inlineStr">
-        <is>
-          <t>Rulaj C</t>
-        </is>
-      </c>
-      <c r="D5" s="65" t="inlineStr">
-        <is>
-          <t>Sold C</t>
-        </is>
-      </c>
-      <c r="E5" s="65" t="inlineStr">
-        <is>
-          <t>Diferență</t>
-        </is>
-      </c>
-      <c r="F5" s="65" t="inlineStr">
-        <is>
-          <t>Verdict</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="43" t="inlineStr">
-        <is>
-          <t>C-25</t>
-        </is>
-      </c>
-      <c r="B6" s="43" t="inlineStr">
-        <is>
-          <t>444 — Impozit pe venituri din salarii</t>
-        </is>
-      </c>
-      <c r="C6" s="43">
-        <f>Declarații_INCHIDERE_LUNARA!D11</f>
-        <v>3250</v>
-      </c>
-      <c r="D6" s="43">
-        <f>Declarații_INCHIDERE_LUNARA!E11</f>
-        <v>3250</v>
-      </c>
-      <c r="E6" s="43">
-        <f>Declarații_INCHIDERE_LUNARA!E11-Declarații_INCHIDERE_LUNARA!D11</f>
-        <v>0</v>
-      </c>
-      <c r="F6" s="43" t="str">
-        <f>IF(ABS(E6)&lt;0.01,"OK","ATENȚIE — sold peste rulaj: restanță de "&amp;TEXT(E6,"#,##0")&amp;" lei")</f>
-        <v>OK</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="43" t="inlineStr">
-        <is>
-          <t>C-26</t>
-        </is>
-      </c>
-      <c r="B7" s="43" t="inlineStr">
-        <is>
-          <t>4315 — CAS — contribuția de asigurări sociale</t>
-        </is>
-      </c>
-      <c r="C7" s="43">
-        <f>Declarații_INCHIDERE_LUNARA!D12</f>
-        <v>12500</v>
-      </c>
-      <c r="D7" s="43">
-        <f>Declarații_INCHIDERE_LUNARA!E12</f>
-        <v>12500</v>
-      </c>
-      <c r="E7" s="43">
-        <f>Declarații_INCHIDERE_LUNARA!E12-Declarații_INCHIDERE_LUNARA!D12</f>
-        <v>0</v>
-      </c>
-      <c r="F7" s="43" t="str">
-        <f>IF(ABS(E7)&lt;0.01,"OK","ATENȚIE — sold peste rulaj: restanță de "&amp;TEXT(E7,"#,##0")&amp;" lei")</f>
-        <v>OK</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="43" t="inlineStr">
-        <is>
-          <t>C-26</t>
-        </is>
-      </c>
-      <c r="B8" s="43" t="inlineStr">
-        <is>
-          <t>4316 — CASS — asigurări sociale de sănătate</t>
-        </is>
-      </c>
-      <c r="C8" s="43">
-        <f>Declarații_INCHIDERE_LUNARA!D13</f>
-        <v>5000</v>
-      </c>
-      <c r="D8" s="43">
-        <f>Declarații_INCHIDERE_LUNARA!E13</f>
-        <v>5000</v>
-      </c>
-      <c r="E8" s="43">
-        <f>Declarații_INCHIDERE_LUNARA!E13-Declarații_INCHIDERE_LUNARA!D13</f>
-        <v>0</v>
-      </c>
-      <c r="F8" s="43" t="str">
-        <f>IF(ABS(E8)&lt;0.01,"OK","ATENȚIE — sold peste rulaj: restanță de "&amp;TEXT(E8,"#,##0")&amp;" lei")</f>
-        <v>OK</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="43" t="inlineStr">
-        <is>
-          <t>C-26</t>
-        </is>
-      </c>
-      <c r="B9" s="43" t="inlineStr">
-        <is>
-          <t>436 — CAM — contribuția asiguratorie pentru muncă</t>
-        </is>
-      </c>
-      <c r="C9" s="43">
-        <f>Declarații_INCHIDERE_LUNARA!D14</f>
-        <v>1125</v>
-      </c>
-      <c r="D9" s="43">
-        <f>Declarații_INCHIDERE_LUNARA!E14</f>
-        <v>1125</v>
-      </c>
-      <c r="E9" s="43">
-        <f>Declarații_INCHIDERE_LUNARA!E14-Declarații_INCHIDERE_LUNARA!D14</f>
-        <v>0</v>
-      </c>
-      <c r="F9" s="43" t="str">
-        <f>IF(ABS(E9)&lt;0.01,"OK","ATENȚIE — sold peste rulaj: restanță de "&amp;TEXT(E9,"#,##0")&amp;" lei")</f>
-        <v>OK</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="43" t="inlineStr">
-        <is>
-          <t>C-28</t>
-        </is>
-      </c>
-      <c r="B10" s="43" t="inlineStr">
-        <is>
-          <t>427 — Rețineri din salarii datorate terților</t>
-        </is>
-      </c>
-      <c r="C10" s="43">
-        <f>Declarații_INCHIDERE_LUNARA!D15</f>
-        <v>0</v>
-      </c>
-      <c r="D10" s="43">
-        <f>Declarații_INCHIDERE_LUNARA!E15</f>
-        <v>0</v>
-      </c>
-      <c r="E10" s="43">
-        <f>Declarații_INCHIDERE_LUNARA!E15-Declarații_INCHIDERE_LUNARA!D15</f>
-        <v>0</v>
-      </c>
-      <c r="F10" s="43" t="str">
-        <f>IF(ABS(E10)&lt;0.01,"OK","ATENȚIE — sold peste rulaj: restanță de "&amp;TEXT(E10,"#,##0")&amp;" lei")</f>
-        <v>OK</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="42" t="inlineStr">
-        <is>
-          <t>V2 — datoria față de salariați</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="65" t="inlineStr">
-        <is>
-          <t>Cod</t>
-        </is>
-      </c>
-      <c r="B13" s="65" t="inlineStr">
-        <is>
-          <t>Ce verifică</t>
-        </is>
-      </c>
-      <c r="C13" s="65" t="inlineStr">
-        <is>
-          <t>Din balanță</t>
-        </is>
-      </c>
-      <c r="D13" s="65" t="inlineStr">
-        <is>
-          <t>Din stat</t>
-        </is>
-      </c>
-      <c r="E13" s="65" t="inlineStr">
-        <is>
-          <t>Diferență</t>
-        </is>
-      </c>
-      <c r="F13" s="65" t="inlineStr">
-        <is>
-          <t>Verdict</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="43" t="inlineStr">
-        <is>
-          <t>C-24</t>
-        </is>
-      </c>
-      <c r="B14" s="43" t="inlineStr">
-        <is>
-          <t>421 + 423 = rest de plată de pe stat</t>
-        </is>
-      </c>
-      <c r="C14" s="43">
-        <f>Declarații_INCHIDERE_LUNARA!B18+Declarații_INCHIDERE_LUNARA!B19</f>
-        <v>29250</v>
-      </c>
-      <c r="D14" s="43">
-        <f>Declarații_INCHIDERE_LUNARA!B20</f>
-        <v>29250</v>
-      </c>
-      <c r="E14" s="43">
-        <f>Declarații_INCHIDERE_LUNARA!B18+Declarații_INCHIDERE_LUNARA!B19-Declarații_INCHIDERE_LUNARA!B20</f>
-        <v>0</v>
-      </c>
-      <c r="F14" s="43" t="str">
-        <f>IF(ABS(E14)&lt;0.01,"OK","ATENȚIE — balanța nu corespunde statului")</f>
-        <v>OK</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="42" t="inlineStr">
-        <is>
-          <t>V3 — conturi de tranzit, care trebuie golite</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="65" t="inlineStr">
-        <is>
-          <t>Cod</t>
-        </is>
-      </c>
-      <c r="B17" s="65" t="inlineStr">
-        <is>
-          <t>Ce verifică</t>
-        </is>
-      </c>
-      <c r="C17" s="65" t="inlineStr">
-        <is>
-          <t>Sold</t>
-        </is>
-      </c>
-      <c r="D17" s="65" t="inlineStr">
-        <is>
-          <t>Așteptat</t>
-        </is>
-      </c>
-      <c r="E17" s="65" t="inlineStr">
-        <is>
-          <t>Diferență</t>
-        </is>
-      </c>
-      <c r="F17" s="65" t="inlineStr">
-        <is>
-          <t>Verdict</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="43" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="B18" s="43" t="inlineStr">
-        <is>
-          <t>473 — Decontări din operațiuni în curs de clarificare</t>
-        </is>
-      </c>
-      <c r="C18" s="43">
-        <f>Declarații_INCHIDERE_LUNARA!C28</f>
-        <v>0</v>
-      </c>
-      <c r="D18" s="43" t="n">
-        <v>0</v>
-      </c>
-      <c r="E18" s="43">
-        <f>Declarații_INCHIDERE_LUNARA!C28</f>
-        <v>0</v>
-      </c>
-      <c r="F18" s="43" t="str">
-        <f>IF(ABS(E18)&lt;0.01,"OK","ATENȚIE — operațiune neterminată, ascunsă în balanță")</f>
-        <v>OK</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="43" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="B19" s="43" t="inlineStr">
-        <is>
-          <t>581 — Viramente interne</t>
-        </is>
-      </c>
-      <c r="C19" s="43">
-        <f>Declarații_INCHIDERE_LUNARA!C29</f>
-        <v>0</v>
-      </c>
-      <c r="D19" s="43" t="n">
-        <v>0</v>
-      </c>
-      <c r="E19" s="43">
-        <f>Declarații_INCHIDERE_LUNARA!C29</f>
-        <v>0</v>
-      </c>
-      <c r="F19" s="43" t="str">
-        <f>IF(ABS(E19)&lt;0.01,"OK","ATENȚIE — operațiune neterminată, ascunsă în balanță")</f>
-        <v>OK</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="43" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="B20" s="43" t="inlineStr">
-        <is>
-          <t>542 — Avansuri de trezorerie</t>
-        </is>
-      </c>
-      <c r="C20" s="43">
-        <f>Declarații_INCHIDERE_LUNARA!C30</f>
-        <v>0</v>
-      </c>
-      <c r="D20" s="43" t="n">
-        <v>0</v>
-      </c>
-      <c r="E20" s="43">
-        <f>Declarații_INCHIDERE_LUNARA!C30</f>
-        <v>0</v>
-      </c>
-      <c r="F20" s="43" t="str">
-        <f>IF(ABS(E20)&lt;0.01,"OK","ATENȚIE — operațiune neterminată, ascunsă în balanță")</f>
-        <v>OK</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="43" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="B21" s="43" t="inlineStr">
-        <is>
-          <t>4382 — Alte creanțe sociale (de recuperat de la FNUASS)</t>
-        </is>
-      </c>
-      <c r="C21" s="43">
-        <f>Declarații_INCHIDERE_LUNARA!C31</f>
-        <v>0</v>
-      </c>
-      <c r="D21" s="43" t="n">
-        <v>0</v>
-      </c>
-      <c r="E21" s="43">
-        <f>Declarații_INCHIDERE_LUNARA!C31</f>
-        <v>0</v>
-      </c>
-      <c r="F21" s="43" t="str">
-        <f>IF(ABS(E21)&lt;0.01,"OK","ATENȚIE — operațiune neterminată, ascunsă în balanță")</f>
-        <v>OK</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="42" t="inlineStr">
-        <is>
-          <t>V4 — CAM pe cifre și TVA</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="65" t="inlineStr">
-        <is>
-          <t>Cod</t>
-        </is>
-      </c>
-      <c r="B24" s="65" t="inlineStr">
-        <is>
-          <t>Ce verifică</t>
-        </is>
-      </c>
-      <c r="C24" s="65" t="inlineStr">
-        <is>
-          <t>Calculat</t>
-        </is>
-      </c>
-      <c r="D24" s="65" t="inlineStr">
-        <is>
-          <t>Din balanță</t>
-        </is>
-      </c>
-      <c r="E24" s="65" t="inlineStr">
-        <is>
-          <t>Diferență</t>
-        </is>
-      </c>
-      <c r="F24" s="65" t="inlineStr">
-        <is>
-          <t>Verdict</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="43" t="inlineStr">
-        <is>
-          <t>C-27</t>
-        </is>
-      </c>
-      <c r="B25" s="43" t="inlineStr">
-        <is>
-          <t>cota CAM × brut = rulaj C 436</t>
-        </is>
-      </c>
-      <c r="C25" s="43">
-        <f>ROUND(Declarații_INCHIDERE_LUNARA!B23*param_cota_cam,2)</f>
-        <v>1125</v>
-      </c>
-      <c r="D25" s="43">
-        <f>Declarații_INCHIDERE_LUNARA!D14</f>
-        <v>1125</v>
-      </c>
-      <c r="E25" s="43">
-        <f>Declarații_INCHIDERE_LUNARA!D14-ROUND(Declarații_INCHIDERE_LUNARA!B23*param_cota_cam,2)</f>
-        <v>0</v>
-      </c>
-      <c r="F25" s="43" t="str">
-        <f>IF(ABS(E25)&lt;0.01,"OK","ATENȚIE — bază de calcul greșită sau concedii medicale (vezi Reguli A)")</f>
-        <v>OK</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="43" t="inlineStr">
-        <is>
-          <t>C-29</t>
-        </is>
-      </c>
-      <c r="B26" s="43" t="inlineStr">
-        <is>
-          <t>sold 4423 din balanță = sold din decont</t>
-        </is>
-      </c>
-      <c r="C26" s="43">
-        <f>Declarații_INCHIDERE_LUNARA!B34</f>
-        <v>5250</v>
-      </c>
-      <c r="D26" s="43">
-        <f>Declarații_INCHIDERE_LUNARA!B35</f>
-        <v>5250</v>
-      </c>
-      <c r="E26" s="43">
-        <f>Declarații_INCHIDERE_LUNARA!B34-Declarații_INCHIDERE_LUNARA!B35</f>
-        <v>0</v>
-      </c>
-      <c r="F26" s="43" t="str">
-        <f>IF(ABS(E26)&lt;0.01,"OK","ATENȚIE — decontul și balanța nu spun același lucru")</f>
-        <v>OK</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="42" t="inlineStr">
-        <is>
-          <t>Control final</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="43" t="inlineStr">
-        <is>
-          <t>Check — toate corelațiile lunii</t>
-        </is>
-      </c>
-      <c r="B29" s="43">
-        <f>ABS(E6)+ABS(E7)+ABS(E8)+ABS(E9)+ABS(E10)+ABS(E14)+ABS(E18)+ABS(E19)+ABS(E20)+ABS(E21)+ABS(E25)+ABS(E26)</f>
-        <v>0</v>
-      </c>
-      <c r="C29" s="43" t="str">
-        <f>IF(ABS(B29)&lt;0.01,"OK — luna se reconciliază pe toate corelațiile","EROARE — vezi foaia Abateri")</f>
-        <v>OK — luna se reconciliază pe toate corelațiile</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet88.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:E18"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="10" customWidth="1" style="40" min="1" max="1"/>
-    <col width="12" customWidth="1" style="40" min="2" max="2"/>
-    <col width="46" customWidth="1" style="40" min="3" max="3"/>
-    <col width="16" customWidth="1" style="40" min="4" max="4"/>
-    <col width="56" customWidth="1" style="40" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="41" t="inlineStr">
-        <is>
-          <t>MOD_INCHIDERE_LUNARA — Abateri</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="44" t="inlineStr">
-        <is>
-          <t>Coloana „Include” spune DA doar unde corelația nu s-a potrivit. Lista e completă: dacă toate sunt NU, luna e curată.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="65" t="inlineStr">
-        <is>
-          <t>Include</t>
-        </is>
-      </c>
-      <c r="B4" s="65" t="inlineStr">
-        <is>
-          <t>Cod</t>
-        </is>
-      </c>
-      <c r="C4" s="65" t="inlineStr">
-        <is>
-          <t>Ce nu s-a potrivit</t>
-        </is>
-      </c>
-      <c r="D4" s="65" t="inlineStr">
-        <is>
-          <t>Diferență</t>
-        </is>
-      </c>
-      <c r="E4" s="65" t="inlineStr">
-        <is>
-          <t>Ce se face</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="43" t="str">
-        <f>IF(ABS(Verificări_INCHIDERE_LUNARA!E6)&lt;0.01,"NU","DA")</f>
-        <v>NU</v>
-      </c>
-      <c r="B5" s="43" t="inlineStr">
-        <is>
-          <t>C-25</t>
-        </is>
-      </c>
-      <c r="C5" s="43" t="inlineStr">
-        <is>
-          <t>444 Impozit pe venituri din salarii</t>
-        </is>
-      </c>
-      <c r="D5" s="43">
-        <f>Verificări_INCHIDERE_LUNARA!E6</f>
-        <v>0</v>
-      </c>
-      <c r="E5" s="43" t="inlineStr">
-        <is>
-          <t>Se verifică fișa de plătitor din SPV. Stopaj nevirat peste 30 de zile = răspundere penală, nu întârziere.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="43" t="str">
-        <f>IF(ABS(Verificări_INCHIDERE_LUNARA!E7)&lt;0.01,"NU","DA")</f>
-        <v>NU</v>
-      </c>
-      <c r="B6" s="43" t="inlineStr">
-        <is>
-          <t>C-26</t>
-        </is>
-      </c>
-      <c r="C6" s="43" t="inlineStr">
-        <is>
-          <t>4315 CAS — contribuția de asigurări sociale</t>
-        </is>
-      </c>
-      <c r="D6" s="43">
-        <f>Verificări_INCHIDERE_LUNARA!E7</f>
-        <v>0</v>
-      </c>
-      <c r="E6" s="43" t="inlineStr">
-        <is>
-          <t>Se confruntă cu D112. Dacă e eșalonare, se notează; altfel e restanță.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="43" t="str">
-        <f>IF(ABS(Verificări_INCHIDERE_LUNARA!E8)&lt;0.01,"NU","DA")</f>
-        <v>NU</v>
-      </c>
-      <c r="B7" s="43" t="inlineStr">
-        <is>
-          <t>C-26</t>
-        </is>
-      </c>
-      <c r="C7" s="43" t="inlineStr">
-        <is>
-          <t>4316 CASS — asigurări sociale de sănătate</t>
-        </is>
-      </c>
-      <c r="D7" s="43">
-        <f>Verificări_INCHIDERE_LUNARA!E8</f>
-        <v>0</v>
-      </c>
-      <c r="E7" s="43" t="inlineStr">
-        <is>
-          <t>Se confruntă cu D112. Dacă e eșalonare, se notează; altfel e restanță.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="43" t="str">
-        <f>IF(ABS(Verificări_INCHIDERE_LUNARA!E9)&lt;0.01,"NU","DA")</f>
-        <v>NU</v>
-      </c>
-      <c r="B8" s="43" t="inlineStr">
-        <is>
-          <t>C-26</t>
-        </is>
-      </c>
-      <c r="C8" s="43" t="inlineStr">
-        <is>
-          <t>436 CAM — contribuția asiguratorie pentru muncă</t>
-        </is>
-      </c>
-      <c r="D8" s="43">
-        <f>Verificări_INCHIDERE_LUNARA!E9</f>
-        <v>0</v>
-      </c>
-      <c r="E8" s="43" t="inlineStr">
-        <is>
-          <t>Se confruntă cu D112. Dacă e eșalonare, se notează; altfel e restanță.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="43" t="str">
-        <f>IF(ABS(Verificări_INCHIDERE_LUNARA!E10)&lt;0.01,"NU","DA")</f>
-        <v>NU</v>
-      </c>
-      <c r="B9" s="43" t="inlineStr">
-        <is>
-          <t>C-28</t>
-        </is>
-      </c>
-      <c r="C9" s="43" t="inlineStr">
-        <is>
-          <t>427 Rețineri din salarii datorate terților</t>
-        </is>
-      </c>
-      <c r="D9" s="43">
-        <f>Verificări_INCHIDERE_LUNARA!E10</f>
-        <v>0</v>
-      </c>
-      <c r="E9" s="43" t="inlineStr">
-        <is>
-          <t>Se virează imediat. Banii sunt ai salariatului, opriți pentru altcineva.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="43" t="str">
-        <f>IF(ABS(Verificări_INCHIDERE_LUNARA!E14)&lt;0.01,"NU","DA")</f>
-        <v>NU</v>
-      </c>
-      <c r="B10" s="43" t="inlineStr">
-        <is>
-          <t>C-24</t>
-        </is>
-      </c>
-      <c r="C10" s="43" t="inlineStr">
-        <is>
-          <t>421 + 423 vs. stat</t>
-        </is>
-      </c>
-      <c r="D10" s="43">
-        <f>Verificări_INCHIDERE_LUNARA!E14</f>
-        <v>0</v>
-      </c>
-      <c r="E10" s="43" t="inlineStr">
-        <is>
-          <t>Se scot statele lună de lună și se caută luna în care s-a rupt. Cauza tipică: plată pe alt cont decât 421.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="43" t="str">
-        <f>IF(ABS(Verificări_INCHIDERE_LUNARA!E18)&lt;0.01,"NU","DA")</f>
-        <v>NU</v>
-      </c>
-      <c r="B11" s="43" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C11" s="43" t="inlineStr">
-        <is>
-          <t>473 sold zero</t>
-        </is>
-      </c>
-      <c r="D11" s="43">
-        <f>Verificări_INCHIDERE_LUNARA!E18</f>
-        <v>0</v>
-      </c>
-      <c r="E11" s="43" t="inlineStr">
-        <is>
-          <t>Se identifică operațiunea neterminată și se închide. Un sold reportat pe un cont de tranzit ascunde ceva.</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="43" t="str">
-        <f>IF(ABS(Verificări_INCHIDERE_LUNARA!E19)&lt;0.01,"NU","DA")</f>
-        <v>NU</v>
-      </c>
-      <c r="B12" s="43" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C12" s="43" t="inlineStr">
-        <is>
-          <t>581 sold zero</t>
-        </is>
-      </c>
-      <c r="D12" s="43">
-        <f>Verificări_INCHIDERE_LUNARA!E19</f>
-        <v>0</v>
-      </c>
-      <c r="E12" s="43" t="inlineStr">
-        <is>
-          <t>Se identifică operațiunea neterminată și se închide. Un sold reportat pe un cont de tranzit ascunde ceva.</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="43" t="str">
-        <f>IF(ABS(Verificări_INCHIDERE_LUNARA!E20)&lt;0.01,"NU","DA")</f>
-        <v>NU</v>
-      </c>
-      <c r="B13" s="43" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C13" s="43" t="inlineStr">
-        <is>
-          <t>542 sold zero</t>
-        </is>
-      </c>
-      <c r="D13" s="43">
-        <f>Verificări_INCHIDERE_LUNARA!E20</f>
-        <v>0</v>
-      </c>
-      <c r="E13" s="43" t="inlineStr">
-        <is>
-          <t>Se identifică operațiunea neterminată și se închide. Un sold reportat pe un cont de tranzit ascunde ceva.</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="43" t="str">
-        <f>IF(ABS(Verificări_INCHIDERE_LUNARA!E21)&lt;0.01,"NU","DA")</f>
-        <v>NU</v>
-      </c>
-      <c r="B14" s="43" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C14" s="43" t="inlineStr">
-        <is>
-          <t>4382 sold zero</t>
-        </is>
-      </c>
-      <c r="D14" s="43">
-        <f>Verificări_INCHIDERE_LUNARA!E21</f>
-        <v>0</v>
-      </c>
-      <c r="E14" s="43" t="inlineStr">
-        <is>
-          <t>Se identifică operațiunea neterminată și se închide. Un sold reportat pe un cont de tranzit ascunde ceva.</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="43" t="str">
-        <f>IF(ABS(Verificări_INCHIDERE_LUNARA!E25)&lt;0.01,"NU","DA")</f>
-        <v>NU</v>
-      </c>
-      <c r="B15" s="43" t="inlineStr">
-        <is>
-          <t>C-27</t>
-        </is>
-      </c>
-      <c r="C15" s="43" t="inlineStr">
-        <is>
-          <t>CAM pe cifre</t>
-        </is>
-      </c>
-      <c r="D15" s="43">
-        <f>Verificări_INCHIDERE_LUNARA!E25</f>
-        <v>0</v>
-      </c>
-      <c r="E15" s="43" t="inlineStr">
-        <is>
-          <t>Se verifică dacă luna are concedii medicale — CAM nu se datorează pe partea din FNUASS. Altfel, bază de calcul incompletă.</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="43" t="str">
-        <f>IF(ABS(Verificări_INCHIDERE_LUNARA!E26)&lt;0.01,"NU","DA")</f>
-        <v>NU</v>
-      </c>
-      <c r="B16" s="43" t="inlineStr">
-        <is>
-          <t>C-29</t>
-        </is>
-      </c>
-      <c r="C16" s="43" t="inlineStr">
-        <is>
-          <t>4423 vs. decont</t>
-        </is>
-      </c>
-      <c r="D16" s="43">
-        <f>Verificări_INCHIDERE_LUNARA!E26</f>
-        <v>0</v>
-      </c>
-      <c r="E16" s="43" t="inlineStr">
-        <is>
-          <t>Se verifică dacă e sumă din decizie de impunere (analitic distinct) sau TVA neachitat din perioade precedente, omis din decont.</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="43" t="inlineStr">
-        <is>
-          <t>Check — număr de abateri</t>
-        </is>
-      </c>
-      <c r="B18" s="43">
-        <f>COUNTIF(A5:A16,"DA")</f>
-        <v>0</v>
-      </c>
-      <c r="C18" s="43" t="str">
-        <f>IF(B18=0,"OK — nicio abatere","ATENȚIE — "&amp;B18&amp;" corelații nu se potrivesc")</f>
-        <v>OK — nicio abatere</v>
       </c>
     </row>
   </sheetData>
@@ -39381,4 +40465,1225 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet90.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D22"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" style="40" min="1" max="1"/>
+    <col width="52" customWidth="1" style="40" min="2" max="2"/>
+    <col width="52" customWidth="1" style="40" min="3" max="3"/>
+    <col width="52" customWidth="1" style="40" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="41" t="inlineStr">
+        <is>
+          <t>MOD_INCHIDERE_LUNARA — Reguli</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="44" t="inlineStr">
+        <is>
+          <t>Tabele fixe. Se editează doar când se schimbă legea sau când o corelație nouă intră în workbook-ul de plan.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="42" t="inlineStr">
+        <is>
+          <t>Tabelul A — corelațiile verificate și ce le rupe</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="65" t="inlineStr">
+        <is>
+          <t>Cod</t>
+        </is>
+      </c>
+      <c r="B5" s="65" t="inlineStr">
+        <is>
+          <t>Corelația</t>
+        </is>
+      </c>
+      <c r="C5" s="65" t="inlineStr">
+        <is>
+          <t>Ce o rupe LEGITIM</t>
+        </is>
+      </c>
+      <c r="D5" s="65" t="inlineStr">
+        <is>
+          <t>Ce o rupe SUSPECT</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="43" t="inlineStr">
+        <is>
+          <t>C-24</t>
+        </is>
+      </c>
+      <c r="B6" s="43" t="inlineStr">
+        <is>
+          <t>sold C 421 + sold C 423 = rest de plată din stat</t>
+        </is>
+      </c>
+      <c r="C6" s="43" t="inlineStr">
+        <is>
+          <t>Avans pe 425, nescăzut încă · drepturi neridicate mutate pe 426</t>
+        </is>
+      </c>
+      <c r="D6" s="43" t="inlineStr">
+        <is>
+          <t>Plată înregistrată pe alt cont decât 421 · salarii restante nereclasificate</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="43" t="inlineStr">
+        <is>
+          <t>C-25</t>
+        </is>
+      </c>
+      <c r="B7" s="43" t="inlineStr">
+        <is>
+          <t>rulaj C 444 = sold C 444</t>
+        </is>
+      </c>
+      <c r="C7" s="43" t="inlineStr">
+        <is>
+          <t>Rectificativă pe o lună anterioară · plată în avans</t>
+        </is>
+      </c>
+      <c r="D7" s="43" t="inlineStr">
+        <is>
+          <t>Sold &gt; rulaj constant = stopaj la sursă nevirat. Peste 30 de zile, penal</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="43" t="inlineStr">
+        <is>
+          <t>C-26</t>
+        </is>
+      </c>
+      <c r="B8" s="43" t="inlineStr">
+        <is>
+          <t>rulaj C 4315/4316/436 = soldurile lor</t>
+        </is>
+      </c>
+      <c r="C8" s="43" t="inlineStr">
+        <is>
+          <t>Rectificativă · eșalonare la plată aprobată de ANAF</t>
+        </is>
+      </c>
+      <c r="D8" s="43" t="inlineStr">
+        <is>
+          <t>Contribuții restante · bază de calcul care nu corespunde brutului</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="43" t="inlineStr">
+        <is>
+          <t>C-27</t>
+        </is>
+      </c>
+      <c r="B9" s="43" t="inlineStr">
+        <is>
+          <t>cota CAM × rulaj C 421 = rulaj C 436</t>
+        </is>
+      </c>
+      <c r="C9" s="43" t="inlineStr">
+        <is>
+          <t>Luni cu concedii medicale: CAM nu se datorează pe partea din FNUASS (art. 220^5) · categorii cu cotă redusă</t>
+        </is>
+      </c>
+      <c r="D9" s="43" t="inlineStr">
+        <is>
+          <t>Sporuri sau prime omise din fondul de salarii · CAM înregistrat invers</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="43" t="inlineStr">
+        <is>
+          <t>C-28</t>
+        </is>
+      </c>
+      <c r="B10" s="43" t="inlineStr">
+        <is>
+          <t>rulaj C 427 = sold C 427</t>
+        </is>
+      </c>
+      <c r="C10" s="43" t="inlineStr">
+        <is>
+          <t>Poprire înființată la final de lună, cu virare în luna următoare</t>
+        </is>
+      </c>
+      <c r="D10" s="43" t="inlineStr">
+        <is>
+          <t>Sold care persistă = bani opriți din salariul altcuiva și nevirați</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="43" t="inlineStr">
+        <is>
+          <t>C-29</t>
+        </is>
+      </c>
+      <c r="B11" s="43" t="inlineStr">
+        <is>
+          <t>sold 4423 din balanță = sold din decontul de TVA</t>
+        </is>
+      </c>
+      <c r="C11" s="43" t="inlineStr">
+        <is>
+          <t>Sume din decizii de impunere, pe analitic distinct (F-421)</t>
+        </is>
+      </c>
+      <c r="D11" s="43" t="inlineStr">
+        <is>
+          <t>TVA neachitat din perioade precedente, omis din decont</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="43" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="B12" s="43" t="inlineStr">
+        <is>
+          <t>sold 473, 581, 542, 4382 = 0</t>
+        </is>
+      </c>
+      <c r="C12" s="43" t="inlineStr">
+        <is>
+          <t>Operațiune de final de lună, închisă în primele zile ale lunii următoare</t>
+        </is>
+      </c>
+      <c r="D12" s="43" t="inlineStr">
+        <is>
+          <t>Sold care se reportează = operațiune neterminată, ascunsă în balanță</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="42" t="inlineStr">
+        <is>
+          <t>Tabelul B — cadențele, din foaia „Închideri periodice”</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="44" t="inlineStr">
+        <is>
+          <t>Lista nu se rescrie aici: e aceeași cu cea din workbook-ul de plan, care o derivă din stările terminale ale fluxurilor (poarta 17).</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="42" t="inlineStr">
+        <is>
+          <t>Tabelul C — LIMITĂRI DECLARATE</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="65" t="inlineStr">
+        <is>
+          <t>Ce NU face modulul</t>
+        </is>
+      </c>
+      <c r="B18" s="65" t="inlineStr">
+        <is>
+          <t>De ce contează</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="43" t="inlineStr">
+        <is>
+          <t>Verifică solduri, nu documente</t>
+        </is>
+      </c>
+      <c r="B19" s="43" t="inlineStr">
+        <is>
+          <t>Nu poate spune dacă statul de plată e corect întocmit — doar dacă balanța se potrivește cu el. Un stat greșit, reflectat fidel în balanță, trece.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="43" t="inlineStr">
+        <is>
+          <t>Restul de plată se introduce manual</t>
+        </is>
+      </c>
+      <c r="B20" s="43" t="inlineStr">
+        <is>
+          <t>Vine din stat, nu din balanță. Dacă îl copiezi din balanță, corelația devine tautologie și nu mai verifică nimic.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="43" t="inlineStr">
+        <is>
+          <t>Conturile fără corelație declarată nu apar</t>
+        </is>
+      </c>
+      <c r="B21" s="43" t="inlineStr">
+        <is>
+          <t>455, 461, 462, 5187 au cadență, dar niciun flux nu le declară starea terminală. Golul e declarat în `date/inchideri.py`, nu ascuns aici.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="43" t="inlineStr">
+        <is>
+          <t>O singură lună odată</t>
+        </is>
+      </c>
+      <c r="B22" s="43" t="inlineStr">
+        <is>
+          <t>Restanța se vede ca diferență sold − rulaj, dar vechimea ei se află doar comparând mai multe luni. Aici se vede CĂ există, nu de când.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet91.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F29"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" style="40" min="1" max="1"/>
+    <col width="46" customWidth="1" style="40" min="2" max="2"/>
+    <col width="16" customWidth="1" style="40" min="3" max="3"/>
+    <col width="16" customWidth="1" style="40" min="4" max="4"/>
+    <col width="16" customWidth="1" style="40" min="5" max="5"/>
+    <col width="40" customWidth="1" style="40" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="41" t="inlineStr">
+        <is>
+          <t>MOD_INCHIDERE_LUNARA — Verificări</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="44" t="inlineStr">
+        <is>
+          <t>O linie pe corelație, calculată din Declarații. Coloana „Diferență” e ce contează: zero înseamnă că se potrivește.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="42" t="inlineStr">
+        <is>
+          <t>V1 — obligații lunare: rulaj creditor = sold creditor</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="65" t="inlineStr">
+        <is>
+          <t>Cod</t>
+        </is>
+      </c>
+      <c r="B5" s="65" t="inlineStr">
+        <is>
+          <t>Ce verifică</t>
+        </is>
+      </c>
+      <c r="C5" s="65" t="inlineStr">
+        <is>
+          <t>Rulaj C</t>
+        </is>
+      </c>
+      <c r="D5" s="65" t="inlineStr">
+        <is>
+          <t>Sold C</t>
+        </is>
+      </c>
+      <c r="E5" s="65" t="inlineStr">
+        <is>
+          <t>Diferență</t>
+        </is>
+      </c>
+      <c r="F5" s="65" t="inlineStr">
+        <is>
+          <t>Verdict</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="43" t="inlineStr">
+        <is>
+          <t>C-25</t>
+        </is>
+      </c>
+      <c r="B6" s="43" t="inlineStr">
+        <is>
+          <t>444 — Impozit pe venituri din salarii</t>
+        </is>
+      </c>
+      <c r="C6" s="43">
+        <f>Declarații_INCHIDERE_LUNARA!D11</f>
+        <v>3250</v>
+      </c>
+      <c r="D6" s="43">
+        <f>Declarații_INCHIDERE_LUNARA!E11</f>
+        <v>3250</v>
+      </c>
+      <c r="E6" s="43">
+        <f>Declarații_INCHIDERE_LUNARA!E11-Declarații_INCHIDERE_LUNARA!D11</f>
+        <v>0</v>
+      </c>
+      <c r="F6" s="43" t="str">
+        <f>IF(ABS(E6)&lt;0.01,"OK","ATENȚIE — sold peste rulaj: restanță de "&amp;TEXT(E6,"#,##0")&amp;" lei")</f>
+        <v>OK</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="43" t="inlineStr">
+        <is>
+          <t>C-26</t>
+        </is>
+      </c>
+      <c r="B7" s="43" t="inlineStr">
+        <is>
+          <t>4315 — CAS — contribuția de asigurări sociale</t>
+        </is>
+      </c>
+      <c r="C7" s="43">
+        <f>Declarații_INCHIDERE_LUNARA!D12</f>
+        <v>12500</v>
+      </c>
+      <c r="D7" s="43">
+        <f>Declarații_INCHIDERE_LUNARA!E12</f>
+        <v>12500</v>
+      </c>
+      <c r="E7" s="43">
+        <f>Declarații_INCHIDERE_LUNARA!E12-Declarații_INCHIDERE_LUNARA!D12</f>
+        <v>0</v>
+      </c>
+      <c r="F7" s="43" t="str">
+        <f>IF(ABS(E7)&lt;0.01,"OK","ATENȚIE — sold peste rulaj: restanță de "&amp;TEXT(E7,"#,##0")&amp;" lei")</f>
+        <v>OK</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="43" t="inlineStr">
+        <is>
+          <t>C-26</t>
+        </is>
+      </c>
+      <c r="B8" s="43" t="inlineStr">
+        <is>
+          <t>4316 — CASS — asigurări sociale de sănătate</t>
+        </is>
+      </c>
+      <c r="C8" s="43">
+        <f>Declarații_INCHIDERE_LUNARA!D13</f>
+        <v>5000</v>
+      </c>
+      <c r="D8" s="43">
+        <f>Declarații_INCHIDERE_LUNARA!E13</f>
+        <v>5000</v>
+      </c>
+      <c r="E8" s="43">
+        <f>Declarații_INCHIDERE_LUNARA!E13-Declarații_INCHIDERE_LUNARA!D13</f>
+        <v>0</v>
+      </c>
+      <c r="F8" s="43" t="str">
+        <f>IF(ABS(E8)&lt;0.01,"OK","ATENȚIE — sold peste rulaj: restanță de "&amp;TEXT(E8,"#,##0")&amp;" lei")</f>
+        <v>OK</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="43" t="inlineStr">
+        <is>
+          <t>C-26</t>
+        </is>
+      </c>
+      <c r="B9" s="43" t="inlineStr">
+        <is>
+          <t>436 — CAM — contribuția asiguratorie pentru muncă</t>
+        </is>
+      </c>
+      <c r="C9" s="43">
+        <f>Declarații_INCHIDERE_LUNARA!D14</f>
+        <v>1125</v>
+      </c>
+      <c r="D9" s="43">
+        <f>Declarații_INCHIDERE_LUNARA!E14</f>
+        <v>1125</v>
+      </c>
+      <c r="E9" s="43">
+        <f>Declarații_INCHIDERE_LUNARA!E14-Declarații_INCHIDERE_LUNARA!D14</f>
+        <v>0</v>
+      </c>
+      <c r="F9" s="43" t="str">
+        <f>IF(ABS(E9)&lt;0.01,"OK","ATENȚIE — sold peste rulaj: restanță de "&amp;TEXT(E9,"#,##0")&amp;" lei")</f>
+        <v>OK</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="43" t="inlineStr">
+        <is>
+          <t>C-28</t>
+        </is>
+      </c>
+      <c r="B10" s="43" t="inlineStr">
+        <is>
+          <t>427 — Rețineri din salarii datorate terților</t>
+        </is>
+      </c>
+      <c r="C10" s="43">
+        <f>Declarații_INCHIDERE_LUNARA!D15</f>
+        <v>0</v>
+      </c>
+      <c r="D10" s="43">
+        <f>Declarații_INCHIDERE_LUNARA!E15</f>
+        <v>0</v>
+      </c>
+      <c r="E10" s="43">
+        <f>Declarații_INCHIDERE_LUNARA!E15-Declarații_INCHIDERE_LUNARA!D15</f>
+        <v>0</v>
+      </c>
+      <c r="F10" s="43" t="str">
+        <f>IF(ABS(E10)&lt;0.01,"OK","ATENȚIE — sold peste rulaj: restanță de "&amp;TEXT(E10,"#,##0")&amp;" lei")</f>
+        <v>OK</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="42" t="inlineStr">
+        <is>
+          <t>V2 — datoria față de salariați</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="65" t="inlineStr">
+        <is>
+          <t>Cod</t>
+        </is>
+      </c>
+      <c r="B13" s="65" t="inlineStr">
+        <is>
+          <t>Ce verifică</t>
+        </is>
+      </c>
+      <c r="C13" s="65" t="inlineStr">
+        <is>
+          <t>Din balanță</t>
+        </is>
+      </c>
+      <c r="D13" s="65" t="inlineStr">
+        <is>
+          <t>Din stat</t>
+        </is>
+      </c>
+      <c r="E13" s="65" t="inlineStr">
+        <is>
+          <t>Diferență</t>
+        </is>
+      </c>
+      <c r="F13" s="65" t="inlineStr">
+        <is>
+          <t>Verdict</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="43" t="inlineStr">
+        <is>
+          <t>C-24</t>
+        </is>
+      </c>
+      <c r="B14" s="43" t="inlineStr">
+        <is>
+          <t>421 + 423 = rest de plată de pe stat</t>
+        </is>
+      </c>
+      <c r="C14" s="43">
+        <f>Declarații_INCHIDERE_LUNARA!B18+Declarații_INCHIDERE_LUNARA!B19</f>
+        <v>29250</v>
+      </c>
+      <c r="D14" s="43">
+        <f>Declarații_INCHIDERE_LUNARA!B20</f>
+        <v>29250</v>
+      </c>
+      <c r="E14" s="43">
+        <f>Declarații_INCHIDERE_LUNARA!B18+Declarații_INCHIDERE_LUNARA!B19-Declarații_INCHIDERE_LUNARA!B20</f>
+        <v>0</v>
+      </c>
+      <c r="F14" s="43" t="str">
+        <f>IF(ABS(E14)&lt;0.01,"OK","ATENȚIE — balanța nu corespunde statului")</f>
+        <v>OK</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="42" t="inlineStr">
+        <is>
+          <t>V3 — conturi de tranzit, care trebuie golite</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="65" t="inlineStr">
+        <is>
+          <t>Cod</t>
+        </is>
+      </c>
+      <c r="B17" s="65" t="inlineStr">
+        <is>
+          <t>Ce verifică</t>
+        </is>
+      </c>
+      <c r="C17" s="65" t="inlineStr">
+        <is>
+          <t>Sold</t>
+        </is>
+      </c>
+      <c r="D17" s="65" t="inlineStr">
+        <is>
+          <t>Așteptat</t>
+        </is>
+      </c>
+      <c r="E17" s="65" t="inlineStr">
+        <is>
+          <t>Diferență</t>
+        </is>
+      </c>
+      <c r="F17" s="65" t="inlineStr">
+        <is>
+          <t>Verdict</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="43" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="B18" s="43" t="inlineStr">
+        <is>
+          <t>473 — Decontări din operațiuni în curs de clarificare</t>
+        </is>
+      </c>
+      <c r="C18" s="43">
+        <f>Declarații_INCHIDERE_LUNARA!C28</f>
+        <v>0</v>
+      </c>
+      <c r="D18" s="43" t="n">
+        <v>0</v>
+      </c>
+      <c r="E18" s="43">
+        <f>Declarații_INCHIDERE_LUNARA!C28</f>
+        <v>0</v>
+      </c>
+      <c r="F18" s="43" t="str">
+        <f>IF(ABS(E18)&lt;0.01,"OK","ATENȚIE — operațiune neterminată, ascunsă în balanță")</f>
+        <v>OK</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="43" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="B19" s="43" t="inlineStr">
+        <is>
+          <t>581 — Viramente interne</t>
+        </is>
+      </c>
+      <c r="C19" s="43">
+        <f>Declarații_INCHIDERE_LUNARA!C29</f>
+        <v>0</v>
+      </c>
+      <c r="D19" s="43" t="n">
+        <v>0</v>
+      </c>
+      <c r="E19" s="43">
+        <f>Declarații_INCHIDERE_LUNARA!C29</f>
+        <v>0</v>
+      </c>
+      <c r="F19" s="43" t="str">
+        <f>IF(ABS(E19)&lt;0.01,"OK","ATENȚIE — operațiune neterminată, ascunsă în balanță")</f>
+        <v>OK</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="43" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="B20" s="43" t="inlineStr">
+        <is>
+          <t>542 — Avansuri de trezorerie</t>
+        </is>
+      </c>
+      <c r="C20" s="43">
+        <f>Declarații_INCHIDERE_LUNARA!C30</f>
+        <v>0</v>
+      </c>
+      <c r="D20" s="43" t="n">
+        <v>0</v>
+      </c>
+      <c r="E20" s="43">
+        <f>Declarații_INCHIDERE_LUNARA!C30</f>
+        <v>0</v>
+      </c>
+      <c r="F20" s="43" t="str">
+        <f>IF(ABS(E20)&lt;0.01,"OK","ATENȚIE — operațiune neterminată, ascunsă în balanță")</f>
+        <v>OK</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="43" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="B21" s="43" t="inlineStr">
+        <is>
+          <t>4382 — Alte creanțe sociale (de recuperat de la FNUASS)</t>
+        </is>
+      </c>
+      <c r="C21" s="43">
+        <f>Declarații_INCHIDERE_LUNARA!C31</f>
+        <v>0</v>
+      </c>
+      <c r="D21" s="43" t="n">
+        <v>0</v>
+      </c>
+      <c r="E21" s="43">
+        <f>Declarații_INCHIDERE_LUNARA!C31</f>
+        <v>0</v>
+      </c>
+      <c r="F21" s="43" t="str">
+        <f>IF(ABS(E21)&lt;0.01,"OK","ATENȚIE — operațiune neterminată, ascunsă în balanță")</f>
+        <v>OK</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="42" t="inlineStr">
+        <is>
+          <t>V4 — CAM pe cifre și TVA</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="65" t="inlineStr">
+        <is>
+          <t>Cod</t>
+        </is>
+      </c>
+      <c r="B24" s="65" t="inlineStr">
+        <is>
+          <t>Ce verifică</t>
+        </is>
+      </c>
+      <c r="C24" s="65" t="inlineStr">
+        <is>
+          <t>Calculat</t>
+        </is>
+      </c>
+      <c r="D24" s="65" t="inlineStr">
+        <is>
+          <t>Din balanță</t>
+        </is>
+      </c>
+      <c r="E24" s="65" t="inlineStr">
+        <is>
+          <t>Diferență</t>
+        </is>
+      </c>
+      <c r="F24" s="65" t="inlineStr">
+        <is>
+          <t>Verdict</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="43" t="inlineStr">
+        <is>
+          <t>C-27</t>
+        </is>
+      </c>
+      <c r="B25" s="43" t="inlineStr">
+        <is>
+          <t>cota CAM × brut = rulaj C 436</t>
+        </is>
+      </c>
+      <c r="C25" s="43">
+        <f>ROUND(Declarații_INCHIDERE_LUNARA!B23*param_cota_cam,2)</f>
+        <v>1125</v>
+      </c>
+      <c r="D25" s="43">
+        <f>Declarații_INCHIDERE_LUNARA!D14</f>
+        <v>1125</v>
+      </c>
+      <c r="E25" s="43">
+        <f>Declarații_INCHIDERE_LUNARA!D14-ROUND(Declarații_INCHIDERE_LUNARA!B23*param_cota_cam,2)</f>
+        <v>0</v>
+      </c>
+      <c r="F25" s="43" t="str">
+        <f>IF(ABS(E25)&lt;0.01,"OK","ATENȚIE — bază de calcul greșită sau concedii medicale (vezi Reguli A)")</f>
+        <v>OK</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="43" t="inlineStr">
+        <is>
+          <t>C-29</t>
+        </is>
+      </c>
+      <c r="B26" s="43" t="inlineStr">
+        <is>
+          <t>sold 4423 din balanță = sold din decont</t>
+        </is>
+      </c>
+      <c r="C26" s="43">
+        <f>Declarații_INCHIDERE_LUNARA!B34</f>
+        <v>5250</v>
+      </c>
+      <c r="D26" s="43">
+        <f>Declarații_INCHIDERE_LUNARA!B35</f>
+        <v>5250</v>
+      </c>
+      <c r="E26" s="43">
+        <f>Declarații_INCHIDERE_LUNARA!B34-Declarații_INCHIDERE_LUNARA!B35</f>
+        <v>0</v>
+      </c>
+      <c r="F26" s="43" t="str">
+        <f>IF(ABS(E26)&lt;0.01,"OK","ATENȚIE — decontul și balanța nu spun același lucru")</f>
+        <v>OK</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="42" t="inlineStr">
+        <is>
+          <t>Control final</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="43" t="inlineStr">
+        <is>
+          <t>Check — toate corelațiile lunii</t>
+        </is>
+      </c>
+      <c r="B29" s="43">
+        <f>ABS(E6)+ABS(E7)+ABS(E8)+ABS(E9)+ABS(E10)+ABS(E14)+ABS(E18)+ABS(E19)+ABS(E20)+ABS(E21)+ABS(E25)+ABS(E26)</f>
+        <v>0</v>
+      </c>
+      <c r="C29" s="43" t="str">
+        <f>IF(ABS(B29)&lt;0.01,"OK — luna se reconciliază pe toate corelațiile","EROARE — vezi foaia Abateri")</f>
+        <v>OK — luna se reconciliază pe toate corelațiile</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet92.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E18"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" style="40" min="1" max="1"/>
+    <col width="12" customWidth="1" style="40" min="2" max="2"/>
+    <col width="46" customWidth="1" style="40" min="3" max="3"/>
+    <col width="16" customWidth="1" style="40" min="4" max="4"/>
+    <col width="56" customWidth="1" style="40" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="41" t="inlineStr">
+        <is>
+          <t>MOD_INCHIDERE_LUNARA — Abateri</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="44" t="inlineStr">
+        <is>
+          <t>Coloana „Include” spune DA doar unde corelația nu s-a potrivit. Lista e completă: dacă toate sunt NU, luna e curată.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="65" t="inlineStr">
+        <is>
+          <t>Include</t>
+        </is>
+      </c>
+      <c r="B4" s="65" t="inlineStr">
+        <is>
+          <t>Cod</t>
+        </is>
+      </c>
+      <c r="C4" s="65" t="inlineStr">
+        <is>
+          <t>Ce nu s-a potrivit</t>
+        </is>
+      </c>
+      <c r="D4" s="65" t="inlineStr">
+        <is>
+          <t>Diferență</t>
+        </is>
+      </c>
+      <c r="E4" s="65" t="inlineStr">
+        <is>
+          <t>Ce se face</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="43" t="str">
+        <f>IF(ABS(Verificări_INCHIDERE_LUNARA!E6)&lt;0.01,"NU","DA")</f>
+        <v>NU</v>
+      </c>
+      <c r="B5" s="43" t="inlineStr">
+        <is>
+          <t>C-25</t>
+        </is>
+      </c>
+      <c r="C5" s="43" t="inlineStr">
+        <is>
+          <t>444 Impozit pe venituri din salarii</t>
+        </is>
+      </c>
+      <c r="D5" s="43">
+        <f>Verificări_INCHIDERE_LUNARA!E6</f>
+        <v>0</v>
+      </c>
+      <c r="E5" s="43" t="inlineStr">
+        <is>
+          <t>Se verifică fișa de plătitor din SPV. Stopaj nevirat peste 30 de zile = răspundere penală, nu întârziere.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="43" t="str">
+        <f>IF(ABS(Verificări_INCHIDERE_LUNARA!E7)&lt;0.01,"NU","DA")</f>
+        <v>NU</v>
+      </c>
+      <c r="B6" s="43" t="inlineStr">
+        <is>
+          <t>C-26</t>
+        </is>
+      </c>
+      <c r="C6" s="43" t="inlineStr">
+        <is>
+          <t>4315 CAS — contribuția de asigurări sociale</t>
+        </is>
+      </c>
+      <c r="D6" s="43">
+        <f>Verificări_INCHIDERE_LUNARA!E7</f>
+        <v>0</v>
+      </c>
+      <c r="E6" s="43" t="inlineStr">
+        <is>
+          <t>Se confruntă cu D112. Dacă e eșalonare, se notează; altfel e restanță.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="43" t="str">
+        <f>IF(ABS(Verificări_INCHIDERE_LUNARA!E8)&lt;0.01,"NU","DA")</f>
+        <v>NU</v>
+      </c>
+      <c r="B7" s="43" t="inlineStr">
+        <is>
+          <t>C-26</t>
+        </is>
+      </c>
+      <c r="C7" s="43" t="inlineStr">
+        <is>
+          <t>4316 CASS — asigurări sociale de sănătate</t>
+        </is>
+      </c>
+      <c r="D7" s="43">
+        <f>Verificări_INCHIDERE_LUNARA!E8</f>
+        <v>0</v>
+      </c>
+      <c r="E7" s="43" t="inlineStr">
+        <is>
+          <t>Se confruntă cu D112. Dacă e eșalonare, se notează; altfel e restanță.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="43" t="str">
+        <f>IF(ABS(Verificări_INCHIDERE_LUNARA!E9)&lt;0.01,"NU","DA")</f>
+        <v>NU</v>
+      </c>
+      <c r="B8" s="43" t="inlineStr">
+        <is>
+          <t>C-26</t>
+        </is>
+      </c>
+      <c r="C8" s="43" t="inlineStr">
+        <is>
+          <t>436 CAM — contribuția asiguratorie pentru muncă</t>
+        </is>
+      </c>
+      <c r="D8" s="43">
+        <f>Verificări_INCHIDERE_LUNARA!E9</f>
+        <v>0</v>
+      </c>
+      <c r="E8" s="43" t="inlineStr">
+        <is>
+          <t>Se confruntă cu D112. Dacă e eșalonare, se notează; altfel e restanță.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="43" t="str">
+        <f>IF(ABS(Verificări_INCHIDERE_LUNARA!E10)&lt;0.01,"NU","DA")</f>
+        <v>NU</v>
+      </c>
+      <c r="B9" s="43" t="inlineStr">
+        <is>
+          <t>C-28</t>
+        </is>
+      </c>
+      <c r="C9" s="43" t="inlineStr">
+        <is>
+          <t>427 Rețineri din salarii datorate terților</t>
+        </is>
+      </c>
+      <c r="D9" s="43">
+        <f>Verificări_INCHIDERE_LUNARA!E10</f>
+        <v>0</v>
+      </c>
+      <c r="E9" s="43" t="inlineStr">
+        <is>
+          <t>Se virează imediat. Banii sunt ai salariatului, opriți pentru altcineva.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="43" t="str">
+        <f>IF(ABS(Verificări_INCHIDERE_LUNARA!E14)&lt;0.01,"NU","DA")</f>
+        <v>NU</v>
+      </c>
+      <c r="B10" s="43" t="inlineStr">
+        <is>
+          <t>C-24</t>
+        </is>
+      </c>
+      <c r="C10" s="43" t="inlineStr">
+        <is>
+          <t>421 + 423 vs. stat</t>
+        </is>
+      </c>
+      <c r="D10" s="43">
+        <f>Verificări_INCHIDERE_LUNARA!E14</f>
+        <v>0</v>
+      </c>
+      <c r="E10" s="43" t="inlineStr">
+        <is>
+          <t>Se scot statele lună de lună și se caută luna în care s-a rupt. Cauza tipică: plată pe alt cont decât 421.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="43" t="str">
+        <f>IF(ABS(Verificări_INCHIDERE_LUNARA!E18)&lt;0.01,"NU","DA")</f>
+        <v>NU</v>
+      </c>
+      <c r="B11" s="43" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C11" s="43" t="inlineStr">
+        <is>
+          <t>473 sold zero</t>
+        </is>
+      </c>
+      <c r="D11" s="43">
+        <f>Verificări_INCHIDERE_LUNARA!E18</f>
+        <v>0</v>
+      </c>
+      <c r="E11" s="43" t="inlineStr">
+        <is>
+          <t>Se identifică operațiunea neterminată și se închide. Un sold reportat pe un cont de tranzit ascunde ceva.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="43" t="str">
+        <f>IF(ABS(Verificări_INCHIDERE_LUNARA!E19)&lt;0.01,"NU","DA")</f>
+        <v>NU</v>
+      </c>
+      <c r="B12" s="43" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C12" s="43" t="inlineStr">
+        <is>
+          <t>581 sold zero</t>
+        </is>
+      </c>
+      <c r="D12" s="43">
+        <f>Verificări_INCHIDERE_LUNARA!E19</f>
+        <v>0</v>
+      </c>
+      <c r="E12" s="43" t="inlineStr">
+        <is>
+          <t>Se identifică operațiunea neterminată și se închide. Un sold reportat pe un cont de tranzit ascunde ceva.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="43" t="str">
+        <f>IF(ABS(Verificări_INCHIDERE_LUNARA!E20)&lt;0.01,"NU","DA")</f>
+        <v>NU</v>
+      </c>
+      <c r="B13" s="43" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C13" s="43" t="inlineStr">
+        <is>
+          <t>542 sold zero</t>
+        </is>
+      </c>
+      <c r="D13" s="43">
+        <f>Verificări_INCHIDERE_LUNARA!E20</f>
+        <v>0</v>
+      </c>
+      <c r="E13" s="43" t="inlineStr">
+        <is>
+          <t>Se identifică operațiunea neterminată și se închide. Un sold reportat pe un cont de tranzit ascunde ceva.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="43" t="str">
+        <f>IF(ABS(Verificări_INCHIDERE_LUNARA!E21)&lt;0.01,"NU","DA")</f>
+        <v>NU</v>
+      </c>
+      <c r="B14" s="43" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C14" s="43" t="inlineStr">
+        <is>
+          <t>4382 sold zero</t>
+        </is>
+      </c>
+      <c r="D14" s="43">
+        <f>Verificări_INCHIDERE_LUNARA!E21</f>
+        <v>0</v>
+      </c>
+      <c r="E14" s="43" t="inlineStr">
+        <is>
+          <t>Se identifică operațiunea neterminată și se închide. Un sold reportat pe un cont de tranzit ascunde ceva.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="43" t="str">
+        <f>IF(ABS(Verificări_INCHIDERE_LUNARA!E25)&lt;0.01,"NU","DA")</f>
+        <v>NU</v>
+      </c>
+      <c r="B15" s="43" t="inlineStr">
+        <is>
+          <t>C-27</t>
+        </is>
+      </c>
+      <c r="C15" s="43" t="inlineStr">
+        <is>
+          <t>CAM pe cifre</t>
+        </is>
+      </c>
+      <c r="D15" s="43">
+        <f>Verificări_INCHIDERE_LUNARA!E25</f>
+        <v>0</v>
+      </c>
+      <c r="E15" s="43" t="inlineStr">
+        <is>
+          <t>Se verifică dacă luna are concedii medicale — CAM nu se datorează pe partea din FNUASS. Altfel, bază de calcul incompletă.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="43" t="str">
+        <f>IF(ABS(Verificări_INCHIDERE_LUNARA!E26)&lt;0.01,"NU","DA")</f>
+        <v>NU</v>
+      </c>
+      <c r="B16" s="43" t="inlineStr">
+        <is>
+          <t>C-29</t>
+        </is>
+      </c>
+      <c r="C16" s="43" t="inlineStr">
+        <is>
+          <t>4423 vs. decont</t>
+        </is>
+      </c>
+      <c r="D16" s="43">
+        <f>Verificări_INCHIDERE_LUNARA!E26</f>
+        <v>0</v>
+      </c>
+      <c r="E16" s="43" t="inlineStr">
+        <is>
+          <t>Se verifică dacă e sumă din decizie de impunere (analitic distinct) sau TVA neachitat din perioade precedente, omis din decont.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="43" t="inlineStr">
+        <is>
+          <t>Check — număr de abateri</t>
+        </is>
+      </c>
+      <c r="B18" s="43">
+        <f>COUNTIF(A5:A16,"DA")</f>
+        <v>0</v>
+      </c>
+      <c r="C18" s="43" t="str">
+        <f>IF(B18=0,"OK — nicio abatere","ATENȚIE — "&amp;B18&amp;" corelații nu se potrivesc")</f>
+        <v>OK — nicio abatere</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/dist/Module_Declarative_Fluxuri.xlsx
+++ b/dist/Module_Declarative_Fluxuri.xlsx
@@ -10580,7 +10580,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F21"/>
+  <dimension ref="A1:F27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" style="40" min="1" max="1"/>
@@ -10814,6 +10814,61 @@
       <c r="A21" s="44" t="inlineStr">
         <is>
           <t>• „711 sau 712” la servicii — pentru servicii e strict 712</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="42" t="inlineStr">
+        <is>
+          <t>Temei legal</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="65" t="inlineStr">
+        <is>
+          <t>Ce se sprijină pe el</t>
+        </is>
+      </c>
+      <c r="B24" s="65" t="inlineStr">
+        <is>
+          <t>Temei</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="43" t="inlineStr">
+        <is>
+          <t>Producția de imobilizări în regie proprie se evidențiază prin 722</t>
+        </is>
+      </c>
+      <c r="B25" s="43" t="inlineStr">
+        <is>
+          <t>OMFP 1802/2014 — funcțiunea contului 722</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="43" t="inlineStr">
+        <is>
+          <t>Variația stocurilor de produse și producție în curs, prin 711</t>
+        </is>
+      </c>
+      <c r="B26" s="43" t="inlineStr">
+        <is>
+          <t>OMFP 1802/2014 — funcțiunea contului 711</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="43" t="inlineStr">
+        <is>
+          <t>Costul de producție cuprinde materiile, manopera și cota de cheltuieli indirecte</t>
+        </is>
+      </c>
+      <c r="B27" s="43" t="inlineStr">
+        <is>
+          <t>OMFP 1802/2014, pct. 9</t>
         </is>
       </c>
     </row>
@@ -13356,7 +13411,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F22"/>
+  <dimension ref="A1:F28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" style="40" min="1" max="1"/>
@@ -13816,6 +13871,61 @@
       <c r="F22" s="43" t="inlineStr">
         <is>
           <t>Subvenția se epuizează înainte sau după activ</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="42" t="inlineStr">
+        <is>
+          <t>Temei legal</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="65" t="inlineStr">
+        <is>
+          <t>Ce se sprijină pe el</t>
+        </is>
+      </c>
+      <c r="B25" s="65" t="inlineStr">
+        <is>
+          <t>Temei</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="43" t="inlineStr">
+        <is>
+          <t>Subvenția pentru investiții se înregistrează ca venit amânat, nu ca venit al lunii</t>
+        </is>
+      </c>
+      <c r="B26" s="43" t="inlineStr">
+        <is>
+          <t>OMFP 1802/2014, pct. 397–404 — conturile 475x</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="43" t="inlineStr">
+        <is>
+          <t>Se eliberează la venit pe măsura amortizării activului finanțat</t>
+        </is>
+      </c>
+      <c r="B27" s="43" t="inlineStr">
+        <is>
+          <t>OMFP 1802/2014, pct. 400 — simetrie cu cheltuiala pe care o compensează</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="43" t="inlineStr">
+        <is>
+          <t>Cota de finanțare: dacă subvenția acoperă doar o parte, eliberarea e proporțională</t>
+        </is>
+      </c>
+      <c r="B28" s="43" t="inlineStr">
+        <is>
+          <t>OMFP 1802/2014, pct. 401</t>
         </is>
       </c>
     </row>
@@ -18219,7 +18329,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E26"/>
+  <dimension ref="A1:E32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" style="40" min="1" max="1"/>
@@ -18492,6 +18602,61 @@
       <c r="A26" s="44" t="inlineStr">
         <is>
           <t>• La închiderea lunară, sumele astea intră în 4426/4427 ca oricare altele și se anulează reciproc — vezi MOD_INCHIDERE_TVA</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="42" t="inlineStr">
+        <is>
+          <t>Temei legal</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="65" t="inlineStr">
+        <is>
+          <t>Ce se sprijină pe el</t>
+        </is>
+      </c>
+      <c r="B29" s="65" t="inlineStr">
+        <is>
+          <t>Temei</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="43" t="inlineStr">
+        <is>
+          <t>Taxare inversă la achiziții intracomunitare de bunuri</t>
+        </is>
+      </c>
+      <c r="B30" s="43" t="inlineStr">
+        <is>
+          <t>art. 307 alin. (2) Cod fiscal — persoana obligată la plată e beneficiarul</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="43" t="inlineStr">
+        <is>
+          <t>Taxare inversă internă, pe lista limitativă de operațiuni</t>
+        </is>
+      </c>
+      <c r="B31" s="43" t="inlineStr">
+        <is>
+          <t>art. 331 Cod fiscal — pe baza derogării UE, valabilă până la 31.12.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="43" t="inlineStr">
+        <is>
+          <t>Declarația recapitulativă pentru operațiunile intracomunitare</t>
+        </is>
+      </c>
+      <c r="B32" s="43" t="inlineStr">
+        <is>
+          <t>art. 325 Cod fiscal — D390</t>
         </is>
       </c>
     </row>
@@ -21978,7 +22143,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D24"/>
+  <dimension ref="A1:D30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="44" customWidth="1" style="40" min="1" max="1"/>
@@ -22281,6 +22446,61 @@
       <c r="A24" s="44" t="inlineStr">
         <is>
           <t>• TVA-ul vamal merge pe 4426 și se închide lunar ca oricare altul (vezi MOD_INCHIDERE_TVA); nu intră niciodată în costul stocului</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="42" t="inlineStr">
+        <is>
+          <t>Temei legal</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="65" t="inlineStr">
+        <is>
+          <t>Ce se sprijină pe el</t>
+        </is>
+      </c>
+      <c r="B27" s="65" t="inlineStr">
+        <is>
+          <t>Temei</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="43" t="inlineStr">
+        <is>
+          <t>Baza de impozitare la import = valoarea în vamă + taxele vamale datorate</t>
+        </is>
+      </c>
+      <c r="B28" s="43" t="inlineStr">
+        <is>
+          <t>art. 289 Cod fiscal</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="43" t="inlineStr">
+        <is>
+          <t>Taxele vamale intră în costul de achiziție al stocului</t>
+        </is>
+      </c>
+      <c r="B29" s="43" t="inlineStr">
+        <is>
+          <t>OMFP 1802/2014, pct. 8 — costul include taxele nerecuperabile</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="43" t="inlineStr">
+        <is>
+          <t>Transportul intern e cost de achiziție, dar nu intră în baza vamală</t>
+        </is>
+      </c>
+      <c r="B30" s="43" t="inlineStr">
+        <is>
+          <t>art. 289 CF (baza vamală) coroborat cu OMFP 1802/2014, pct. 8 (costul)</t>
         </is>
       </c>
     </row>
@@ -27945,7 +28165,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F20"/>
+  <dimension ref="A1:F26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" style="40" min="1" max="1"/>
@@ -28238,6 +28458,61 @@
       <c r="A20" s="44" t="inlineStr">
         <is>
           <t>• Modulul nu amestecă tipurile — un set de Declarații = un tip + o operațiune</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="42" t="inlineStr">
+        <is>
+          <t>Temei legal</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="65" t="inlineStr">
+        <is>
+          <t>Ce se sprijină pe el</t>
+        </is>
+      </c>
+      <c r="B23" s="65" t="inlineStr">
+        <is>
+          <t>Temei</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="43" t="inlineStr">
+        <is>
+          <t>408 / 418 — datorii și creanțe pentru care documentul n-a sosit</t>
+        </is>
+      </c>
+      <c r="B24" s="43" t="inlineStr">
+        <is>
+          <t>OMFP 1802/2014 — funcțiunea conturilor de facturi nesosite / de întocmit</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="43" t="inlineStr">
+        <is>
+          <t>473 — operațiuni în curs de clarificare, cu sold nul la închiderea exercițiului</t>
+        </is>
+      </c>
+      <c r="B25" s="43" t="inlineStr">
+        <is>
+          <t>OMFP 1802/2014 — funcțiunea contului 473; soldul la 31.12 e semnalat la audit</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="43" t="inlineStr">
+        <is>
+          <t>581 — viramente interne, evită dubla înregistrare între conturi de trezorerie</t>
+        </is>
+      </c>
+      <c r="B26" s="43" t="inlineStr">
+        <is>
+          <t>OMFP 1802/2014 — funcțiunea contului 581</t>
         </is>
       </c>
     </row>
@@ -29768,7 +30043,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C24"/>
+  <dimension ref="A1:C30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" style="40" min="1" max="1"/>
@@ -29980,6 +30255,61 @@
       <c r="A24" s="44" t="inlineStr">
         <is>
           <t>• La regimul TVA la încasare, TVA-ul avansului trece prin 4428.INC — vezi MOD_TVA_INCASARE</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="42" t="inlineStr">
+        <is>
+          <t>Temei legal</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="65" t="inlineStr">
+        <is>
+          <t>Ce se sprijină pe el</t>
+        </is>
+      </c>
+      <c r="B27" s="65" t="inlineStr">
+        <is>
+          <t>Temei</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="43" t="inlineStr">
+        <is>
+          <t>TVA devine exigibilă la data încasării avansului, înainte de livrare</t>
+        </is>
+      </c>
+      <c r="B28" s="43" t="inlineStr">
+        <is>
+          <t>art. 282 alin. (2) lit. b) Cod fiscal</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="43" t="inlineStr">
+        <is>
+          <t>La factura finală se regularizează avansul facturat anterior</t>
+        </is>
+      </c>
+      <c r="B29" s="43" t="inlineStr">
+        <is>
+          <t>art. 330 alin. (1) lit. c) Cod fiscal — corectarea facturii</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="43" t="inlineStr">
+        <is>
+          <t>Sumele încasate peste valoarea facturii sunt datorie față de client, nu venit</t>
+        </is>
+      </c>
+      <c r="B30" s="43" t="inlineStr">
+        <is>
+          <t>OMFP 1802/2014 — funcțiunea contului 419</t>
         </is>
       </c>
     </row>
@@ -39993,7 +40323,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F28"/>
+  <dimension ref="A1:F34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" style="40" min="1" max="1"/>
@@ -40462,6 +40792,61 @@
         </is>
       </c>
     </row>
+    <row r="30">
+      <c r="A30" s="42" t="inlineStr">
+        <is>
+          <t>Temei legal</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="65" t="inlineStr">
+        <is>
+          <t>Ce se sprijină pe el</t>
+        </is>
+      </c>
+      <c r="B31" s="65" t="inlineStr">
+        <is>
+          <t>Temei</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="43" t="inlineStr">
+        <is>
+          <t>Veniturile și cheltuielile se închid prin 121 la sfârșitul exercițiului</t>
+        </is>
+      </c>
+      <c r="B32" s="43" t="inlineStr">
+        <is>
+          <t>OMFP 1802/2014 — funcțiunea contului 121</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="43" t="inlineStr">
+        <is>
+          <t>Cota de impozit pe profit</t>
+        </is>
+      </c>
+      <c r="B33" s="43" t="inlineStr">
+        <is>
+          <t>art. 17 Cod fiscal</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="43" t="inlineStr">
+        <is>
+          <t>Rezultatul rămas se reportează pe 117 până la repartizare sau acoperire</t>
+        </is>
+      </c>
+      <c r="B34" s="43" t="inlineStr">
+        <is>
+          <t>OMFP 1802/2014 — funcțiunea contului 117</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -40473,7 +40858,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D22"/>
+  <dimension ref="A1:D28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" style="40" min="1" max="1"/>
@@ -40757,6 +41142,61 @@
       <c r="B22" s="43" t="inlineStr">
         <is>
           <t>Restanța se vede ca diferență sold − rulaj, dar vechimea ei se află doar comparând mai multe luni. Aici se vede CĂ există, nu de când.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="42" t="inlineStr">
+        <is>
+          <t>Temei legal</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="65" t="inlineStr">
+        <is>
+          <t>Ce se sprijină pe el</t>
+        </is>
+      </c>
+      <c r="B25" s="65" t="inlineStr">
+        <is>
+          <t>Temei</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="43" t="inlineStr">
+        <is>
+          <t>Perioada fiscală pentru TVA e luna calendaristică, cu excepțiile prevăzute</t>
+        </is>
+      </c>
+      <c r="B26" s="43" t="inlineStr">
+        <is>
+          <t>art. 322 Cod fiscal</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="43" t="inlineStr">
+        <is>
+          <t>Contribuțiile reținute și cele datorate de angajator se declară lunar</t>
+        </is>
+      </c>
+      <c r="B27" s="43" t="inlineStr">
+        <is>
+          <t>art. 147 Cod fiscal — termenul de 25 al lunii următoare</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="43" t="inlineStr">
+        <is>
+          <t>Corelațiile verificate aici sunt cele din foaia „Corelații de control”</t>
+        </is>
+      </c>
+      <c r="B28" s="43" t="inlineStr">
+        <is>
+          <t>sursă internă: C-24…C-29, derivate din monografii</t>
         </is>
       </c>
     </row>

--- a/dist/Module_Declarative_Fluxuri.xlsx
+++ b/dist/Module_Declarative_Fluxuri.xlsx
@@ -99,10 +99,14 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Registru_DECONT" sheetId="90" state="visible" r:id="rId90"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Jurnale_DECONT" sheetId="91" state="visible" r:id="rId91"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NotaExport_DECONT" sheetId="92" state="visible" r:id="rId92"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Declarații_INCHIDERE_LUNARA" sheetId="93" state="visible" r:id="rId93"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reguli_INCHIDERE_LUNARA" sheetId="94" state="visible" r:id="rId94"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Verificări_INCHIDERE_LUNARA" sheetId="95" state="visible" r:id="rId95"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Abateri_INCHIDERE_LUNARA" sheetId="96" state="visible" r:id="rId96"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Declarații_CONTROL_BALANTA" sheetId="93" state="visible" r:id="rId93"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reguli_CONTROL_BALANTA" sheetId="94" state="visible" r:id="rId94"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Verificări_CONTROL_BALANTA" sheetId="95" state="visible" r:id="rId95"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Abateri_CONTROL_BALANTA" sheetId="96" state="visible" r:id="rId96"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Declarații_INCHIDERE_LUNARA" sheetId="97" state="visible" r:id="rId97"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reguli_INCHIDERE_LUNARA" sheetId="98" state="visible" r:id="rId98"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Verificări_INCHIDERE_LUNARA" sheetId="99" state="visible" r:id="rId99"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Abateri_INCHIDERE_LUNARA" sheetId="100" state="visible" r:id="rId100"/>
   </sheets>
   <definedNames>
     <definedName name="param_proc_rezerva">Parametri!$B$18</definedName>
@@ -849,7 +853,7 @@
     <row r="4" ht="15" customHeight="1" s="40">
       <c r="A4" s="43" t="inlineStr">
         <is>
-          <t>Cele 23 module declarative care execută fluxurile din „Plan de conturi”. Fluxul explică de ce; modulul face înregistrarea. Completezi câteva variabile într-o foaie de input și ies jurnalele și nota de export.</t>
+          <t>Cele 24 module declarative care execută fluxurile din „Plan de conturi”. Fluxul explică de ce; modulul face înregistrarea. Completezi câteva variabile într-o foaie de input și ies jurnalele și nota de export.</t>
         </is>
       </c>
     </row>
@@ -950,7 +954,7 @@
     <row r="21" ht="15" customHeight="1" s="40">
       <c r="A21" s="43" t="inlineStr">
         <is>
-          <t>Implicit DA: MOD_INCHIDERE_TVA, MOD_SALARII, MOD_INCHIDERE_LUNARA.</t>
+          <t>Implicit DA: MOD_INCHIDERE_TVA, MOD_SALARII, MOD_CONTROL_BALANTA, MOD_INCHIDERE_LUNARA.</t>
         </is>
       </c>
     </row>
@@ -1438,6 +1442,383 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet100.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E18"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" style="40" min="1" max="1"/>
+    <col width="12" customWidth="1" style="40" min="2" max="2"/>
+    <col width="46" customWidth="1" style="40" min="3" max="3"/>
+    <col width="16" customWidth="1" style="40" min="4" max="4"/>
+    <col width="56" customWidth="1" style="40" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="41" t="inlineStr">
+        <is>
+          <t>MOD_INCHIDERE_LUNARA — Abateri</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="44" t="inlineStr">
+        <is>
+          <t>Coloana „Include” spune DA doar unde corelația nu s-a potrivit. Lista e completă: dacă toate sunt NU, luna e curată.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="65" t="inlineStr">
+        <is>
+          <t>Include</t>
+        </is>
+      </c>
+      <c r="B4" s="65" t="inlineStr">
+        <is>
+          <t>Cod</t>
+        </is>
+      </c>
+      <c r="C4" s="65" t="inlineStr">
+        <is>
+          <t>Ce nu s-a potrivit</t>
+        </is>
+      </c>
+      <c r="D4" s="65" t="inlineStr">
+        <is>
+          <t>Diferență</t>
+        </is>
+      </c>
+      <c r="E4" s="65" t="inlineStr">
+        <is>
+          <t>Ce se face</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="43" t="str">
+        <f>IF(ABS(Verificări_INCHIDERE_LUNARA!E6)&lt;0.01,"NU","DA")</f>
+        <v>NU</v>
+      </c>
+      <c r="B5" s="43" t="inlineStr">
+        <is>
+          <t>C-25</t>
+        </is>
+      </c>
+      <c r="C5" s="43" t="inlineStr">
+        <is>
+          <t>444 Impozit pe venituri din salarii</t>
+        </is>
+      </c>
+      <c r="D5" s="43">
+        <f>Verificări_INCHIDERE_LUNARA!E6</f>
+        <v>0</v>
+      </c>
+      <c r="E5" s="43" t="inlineStr">
+        <is>
+          <t>Se verifică fișa de plătitor din SPV. Stopaj nevirat peste 30 de zile = răspundere penală, nu întârziere.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="43" t="str">
+        <f>IF(ABS(Verificări_INCHIDERE_LUNARA!E7)&lt;0.01,"NU","DA")</f>
+        <v>NU</v>
+      </c>
+      <c r="B6" s="43" t="inlineStr">
+        <is>
+          <t>C-26</t>
+        </is>
+      </c>
+      <c r="C6" s="43" t="inlineStr">
+        <is>
+          <t>4315 CAS — contribuția de asigurări sociale</t>
+        </is>
+      </c>
+      <c r="D6" s="43">
+        <f>Verificări_INCHIDERE_LUNARA!E7</f>
+        <v>0</v>
+      </c>
+      <c r="E6" s="43" t="inlineStr">
+        <is>
+          <t>Se confruntă cu D112. Dacă e eșalonare, se notează; altfel e restanță.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="43" t="str">
+        <f>IF(ABS(Verificări_INCHIDERE_LUNARA!E8)&lt;0.01,"NU","DA")</f>
+        <v>NU</v>
+      </c>
+      <c r="B7" s="43" t="inlineStr">
+        <is>
+          <t>C-26</t>
+        </is>
+      </c>
+      <c r="C7" s="43" t="inlineStr">
+        <is>
+          <t>4316 CASS — asigurări sociale de sănătate</t>
+        </is>
+      </c>
+      <c r="D7" s="43">
+        <f>Verificări_INCHIDERE_LUNARA!E8</f>
+        <v>0</v>
+      </c>
+      <c r="E7" s="43" t="inlineStr">
+        <is>
+          <t>Se confruntă cu D112. Dacă e eșalonare, se notează; altfel e restanță.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="43" t="str">
+        <f>IF(ABS(Verificări_INCHIDERE_LUNARA!E9)&lt;0.01,"NU","DA")</f>
+        <v>NU</v>
+      </c>
+      <c r="B8" s="43" t="inlineStr">
+        <is>
+          <t>C-26</t>
+        </is>
+      </c>
+      <c r="C8" s="43" t="inlineStr">
+        <is>
+          <t>436 CAM — contribuția asiguratorie pentru muncă</t>
+        </is>
+      </c>
+      <c r="D8" s="43">
+        <f>Verificări_INCHIDERE_LUNARA!E9</f>
+        <v>0</v>
+      </c>
+      <c r="E8" s="43" t="inlineStr">
+        <is>
+          <t>Se confruntă cu D112. Dacă e eșalonare, se notează; altfel e restanță.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="43" t="str">
+        <f>IF(ABS(Verificări_INCHIDERE_LUNARA!E10)&lt;0.01,"NU","DA")</f>
+        <v>NU</v>
+      </c>
+      <c r="B9" s="43" t="inlineStr">
+        <is>
+          <t>C-28</t>
+        </is>
+      </c>
+      <c r="C9" s="43" t="inlineStr">
+        <is>
+          <t>427 Rețineri din salarii datorate terților</t>
+        </is>
+      </c>
+      <c r="D9" s="43">
+        <f>Verificări_INCHIDERE_LUNARA!E10</f>
+        <v>0</v>
+      </c>
+      <c r="E9" s="43" t="inlineStr">
+        <is>
+          <t>Se virează imediat. Banii sunt ai salariatului, opriți pentru altcineva.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="43" t="str">
+        <f>IF(ABS(Verificări_INCHIDERE_LUNARA!E14)&lt;0.01,"NU","DA")</f>
+        <v>NU</v>
+      </c>
+      <c r="B10" s="43" t="inlineStr">
+        <is>
+          <t>C-24</t>
+        </is>
+      </c>
+      <c r="C10" s="43" t="inlineStr">
+        <is>
+          <t>421 + 423 vs. stat</t>
+        </is>
+      </c>
+      <c r="D10" s="43">
+        <f>Verificări_INCHIDERE_LUNARA!E14</f>
+        <v>0</v>
+      </c>
+      <c r="E10" s="43" t="inlineStr">
+        <is>
+          <t>Se scot statele lună de lună și se caută luna în care s-a rupt. Cauza tipică: plată pe alt cont decât 421.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="43" t="str">
+        <f>IF(ABS(Verificări_INCHIDERE_LUNARA!E18)&lt;0.01,"NU","DA")</f>
+        <v>NU</v>
+      </c>
+      <c r="B11" s="43" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C11" s="43" t="inlineStr">
+        <is>
+          <t>473 sold zero</t>
+        </is>
+      </c>
+      <c r="D11" s="43">
+        <f>Verificări_INCHIDERE_LUNARA!E18</f>
+        <v>0</v>
+      </c>
+      <c r="E11" s="43" t="inlineStr">
+        <is>
+          <t>Se identifică operațiunea neterminată și se închide. Un sold reportat pe un cont de tranzit ascunde ceva.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="43" t="str">
+        <f>IF(ABS(Verificări_INCHIDERE_LUNARA!E19)&lt;0.01,"NU","DA")</f>
+        <v>NU</v>
+      </c>
+      <c r="B12" s="43" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C12" s="43" t="inlineStr">
+        <is>
+          <t>581 sold zero</t>
+        </is>
+      </c>
+      <c r="D12" s="43">
+        <f>Verificări_INCHIDERE_LUNARA!E19</f>
+        <v>0</v>
+      </c>
+      <c r="E12" s="43" t="inlineStr">
+        <is>
+          <t>Se identifică operațiunea neterminată și se închide. Un sold reportat pe un cont de tranzit ascunde ceva.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="43" t="str">
+        <f>IF(ABS(Verificări_INCHIDERE_LUNARA!E20)&lt;0.01,"NU","DA")</f>
+        <v>NU</v>
+      </c>
+      <c r="B13" s="43" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C13" s="43" t="inlineStr">
+        <is>
+          <t>542 sold zero</t>
+        </is>
+      </c>
+      <c r="D13" s="43">
+        <f>Verificări_INCHIDERE_LUNARA!E20</f>
+        <v>0</v>
+      </c>
+      <c r="E13" s="43" t="inlineStr">
+        <is>
+          <t>Se identifică operațiunea neterminată și se închide. Un sold reportat pe un cont de tranzit ascunde ceva.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="43" t="str">
+        <f>IF(ABS(Verificări_INCHIDERE_LUNARA!E21)&lt;0.01,"NU","DA")</f>
+        <v>NU</v>
+      </c>
+      <c r="B14" s="43" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C14" s="43" t="inlineStr">
+        <is>
+          <t>4382 sold zero</t>
+        </is>
+      </c>
+      <c r="D14" s="43">
+        <f>Verificări_INCHIDERE_LUNARA!E21</f>
+        <v>0</v>
+      </c>
+      <c r="E14" s="43" t="inlineStr">
+        <is>
+          <t>Se identifică operațiunea neterminată și se închide. Un sold reportat pe un cont de tranzit ascunde ceva.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="43" t="str">
+        <f>IF(ABS(Verificări_INCHIDERE_LUNARA!E25)&lt;0.01,"NU","DA")</f>
+        <v>NU</v>
+      </c>
+      <c r="B15" s="43" t="inlineStr">
+        <is>
+          <t>C-27</t>
+        </is>
+      </c>
+      <c r="C15" s="43" t="inlineStr">
+        <is>
+          <t>CAM pe cifre</t>
+        </is>
+      </c>
+      <c r="D15" s="43">
+        <f>Verificări_INCHIDERE_LUNARA!E25</f>
+        <v>0</v>
+      </c>
+      <c r="E15" s="43" t="inlineStr">
+        <is>
+          <t>Se verifică dacă luna are concedii medicale — CAM nu se datorează pe partea din FNUASS. Altfel, bază de calcul incompletă.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="43" t="str">
+        <f>IF(ABS(Verificări_INCHIDERE_LUNARA!E26)&lt;0.01,"NU","DA")</f>
+        <v>NU</v>
+      </c>
+      <c r="B16" s="43" t="inlineStr">
+        <is>
+          <t>C-29</t>
+        </is>
+      </c>
+      <c r="C16" s="43" t="inlineStr">
+        <is>
+          <t>4423 vs. decont</t>
+        </is>
+      </c>
+      <c r="D16" s="43">
+        <f>Verificări_INCHIDERE_LUNARA!E26</f>
+        <v>0</v>
+      </c>
+      <c r="E16" s="43" t="inlineStr">
+        <is>
+          <t>Se verifică dacă e sumă din decizie de impunere (analitic distinct) sau TVA neachitat din perioade precedente, omis din decont.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="43" t="inlineStr">
+        <is>
+          <t>Check — număr de abateri</t>
+        </is>
+      </c>
+      <c r="B18" s="43">
+        <f>COUNTIF(A5:A16,"DA")</f>
+        <v>0</v>
+      </c>
+      <c r="C18" s="43" t="str">
+        <f>IF(B18=0,"OK — nicio abatere","ATENȚIE — "&amp;B18&amp;" corelații nu se potrivesc")</f>
+        <v>OK — nicio abatere</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
@@ -12158,7 +12539,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:H36"/>
+  <dimension ref="A1:H37"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="8" customWidth="1" style="39" min="1" max="1"/>
@@ -13166,77 +13547,119 @@
       </c>
       <c r="B29" s="61" t="inlineStr">
         <is>
+          <t>MOD_CONTROL_BALANTA</t>
+        </is>
+      </c>
+      <c r="C29" s="61" t="inlineStr">
+        <is>
+          <t>F-214, F-104</t>
+        </is>
+      </c>
+      <c r="D29" s="61" t="inlineStr">
+        <is>
+          <t>Lunar, pe balanța de verificare; obligatoriu la preluarea unei societăți</t>
+        </is>
+      </c>
+      <c r="E29" s="61" t="inlineStr">
+        <is>
+          <t>Σ analitice și sold sintetic pe fiecare cont urmărit; rulajele claselor 6 și 7; soldul lui 121; total sume debitoare și creditoare</t>
+        </is>
+      </c>
+      <c r="F29" s="61" t="inlineStr">
+        <is>
+          <t>Fiecare comparație are două intrări din surse diferite — vezi Reguli, tabelul C</t>
+        </is>
+      </c>
+      <c r="G29" s="61" t="inlineStr">
+        <is>
+          <t>V1 Analitic ↔ sintetic; V2 121 cu clasele 6 și 7; V3 Solduri cu semn contrar naturii; V4 Continuitatea total-sumelor</t>
+        </is>
+      </c>
+      <c r="H29" s="61" t="inlineStr">
+        <is>
+          <t>IMPLEMENTAT</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="62" t="inlineStr">
+        <is>
+          <t>DA</t>
+        </is>
+      </c>
+      <c r="B30" s="61" t="inlineStr">
+        <is>
           <t>MOD_INCHIDERE_LUNARA</t>
         </is>
       </c>
-      <c r="C29" s="61" t="inlineStr">
+      <c r="C30" s="61" t="inlineStr">
         <is>
           <t>F-422, F-413</t>
         </is>
       </c>
-      <c r="D29" s="61" t="inlineStr">
+      <c r="D30" s="61" t="inlineStr">
         <is>
           <t>Lunar, pe balanța de verificare</t>
         </is>
       </c>
-      <c r="E29" s="61" t="inlineStr">
+      <c r="E30" s="61" t="inlineStr">
         <is>
           <t>Rulaj debitor, rulaj creditor și sold pentru conturile cu cadență; restul de plată de pe stat; soldul din decontul de TVA</t>
         </is>
       </c>
-      <c r="F29" s="61" t="inlineStr">
+      <c r="F30" s="61" t="inlineStr">
         <is>
           <t>Verifică solduri, nu documente — vezi Reguli, tabelul C</t>
         </is>
       </c>
-      <c r="G29" s="61" t="inlineStr">
+      <c r="G30" s="61" t="inlineStr">
         <is>
           <t>V1 Obligații lunare (rulaj = sold); V2 Datoria față de salariați; V3 Conturi care trebuie golite; V4 Verificarea CAM pe cifre</t>
         </is>
       </c>
-      <c r="H29" s="61" t="inlineStr">
+      <c r="H30" s="61" t="inlineStr">
         <is>
           <t>IMPLEMENTAT</t>
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="63" t="inlineStr">
+    <row r="32">
+      <c r="A32" s="63" t="inlineStr">
         <is>
           <t>REGULĂ DE SUMONARE</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="46" t="inlineStr">
-        <is>
-          <t>1. În CatalogModule setezi Activ=DA doar pe modulele necesare lunii.</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="46" t="inlineStr">
         <is>
-          <t>2. Completezi variabilele din foaia Declarații_Modul (galben).</t>
+          <t>1. În CatalogModule setezi Activ=DA doar pe modulele necesare lunii.</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="46" t="inlineStr">
         <is>
-          <t>3. Jurnalele și NotaExport se populează automat doar pentru modulele active.</t>
+          <t>2. Completezi variabilele din foaia Declarații_Modul (galben).</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="46" t="inlineStr">
         <is>
-          <t>4. Verifici Check=0 pe fiecare bloc; filtrezi NotaExport pe Include=DA și imporți.</t>
+          <t>3. Jurnalele și NotaExport se populează automat doar pentru modulele active.</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="46" t="inlineStr">
+        <is>
+          <t>4. Verifici Check=0 pe fiecare bloc; filtrezi NotaExport pe Include=DA și imporți.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="46" t="inlineStr">
         <is>
           <t>Nu se creează conturi noi din modul — se folosesc doar conturile din politica declarată + planul de conturi pe rol.</t>
         </is>
@@ -13250,8 +13673,8 @@
     <mergeCell ref="A36:H36"/>
     <mergeCell ref="A33:H33"/>
     <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A37:H37"/>
     <mergeCell ref="A32:H32"/>
-    <mergeCell ref="A31:H31"/>
     <mergeCell ref="A34:H34"/>
   </mergeCells>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
@@ -43344,6 +43767,2442 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:D47"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="34" customWidth="1" style="40" min="1" max="1"/>
+    <col width="18" customWidth="1" style="40" min="2" max="2"/>
+    <col width="18" customWidth="1" style="40" min="3" max="3"/>
+    <col width="54" customWidth="1" style="40" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="41" t="inlineStr">
+        <is>
+          <t>MOD_CONTROL_BALANTA — Declarații (input)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="44" t="inlineStr">
+        <is>
+          <t>Cele două coloane se transcriu din DOUĂ rapoarte diferite ale aceleiași balanțe — analitică și sintetică. Dacă ar veni din același loc, sau dacă una s-ar calcula din cealaltă, verificarea ar fi verde întotdeauna.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="42" t="inlineStr">
+        <is>
+          <t>1. Antet</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="43" t="inlineStr">
+        <is>
+          <t>Societate</t>
+        </is>
+      </c>
+      <c r="B5" s="43" t="str">
+        <f>Parametri!B5</f>
+        <v>SC EXEMPLU SRL</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="43" t="inlineStr">
+        <is>
+          <t>CUI</t>
+        </is>
+      </c>
+      <c r="B6" s="43" t="str">
+        <f>Parametri!B6</f>
+        <v>RO00000000</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="43" t="inlineStr">
+        <is>
+          <t>Luna verificată (AAAA-LL)</t>
+        </is>
+      </c>
+      <c r="B7" s="64" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="43" t="inlineStr">
+        <is>
+          <t>E prima lună după preluarea societății? (DA/NU)</t>
+        </is>
+      </c>
+      <c r="B8" s="64" t="inlineStr">
+        <is>
+          <t>NU</t>
+        </is>
+      </c>
+      <c r="C8" s="44" t="inlineStr">
+        <is>
+          <t>DA activează blocul V4 — continuitatea total-sumelor</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="42" t="inlineStr">
+        <is>
+          <t>2. Analitic ↔ sintetic — cele două coloane, din două rapoarte</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="65" t="inlineStr">
+        <is>
+          <t>Cont</t>
+        </is>
+      </c>
+      <c r="B11" s="65" t="inlineStr">
+        <is>
+          <t>Σ analitice</t>
+        </is>
+      </c>
+      <c r="C11" s="65" t="inlineStr">
+        <is>
+          <t>Sold sintetic</t>
+        </is>
+      </c>
+      <c r="D11" s="65" t="inlineStr">
+        <is>
+          <t>Sursa externă de confruntat</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="43" t="inlineStr">
+        <is>
+          <t>512x — Conturi la bănci</t>
+        </is>
+      </c>
+      <c r="B12" s="43" t="n">
+        <v>145320.5</v>
+      </c>
+      <c r="C12" s="43" t="n">
+        <v>145320.5</v>
+      </c>
+      <c r="D12" s="43" t="inlineStr">
+        <is>
+          <t>Extrasul de cont, pe fiecare bancă</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="43" t="inlineStr">
+        <is>
+          <t>4111 — Clienți</t>
+        </is>
+      </c>
+      <c r="B13" s="43" t="n">
+        <v>238400</v>
+      </c>
+      <c r="C13" s="43" t="n">
+        <v>238400</v>
+      </c>
+      <c r="D13" s="43" t="inlineStr">
+        <is>
+          <t>Confirmarea de sold / fișa partenerului</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="43" t="inlineStr">
+        <is>
+          <t>401 — Furnizori</t>
+        </is>
+      </c>
+      <c r="B14" s="43" t="n">
+        <v>176250</v>
+      </c>
+      <c r="C14" s="43" t="n">
+        <v>176250</v>
+      </c>
+      <c r="D14" s="43" t="inlineStr">
+        <is>
+          <t>Fișa partenerului</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="43" t="inlineStr">
+        <is>
+          <t>542 — Avansuri de trezorerie</t>
+        </is>
+      </c>
+      <c r="B15" s="43" t="n">
+        <v>5000</v>
+      </c>
+      <c r="C15" s="43" t="n">
+        <v>5000</v>
+      </c>
+      <c r="D15" s="43" t="inlineStr">
+        <is>
+          <t>Deconturile semnate, pe fiecare salariat</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="43" t="inlineStr">
+        <is>
+          <t>21x / 28x — Imobilizări și amortizarea lor</t>
+        </is>
+      </c>
+      <c r="B16" s="43" t="n">
+        <v>412000</v>
+      </c>
+      <c r="C16" s="43" t="n">
+        <v>412000</v>
+      </c>
+      <c r="D16" s="43" t="inlineStr">
+        <is>
+          <t>Registrul mijloacelor fixe (F-214)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="43" t="inlineStr">
+        <is>
+          <t>446 — Alte impozite și taxe</t>
+        </is>
+      </c>
+      <c r="B17" s="43" t="n">
+        <v>12240</v>
+      </c>
+      <c r="C17" s="43" t="n">
+        <v>12240</v>
+      </c>
+      <c r="D17" s="43" t="inlineStr">
+        <is>
+          <t>Fișa pe plătitor din SPV</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="43" t="inlineStr">
+        <is>
+          <t>455 — Sume datorate asociaților</t>
+        </is>
+      </c>
+      <c r="B18" s="43" t="n">
+        <v>20000</v>
+      </c>
+      <c r="C18" s="43" t="n">
+        <v>20000</v>
+      </c>
+      <c r="D18" s="43" t="inlineStr">
+        <is>
+          <t>Contractele de creditare</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="43" t="inlineStr">
+        <is>
+          <t>1012 — Capital subscris vărsat</t>
+        </is>
+      </c>
+      <c r="B19" s="43" t="n">
+        <v>30000</v>
+      </c>
+      <c r="C19" s="43" t="n">
+        <v>30000</v>
+      </c>
+      <c r="D19" s="43" t="inlineStr">
+        <is>
+          <t>Certificatul constatator ONRC</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="42" t="inlineStr">
+        <is>
+          <t>3. Închiderea claselor 6 și 7 în 121</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="43" t="inlineStr">
+        <is>
+          <t>Rulaj total clasa 6 (cheltuieli)</t>
+        </is>
+      </c>
+      <c r="B22" s="64" t="n">
+        <v>480000</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="43" t="inlineStr">
+        <is>
+          <t>Rulaj total clasa 7 (venituri)</t>
+        </is>
+      </c>
+      <c r="B23" s="64" t="n">
+        <v>560000</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="43" t="inlineStr">
+        <is>
+          <t>Sold 121 din balanță (creditor pozitiv)</t>
+        </is>
+      </c>
+      <c r="B24" s="64" t="n">
+        <v>80000</v>
+      </c>
+      <c r="C24" s="44" t="inlineStr">
+        <is>
+          <t>Se citește din balanță, nu se calculează din cele de mai sus</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="42" t="inlineStr">
+        <is>
+          <t>4. Solduri, pentru verificarea semnului</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="44" t="inlineStr">
+        <is>
+          <t>Soldul se scrie CU SEMN: pozitiv = debitor, negativ = creditor. Natura contului vine din tabelul din Reguli, nu din semnul introdus.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="65" t="inlineStr">
+        <is>
+          <t>Cont</t>
+        </is>
+      </c>
+      <c r="B28" s="65" t="inlineStr">
+        <is>
+          <t>Sold cu semn</t>
+        </is>
+      </c>
+      <c r="C28" s="65" t="inlineStr"/>
+      <c r="D28" s="65" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="43" t="inlineStr">
+        <is>
+          <t>4111</t>
+        </is>
+      </c>
+      <c r="B29" s="43" t="n">
+        <v>238400</v>
+      </c>
+      <c r="C29" s="43" t="inlineStr"/>
+      <c r="D29" s="43" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="43" t="inlineStr">
+        <is>
+          <t>401</t>
+        </is>
+      </c>
+      <c r="B30" s="43" t="n">
+        <v>-176250</v>
+      </c>
+      <c r="C30" s="43" t="inlineStr"/>
+      <c r="D30" s="43" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="43" t="inlineStr">
+        <is>
+          <t>409</t>
+        </is>
+      </c>
+      <c r="B31" s="43" t="n">
+        <v>8500</v>
+      </c>
+      <c r="C31" s="43" t="inlineStr"/>
+      <c r="D31" s="43" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="43" t="inlineStr">
+        <is>
+          <t>419</t>
+        </is>
+      </c>
+      <c r="B32" s="43" t="n">
+        <v>-12100</v>
+      </c>
+      <c r="C32" s="43" t="inlineStr"/>
+      <c r="D32" s="43" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="43" t="inlineStr">
+        <is>
+          <t>4551</t>
+        </is>
+      </c>
+      <c r="B33" s="43" t="n">
+        <v>-20000</v>
+      </c>
+      <c r="C33" s="43" t="inlineStr"/>
+      <c r="D33" s="43" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="43" t="inlineStr">
+        <is>
+          <t>5191</t>
+        </is>
+      </c>
+      <c r="B34" s="43" t="n">
+        <v>-1000</v>
+      </c>
+      <c r="C34" s="43" t="inlineStr"/>
+      <c r="D34" s="43" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="43" t="inlineStr">
+        <is>
+          <t>444</t>
+        </is>
+      </c>
+      <c r="B35" s="43" t="n">
+        <v>-3250</v>
+      </c>
+      <c r="C35" s="43" t="inlineStr"/>
+      <c r="D35" s="43" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="43" t="inlineStr">
+        <is>
+          <t>4282</t>
+        </is>
+      </c>
+      <c r="B36" s="43" t="n">
+        <v>1200</v>
+      </c>
+      <c r="C36" s="43" t="inlineStr"/>
+      <c r="D36" s="43" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="42" t="inlineStr">
+        <is>
+          <t>5. Continuitatea total-sumelor (doar la preluare)</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="43" t="inlineStr">
+        <is>
+          <t>Total sume DEBITOARE, balanța lunii anterioare</t>
+        </is>
+      </c>
+      <c r="B39" s="64" t="n">
+        <v>2450000</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="43" t="inlineStr">
+        <is>
+          <t>Total sume CREDITOARE, balanța lunii anterioare</t>
+        </is>
+      </c>
+      <c r="B40" s="64" t="n">
+        <v>2450000</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="43" t="inlineStr">
+        <is>
+          <t>Total sume DEBITOARE, luna curentă</t>
+        </is>
+      </c>
+      <c r="B41" s="64" t="n">
+        <v>2780000</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="43" t="inlineStr">
+        <is>
+          <t>Total sume CREDITOARE, luna curentă</t>
+        </is>
+      </c>
+      <c r="B42" s="64" t="n">
+        <v>2780000</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="42" t="inlineStr">
+        <is>
+          <t>6. Control</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="43" t="inlineStr">
+        <is>
+          <t>Modul activ?</t>
+        </is>
+      </c>
+      <c r="B45" s="43" t="str">
+        <f>IF(INDEX(CatalogModule!$A$1:$A$200,MATCH("MOD_CONTROL_BALANTA",CatalogModule!$B$1:$B$200,0))="DA","ACTIV","INACTIV")</f>
+        <v>ACTIV</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="43" t="inlineStr">
+        <is>
+          <t>Cauza cea mai frecventă a diferenței analitic ↔ sintetic</t>
+        </is>
+      </c>
+      <c r="B46" s="43" t="inlineStr">
+        <is>
+          <t>O operațiune făcută DUPĂ închiderea de lună, fără refacerea închiderii. Programul te lasă, iar diferența nu se anunță singură.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="43" t="inlineStr">
+        <is>
+          <t>Ordinea de verificare</t>
+        </is>
+      </c>
+      <c r="B47" s="43" t="inlineStr">
+        <is>
+          <t>Tabelul A din Reguli e ordonat după cât de mult strică eroarea, nu după simbolul contului — cum a cerut formatorul la finalul ședinței.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet94.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D46"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" style="40" min="1" max="1"/>
+    <col width="30" customWidth="1" style="40" min="2" max="2"/>
+    <col width="52" customWidth="1" style="40" min="3" max="3"/>
+    <col width="40" customWidth="1" style="40" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="41" t="inlineStr">
+        <is>
+          <t>MOD_CONTROL_BALANTA — Reguli (tabele fixe)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="44" t="inlineStr">
+        <is>
+          <t>Ce e regulă dată, nu formulă: ordinea de verificare, naturile conturilor și limitele modulului.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="42" t="inlineStr">
+        <is>
+          <t>Tabelul A — Ordinea de verificare</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="44" t="inlineStr">
+        <is>
+          <t>Ordonat după cât de mult strică eroarea, nu după simbolul contului. Formatorul a cerut explicit „conturile cele mai comune, cele mai esențiale, în ce ordine”.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="65" t="inlineStr">
+        <is>
+          <t>Cont</t>
+        </is>
+      </c>
+      <c r="B6" s="65" t="inlineStr">
+        <is>
+          <t>Denumire</t>
+        </is>
+      </c>
+      <c r="C6" s="65" t="inlineStr">
+        <is>
+          <t>De ce are analitic obligatoriu</t>
+        </is>
+      </c>
+      <c r="D6" s="65" t="inlineStr">
+        <is>
+          <t>Sursa externă</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="43" t="inlineStr">
+        <is>
+          <t>512x</t>
+        </is>
+      </c>
+      <c r="B7" s="43" t="inlineStr">
+        <is>
+          <t>Conturi la bănci</t>
+        </is>
+      </c>
+      <c r="C7" s="43" t="inlineStr">
+        <is>
+          <t>Extrasul e o sursă externă, independentă de contabilitate — deci diferența se localizează, nu se presupune</t>
+        </is>
+      </c>
+      <c r="D7" s="43" t="inlineStr">
+        <is>
+          <t>Extrasul de cont, pe fiecare bancă</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="43" t="inlineStr">
+        <is>
+          <t>4111</t>
+        </is>
+      </c>
+      <c r="B8" s="43" t="inlineStr">
+        <is>
+          <t>Clienți</t>
+        </is>
+      </c>
+      <c r="C8" s="43" t="inlineStr">
+        <is>
+          <t>Fișa clientului e documentul pe care îl vede și partenerul; o denaturezi o dată și se propagă în toate confirmările de sold</t>
+        </is>
+      </c>
+      <c r="D8" s="43" t="inlineStr">
+        <is>
+          <t>Confirmarea de sold / fișa partenerului</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="43" t="inlineStr">
+        <is>
+          <t>401</t>
+        </is>
+      </c>
+      <c r="B9" s="43" t="inlineStr">
+        <is>
+          <t>Furnizori</t>
+        </is>
+      </c>
+      <c r="C9" s="43" t="inlineStr">
+        <is>
+          <t>Oglinda lui 4111. E și a doua căsuță verde din softul formatorului</t>
+        </is>
+      </c>
+      <c r="D9" s="43" t="inlineStr">
+        <is>
+          <t>Fișa partenerului</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="43" t="inlineStr">
+        <is>
+          <t>542</t>
+        </is>
+      </c>
+      <c r="B10" s="43" t="inlineStr">
+        <is>
+          <t>Avansuri de trezorerie</t>
+        </is>
+      </c>
+      <c r="C10" s="43" t="inlineStr">
+        <is>
+          <t>Soldul merge în ambele sensuri pe persoane diferite; pe sintetic se anulează și arată aproape zero — corect ca sumă, fals pe fiecare om</t>
+        </is>
+      </c>
+      <c r="D10" s="43" t="inlineStr">
+        <is>
+          <t>Deconturile semnate, pe fiecare salariat</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="43" t="inlineStr">
+        <is>
+          <t>21x / 28x</t>
+        </is>
+      </c>
+      <c r="B11" s="43" t="inlineStr">
+        <is>
+          <t>Imobilizări și amortizarea lor</t>
+        </is>
+      </c>
+      <c r="C11" s="43" t="inlineStr">
+        <is>
+          <t>Prima verificare cerută de formator pentru aplicație. Registrul mijloacelor fixe e sursa externă</t>
+        </is>
+      </c>
+      <c r="D11" s="43" t="inlineStr">
+        <is>
+          <t>Registrul mijloacelor fixe (F-214)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="43" t="inlineStr">
+        <is>
+          <t>446</t>
+        </is>
+      </c>
+      <c r="B12" s="43" t="inlineStr">
+        <is>
+          <t>Alte impozite și taxe</t>
+        </is>
+      </c>
+      <c r="C12" s="43" t="inlineStr">
+        <is>
+          <t>Se ține pe analitic DE LA BUN ÎNCEPUT — a doua taxă apare întotdeauna, iar despărțirea retroactivă e mult mai scumpă decât analiticul făcut din prima</t>
+        </is>
+      </c>
+      <c r="D12" s="43" t="inlineStr">
+        <is>
+          <t>Fișa pe plătitor din SPV</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="43" t="inlineStr">
+        <is>
+          <t>455</t>
+        </is>
+      </c>
+      <c r="B13" s="43" t="inlineStr">
+        <is>
+          <t>Sume datorate asociaților</t>
+        </is>
+      </c>
+      <c r="C13" s="43" t="inlineStr">
+        <is>
+          <t>Fără analitic, compensarea între doi asociați se ascunde într-un sold total care arată curat (C-30)</t>
+        </is>
+      </c>
+      <c r="D13" s="43" t="inlineStr">
+        <is>
+          <t>Contractele de creditare</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="43" t="inlineStr">
+        <is>
+          <t>1012</t>
+        </is>
+      </c>
+      <c r="B14" s="43" t="inlineStr">
+        <is>
+          <t>Capital subscris vărsat</t>
+        </is>
+      </c>
+      <c r="C14" s="43" t="inlineStr">
+        <is>
+          <t>Cotele trebuie să se citească din balanță în ziua în care vine hotărârea AGA (C-31)</t>
+        </is>
+      </c>
+      <c r="D14" s="43" t="inlineStr">
+        <is>
+          <t>Certificatul constatator ONRC</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="42" t="inlineStr">
+        <is>
+          <t>Tabelul B — Naturile conturilor verificate</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="44" t="inlineStr">
+        <is>
+          <t>Natura vine de aici, nu din soldul introdus. Un cont de activ cu sold creditor nu e o curiozitate de balanță — e o eroare care încă n-a fost căutată (C-23).</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="65" t="inlineStr">
+        <is>
+          <t>Cont</t>
+        </is>
+      </c>
+      <c r="B18" s="65" t="inlineStr">
+        <is>
+          <t>Natura</t>
+        </is>
+      </c>
+      <c r="C18" s="65" t="inlineStr">
+        <is>
+          <t>Sensul normal al soldului</t>
+        </is>
+      </c>
+      <c r="D18" s="65" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="43" t="inlineStr">
+        <is>
+          <t>4111</t>
+        </is>
+      </c>
+      <c r="B19" s="43" t="inlineStr">
+        <is>
+          <t>Activ</t>
+        </is>
+      </c>
+      <c r="C19" s="43" t="inlineStr">
+        <is>
+          <t>Debitor</t>
+        </is>
+      </c>
+      <c r="D19" s="43" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="43" t="inlineStr">
+        <is>
+          <t>401</t>
+        </is>
+      </c>
+      <c r="B20" s="43" t="inlineStr">
+        <is>
+          <t>Pasiv</t>
+        </is>
+      </c>
+      <c r="C20" s="43" t="inlineStr">
+        <is>
+          <t>Creditor</t>
+        </is>
+      </c>
+      <c r="D20" s="43" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="43" t="inlineStr">
+        <is>
+          <t>409</t>
+        </is>
+      </c>
+      <c r="B21" s="43" t="inlineStr">
+        <is>
+          <t>Activ</t>
+        </is>
+      </c>
+      <c r="C21" s="43" t="inlineStr">
+        <is>
+          <t>Debitor</t>
+        </is>
+      </c>
+      <c r="D21" s="43" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="43" t="inlineStr">
+        <is>
+          <t>419</t>
+        </is>
+      </c>
+      <c r="B22" s="43" t="inlineStr">
+        <is>
+          <t>Pasiv</t>
+        </is>
+      </c>
+      <c r="C22" s="43" t="inlineStr">
+        <is>
+          <t>Creditor</t>
+        </is>
+      </c>
+      <c r="D22" s="43" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="43" t="inlineStr">
+        <is>
+          <t>4551</t>
+        </is>
+      </c>
+      <c r="B23" s="43" t="inlineStr">
+        <is>
+          <t>Pasiv</t>
+        </is>
+      </c>
+      <c r="C23" s="43" t="inlineStr">
+        <is>
+          <t>Creditor</t>
+        </is>
+      </c>
+      <c r="D23" s="43" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="43" t="inlineStr">
+        <is>
+          <t>5191</t>
+        </is>
+      </c>
+      <c r="B24" s="43" t="inlineStr">
+        <is>
+          <t>Pasiv</t>
+        </is>
+      </c>
+      <c r="C24" s="43" t="inlineStr">
+        <is>
+          <t>Creditor</t>
+        </is>
+      </c>
+      <c r="D24" s="43" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="43" t="inlineStr">
+        <is>
+          <t>444</t>
+        </is>
+      </c>
+      <c r="B25" s="43" t="inlineStr">
+        <is>
+          <t>Pasiv</t>
+        </is>
+      </c>
+      <c r="C25" s="43" t="inlineStr">
+        <is>
+          <t>Creditor</t>
+        </is>
+      </c>
+      <c r="D25" s="43" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="43" t="inlineStr">
+        <is>
+          <t>4282</t>
+        </is>
+      </c>
+      <c r="B26" s="43" t="inlineStr">
+        <is>
+          <t>Activ</t>
+        </is>
+      </c>
+      <c r="C26" s="43" t="inlineStr">
+        <is>
+          <t>Debitor</t>
+        </is>
+      </c>
+      <c r="D26" s="43" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="42" t="inlineStr">
+        <is>
+          <t>Tabelul C — LIMITĂRI DECLARATE</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="44" t="inlineStr">
+        <is>
+          <t>• Modulul verifică CE I SE DĂ, nu balanța însăși. Dacă ambele coloane sunt transcrise greșit în același fel, iese verde — e verificare de coerență, nu de exactitate.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="44" t="inlineStr">
+        <is>
+          <t>• Lista conturilor cu analitic obligatoriu e o convenție de cabinet, nu o regulă legală. Se completează pe măsură ce apar conturi noi cu analitic.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="44" t="inlineStr">
+        <is>
+          <t>• Cifrele se introduc; modulul nu citește balanța din fișier. Citirea automată e sarcina următoare — vezi tabelul D.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="44" t="inlineStr">
+        <is>
+          <t>• Decontul de TVA (a treia căsuță a formatorului) NU e aici: e deja implementat în MOD_INCHIDERE_LUNARA, blocul V4, corelația C-29.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="44" t="inlineStr">
+        <is>
+          <t>• V4 se rulează doar la preluare. În restul lunilor continuitatea e dată de faptul că lucrezi în același fișier.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="42" t="inlineStr">
+        <is>
+          <t>Tabelul D — Ce rămâne de automatizat</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="65" t="inlineStr">
+        <is>
+          <t>Pasul</t>
+        </is>
+      </c>
+      <c r="B36" s="65" t="inlineStr">
+        <is>
+          <t>Ce ar face</t>
+        </is>
+      </c>
+      <c r="C36" s="65" t="inlineStr">
+        <is>
+          <t>De ce nu e făcut încă</t>
+        </is>
+      </c>
+      <c r="D36" s="65" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="43" t="inlineStr">
+        <is>
+          <t>Citirea balanței</t>
+        </is>
+      </c>
+      <c r="B37" s="43" t="inlineStr">
+        <is>
+          <t>Preluarea cifrelor direct din fișierul de balanță</t>
+        </is>
+      </c>
+      <c r="C37" s="43" t="inlineStr">
+        <is>
+          <t>Formatul diferă de la un program la altul; cere o hartă pe fiecare</t>
+        </is>
+      </c>
+      <c r="D37" s="43" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="43" t="inlineStr">
+        <is>
+          <t>Detectarea analiticelor</t>
+        </is>
+      </c>
+      <c r="B38" s="43" t="inlineStr">
+        <is>
+          <t>Recunoașterea automată a conturilor cu analitic</t>
+        </is>
+      </c>
+      <c r="C38" s="43" t="inlineStr">
+        <is>
+          <t>Cere convenția de denumire a analiticelor, care nu e uniformă</t>
+        </is>
+      </c>
+      <c r="D38" s="43" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="43" t="inlineStr">
+        <is>
+          <t>Localizarea diferenței</t>
+        </is>
+      </c>
+      <c r="B39" s="43" t="inlineStr">
+        <is>
+          <t>Nu doar CĂ diferă, ci pe ce analitic</t>
+        </is>
+      </c>
+      <c r="C39" s="43" t="inlineStr">
+        <is>
+          <t>Cere balanța analitică rând cu rând, nu doar totalul</t>
+        </is>
+      </c>
+      <c r="D39" s="43" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="42" t="inlineStr">
+        <is>
+          <t>Temei legal</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="65" t="inlineStr">
+        <is>
+          <t>Ce se sprijină pe el</t>
+        </is>
+      </c>
+      <c r="B42" s="65" t="inlineStr">
+        <is>
+          <t>Temei</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="43" t="inlineStr">
+        <is>
+          <t>Contabilitatea analitică se ține obligatoriu, în dezvoltarea celei sintetice</t>
+        </is>
+      </c>
+      <c r="B43" s="43" t="inlineStr">
+        <is>
+          <t>Legea contabilității 82/1991, art. 2 alin. (1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="43" t="inlineStr">
+        <is>
+          <t>Balanța de verificare are rolul de a controla exactitatea înregistrărilor și concordanța dintre contabilitatea sintetică și cea analitică</t>
+        </is>
+      </c>
+      <c r="B44" s="43" t="inlineStr">
+        <is>
+          <t>Legea 82/1991, art. 22 — chiar rostul declarat al balanței</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="43" t="inlineStr">
+        <is>
+          <t>Registrele obligatorii: registrul-jurnal, registrul-inventar și Cartea mare</t>
+        </is>
+      </c>
+      <c r="B45" s="43" t="inlineStr">
+        <is>
+          <t>Legea 82/1991, art. 20</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="43" t="inlineStr">
+        <is>
+          <t>Situațiile financiare se întocmesc pe baza balanței de verificare</t>
+        </is>
+      </c>
+      <c r="B46" s="43" t="inlineStr">
+        <is>
+          <t>OMFP 1802/2014, pct. 26 și 583</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet95.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F36"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" style="40" min="1" max="1"/>
+    <col width="40" customWidth="1" style="40" min="2" max="2"/>
+    <col width="18" customWidth="1" style="40" min="3" max="3"/>
+    <col width="18" customWidth="1" style="40" min="4" max="4"/>
+    <col width="16" customWidth="1" style="40" min="5" max="5"/>
+    <col width="56" customWidth="1" style="40" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="41" t="inlineStr">
+        <is>
+          <t>MOD_CONTROL_BALANTA — Verificări</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="44" t="inlineStr">
+        <is>
+          <t>O linie pe verificare. Coloana „Diferență” e ce contează: zero înseamnă că cele două surse spun același lucru.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="42" t="inlineStr">
+        <is>
+          <t>V1 — analitic ↔ sintetic, în ordinea de verificare</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="65" t="inlineStr">
+        <is>
+          <t>Cod</t>
+        </is>
+      </c>
+      <c r="B5" s="65" t="inlineStr">
+        <is>
+          <t>Ce verifică</t>
+        </is>
+      </c>
+      <c r="C5" s="65" t="inlineStr">
+        <is>
+          <t>Σ analitice</t>
+        </is>
+      </c>
+      <c r="D5" s="65" t="inlineStr">
+        <is>
+          <t>Sold sintetic</t>
+        </is>
+      </c>
+      <c r="E5" s="65" t="inlineStr">
+        <is>
+          <t>Diferență</t>
+        </is>
+      </c>
+      <c r="F5" s="65" t="inlineStr">
+        <is>
+          <t>Verdict</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="43" t="inlineStr">
+        <is>
+          <t>C-37</t>
+        </is>
+      </c>
+      <c r="B6" s="43" t="inlineStr">
+        <is>
+          <t>512x — Conturi la bănci</t>
+        </is>
+      </c>
+      <c r="C6" s="43">
+        <f>Declarații_CONTROL_BALANTA!B12</f>
+        <v>145320.5</v>
+      </c>
+      <c r="D6" s="43">
+        <f>Declarații_CONTROL_BALANTA!C12</f>
+        <v>145320.5</v>
+      </c>
+      <c r="E6" s="43">
+        <f>Declarații_CONTROL_BALANTA!B12-Declarații_CONTROL_BALANTA!C12</f>
+        <v>0</v>
+      </c>
+      <c r="F6" s="43" t="str">
+        <f>IF(ABS(E6)&lt;0.01,"OK","ATENȚIE — analiticul diferă de sintetic cu "&amp;TEXT(E6,"#,##0.00")&amp;" lei; cauza tipică: operațiune după închiderea de lună, fără refacerea ei")</f>
+        <v>OK</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="43" t="inlineStr">
+        <is>
+          <t>C-37</t>
+        </is>
+      </c>
+      <c r="B7" s="43" t="inlineStr">
+        <is>
+          <t>4111 — Clienți</t>
+        </is>
+      </c>
+      <c r="C7" s="43">
+        <f>Declarații_CONTROL_BALANTA!B13</f>
+        <v>238400</v>
+      </c>
+      <c r="D7" s="43">
+        <f>Declarații_CONTROL_BALANTA!C13</f>
+        <v>238400</v>
+      </c>
+      <c r="E7" s="43">
+        <f>Declarații_CONTROL_BALANTA!B13-Declarații_CONTROL_BALANTA!C13</f>
+        <v>0</v>
+      </c>
+      <c r="F7" s="43" t="str">
+        <f>IF(ABS(E7)&lt;0.01,"OK","ATENȚIE — analiticul diferă de sintetic cu "&amp;TEXT(E7,"#,##0.00")&amp;" lei; cauza tipică: operațiune după închiderea de lună, fără refacerea ei")</f>
+        <v>OK</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="43" t="inlineStr">
+        <is>
+          <t>C-37</t>
+        </is>
+      </c>
+      <c r="B8" s="43" t="inlineStr">
+        <is>
+          <t>401 — Furnizori</t>
+        </is>
+      </c>
+      <c r="C8" s="43">
+        <f>Declarații_CONTROL_BALANTA!B14</f>
+        <v>176250</v>
+      </c>
+      <c r="D8" s="43">
+        <f>Declarații_CONTROL_BALANTA!C14</f>
+        <v>176250</v>
+      </c>
+      <c r="E8" s="43">
+        <f>Declarații_CONTROL_BALANTA!B14-Declarații_CONTROL_BALANTA!C14</f>
+        <v>0</v>
+      </c>
+      <c r="F8" s="43" t="str">
+        <f>IF(ABS(E8)&lt;0.01,"OK","ATENȚIE — analiticul diferă de sintetic cu "&amp;TEXT(E8,"#,##0.00")&amp;" lei; cauza tipică: operațiune după închiderea de lună, fără refacerea ei")</f>
+        <v>OK</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="43" t="inlineStr">
+        <is>
+          <t>C-37</t>
+        </is>
+      </c>
+      <c r="B9" s="43" t="inlineStr">
+        <is>
+          <t>542 — Avansuri de trezorerie</t>
+        </is>
+      </c>
+      <c r="C9" s="43">
+        <f>Declarații_CONTROL_BALANTA!B15</f>
+        <v>5000</v>
+      </c>
+      <c r="D9" s="43">
+        <f>Declarații_CONTROL_BALANTA!C15</f>
+        <v>5000</v>
+      </c>
+      <c r="E9" s="43">
+        <f>Declarații_CONTROL_BALANTA!B15-Declarații_CONTROL_BALANTA!C15</f>
+        <v>0</v>
+      </c>
+      <c r="F9" s="43" t="str">
+        <f>IF(ABS(E9)&lt;0.01,"OK","ATENȚIE — analiticul diferă de sintetic cu "&amp;TEXT(E9,"#,##0.00")&amp;" lei; cauza tipică: operațiune după închiderea de lună, fără refacerea ei")</f>
+        <v>OK</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="43" t="inlineStr">
+        <is>
+          <t>C-37</t>
+        </is>
+      </c>
+      <c r="B10" s="43" t="inlineStr">
+        <is>
+          <t>21x / 28x — Imobilizări și amortizarea lor</t>
+        </is>
+      </c>
+      <c r="C10" s="43">
+        <f>Declarații_CONTROL_BALANTA!B16</f>
+        <v>412000</v>
+      </c>
+      <c r="D10" s="43">
+        <f>Declarații_CONTROL_BALANTA!C16</f>
+        <v>412000</v>
+      </c>
+      <c r="E10" s="43">
+        <f>Declarații_CONTROL_BALANTA!B16-Declarații_CONTROL_BALANTA!C16</f>
+        <v>0</v>
+      </c>
+      <c r="F10" s="43" t="str">
+        <f>IF(ABS(E10)&lt;0.01,"OK","ATENȚIE — analiticul diferă de sintetic cu "&amp;TEXT(E10,"#,##0.00")&amp;" lei; cauza tipică: operațiune după închiderea de lună, fără refacerea ei")</f>
+        <v>OK</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="43" t="inlineStr">
+        <is>
+          <t>C-37</t>
+        </is>
+      </c>
+      <c r="B11" s="43" t="inlineStr">
+        <is>
+          <t>446 — Alte impozite și taxe</t>
+        </is>
+      </c>
+      <c r="C11" s="43">
+        <f>Declarații_CONTROL_BALANTA!B17</f>
+        <v>12240</v>
+      </c>
+      <c r="D11" s="43">
+        <f>Declarații_CONTROL_BALANTA!C17</f>
+        <v>12240</v>
+      </c>
+      <c r="E11" s="43">
+        <f>Declarații_CONTROL_BALANTA!B17-Declarații_CONTROL_BALANTA!C17</f>
+        <v>0</v>
+      </c>
+      <c r="F11" s="43" t="str">
+        <f>IF(ABS(E11)&lt;0.01,"OK","ATENȚIE — analiticul diferă de sintetic cu "&amp;TEXT(E11,"#,##0.00")&amp;" lei; cauza tipică: operațiune după închiderea de lună, fără refacerea ei")</f>
+        <v>OK</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="43" t="inlineStr">
+        <is>
+          <t>C-37</t>
+        </is>
+      </c>
+      <c r="B12" s="43" t="inlineStr">
+        <is>
+          <t>455 — Sume datorate asociaților</t>
+        </is>
+      </c>
+      <c r="C12" s="43">
+        <f>Declarații_CONTROL_BALANTA!B18</f>
+        <v>20000</v>
+      </c>
+      <c r="D12" s="43">
+        <f>Declarații_CONTROL_BALANTA!C18</f>
+        <v>20000</v>
+      </c>
+      <c r="E12" s="43">
+        <f>Declarații_CONTROL_BALANTA!B18-Declarații_CONTROL_BALANTA!C18</f>
+        <v>0</v>
+      </c>
+      <c r="F12" s="43" t="str">
+        <f>IF(ABS(E12)&lt;0.01,"OK","ATENȚIE — analiticul diferă de sintetic cu "&amp;TEXT(E12,"#,##0.00")&amp;" lei; cauza tipică: operațiune după închiderea de lună, fără refacerea ei")</f>
+        <v>OK</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="43" t="inlineStr">
+        <is>
+          <t>C-37</t>
+        </is>
+      </c>
+      <c r="B13" s="43" t="inlineStr">
+        <is>
+          <t>1012 — Capital subscris vărsat</t>
+        </is>
+      </c>
+      <c r="C13" s="43">
+        <f>Declarații_CONTROL_BALANTA!B19</f>
+        <v>30000</v>
+      </c>
+      <c r="D13" s="43">
+        <f>Declarații_CONTROL_BALANTA!C19</f>
+        <v>30000</v>
+      </c>
+      <c r="E13" s="43">
+        <f>Declarații_CONTROL_BALANTA!B19-Declarații_CONTROL_BALANTA!C19</f>
+        <v>0</v>
+      </c>
+      <c r="F13" s="43" t="str">
+        <f>IF(ABS(E13)&lt;0.01,"OK","ATENȚIE — analiticul diferă de sintetic cu "&amp;TEXT(E13,"#,##0.00")&amp;" lei; cauza tipică: operațiune după închiderea de lună, fără refacerea ei")</f>
+        <v>OK</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="42" t="inlineStr">
+        <is>
+          <t>V2 — 121 cu clasele 6 și 7</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="65" t="inlineStr">
+        <is>
+          <t>Cod</t>
+        </is>
+      </c>
+      <c r="B16" s="65" t="inlineStr">
+        <is>
+          <t>Ce verifică</t>
+        </is>
+      </c>
+      <c r="C16" s="65" t="inlineStr">
+        <is>
+          <t>Calculat</t>
+        </is>
+      </c>
+      <c r="D16" s="65" t="inlineStr">
+        <is>
+          <t>Din balanță</t>
+        </is>
+      </c>
+      <c r="E16" s="65" t="inlineStr">
+        <is>
+          <t>Diferență</t>
+        </is>
+      </c>
+      <c r="F16" s="65" t="inlineStr">
+        <is>
+          <t>Verdict</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="43" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="B17" s="43" t="inlineStr">
+        <is>
+          <t>clasa 7 − clasa 6 = sold 121</t>
+        </is>
+      </c>
+      <c r="C17" s="43">
+        <f>Declarații_CONTROL_BALANTA!B23-Declarații_CONTROL_BALANTA!B22</f>
+        <v>80000</v>
+      </c>
+      <c r="D17" s="43">
+        <f>Declarații_CONTROL_BALANTA!B24</f>
+        <v>80000</v>
+      </c>
+      <c r="E17" s="43">
+        <f>Declarații_CONTROL_BALANTA!B24-(Declarații_CONTROL_BALANTA!B23-Declarații_CONTROL_BALANTA!B22)</f>
+        <v>0</v>
+      </c>
+      <c r="F17" s="43" t="str">
+        <f>IF(ABS(E17)&lt;0.01,"OK — 6 și 7 s-au închis complet în 121","ATENȚIE — cel mai probabil 121 din anul precedent n-a fost închis; se vede la bilanț, când cifrele nu se leagă")</f>
+        <v>OK — 6 și 7 s-au închis complet în 121</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="42" t="inlineStr">
+        <is>
+          <t>V3 — solduri cu semn contrar naturii contului</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="65" t="inlineStr">
+        <is>
+          <t>Cod</t>
+        </is>
+      </c>
+      <c r="B20" s="65" t="inlineStr">
+        <is>
+          <t>Ce verifică</t>
+        </is>
+      </c>
+      <c r="C20" s="65" t="inlineStr">
+        <is>
+          <t>Sold cu semn</t>
+        </is>
+      </c>
+      <c r="D20" s="65" t="inlineStr">
+        <is>
+          <t>Sens normal</t>
+        </is>
+      </c>
+      <c r="E20" s="65" t="inlineStr">
+        <is>
+          <t>Abatere</t>
+        </is>
+      </c>
+      <c r="F20" s="65" t="inlineStr">
+        <is>
+          <t>Verdict</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="43" t="inlineStr">
+        <is>
+          <t>C-23</t>
+        </is>
+      </c>
+      <c r="B21" s="43" t="inlineStr">
+        <is>
+          <t>4111 — Activ, sold normal debitor</t>
+        </is>
+      </c>
+      <c r="C21" s="43">
+        <f>Declarații_CONTROL_BALANTA!B29</f>
+        <v>238400</v>
+      </c>
+      <c r="D21" s="43" t="inlineStr">
+        <is>
+          <t>Debitor</t>
+        </is>
+      </c>
+      <c r="E21" s="43">
+        <f>IF(Declarații_CONTROL_BALANTA!B29&lt;0,ABS(Declarații_CONTROL_BALANTA!B29),0)</f>
+        <v>0</v>
+      </c>
+      <c r="F21" s="43" t="str">
+        <f>IF(E21&lt;0.01,"OK","ATENȚIE — 4111 are sold contrar naturii: "&amp;TEXT(E21,"#,##0.00")&amp;" lei pe sensul greșit")</f>
+        <v>OK</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="43" t="inlineStr">
+        <is>
+          <t>C-23</t>
+        </is>
+      </c>
+      <c r="B22" s="43" t="inlineStr">
+        <is>
+          <t>401 — Pasiv, sold normal creditor</t>
+        </is>
+      </c>
+      <c r="C22" s="43">
+        <f>Declarații_CONTROL_BALANTA!B30</f>
+        <v>-176250</v>
+      </c>
+      <c r="D22" s="43" t="inlineStr">
+        <is>
+          <t>Creditor</t>
+        </is>
+      </c>
+      <c r="E22" s="43">
+        <f>IF(Declarații_CONTROL_BALANTA!B30&gt;0,ABS(Declarații_CONTROL_BALANTA!B30),0)</f>
+        <v>0</v>
+      </c>
+      <c r="F22" s="43" t="str">
+        <f>IF(E22&lt;0.01,"OK","ATENȚIE — 401 are sold contrar naturii: "&amp;TEXT(E22,"#,##0.00")&amp;" lei pe sensul greșit")</f>
+        <v>OK</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="43" t="inlineStr">
+        <is>
+          <t>C-23</t>
+        </is>
+      </c>
+      <c r="B23" s="43" t="inlineStr">
+        <is>
+          <t>409 — Activ, sold normal debitor</t>
+        </is>
+      </c>
+      <c r="C23" s="43">
+        <f>Declarații_CONTROL_BALANTA!B31</f>
+        <v>8500</v>
+      </c>
+      <c r="D23" s="43" t="inlineStr">
+        <is>
+          <t>Debitor</t>
+        </is>
+      </c>
+      <c r="E23" s="43">
+        <f>IF(Declarații_CONTROL_BALANTA!B31&lt;0,ABS(Declarații_CONTROL_BALANTA!B31),0)</f>
+        <v>0</v>
+      </c>
+      <c r="F23" s="43" t="str">
+        <f>IF(E23&lt;0.01,"OK","ATENȚIE — 409 are sold contrar naturii: "&amp;TEXT(E23,"#,##0.00")&amp;" lei pe sensul greșit")</f>
+        <v>OK</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="43" t="inlineStr">
+        <is>
+          <t>C-23</t>
+        </is>
+      </c>
+      <c r="B24" s="43" t="inlineStr">
+        <is>
+          <t>419 — Pasiv, sold normal creditor</t>
+        </is>
+      </c>
+      <c r="C24" s="43">
+        <f>Declarații_CONTROL_BALANTA!B32</f>
+        <v>-12100</v>
+      </c>
+      <c r="D24" s="43" t="inlineStr">
+        <is>
+          <t>Creditor</t>
+        </is>
+      </c>
+      <c r="E24" s="43">
+        <f>IF(Declarații_CONTROL_BALANTA!B32&gt;0,ABS(Declarații_CONTROL_BALANTA!B32),0)</f>
+        <v>0</v>
+      </c>
+      <c r="F24" s="43" t="str">
+        <f>IF(E24&lt;0.01,"OK","ATENȚIE — 419 are sold contrar naturii: "&amp;TEXT(E24,"#,##0.00")&amp;" lei pe sensul greșit")</f>
+        <v>OK</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="43" t="inlineStr">
+        <is>
+          <t>C-23</t>
+        </is>
+      </c>
+      <c r="B25" s="43" t="inlineStr">
+        <is>
+          <t>4551 — Pasiv, sold normal creditor</t>
+        </is>
+      </c>
+      <c r="C25" s="43">
+        <f>Declarații_CONTROL_BALANTA!B33</f>
+        <v>-20000</v>
+      </c>
+      <c r="D25" s="43" t="inlineStr">
+        <is>
+          <t>Creditor</t>
+        </is>
+      </c>
+      <c r="E25" s="43">
+        <f>IF(Declarații_CONTROL_BALANTA!B33&gt;0,ABS(Declarații_CONTROL_BALANTA!B33),0)</f>
+        <v>0</v>
+      </c>
+      <c r="F25" s="43" t="str">
+        <f>IF(E25&lt;0.01,"OK","ATENȚIE — 4551 are sold contrar naturii: "&amp;TEXT(E25,"#,##0.00")&amp;" lei pe sensul greșit")</f>
+        <v>OK</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="43" t="inlineStr">
+        <is>
+          <t>C-23</t>
+        </is>
+      </c>
+      <c r="B26" s="43" t="inlineStr">
+        <is>
+          <t>5191 — Pasiv, sold normal creditor</t>
+        </is>
+      </c>
+      <c r="C26" s="43">
+        <f>Declarații_CONTROL_BALANTA!B34</f>
+        <v>-1000</v>
+      </c>
+      <c r="D26" s="43" t="inlineStr">
+        <is>
+          <t>Creditor</t>
+        </is>
+      </c>
+      <c r="E26" s="43">
+        <f>IF(Declarații_CONTROL_BALANTA!B34&gt;0,ABS(Declarații_CONTROL_BALANTA!B34),0)</f>
+        <v>0</v>
+      </c>
+      <c r="F26" s="43" t="str">
+        <f>IF(E26&lt;0.01,"OK","ATENȚIE — 5191 are sold contrar naturii: "&amp;TEXT(E26,"#,##0.00")&amp;" lei pe sensul greșit")</f>
+        <v>OK</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="43" t="inlineStr">
+        <is>
+          <t>C-23</t>
+        </is>
+      </c>
+      <c r="B27" s="43" t="inlineStr">
+        <is>
+          <t>444 — Pasiv, sold normal creditor</t>
+        </is>
+      </c>
+      <c r="C27" s="43">
+        <f>Declarații_CONTROL_BALANTA!B35</f>
+        <v>-3250</v>
+      </c>
+      <c r="D27" s="43" t="inlineStr">
+        <is>
+          <t>Creditor</t>
+        </is>
+      </c>
+      <c r="E27" s="43">
+        <f>IF(Declarații_CONTROL_BALANTA!B35&gt;0,ABS(Declarații_CONTROL_BALANTA!B35),0)</f>
+        <v>0</v>
+      </c>
+      <c r="F27" s="43" t="str">
+        <f>IF(E27&lt;0.01,"OK","ATENȚIE — 444 are sold contrar naturii: "&amp;TEXT(E27,"#,##0.00")&amp;" lei pe sensul greșit")</f>
+        <v>OK</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="43" t="inlineStr">
+        <is>
+          <t>C-23</t>
+        </is>
+      </c>
+      <c r="B28" s="43" t="inlineStr">
+        <is>
+          <t>4282 — Activ, sold normal debitor</t>
+        </is>
+      </c>
+      <c r="C28" s="43">
+        <f>Declarații_CONTROL_BALANTA!B36</f>
+        <v>1200</v>
+      </c>
+      <c r="D28" s="43" t="inlineStr">
+        <is>
+          <t>Debitor</t>
+        </is>
+      </c>
+      <c r="E28" s="43">
+        <f>IF(Declarații_CONTROL_BALANTA!B36&lt;0,ABS(Declarații_CONTROL_BALANTA!B36),0)</f>
+        <v>0</v>
+      </c>
+      <c r="F28" s="43" t="str">
+        <f>IF(E28&lt;0.01,"OK","ATENȚIE — 4282 are sold contrar naturii: "&amp;TEXT(E28,"#,##0.00")&amp;" lei pe sensul greșit")</f>
+        <v>OK</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="42" t="inlineStr">
+        <is>
+          <t>V4 — continuitatea total-sumelor (la preluare)</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="65" t="inlineStr">
+        <is>
+          <t>Cod</t>
+        </is>
+      </c>
+      <c r="B31" s="65" t="inlineStr">
+        <is>
+          <t>Ce verifică</t>
+        </is>
+      </c>
+      <c r="C31" s="65" t="inlineStr">
+        <is>
+          <t>Luna anterioară</t>
+        </is>
+      </c>
+      <c r="D31" s="65" t="inlineStr">
+        <is>
+          <t>Luna curentă</t>
+        </is>
+      </c>
+      <c r="E31" s="65" t="inlineStr">
+        <is>
+          <t>Creștere</t>
+        </is>
+      </c>
+      <c r="F31" s="65" t="inlineStr">
+        <is>
+          <t>Verdict</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="43" t="inlineStr">
+        <is>
+          <t>C-39</t>
+        </is>
+      </c>
+      <c r="B32" s="43" t="inlineStr">
+        <is>
+          <t>total sume debitoare cresc monoton</t>
+        </is>
+      </c>
+      <c r="C32" s="43">
+        <f>Declarații_CONTROL_BALANTA!B39</f>
+        <v>2450000</v>
+      </c>
+      <c r="D32" s="43">
+        <f>Declarații_CONTROL_BALANTA!B41</f>
+        <v>2780000</v>
+      </c>
+      <c r="E32" s="43">
+        <f>IF(Declarații_CONTROL_BALANTA!B8&lt;&gt;"DA",0,MIN(0,Declarații_CONTROL_BALANTA!B41-Declarații_CONTROL_BALANTA!B39))</f>
+        <v>0</v>
+      </c>
+      <c r="F32" s="43" t="str">
+        <f>IF(Declarații_CONTROL_BALANTA!B8&lt;&gt;"DA","— (nu e lună de preluare)",IF(E32&gt;=0,"OK — total sumele au continuitate","ATENȚIE — total sumele au SCĂZUT: s-au preluat soldurile ca sold inițial, nu total sumele. Orice verificare pe rulaj devine falsă"))</f>
+        <v>— (nu e lună de preluare)</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="43" t="inlineStr">
+        <is>
+          <t>C-39</t>
+        </is>
+      </c>
+      <c r="B33" s="43" t="inlineStr">
+        <is>
+          <t>total sume creditoare cresc monoton</t>
+        </is>
+      </c>
+      <c r="C33" s="43">
+        <f>Declarații_CONTROL_BALANTA!B40</f>
+        <v>2450000</v>
+      </c>
+      <c r="D33" s="43">
+        <f>Declarații_CONTROL_BALANTA!B42</f>
+        <v>2780000</v>
+      </c>
+      <c r="E33" s="43">
+        <f>IF(Declarații_CONTROL_BALANTA!B8&lt;&gt;"DA",0,MIN(0,Declarații_CONTROL_BALANTA!B42-Declarații_CONTROL_BALANTA!B40))</f>
+        <v>0</v>
+      </c>
+      <c r="F33" s="43" t="str">
+        <f>IF(Declarații_CONTROL_BALANTA!B8&lt;&gt;"DA","— (nu e lună de preluare)",IF(E33&gt;=0,"OK — total sumele au continuitate","ATENȚIE — total sumele au SCĂZUT: s-au preluat soldurile ca sold inițial, nu total sumele. Orice verificare pe rulaj devine falsă"))</f>
+        <v>— (nu e lună de preluare)</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="42" t="inlineStr">
+        <is>
+          <t>Control final</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="43" t="inlineStr">
+        <is>
+          <t>Check — toate verificările balanței</t>
+        </is>
+      </c>
+      <c r="B36" s="43">
+        <f>ABS(E6)+ABS(E7)+ABS(E8)+ABS(E9)+ABS(E10)+ABS(E11)+ABS(E12)+ABS(E13)+ABS(E17)+ABS(E21)+ABS(E22)+ABS(E23)+ABS(E24)+ABS(E25)+ABS(E26)+ABS(E27)+ABS(E28)+ABS(E32)+ABS(E33)</f>
+        <v>0</v>
+      </c>
+      <c r="C36" s="43" t="str">
+        <f>IF(ABS(B36)&lt;0.01,"OK — balanța e coerentă pe toate verificările","EROARE — vezi foaia Abateri")</f>
+        <v>OK — balanța e coerentă pe toate verificările</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet96.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" style="40" min="1" max="1"/>
+    <col width="12" customWidth="1" style="40" min="2" max="2"/>
+    <col width="44" customWidth="1" style="40" min="3" max="3"/>
+    <col width="16" customWidth="1" style="40" min="4" max="4"/>
+    <col width="60" customWidth="1" style="40" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="41" t="inlineStr">
+        <is>
+          <t>MOD_CONTROL_BALANTA — Abateri</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="44" t="inlineStr">
+        <is>
+          <t>Coloana „Include” spune DA doar unde verificarea n-a trecut. Lista e completă: dacă toate sunt NU, balanța e coerentă.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="65" t="inlineStr">
+        <is>
+          <t>Include</t>
+        </is>
+      </c>
+      <c r="B4" s="65" t="inlineStr">
+        <is>
+          <t>Cod</t>
+        </is>
+      </c>
+      <c r="C4" s="65" t="inlineStr">
+        <is>
+          <t>Ce nu s-a potrivit</t>
+        </is>
+      </c>
+      <c r="D4" s="65" t="inlineStr">
+        <is>
+          <t>Diferență</t>
+        </is>
+      </c>
+      <c r="E4" s="65" t="inlineStr">
+        <is>
+          <t>Ce se face</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="43" t="str">
+        <f>IF(ABS(Verificări_CONTROL_BALANTA!E6)&lt;0.01,"NU","DA")</f>
+        <v>NU</v>
+      </c>
+      <c r="B5" s="43" t="inlineStr">
+        <is>
+          <t>C-37</t>
+        </is>
+      </c>
+      <c r="C5" s="43" t="inlineStr">
+        <is>
+          <t>512x analitic ↔ sintetic</t>
+        </is>
+      </c>
+      <c r="D5" s="43">
+        <f>Verificări_CONTROL_BALANTA!E6</f>
+        <v>0</v>
+      </c>
+      <c r="E5" s="43" t="inlineStr">
+        <is>
+          <t>Se reface închiderea de lună — cauza cea mai frecventă. Dacă persistă, se compară balanța analitică rând cu rând cu sursa externă din tabelul A, ca să se localizeze analiticul.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="43" t="str">
+        <f>IF(ABS(Verificări_CONTROL_BALANTA!E7)&lt;0.01,"NU","DA")</f>
+        <v>NU</v>
+      </c>
+      <c r="B6" s="43" t="inlineStr">
+        <is>
+          <t>C-37</t>
+        </is>
+      </c>
+      <c r="C6" s="43" t="inlineStr">
+        <is>
+          <t>4111 analitic ↔ sintetic</t>
+        </is>
+      </c>
+      <c r="D6" s="43">
+        <f>Verificări_CONTROL_BALANTA!E7</f>
+        <v>0</v>
+      </c>
+      <c r="E6" s="43" t="inlineStr">
+        <is>
+          <t>Se reface închiderea de lună — cauza cea mai frecventă. Dacă persistă, se compară balanța analitică rând cu rând cu sursa externă din tabelul A, ca să se localizeze analiticul.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="43" t="str">
+        <f>IF(ABS(Verificări_CONTROL_BALANTA!E8)&lt;0.01,"NU","DA")</f>
+        <v>NU</v>
+      </c>
+      <c r="B7" s="43" t="inlineStr">
+        <is>
+          <t>C-37</t>
+        </is>
+      </c>
+      <c r="C7" s="43" t="inlineStr">
+        <is>
+          <t>401 analitic ↔ sintetic</t>
+        </is>
+      </c>
+      <c r="D7" s="43">
+        <f>Verificări_CONTROL_BALANTA!E8</f>
+        <v>0</v>
+      </c>
+      <c r="E7" s="43" t="inlineStr">
+        <is>
+          <t>Se reface închiderea de lună — cauza cea mai frecventă. Dacă persistă, se compară balanța analitică rând cu rând cu sursa externă din tabelul A, ca să se localizeze analiticul.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="43" t="str">
+        <f>IF(ABS(Verificări_CONTROL_BALANTA!E9)&lt;0.01,"NU","DA")</f>
+        <v>NU</v>
+      </c>
+      <c r="B8" s="43" t="inlineStr">
+        <is>
+          <t>C-37</t>
+        </is>
+      </c>
+      <c r="C8" s="43" t="inlineStr">
+        <is>
+          <t>542 analitic ↔ sintetic</t>
+        </is>
+      </c>
+      <c r="D8" s="43">
+        <f>Verificări_CONTROL_BALANTA!E9</f>
+        <v>0</v>
+      </c>
+      <c r="E8" s="43" t="inlineStr">
+        <is>
+          <t>Se reface închiderea de lună — cauza cea mai frecventă. Dacă persistă, se compară balanța analitică rând cu rând cu sursa externă din tabelul A, ca să se localizeze analiticul.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="43" t="str">
+        <f>IF(ABS(Verificări_CONTROL_BALANTA!E10)&lt;0.01,"NU","DA")</f>
+        <v>NU</v>
+      </c>
+      <c r="B9" s="43" t="inlineStr">
+        <is>
+          <t>C-37</t>
+        </is>
+      </c>
+      <c r="C9" s="43" t="inlineStr">
+        <is>
+          <t>21x / 28x analitic ↔ sintetic</t>
+        </is>
+      </c>
+      <c r="D9" s="43">
+        <f>Verificări_CONTROL_BALANTA!E10</f>
+        <v>0</v>
+      </c>
+      <c r="E9" s="43" t="inlineStr">
+        <is>
+          <t>Se reface închiderea de lună — cauza cea mai frecventă. Dacă persistă, se compară balanța analitică rând cu rând cu sursa externă din tabelul A, ca să se localizeze analiticul.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="43" t="str">
+        <f>IF(ABS(Verificări_CONTROL_BALANTA!E11)&lt;0.01,"NU","DA")</f>
+        <v>NU</v>
+      </c>
+      <c r="B10" s="43" t="inlineStr">
+        <is>
+          <t>C-37</t>
+        </is>
+      </c>
+      <c r="C10" s="43" t="inlineStr">
+        <is>
+          <t>446 analitic ↔ sintetic</t>
+        </is>
+      </c>
+      <c r="D10" s="43">
+        <f>Verificări_CONTROL_BALANTA!E11</f>
+        <v>0</v>
+      </c>
+      <c r="E10" s="43" t="inlineStr">
+        <is>
+          <t>Se reface închiderea de lună — cauza cea mai frecventă. Dacă persistă, se compară balanța analitică rând cu rând cu sursa externă din tabelul A, ca să se localizeze analiticul.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="43" t="str">
+        <f>IF(ABS(Verificări_CONTROL_BALANTA!E12)&lt;0.01,"NU","DA")</f>
+        <v>NU</v>
+      </c>
+      <c r="B11" s="43" t="inlineStr">
+        <is>
+          <t>C-37</t>
+        </is>
+      </c>
+      <c r="C11" s="43" t="inlineStr">
+        <is>
+          <t>455 analitic ↔ sintetic</t>
+        </is>
+      </c>
+      <c r="D11" s="43">
+        <f>Verificări_CONTROL_BALANTA!E12</f>
+        <v>0</v>
+      </c>
+      <c r="E11" s="43" t="inlineStr">
+        <is>
+          <t>Se reface închiderea de lună — cauza cea mai frecventă. Dacă persistă, se compară balanța analitică rând cu rând cu sursa externă din tabelul A, ca să se localizeze analiticul.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="43" t="str">
+        <f>IF(ABS(Verificări_CONTROL_BALANTA!E13)&lt;0.01,"NU","DA")</f>
+        <v>NU</v>
+      </c>
+      <c r="B12" s="43" t="inlineStr">
+        <is>
+          <t>C-37</t>
+        </is>
+      </c>
+      <c r="C12" s="43" t="inlineStr">
+        <is>
+          <t>1012 analitic ↔ sintetic</t>
+        </is>
+      </c>
+      <c r="D12" s="43">
+        <f>Verificări_CONTROL_BALANTA!E13</f>
+        <v>0</v>
+      </c>
+      <c r="E12" s="43" t="inlineStr">
+        <is>
+          <t>Se reface închiderea de lună — cauza cea mai frecventă. Dacă persistă, se compară balanța analitică rând cu rând cu sursa externă din tabelul A, ca să se localizeze analiticul.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="43" t="str">
+        <f>IF(ABS(Verificări_CONTROL_BALANTA!E17)&lt;0.01,"NU","DA")</f>
+        <v>NU</v>
+      </c>
+      <c r="B13" s="43" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C13" s="43" t="inlineStr">
+        <is>
+          <t>121 vs. clasele 6 și 7</t>
+        </is>
+      </c>
+      <c r="D13" s="43">
+        <f>Verificări_CONTROL_BALANTA!E17</f>
+        <v>0</v>
+      </c>
+      <c r="E13" s="43" t="inlineStr">
+        <is>
+          <t>Se verifică dacă 121 din anul precedent a fost închis. Nu există automatism ca la TVA: închiderea lui 121 se face manual, la începutul exercițiului următor.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="43" t="str">
+        <f>IF(ABS(Verificări_CONTROL_BALANTA!E21)&lt;0.01,"NU","DA")</f>
+        <v>NU</v>
+      </c>
+      <c r="B14" s="43" t="inlineStr">
+        <is>
+          <t>C-23</t>
+        </is>
+      </c>
+      <c r="C14" s="43" t="inlineStr">
+        <is>
+          <t>4111 sens sold</t>
+        </is>
+      </c>
+      <c r="D14" s="43">
+        <f>Verificări_CONTROL_BALANTA!E21</f>
+        <v>0</v>
+      </c>
+      <c r="E14" s="43" t="inlineStr">
+        <is>
+          <t>Se caută operațiunea care a răsturnat soldul. Un cont de activ cu sold creditor e cel mai des un avans neînregistrat ca avans (vezi F-415).</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="43" t="str">
+        <f>IF(ABS(Verificări_CONTROL_BALANTA!E22)&lt;0.01,"NU","DA")</f>
+        <v>NU</v>
+      </c>
+      <c r="B15" s="43" t="inlineStr">
+        <is>
+          <t>C-23</t>
+        </is>
+      </c>
+      <c r="C15" s="43" t="inlineStr">
+        <is>
+          <t>401 sens sold</t>
+        </is>
+      </c>
+      <c r="D15" s="43">
+        <f>Verificări_CONTROL_BALANTA!E22</f>
+        <v>0</v>
+      </c>
+      <c r="E15" s="43" t="inlineStr">
+        <is>
+          <t>Se caută operațiunea care a răsturnat soldul. Un cont de activ cu sold creditor e cel mai des un avans neînregistrat ca avans (vezi F-415).</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="43" t="str">
+        <f>IF(ABS(Verificări_CONTROL_BALANTA!E23)&lt;0.01,"NU","DA")</f>
+        <v>NU</v>
+      </c>
+      <c r="B16" s="43" t="inlineStr">
+        <is>
+          <t>C-23</t>
+        </is>
+      </c>
+      <c r="C16" s="43" t="inlineStr">
+        <is>
+          <t>409 sens sold</t>
+        </is>
+      </c>
+      <c r="D16" s="43">
+        <f>Verificări_CONTROL_BALANTA!E23</f>
+        <v>0</v>
+      </c>
+      <c r="E16" s="43" t="inlineStr">
+        <is>
+          <t>Se caută operațiunea care a răsturnat soldul. Un cont de activ cu sold creditor e cel mai des un avans neînregistrat ca avans (vezi F-415).</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="43" t="str">
+        <f>IF(ABS(Verificări_CONTROL_BALANTA!E24)&lt;0.01,"NU","DA")</f>
+        <v>NU</v>
+      </c>
+      <c r="B17" s="43" t="inlineStr">
+        <is>
+          <t>C-23</t>
+        </is>
+      </c>
+      <c r="C17" s="43" t="inlineStr">
+        <is>
+          <t>419 sens sold</t>
+        </is>
+      </c>
+      <c r="D17" s="43">
+        <f>Verificări_CONTROL_BALANTA!E24</f>
+        <v>0</v>
+      </c>
+      <c r="E17" s="43" t="inlineStr">
+        <is>
+          <t>Se caută operațiunea care a răsturnat soldul. Un cont de activ cu sold creditor e cel mai des un avans neînregistrat ca avans (vezi F-415).</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="43" t="str">
+        <f>IF(ABS(Verificări_CONTROL_BALANTA!E25)&lt;0.01,"NU","DA")</f>
+        <v>NU</v>
+      </c>
+      <c r="B18" s="43" t="inlineStr">
+        <is>
+          <t>C-23</t>
+        </is>
+      </c>
+      <c r="C18" s="43" t="inlineStr">
+        <is>
+          <t>4551 sens sold</t>
+        </is>
+      </c>
+      <c r="D18" s="43">
+        <f>Verificări_CONTROL_BALANTA!E25</f>
+        <v>0</v>
+      </c>
+      <c r="E18" s="43" t="inlineStr">
+        <is>
+          <t>Se caută operațiunea care a răsturnat soldul. Un cont de activ cu sold creditor e cel mai des un avans neînregistrat ca avans (vezi F-415).</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="43" t="str">
+        <f>IF(ABS(Verificări_CONTROL_BALANTA!E26)&lt;0.01,"NU","DA")</f>
+        <v>NU</v>
+      </c>
+      <c r="B19" s="43" t="inlineStr">
+        <is>
+          <t>C-23</t>
+        </is>
+      </c>
+      <c r="C19" s="43" t="inlineStr">
+        <is>
+          <t>5191 sens sold</t>
+        </is>
+      </c>
+      <c r="D19" s="43">
+        <f>Verificări_CONTROL_BALANTA!E26</f>
+        <v>0</v>
+      </c>
+      <c r="E19" s="43" t="inlineStr">
+        <is>
+          <t>Se caută operațiunea care a răsturnat soldul. Un cont de activ cu sold creditor e cel mai des un avans neînregistrat ca avans (vezi F-415).</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="43" t="str">
+        <f>IF(ABS(Verificări_CONTROL_BALANTA!E27)&lt;0.01,"NU","DA")</f>
+        <v>NU</v>
+      </c>
+      <c r="B20" s="43" t="inlineStr">
+        <is>
+          <t>C-23</t>
+        </is>
+      </c>
+      <c r="C20" s="43" t="inlineStr">
+        <is>
+          <t>444 sens sold</t>
+        </is>
+      </c>
+      <c r="D20" s="43">
+        <f>Verificări_CONTROL_BALANTA!E27</f>
+        <v>0</v>
+      </c>
+      <c r="E20" s="43" t="inlineStr">
+        <is>
+          <t>Se caută operațiunea care a răsturnat soldul. Un cont de activ cu sold creditor e cel mai des un avans neînregistrat ca avans (vezi F-415).</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="43" t="str">
+        <f>IF(ABS(Verificări_CONTROL_BALANTA!E28)&lt;0.01,"NU","DA")</f>
+        <v>NU</v>
+      </c>
+      <c r="B21" s="43" t="inlineStr">
+        <is>
+          <t>C-23</t>
+        </is>
+      </c>
+      <c r="C21" s="43" t="inlineStr">
+        <is>
+          <t>4282 sens sold</t>
+        </is>
+      </c>
+      <c r="D21" s="43">
+        <f>Verificări_CONTROL_BALANTA!E28</f>
+        <v>0</v>
+      </c>
+      <c r="E21" s="43" t="inlineStr">
+        <is>
+          <t>Se caută operațiunea care a răsturnat soldul. Un cont de activ cu sold creditor e cel mai des un avans neînregistrat ca avans (vezi F-415).</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="43" t="str">
+        <f>IF(ABS(Verificări_CONTROL_BALANTA!E32)&lt;0.01,"NU","DA")</f>
+        <v>NU</v>
+      </c>
+      <c r="B22" s="43" t="inlineStr">
+        <is>
+          <t>C-39</t>
+        </is>
+      </c>
+      <c r="C22" s="43" t="inlineStr">
+        <is>
+          <t>total sume debitoare</t>
+        </is>
+      </c>
+      <c r="D22" s="43">
+        <f>Verificări_CONTROL_BALANTA!E32</f>
+        <v>0</v>
+      </c>
+      <c r="E22" s="43" t="inlineStr">
+        <is>
+          <t>Se reface preluarea: se introduc TOTAL SUMELE debitoare și creditoare din balanța de preluare, nu soldurile. Altfel rulajele anului pornesc de la zero din luna preluării.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="43" t="str">
+        <f>IF(ABS(Verificări_CONTROL_BALANTA!E33)&lt;0.01,"NU","DA")</f>
+        <v>NU</v>
+      </c>
+      <c r="B23" s="43" t="inlineStr">
+        <is>
+          <t>C-39</t>
+        </is>
+      </c>
+      <c r="C23" s="43" t="inlineStr">
+        <is>
+          <t>total sume creditoare</t>
+        </is>
+      </c>
+      <c r="D23" s="43">
+        <f>Verificări_CONTROL_BALANTA!E33</f>
+        <v>0</v>
+      </c>
+      <c r="E23" s="43" t="inlineStr">
+        <is>
+          <t>Se reface preluarea: se introduc TOTAL SUMELE debitoare și creditoare din balanța de preluare, nu soldurile. Altfel rulajele anului pornesc de la zero din luna preluării.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="43" t="inlineStr">
+        <is>
+          <t>Check — număr de abateri</t>
+        </is>
+      </c>
+      <c r="B25" s="43">
+        <f>COUNTIF(A5:A23,"DA")</f>
+        <v>0</v>
+      </c>
+      <c r="C25" s="43" t="str">
+        <f>IF(B25=0,"OK — nicio abatere","ATENȚIE — "&amp;B25&amp;" verificări nu trec")</f>
+        <v>OK — nicio abatere</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet97.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:E35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -43741,7 +46600,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet94.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet98.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -44094,7 +46953,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet95.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet99.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -44638,381 +47497,4 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet96.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:E18"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="10" customWidth="1" style="40" min="1" max="1"/>
-    <col width="12" customWidth="1" style="40" min="2" max="2"/>
-    <col width="46" customWidth="1" style="40" min="3" max="3"/>
-    <col width="16" customWidth="1" style="40" min="4" max="4"/>
-    <col width="56" customWidth="1" style="40" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="41" t="inlineStr">
-        <is>
-          <t>MOD_INCHIDERE_LUNARA — Abateri</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="44" t="inlineStr">
-        <is>
-          <t>Coloana „Include” spune DA doar unde corelația nu s-a potrivit. Lista e completă: dacă toate sunt NU, luna e curată.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="65" t="inlineStr">
-        <is>
-          <t>Include</t>
-        </is>
-      </c>
-      <c r="B4" s="65" t="inlineStr">
-        <is>
-          <t>Cod</t>
-        </is>
-      </c>
-      <c r="C4" s="65" t="inlineStr">
-        <is>
-          <t>Ce nu s-a potrivit</t>
-        </is>
-      </c>
-      <c r="D4" s="65" t="inlineStr">
-        <is>
-          <t>Diferență</t>
-        </is>
-      </c>
-      <c r="E4" s="65" t="inlineStr">
-        <is>
-          <t>Ce se face</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="43" t="str">
-        <f>IF(ABS(Verificări_INCHIDERE_LUNARA!E6)&lt;0.01,"NU","DA")</f>
-        <v>NU</v>
-      </c>
-      <c r="B5" s="43" t="inlineStr">
-        <is>
-          <t>C-25</t>
-        </is>
-      </c>
-      <c r="C5" s="43" t="inlineStr">
-        <is>
-          <t>444 Impozit pe venituri din salarii</t>
-        </is>
-      </c>
-      <c r="D5" s="43">
-        <f>Verificări_INCHIDERE_LUNARA!E6</f>
-        <v>0</v>
-      </c>
-      <c r="E5" s="43" t="inlineStr">
-        <is>
-          <t>Se verifică fișa de plătitor din SPV. Stopaj nevirat peste 30 de zile = răspundere penală, nu întârziere.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="43" t="str">
-        <f>IF(ABS(Verificări_INCHIDERE_LUNARA!E7)&lt;0.01,"NU","DA")</f>
-        <v>NU</v>
-      </c>
-      <c r="B6" s="43" t="inlineStr">
-        <is>
-          <t>C-26</t>
-        </is>
-      </c>
-      <c r="C6" s="43" t="inlineStr">
-        <is>
-          <t>4315 CAS — contribuția de asigurări sociale</t>
-        </is>
-      </c>
-      <c r="D6" s="43">
-        <f>Verificări_INCHIDERE_LUNARA!E7</f>
-        <v>0</v>
-      </c>
-      <c r="E6" s="43" t="inlineStr">
-        <is>
-          <t>Se confruntă cu D112. Dacă e eșalonare, se notează; altfel e restanță.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="43" t="str">
-        <f>IF(ABS(Verificări_INCHIDERE_LUNARA!E8)&lt;0.01,"NU","DA")</f>
-        <v>NU</v>
-      </c>
-      <c r="B7" s="43" t="inlineStr">
-        <is>
-          <t>C-26</t>
-        </is>
-      </c>
-      <c r="C7" s="43" t="inlineStr">
-        <is>
-          <t>4316 CASS — asigurări sociale de sănătate</t>
-        </is>
-      </c>
-      <c r="D7" s="43">
-        <f>Verificări_INCHIDERE_LUNARA!E8</f>
-        <v>0</v>
-      </c>
-      <c r="E7" s="43" t="inlineStr">
-        <is>
-          <t>Se confruntă cu D112. Dacă e eșalonare, se notează; altfel e restanță.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="43" t="str">
-        <f>IF(ABS(Verificări_INCHIDERE_LUNARA!E9)&lt;0.01,"NU","DA")</f>
-        <v>NU</v>
-      </c>
-      <c r="B8" s="43" t="inlineStr">
-        <is>
-          <t>C-26</t>
-        </is>
-      </c>
-      <c r="C8" s="43" t="inlineStr">
-        <is>
-          <t>436 CAM — contribuția asiguratorie pentru muncă</t>
-        </is>
-      </c>
-      <c r="D8" s="43">
-        <f>Verificări_INCHIDERE_LUNARA!E9</f>
-        <v>0</v>
-      </c>
-      <c r="E8" s="43" t="inlineStr">
-        <is>
-          <t>Se confruntă cu D112. Dacă e eșalonare, se notează; altfel e restanță.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="43" t="str">
-        <f>IF(ABS(Verificări_INCHIDERE_LUNARA!E10)&lt;0.01,"NU","DA")</f>
-        <v>NU</v>
-      </c>
-      <c r="B9" s="43" t="inlineStr">
-        <is>
-          <t>C-28</t>
-        </is>
-      </c>
-      <c r="C9" s="43" t="inlineStr">
-        <is>
-          <t>427 Rețineri din salarii datorate terților</t>
-        </is>
-      </c>
-      <c r="D9" s="43">
-        <f>Verificări_INCHIDERE_LUNARA!E10</f>
-        <v>0</v>
-      </c>
-      <c r="E9" s="43" t="inlineStr">
-        <is>
-          <t>Se virează imediat. Banii sunt ai salariatului, opriți pentru altcineva.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="43" t="str">
-        <f>IF(ABS(Verificări_INCHIDERE_LUNARA!E14)&lt;0.01,"NU","DA")</f>
-        <v>NU</v>
-      </c>
-      <c r="B10" s="43" t="inlineStr">
-        <is>
-          <t>C-24</t>
-        </is>
-      </c>
-      <c r="C10" s="43" t="inlineStr">
-        <is>
-          <t>421 + 423 vs. stat</t>
-        </is>
-      </c>
-      <c r="D10" s="43">
-        <f>Verificări_INCHIDERE_LUNARA!E14</f>
-        <v>0</v>
-      </c>
-      <c r="E10" s="43" t="inlineStr">
-        <is>
-          <t>Se scot statele lună de lună și se caută luna în care s-a rupt. Cauza tipică: plată pe alt cont decât 421.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="43" t="str">
-        <f>IF(ABS(Verificări_INCHIDERE_LUNARA!E18)&lt;0.01,"NU","DA")</f>
-        <v>NU</v>
-      </c>
-      <c r="B11" s="43" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C11" s="43" t="inlineStr">
-        <is>
-          <t>473 sold zero</t>
-        </is>
-      </c>
-      <c r="D11" s="43">
-        <f>Verificări_INCHIDERE_LUNARA!E18</f>
-        <v>0</v>
-      </c>
-      <c r="E11" s="43" t="inlineStr">
-        <is>
-          <t>Se identifică operațiunea neterminată și se închide. Un sold reportat pe un cont de tranzit ascunde ceva.</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="43" t="str">
-        <f>IF(ABS(Verificări_INCHIDERE_LUNARA!E19)&lt;0.01,"NU","DA")</f>
-        <v>NU</v>
-      </c>
-      <c r="B12" s="43" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C12" s="43" t="inlineStr">
-        <is>
-          <t>581 sold zero</t>
-        </is>
-      </c>
-      <c r="D12" s="43">
-        <f>Verificări_INCHIDERE_LUNARA!E19</f>
-        <v>0</v>
-      </c>
-      <c r="E12" s="43" t="inlineStr">
-        <is>
-          <t>Se identifică operațiunea neterminată și se închide. Un sold reportat pe un cont de tranzit ascunde ceva.</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="43" t="str">
-        <f>IF(ABS(Verificări_INCHIDERE_LUNARA!E20)&lt;0.01,"NU","DA")</f>
-        <v>NU</v>
-      </c>
-      <c r="B13" s="43" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C13" s="43" t="inlineStr">
-        <is>
-          <t>542 sold zero</t>
-        </is>
-      </c>
-      <c r="D13" s="43">
-        <f>Verificări_INCHIDERE_LUNARA!E20</f>
-        <v>0</v>
-      </c>
-      <c r="E13" s="43" t="inlineStr">
-        <is>
-          <t>Se identifică operațiunea neterminată și se închide. Un sold reportat pe un cont de tranzit ascunde ceva.</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="43" t="str">
-        <f>IF(ABS(Verificări_INCHIDERE_LUNARA!E21)&lt;0.01,"NU","DA")</f>
-        <v>NU</v>
-      </c>
-      <c r="B14" s="43" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C14" s="43" t="inlineStr">
-        <is>
-          <t>4382 sold zero</t>
-        </is>
-      </c>
-      <c r="D14" s="43">
-        <f>Verificări_INCHIDERE_LUNARA!E21</f>
-        <v>0</v>
-      </c>
-      <c r="E14" s="43" t="inlineStr">
-        <is>
-          <t>Se identifică operațiunea neterminată și se închide. Un sold reportat pe un cont de tranzit ascunde ceva.</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="43" t="str">
-        <f>IF(ABS(Verificări_INCHIDERE_LUNARA!E25)&lt;0.01,"NU","DA")</f>
-        <v>NU</v>
-      </c>
-      <c r="B15" s="43" t="inlineStr">
-        <is>
-          <t>C-27</t>
-        </is>
-      </c>
-      <c r="C15" s="43" t="inlineStr">
-        <is>
-          <t>CAM pe cifre</t>
-        </is>
-      </c>
-      <c r="D15" s="43">
-        <f>Verificări_INCHIDERE_LUNARA!E25</f>
-        <v>0</v>
-      </c>
-      <c r="E15" s="43" t="inlineStr">
-        <is>
-          <t>Se verifică dacă luna are concedii medicale — CAM nu se datorează pe partea din FNUASS. Altfel, bază de calcul incompletă.</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="43" t="str">
-        <f>IF(ABS(Verificări_INCHIDERE_LUNARA!E26)&lt;0.01,"NU","DA")</f>
-        <v>NU</v>
-      </c>
-      <c r="B16" s="43" t="inlineStr">
-        <is>
-          <t>C-29</t>
-        </is>
-      </c>
-      <c r="C16" s="43" t="inlineStr">
-        <is>
-          <t>4423 vs. decont</t>
-        </is>
-      </c>
-      <c r="D16" s="43">
-        <f>Verificări_INCHIDERE_LUNARA!E26</f>
-        <v>0</v>
-      </c>
-      <c r="E16" s="43" t="inlineStr">
-        <is>
-          <t>Se verifică dacă e sumă din decizie de impunere (analitic distinct) sau TVA neachitat din perioade precedente, omis din decont.</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="43" t="inlineStr">
-        <is>
-          <t>Check — număr de abateri</t>
-        </is>
-      </c>
-      <c r="B18" s="43">
-        <f>COUNTIF(A5:A16,"DA")</f>
-        <v>0</v>
-      </c>
-      <c r="C18" s="43" t="str">
-        <f>IF(B18=0,"OK — nicio abatere","ATENȚIE — "&amp;B18&amp;" corelații nu se potrivesc")</f>
-        <v>OK — nicio abatere</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>
--- a/dist/Module_Declarative_Fluxuri.xlsx
+++ b/dist/Module_Declarative_Fluxuri.xlsx
@@ -43767,7 +43767,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D47"/>
+  <dimension ref="A1:D48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" style="40" min="1" max="1"/>
@@ -44187,27 +44187,29 @@
       <c r="C36" s="43" t="inlineStr"/>
       <c r="D36" s="43" t="inlineStr"/>
     </row>
-    <row r="38">
-      <c r="A38" s="42" t="inlineStr">
+    <row r="37">
+      <c r="A37" s="43" t="inlineStr">
+        <is>
+          <t>1621</t>
+        </is>
+      </c>
+      <c r="B37" s="43" t="n">
+        <v>-85000</v>
+      </c>
+      <c r="C37" s="43" t="inlineStr"/>
+      <c r="D37" s="43" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="42" t="inlineStr">
         <is>
           <t>5. Continuitatea total-sumelor (doar la preluare)</t>
         </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="43" t="inlineStr">
-        <is>
-          <t>Total sume DEBITOARE, balanța lunii anterioare</t>
-        </is>
-      </c>
-      <c r="B39" s="64" t="n">
-        <v>2450000</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="43" t="inlineStr">
         <is>
-          <t>Total sume CREDITOARE, balanța lunii anterioare</t>
+          <t>Total sume DEBITOARE, balanța lunii anterioare</t>
         </is>
       </c>
       <c r="B40" s="64" t="n">
@@ -44217,60 +44219,70 @@
     <row r="41">
       <c r="A41" s="43" t="inlineStr">
         <is>
-          <t>Total sume DEBITOARE, luna curentă</t>
+          <t>Total sume CREDITOARE, balanța lunii anterioare</t>
         </is>
       </c>
       <c r="B41" s="64" t="n">
-        <v>2780000</v>
+        <v>2450000</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="43" t="inlineStr">
         <is>
-          <t>Total sume CREDITOARE, luna curentă</t>
+          <t>Total sume DEBITOARE, luna curentă</t>
         </is>
       </c>
       <c r="B42" s="64" t="n">
         <v>2780000</v>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" s="42" t="inlineStr">
+    <row r="43">
+      <c r="A43" s="43" t="inlineStr">
+        <is>
+          <t>Total sume CREDITOARE, luna curentă</t>
+        </is>
+      </c>
+      <c r="B43" s="64" t="n">
+        <v>2780000</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="42" t="inlineStr">
         <is>
           <t>6. Control</t>
         </is>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" s="43" t="inlineStr">
+    <row r="46">
+      <c r="A46" s="43" t="inlineStr">
         <is>
           <t>Modul activ?</t>
         </is>
       </c>
-      <c r="B45" s="43" t="str">
+      <c r="B46" s="43" t="str">
         <f>IF(INDEX(CatalogModule!$A$1:$A$200,MATCH("MOD_CONTROL_BALANTA",CatalogModule!$B$1:$B$200,0))="DA","ACTIV","INACTIV")</f>
         <v>ACTIV</v>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" s="43" t="inlineStr">
-        <is>
-          <t>Cauza cea mai frecventă a diferenței analitic ↔ sintetic</t>
-        </is>
-      </c>
-      <c r="B46" s="43" t="inlineStr">
-        <is>
-          <t>O operațiune făcută DUPĂ închiderea de lună, fără refacerea închiderii. Programul te lasă, iar diferența nu se anunță singură.</t>
-        </is>
-      </c>
-    </row>
     <row r="47">
       <c r="A47" s="43" t="inlineStr">
         <is>
+          <t>Cauza cea mai frecventă a diferenței analitic ↔ sintetic</t>
+        </is>
+      </c>
+      <c r="B47" s="43" t="inlineStr">
+        <is>
+          <t>O operațiune făcută DUPĂ închiderea de lună, fără refacerea închiderii. Programul te lasă, iar diferența nu se anunță singură.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="43" t="inlineStr">
+        <is>
           <t>Ordinea de verificare</t>
         </is>
       </c>
-      <c r="B47" s="43" t="inlineStr">
+      <c r="B48" s="43" t="inlineStr">
         <is>
           <t>Tabelul A din Reguli e ordonat după cât de mult strică eroarea, nu după simbolul contului — cum a cerut formatorul la finalul ședinței.</t>
         </is>
@@ -44287,7 +44299,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D46"/>
+  <dimension ref="A1:D47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" style="40" min="1" max="1"/>
@@ -44698,105 +44710,105 @@
       </c>
       <c r="D26" s="43" t="inlineStr"/>
     </row>
-    <row r="28">
-      <c r="A28" s="42" t="inlineStr">
+    <row r="27">
+      <c r="A27" s="43" t="inlineStr">
+        <is>
+          <t>1621</t>
+        </is>
+      </c>
+      <c r="B27" s="43" t="inlineStr">
+        <is>
+          <t>Pasiv</t>
+        </is>
+      </c>
+      <c r="C27" s="43" t="inlineStr">
+        <is>
+          <t>Creditor</t>
+        </is>
+      </c>
+      <c r="D27" s="43" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="42" t="inlineStr">
         <is>
           <t>Tabelul C — LIMITĂRI DECLARATE</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="44" t="inlineStr">
-        <is>
-          <t>• Modulul verifică CE I SE DĂ, nu balanța însăși. Dacă ambele coloane sunt transcrise greșit în același fel, iese verde — e verificare de coerență, nu de exactitate.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="44" t="inlineStr">
         <is>
-          <t>• Lista conturilor cu analitic obligatoriu e o convenție de cabinet, nu o regulă legală. Se completează pe măsură ce apar conturi noi cu analitic.</t>
+          <t>• Modulul verifică CE I SE DĂ, nu balanța însăși. Dacă ambele coloane sunt transcrise greșit în același fel, iese verde — e verificare de coerență, nu de exactitate.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="44" t="inlineStr">
         <is>
-          <t>• Cifrele se introduc; modulul nu citește balanța din fișier. Citirea automată e sarcina următoare — vezi tabelul D.</t>
+          <t>• Lista conturilor cu analitic obligatoriu e o convenție de cabinet, nu o regulă legală. Se completează pe măsură ce apar conturi noi cu analitic.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="44" t="inlineStr">
         <is>
-          <t>• Decontul de TVA (a treia căsuță a formatorului) NU e aici: e deja implementat în MOD_INCHIDERE_LUNARA, blocul V4, corelația C-29.</t>
+          <t>• Cifrele se introduc; modulul nu citește balanța din fișier. Citirea automată e sarcina următoare — vezi tabelul D.</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="44" t="inlineStr">
         <is>
+          <t>• Decontul de TVA (a treia căsuță a formatorului) NU e aici: e deja implementat în MOD_INCHIDERE_LUNARA, blocul V4, corelația C-29.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="44" t="inlineStr">
+        <is>
           <t>• V4 se rulează doar la preluare. În restul lunilor continuitatea e dată de faptul că lucrezi în același fișier.</t>
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="42" t="inlineStr">
+    <row r="36">
+      <c r="A36" s="42" t="inlineStr">
         <is>
           <t>Tabelul D — Ce rămâne de automatizat</t>
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="65" t="inlineStr">
+    <row r="37">
+      <c r="A37" s="65" t="inlineStr">
         <is>
           <t>Pasul</t>
         </is>
       </c>
-      <c r="B36" s="65" t="inlineStr">
+      <c r="B37" s="65" t="inlineStr">
         <is>
           <t>Ce ar face</t>
         </is>
       </c>
-      <c r="C36" s="65" t="inlineStr">
+      <c r="C37" s="65" t="inlineStr">
         <is>
           <t>De ce nu e făcut încă</t>
         </is>
       </c>
-      <c r="D36" s="65" t="inlineStr"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="43" t="inlineStr">
-        <is>
-          <t>Citirea balanței</t>
-        </is>
-      </c>
-      <c r="B37" s="43" t="inlineStr">
-        <is>
-          <t>Preluarea cifrelor direct din fișierul de balanță</t>
-        </is>
-      </c>
-      <c r="C37" s="43" t="inlineStr">
-        <is>
-          <t>Formatul diferă de la un program la altul; cere o hartă pe fiecare</t>
-        </is>
-      </c>
-      <c r="D37" s="43" t="inlineStr"/>
+      <c r="D37" s="65" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="43" t="inlineStr">
         <is>
-          <t>Detectarea analiticelor</t>
+          <t>Citirea balanței</t>
         </is>
       </c>
       <c r="B38" s="43" t="inlineStr">
         <is>
-          <t>Recunoașterea automată a conturilor cu analitic</t>
+          <t>Preluarea cifrelor direct din fișierul de balanță</t>
         </is>
       </c>
       <c r="C38" s="43" t="inlineStr">
         <is>
-          <t>Cere convenția de denumire a analiticelor, care nu e uniformă</t>
+          <t>Formatul diferă de la un program la altul; cere o hartă pe fiecare</t>
         </is>
       </c>
       <c r="D38" s="43" t="inlineStr"/>
@@ -44804,83 +44816,101 @@
     <row r="39">
       <c r="A39" s="43" t="inlineStr">
         <is>
+          <t>Detectarea analiticelor</t>
+        </is>
+      </c>
+      <c r="B39" s="43" t="inlineStr">
+        <is>
+          <t>Recunoașterea automată a conturilor cu analitic</t>
+        </is>
+      </c>
+      <c r="C39" s="43" t="inlineStr">
+        <is>
+          <t>Cere convenția de denumire a analiticelor, care nu e uniformă</t>
+        </is>
+      </c>
+      <c r="D39" s="43" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="43" t="inlineStr">
+        <is>
           <t>Localizarea diferenței</t>
         </is>
       </c>
-      <c r="B39" s="43" t="inlineStr">
+      <c r="B40" s="43" t="inlineStr">
         <is>
           <t>Nu doar CĂ diferă, ci pe ce analitic</t>
         </is>
       </c>
-      <c r="C39" s="43" t="inlineStr">
+      <c r="C40" s="43" t="inlineStr">
         <is>
           <t>Cere balanța analitică rând cu rând, nu doar totalul</t>
         </is>
       </c>
-      <c r="D39" s="43" t="inlineStr"/>
-    </row>
-    <row r="41">
-      <c r="A41" s="42" t="inlineStr">
+      <c r="D40" s="43" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="42" t="inlineStr">
         <is>
           <t>Temei legal</t>
         </is>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" s="65" t="inlineStr">
+    <row r="43">
+      <c r="A43" s="65" t="inlineStr">
         <is>
           <t>Ce se sprijină pe el</t>
         </is>
       </c>
-      <c r="B42" s="65" t="inlineStr">
+      <c r="B43" s="65" t="inlineStr">
         <is>
           <t>Temei</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="43" t="inlineStr">
-        <is>
-          <t>Contabilitatea analitică se ține obligatoriu, în dezvoltarea celei sintetice</t>
-        </is>
-      </c>
-      <c r="B43" s="43" t="inlineStr">
-        <is>
-          <t>Legea contabilității 82/1991, art. 2 alin. (1)</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="43" t="inlineStr">
         <is>
-          <t>Balanța de verificare are rolul de a controla exactitatea înregistrărilor și concordanța dintre contabilitatea sintetică și cea analitică</t>
+          <t>Contabilitatea analitică se ține obligatoriu, în dezvoltarea celei sintetice</t>
         </is>
       </c>
       <c r="B44" s="43" t="inlineStr">
         <is>
-          <t>Legea 82/1991, art. 22 — chiar rostul declarat al balanței</t>
+          <t>Legea contabilității 82/1991, art. 2 alin. (1)</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="43" t="inlineStr">
         <is>
-          <t>Registrele obligatorii: registrul-jurnal, registrul-inventar și Cartea mare</t>
+          <t>Balanța de verificare are rolul de a controla exactitatea înregistrărilor și concordanța dintre contabilitatea sintetică și cea analitică</t>
         </is>
       </c>
       <c r="B45" s="43" t="inlineStr">
         <is>
-          <t>Legea 82/1991, art. 20</t>
+          <t>Legea 82/1991, art. 22 — chiar rostul declarat al balanței</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="43" t="inlineStr">
         <is>
+          <t>Registrele obligatorii: registrul-jurnal, registrul-inventar și Cartea mare</t>
+        </is>
+      </c>
+      <c r="B46" s="43" t="inlineStr">
+        <is>
+          <t>Legea 82/1991, art. 20</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="43" t="inlineStr">
+        <is>
           <t>Situațiile financiare se întocmesc pe baza balanței de verificare</t>
         </is>
       </c>
-      <c r="B46" s="43" t="inlineStr">
+      <c r="B47" s="43" t="inlineStr">
         <is>
           <t>OMFP 1802/2014, pct. 26 și 583</t>
         </is>
@@ -44897,7 +44927,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F36"/>
+  <dimension ref="A1:F37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" style="40" min="1" max="1"/>
@@ -45523,71 +45553,72 @@
         <v>OK</v>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="42" t="inlineStr">
+    <row r="29">
+      <c r="A29" s="43" t="inlineStr">
+        <is>
+          <t>C-23</t>
+        </is>
+      </c>
+      <c r="B29" s="43" t="inlineStr">
+        <is>
+          <t>1621 — Pasiv, sold normal creditor</t>
+        </is>
+      </c>
+      <c r="C29" s="43">
+        <f>Declarații_CONTROL_BALANTA!B37</f>
+        <v>-85000</v>
+      </c>
+      <c r="D29" s="43" t="inlineStr">
+        <is>
+          <t>Creditor</t>
+        </is>
+      </c>
+      <c r="E29" s="43">
+        <f>IF(Declarații_CONTROL_BALANTA!B37&gt;0,ABS(Declarații_CONTROL_BALANTA!B37),0)</f>
+        <v>0</v>
+      </c>
+      <c r="F29" s="43" t="str">
+        <f>IF(E29&lt;0.01,"OK","ATENȚIE — 1621 are sold contrar naturii: "&amp;TEXT(E29,"#,##0.00")&amp;" lei pe sensul greșit")</f>
+        <v>OK</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="42" t="inlineStr">
         <is>
           <t>V4 — continuitatea total-sumelor (la preluare)</t>
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="65" t="inlineStr">
+    <row r="32">
+      <c r="A32" s="65" t="inlineStr">
         <is>
           <t>Cod</t>
         </is>
       </c>
-      <c r="B31" s="65" t="inlineStr">
+      <c r="B32" s="65" t="inlineStr">
         <is>
           <t>Ce verifică</t>
         </is>
       </c>
-      <c r="C31" s="65" t="inlineStr">
+      <c r="C32" s="65" t="inlineStr">
         <is>
           <t>Luna anterioară</t>
         </is>
       </c>
-      <c r="D31" s="65" t="inlineStr">
+      <c r="D32" s="65" t="inlineStr">
         <is>
           <t>Luna curentă</t>
         </is>
       </c>
-      <c r="E31" s="65" t="inlineStr">
+      <c r="E32" s="65" t="inlineStr">
         <is>
           <t>Creștere</t>
         </is>
       </c>
-      <c r="F31" s="65" t="inlineStr">
+      <c r="F32" s="65" t="inlineStr">
         <is>
           <t>Verdict</t>
         </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="43" t="inlineStr">
-        <is>
-          <t>C-39</t>
-        </is>
-      </c>
-      <c r="B32" s="43" t="inlineStr">
-        <is>
-          <t>total sume debitoare cresc monoton</t>
-        </is>
-      </c>
-      <c r="C32" s="43">
-        <f>Declarații_CONTROL_BALANTA!B39</f>
-        <v>2450000</v>
-      </c>
-      <c r="D32" s="43">
-        <f>Declarații_CONTROL_BALANTA!B41</f>
-        <v>2780000</v>
-      </c>
-      <c r="E32" s="43">
-        <f>IF(Declarații_CONTROL_BALANTA!B8&lt;&gt;"DA",0,MIN(0,Declarații_CONTROL_BALANTA!B41-Declarații_CONTROL_BALANTA!B39))</f>
-        <v>0</v>
-      </c>
-      <c r="F32" s="43" t="str">
-        <f>IF(Declarații_CONTROL_BALANTA!B8&lt;&gt;"DA","— (nu e lună de preluare)",IF(E32&gt;=0,"OK — total sumele au continuitate","ATENȚIE — total sumele au SCĂZUT: s-au preluat soldurile ca sold inițial, nu total sumele. Orice verificare pe rulaj devine falsă"))</f>
-        <v>— (nu e lună de preluare)</v>
       </c>
     </row>
     <row r="33">
@@ -45598,7 +45629,7 @@
       </c>
       <c r="B33" s="43" t="inlineStr">
         <is>
-          <t>total sume creditoare cresc monoton</t>
+          <t>total sume debitoare cresc monoton</t>
         </is>
       </c>
       <c r="C33" s="43">
@@ -45618,25 +45649,53 @@
         <v>— (nu e lună de preluare)</v>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="42" t="inlineStr">
+    <row r="34">
+      <c r="A34" s="43" t="inlineStr">
+        <is>
+          <t>C-39</t>
+        </is>
+      </c>
+      <c r="B34" s="43" t="inlineStr">
+        <is>
+          <t>total sume creditoare cresc monoton</t>
+        </is>
+      </c>
+      <c r="C34" s="43">
+        <f>Declarații_CONTROL_BALANTA!B41</f>
+        <v>2450000</v>
+      </c>
+      <c r="D34" s="43">
+        <f>Declarații_CONTROL_BALANTA!B43</f>
+        <v>2780000</v>
+      </c>
+      <c r="E34" s="43">
+        <f>IF(Declarații_CONTROL_BALANTA!B8&lt;&gt;"DA",0,MIN(0,Declarații_CONTROL_BALANTA!B43-Declarații_CONTROL_BALANTA!B41))</f>
+        <v>0</v>
+      </c>
+      <c r="F34" s="43" t="str">
+        <f>IF(Declarații_CONTROL_BALANTA!B8&lt;&gt;"DA","— (nu e lună de preluare)",IF(E34&gt;=0,"OK — total sumele au continuitate","ATENȚIE — total sumele au SCĂZUT: s-au preluat soldurile ca sold inițial, nu total sumele. Orice verificare pe rulaj devine falsă"))</f>
+        <v>— (nu e lună de preluare)</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="42" t="inlineStr">
         <is>
           <t>Control final</t>
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="43" t="inlineStr">
+    <row r="37">
+      <c r="A37" s="43" t="inlineStr">
         <is>
           <t>Check — toate verificările balanței</t>
         </is>
       </c>
-      <c r="B36" s="43">
-        <f>ABS(E6)+ABS(E7)+ABS(E8)+ABS(E9)+ABS(E10)+ABS(E11)+ABS(E12)+ABS(E13)+ABS(E17)+ABS(E21)+ABS(E22)+ABS(E23)+ABS(E24)+ABS(E25)+ABS(E26)+ABS(E27)+ABS(E28)+ABS(E32)+ABS(E33)</f>
+      <c r="B37" s="43">
+        <f>ABS(E6)+ABS(E7)+ABS(E8)+ABS(E9)+ABS(E10)+ABS(E11)+ABS(E12)+ABS(E13)+ABS(E17)+ABS(E21)+ABS(E22)+ABS(E23)+ABS(E24)+ABS(E25)+ABS(E26)+ABS(E27)+ABS(E28)+ABS(E29)+ABS(E33)+ABS(E34)</f>
         <v>0</v>
       </c>
-      <c r="C36" s="43" t="str">
-        <f>IF(ABS(B36)&lt;0.01,"OK — balanța e coerentă pe toate verificările","EROARE — vezi foaia Abateri")</f>
+      <c r="C37" s="43" t="str">
+        <f>IF(ABS(B37)&lt;0.01,"OK — balanța e coerentă pe toate verificările","EROARE — vezi foaia Abateri")</f>
         <v>OK — balanța e coerentă pe toate verificările</v>
       </c>
     </row>
@@ -45651,7 +45710,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E25"/>
+  <dimension ref="A1:E26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" style="40" min="1" max="1"/>
@@ -46129,26 +46188,26 @@
     </row>
     <row r="22">
       <c r="A22" s="43" t="str">
-        <f>IF(ABS(Verificări_CONTROL_BALANTA!E32)&lt;0.01,"NU","DA")</f>
+        <f>IF(ABS(Verificări_CONTROL_BALANTA!E29)&lt;0.01,"NU","DA")</f>
         <v>NU</v>
       </c>
       <c r="B22" s="43" t="inlineStr">
         <is>
-          <t>C-39</t>
+          <t>C-23</t>
         </is>
       </c>
       <c r="C22" s="43" t="inlineStr">
         <is>
-          <t>total sume debitoare</t>
+          <t>1621 sens sold</t>
         </is>
       </c>
       <c r="D22" s="43">
-        <f>Verificări_CONTROL_BALANTA!E32</f>
+        <f>Verificări_CONTROL_BALANTA!E29</f>
         <v>0</v>
       </c>
       <c r="E22" s="43" t="inlineStr">
         <is>
-          <t>Se reface preluarea: se introduc TOTAL SUMELE debitoare și creditoare din balanța de preluare, nu soldurile. Altfel rulajele anului pornesc de la zero din luna preluării.</t>
+          <t>Se caută operațiunea care a răsturnat soldul. Un cont de activ cu sold creditor e cel mai des un avans neînregistrat ca avans (vezi F-415).</t>
         </is>
       </c>
     </row>
@@ -46164,7 +46223,7 @@
       </c>
       <c r="C23" s="43" t="inlineStr">
         <is>
-          <t>total sume creditoare</t>
+          <t>total sume debitoare</t>
         </is>
       </c>
       <c r="D23" s="43">
@@ -46177,18 +46236,43 @@
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="43" t="inlineStr">
+    <row r="24">
+      <c r="A24" s="43" t="str">
+        <f>IF(ABS(Verificări_CONTROL_BALANTA!E34)&lt;0.01,"NU","DA")</f>
+        <v>NU</v>
+      </c>
+      <c r="B24" s="43" t="inlineStr">
+        <is>
+          <t>C-39</t>
+        </is>
+      </c>
+      <c r="C24" s="43" t="inlineStr">
+        <is>
+          <t>total sume creditoare</t>
+        </is>
+      </c>
+      <c r="D24" s="43">
+        <f>Verificări_CONTROL_BALANTA!E34</f>
+        <v>0</v>
+      </c>
+      <c r="E24" s="43" t="inlineStr">
+        <is>
+          <t>Se reface preluarea: se introduc TOTAL SUMELE debitoare și creditoare din balanța de preluare, nu soldurile. Altfel rulajele anului pornesc de la zero din luna preluării.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="43" t="inlineStr">
         <is>
           <t>Check — număr de abateri</t>
         </is>
       </c>
-      <c r="B25" s="43">
-        <f>COUNTIF(A5:A23,"DA")</f>
+      <c r="B26" s="43">
+        <f>COUNTIF(A5:A24,"DA")</f>
         <v>0</v>
       </c>
-      <c r="C25" s="43" t="str">
-        <f>IF(B25=0,"OK — nicio abatere","ATENȚIE — "&amp;B25&amp;" verificări nu trec")</f>
+      <c r="C26" s="43" t="str">
+        <f>IF(B26=0,"OK — nicio abatere","ATENȚIE — "&amp;B26&amp;" verificări nu trec")</f>
         <v>OK — nicio abatere</v>
       </c>
     </row>
